--- a/Assets/Data/Skills.xlsx
+++ b/Assets/Data/Skills.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\hibikake_unity\Assets\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{886E1454-3774-4E95-8211-AE52F568C84B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36EA1D42-7E41-4FBB-971D-BEA9849D1289}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="490" windowWidth="19420" windowHeight="11620" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Assets/Data/Skills.xlsx
+++ b/Assets/Data/Skills.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8270"/>
+    <workbookView windowWidth="19200" windowHeight="7820"/>
   </bookViews>
   <sheets>
     <sheet name="Skills" sheetId="1" r:id="rId1"/>
@@ -2433,8 +2433,39 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -2455,7 +2486,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -2469,14 +2500,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -2485,7 +2508,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -2496,14 +2519,6 @@
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -2541,29 +2556,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -2572,6 +2565,13 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -2592,19 +2592,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2616,25 +2640,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2646,7 +2652,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2670,7 +2676,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2682,31 +2730,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2718,61 +2742,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2783,15 +2783,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -2821,6 +2812,15 @@
       </top>
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -2891,7 +2891,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -2900,7 +2900,7 @@
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -2909,131 +2909,131 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="19" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="20" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="19" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="20" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="23" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="27" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3050,6 +3050,9 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -8254,7 +8257,7 @@
         <v>単体</v>
       </c>
       <c r="J10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K10">
         <v>0</v>
@@ -8336,10 +8339,10 @@
         <v>列</v>
       </c>
       <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11">
         <v>3</v>
-      </c>
-      <c r="K11">
-        <v>0</v>
       </c>
       <c r="L11">
         <v>2</v>
@@ -8418,10 +8421,10 @@
         <v>単体</v>
       </c>
       <c r="J12">
+        <v>0</v>
+      </c>
+      <c r="K12">
         <v>2</v>
-      </c>
-      <c r="K12">
-        <v>0</v>
       </c>
       <c r="L12">
         <v>2</v>
@@ -8500,10 +8503,10 @@
         <v>単体</v>
       </c>
       <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13">
         <v>3</v>
-      </c>
-      <c r="K13">
-        <v>0</v>
       </c>
       <c r="L13">
         <v>2</v>
@@ -8582,10 +8585,10 @@
         <v>単体</v>
       </c>
       <c r="J14">
+        <v>0</v>
+      </c>
+      <c r="K14">
         <v>2</v>
-      </c>
-      <c r="K14">
-        <v>0</v>
       </c>
       <c r="L14">
         <v>2</v>
@@ -8664,10 +8667,10 @@
         <v>単体</v>
       </c>
       <c r="J15">
+        <v>0</v>
+      </c>
+      <c r="K15">
         <v>3</v>
-      </c>
-      <c r="K15">
-        <v>0</v>
       </c>
       <c r="L15">
         <v>2</v>
@@ -8746,10 +8749,10 @@
         <v>単体</v>
       </c>
       <c r="J16">
+        <v>0</v>
+      </c>
+      <c r="K16">
         <v>3</v>
-      </c>
-      <c r="K16">
-        <v>0</v>
       </c>
       <c r="L16">
         <v>2</v>
@@ -8828,10 +8831,10 @@
         <v>単体</v>
       </c>
       <c r="J17">
+        <v>0</v>
+      </c>
+      <c r="K17">
         <v>2</v>
-      </c>
-      <c r="K17">
-        <v>0</v>
       </c>
       <c r="L17">
         <v>2</v>
@@ -8910,7 +8913,7 @@
         <v>単体</v>
       </c>
       <c r="J18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K18">
         <v>0</v>
@@ -8992,7 +8995,7 @@
         <v>単体</v>
       </c>
       <c r="J19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K19">
         <v>0</v>
@@ -9074,10 +9077,10 @@
         <v>単体</v>
       </c>
       <c r="J20">
+        <v>0</v>
+      </c>
+      <c r="K20">
         <v>3</v>
-      </c>
-      <c r="K20">
-        <v>0</v>
       </c>
       <c r="L20">
         <v>2</v>
@@ -9156,10 +9159,10 @@
         <v>単体</v>
       </c>
       <c r="J21">
+        <v>0</v>
+      </c>
+      <c r="K21" s="6">
         <v>3</v>
-      </c>
-      <c r="K21">
-        <v>0</v>
       </c>
       <c r="L21">
         <v>2</v>
@@ -9238,10 +9241,10 @@
         <v>単体</v>
       </c>
       <c r="J22">
+        <v>0</v>
+      </c>
+      <c r="K22">
         <v>2</v>
-      </c>
-      <c r="K22">
-        <v>0</v>
       </c>
       <c r="L22">
         <v>2</v>
@@ -9320,10 +9323,10 @@
         <v>単体</v>
       </c>
       <c r="J23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L23">
         <v>2</v>
@@ -9484,10 +9487,10 @@
         <v>単体</v>
       </c>
       <c r="J25">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L25">
         <v>2</v>
@@ -9566,10 +9569,10 @@
         <v>単体</v>
       </c>
       <c r="J26">
+        <v>0</v>
+      </c>
+      <c r="K26">
         <v>3</v>
-      </c>
-      <c r="K26">
-        <v>0</v>
       </c>
       <c r="L26">
         <v>2</v>
@@ -9648,7 +9651,7 @@
         <v>単体</v>
       </c>
       <c r="J27">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K27">
         <v>0</v>
@@ -9730,10 +9733,10 @@
         <v>単体</v>
       </c>
       <c r="J28">
+        <v>0</v>
+      </c>
+      <c r="K28">
         <v>2</v>
-      </c>
-      <c r="K28">
-        <v>0</v>
       </c>
       <c r="L28">
         <v>2</v>
@@ -9812,10 +9815,10 @@
         <v>単体</v>
       </c>
       <c r="J29">
+        <v>0</v>
+      </c>
+      <c r="K29">
         <v>4</v>
-      </c>
-      <c r="K29">
-        <v>0</v>
       </c>
       <c r="L29">
         <v>2</v>
@@ -9894,10 +9897,10 @@
         <v>単体</v>
       </c>
       <c r="J30">
+        <v>0</v>
+      </c>
+      <c r="K30">
         <v>3</v>
-      </c>
-      <c r="K30">
-        <v>0</v>
       </c>
       <c r="L30">
         <v>2</v>
@@ -9976,10 +9979,10 @@
         <v>単体</v>
       </c>
       <c r="J31">
+        <v>0</v>
+      </c>
+      <c r="K31">
         <v>4</v>
-      </c>
-      <c r="K31">
-        <v>0</v>
       </c>
       <c r="L31">
         <v>2</v>
@@ -10058,10 +10061,10 @@
         <v>単体</v>
       </c>
       <c r="J32">
+        <v>0</v>
+      </c>
+      <c r="K32">
         <v>2</v>
-      </c>
-      <c r="K32">
-        <v>0</v>
       </c>
       <c r="L32">
         <v>2</v>
@@ -10140,10 +10143,10 @@
         <v>単体</v>
       </c>
       <c r="J33">
+        <v>0</v>
+      </c>
+      <c r="K33">
         <v>2</v>
-      </c>
-      <c r="K33">
-        <v>0</v>
       </c>
       <c r="L33">
         <v>2</v>
@@ -10222,10 +10225,10 @@
         <v>単体</v>
       </c>
       <c r="J34">
+        <v>0</v>
+      </c>
+      <c r="K34">
         <v>5</v>
-      </c>
-      <c r="K34">
-        <v>0</v>
       </c>
       <c r="L34">
         <v>2</v>
@@ -10304,7 +10307,7 @@
         <v>単体</v>
       </c>
       <c r="J35">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K35">
         <v>0</v>
@@ -10386,9 +10389,9 @@
         <v>単体</v>
       </c>
       <c r="J36">
-        <v>1</v>
-      </c>
-      <c r="K36">
+        <v>0</v>
+      </c>
+      <c r="K36" s="6">
         <v>0</v>
       </c>
       <c r="L36">
@@ -10468,10 +10471,10 @@
         <v>単体</v>
       </c>
       <c r="J37">
+        <v>0</v>
+      </c>
+      <c r="K37">
         <v>3</v>
-      </c>
-      <c r="K37">
-        <v>0</v>
       </c>
       <c r="L37">
         <v>2</v>
@@ -10550,10 +10553,10 @@
         <v>単体</v>
       </c>
       <c r="J38">
+        <v>0</v>
+      </c>
+      <c r="K38">
         <v>3</v>
-      </c>
-      <c r="K38">
-        <v>0</v>
       </c>
       <c r="L38">
         <v>2</v>
@@ -10632,10 +10635,10 @@
         <v>単体</v>
       </c>
       <c r="J39">
+        <v>0</v>
+      </c>
+      <c r="K39" s="6">
         <v>3</v>
-      </c>
-      <c r="K39">
-        <v>0</v>
       </c>
       <c r="L39">
         <v>2</v>
@@ -10714,10 +10717,10 @@
         <v>単体</v>
       </c>
       <c r="J40">
+        <v>0</v>
+      </c>
+      <c r="K40">
         <v>7</v>
-      </c>
-      <c r="K40">
-        <v>0</v>
       </c>
       <c r="L40">
         <v>2</v>
@@ -10796,10 +10799,10 @@
         <v>単体</v>
       </c>
       <c r="J41">
+        <v>0</v>
+      </c>
+      <c r="K41">
         <v>4</v>
-      </c>
-      <c r="K41">
-        <v>0</v>
       </c>
       <c r="L41">
         <v>2</v>
@@ -10878,10 +10881,10 @@
         <v>単体</v>
       </c>
       <c r="J42">
+        <v>0</v>
+      </c>
+      <c r="K42">
         <v>4</v>
-      </c>
-      <c r="K42">
-        <v>0</v>
       </c>
       <c r="L42">
         <v>2</v>
@@ -10960,7 +10963,7 @@
         <v>単体</v>
       </c>
       <c r="J43">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K43">
         <v>0</v>
@@ -11042,10 +11045,10 @@
         <v>単体</v>
       </c>
       <c r="J44">
+        <v>0</v>
+      </c>
+      <c r="K44">
         <v>5</v>
-      </c>
-      <c r="K44">
-        <v>0</v>
       </c>
       <c r="L44">
         <v>2</v>
@@ -11124,10 +11127,10 @@
         <v>単体</v>
       </c>
       <c r="J45">
+        <v>0</v>
+      </c>
+      <c r="K45">
         <v>5</v>
-      </c>
-      <c r="K45">
-        <v>0</v>
       </c>
       <c r="L45">
         <v>2</v>
@@ -11206,10 +11209,10 @@
         <v>単体</v>
       </c>
       <c r="J46">
+        <v>0</v>
+      </c>
+      <c r="K46">
         <v>3</v>
-      </c>
-      <c r="K46">
-        <v>0</v>
       </c>
       <c r="L46">
         <v>2</v>
@@ -11288,10 +11291,10 @@
         <v>単体</v>
       </c>
       <c r="J47">
+        <v>0</v>
+      </c>
+      <c r="K47" s="6">
         <v>2</v>
-      </c>
-      <c r="K47">
-        <v>0</v>
       </c>
       <c r="L47">
         <v>2</v>
@@ -11370,10 +11373,10 @@
         <v>単体</v>
       </c>
       <c r="J48">
+        <v>0</v>
+      </c>
+      <c r="K48">
         <v>3</v>
-      </c>
-      <c r="K48">
-        <v>0</v>
       </c>
       <c r="L48">
         <v>2</v>
@@ -11452,10 +11455,10 @@
         <v>単体</v>
       </c>
       <c r="J49">
+        <v>0</v>
+      </c>
+      <c r="K49">
         <v>2</v>
-      </c>
-      <c r="K49">
-        <v>0</v>
       </c>
       <c r="L49">
         <v>2</v>
@@ -11534,10 +11537,10 @@
         <v>単体</v>
       </c>
       <c r="J50">
+        <v>0</v>
+      </c>
+      <c r="K50">
         <v>2</v>
-      </c>
-      <c r="K50">
-        <v>0</v>
       </c>
       <c r="L50">
         <v>2</v>
@@ -13906,7 +13909,7 @@
       <c r="J79">
         <v>0</v>
       </c>
-      <c r="K79">
+      <c r="K79" s="6">
         <v>3</v>
       </c>
       <c r="L79">
@@ -13988,7 +13991,7 @@
       <c r="J80">
         <v>0</v>
       </c>
-      <c r="K80">
+      <c r="K80" s="6">
         <v>2</v>
       </c>
       <c r="L80">
@@ -16024,7 +16027,6 @@
       <c r="F105">
         <v>0</v>
       </c>
-      <c r="G105"/>
       <c r="H105">
         <v>1</v>
       </c>

--- a/Assets/Data/Skills.xlsx
+++ b/Assets/Data/Skills.xlsx
@@ -2412,10 +2412,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -2433,9 +2433,47 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -2443,6 +2481,28 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -2465,21 +2525,22 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -2492,49 +2553,11 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <i/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -2548,30 +2571,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -2592,13 +2592,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2616,13 +2634,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2634,25 +2646,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2670,7 +2682,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2682,67 +2742,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2754,13 +2754,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2772,7 +2772,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2783,6 +2783,45 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -2797,6 +2836,15 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -2825,54 +2873,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top style="thin">
@@ -2891,19 +2891,19 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -2912,124 +2912,124 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="20" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="20" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="27" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -8243,11 +8243,11 @@
         <v>元素</v>
       </c>
       <c r="F10">
-        <v>101</v>
+        <v>2101</v>
       </c>
       <c r="G10" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F10,[1]Animations!A:A))</f>
-        <v>FireOne1</v>
+        <v>tktk01/Fire2</v>
       </c>
       <c r="H10">
         <v>1</v>

--- a/Assets/Data/Skills.xlsx
+++ b/Assets/Data/Skills.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="7820"/>
+    <workbookView windowWidth="19200" windowHeight="7820" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="Skills" sheetId="1" r:id="rId1"/>
@@ -478,7 +478,7 @@
     <t>アクティブギフト</t>
   </si>
   <si>
-    <t>(条件)他の味方が攻撃する直前に発動
+    <t>(条件)他の味方が攻撃する際に発動
 \sのCT-/f[f,0,1]</t>
   </si>
   <si>
@@ -2412,10 +2412,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -2434,7 +2434,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -2442,33 +2442,16 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -2486,13 +2469,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
@@ -2502,23 +2478,31 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -2531,9 +2515,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -2546,16 +2529,25 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -2571,7 +2563,15 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -2592,7 +2592,109 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2604,7 +2706,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2616,13 +2730,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2634,25 +2754,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2664,115 +2766,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2783,45 +2783,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -2844,7 +2805,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -2866,6 +2827,17 @@
     <border>
       <left/>
       <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top/>
       <bottom style="double">
         <color rgb="FFFF8001"/>
@@ -2873,13 +2845,41 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
       </top>
       <bottom style="double">
-        <color theme="4"/>
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -2891,145 +2891,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="23" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>

--- a/Assets/Data/Skills.xlsx
+++ b/Assets/Data/Skills.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="7820" activeTab="4"/>
+    <workbookView windowWidth="19200" windowHeight="8270" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="Skills" sheetId="1" r:id="rId1"/>
@@ -21,14 +21,14 @@
     <externalReference r:id="rId10"/>
   </externalReferences>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Skills!$F$1:$F$205</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Skills!$F$1:$F$206</definedName>
   </definedNames>
   <calcPr calcId="144525" concurrentCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="840" uniqueCount="731">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="843" uniqueCount="734">
   <si>
     <t>Id</t>
   </si>
@@ -1216,6 +1216,13 @@
     <t>ファーストテイク</t>
   </si>
   <si>
+    <t>ヒールユニット</t>
+  </si>
+  <si>
+    <t>(条件)所持していると自動で効果を発揮
+移動するたびにHpを1回復</t>
+  </si>
+  <si>
     <t>ファイアボール+</t>
   </si>
   <si>
@@ -2405,6 +2412,9 @@
   </si>
   <si>
     <t>存在猶予を延長している</t>
+  </si>
+  <si>
+    <t>ダンジョンで移動する</t>
   </si>
 </sst>
 </file>
@@ -2412,10 +2422,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -2434,7 +2444,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -2448,6 +2458,51 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -2455,15 +2510,17 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -2493,14 +2550,6 @@
     </font>
     <font>
       <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -2509,37 +2558,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -2554,24 +2573,15 @@
     </font>
     <font>
       <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -2592,7 +2602,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2604,7 +2638,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2616,25 +2656,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2646,37 +2668,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2688,49 +2686,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2748,19 +2710,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2772,7 +2740,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2797,6 +2807,15 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -2860,15 +2879,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -2891,149 +2901,149 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="19" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="23" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3047,6 +3057,9 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
@@ -7500,7 +7513,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:X250"/>
+  <dimension ref="A1:X251"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13"/>
   <cols>
     <col min="1" max="2" width="7.63636363636364" customWidth="1"/>
@@ -7509,8 +7522,8 @@
     <col min="8" max="8" width="14.4545454545455" customWidth="1"/>
     <col min="9" max="10" width="5.54545454545455" customWidth="1"/>
     <col min="11" max="12" width="6.63636363636364" customWidth="1"/>
-    <col min="13" max="13" width="5.36363636363636" style="5" customWidth="1"/>
-    <col min="14" max="14" width="4.90909090909091" style="5" customWidth="1"/>
+    <col min="13" max="13" width="5.36363636363636" style="6" customWidth="1"/>
+    <col min="14" max="14" width="4.90909090909091" style="6" customWidth="1"/>
     <col min="15" max="15" width="4.45454545454545" customWidth="1"/>
     <col min="16" max="16" width="5.54545454545455" customWidth="1"/>
     <col min="17" max="17" width="5.18181818181818" customWidth="1"/>
@@ -9161,7 +9174,7 @@
       <c r="J21">
         <v>0</v>
       </c>
-      <c r="K21" s="6">
+      <c r="K21" s="7">
         <v>3</v>
       </c>
       <c r="L21">
@@ -10391,7 +10404,7 @@
       <c r="J36">
         <v>0</v>
       </c>
-      <c r="K36" s="6">
+      <c r="K36" s="7">
         <v>0</v>
       </c>
       <c r="L36">
@@ -10637,7 +10650,7 @@
       <c r="J39">
         <v>0</v>
       </c>
-      <c r="K39" s="6">
+      <c r="K39" s="7">
         <v>3</v>
       </c>
       <c r="L39">
@@ -11293,7 +11306,7 @@
       <c r="J47">
         <v>0</v>
       </c>
-      <c r="K47" s="6">
+      <c r="K47" s="7">
         <v>2</v>
       </c>
       <c r="L47">
@@ -13909,7 +13922,7 @@
       <c r="J79">
         <v>0</v>
       </c>
-      <c r="K79" s="6">
+      <c r="K79" s="7">
         <v>3</v>
       </c>
       <c r="L79">
@@ -13991,7 +14004,7 @@
       <c r="J80">
         <v>0</v>
       </c>
-      <c r="K80" s="6">
+      <c r="K80" s="7">
         <v>2</v>
       </c>
       <c r="L80">
@@ -21006,29 +21019,26 @@
     </row>
     <row r="166" spans="1:24">
       <c r="A166">
-        <v>401010</v>
+        <v>310010</v>
       </c>
       <c r="B166">
-        <v>401010</v>
+        <v>310010</v>
       </c>
       <c r="C166" t="str">
         <f>INDEX(TextData!B:B,MATCH(B166,TextData!A:A))</f>
-        <v>ファイアボール+</v>
+        <v>ヒールユニット</v>
       </c>
       <c r="D166">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E166" t="str">
         <f>INDEX(Define!X:X,MATCH(D166,Define!W:W))</f>
-        <v>元素</v>
+        <v>自己強化</v>
       </c>
       <c r="F166">
-        <v>101</v>
-      </c>
-      <c r="G166" t="str">
-        <f>INDEX([1]Animations!B:B,MATCH(F166,[1]Animations!A:A))</f>
-        <v>FireOne1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G166"/>
       <c r="H166">
         <v>1</v>
       </c>
@@ -21043,38 +21053,38 @@
         <v>0</v>
       </c>
       <c r="L166">
-        <v>120</v>
+        <v>220</v>
       </c>
       <c r="M166">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="N166" t="str">
         <f>INDEX(Define!E:E,MATCH(M166,Define!D:D))</f>
-        <v>炎</v>
+        <v>光</v>
       </c>
       <c r="O166">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P166" t="str">
         <f>INDEX(Define!H:H,MATCH(O166,Define!G:G))</f>
-        <v>強化</v>
+        <v>レリック</v>
       </c>
       <c r="Q166">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R166" t="str">
         <f>INDEX(Define!K:K,MATCH(Q166,Define!J:J))</f>
-        <v>自身</v>
+        <v>味方</v>
       </c>
       <c r="S166">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T166" t="str">
         <f>INDEX(Define!N:N,MATCH(S166,Define!M:M))</f>
-        <v>自身</v>
+        <v>全体</v>
       </c>
       <c r="U166">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V166">
         <v>1</v>
@@ -21088,14 +21098,14 @@
     </row>
     <row r="167" spans="1:24">
       <c r="A167">
-        <v>401020</v>
+        <v>401010</v>
       </c>
       <c r="B167">
-        <v>401020</v>
+        <v>401010</v>
       </c>
       <c r="C167" t="str">
         <f>INDEX(TextData!B:B,MATCH(B167,TextData!A:A))</f>
-        <v>バーンストーム+</v>
+        <v>ファイアボール+</v>
       </c>
       <c r="D167">
         <v>1</v>
@@ -21112,11 +21122,11 @@
         <v>FireOne1</v>
       </c>
       <c r="H167">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I167" t="str">
         <f>INDEX(Define!B:B,MATCH(H167,Define!A:A))</f>
-        <v>列</v>
+        <v>単体</v>
       </c>
       <c r="J167">
         <v>0</v>
@@ -21170,35 +21180,35 @@
     </row>
     <row r="168" spans="1:24">
       <c r="A168">
-        <v>401030</v>
+        <v>401020</v>
       </c>
       <c r="B168">
-        <v>401030</v>
+        <v>401020</v>
       </c>
       <c r="C168" t="str">
         <f>INDEX(TextData!B:B,MATCH(B168,TextData!A:A))</f>
-        <v>ヒートスタンプ+</v>
+        <v>バーンストーム+</v>
       </c>
       <c r="D168">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E168" t="str">
         <f>INDEX(Define!X:X,MATCH(D168,Define!W:W))</f>
-        <v>光</v>
+        <v>元素</v>
       </c>
       <c r="F168">
-        <v>21</v>
+        <v>101</v>
       </c>
       <c r="G168" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F168,[1]Animations!A:A))</f>
-        <v>tktk01/Magic2</v>
+        <v>FireOne1</v>
       </c>
       <c r="H168">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I168" t="str">
         <f>INDEX(Define!B:B,MATCH(H168,Define!A:A))</f>
-        <v>単体</v>
+        <v>列</v>
       </c>
       <c r="J168">
         <v>0</v>
@@ -21252,28 +21262,28 @@
     </row>
     <row r="169" spans="1:24">
       <c r="A169">
-        <v>401040</v>
+        <v>401030</v>
       </c>
       <c r="B169">
-        <v>401040</v>
+        <v>401030</v>
       </c>
       <c r="C169" t="str">
         <f>INDEX(TextData!B:B,MATCH(B169,TextData!A:A))</f>
-        <v>ソードアダプト+</v>
+        <v>ヒートスタンプ+</v>
       </c>
       <c r="D169">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E169" t="str">
         <f>INDEX(Define!X:X,MATCH(D169,Define!W:W))</f>
-        <v>精神</v>
+        <v>光</v>
       </c>
       <c r="F169">
-        <v>51</v>
+        <v>21</v>
       </c>
       <c r="G169" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F169,[1]Animations!A:A))</f>
-        <v>NA_Effekseer/NA_aura_001</v>
+        <v>tktk01/Magic2</v>
       </c>
       <c r="H169">
         <v>1</v>
@@ -21332,30 +21342,30 @@
         <v>0</v>
       </c>
     </row>
-    <row r="170" ht="12" customHeight="1" spans="1:24">
+    <row r="170" spans="1:24">
       <c r="A170">
-        <v>401050</v>
+        <v>401040</v>
       </c>
       <c r="B170">
-        <v>401050</v>
+        <v>401040</v>
       </c>
       <c r="C170" t="str">
         <f>INDEX(TextData!B:B,MATCH(B170,TextData!A:A))</f>
-        <v>フレイムレイン+</v>
+        <v>ソードアダプト+</v>
       </c>
       <c r="D170">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E170" t="str">
         <f>INDEX(Define!X:X,MATCH(D170,Define!W:W))</f>
-        <v>元素</v>
+        <v>精神</v>
       </c>
       <c r="F170">
-        <v>101</v>
+        <v>51</v>
       </c>
       <c r="G170" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F170,[1]Animations!A:A))</f>
-        <v>FireOne1</v>
+        <v>NA_Effekseer/NA_aura_001</v>
       </c>
       <c r="H170">
         <v>1</v>
@@ -21416,14 +21426,14 @@
     </row>
     <row r="171" ht="12" customHeight="1" spans="1:24">
       <c r="A171">
-        <v>401060</v>
+        <v>401050</v>
       </c>
       <c r="B171">
-        <v>401060</v>
+        <v>401050</v>
       </c>
       <c r="C171" t="str">
         <f>INDEX(TextData!B:B,MATCH(B171,TextData!A:A))</f>
-        <v>イクスティンクション+</v>
+        <v>フレイムレイン+</v>
       </c>
       <c r="D171">
         <v>1</v>
@@ -21498,21 +21508,21 @@
     </row>
     <row r="172" ht="12" customHeight="1" spans="1:24">
       <c r="A172">
-        <v>401070</v>
+        <v>401060</v>
       </c>
       <c r="B172">
-        <v>401070</v>
+        <v>401060</v>
       </c>
       <c r="C172" t="str">
         <f>INDEX(TextData!B:B,MATCH(B172,TextData!A:A))</f>
-        <v>バーニングソウル+</v>
+        <v>イクスティンクション+</v>
       </c>
       <c r="D172">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E172" t="str">
         <f>INDEX(Define!X:X,MATCH(D172,Define!W:W))</f>
-        <v>光</v>
+        <v>元素</v>
       </c>
       <c r="F172">
         <v>101</v>
@@ -21580,28 +21590,28 @@
     </row>
     <row r="173" ht="12" customHeight="1" spans="1:24">
       <c r="A173">
-        <v>401080</v>
+        <v>401070</v>
       </c>
       <c r="B173">
-        <v>401080</v>
+        <v>401070</v>
       </c>
       <c r="C173" t="str">
         <f>INDEX(TextData!B:B,MATCH(B173,TextData!A:A))</f>
-        <v>レイジングバウンサー+</v>
+        <v>バーニングソウル+</v>
       </c>
       <c r="D173">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E173" t="str">
         <f>INDEX(Define!X:X,MATCH(D173,Define!W:W))</f>
-        <v>元素</v>
+        <v>光</v>
       </c>
       <c r="F173">
-        <v>51</v>
+        <v>101</v>
       </c>
       <c r="G173" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F173,[1]Animations!A:A))</f>
-        <v>NA_Effekseer/NA_aura_001</v>
+        <v>FireOne1</v>
       </c>
       <c r="H173">
         <v>1</v>
@@ -21660,16 +21670,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="174" spans="1:24">
+    <row r="174" ht="12" customHeight="1" spans="1:24">
       <c r="A174">
-        <v>402010</v>
+        <v>401080</v>
       </c>
       <c r="B174">
-        <v>402010</v>
+        <v>401080</v>
       </c>
       <c r="C174" t="str">
         <f>INDEX(TextData!B:B,MATCH(B174,TextData!A:A))</f>
-        <v>ディスチャージ+</v>
+        <v>レイジングバウンサー+</v>
       </c>
       <c r="D174">
         <v>1</v>
@@ -21679,11 +21689,11 @@
         <v>元素</v>
       </c>
       <c r="F174">
-        <v>201</v>
+        <v>51</v>
       </c>
       <c r="G174" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F174,[1]Animations!A:A))</f>
-        <v>ThunderOne1</v>
+        <v>NA_Effekseer/NA_aura_001</v>
       </c>
       <c r="H174">
         <v>1</v>
@@ -21702,11 +21712,11 @@
         <v>120</v>
       </c>
       <c r="M174">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N174" t="str">
         <f>INDEX(Define!E:E,MATCH(M174,Define!D:D))</f>
-        <v>雷</v>
+        <v>炎</v>
       </c>
       <c r="O174">
         <v>6</v>
@@ -21744,28 +21754,28 @@
     </row>
     <row r="175" spans="1:24">
       <c r="A175">
-        <v>402020</v>
+        <v>402010</v>
       </c>
       <c r="B175">
-        <v>402020</v>
+        <v>402010</v>
       </c>
       <c r="C175" t="str">
         <f>INDEX(TextData!B:B,MATCH(B175,TextData!A:A))</f>
-        <v>イベイドコード+</v>
+        <v>ディスチャージ+</v>
       </c>
       <c r="D175">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E175" t="str">
         <f>INDEX(Define!X:X,MATCH(D175,Define!W:W))</f>
-        <v>精神</v>
+        <v>元素</v>
       </c>
       <c r="F175">
-        <v>51</v>
+        <v>201</v>
       </c>
       <c r="G175" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F175,[1]Animations!A:A))</f>
-        <v>NA_Effekseer/NA_aura_001</v>
+        <v>ThunderOne1</v>
       </c>
       <c r="H175">
         <v>1</v>
@@ -21826,28 +21836,28 @@
     </row>
     <row r="176" spans="1:24">
       <c r="A176">
-        <v>402030</v>
+        <v>402020</v>
       </c>
       <c r="B176">
-        <v>402030</v>
+        <v>402020</v>
       </c>
       <c r="C176" t="str">
         <f>INDEX(TextData!B:B,MATCH(B176,TextData!A:A))</f>
-        <v>ショックインパルス+</v>
+        <v>イベイドコード+</v>
       </c>
       <c r="D176">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E176" t="str">
         <f>INDEX(Define!X:X,MATCH(D176,Define!W:W))</f>
-        <v>理術</v>
+        <v>精神</v>
       </c>
       <c r="F176">
-        <v>201</v>
+        <v>51</v>
       </c>
       <c r="G176" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F176,[1]Animations!A:A))</f>
-        <v>ThunderOne1</v>
+        <v>NA_Effekseer/NA_aura_001</v>
       </c>
       <c r="H176">
         <v>1</v>
@@ -21908,28 +21918,28 @@
     </row>
     <row r="177" spans="1:24">
       <c r="A177">
-        <v>402040</v>
+        <v>402030</v>
       </c>
       <c r="B177">
-        <v>402040</v>
+        <v>402030</v>
       </c>
       <c r="C177" t="str">
         <f>INDEX(TextData!B:B,MATCH(B177,TextData!A:A))</f>
-        <v>トラストチェイン+</v>
+        <v>ショックインパルス+</v>
       </c>
       <c r="D177">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E177" t="str">
         <f>INDEX(Define!X:X,MATCH(D177,Define!W:W))</f>
-        <v>元素</v>
+        <v>理術</v>
       </c>
       <c r="F177">
-        <v>51</v>
+        <v>201</v>
       </c>
       <c r="G177" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F177,[1]Animations!A:A))</f>
-        <v>NA_Effekseer/NA_aura_001</v>
+        <v>ThunderOne1</v>
       </c>
       <c r="H177">
         <v>1</v>
@@ -21990,14 +22000,14 @@
     </row>
     <row r="178" spans="1:24">
       <c r="A178">
-        <v>402050</v>
+        <v>402040</v>
       </c>
       <c r="B178">
-        <v>402050</v>
+        <v>402040</v>
       </c>
       <c r="C178" t="str">
         <f>INDEX(TextData!B:B,MATCH(B178,TextData!A:A))</f>
-        <v>スペルバニシング+</v>
+        <v>トラストチェイン+</v>
       </c>
       <c r="D178">
         <v>1</v>
@@ -22007,11 +22017,11 @@
         <v>元素</v>
       </c>
       <c r="F178">
-        <v>201</v>
+        <v>51</v>
       </c>
       <c r="G178" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F178,[1]Animations!A:A))</f>
-        <v>ThunderOne1</v>
+        <v>NA_Effekseer/NA_aura_001</v>
       </c>
       <c r="H178">
         <v>1</v>
@@ -22072,14 +22082,14 @@
     </row>
     <row r="179" spans="1:24">
       <c r="A179">
-        <v>402060</v>
+        <v>402050</v>
       </c>
       <c r="B179">
-        <v>402060</v>
+        <v>402050</v>
       </c>
       <c r="C179" t="str">
         <f>INDEX(TextData!B:B,MATCH(B179,TextData!A:A))</f>
-        <v>アーテニーストライク+</v>
+        <v>スペルバニシング+</v>
       </c>
       <c r="D179">
         <v>1</v>
@@ -22154,28 +22164,28 @@
     </row>
     <row r="180" spans="1:24">
       <c r="A180">
-        <v>402070</v>
+        <v>402060</v>
       </c>
       <c r="B180">
-        <v>402070</v>
+        <v>402060</v>
       </c>
       <c r="C180" t="str">
         <f>INDEX(TextData!B:B,MATCH(B180,TextData!A:A))</f>
-        <v>コンセントレイト+</v>
+        <v>アーテニーストライク+</v>
       </c>
       <c r="D180">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E180" t="str">
         <f>INDEX(Define!X:X,MATCH(D180,Define!W:W))</f>
-        <v>理術</v>
+        <v>元素</v>
       </c>
       <c r="F180">
-        <v>51</v>
+        <v>201</v>
       </c>
       <c r="G180" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F180,[1]Animations!A:A))</f>
-        <v>NA_Effekseer/NA_aura_001</v>
+        <v>ThunderOne1</v>
       </c>
       <c r="H180">
         <v>1</v>
@@ -22236,28 +22246,28 @@
     </row>
     <row r="181" spans="1:24">
       <c r="A181">
-        <v>402080</v>
+        <v>402070</v>
       </c>
       <c r="B181">
-        <v>402080</v>
+        <v>402070</v>
       </c>
       <c r="C181" t="str">
         <f>INDEX(TextData!B:B,MATCH(B181,TextData!A:A))</f>
-        <v>ディレイマジック+</v>
+        <v>コンセントレイト+</v>
       </c>
       <c r="D181">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E181" t="str">
         <f>INDEX(Define!X:X,MATCH(D181,Define!W:W))</f>
-        <v>超次元</v>
+        <v>理術</v>
       </c>
       <c r="F181">
-        <v>201</v>
+        <v>51</v>
       </c>
       <c r="G181" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F181,[1]Animations!A:A))</f>
-        <v>ThunderOne1</v>
+        <v>NA_Effekseer/NA_aura_001</v>
       </c>
       <c r="H181">
         <v>1</v>
@@ -22318,28 +22328,28 @@
     </row>
     <row r="182" spans="1:24">
       <c r="A182">
-        <v>403010</v>
+        <v>402080</v>
       </c>
       <c r="B182">
-        <v>403010</v>
+        <v>402080</v>
       </c>
       <c r="C182" t="str">
         <f>INDEX(TextData!B:B,MATCH(B182,TextData!A:A))</f>
-        <v>アイスブレイド+</v>
+        <v>ディレイマジック+</v>
       </c>
       <c r="D182">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E182" t="str">
         <f>INDEX(Define!X:X,MATCH(D182,Define!W:W))</f>
-        <v>元素</v>
+        <v>超次元</v>
       </c>
       <c r="F182">
-        <v>301</v>
+        <v>201</v>
       </c>
       <c r="G182" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F182,[1]Animations!A:A))</f>
-        <v>IceOne1</v>
+        <v>ThunderOne1</v>
       </c>
       <c r="H182">
         <v>1</v>
@@ -22358,11 +22368,11 @@
         <v>120</v>
       </c>
       <c r="M182">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N182" t="str">
         <f>INDEX(Define!E:E,MATCH(M182,Define!D:D))</f>
-        <v>氷</v>
+        <v>雷</v>
       </c>
       <c r="O182">
         <v>6</v>
@@ -22400,21 +22410,21 @@
     </row>
     <row r="183" spans="1:24">
       <c r="A183">
-        <v>403020</v>
+        <v>403010</v>
       </c>
       <c r="B183">
-        <v>403020</v>
+        <v>403010</v>
       </c>
       <c r="C183" t="str">
         <f>INDEX(TextData!B:B,MATCH(B183,TextData!A:A))</f>
-        <v>カウンターオーラ+</v>
+        <v>アイスブレイド+</v>
       </c>
       <c r="D183">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E183" t="str">
         <f>INDEX(Define!X:X,MATCH(D183,Define!W:W))</f>
-        <v>光</v>
+        <v>元素</v>
       </c>
       <c r="F183">
         <v>301</v>
@@ -22482,28 +22492,28 @@
     </row>
     <row r="184" spans="1:24">
       <c r="A184">
-        <v>403030</v>
+        <v>403020</v>
       </c>
       <c r="B184">
-        <v>403030</v>
+        <v>403020</v>
       </c>
       <c r="C184" t="str">
         <f>INDEX(TextData!B:B,MATCH(B184,TextData!A:A))</f>
-        <v>ラインプロテクト+</v>
+        <v>カウンターオーラ+</v>
       </c>
       <c r="D184">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E184" t="str">
         <f>INDEX(Define!X:X,MATCH(D184,Define!W:W))</f>
-        <v>精神</v>
+        <v>光</v>
       </c>
       <c r="F184">
-        <v>51</v>
+        <v>301</v>
       </c>
       <c r="G184" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F184,[1]Animations!A:A))</f>
-        <v>NA_Effekseer/NA_aura_001</v>
+        <v>IceOne1</v>
       </c>
       <c r="H184">
         <v>1</v>
@@ -22564,28 +22574,28 @@
     </row>
     <row r="185" spans="1:24">
       <c r="A185">
-        <v>403040</v>
+        <v>403030</v>
       </c>
       <c r="B185">
-        <v>403040</v>
+        <v>403030</v>
       </c>
       <c r="C185" t="str">
         <f>INDEX(TextData!B:B,MATCH(B185,TextData!A:A))</f>
-        <v>エスコートソール+</v>
+        <v>ラインプロテクト+</v>
       </c>
       <c r="D185">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E185" t="str">
         <f>INDEX(Define!X:X,MATCH(D185,Define!W:W))</f>
-        <v>理術</v>
+        <v>精神</v>
       </c>
       <c r="F185">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="G185" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F185,[1]Animations!A:A))</f>
-        <v>NA_Effekseer/NA_aura_002</v>
+        <v>NA_Effekseer/NA_aura_001</v>
       </c>
       <c r="H185">
         <v>1</v>
@@ -22646,14 +22656,14 @@
     </row>
     <row r="186" spans="1:24">
       <c r="A186">
-        <v>403050</v>
+        <v>403040</v>
       </c>
       <c r="B186">
-        <v>403050</v>
+        <v>403040</v>
       </c>
       <c r="C186" t="str">
         <f>INDEX(TextData!B:B,MATCH(B186,TextData!A:A))</f>
-        <v>ディープフリーズ+</v>
+        <v>エスコートソール+</v>
       </c>
       <c r="D186">
         <v>3</v>
@@ -22663,11 +22673,11 @@
         <v>理術</v>
       </c>
       <c r="F186">
-        <v>301</v>
+        <v>61</v>
       </c>
       <c r="G186" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F186,[1]Animations!A:A))</f>
-        <v>IceOne1</v>
+        <v>NA_Effekseer/NA_aura_002</v>
       </c>
       <c r="H186">
         <v>1</v>
@@ -22728,14 +22738,14 @@
     </row>
     <row r="187" spans="1:24">
       <c r="A187">
-        <v>403060</v>
+        <v>403050</v>
       </c>
       <c r="B187">
-        <v>403060</v>
+        <v>403050</v>
       </c>
       <c r="C187" t="str">
         <f>INDEX(TextData!B:B,MATCH(B187,TextData!A:A))</f>
-        <v>バブルブロウ+</v>
+        <v>ディープフリーズ+</v>
       </c>
       <c r="D187">
         <v>3</v>
@@ -22810,28 +22820,28 @@
     </row>
     <row r="188" spans="1:24">
       <c r="A188">
-        <v>403070</v>
+        <v>403060</v>
       </c>
       <c r="B188">
-        <v>403070</v>
+        <v>403060</v>
       </c>
       <c r="C188" t="str">
         <f>INDEX(TextData!B:B,MATCH(B188,TextData!A:A))</f>
-        <v>アクアミラージュ+</v>
+        <v>バブルブロウ+</v>
       </c>
       <c r="D188">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E188" t="str">
         <f>INDEX(Define!X:X,MATCH(D188,Define!W:W))</f>
-        <v>精神</v>
+        <v>理術</v>
       </c>
       <c r="F188">
-        <v>51</v>
+        <v>301</v>
       </c>
       <c r="G188" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F188,[1]Animations!A:A))</f>
-        <v>NA_Effekseer/NA_aura_001</v>
+        <v>IceOne1</v>
       </c>
       <c r="H188">
         <v>1</v>
@@ -22892,14 +22902,14 @@
     </row>
     <row r="189" spans="1:24">
       <c r="A189">
-        <v>403080</v>
+        <v>403070</v>
       </c>
       <c r="B189">
-        <v>403080</v>
+        <v>403070</v>
       </c>
       <c r="C189" t="str">
         <f>INDEX(TextData!B:B,MATCH(B189,TextData!A:A))</f>
-        <v>フロストシールド+</v>
+        <v>アクアミラージュ+</v>
       </c>
       <c r="D189">
         <v>4</v>
@@ -22972,30 +22982,30 @@
         <v>0</v>
       </c>
     </row>
-    <row r="190" ht="12" customHeight="1" spans="1:24">
+    <row r="190" spans="1:24">
       <c r="A190">
-        <v>404010</v>
+        <v>403080</v>
       </c>
       <c r="B190">
-        <v>404010</v>
+        <v>403080</v>
       </c>
       <c r="C190" t="str">
         <f>INDEX(TextData!B:B,MATCH(B190,TextData!A:A))</f>
-        <v>セイントレーザー+</v>
+        <v>フロストシールド+</v>
       </c>
       <c r="D190">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E190" t="str">
         <f>INDEX(Define!X:X,MATCH(D190,Define!W:W))</f>
-        <v>元素</v>
+        <v>精神</v>
       </c>
       <c r="F190">
-        <v>401</v>
+        <v>51</v>
       </c>
       <c r="G190" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F190,[1]Animations!A:A))</f>
-        <v>LightOne1</v>
+        <v>NA_Effekseer/NA_aura_001</v>
       </c>
       <c r="H190">
         <v>1</v>
@@ -23014,11 +23024,11 @@
         <v>120</v>
       </c>
       <c r="M190">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N190" t="str">
         <f>INDEX(Define!E:E,MATCH(M190,Define!D:D))</f>
-        <v>光</v>
+        <v>氷</v>
       </c>
       <c r="O190">
         <v>6</v>
@@ -23056,14 +23066,14 @@
     </row>
     <row r="191" ht="12" customHeight="1" spans="1:24">
       <c r="A191">
-        <v>404020</v>
+        <v>404010</v>
       </c>
       <c r="B191">
-        <v>404020</v>
+        <v>404010</v>
       </c>
       <c r="C191" t="str">
         <f>INDEX(TextData!B:B,MATCH(B191,TextData!A:A))</f>
-        <v>ペネトレイト+</v>
+        <v>セイントレーザー+</v>
       </c>
       <c r="D191">
         <v>1</v>
@@ -23138,28 +23148,28 @@
     </row>
     <row r="192" ht="12" customHeight="1" spans="1:24">
       <c r="A192">
-        <v>404030</v>
+        <v>404020</v>
       </c>
       <c r="B192">
-        <v>404030</v>
+        <v>404020</v>
       </c>
       <c r="C192" t="str">
         <f>INDEX(TextData!B:B,MATCH(B192,TextData!A:A))</f>
-        <v>ヒーリング+</v>
+        <v>ペネトレイト+</v>
       </c>
       <c r="D192">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E192" t="str">
         <f>INDEX(Define!X:X,MATCH(D192,Define!W:W))</f>
-        <v>光</v>
+        <v>元素</v>
       </c>
       <c r="F192">
-        <v>21</v>
+        <v>401</v>
       </c>
       <c r="G192" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F192,[1]Animations!A:A))</f>
-        <v>tktk01/Magic2</v>
+        <v>LightOne1</v>
       </c>
       <c r="H192">
         <v>1</v>
@@ -23218,16 +23228,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="193" spans="1:24">
+    <row r="193" ht="12" customHeight="1" spans="1:24">
       <c r="A193">
-        <v>404040</v>
+        <v>404030</v>
       </c>
       <c r="B193">
-        <v>404040</v>
+        <v>404030</v>
       </c>
       <c r="C193" t="str">
         <f>INDEX(TextData!B:B,MATCH(B193,TextData!A:A))</f>
-        <v>リザイアフォトン+</v>
+        <v>ヒーリング+</v>
       </c>
       <c r="D193">
         <v>2</v>
@@ -23237,11 +23247,11 @@
         <v>光</v>
       </c>
       <c r="F193">
-        <v>401</v>
+        <v>21</v>
       </c>
       <c r="G193" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F193,[1]Animations!A:A))</f>
-        <v>LightOne1</v>
+        <v>tktk01/Magic2</v>
       </c>
       <c r="H193">
         <v>1</v>
@@ -23300,16 +23310,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="194" ht="12" customHeight="1" spans="1:24">
+    <row r="194" spans="1:24">
       <c r="A194">
-        <v>404050</v>
+        <v>404040</v>
       </c>
       <c r="B194">
-        <v>404050</v>
+        <v>404040</v>
       </c>
       <c r="C194" t="str">
         <f>INDEX(TextData!B:B,MATCH(B194,TextData!A:A))</f>
-        <v>べネディクション+</v>
+        <v>リザイアフォトン+</v>
       </c>
       <c r="D194">
         <v>2</v>
@@ -23319,11 +23329,11 @@
         <v>光</v>
       </c>
       <c r="F194">
-        <v>21</v>
+        <v>401</v>
       </c>
       <c r="G194" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F194,[1]Animations!A:A))</f>
-        <v>tktk01/Magic2</v>
+        <v>LightOne1</v>
       </c>
       <c r="H194">
         <v>1</v>
@@ -23382,16 +23392,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="195" spans="1:24">
+    <row r="195" ht="12" customHeight="1" spans="1:24">
       <c r="A195">
-        <v>404060</v>
+        <v>404050</v>
       </c>
       <c r="B195">
-        <v>404060</v>
+        <v>404050</v>
       </c>
       <c r="C195" t="str">
         <f>INDEX(TextData!B:B,MATCH(B195,TextData!A:A))</f>
-        <v>ホーリーグレイス+</v>
+        <v>べネディクション+</v>
       </c>
       <c r="D195">
         <v>2</v>
@@ -23466,14 +23476,14 @@
     </row>
     <row r="196" spans="1:24">
       <c r="A196">
-        <v>404070</v>
+        <v>404060</v>
       </c>
       <c r="B196">
-        <v>404070</v>
+        <v>404060</v>
       </c>
       <c r="C196" t="str">
         <f>INDEX(TextData!B:B,MATCH(B196,TextData!A:A))</f>
-        <v>キュアエール+</v>
+        <v>ホーリーグレイス+</v>
       </c>
       <c r="D196">
         <v>2</v>
@@ -23548,14 +23558,14 @@
     </row>
     <row r="197" spans="1:24">
       <c r="A197">
-        <v>404080</v>
+        <v>404070</v>
       </c>
       <c r="B197">
-        <v>404080</v>
+        <v>404070</v>
       </c>
       <c r="C197" t="str">
         <f>INDEX(TextData!B:B,MATCH(B197,TextData!A:A))</f>
-        <v>ラインバリア+</v>
+        <v>キュアエール+</v>
       </c>
       <c r="D197">
         <v>2</v>
@@ -23565,11 +23575,11 @@
         <v>光</v>
       </c>
       <c r="F197">
-        <v>51</v>
+        <v>21</v>
       </c>
       <c r="G197" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F197,[1]Animations!A:A))</f>
-        <v>NA_Effekseer/NA_aura_001</v>
+        <v>tktk01/Magic2</v>
       </c>
       <c r="H197">
         <v>1</v>
@@ -23628,30 +23638,30 @@
         <v>0</v>
       </c>
     </row>
-    <row r="198" ht="12" customHeight="1" spans="1:24">
+    <row r="198" spans="1:24">
       <c r="A198">
-        <v>405010</v>
+        <v>404080</v>
       </c>
       <c r="B198">
-        <v>405010</v>
+        <v>404080</v>
       </c>
       <c r="C198" t="str">
         <f>INDEX(TextData!B:B,MATCH(B198,TextData!A:A))</f>
-        <v>ダークプリズン+</v>
+        <v>ラインバリア+</v>
       </c>
       <c r="D198">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E198" t="str">
         <f>INDEX(Define!X:X,MATCH(D198,Define!W:W))</f>
-        <v>超次元</v>
+        <v>光</v>
       </c>
       <c r="F198">
-        <v>501</v>
+        <v>51</v>
       </c>
       <c r="G198" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F198,[1]Animations!A:A))</f>
-        <v>DarknessOne1</v>
+        <v>NA_Effekseer/NA_aura_001</v>
       </c>
       <c r="H198">
         <v>1</v>
@@ -23670,11 +23680,11 @@
         <v>120</v>
       </c>
       <c r="M198">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N198" t="str">
         <f>INDEX(Define!E:E,MATCH(M198,Define!D:D))</f>
-        <v>闇</v>
+        <v>光</v>
       </c>
       <c r="O198">
         <v>6</v>
@@ -23712,14 +23722,14 @@
     </row>
     <row r="199" ht="12" customHeight="1" spans="1:24">
       <c r="A199">
-        <v>405020</v>
+        <v>405010</v>
       </c>
       <c r="B199">
-        <v>405020</v>
+        <v>405010</v>
       </c>
       <c r="C199" t="str">
         <f>INDEX(TextData!B:B,MATCH(B199,TextData!A:A))</f>
-        <v>ユーサネイジア+</v>
+        <v>ダークプリズン+</v>
       </c>
       <c r="D199">
         <v>5</v>
@@ -23736,11 +23746,11 @@
         <v>DarknessOne1</v>
       </c>
       <c r="H199">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I199" t="str">
         <f>INDEX(Define!B:B,MATCH(H199,Define!A:A))</f>
-        <v>全体</v>
+        <v>単体</v>
       </c>
       <c r="J199">
         <v>0</v>
@@ -23794,14 +23804,14 @@
     </row>
     <row r="200" ht="12" customHeight="1" spans="1:24">
       <c r="A200">
-        <v>405030</v>
+        <v>405020</v>
       </c>
       <c r="B200">
-        <v>405030</v>
+        <v>405020</v>
       </c>
       <c r="C200" t="str">
         <f>INDEX(TextData!B:B,MATCH(B200,TextData!A:A))</f>
-        <v>ドレインヒール+</v>
+        <v>ユーサネイジア+</v>
       </c>
       <c r="D200">
         <v>5</v>
@@ -23818,11 +23828,11 @@
         <v>DarknessOne1</v>
       </c>
       <c r="H200">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I200" t="str">
         <f>INDEX(Define!B:B,MATCH(H200,Define!A:A))</f>
-        <v>単体</v>
+        <v>全体</v>
       </c>
       <c r="J200">
         <v>0</v>
@@ -23876,14 +23886,14 @@
     </row>
     <row r="201" ht="12" customHeight="1" spans="1:24">
       <c r="A201">
-        <v>405040</v>
+        <v>405030</v>
       </c>
       <c r="B201">
-        <v>405040</v>
+        <v>405030</v>
       </c>
       <c r="C201" t="str">
         <f>INDEX(TextData!B:B,MATCH(B201,TextData!A:A))</f>
-        <v>アビサルデスペア+</v>
+        <v>ドレインヒール+</v>
       </c>
       <c r="D201">
         <v>5</v>
@@ -23958,21 +23968,21 @@
     </row>
     <row r="202" ht="12" customHeight="1" spans="1:24">
       <c r="A202">
-        <v>405050</v>
+        <v>405040</v>
       </c>
       <c r="B202">
-        <v>405050</v>
+        <v>405040</v>
       </c>
       <c r="C202" t="str">
         <f>INDEX(TextData!B:B,MATCH(B202,TextData!A:A))</f>
-        <v>ディプラヴィティ+</v>
+        <v>アビサルデスペア+</v>
       </c>
       <c r="D202">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E202" t="str">
         <f>INDEX(Define!X:X,MATCH(D202,Define!W:W))</f>
-        <v>理術</v>
+        <v>超次元</v>
       </c>
       <c r="F202">
         <v>501</v>
@@ -24040,14 +24050,14 @@
     </row>
     <row r="203" ht="12" customHeight="1" spans="1:24">
       <c r="A203">
-        <v>405060</v>
+        <v>405050</v>
       </c>
       <c r="B203">
-        <v>405060</v>
+        <v>405050</v>
       </c>
       <c r="C203" t="str">
         <f>INDEX(TextData!B:B,MATCH(B203,TextData!A:A))</f>
-        <v>ダークネス+</v>
+        <v>ディプラヴィティ+</v>
       </c>
       <c r="D203">
         <v>3</v>
@@ -24057,11 +24067,11 @@
         <v>理術</v>
       </c>
       <c r="F203">
-        <v>61</v>
+        <v>501</v>
       </c>
       <c r="G203" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F203,[1]Animations!A:A))</f>
-        <v>NA_Effekseer/NA_aura_002</v>
+        <v>DarknessOne1</v>
       </c>
       <c r="H203">
         <v>1</v>
@@ -24122,21 +24132,21 @@
     </row>
     <row r="204" ht="12" customHeight="1" spans="1:24">
       <c r="A204">
-        <v>405070</v>
+        <v>405060</v>
       </c>
       <c r="B204">
-        <v>405070</v>
+        <v>405060</v>
       </c>
       <c r="C204" t="str">
         <f>INDEX(TextData!B:B,MATCH(B204,TextData!A:A))</f>
-        <v>シェイディークラウド+</v>
+        <v>ダークネス+</v>
       </c>
       <c r="D204">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E204" t="str">
         <f>INDEX(Define!X:X,MATCH(D204,Define!W:W))</f>
-        <v>超次元</v>
+        <v>理術</v>
       </c>
       <c r="F204">
         <v>61</v>
@@ -24204,14 +24214,14 @@
     </row>
     <row r="205" ht="12" customHeight="1" spans="1:24">
       <c r="A205">
-        <v>405080</v>
+        <v>405070</v>
       </c>
       <c r="B205">
-        <v>405080</v>
+        <v>405070</v>
       </c>
       <c r="C205" t="str">
         <f>INDEX(TextData!B:B,MATCH(B205,TextData!A:A))</f>
-        <v>ポイズンブロウ+</v>
+        <v>シェイディークラウド+</v>
       </c>
       <c r="D205">
         <v>5</v>
@@ -24221,11 +24231,11 @@
         <v>超次元</v>
       </c>
       <c r="F205">
-        <v>501</v>
+        <v>61</v>
       </c>
       <c r="G205" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F205,[1]Animations!A:A))</f>
-        <v>DarknessOne1</v>
+        <v>NA_Effekseer/NA_aura_002</v>
       </c>
       <c r="H205">
         <v>1</v>
@@ -24284,23 +24294,30 @@
         <v>0</v>
       </c>
     </row>
-    <row r="206" spans="1:24">
+    <row r="206" ht="12" customHeight="1" spans="1:24">
       <c r="A206">
-        <v>411010</v>
+        <v>405080</v>
       </c>
       <c r="B206">
-        <v>411010</v>
+        <v>405080</v>
       </c>
       <c r="C206" t="str">
         <f>INDEX(TextData!B:B,MATCH(B206,TextData!A:A))</f>
-        <v>ウルフソウル+</v>
+        <v>ポイズンブロウ+</v>
       </c>
       <c r="D206">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E206" t="str">
         <f>INDEX(Define!X:X,MATCH(D206,Define!W:W))</f>
-        <v>自己強化</v>
+        <v>超次元</v>
+      </c>
+      <c r="F206">
+        <v>501</v>
+      </c>
+      <c r="G206" t="str">
+        <f>INDEX([1]Animations!B:B,MATCH(F206,[1]Animations!A:A))</f>
+        <v>DarknessOne1</v>
       </c>
       <c r="H206">
         <v>1</v>
@@ -24316,14 +24333,14 @@
         <v>0</v>
       </c>
       <c r="L206">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="M206">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="N206" t="str">
         <f>INDEX(Define!E:E,MATCH(M206,Define!D:D))</f>
-        <v>炎</v>
+        <v>闇</v>
       </c>
       <c r="O206">
         <v>6</v>
@@ -24361,14 +24378,14 @@
     </row>
     <row r="207" spans="1:24">
       <c r="A207">
-        <v>411020</v>
+        <v>411010</v>
       </c>
       <c r="B207">
-        <v>411020</v>
+        <v>411010</v>
       </c>
       <c r="C207" t="str">
         <f>INDEX(TextData!B:B,MATCH(B207,TextData!A:A))</f>
-        <v>プリディカメント+</v>
+        <v>ウルフソウル+</v>
       </c>
       <c r="D207">
         <v>6</v>
@@ -24436,14 +24453,14 @@
     </row>
     <row r="208" spans="1:24">
       <c r="A208">
-        <v>411030</v>
+        <v>411020</v>
       </c>
       <c r="B208">
-        <v>411030</v>
+        <v>411020</v>
       </c>
       <c r="C208" t="str">
         <f>INDEX(TextData!B:B,MATCH(B208,TextData!A:A))</f>
-        <v>アサルトシフト+</v>
+        <v>プリディカメント+</v>
       </c>
       <c r="D208">
         <v>6</v>
@@ -24511,14 +24528,14 @@
     </row>
     <row r="209" spans="1:24">
       <c r="A209">
-        <v>411040</v>
+        <v>411030</v>
       </c>
       <c r="B209">
-        <v>411040</v>
+        <v>411030</v>
       </c>
       <c r="C209" t="str">
         <f>INDEX(TextData!B:B,MATCH(B209,TextData!A:A))</f>
-        <v>アクティブギフト+</v>
+        <v>アサルトシフト+</v>
       </c>
       <c r="D209">
         <v>6</v>
@@ -24586,14 +24603,14 @@
     </row>
     <row r="210" spans="1:24">
       <c r="A210">
-        <v>411050</v>
+        <v>411040</v>
       </c>
       <c r="B210">
-        <v>411050</v>
+        <v>411040</v>
       </c>
       <c r="C210" t="str">
         <f>INDEX(TextData!B:B,MATCH(B210,TextData!A:A))</f>
-        <v>イグナイテッド+</v>
+        <v>アクティブギフト+</v>
       </c>
       <c r="D210">
         <v>6</v>
@@ -24661,14 +24678,14 @@
     </row>
     <row r="211" spans="1:24">
       <c r="A211">
-        <v>411060</v>
+        <v>411050</v>
       </c>
       <c r="B211">
-        <v>411060</v>
+        <v>411050</v>
       </c>
       <c r="C211" t="str">
         <f>INDEX(TextData!B:B,MATCH(B211,TextData!A:A))</f>
-        <v>ライジングファイア+</v>
+        <v>イグナイテッド+</v>
       </c>
       <c r="D211">
         <v>6</v>
@@ -24691,7 +24708,7 @@
         <v>0</v>
       </c>
       <c r="L211">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="M211">
         <v>1</v>
@@ -24736,14 +24753,14 @@
     </row>
     <row r="212" spans="1:24">
       <c r="A212">
-        <v>411070</v>
+        <v>411060</v>
       </c>
       <c r="B212">
-        <v>411070</v>
+        <v>411060</v>
       </c>
       <c r="C212" t="str">
         <f>INDEX(TextData!B:B,MATCH(B212,TextData!A:A))</f>
-        <v>ルージュバック+</v>
+        <v>ライジングファイア+</v>
       </c>
       <c r="D212">
         <v>6</v>
@@ -24811,14 +24828,14 @@
     </row>
     <row r="213" spans="1:24">
       <c r="A213">
-        <v>411080</v>
+        <v>411070</v>
       </c>
       <c r="B213">
-        <v>411080</v>
+        <v>411070</v>
       </c>
       <c r="C213" t="str">
         <f>INDEX(TextData!B:B,MATCH(B213,TextData!A:A))</f>
-        <v>パワーエール+</v>
+        <v>ルージュバック+</v>
       </c>
       <c r="D213">
         <v>6</v>
@@ -24886,14 +24903,14 @@
     </row>
     <row r="214" spans="1:24">
       <c r="A214">
-        <v>411090</v>
+        <v>411080</v>
       </c>
       <c r="B214">
-        <v>411090</v>
+        <v>411080</v>
       </c>
       <c r="C214" t="str">
         <f>INDEX(TextData!B:B,MATCH(B214,TextData!A:A))</f>
-        <v>スレイプニル+</v>
+        <v>パワーエール+</v>
       </c>
       <c r="D214">
         <v>6</v>
@@ -24961,14 +24978,14 @@
     </row>
     <row r="215" spans="1:24">
       <c r="A215">
-        <v>412010</v>
+        <v>411090</v>
       </c>
       <c r="B215">
-        <v>412010</v>
+        <v>411090</v>
       </c>
       <c r="C215" t="str">
         <f>INDEX(TextData!B:B,MATCH(B215,TextData!A:A))</f>
-        <v>エクステンション+</v>
+        <v>スレイプニル+</v>
       </c>
       <c r="D215">
         <v>6</v>
@@ -24991,14 +25008,14 @@
         <v>0</v>
       </c>
       <c r="L215">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="M215">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N215" t="str">
         <f>INDEX(Define!E:E,MATCH(M215,Define!D:D))</f>
-        <v>雷</v>
+        <v>炎</v>
       </c>
       <c r="O215">
         <v>6</v>
@@ -25036,14 +25053,14 @@
     </row>
     <row r="216" spans="1:24">
       <c r="A216">
-        <v>412020</v>
+        <v>412010</v>
       </c>
       <c r="B216">
-        <v>412020</v>
+        <v>412010</v>
       </c>
       <c r="C216" t="str">
         <f>INDEX(TextData!B:B,MATCH(B216,TextData!A:A))</f>
-        <v>ヘブンリーラック+</v>
+        <v>エクステンション+</v>
       </c>
       <c r="D216">
         <v>6</v>
@@ -25111,14 +25128,14 @@
     </row>
     <row r="217" spans="1:24">
       <c r="A217">
-        <v>412030</v>
+        <v>412020</v>
       </c>
       <c r="B217">
-        <v>412030</v>
+        <v>412020</v>
       </c>
       <c r="C217" t="str">
         <f>INDEX(TextData!B:B,MATCH(B217,TextData!A:A))</f>
-        <v>スウィフトカレント+</v>
+        <v>ヘブンリーラック+</v>
       </c>
       <c r="D217">
         <v>6</v>
@@ -25131,7 +25148,7 @@
         <v>1</v>
       </c>
       <c r="I217" t="str">
-        <f>INDEX([2]Define!B:B,MATCH(H217,[2]Define!A:A))</f>
+        <f>INDEX(Define!B:B,MATCH(H217,Define!A:A))</f>
         <v>単体</v>
       </c>
       <c r="J217">
@@ -25186,14 +25203,14 @@
     </row>
     <row r="218" spans="1:24">
       <c r="A218">
-        <v>412040</v>
+        <v>412030</v>
       </c>
       <c r="B218">
-        <v>412040</v>
+        <v>412030</v>
       </c>
       <c r="C218" t="str">
         <f>INDEX(TextData!B:B,MATCH(B218,TextData!A:A))</f>
-        <v>イヴェイドオール+</v>
+        <v>スウィフトカレント+</v>
       </c>
       <c r="D218">
         <v>6</v>
@@ -25261,14 +25278,14 @@
     </row>
     <row r="219" spans="1:24">
       <c r="A219">
-        <v>412050</v>
+        <v>412040</v>
       </c>
       <c r="B219">
-        <v>412050</v>
+        <v>412040</v>
       </c>
       <c r="C219" t="str">
         <f>INDEX(TextData!B:B,MATCH(B219,TextData!A:A))</f>
-        <v>クイックムーブ+</v>
+        <v>イヴェイドオール+</v>
       </c>
       <c r="D219">
         <v>6</v>
@@ -25336,14 +25353,14 @@
     </row>
     <row r="220" spans="1:24">
       <c r="A220">
-        <v>412060</v>
+        <v>412050</v>
       </c>
       <c r="B220">
-        <v>412060</v>
+        <v>412050</v>
       </c>
       <c r="C220" t="str">
         <f>INDEX(TextData!B:B,MATCH(B220,TextData!A:A))</f>
-        <v>チェイスマジック+</v>
+        <v>クイックムーブ+</v>
       </c>
       <c r="D220">
         <v>6</v>
@@ -25366,7 +25383,7 @@
         <v>0</v>
       </c>
       <c r="L220">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="M220">
         <v>2</v>
@@ -25411,14 +25428,14 @@
     </row>
     <row r="221" spans="1:24">
       <c r="A221">
-        <v>412070</v>
+        <v>412060</v>
       </c>
       <c r="B221">
-        <v>412070</v>
+        <v>412060</v>
       </c>
       <c r="C221" t="str">
         <f>INDEX(TextData!B:B,MATCH(B221,TextData!A:A))</f>
-        <v>ソーサリーコネクト+</v>
+        <v>チェイスマジック+</v>
       </c>
       <c r="D221">
         <v>6</v>
@@ -25486,14 +25503,14 @@
     </row>
     <row r="222" spans="1:24">
       <c r="A222">
-        <v>412080</v>
+        <v>412070</v>
       </c>
       <c r="B222">
-        <v>412080</v>
+        <v>412070</v>
       </c>
       <c r="C222" t="str">
         <f>INDEX(TextData!B:B,MATCH(B222,TextData!A:A))</f>
-        <v>ウィンドライズ+</v>
+        <v>ソーサリーコネクト+</v>
       </c>
       <c r="D222">
         <v>6</v>
@@ -25561,14 +25578,14 @@
     </row>
     <row r="223" spans="1:24">
       <c r="A223">
-        <v>412090</v>
+        <v>412080</v>
       </c>
       <c r="B223">
-        <v>412090</v>
+        <v>412080</v>
       </c>
       <c r="C223" t="str">
         <f>INDEX(TextData!B:B,MATCH(B223,TextData!A:A))</f>
-        <v>アウトオブオーダー+</v>
+        <v>ウィンドライズ+</v>
       </c>
       <c r="D223">
         <v>6</v>
@@ -25636,14 +25653,14 @@
     </row>
     <row r="224" spans="1:24">
       <c r="A224">
-        <v>413010</v>
+        <v>412090</v>
       </c>
       <c r="B224">
-        <v>413010</v>
+        <v>412090</v>
       </c>
       <c r="C224" t="str">
         <f>INDEX(TextData!B:B,MATCH(B224,TextData!A:A))</f>
-        <v>アーマーコード+</v>
+        <v>アウトオブオーダー+</v>
       </c>
       <c r="D224">
         <v>6</v>
@@ -25666,14 +25683,14 @@
         <v>0</v>
       </c>
       <c r="L224">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="M224">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N224" t="str">
         <f>INDEX(Define!E:E,MATCH(M224,Define!D:D))</f>
-        <v>氷</v>
+        <v>雷</v>
       </c>
       <c r="O224">
         <v>6</v>
@@ -25709,16 +25726,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="225" ht="12" customHeight="1" spans="1:24">
+    <row r="225" spans="1:24">
       <c r="A225">
-        <v>413020</v>
+        <v>413010</v>
       </c>
       <c r="B225">
-        <v>413020</v>
+        <v>413010</v>
       </c>
       <c r="C225" t="str">
         <f>INDEX(TextData!B:B,MATCH(B225,TextData!A:A))</f>
-        <v>クイックバリア+</v>
+        <v>アーマーコード+</v>
       </c>
       <c r="D225">
         <v>6</v>
@@ -25731,7 +25748,7 @@
         <v>1</v>
       </c>
       <c r="I225" t="str">
-        <f>INDEX(Define!B:B,MATCH(H225,Define!A:A))</f>
+        <f>INDEX([2]Define!B:B,MATCH(H225,[2]Define!A:A))</f>
         <v>単体</v>
       </c>
       <c r="J225">
@@ -25786,14 +25803,14 @@
     </row>
     <row r="226" ht="12" customHeight="1" spans="1:24">
       <c r="A226">
-        <v>413030</v>
+        <v>413020</v>
       </c>
       <c r="B226">
-        <v>413030</v>
+        <v>413020</v>
       </c>
       <c r="C226" t="str">
         <f>INDEX(TextData!B:B,MATCH(B226,TextData!A:A))</f>
-        <v>クイックキュア+</v>
+        <v>クイックバリア+</v>
       </c>
       <c r="D226">
         <v>6</v>
@@ -25859,16 +25876,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="227" spans="1:24">
+    <row r="227" ht="12" customHeight="1" spans="1:24">
       <c r="A227">
-        <v>413040</v>
+        <v>413030</v>
       </c>
       <c r="B227">
-        <v>413040</v>
+        <v>413030</v>
       </c>
       <c r="C227" t="str">
         <f>INDEX(TextData!B:B,MATCH(B227,TextData!A:A))</f>
-        <v>セルフシールド+</v>
+        <v>クイックキュア+</v>
       </c>
       <c r="D227">
         <v>6</v>
@@ -25936,14 +25953,14 @@
     </row>
     <row r="228" spans="1:24">
       <c r="A228">
-        <v>413050</v>
+        <v>413040</v>
       </c>
       <c r="B228">
-        <v>413050</v>
+        <v>413040</v>
       </c>
       <c r="C228" t="str">
         <f>INDEX(TextData!B:B,MATCH(B228,TextData!A:A))</f>
-        <v>パッシブジャミング+</v>
+        <v>セルフシールド+</v>
       </c>
       <c r="D228">
         <v>6</v>
@@ -26011,14 +26028,14 @@
     </row>
     <row r="229" spans="1:24">
       <c r="A229">
-        <v>413060</v>
+        <v>413050</v>
       </c>
       <c r="B229">
-        <v>413060</v>
+        <v>413050</v>
       </c>
       <c r="C229" t="str">
         <f>INDEX(TextData!B:B,MATCH(B229,TextData!A:A))</f>
-        <v>サプライカバー+</v>
+        <v>パッシブジャミング+</v>
       </c>
       <c r="D229">
         <v>6</v>
@@ -26041,7 +26058,7 @@
         <v>0</v>
       </c>
       <c r="L229">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="M229">
         <v>3</v>
@@ -26086,14 +26103,14 @@
     </row>
     <row r="230" spans="1:24">
       <c r="A230">
-        <v>413070</v>
+        <v>413060</v>
       </c>
       <c r="B230">
-        <v>413070</v>
+        <v>413060</v>
       </c>
       <c r="C230" t="str">
         <f>INDEX(TextData!B:B,MATCH(B230,TextData!A:A))</f>
-        <v>アシッドラッシュ+</v>
+        <v>サプライカバー+</v>
       </c>
       <c r="D230">
         <v>6</v>
@@ -26161,14 +26178,14 @@
     </row>
     <row r="231" spans="1:24">
       <c r="A231">
-        <v>413080</v>
+        <v>413070</v>
       </c>
       <c r="B231">
-        <v>413080</v>
+        <v>413070</v>
       </c>
       <c r="C231" t="str">
         <f>INDEX(TextData!B:B,MATCH(B231,TextData!A:A))</f>
-        <v>ライフスティール+</v>
+        <v>アシッドラッシュ+</v>
       </c>
       <c r="D231">
         <v>6</v>
@@ -26236,14 +26253,14 @@
     </row>
     <row r="232" spans="1:24">
       <c r="A232">
-        <v>413090</v>
+        <v>413080</v>
       </c>
       <c r="B232">
-        <v>413090</v>
+        <v>413080</v>
       </c>
       <c r="C232" t="str">
         <f>INDEX(TextData!B:B,MATCH(B232,TextData!A:A))</f>
-        <v>アイスセイバー+</v>
+        <v>ライフスティール+</v>
       </c>
       <c r="D232">
         <v>6</v>
@@ -26309,16 +26326,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="233" ht="12" customHeight="1" spans="1:24">
+    <row r="233" spans="1:24">
       <c r="A233">
-        <v>414010</v>
+        <v>413090</v>
       </c>
       <c r="B233">
-        <v>414010</v>
+        <v>413090</v>
       </c>
       <c r="C233" t="str">
         <f>INDEX(TextData!B:B,MATCH(B233,TextData!A:A))</f>
-        <v>ディバインシールド+</v>
+        <v>アイスセイバー+</v>
       </c>
       <c r="D233">
         <v>6</v>
@@ -26341,14 +26358,14 @@
         <v>0</v>
       </c>
       <c r="L233">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="M233">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N233" t="str">
         <f>INDEX(Define!E:E,MATCH(M233,Define!D:D))</f>
-        <v>光</v>
+        <v>氷</v>
       </c>
       <c r="O233">
         <v>6</v>
@@ -26386,14 +26403,14 @@
     </row>
     <row r="234" ht="12" customHeight="1" spans="1:24">
       <c r="A234">
-        <v>414020</v>
+        <v>414010</v>
       </c>
       <c r="B234">
-        <v>414020</v>
+        <v>414010</v>
       </c>
       <c r="C234" t="str">
         <f>INDEX(TextData!B:B,MATCH(B234,TextData!A:A))</f>
-        <v>ライフディバイド+</v>
+        <v>ディバインシールド+</v>
       </c>
       <c r="D234">
         <v>6</v>
@@ -26461,14 +26478,14 @@
     </row>
     <row r="235" ht="12" customHeight="1" spans="1:24">
       <c r="A235">
-        <v>414030</v>
+        <v>414020</v>
       </c>
       <c r="B235">
-        <v>414030</v>
+        <v>414020</v>
       </c>
       <c r="C235" t="str">
         <f>INDEX(TextData!B:B,MATCH(B235,TextData!A:A))</f>
-        <v>エイミングスコープ+</v>
+        <v>ライフディバイド+</v>
       </c>
       <c r="D235">
         <v>6</v>
@@ -26536,14 +26553,14 @@
     </row>
     <row r="236" ht="12" customHeight="1" spans="1:24">
       <c r="A236">
-        <v>414040</v>
+        <v>414030</v>
       </c>
       <c r="B236">
-        <v>414040</v>
+        <v>414030</v>
       </c>
       <c r="C236" t="str">
         <f>INDEX(TextData!B:B,MATCH(B236,TextData!A:A))</f>
-        <v>リジェネレーション+</v>
+        <v>エイミングスコープ+</v>
       </c>
       <c r="D236">
         <v>6</v>
@@ -26611,14 +26628,14 @@
     </row>
     <row r="237" ht="12" customHeight="1" spans="1:24">
       <c r="A237">
-        <v>414050</v>
+        <v>414040</v>
       </c>
       <c r="B237">
-        <v>414050</v>
+        <v>414040</v>
       </c>
       <c r="C237" t="str">
         <f>INDEX(TextData!B:B,MATCH(B237,TextData!A:A))</f>
-        <v>ホープフルアイリス+</v>
+        <v>リジェネレーション+</v>
       </c>
       <c r="D237">
         <v>6</v>
@@ -26686,14 +26703,14 @@
     </row>
     <row r="238" ht="12" customHeight="1" spans="1:24">
       <c r="A238">
-        <v>414060</v>
+        <v>414050</v>
       </c>
       <c r="B238">
-        <v>414060</v>
+        <v>414050</v>
       </c>
       <c r="C238" t="str">
         <f>INDEX(TextData!B:B,MATCH(B238,TextData!A:A))</f>
-        <v>パッシブサプライ+</v>
+        <v>ホープフルアイリス+</v>
       </c>
       <c r="D238">
         <v>6</v>
@@ -26716,7 +26733,7 @@
         <v>0</v>
       </c>
       <c r="L238">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="M238">
         <v>4</v>
@@ -26761,14 +26778,14 @@
     </row>
     <row r="239" ht="12" customHeight="1" spans="1:24">
       <c r="A239">
-        <v>414070</v>
+        <v>414060</v>
       </c>
       <c r="B239">
-        <v>414070</v>
+        <v>414060</v>
       </c>
       <c r="C239" t="str">
         <f>INDEX(TextData!B:B,MATCH(B239,TextData!A:A))</f>
-        <v>ホーミングクルセイド+</v>
+        <v>パッシブサプライ+</v>
       </c>
       <c r="D239">
         <v>6</v>
@@ -26836,14 +26853,14 @@
     </row>
     <row r="240" ht="12" customHeight="1" spans="1:24">
       <c r="A240">
-        <v>414080</v>
+        <v>414070</v>
       </c>
       <c r="B240">
-        <v>414080</v>
+        <v>414070</v>
       </c>
       <c r="C240" t="str">
         <f>INDEX(TextData!B:B,MATCH(B240,TextData!A:A))</f>
-        <v>クイックヒール+</v>
+        <v>ホーミングクルセイド+</v>
       </c>
       <c r="D240">
         <v>6</v>
@@ -26911,14 +26928,14 @@
     </row>
     <row r="241" ht="12" customHeight="1" spans="1:24">
       <c r="A241">
-        <v>414090</v>
+        <v>414080</v>
       </c>
       <c r="B241">
-        <v>414090</v>
+        <v>414080</v>
       </c>
       <c r="C241" t="str">
         <f>INDEX(TextData!B:B,MATCH(B241,TextData!A:A))</f>
-        <v>リレイズ+</v>
+        <v>クイックヒール+</v>
       </c>
       <c r="D241">
         <v>6</v>
@@ -26986,14 +27003,14 @@
     </row>
     <row r="242" ht="12" customHeight="1" spans="1:24">
       <c r="A242">
-        <v>415010</v>
+        <v>414090</v>
       </c>
       <c r="B242">
-        <v>415010</v>
+        <v>414090</v>
       </c>
       <c r="C242" t="str">
         <f>INDEX(TextData!B:B,MATCH(B242,TextData!A:A))</f>
-        <v>イーグルアイ+</v>
+        <v>リレイズ+</v>
       </c>
       <c r="D242">
         <v>6</v>
@@ -27016,14 +27033,14 @@
         <v>0</v>
       </c>
       <c r="L242">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="M242">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N242" t="str">
         <f>INDEX(Define!E:E,MATCH(M242,Define!D:D))</f>
-        <v>闇</v>
+        <v>光</v>
       </c>
       <c r="O242">
         <v>6</v>
@@ -27061,14 +27078,14 @@
     </row>
     <row r="243" ht="12" customHeight="1" spans="1:24">
       <c r="A243">
-        <v>415020</v>
+        <v>415010</v>
       </c>
       <c r="B243">
-        <v>415020</v>
+        <v>415010</v>
       </c>
       <c r="C243" t="str">
         <f>INDEX(TextData!B:B,MATCH(B243,TextData!A:A))</f>
-        <v>ネヴァーエンド+</v>
+        <v>イーグルアイ+</v>
       </c>
       <c r="D243">
         <v>6</v>
@@ -27136,14 +27153,14 @@
     </row>
     <row r="244" ht="12" customHeight="1" spans="1:24">
       <c r="A244">
-        <v>415030</v>
+        <v>415020</v>
       </c>
       <c r="B244">
-        <v>415030</v>
+        <v>415020</v>
       </c>
       <c r="C244" t="str">
         <f>INDEX(TextData!B:B,MATCH(B244,TextData!A:A))</f>
-        <v>グレイブアクト+</v>
+        <v>ネヴァーエンド+</v>
       </c>
       <c r="D244">
         <v>6</v>
@@ -27211,14 +27228,14 @@
     </row>
     <row r="245" ht="12" customHeight="1" spans="1:24">
       <c r="A245">
-        <v>415040</v>
+        <v>415030</v>
       </c>
       <c r="B245">
-        <v>415040</v>
+        <v>415030</v>
       </c>
       <c r="C245" t="str">
         <f>INDEX(TextData!B:B,MATCH(B245,TextData!A:A))</f>
-        <v>スカルグラッジ+</v>
+        <v>グレイブアクト+</v>
       </c>
       <c r="D245">
         <v>6</v>
@@ -27286,14 +27303,14 @@
     </row>
     <row r="246" ht="12" customHeight="1" spans="1:24">
       <c r="A246">
-        <v>415050</v>
+        <v>415040</v>
       </c>
       <c r="B246">
-        <v>415050</v>
+        <v>415040</v>
       </c>
       <c r="C246" t="str">
         <f>INDEX(TextData!B:B,MATCH(B246,TextData!A:A))</f>
-        <v>ネガティブドレイン+</v>
+        <v>スカルグラッジ+</v>
       </c>
       <c r="D246">
         <v>6</v>
@@ -27361,14 +27378,14 @@
     </row>
     <row r="247" ht="12" customHeight="1" spans="1:24">
       <c r="A247">
-        <v>415060</v>
+        <v>415050</v>
       </c>
       <c r="B247">
-        <v>415060</v>
+        <v>415050</v>
       </c>
       <c r="C247" t="str">
         <f>INDEX(TextData!B:B,MATCH(B247,TextData!A:A))</f>
-        <v>アンデッドペイン+</v>
+        <v>ネガティブドレイン+</v>
       </c>
       <c r="D247">
         <v>6</v>
@@ -27391,7 +27408,7 @@
         <v>0</v>
       </c>
       <c r="L247">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="M247">
         <v>5</v>
@@ -27436,14 +27453,14 @@
     </row>
     <row r="248" ht="12" customHeight="1" spans="1:24">
       <c r="A248">
-        <v>415070</v>
+        <v>415060</v>
       </c>
       <c r="B248">
-        <v>415070</v>
+        <v>415060</v>
       </c>
       <c r="C248" t="str">
         <f>INDEX(TextData!B:B,MATCH(B248,TextData!A:A))</f>
-        <v>ジャックポッド+</v>
+        <v>アンデッドペイン+</v>
       </c>
       <c r="D248">
         <v>6</v>
@@ -27511,14 +27528,14 @@
     </row>
     <row r="249" ht="12" customHeight="1" spans="1:24">
       <c r="A249">
-        <v>415080</v>
+        <v>415070</v>
       </c>
       <c r="B249">
-        <v>415080</v>
+        <v>415070</v>
       </c>
       <c r="C249" t="str">
         <f>INDEX(TextData!B:B,MATCH(B249,TextData!A:A))</f>
-        <v>ヒールハント+</v>
+        <v>ジャックポッド+</v>
       </c>
       <c r="D249">
         <v>6</v>
@@ -27586,14 +27603,14 @@
     </row>
     <row r="250" ht="12" customHeight="1" spans="1:24">
       <c r="A250">
-        <v>415090</v>
+        <v>415080</v>
       </c>
       <c r="B250">
-        <v>415090</v>
+        <v>415080</v>
       </c>
       <c r="C250" t="str">
         <f>INDEX(TextData!B:B,MATCH(B250,TextData!A:A))</f>
-        <v>クイックカース+</v>
+        <v>ヒールハント+</v>
       </c>
       <c r="D250">
         <v>6</v>
@@ -27659,8 +27676,83 @@
         <v>0</v>
       </c>
     </row>
+    <row r="251" ht="12" customHeight="1" spans="1:24">
+      <c r="A251">
+        <v>415090</v>
+      </c>
+      <c r="B251">
+        <v>415090</v>
+      </c>
+      <c r="C251" t="str">
+        <f>INDEX(TextData!B:B,MATCH(B251,TextData!A:A))</f>
+        <v>クイックカース+</v>
+      </c>
+      <c r="D251">
+        <v>6</v>
+      </c>
+      <c r="E251" t="str">
+        <f>INDEX(Define!X:X,MATCH(D251,Define!W:W))</f>
+        <v>自己強化</v>
+      </c>
+      <c r="H251">
+        <v>1</v>
+      </c>
+      <c r="I251" t="str">
+        <f>INDEX(Define!B:B,MATCH(H251,Define!A:A))</f>
+        <v>単体</v>
+      </c>
+      <c r="J251">
+        <v>0</v>
+      </c>
+      <c r="K251">
+        <v>0</v>
+      </c>
+      <c r="L251">
+        <v>120</v>
+      </c>
+      <c r="M251">
+        <v>5</v>
+      </c>
+      <c r="N251" t="str">
+        <f>INDEX(Define!E:E,MATCH(M251,Define!D:D))</f>
+        <v>闇</v>
+      </c>
+      <c r="O251">
+        <v>6</v>
+      </c>
+      <c r="P251" t="str">
+        <f>INDEX(Define!H:H,MATCH(O251,Define!G:G))</f>
+        <v>強化</v>
+      </c>
+      <c r="Q251">
+        <v>4</v>
+      </c>
+      <c r="R251" t="str">
+        <f>INDEX(Define!K:K,MATCH(Q251,Define!J:J))</f>
+        <v>自身</v>
+      </c>
+      <c r="S251">
+        <v>4</v>
+      </c>
+      <c r="T251" t="str">
+        <f>INDEX(Define!N:N,MATCH(S251,Define!M:M))</f>
+        <v>自身</v>
+      </c>
+      <c r="U251">
+        <v>1</v>
+      </c>
+      <c r="V251">
+        <v>1</v>
+      </c>
+      <c r="W251">
+        <v>1</v>
+      </c>
+      <c r="X251">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="F1:F205">
+  <autoFilter ref="F1:F206">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -27672,7 +27764,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I317"/>
+  <dimension ref="A1:I318"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13"/>
   <cols>
     <col min="2" max="2" width="20" customWidth="1"/>
@@ -34568,27 +34660,27 @@
     </row>
     <row r="232" spans="1:8">
       <c r="A232">
-        <v>401010</v>
+        <v>310010</v>
       </c>
       <c r="B232" t="str">
         <f>INDEX(TextData!B:B,MATCH(A232,TextData!A:A))</f>
-        <v>ファイアボール+</v>
+        <v>ヒールユニット</v>
       </c>
       <c r="C232">
-        <v>6010</v>
+        <v>2010</v>
       </c>
       <c r="D232" t="str">
         <f>INDEX([2]Define!Q:Q,MATCH(C232,[2]Define!P:P))</f>
-        <v>指定のFeatureのParam1を増やす</v>
+        <v>Hp回復</v>
       </c>
       <c r="E232">
-        <v>1010</v>
+        <v>1</v>
       </c>
       <c r="F232">
         <v>0</v>
       </c>
       <c r="G232">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="H232">
         <v>100</v>
@@ -34596,11 +34688,11 @@
     </row>
     <row r="233" spans="1:8">
       <c r="A233">
-        <v>401020</v>
+        <v>401010</v>
       </c>
       <c r="B233" t="str">
         <f>INDEX(TextData!B:B,MATCH(A233,TextData!A:A))</f>
-        <v>バーンストーム+</v>
+        <v>ファイアボール+</v>
       </c>
       <c r="C233">
         <v>6010</v>
@@ -34610,7 +34702,7 @@
         <v>指定のFeatureのParam1を増やす</v>
       </c>
       <c r="E233">
-        <v>1020</v>
+        <v>1010</v>
       </c>
       <c r="F233">
         <v>0</v>
@@ -34624,11 +34716,11 @@
     </row>
     <row r="234" spans="1:8">
       <c r="A234">
-        <v>401030</v>
+        <v>401020</v>
       </c>
       <c r="B234" t="str">
         <f>INDEX(TextData!B:B,MATCH(A234,TextData!A:A))</f>
-        <v>ヒートスタンプ+</v>
+        <v>バーンストーム+</v>
       </c>
       <c r="C234">
         <v>6010</v>
@@ -34638,13 +34730,13 @@
         <v>指定のFeatureのParam1を増やす</v>
       </c>
       <c r="E234">
-        <v>1030</v>
+        <v>1020</v>
       </c>
       <c r="F234">
         <v>0</v>
       </c>
       <c r="G234">
-        <v>2</v>
+        <v>250</v>
       </c>
       <c r="H234">
         <v>100</v>
@@ -34652,11 +34744,11 @@
     </row>
     <row r="235" spans="1:8">
       <c r="A235">
-        <v>401040</v>
+        <v>401030</v>
       </c>
       <c r="B235" t="str">
         <f>INDEX(TextData!B:B,MATCH(A235,TextData!A:A))</f>
-        <v>ソードアダプト+</v>
+        <v>ヒートスタンプ+</v>
       </c>
       <c r="C235">
         <v>6010</v>
@@ -34666,13 +34758,13 @@
         <v>指定のFeatureのParam1を増やす</v>
       </c>
       <c r="E235">
-        <v>1040</v>
+        <v>1030</v>
       </c>
       <c r="F235">
         <v>0</v>
       </c>
       <c r="G235">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="H235">
         <v>100</v>
@@ -34680,11 +34772,11 @@
     </row>
     <row r="236" spans="1:8">
       <c r="A236">
-        <v>401050</v>
+        <v>401040</v>
       </c>
       <c r="B236" t="str">
         <f>INDEX(TextData!B:B,MATCH(A236,TextData!A:A))</f>
-        <v>フレイムレイン+</v>
+        <v>ソードアダプト+</v>
       </c>
       <c r="C236">
         <v>6010</v>
@@ -34694,13 +34786,13 @@
         <v>指定のFeatureのParam1を増やす</v>
       </c>
       <c r="E236">
-        <v>1050</v>
+        <v>1040</v>
       </c>
       <c r="F236">
         <v>0</v>
       </c>
       <c r="G236">
-        <v>60</v>
+        <v>15</v>
       </c>
       <c r="H236">
         <v>100</v>
@@ -34708,11 +34800,11 @@
     </row>
     <row r="237" spans="1:8">
       <c r="A237">
-        <v>401060</v>
+        <v>401050</v>
       </c>
       <c r="B237" t="str">
         <f>INDEX(TextData!B:B,MATCH(A237,TextData!A:A))</f>
-        <v>イクスティンクション+</v>
+        <v>フレイムレイン+</v>
       </c>
       <c r="C237">
         <v>6010</v>
@@ -34722,13 +34814,13 @@
         <v>指定のFeatureのParam1を増やす</v>
       </c>
       <c r="E237">
-        <v>1060</v>
+        <v>1050</v>
       </c>
       <c r="F237">
         <v>0</v>
       </c>
       <c r="G237">
-        <v>400</v>
+        <v>60</v>
       </c>
       <c r="H237">
         <v>100</v>
@@ -34736,27 +34828,27 @@
     </row>
     <row r="238" spans="1:8">
       <c r="A238">
-        <v>401070</v>
+        <v>401060</v>
       </c>
       <c r="B238" t="str">
         <f>INDEX(TextData!B:B,MATCH(A238,TextData!A:A))</f>
-        <v>バーニングソウル+</v>
+        <v>イクスティンクション+</v>
       </c>
       <c r="C238">
-        <v>6080</v>
+        <v>6010</v>
       </c>
       <c r="D238" t="str">
         <f>INDEX([2]Define!Q:Q,MATCH(C238,[2]Define!P:P))</f>
-        <v>指定魔法のCTリセット値を変更する</v>
+        <v>指定のFeatureのParam1を増やす</v>
       </c>
       <c r="E238">
-        <v>1070</v>
+        <v>1060</v>
       </c>
       <c r="F238">
         <v>0</v>
       </c>
       <c r="G238">
-        <v>2</v>
+        <v>400</v>
       </c>
       <c r="H238">
         <v>100</v>
@@ -34764,27 +34856,27 @@
     </row>
     <row r="239" spans="1:8">
       <c r="A239">
-        <v>401080</v>
+        <v>401070</v>
       </c>
       <c r="B239" t="str">
         <f>INDEX(TextData!B:B,MATCH(A239,TextData!A:A))</f>
-        <v>レイジングバウンサー+</v>
+        <v>バーニングソウル+</v>
       </c>
       <c r="C239">
-        <v>6030</v>
+        <v>6080</v>
       </c>
       <c r="D239" t="str">
         <f>INDEX([2]Define!Q:Q,MATCH(C239,[2]Define!P:P))</f>
-        <v>指定のFeatureのParam3を増やす</v>
+        <v>指定魔法のCTリセット値を変更する</v>
       </c>
       <c r="E239">
-        <v>1080</v>
+        <v>1070</v>
       </c>
       <c r="F239">
         <v>0</v>
       </c>
       <c r="G239">
-        <v>45</v>
+        <v>2</v>
       </c>
       <c r="H239">
         <v>100</v>
@@ -34792,27 +34884,27 @@
     </row>
     <row r="240" spans="1:8">
       <c r="A240">
-        <v>402010</v>
+        <v>401080</v>
       </c>
       <c r="B240" t="str">
         <f>INDEX(TextData!B:B,MATCH(A240,TextData!A:A))</f>
-        <v>ディスチャージ+</v>
+        <v>レイジングバウンサー+</v>
       </c>
       <c r="C240">
-        <v>6010</v>
+        <v>6030</v>
       </c>
       <c r="D240" t="str">
         <f>INDEX([2]Define!Q:Q,MATCH(C240,[2]Define!P:P))</f>
-        <v>指定のFeatureのParam1を増やす</v>
+        <v>指定のFeatureのParam3を増やす</v>
       </c>
       <c r="E240">
-        <v>2010</v>
+        <v>1080</v>
       </c>
       <c r="F240">
         <v>0</v>
       </c>
       <c r="G240">
-        <v>250</v>
+        <v>45</v>
       </c>
       <c r="H240">
         <v>100</v>
@@ -34820,27 +34912,27 @@
     </row>
     <row r="241" spans="1:8">
       <c r="A241">
-        <v>402020</v>
+        <v>402010</v>
       </c>
       <c r="B241" t="str">
         <f>INDEX(TextData!B:B,MATCH(A241,TextData!A:A))</f>
-        <v>イベイドコード+</v>
+        <v>ディスチャージ+</v>
       </c>
       <c r="C241">
-        <v>6030</v>
+        <v>6010</v>
       </c>
       <c r="D241" t="str">
         <f>INDEX([2]Define!Q:Q,MATCH(C241,[2]Define!P:P))</f>
-        <v>指定のFeatureのParam3を増やす</v>
+        <v>指定のFeatureのParam1を増やす</v>
       </c>
       <c r="E241">
-        <v>2020</v>
+        <v>2010</v>
       </c>
       <c r="F241">
         <v>0</v>
       </c>
       <c r="G241">
-        <v>25</v>
+        <v>250</v>
       </c>
       <c r="H241">
         <v>100</v>
@@ -34848,27 +34940,27 @@
     </row>
     <row r="242" spans="1:8">
       <c r="A242">
-        <v>402030</v>
+        <v>402020</v>
       </c>
       <c r="B242" t="str">
         <f>INDEX(TextData!B:B,MATCH(A242,TextData!A:A))</f>
-        <v>ショックインパルス+</v>
+        <v>イベイドコード+</v>
       </c>
       <c r="C242">
-        <v>6080</v>
+        <v>6030</v>
       </c>
       <c r="D242" t="str">
         <f>INDEX([2]Define!Q:Q,MATCH(C242,[2]Define!P:P))</f>
-        <v>指定魔法のCTリセット値を変更する</v>
+        <v>指定のFeatureのParam3を増やす</v>
       </c>
       <c r="E242">
-        <v>2030</v>
+        <v>2020</v>
       </c>
       <c r="F242">
         <v>0</v>
       </c>
       <c r="G242">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="H242">
         <v>100</v>
@@ -34876,27 +34968,27 @@
     </row>
     <row r="243" spans="1:8">
       <c r="A243">
-        <v>402040</v>
+        <v>402030</v>
       </c>
       <c r="B243" t="str">
         <f>INDEX(TextData!B:B,MATCH(A243,TextData!A:A))</f>
-        <v>トラストチェイン+</v>
+        <v>ショックインパルス+</v>
       </c>
       <c r="C243">
-        <v>6010</v>
+        <v>6080</v>
       </c>
       <c r="D243" t="str">
         <f>INDEX([2]Define!Q:Q,MATCH(C243,[2]Define!P:P))</f>
-        <v>指定のFeatureのParam1を増やす</v>
+        <v>指定魔法のCTリセット値を変更する</v>
       </c>
       <c r="E243">
-        <v>2040</v>
+        <v>2030</v>
       </c>
       <c r="F243">
         <v>0</v>
       </c>
       <c r="G243">
-        <v>400</v>
+        <v>2</v>
       </c>
       <c r="H243">
         <v>100</v>
@@ -34904,27 +34996,27 @@
     </row>
     <row r="244" spans="1:8">
       <c r="A244">
-        <v>402050</v>
+        <v>402040</v>
       </c>
       <c r="B244" t="str">
         <f>INDEX(TextData!B:B,MATCH(A244,TextData!A:A))</f>
-        <v>スペルバニシング+</v>
+        <v>トラストチェイン+</v>
       </c>
       <c r="C244">
-        <v>6080</v>
+        <v>6010</v>
       </c>
       <c r="D244" t="str">
         <f>INDEX([2]Define!Q:Q,MATCH(C244,[2]Define!P:P))</f>
-        <v>指定魔法のCTリセット値を変更する</v>
+        <v>指定のFeatureのParam1を増やす</v>
       </c>
       <c r="E244">
-        <v>2050</v>
+        <v>2040</v>
       </c>
       <c r="F244">
         <v>0</v>
       </c>
       <c r="G244">
-        <v>1</v>
+        <v>400</v>
       </c>
       <c r="H244">
         <v>100</v>
@@ -34932,27 +35024,27 @@
     </row>
     <row r="245" spans="1:8">
       <c r="A245">
-        <v>402060</v>
+        <v>402050</v>
       </c>
       <c r="B245" t="str">
         <f>INDEX(TextData!B:B,MATCH(A245,TextData!A:A))</f>
-        <v>アーテニーストライク+</v>
+        <v>スペルバニシング+</v>
       </c>
       <c r="C245">
-        <v>6010</v>
+        <v>6080</v>
       </c>
       <c r="D245" t="str">
         <f>INDEX([2]Define!Q:Q,MATCH(C245,[2]Define!P:P))</f>
-        <v>指定のFeatureのParam1を増やす</v>
+        <v>指定魔法のCTリセット値を変更する</v>
       </c>
       <c r="E245">
-        <v>2060</v>
+        <v>2050</v>
       </c>
       <c r="F245">
         <v>0</v>
       </c>
       <c r="G245">
-        <v>250</v>
+        <v>1</v>
       </c>
       <c r="H245">
         <v>100</v>
@@ -34960,27 +35052,27 @@
     </row>
     <row r="246" spans="1:8">
       <c r="A246">
-        <v>402070</v>
+        <v>402060</v>
       </c>
       <c r="B246" t="str">
         <f>INDEX(TextData!B:B,MATCH(A246,TextData!A:A))</f>
-        <v>コンセントレイト+</v>
+        <v>アーテニーストライク+</v>
       </c>
       <c r="C246">
-        <v>6030</v>
+        <v>6010</v>
       </c>
       <c r="D246" t="str">
         <f>INDEX([2]Define!Q:Q,MATCH(C246,[2]Define!P:P))</f>
-        <v>指定のFeatureのParam3を増やす</v>
+        <v>指定のFeatureのParam1を増やす</v>
       </c>
       <c r="E246">
-        <v>2070</v>
+        <v>2060</v>
       </c>
       <c r="F246">
         <v>0</v>
       </c>
       <c r="G246">
-        <v>40</v>
+        <v>250</v>
       </c>
       <c r="H246">
         <v>100</v>
@@ -34988,27 +35080,27 @@
     </row>
     <row r="247" spans="1:8">
       <c r="A247">
-        <v>402080</v>
+        <v>402070</v>
       </c>
       <c r="B247" t="str">
         <f>INDEX(TextData!B:B,MATCH(A247,TextData!A:A))</f>
-        <v>ディレイマジック+</v>
+        <v>コンセントレイト+</v>
       </c>
       <c r="C247">
-        <v>6010</v>
+        <v>6030</v>
       </c>
       <c r="D247" t="str">
         <f>INDEX([2]Define!Q:Q,MATCH(C247,[2]Define!P:P))</f>
-        <v>指定のFeatureのParam1を増やす</v>
+        <v>指定のFeatureのParam3を増やす</v>
       </c>
       <c r="E247">
-        <v>2080</v>
+        <v>2070</v>
       </c>
       <c r="F247">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G247">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="H247">
         <v>100</v>
@@ -35016,11 +35108,11 @@
     </row>
     <row r="248" spans="1:8">
       <c r="A248">
-        <v>403010</v>
+        <v>402080</v>
       </c>
       <c r="B248" t="str">
         <f>INDEX(TextData!B:B,MATCH(A248,TextData!A:A))</f>
-        <v>アイスブレイド+</v>
+        <v>ディレイマジック+</v>
       </c>
       <c r="C248">
         <v>6010</v>
@@ -35030,13 +35122,13 @@
         <v>指定のFeatureのParam1を増やす</v>
       </c>
       <c r="E248">
-        <v>3010</v>
+        <v>2080</v>
       </c>
       <c r="F248">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G248">
-        <v>250</v>
+        <v>2</v>
       </c>
       <c r="H248">
         <v>100</v>
@@ -35044,27 +35136,27 @@
     </row>
     <row r="249" spans="1:8">
       <c r="A249">
-        <v>403020</v>
+        <v>403010</v>
       </c>
       <c r="B249" t="str">
         <f>INDEX(TextData!B:B,MATCH(A249,TextData!A:A))</f>
-        <v>カウンターオーラ+</v>
+        <v>アイスブレイド+</v>
       </c>
       <c r="C249">
-        <v>6030</v>
+        <v>6010</v>
       </c>
       <c r="D249" t="str">
         <f>INDEX([2]Define!Q:Q,MATCH(C249,[2]Define!P:P))</f>
-        <v>指定のFeatureのParam3を増やす</v>
+        <v>指定のFeatureのParam1を増やす</v>
       </c>
       <c r="E249">
-        <v>3020</v>
+        <v>3010</v>
       </c>
       <c r="F249">
         <v>0</v>
       </c>
       <c r="G249">
-        <v>40</v>
+        <v>250</v>
       </c>
       <c r="H249">
         <v>100</v>
@@ -35072,11 +35164,11 @@
     </row>
     <row r="250" spans="1:8">
       <c r="A250">
-        <v>403030</v>
+        <v>403020</v>
       </c>
       <c r="B250" t="str">
         <f>INDEX(TextData!B:B,MATCH(A250,TextData!A:A))</f>
-        <v>ラインプロテクト+</v>
+        <v>カウンターオーラ+</v>
       </c>
       <c r="C250">
         <v>6030</v>
@@ -35086,13 +35178,13 @@
         <v>指定のFeatureのParam3を増やす</v>
       </c>
       <c r="E250">
-        <v>3030</v>
+        <v>3020</v>
       </c>
       <c r="F250">
         <v>0</v>
       </c>
       <c r="G250">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="H250">
         <v>100</v>
@@ -35100,11 +35192,11 @@
     </row>
     <row r="251" spans="1:8">
       <c r="A251">
-        <v>403040</v>
+        <v>403030</v>
       </c>
       <c r="B251" t="str">
         <f>INDEX(TextData!B:B,MATCH(A251,TextData!A:A))</f>
-        <v>エスコートソール+</v>
+        <v>ラインプロテクト+</v>
       </c>
       <c r="C251">
         <v>6030</v>
@@ -35114,13 +35206,13 @@
         <v>指定のFeatureのParam3を増やす</v>
       </c>
       <c r="E251">
-        <v>3040</v>
+        <v>3030</v>
       </c>
       <c r="F251">
         <v>0</v>
       </c>
       <c r="G251">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="H251">
         <v>100</v>
@@ -35128,11 +35220,11 @@
     </row>
     <row r="252" spans="1:8">
       <c r="A252">
-        <v>403050</v>
+        <v>403040</v>
       </c>
       <c r="B252" t="str">
         <f>INDEX(TextData!B:B,MATCH(A252,TextData!A:A))</f>
-        <v>ディープフリーズ+</v>
+        <v>エスコートソール+</v>
       </c>
       <c r="C252">
         <v>6030</v>
@@ -35142,7 +35234,7 @@
         <v>指定のFeatureのParam3を増やす</v>
       </c>
       <c r="E252">
-        <v>3050</v>
+        <v>3040</v>
       </c>
       <c r="F252">
         <v>0</v>
@@ -35156,11 +35248,11 @@
     </row>
     <row r="253" spans="1:8">
       <c r="A253">
-        <v>403060</v>
+        <v>403050</v>
       </c>
       <c r="B253" t="str">
         <f>INDEX(TextData!B:B,MATCH(A253,TextData!A:A))</f>
-        <v>バブルブロウ+</v>
+        <v>ディープフリーズ+</v>
       </c>
       <c r="C253">
         <v>6030</v>
@@ -35170,13 +35262,13 @@
         <v>指定のFeatureのParam3を増やす</v>
       </c>
       <c r="E253">
-        <v>3060</v>
+        <v>3050</v>
       </c>
       <c r="F253">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G253">
-        <v>12</v>
+        <v>40</v>
       </c>
       <c r="H253">
         <v>100</v>
@@ -35184,27 +35276,27 @@
     </row>
     <row r="254" spans="1:8">
       <c r="A254">
-        <v>403070</v>
+        <v>403060</v>
       </c>
       <c r="B254" t="str">
         <f>INDEX(TextData!B:B,MATCH(A254,TextData!A:A))</f>
-        <v>アクアミラージュ+</v>
+        <v>バブルブロウ+</v>
       </c>
       <c r="C254">
-        <v>6020</v>
+        <v>6030</v>
       </c>
       <c r="D254" t="str">
         <f>INDEX([2]Define!Q:Q,MATCH(C254,[2]Define!P:P))</f>
-        <v>指定のFeatureのParam2を増やす</v>
+        <v>指定のFeatureのParam3を増やす</v>
       </c>
       <c r="E254">
-        <v>3070</v>
+        <v>3060</v>
       </c>
       <c r="F254">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G254">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="H254">
         <v>100</v>
@@ -35212,27 +35304,27 @@
     </row>
     <row r="255" spans="1:8">
       <c r="A255">
-        <v>403080</v>
+        <v>403070</v>
       </c>
       <c r="B255" t="str">
         <f>INDEX(TextData!B:B,MATCH(A255,TextData!A:A))</f>
-        <v>フロストシールド+</v>
+        <v>アクアミラージュ+</v>
       </c>
       <c r="C255">
-        <v>6030</v>
+        <v>6020</v>
       </c>
       <c r="D255" t="str">
         <f>INDEX([2]Define!Q:Q,MATCH(C255,[2]Define!P:P))</f>
-        <v>指定のFeatureのParam3を増やす</v>
+        <v>指定のFeatureのParam2を増やす</v>
       </c>
       <c r="E255">
-        <v>3080</v>
+        <v>3070</v>
       </c>
       <c r="F255">
         <v>0</v>
       </c>
       <c r="G255">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="H255">
         <v>100</v>
@@ -35240,27 +35332,27 @@
     </row>
     <row r="256" spans="1:8">
       <c r="A256">
-        <v>404010</v>
+        <v>403080</v>
       </c>
       <c r="B256" t="str">
         <f>INDEX(TextData!B:B,MATCH(A256,TextData!A:A))</f>
-        <v>セイントレーザー+</v>
+        <v>フロストシールド+</v>
       </c>
       <c r="C256">
-        <v>6010</v>
+        <v>6030</v>
       </c>
       <c r="D256" t="str">
         <f>INDEX([2]Define!Q:Q,MATCH(C256,[2]Define!P:P))</f>
-        <v>指定のFeatureのParam1を増やす</v>
+        <v>指定のFeatureのParam3を増やす</v>
       </c>
       <c r="E256">
-        <v>4010</v>
+        <v>3080</v>
       </c>
       <c r="F256">
         <v>0</v>
       </c>
       <c r="G256">
-        <v>250</v>
+        <v>30</v>
       </c>
       <c r="H256">
         <v>100</v>
@@ -35268,11 +35360,11 @@
     </row>
     <row r="257" spans="1:8">
       <c r="A257">
-        <v>404020</v>
+        <v>404010</v>
       </c>
       <c r="B257" t="str">
         <f>INDEX(TextData!B:B,MATCH(A257,TextData!A:A))</f>
-        <v>ペネトレイト+</v>
+        <v>セイントレーザー+</v>
       </c>
       <c r="C257">
         <v>6010</v>
@@ -35282,7 +35374,7 @@
         <v>指定のFeatureのParam1を増やす</v>
       </c>
       <c r="E257">
-        <v>4020</v>
+        <v>4010</v>
       </c>
       <c r="F257">
         <v>0</v>
@@ -35296,27 +35388,27 @@
     </row>
     <row r="258" spans="1:8">
       <c r="A258">
-        <v>404030</v>
+        <v>404020</v>
       </c>
       <c r="B258" t="str">
         <f>INDEX(TextData!B:B,MATCH(A258,TextData!A:A))</f>
-        <v>ヒーリング+</v>
+        <v>ペネトレイト+</v>
       </c>
       <c r="C258">
-        <v>6210</v>
+        <v>6010</v>
       </c>
       <c r="D258" t="str">
         <f>INDEX([2]Define!Q:Q,MATCH(C258,[2]Define!P:P))</f>
-        <v>指定魔法の対象を変更（強化限定）</v>
+        <v>指定のFeatureのParam1を増やす</v>
       </c>
       <c r="E258">
-        <v>4030</v>
+        <v>4020</v>
       </c>
       <c r="F258">
         <v>0</v>
       </c>
       <c r="G258">
-        <v>31</v>
+        <v>250</v>
       </c>
       <c r="H258">
         <v>100</v>
@@ -35324,27 +35416,27 @@
     </row>
     <row r="259" spans="1:8">
       <c r="A259">
-        <v>404040</v>
+        <v>404030</v>
       </c>
       <c r="B259" t="str">
         <f>INDEX(TextData!B:B,MATCH(A259,TextData!A:A))</f>
-        <v>リザイアフォトン+</v>
+        <v>ヒーリング+</v>
       </c>
       <c r="C259">
-        <v>6030</v>
+        <v>6210</v>
       </c>
       <c r="D259" t="str">
         <f>INDEX([2]Define!Q:Q,MATCH(C259,[2]Define!P:P))</f>
-        <v>指定のFeatureのParam3を増やす</v>
+        <v>指定魔法の対象を変更（強化限定）</v>
       </c>
       <c r="E259">
-        <v>4040</v>
+        <v>4030</v>
       </c>
       <c r="F259">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G259">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H259">
         <v>100</v>
@@ -35352,27 +35444,27 @@
     </row>
     <row r="260" spans="1:8">
       <c r="A260">
-        <v>404050</v>
+        <v>404040</v>
       </c>
       <c r="B260" t="str">
         <f>INDEX(TextData!B:B,MATCH(A260,TextData!A:A))</f>
-        <v>べネディクション+</v>
+        <v>リザイアフォトン+</v>
       </c>
       <c r="C260">
-        <v>6080</v>
+        <v>6030</v>
       </c>
       <c r="D260" t="str">
         <f>INDEX([2]Define!Q:Q,MATCH(C260,[2]Define!P:P))</f>
-        <v>指定魔法のCTリセット値を変更する</v>
+        <v>指定のFeatureのParam3を増やす</v>
       </c>
       <c r="E260">
-        <v>4050</v>
+        <v>4040</v>
       </c>
       <c r="F260">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G260">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="H260">
         <v>100</v>
@@ -35380,11 +35472,11 @@
     </row>
     <row r="261" spans="1:8">
       <c r="A261">
-        <v>404060</v>
+        <v>404050</v>
       </c>
       <c r="B261" t="str">
         <f>INDEX(TextData!B:B,MATCH(A261,TextData!A:A))</f>
-        <v>ホーリーグレイス+</v>
+        <v>べネディクション+</v>
       </c>
       <c r="C261">
         <v>6080</v>
@@ -35394,13 +35486,13 @@
         <v>指定魔法のCTリセット値を変更する</v>
       </c>
       <c r="E261">
-        <v>4060</v>
+        <v>4050</v>
       </c>
       <c r="F261">
         <v>0</v>
       </c>
       <c r="G261">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H261">
         <v>100</v>
@@ -35408,27 +35500,27 @@
     </row>
     <row r="262" spans="1:8">
       <c r="A262">
-        <v>404070</v>
+        <v>404060</v>
       </c>
       <c r="B262" t="str">
         <f>INDEX(TextData!B:B,MATCH(A262,TextData!A:A))</f>
-        <v>キュアエール+</v>
+        <v>ホーリーグレイス+</v>
       </c>
       <c r="C262">
-        <v>6030</v>
+        <v>6080</v>
       </c>
       <c r="D262" t="str">
         <f>INDEX([2]Define!Q:Q,MATCH(C262,[2]Define!P:P))</f>
-        <v>指定のFeatureのParam3を増やす</v>
+        <v>指定魔法のCTリセット値を変更する</v>
       </c>
       <c r="E262">
-        <v>4070</v>
+        <v>4060</v>
       </c>
       <c r="F262">
         <v>0</v>
       </c>
       <c r="G262">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="H262">
         <v>100</v>
@@ -35436,27 +35528,27 @@
     </row>
     <row r="263" spans="1:8">
       <c r="A263">
-        <v>404080</v>
+        <v>404070</v>
       </c>
       <c r="B263" t="str">
         <f>INDEX(TextData!B:B,MATCH(A263,TextData!A:A))</f>
-        <v>ラインバリア+</v>
+        <v>キュアエール+</v>
       </c>
       <c r="C263">
-        <v>6080</v>
+        <v>6030</v>
       </c>
       <c r="D263" t="str">
         <f>INDEX([2]Define!Q:Q,MATCH(C263,[2]Define!P:P))</f>
-        <v>指定魔法のCTリセット値を変更する</v>
+        <v>指定のFeatureのParam3を増やす</v>
       </c>
       <c r="E263">
-        <v>4080</v>
+        <v>4070</v>
       </c>
       <c r="F263">
         <v>0</v>
       </c>
       <c r="G263">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="H263">
         <v>100</v>
@@ -35464,27 +35556,27 @@
     </row>
     <row r="264" spans="1:8">
       <c r="A264">
-        <v>405010</v>
+        <v>404080</v>
       </c>
       <c r="B264" t="str">
         <f>INDEX(TextData!B:B,MATCH(A264,TextData!A:A))</f>
-        <v>ダークプリズン+</v>
+        <v>ラインバリア+</v>
       </c>
       <c r="C264">
-        <v>6010</v>
+        <v>6080</v>
       </c>
       <c r="D264" t="str">
         <f>INDEX([2]Define!Q:Q,MATCH(C264,[2]Define!P:P))</f>
-        <v>指定のFeatureのParam1を増やす</v>
+        <v>指定魔法のCTリセット値を変更する</v>
       </c>
       <c r="E264">
-        <v>5010</v>
+        <v>4080</v>
       </c>
       <c r="F264">
         <v>0</v>
       </c>
       <c r="G264">
-        <v>250</v>
+        <v>3</v>
       </c>
       <c r="H264">
         <v>100</v>
@@ -35492,11 +35584,11 @@
     </row>
     <row r="265" spans="1:8">
       <c r="A265">
-        <v>405020</v>
+        <v>405010</v>
       </c>
       <c r="B265" t="str">
         <f>INDEX(TextData!B:B,MATCH(A265,TextData!A:A))</f>
-        <v>ユーサネイジア+</v>
+        <v>ダークプリズン+</v>
       </c>
       <c r="C265">
         <v>6010</v>
@@ -35506,13 +35598,13 @@
         <v>指定のFeatureのParam1を増やす</v>
       </c>
       <c r="E265">
-        <v>5020</v>
+        <v>5010</v>
       </c>
       <c r="F265">
         <v>0</v>
       </c>
       <c r="G265">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="H265">
         <v>100</v>
@@ -35520,27 +35612,27 @@
     </row>
     <row r="266" spans="1:8">
       <c r="A266">
-        <v>405030</v>
+        <v>405020</v>
       </c>
       <c r="B266" t="str">
         <f>INDEX(TextData!B:B,MATCH(A266,TextData!A:A))</f>
-        <v>ドレインヒール+</v>
+        <v>ユーサネイジア+</v>
       </c>
       <c r="C266">
-        <v>6030</v>
+        <v>6010</v>
       </c>
       <c r="D266" t="str">
         <f>INDEX([2]Define!Q:Q,MATCH(C266,[2]Define!P:P))</f>
-        <v>指定のFeatureのParam3を増やす</v>
+        <v>指定のFeatureのParam1を増やす</v>
       </c>
       <c r="E266">
-        <v>5030</v>
+        <v>5020</v>
       </c>
       <c r="F266">
         <v>0</v>
       </c>
       <c r="G266">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="H266">
         <v>100</v>
@@ -35548,27 +35640,27 @@
     </row>
     <row r="267" spans="1:8">
       <c r="A267">
-        <v>405040</v>
+        <v>405030</v>
       </c>
       <c r="B267" t="str">
         <f>INDEX(TextData!B:B,MATCH(A267,TextData!A:A))</f>
-        <v>アビサルデスペア+</v>
+        <v>ドレインヒール+</v>
       </c>
       <c r="C267">
-        <v>6020</v>
+        <v>6030</v>
       </c>
       <c r="D267" t="str">
         <f>INDEX([2]Define!Q:Q,MATCH(C267,[2]Define!P:P))</f>
-        <v>指定のFeatureのParam2を増やす</v>
+        <v>指定のFeatureのParam3を増やす</v>
       </c>
       <c r="E267">
-        <v>5040</v>
+        <v>5030</v>
       </c>
       <c r="F267">
         <v>0</v>
       </c>
       <c r="G267">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="H267">
         <v>100</v>
@@ -35576,27 +35668,27 @@
     </row>
     <row r="268" spans="1:8">
       <c r="A268">
-        <v>405050</v>
+        <v>405040</v>
       </c>
       <c r="B268" t="str">
         <f>INDEX(TextData!B:B,MATCH(A268,TextData!A:A))</f>
-        <v>ディプラヴィティ+</v>
+        <v>アビサルデスペア+</v>
       </c>
       <c r="C268">
-        <v>6030</v>
+        <v>6020</v>
       </c>
       <c r="D268" t="str">
         <f>INDEX([2]Define!Q:Q,MATCH(C268,[2]Define!P:P))</f>
-        <v>指定のFeatureのParam3を増やす</v>
+        <v>指定のFeatureのParam2を増やす</v>
       </c>
       <c r="E268">
-        <v>5050</v>
+        <v>5040</v>
       </c>
       <c r="F268">
         <v>0</v>
       </c>
       <c r="G268">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H268">
         <v>100</v>
@@ -35604,11 +35696,11 @@
     </row>
     <row r="269" spans="1:8">
       <c r="A269">
-        <v>405060</v>
+        <v>405050</v>
       </c>
       <c r="B269" t="str">
         <f>INDEX(TextData!B:B,MATCH(A269,TextData!A:A))</f>
-        <v>ダークネス+</v>
+        <v>ディプラヴィティ+</v>
       </c>
       <c r="C269">
         <v>6030</v>
@@ -35618,13 +35710,13 @@
         <v>指定のFeatureのParam3を増やす</v>
       </c>
       <c r="E269">
-        <v>5060</v>
+        <v>5050</v>
       </c>
       <c r="F269">
         <v>0</v>
       </c>
       <c r="G269">
-        <v>50</v>
+        <v>3</v>
       </c>
       <c r="H269">
         <v>100</v>
@@ -35632,11 +35724,11 @@
     </row>
     <row r="270" spans="1:8">
       <c r="A270">
-        <v>405070</v>
+        <v>405060</v>
       </c>
       <c r="B270" t="str">
         <f>INDEX(TextData!B:B,MATCH(A270,TextData!A:A))</f>
-        <v>シェイディークラウド+</v>
+        <v>ダークネス+</v>
       </c>
       <c r="C270">
         <v>6030</v>
@@ -35646,13 +35738,13 @@
         <v>指定のFeatureのParam3を増やす</v>
       </c>
       <c r="E270">
-        <v>5070</v>
+        <v>5060</v>
       </c>
       <c r="F270">
         <v>0</v>
       </c>
       <c r="G270">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="H270">
         <v>100</v>
@@ -35660,11 +35752,11 @@
     </row>
     <row r="271" spans="1:8">
       <c r="A271">
-        <v>405080</v>
+        <v>405070</v>
       </c>
       <c r="B271" t="str">
         <f>INDEX(TextData!B:B,MATCH(A271,TextData!A:A))</f>
-        <v>ポイズンブロウ+</v>
+        <v>シェイディークラウド+</v>
       </c>
       <c r="C271">
         <v>6030</v>
@@ -35674,13 +35766,13 @@
         <v>指定のFeatureのParam3を増やす</v>
       </c>
       <c r="E271">
-        <v>5080</v>
+        <v>5070</v>
       </c>
       <c r="F271">
         <v>0</v>
       </c>
       <c r="G271">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H271">
         <v>100</v>
@@ -35688,11 +35780,11 @@
     </row>
     <row r="272" spans="1:8">
       <c r="A272">
-        <v>411010</v>
+        <v>405080</v>
       </c>
       <c r="B272" t="str">
         <f>INDEX(TextData!B:B,MATCH(A272,TextData!A:A))</f>
-        <v>ウルフソウル+</v>
+        <v>ポイズンブロウ+</v>
       </c>
       <c r="C272">
         <v>6030</v>
@@ -35702,13 +35794,13 @@
         <v>指定のFeatureのParam3を増やす</v>
       </c>
       <c r="E272">
-        <v>11010</v>
+        <v>5080</v>
       </c>
       <c r="F272">
         <v>0</v>
       </c>
       <c r="G272">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="H272">
         <v>100</v>
@@ -35716,11 +35808,11 @@
     </row>
     <row r="273" spans="1:8">
       <c r="A273">
-        <v>411020</v>
+        <v>411010</v>
       </c>
       <c r="B273" t="str">
         <f>INDEX(TextData!B:B,MATCH(A273,TextData!A:A))</f>
-        <v>プリディカメント+</v>
+        <v>ウルフソウル+</v>
       </c>
       <c r="C273">
         <v>6030</v>
@@ -35730,13 +35822,13 @@
         <v>指定のFeatureのParam3を増やす</v>
       </c>
       <c r="E273">
-        <v>11020</v>
+        <v>11010</v>
       </c>
       <c r="F273">
         <v>0</v>
       </c>
       <c r="G273">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="H273">
         <v>100</v>
@@ -35744,11 +35836,11 @@
     </row>
     <row r="274" spans="1:8">
       <c r="A274">
-        <v>411030</v>
+        <v>411020</v>
       </c>
       <c r="B274" t="str">
         <f>INDEX(TextData!B:B,MATCH(A274,TextData!A:A))</f>
-        <v>アサルトシフト+</v>
+        <v>プリディカメント+</v>
       </c>
       <c r="C274">
         <v>6030</v>
@@ -35758,13 +35850,13 @@
         <v>指定のFeatureのParam3を増やす</v>
       </c>
       <c r="E274">
-        <v>11030</v>
+        <v>11020</v>
       </c>
       <c r="F274">
         <v>0</v>
       </c>
       <c r="G274">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="H274">
         <v>100</v>
@@ -35789,7 +35881,7 @@
         <v>11030</v>
       </c>
       <c r="F275">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G275">
         <v>8</v>
@@ -35800,27 +35892,27 @@
     </row>
     <row r="276" spans="1:8">
       <c r="A276">
-        <v>411040</v>
+        <v>411030</v>
       </c>
       <c r="B276" t="str">
         <f>INDEX(TextData!B:B,MATCH(A276,TextData!A:A))</f>
-        <v>アクティブギフト+</v>
+        <v>アサルトシフト+</v>
       </c>
       <c r="C276">
-        <v>6080</v>
+        <v>6030</v>
       </c>
       <c r="D276" t="str">
         <f>INDEX([2]Define!Q:Q,MATCH(C276,[2]Define!P:P))</f>
-        <v>指定魔法のCTリセット値を変更する</v>
+        <v>指定のFeatureのParam3を増やす</v>
       </c>
       <c r="E276">
-        <v>11040</v>
+        <v>11030</v>
       </c>
       <c r="F276">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G276">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="H276">
         <v>100</v>
@@ -35828,27 +35920,27 @@
     </row>
     <row r="277" spans="1:8">
       <c r="A277">
-        <v>411050</v>
+        <v>411040</v>
       </c>
       <c r="B277" t="str">
         <f>INDEX(TextData!B:B,MATCH(A277,TextData!A:A))</f>
-        <v>イグナイテッド+</v>
+        <v>アクティブギフト+</v>
       </c>
       <c r="C277">
-        <v>6010</v>
+        <v>6080</v>
       </c>
       <c r="D277" t="str">
         <f>INDEX([2]Define!Q:Q,MATCH(C277,[2]Define!P:P))</f>
-        <v>指定のFeatureのParam1を増やす</v>
+        <v>指定魔法のCTリセット値を変更する</v>
       </c>
       <c r="E277">
-        <v>11050</v>
+        <v>11040</v>
       </c>
       <c r="F277">
         <v>0</v>
       </c>
       <c r="G277">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H277">
         <v>100</v>
@@ -35856,11 +35948,11 @@
     </row>
     <row r="278" spans="1:8">
       <c r="A278">
-        <v>411060</v>
+        <v>411050</v>
       </c>
       <c r="B278" t="str">
         <f>INDEX(TextData!B:B,MATCH(A278,TextData!A:A))</f>
-        <v>ライジングファイア+</v>
+        <v>イグナイテッド+</v>
       </c>
       <c r="C278">
         <v>6010</v>
@@ -35870,13 +35962,13 @@
         <v>指定のFeatureのParam1を増やす</v>
       </c>
       <c r="E278">
-        <v>11060</v>
+        <v>11050</v>
       </c>
       <c r="F278">
         <v>0</v>
       </c>
       <c r="G278">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H278">
         <v>100</v>
@@ -35884,27 +35976,27 @@
     </row>
     <row r="279" spans="1:8">
       <c r="A279">
-        <v>411070</v>
+        <v>411060</v>
       </c>
       <c r="B279" t="str">
         <f>INDEX(TextData!B:B,MATCH(A279,TextData!A:A))</f>
-        <v>ルージュバック+</v>
+        <v>ライジングファイア+</v>
       </c>
       <c r="C279">
-        <v>6030</v>
+        <v>6010</v>
       </c>
       <c r="D279" t="str">
         <f>INDEX([2]Define!Q:Q,MATCH(C279,[2]Define!P:P))</f>
-        <v>指定のFeatureのParam3を増やす</v>
+        <v>指定のFeatureのParam1を増やす</v>
       </c>
       <c r="E279">
-        <v>11070</v>
+        <v>11060</v>
       </c>
       <c r="F279">
         <v>0</v>
       </c>
       <c r="G279">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H279">
         <v>100</v>
@@ -35912,11 +36004,11 @@
     </row>
     <row r="280" spans="1:8">
       <c r="A280">
-        <v>411080</v>
+        <v>411070</v>
       </c>
       <c r="B280" t="str">
         <f>INDEX(TextData!B:B,MATCH(A280,TextData!A:A))</f>
-        <v>パワーエール+</v>
+        <v>ルージュバック+</v>
       </c>
       <c r="C280">
         <v>6030</v>
@@ -35926,13 +36018,13 @@
         <v>指定のFeatureのParam3を増やす</v>
       </c>
       <c r="E280">
-        <v>11080</v>
+        <v>11070</v>
       </c>
       <c r="F280">
         <v>0</v>
       </c>
       <c r="G280">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H280">
         <v>100</v>
@@ -35940,11 +36032,11 @@
     </row>
     <row r="281" spans="1:8">
       <c r="A281">
-        <v>411090</v>
+        <v>411080</v>
       </c>
       <c r="B281" t="str">
         <f>INDEX(TextData!B:B,MATCH(A281,TextData!A:A))</f>
-        <v>スレイプニル+</v>
+        <v>パワーエール+</v>
       </c>
       <c r="C281">
         <v>6030</v>
@@ -35954,13 +36046,13 @@
         <v>指定のFeatureのParam3を増やす</v>
       </c>
       <c r="E281">
-        <v>11090</v>
+        <v>11080</v>
       </c>
       <c r="F281">
         <v>0</v>
       </c>
       <c r="G281">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="H281">
         <v>100</v>
@@ -35968,27 +36060,27 @@
     </row>
     <row r="282" spans="1:8">
       <c r="A282">
-        <v>412010</v>
+        <v>411090</v>
       </c>
       <c r="B282" t="str">
         <f>INDEX(TextData!B:B,MATCH(A282,TextData!A:A))</f>
-        <v>エクステンション+</v>
+        <v>スレイプニル+</v>
       </c>
       <c r="C282">
-        <v>6210</v>
+        <v>6030</v>
       </c>
       <c r="D282" t="str">
         <f>INDEX([2]Define!Q:Q,MATCH(C282,[2]Define!P:P))</f>
-        <v>指定魔法の対象を変更（強化限定）</v>
+        <v>指定のFeatureのParam3を増やす</v>
       </c>
       <c r="E282">
-        <v>12010</v>
+        <v>11090</v>
       </c>
       <c r="F282">
         <v>0</v>
       </c>
       <c r="G282">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="H282">
         <v>100</v>
@@ -35996,27 +36088,27 @@
     </row>
     <row r="283" spans="1:8">
       <c r="A283">
-        <v>412020</v>
+        <v>412010</v>
       </c>
       <c r="B283" t="str">
         <f>INDEX(TextData!B:B,MATCH(A283,TextData!A:A))</f>
-        <v>ヘブンリーラック+</v>
+        <v>エクステンション+</v>
       </c>
       <c r="C283">
-        <v>6030</v>
+        <v>6210</v>
       </c>
       <c r="D283" t="str">
         <f>INDEX([2]Define!Q:Q,MATCH(C283,[2]Define!P:P))</f>
-        <v>指定のFeatureのParam3を増やす</v>
+        <v>指定魔法の対象を変更（強化限定）</v>
       </c>
       <c r="E283">
-        <v>12020</v>
+        <v>12010</v>
       </c>
       <c r="F283">
         <v>0</v>
       </c>
       <c r="G283">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="H283">
         <v>100</v>
@@ -36024,11 +36116,11 @@
     </row>
     <row r="284" spans="1:8">
       <c r="A284">
-        <v>412030</v>
+        <v>412020</v>
       </c>
       <c r="B284" t="str">
         <f>INDEX(TextData!B:B,MATCH(A284,TextData!A:A))</f>
-        <v>スウィフトカレント+</v>
+        <v>ヘブンリーラック+</v>
       </c>
       <c r="C284">
         <v>6030</v>
@@ -36038,13 +36130,13 @@
         <v>指定のFeatureのParam3を増やす</v>
       </c>
       <c r="E284">
-        <v>12030</v>
+        <v>12020</v>
       </c>
       <c r="F284">
         <v>0</v>
       </c>
       <c r="G284">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="H284">
         <v>100</v>
@@ -36052,11 +36144,11 @@
     </row>
     <row r="285" spans="1:8">
       <c r="A285">
-        <v>412040</v>
+        <v>412030</v>
       </c>
       <c r="B285" t="str">
         <f>INDEX(TextData!B:B,MATCH(A285,TextData!A:A))</f>
-        <v>イヴェイドオール+</v>
+        <v>スウィフトカレント+</v>
       </c>
       <c r="C285">
         <v>6030</v>
@@ -36066,7 +36158,7 @@
         <v>指定のFeatureのParam3を増やす</v>
       </c>
       <c r="E285">
-        <v>12040</v>
+        <v>12030</v>
       </c>
       <c r="F285">
         <v>0</v>
@@ -36080,27 +36172,27 @@
     </row>
     <row r="286" spans="1:8">
       <c r="A286">
-        <v>412050</v>
+        <v>412040</v>
       </c>
       <c r="B286" t="str">
         <f>INDEX(TextData!B:B,MATCH(A286,TextData!A:A))</f>
-        <v>クイックムーブ+</v>
+        <v>イヴェイドオール+</v>
       </c>
       <c r="C286">
-        <v>6010</v>
+        <v>6030</v>
       </c>
       <c r="D286" t="str">
         <f>INDEX([2]Define!Q:Q,MATCH(C286,[2]Define!P:P))</f>
-        <v>指定のFeatureのParam1を増やす</v>
+        <v>指定のFeatureのParam3を増やす</v>
       </c>
       <c r="E286">
-        <v>12050</v>
+        <v>12040</v>
       </c>
       <c r="F286">
         <v>0</v>
       </c>
       <c r="G286">
-        <v>400</v>
+        <v>10</v>
       </c>
       <c r="H286">
         <v>100</v>
@@ -36108,11 +36200,11 @@
     </row>
     <row r="287" spans="1:8">
       <c r="A287">
-        <v>412060</v>
+        <v>412050</v>
       </c>
       <c r="B287" t="str">
         <f>INDEX(TextData!B:B,MATCH(A287,TextData!A:A))</f>
-        <v>チェイスマジック+</v>
+        <v>クイックムーブ+</v>
       </c>
       <c r="C287">
         <v>6010</v>
@@ -36122,13 +36214,13 @@
         <v>指定のFeatureのParam1を増やす</v>
       </c>
       <c r="E287">
-        <v>12060</v>
+        <v>12050</v>
       </c>
       <c r="F287">
         <v>0</v>
       </c>
       <c r="G287">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="H287">
         <v>100</v>
@@ -36136,27 +36228,27 @@
     </row>
     <row r="288" spans="1:8">
       <c r="A288">
-        <v>412070</v>
+        <v>412060</v>
       </c>
       <c r="B288" t="str">
         <f>INDEX(TextData!B:B,MATCH(A288,TextData!A:A))</f>
-        <v>ソーサリーコネクト+</v>
+        <v>チェイスマジック+</v>
       </c>
       <c r="C288">
-        <v>6030</v>
+        <v>6010</v>
       </c>
       <c r="D288" t="str">
         <f>INDEX([2]Define!Q:Q,MATCH(C288,[2]Define!P:P))</f>
-        <v>指定のFeatureのParam3を増やす</v>
+        <v>指定のFeatureのParam1を増やす</v>
       </c>
       <c r="E288">
-        <v>12070</v>
+        <v>12060</v>
       </c>
       <c r="F288">
         <v>0</v>
       </c>
       <c r="G288">
-        <v>16</v>
+        <v>300</v>
       </c>
       <c r="H288">
         <v>100</v>
@@ -36164,27 +36256,27 @@
     </row>
     <row r="289" spans="1:8">
       <c r="A289">
-        <v>412080</v>
+        <v>412070</v>
       </c>
       <c r="B289" t="str">
         <f>INDEX(TextData!B:B,MATCH(A289,TextData!A:A))</f>
-        <v>ウィンドライズ+</v>
+        <v>ソーサリーコネクト+</v>
       </c>
       <c r="C289">
-        <v>6010</v>
+        <v>6030</v>
       </c>
       <c r="D289" t="str">
         <f>INDEX([2]Define!Q:Q,MATCH(C289,[2]Define!P:P))</f>
-        <v>指定のFeatureのParam1を増やす</v>
+        <v>指定のFeatureのParam3を増やす</v>
       </c>
       <c r="E289">
-        <v>12080</v>
+        <v>12070</v>
       </c>
       <c r="F289">
         <v>0</v>
       </c>
       <c r="G289">
-        <v>300</v>
+        <v>16</v>
       </c>
       <c r="H289">
         <v>100</v>
@@ -36192,11 +36284,11 @@
     </row>
     <row r="290" spans="1:8">
       <c r="A290">
-        <v>412090</v>
+        <v>412080</v>
       </c>
       <c r="B290" t="str">
         <f>INDEX(TextData!B:B,MATCH(A290,TextData!A:A))</f>
-        <v>アウトオブオーダー+</v>
+        <v>ウィンドライズ+</v>
       </c>
       <c r="C290">
         <v>6010</v>
@@ -36206,13 +36298,13 @@
         <v>指定のFeatureのParam1を増やす</v>
       </c>
       <c r="E290">
-        <v>12090</v>
+        <v>12080</v>
       </c>
       <c r="F290">
         <v>0</v>
       </c>
       <c r="G290">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="H290">
         <v>100</v>
@@ -36220,27 +36312,27 @@
     </row>
     <row r="291" spans="1:8">
       <c r="A291">
-        <v>413010</v>
+        <v>412090</v>
       </c>
       <c r="B291" t="str">
         <f>INDEX(TextData!B:B,MATCH(A291,TextData!A:A))</f>
-        <v>アーマーコード+</v>
+        <v>アウトオブオーダー+</v>
       </c>
       <c r="C291">
-        <v>6030</v>
+        <v>6010</v>
       </c>
       <c r="D291" t="str">
         <f>INDEX([2]Define!Q:Q,MATCH(C291,[2]Define!P:P))</f>
-        <v>指定のFeatureのParam3を増やす</v>
+        <v>指定のFeatureのParam1を増やす</v>
       </c>
       <c r="E291">
-        <v>13010</v>
+        <v>12090</v>
       </c>
       <c r="F291">
         <v>0</v>
       </c>
       <c r="G291">
-        <v>8</v>
+        <v>400</v>
       </c>
       <c r="H291">
         <v>100</v>
@@ -36248,11 +36340,11 @@
     </row>
     <row r="292" spans="1:8">
       <c r="A292">
-        <v>413020</v>
+        <v>413010</v>
       </c>
       <c r="B292" t="str">
         <f>INDEX(TextData!B:B,MATCH(A292,TextData!A:A))</f>
-        <v>クイックバリア+</v>
+        <v>アーマーコード+</v>
       </c>
       <c r="C292">
         <v>6030</v>
@@ -36262,13 +36354,13 @@
         <v>指定のFeatureのParam3を増やす</v>
       </c>
       <c r="E292">
-        <v>13020</v>
+        <v>13010</v>
       </c>
       <c r="F292">
         <v>0</v>
       </c>
       <c r="G292">
-        <v>50</v>
+        <v>8</v>
       </c>
       <c r="H292">
         <v>100</v>
@@ -36276,27 +36368,27 @@
     </row>
     <row r="293" spans="1:8">
       <c r="A293">
-        <v>413030</v>
+        <v>413020</v>
       </c>
       <c r="B293" t="str">
         <f>INDEX(TextData!B:B,MATCH(A293,TextData!A:A))</f>
-        <v>クイックキュア+</v>
+        <v>クイックバリア+</v>
       </c>
       <c r="C293">
-        <v>6080</v>
+        <v>6030</v>
       </c>
       <c r="D293" t="str">
         <f>INDEX([2]Define!Q:Q,MATCH(C293,[2]Define!P:P))</f>
-        <v>指定魔法のCTリセット値を変更する</v>
+        <v>指定のFeatureのParam3を増やす</v>
       </c>
       <c r="E293">
-        <v>14090</v>
+        <v>13020</v>
       </c>
       <c r="F293">
         <v>0</v>
       </c>
       <c r="G293">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="H293">
         <v>100</v>
@@ -36304,27 +36396,27 @@
     </row>
     <row r="294" spans="1:8">
       <c r="A294">
-        <v>413040</v>
+        <v>413030</v>
       </c>
       <c r="B294" t="str">
         <f>INDEX(TextData!B:B,MATCH(A294,TextData!A:A))</f>
-        <v>セルフシールド+</v>
+        <v>クイックキュア+</v>
       </c>
       <c r="C294">
-        <v>6030</v>
+        <v>6080</v>
       </c>
       <c r="D294" t="str">
         <f>INDEX([2]Define!Q:Q,MATCH(C294,[2]Define!P:P))</f>
-        <v>指定のFeatureのParam3を増やす</v>
+        <v>指定魔法のCTリセット値を変更する</v>
       </c>
       <c r="E294">
-        <v>13040</v>
+        <v>14090</v>
       </c>
       <c r="F294">
         <v>0</v>
       </c>
       <c r="G294">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="H294">
         <v>100</v>
@@ -36332,27 +36424,27 @@
     </row>
     <row r="295" spans="1:8">
       <c r="A295">
-        <v>413050</v>
+        <v>413040</v>
       </c>
       <c r="B295" t="str">
         <f>INDEX(TextData!B:B,MATCH(A295,TextData!A:A))</f>
-        <v>パッシブジャミング+</v>
+        <v>セルフシールド+</v>
       </c>
       <c r="C295">
-        <v>6080</v>
+        <v>6030</v>
       </c>
       <c r="D295" t="str">
         <f>INDEX([2]Define!Q:Q,MATCH(C295,[2]Define!P:P))</f>
-        <v>指定魔法のCTリセット値を変更する</v>
+        <v>指定のFeatureのParam3を増やす</v>
       </c>
       <c r="E295">
-        <v>14090</v>
+        <v>13040</v>
       </c>
       <c r="F295">
         <v>0</v>
       </c>
       <c r="G295">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="H295">
         <v>100</v>
@@ -36360,11 +36452,11 @@
     </row>
     <row r="296" spans="1:8">
       <c r="A296">
-        <v>413060</v>
+        <v>413050</v>
       </c>
       <c r="B296" t="str">
         <f>INDEX(TextData!B:B,MATCH(A296,TextData!A:A))</f>
-        <v>サプライカバー+</v>
+        <v>パッシブジャミング+</v>
       </c>
       <c r="C296">
         <v>6080</v>
@@ -36388,27 +36480,27 @@
     </row>
     <row r="297" spans="1:8">
       <c r="A297">
-        <v>413070</v>
+        <v>413060</v>
       </c>
       <c r="B297" t="str">
         <f>INDEX(TextData!B:B,MATCH(A297,TextData!A:A))</f>
-        <v>アシッドラッシュ+</v>
+        <v>サプライカバー+</v>
       </c>
       <c r="C297">
-        <v>6010</v>
+        <v>6080</v>
       </c>
       <c r="D297" t="str">
         <f>INDEX([2]Define!Q:Q,MATCH(C297,[2]Define!P:P))</f>
-        <v>指定のFeatureのParam1を増やす</v>
+        <v>指定魔法のCTリセット値を変更する</v>
       </c>
       <c r="E297">
-        <v>13070</v>
+        <v>14090</v>
       </c>
       <c r="F297">
         <v>0</v>
       </c>
       <c r="G297">
-        <v>400</v>
+        <v>1</v>
       </c>
       <c r="H297">
         <v>100</v>
@@ -36416,27 +36508,27 @@
     </row>
     <row r="298" spans="1:8">
       <c r="A298">
-        <v>413080</v>
+        <v>413070</v>
       </c>
       <c r="B298" t="str">
         <f>INDEX(TextData!B:B,MATCH(A298,TextData!A:A))</f>
-        <v>ライフスティール+</v>
+        <v>アシッドラッシュ+</v>
       </c>
       <c r="C298">
-        <v>6030</v>
+        <v>6010</v>
       </c>
       <c r="D298" t="str">
         <f>INDEX([2]Define!Q:Q,MATCH(C298,[2]Define!P:P))</f>
-        <v>指定のFeatureのParam3を増やす</v>
+        <v>指定のFeatureのParam1を増やす</v>
       </c>
       <c r="E298">
-        <v>13080</v>
+        <v>13070</v>
       </c>
       <c r="F298">
         <v>0</v>
       </c>
       <c r="G298">
-        <v>50</v>
+        <v>400</v>
       </c>
       <c r="H298">
         <v>100</v>
@@ -36444,11 +36536,11 @@
     </row>
     <row r="299" spans="1:8">
       <c r="A299">
-        <v>413090</v>
+        <v>413080</v>
       </c>
       <c r="B299" t="str">
         <f>INDEX(TextData!B:B,MATCH(A299,TextData!A:A))</f>
-        <v>アイスセイバー+</v>
+        <v>ライフスティール+</v>
       </c>
       <c r="C299">
         <v>6030</v>
@@ -36458,7 +36550,7 @@
         <v>指定のFeatureのParam3を増やす</v>
       </c>
       <c r="E299">
-        <v>13090</v>
+        <v>13080</v>
       </c>
       <c r="F299">
         <v>0</v>
@@ -36472,27 +36564,27 @@
     </row>
     <row r="300" spans="1:8">
       <c r="A300">
-        <v>414010</v>
+        <v>413090</v>
       </c>
       <c r="B300" t="str">
         <f>INDEX(TextData!B:B,MATCH(A300,TextData!A:A))</f>
-        <v>ディバインシールド+</v>
+        <v>アイスセイバー+</v>
       </c>
       <c r="C300">
-        <v>6020</v>
+        <v>6030</v>
       </c>
       <c r="D300" t="str">
         <f>INDEX([2]Define!Q:Q,MATCH(C300,[2]Define!P:P))</f>
-        <v>指定のFeatureのParam2を増やす</v>
+        <v>指定のFeatureのParam3を増やす</v>
       </c>
       <c r="E300">
-        <v>14010</v>
+        <v>13090</v>
       </c>
       <c r="F300">
         <v>0</v>
       </c>
       <c r="G300">
-        <v>2</v>
+        <v>50</v>
       </c>
       <c r="H300">
         <v>100</v>
@@ -36500,27 +36592,27 @@
     </row>
     <row r="301" spans="1:8">
       <c r="A301">
-        <v>414020</v>
+        <v>414010</v>
       </c>
       <c r="B301" t="str">
         <f>INDEX(TextData!B:B,MATCH(A301,TextData!A:A))</f>
-        <v>ライフディバイド+</v>
+        <v>ディバインシールド+</v>
       </c>
       <c r="C301">
-        <v>6010</v>
+        <v>6020</v>
       </c>
       <c r="D301" t="str">
         <f>INDEX([2]Define!Q:Q,MATCH(C301,[2]Define!P:P))</f>
-        <v>指定のFeatureのParam1を増やす</v>
+        <v>指定のFeatureのParam2を増やす</v>
       </c>
       <c r="E301">
-        <v>14020</v>
+        <v>14010</v>
       </c>
       <c r="F301">
         <v>0</v>
       </c>
       <c r="G301">
-        <v>50</v>
+        <v>2</v>
       </c>
       <c r="H301">
         <v>100</v>
@@ -36528,27 +36620,27 @@
     </row>
     <row r="302" spans="1:8">
       <c r="A302">
-        <v>414030</v>
+        <v>414020</v>
       </c>
       <c r="B302" t="str">
         <f>INDEX(TextData!B:B,MATCH(A302,TextData!A:A))</f>
-        <v>エイミングスコープ+</v>
+        <v>ライフディバイド+</v>
       </c>
       <c r="C302">
-        <v>6030</v>
+        <v>6010</v>
       </c>
       <c r="D302" t="str">
         <f>INDEX([2]Define!Q:Q,MATCH(C302,[2]Define!P:P))</f>
-        <v>指定のFeatureのParam3を増やす</v>
+        <v>指定のFeatureのParam1を増やす</v>
       </c>
       <c r="E302">
-        <v>14030</v>
+        <v>14020</v>
       </c>
       <c r="F302">
         <v>0</v>
       </c>
       <c r="G302">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="H302">
         <v>100</v>
@@ -36556,11 +36648,11 @@
     </row>
     <row r="303" spans="1:8">
       <c r="A303">
-        <v>414040</v>
+        <v>414030</v>
       </c>
       <c r="B303" t="str">
         <f>INDEX(TextData!B:B,MATCH(A303,TextData!A:A))</f>
-        <v>リジェネレーション+</v>
+        <v>エイミングスコープ+</v>
       </c>
       <c r="C303">
         <v>6030</v>
@@ -36570,7 +36662,7 @@
         <v>指定のFeatureのParam3を増やす</v>
       </c>
       <c r="E303">
-        <v>14040</v>
+        <v>14030</v>
       </c>
       <c r="F303">
         <v>0</v>
@@ -36584,11 +36676,11 @@
     </row>
     <row r="304" spans="1:8">
       <c r="A304">
-        <v>414050</v>
+        <v>414040</v>
       </c>
       <c r="B304" t="str">
         <f>INDEX(TextData!B:B,MATCH(A304,TextData!A:A))</f>
-        <v>ホープフルアイリス+</v>
+        <v>リジェネレーション+</v>
       </c>
       <c r="C304">
         <v>6030</v>
@@ -36598,13 +36690,13 @@
         <v>指定のFeatureのParam3を増やす</v>
       </c>
       <c r="E304">
-        <v>14050</v>
+        <v>14040</v>
       </c>
       <c r="F304">
         <v>0</v>
       </c>
       <c r="G304">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="H304">
         <v>100</v>
@@ -36612,27 +36704,27 @@
     </row>
     <row r="305" spans="1:8">
       <c r="A305">
-        <v>414060</v>
+        <v>414050</v>
       </c>
       <c r="B305" t="str">
         <f>INDEX(TextData!B:B,MATCH(A305,TextData!A:A))</f>
-        <v>パッシブサプライ+</v>
+        <v>ホープフルアイリス+</v>
       </c>
       <c r="C305">
-        <v>6010</v>
+        <v>6030</v>
       </c>
       <c r="D305" t="str">
         <f>INDEX([2]Define!Q:Q,MATCH(C305,[2]Define!P:P))</f>
-        <v>指定のFeatureのParam1を増やす</v>
+        <v>指定のFeatureのParam3を増やす</v>
       </c>
       <c r="E305">
-        <v>14060</v>
+        <v>14050</v>
       </c>
       <c r="F305">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G305">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="H305">
         <v>100</v>
@@ -36640,27 +36732,27 @@
     </row>
     <row r="306" spans="1:8">
       <c r="A306">
-        <v>414070</v>
+        <v>414060</v>
       </c>
       <c r="B306" t="str">
         <f>INDEX(TextData!B:B,MATCH(A306,TextData!A:A))</f>
-        <v>ホーミングクルセイド+</v>
+        <v>パッシブサプライ+</v>
       </c>
       <c r="C306">
-        <v>6020</v>
+        <v>6010</v>
       </c>
       <c r="D306" t="str">
         <f>INDEX([2]Define!Q:Q,MATCH(C306,[2]Define!P:P))</f>
-        <v>指定のFeatureのParam2を増やす</v>
+        <v>指定のFeatureのParam1を増やす</v>
       </c>
       <c r="E306">
-        <v>14070</v>
+        <v>14060</v>
       </c>
       <c r="F306">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G306">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H306">
         <v>100</v>
@@ -36668,27 +36760,27 @@
     </row>
     <row r="307" spans="1:8">
       <c r="A307">
-        <v>414080</v>
+        <v>414070</v>
       </c>
       <c r="B307" t="str">
         <f>INDEX(TextData!B:B,MATCH(A307,TextData!A:A))</f>
-        <v>クイックヒール+</v>
+        <v>ホーミングクルセイド+</v>
       </c>
       <c r="C307">
-        <v>6010</v>
+        <v>6020</v>
       </c>
       <c r="D307" t="str">
         <f>INDEX([2]Define!Q:Q,MATCH(C307,[2]Define!P:P))</f>
-        <v>指定のFeatureのParam1を増やす</v>
+        <v>指定のFeatureのParam2を増やす</v>
       </c>
       <c r="E307">
-        <v>14080</v>
+        <v>14070</v>
       </c>
       <c r="F307">
         <v>0</v>
       </c>
       <c r="G307">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="H307">
         <v>100</v>
@@ -36696,27 +36788,27 @@
     </row>
     <row r="308" spans="1:8">
       <c r="A308">
-        <v>414090</v>
+        <v>414080</v>
       </c>
       <c r="B308" t="str">
         <f>INDEX(TextData!B:B,MATCH(A308,TextData!A:A))</f>
-        <v>リレイズ+</v>
+        <v>クイックヒール+</v>
       </c>
       <c r="C308">
-        <v>6080</v>
+        <v>6010</v>
       </c>
       <c r="D308" t="str">
         <f>INDEX([2]Define!Q:Q,MATCH(C308,[2]Define!P:P))</f>
-        <v>指定魔法のCTリセット値を変更する</v>
+        <v>指定のFeatureのParam1を増やす</v>
       </c>
       <c r="E308">
-        <v>14090</v>
+        <v>14080</v>
       </c>
       <c r="F308">
         <v>0</v>
       </c>
       <c r="G308">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="H308">
         <v>100</v>
@@ -36724,27 +36816,27 @@
     </row>
     <row r="309" spans="1:8">
       <c r="A309">
-        <v>415010</v>
+        <v>414090</v>
       </c>
       <c r="B309" t="str">
         <f>INDEX(TextData!B:B,MATCH(A309,TextData!A:A))</f>
-        <v>イーグルアイ+</v>
+        <v>リレイズ+</v>
       </c>
       <c r="C309">
-        <v>6030</v>
+        <v>6080</v>
       </c>
       <c r="D309" t="str">
         <f>INDEX([2]Define!Q:Q,MATCH(C309,[2]Define!P:P))</f>
-        <v>指定のFeatureのParam3を増やす</v>
+        <v>指定魔法のCTリセット値を変更する</v>
       </c>
       <c r="E309">
-        <v>15010</v>
+        <v>14090</v>
       </c>
       <c r="F309">
         <v>0</v>
       </c>
       <c r="G309">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="H309">
         <v>100</v>
@@ -36752,11 +36844,11 @@
     </row>
     <row r="310" spans="1:8">
       <c r="A310">
-        <v>415020</v>
+        <v>415010</v>
       </c>
       <c r="B310" t="str">
         <f>INDEX(TextData!B:B,MATCH(A310,TextData!A:A))</f>
-        <v>ネヴァーエンド+</v>
+        <v>イーグルアイ+</v>
       </c>
       <c r="C310">
         <v>6030</v>
@@ -36766,13 +36858,13 @@
         <v>指定のFeatureのParam3を増やす</v>
       </c>
       <c r="E310">
-        <v>15020</v>
+        <v>15010</v>
       </c>
       <c r="F310">
         <v>0</v>
       </c>
       <c r="G310">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="H310">
         <v>100</v>
@@ -36780,27 +36872,27 @@
     </row>
     <row r="311" spans="1:8">
       <c r="A311">
-        <v>415030</v>
+        <v>415020</v>
       </c>
       <c r="B311" t="str">
         <f>INDEX(TextData!B:B,MATCH(A311,TextData!A:A))</f>
-        <v>グレイブアクト+</v>
+        <v>ネヴァーエンド+</v>
       </c>
       <c r="C311">
-        <v>6010</v>
+        <v>6030</v>
       </c>
       <c r="D311" t="str">
         <f>INDEX([2]Define!Q:Q,MATCH(C311,[2]Define!P:P))</f>
-        <v>指定のFeatureのParam1を増やす</v>
+        <v>指定のFeatureのParam3を増やす</v>
       </c>
       <c r="E311">
-        <v>15030</v>
+        <v>15020</v>
       </c>
       <c r="F311">
         <v>0</v>
       </c>
       <c r="G311">
-        <v>2</v>
+        <v>50</v>
       </c>
       <c r="H311">
         <v>100</v>
@@ -36808,27 +36900,27 @@
     </row>
     <row r="312" spans="1:8">
       <c r="A312">
-        <v>415040</v>
+        <v>415030</v>
       </c>
       <c r="B312" t="str">
         <f>INDEX(TextData!B:B,MATCH(A312,TextData!A:A))</f>
-        <v>スカルグラッジ+</v>
+        <v>グレイブアクト+</v>
       </c>
       <c r="C312">
-        <v>6030</v>
+        <v>6010</v>
       </c>
       <c r="D312" t="str">
         <f>INDEX([2]Define!Q:Q,MATCH(C312,[2]Define!P:P))</f>
-        <v>指定のFeatureのParam3を増やす</v>
+        <v>指定のFeatureのParam1を増やす</v>
       </c>
       <c r="E312">
-        <v>15040</v>
+        <v>15030</v>
       </c>
       <c r="F312">
         <v>0</v>
       </c>
       <c r="G312">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="H312">
         <v>100</v>
@@ -36836,11 +36928,11 @@
     </row>
     <row r="313" spans="1:8">
       <c r="A313">
-        <v>415050</v>
+        <v>415040</v>
       </c>
       <c r="B313" t="str">
         <f>INDEX(TextData!B:B,MATCH(A313,TextData!A:A))</f>
-        <v>ネガティブドレイン+</v>
+        <v>スカルグラッジ+</v>
       </c>
       <c r="C313">
         <v>6030</v>
@@ -36850,13 +36942,13 @@
         <v>指定のFeatureのParam3を増やす</v>
       </c>
       <c r="E313">
-        <v>15050</v>
+        <v>15040</v>
       </c>
       <c r="F313">
         <v>0</v>
       </c>
       <c r="G313">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="H313">
         <v>100</v>
@@ -36864,11 +36956,11 @@
     </row>
     <row r="314" spans="1:8">
       <c r="A314">
-        <v>415060</v>
+        <v>415050</v>
       </c>
       <c r="B314" t="str">
         <f>INDEX(TextData!B:B,MATCH(A314,TextData!A:A))</f>
-        <v>アンデッドペイン+</v>
+        <v>ネガティブドレイン+</v>
       </c>
       <c r="C314">
         <v>6030</v>
@@ -36878,13 +36970,13 @@
         <v>指定のFeatureのParam3を増やす</v>
       </c>
       <c r="E314">
-        <v>15060</v>
+        <v>15050</v>
       </c>
       <c r="F314">
         <v>0</v>
       </c>
       <c r="G314">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="H314">
         <v>100</v>
@@ -36892,11 +36984,11 @@
     </row>
     <row r="315" spans="1:8">
       <c r="A315">
-        <v>415070</v>
+        <v>415060</v>
       </c>
       <c r="B315" t="str">
         <f>INDEX(TextData!B:B,MATCH(A315,TextData!A:A))</f>
-        <v>ジャックポッド+</v>
+        <v>アンデッドペイン+</v>
       </c>
       <c r="C315">
         <v>6030</v>
@@ -36906,13 +36998,13 @@
         <v>指定のFeatureのParam3を増やす</v>
       </c>
       <c r="E315">
-        <v>15070</v>
+        <v>15060</v>
       </c>
       <c r="F315">
         <v>0</v>
       </c>
       <c r="G315">
-        <v>75</v>
+        <v>15</v>
       </c>
       <c r="H315">
         <v>100</v>
@@ -36920,11 +37012,11 @@
     </row>
     <row r="316" spans="1:8">
       <c r="A316">
-        <v>415080</v>
+        <v>415070</v>
       </c>
       <c r="B316" t="str">
         <f>INDEX(TextData!B:B,MATCH(A316,TextData!A:A))</f>
-        <v>ヒールハント+</v>
+        <v>ジャックポッド+</v>
       </c>
       <c r="C316">
         <v>6030</v>
@@ -36934,13 +37026,13 @@
         <v>指定のFeatureのParam3を増やす</v>
       </c>
       <c r="E316">
-        <v>15080</v>
+        <v>15070</v>
       </c>
       <c r="F316">
         <v>0</v>
       </c>
       <c r="G316">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="H316">
         <v>100</v>
@@ -36948,11 +37040,11 @@
     </row>
     <row r="317" spans="1:8">
       <c r="A317">
-        <v>415090</v>
+        <v>415080</v>
       </c>
       <c r="B317" t="str">
         <f>INDEX(TextData!B:B,MATCH(A317,TextData!A:A))</f>
-        <v>クイックカース+</v>
+        <v>ヒールハント+</v>
       </c>
       <c r="C317">
         <v>6030</v>
@@ -36962,15 +37054,43 @@
         <v>指定のFeatureのParam3を増やす</v>
       </c>
       <c r="E317">
+        <v>15080</v>
+      </c>
+      <c r="F317">
+        <v>0</v>
+      </c>
+      <c r="G317">
+        <v>50</v>
+      </c>
+      <c r="H317">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="318" spans="1:8">
+      <c r="A318">
+        <v>415090</v>
+      </c>
+      <c r="B318" t="str">
+        <f>INDEX(TextData!B:B,MATCH(A318,TextData!A:A))</f>
+        <v>クイックカース+</v>
+      </c>
+      <c r="C318">
+        <v>6030</v>
+      </c>
+      <c r="D318" t="str">
+        <f>INDEX([2]Define!Q:Q,MATCH(C318,[2]Define!P:P))</f>
+        <v>指定のFeatureのParam3を増やす</v>
+      </c>
+      <c r="E318">
         <v>15090</v>
       </c>
-      <c r="F317">
-        <v>0</v>
-      </c>
-      <c r="G317">
+      <c r="F318">
+        <v>0</v>
+      </c>
+      <c r="G318">
         <v>35</v>
       </c>
-      <c r="H317">
+      <c r="H318">
         <v>100</v>
       </c>
     </row>
@@ -36983,7 +37103,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H119"/>
+  <dimension ref="A1:H120"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="7"/>
   <cols>
     <col min="2" max="2" width="19.7272727272727" customWidth="1"/>
@@ -40317,6 +40437,34 @@
         <v>0</v>
       </c>
       <c r="H119">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120" spans="1:8">
+      <c r="A120">
+        <v>310010</v>
+      </c>
+      <c r="B120" t="str">
+        <f>INDEX(TextData!B:B,MATCH(A120,TextData!A:A))</f>
+        <v>ヒールユニット</v>
+      </c>
+      <c r="C120">
+        <v>40010</v>
+      </c>
+      <c r="D120" t="str">
+        <f>INDEX([2]Define!V:V,MATCH(C120,[2]Define!U:U))</f>
+        <v>存在猶予を延長している</v>
+      </c>
+      <c r="E120">
+        <v>4</v>
+      </c>
+      <c r="F120">
+        <v>0</v>
+      </c>
+      <c r="G120">
+        <v>0</v>
+      </c>
+      <c r="H120">
         <v>0</v>
       </c>
     </row>
@@ -40735,7 +40883,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D247"/>
+  <dimension ref="A1:D248"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="3"/>
   <cols>
     <col min="2" max="2" width="20" customWidth="1"/>
@@ -42541,86 +42689,86 @@
         <v>157</v>
       </c>
     </row>
-    <row r="163" spans="1:3">
+    <row r="163" ht="26" spans="1:3">
       <c r="A163">
-        <v>401010</v>
+        <v>310010</v>
       </c>
       <c r="B163" t="s">
         <v>334</v>
       </c>
-      <c r="C163" s="3" t="s">
+      <c r="C163" s="5" t="s">
         <v>335</v>
       </c>
     </row>
     <row r="164" spans="1:3">
       <c r="A164">
-        <v>401020</v>
+        <v>401010</v>
       </c>
       <c r="B164" t="s">
         <v>336</v>
       </c>
       <c r="C164" s="3" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="165" spans="1:3">
       <c r="A165">
-        <v>401030</v>
+        <v>401020</v>
       </c>
       <c r="B165" t="s">
+        <v>338</v>
+      </c>
+      <c r="C165" s="3" t="s">
         <v>337</v>
-      </c>
-      <c r="C165" s="3" t="s">
-        <v>338</v>
       </c>
     </row>
     <row r="166" spans="1:3">
       <c r="A166">
-        <v>401040</v>
+        <v>401030</v>
       </c>
       <c r="B166" t="s">
         <v>339</v>
       </c>
-      <c r="C166" t="s">
+      <c r="C166" s="3" t="s">
         <v>340</v>
       </c>
     </row>
     <row r="167" spans="1:3">
       <c r="A167">
-        <v>401050</v>
+        <v>401040</v>
       </c>
       <c r="B167" t="s">
         <v>341</v>
       </c>
-      <c r="C167" s="3" t="s">
-        <v>335</v>
+      <c r="C167" t="s">
+        <v>342</v>
       </c>
     </row>
     <row r="168" spans="1:3">
       <c r="A168">
-        <v>401060</v>
+        <v>401050</v>
       </c>
       <c r="B168" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C168" s="3" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="169" spans="1:3">
       <c r="A169">
-        <v>401070</v>
+        <v>401060</v>
       </c>
       <c r="B169" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C169" s="3" t="s">
-        <v>344</v>
+        <v>337</v>
       </c>
     </row>
     <row r="170" spans="1:3">
       <c r="A170">
-        <v>401080</v>
+        <v>401070</v>
       </c>
       <c r="B170" t="s">
         <v>345</v>
@@ -42631,84 +42779,84 @@
     </row>
     <row r="171" spans="1:3">
       <c r="A171">
-        <v>402010</v>
+        <v>401080</v>
       </c>
       <c r="B171" t="s">
         <v>347</v>
       </c>
       <c r="C171" s="3" t="s">
-        <v>335</v>
+        <v>348</v>
       </c>
     </row>
     <row r="172" spans="1:3">
       <c r="A172">
-        <v>402020</v>
+        <v>402010</v>
       </c>
       <c r="B172" t="s">
-        <v>348</v>
-      </c>
-      <c r="C172" t="s">
         <v>349</v>
+      </c>
+      <c r="C172" s="3" t="s">
+        <v>337</v>
       </c>
     </row>
     <row r="173" spans="1:3">
       <c r="A173">
-        <v>402030</v>
+        <v>402020</v>
       </c>
       <c r="B173" t="s">
         <v>350</v>
       </c>
-      <c r="C173" s="3" t="s">
-        <v>344</v>
+      <c r="C173" t="s">
+        <v>351</v>
       </c>
     </row>
     <row r="174" spans="1:3">
       <c r="A174">
-        <v>402040</v>
+        <v>402030</v>
       </c>
       <c r="B174" t="s">
-        <v>351</v>
-      </c>
-      <c r="C174" s="4" t="s">
         <v>352</v>
+      </c>
+      <c r="C174" s="3" t="s">
+        <v>346</v>
       </c>
     </row>
     <row r="175" spans="1:3">
       <c r="A175">
-        <v>402050</v>
+        <v>402040</v>
       </c>
       <c r="B175" t="s">
         <v>353</v>
       </c>
-      <c r="C175" s="3" t="s">
-        <v>344</v>
+      <c r="C175" s="4" t="s">
+        <v>354</v>
       </c>
     </row>
     <row r="176" spans="1:3">
       <c r="A176">
-        <v>402060</v>
+        <v>402050</v>
       </c>
       <c r="B176" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C176" s="3" t="s">
-        <v>335</v>
+        <v>346</v>
       </c>
     </row>
     <row r="177" spans="1:3">
       <c r="A177">
-        <v>402070</v>
+        <v>402060</v>
       </c>
       <c r="B177" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C177" s="3" t="s">
-        <v>356</v>
+        <v>337</v>
       </c>
     </row>
     <row r="178" spans="1:3">
       <c r="A178">
-        <v>402080</v>
+        <v>402070</v>
       </c>
       <c r="B178" t="s">
         <v>357</v>
@@ -42719,51 +42867,51 @@
     </row>
     <row r="179" spans="1:3">
       <c r="A179">
-        <v>403010</v>
+        <v>402080</v>
       </c>
       <c r="B179" t="s">
         <v>359</v>
       </c>
       <c r="C179" s="3" t="s">
-        <v>335</v>
+        <v>360</v>
       </c>
     </row>
     <row r="180" spans="1:3">
       <c r="A180">
-        <v>403020</v>
+        <v>403010</v>
       </c>
       <c r="B180" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C180" s="3" t="s">
-        <v>361</v>
+        <v>337</v>
       </c>
     </row>
     <row r="181" spans="1:3">
       <c r="A181">
-        <v>403030</v>
+        <v>403020</v>
       </c>
       <c r="B181" t="s">
         <v>362</v>
       </c>
-      <c r="C181" s="4" t="s">
+      <c r="C181" s="3" t="s">
         <v>363</v>
       </c>
     </row>
     <row r="182" spans="1:3">
       <c r="A182">
-        <v>403040</v>
+        <v>403030</v>
       </c>
       <c r="B182" t="s">
         <v>364</v>
       </c>
-      <c r="C182" s="3" t="s">
+      <c r="C182" s="4" t="s">
         <v>365</v>
       </c>
     </row>
     <row r="183" spans="1:3">
       <c r="A183">
-        <v>403050</v>
+        <v>403040</v>
       </c>
       <c r="B183" t="s">
         <v>366</v>
@@ -42774,18 +42922,18 @@
     </row>
     <row r="184" spans="1:3">
       <c r="A184">
-        <v>403060</v>
+        <v>403050</v>
       </c>
       <c r="B184" t="s">
         <v>368</v>
       </c>
-      <c r="C184" s="4" t="s">
+      <c r="C184" s="3" t="s">
         <v>369</v>
       </c>
     </row>
     <row r="185" spans="1:3">
       <c r="A185">
-        <v>403070</v>
+        <v>403060</v>
       </c>
       <c r="B185" t="s">
         <v>370</v>
@@ -42796,51 +42944,51 @@
     </row>
     <row r="186" spans="1:3">
       <c r="A186">
-        <v>403080</v>
+        <v>403070</v>
       </c>
       <c r="B186" t="s">
         <v>372</v>
       </c>
-      <c r="C186" s="3" t="s">
+      <c r="C186" s="4" t="s">
         <v>373</v>
       </c>
     </row>
     <row r="187" spans="1:3">
       <c r="A187">
-        <v>404010</v>
+        <v>403080</v>
       </c>
       <c r="B187" t="s">
         <v>374</v>
       </c>
       <c r="C187" s="3" t="s">
-        <v>335</v>
+        <v>375</v>
       </c>
     </row>
     <row r="188" spans="1:3">
       <c r="A188">
-        <v>404020</v>
+        <v>404010</v>
       </c>
       <c r="B188" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C188" s="3" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="189" spans="1:3">
       <c r="A189">
-        <v>404030</v>
+        <v>404020</v>
       </c>
       <c r="B189" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="C189" s="3" t="s">
-        <v>377</v>
+        <v>337</v>
       </c>
     </row>
     <row r="190" spans="1:3">
       <c r="A190">
-        <v>404040</v>
+        <v>404030</v>
       </c>
       <c r="B190" t="s">
         <v>378</v>
@@ -42851,271 +42999,271 @@
     </row>
     <row r="191" spans="1:3">
       <c r="A191">
-        <v>404050</v>
+        <v>404040</v>
       </c>
       <c r="B191" t="s">
         <v>380</v>
       </c>
-      <c r="C191" s="4" t="s">
+      <c r="C191" s="3" t="s">
         <v>381</v>
       </c>
     </row>
     <row r="192" spans="1:3">
       <c r="A192">
-        <v>404060</v>
+        <v>404050</v>
       </c>
       <c r="B192" t="s">
         <v>382</v>
       </c>
-      <c r="C192" s="3" t="s">
-        <v>344</v>
+      <c r="C192" s="4" t="s">
+        <v>383</v>
       </c>
     </row>
     <row r="193" spans="1:3">
       <c r="A193">
-        <v>404070</v>
+        <v>404060</v>
       </c>
       <c r="B193" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C193" s="3" t="s">
-        <v>384</v>
+        <v>346</v>
       </c>
     </row>
     <row r="194" spans="1:3">
       <c r="A194">
-        <v>404080</v>
+        <v>404070</v>
       </c>
       <c r="B194" t="s">
         <v>385</v>
       </c>
       <c r="C194" s="3" t="s">
-        <v>344</v>
+        <v>386</v>
       </c>
     </row>
     <row r="195" spans="1:3">
       <c r="A195">
-        <v>405010</v>
+        <v>404080</v>
       </c>
       <c r="B195" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C195" s="3" t="s">
-        <v>335</v>
+        <v>346</v>
       </c>
     </row>
     <row r="196" spans="1:3">
       <c r="A196">
-        <v>405020</v>
+        <v>405010</v>
       </c>
       <c r="B196" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C196" s="3" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="197" spans="1:3">
       <c r="A197">
-        <v>405030</v>
+        <v>405020</v>
       </c>
       <c r="B197" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="C197" s="3" t="s">
-        <v>379</v>
+        <v>337</v>
       </c>
     </row>
     <row r="198" spans="1:3">
       <c r="A198">
-        <v>405040</v>
+        <v>405030</v>
       </c>
       <c r="B198" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C198" s="3" t="s">
-        <v>390</v>
+        <v>381</v>
       </c>
     </row>
     <row r="199" spans="1:3">
       <c r="A199">
-        <v>405050</v>
+        <v>405040</v>
       </c>
       <c r="B199" t="s">
         <v>391</v>
       </c>
       <c r="C199" s="3" t="s">
-        <v>358</v>
+        <v>392</v>
       </c>
     </row>
     <row r="200" spans="1:3">
       <c r="A200">
-        <v>405060</v>
+        <v>405050</v>
       </c>
       <c r="B200" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C200" s="3" t="s">
-        <v>393</v>
+        <v>360</v>
       </c>
     </row>
     <row r="201" spans="1:3">
       <c r="A201">
-        <v>405070</v>
+        <v>405060</v>
       </c>
       <c r="B201" t="s">
         <v>394</v>
       </c>
-      <c r="C201" s="4" t="s">
+      <c r="C201" s="3" t="s">
         <v>395</v>
       </c>
     </row>
     <row r="202" spans="1:3">
       <c r="A202">
-        <v>405080</v>
+        <v>405070</v>
       </c>
       <c r="B202" t="s">
         <v>396</v>
       </c>
-      <c r="C202" s="3" t="s">
+      <c r="C202" s="4" t="s">
         <v>397</v>
       </c>
     </row>
     <row r="203" spans="1:3">
       <c r="A203">
-        <v>411010</v>
+        <v>405080</v>
       </c>
       <c r="B203" t="s">
         <v>398</v>
       </c>
-      <c r="C203" s="4" t="s">
+      <c r="C203" s="3" t="s">
         <v>399</v>
       </c>
     </row>
     <row r="204" spans="1:3">
       <c r="A204">
-        <v>411020</v>
+        <v>411010</v>
       </c>
       <c r="B204" t="s">
         <v>400</v>
       </c>
       <c r="C204" s="4" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
     <row r="205" spans="1:3">
       <c r="A205">
-        <v>411030</v>
+        <v>411020</v>
       </c>
       <c r="B205" t="s">
+        <v>402</v>
+      </c>
+      <c r="C205" s="4" t="s">
         <v>401</v>
-      </c>
-      <c r="C205" s="4" t="s">
-        <v>402</v>
       </c>
     </row>
     <row r="206" spans="1:3">
       <c r="A206">
-        <v>411040</v>
+        <v>411030</v>
       </c>
       <c r="B206" t="s">
         <v>403</v>
       </c>
       <c r="C206" s="4" t="s">
-        <v>344</v>
+        <v>404</v>
       </c>
     </row>
     <row r="207" spans="1:3">
       <c r="A207">
-        <v>411050</v>
+        <v>411040</v>
       </c>
       <c r="B207" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C207" s="4" t="s">
-        <v>381</v>
+        <v>346</v>
       </c>
     </row>
     <row r="208" spans="1:3">
       <c r="A208">
-        <v>411060</v>
+        <v>411050</v>
       </c>
       <c r="B208" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C208" s="4" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
     <row r="209" spans="1:3">
       <c r="A209">
-        <v>411070</v>
+        <v>411060</v>
       </c>
       <c r="B209" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C209" s="4" t="s">
-        <v>399</v>
+        <v>383</v>
       </c>
     </row>
     <row r="210" spans="1:3">
       <c r="A210">
-        <v>411080</v>
+        <v>411070</v>
       </c>
       <c r="B210" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C210" s="4" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
     <row r="211" spans="1:3">
       <c r="A211">
-        <v>411090</v>
+        <v>411080</v>
       </c>
       <c r="B211" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C211" s="4" t="s">
-        <v>409</v>
+        <v>401</v>
       </c>
     </row>
     <row r="212" spans="1:3">
       <c r="A212">
-        <v>412010</v>
+        <v>411090</v>
       </c>
       <c r="B212" t="s">
         <v>410</v>
       </c>
-      <c r="C212" t="s">
+      <c r="C212" s="4" t="s">
         <v>411</v>
       </c>
     </row>
     <row r="213" spans="1:3">
       <c r="A213">
-        <v>412020</v>
+        <v>412010</v>
       </c>
       <c r="B213" t="s">
         <v>412</v>
       </c>
-      <c r="C213" s="4" t="s">
-        <v>349</v>
+      <c r="C213" t="s">
+        <v>413</v>
       </c>
     </row>
     <row r="214" spans="1:3">
       <c r="A214">
-        <v>412030</v>
+        <v>412020</v>
       </c>
       <c r="B214" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C214" s="4" t="s">
-        <v>414</v>
+        <v>351</v>
       </c>
     </row>
     <row r="215" spans="1:3">
       <c r="A215">
-        <v>412040</v>
+        <v>412030</v>
       </c>
       <c r="B215" t="s">
         <v>415</v>
@@ -43126,161 +43274,161 @@
     </row>
     <row r="216" spans="1:3">
       <c r="A216">
-        <v>412050</v>
+        <v>412040</v>
       </c>
       <c r="B216" t="s">
         <v>417</v>
       </c>
       <c r="C216" s="4" t="s">
-        <v>352</v>
+        <v>418</v>
       </c>
     </row>
     <row r="217" spans="1:3">
       <c r="A217">
-        <v>412060</v>
+        <v>412050</v>
       </c>
       <c r="B217" t="s">
-        <v>418</v>
-      </c>
-      <c r="C217" s="3" t="s">
-        <v>335</v>
+        <v>419</v>
+      </c>
+      <c r="C217" s="4" t="s">
+        <v>354</v>
       </c>
     </row>
     <row r="218" spans="1:3">
       <c r="A218">
-        <v>412070</v>
+        <v>412060</v>
       </c>
       <c r="B218" t="s">
-        <v>419</v>
-      </c>
-      <c r="C218" s="4" t="s">
-        <v>399</v>
+        <v>420</v>
+      </c>
+      <c r="C218" s="3" t="s">
+        <v>337</v>
       </c>
     </row>
     <row r="219" spans="1:3">
       <c r="A219">
-        <v>412080</v>
+        <v>412070</v>
       </c>
       <c r="B219" t="s">
-        <v>420</v>
-      </c>
-      <c r="C219" s="3" t="s">
-        <v>335</v>
+        <v>421</v>
+      </c>
+      <c r="C219" s="4" t="s">
+        <v>401</v>
       </c>
     </row>
     <row r="220" spans="1:3">
       <c r="A220">
-        <v>412090</v>
+        <v>412080</v>
       </c>
       <c r="B220" t="s">
-        <v>421</v>
-      </c>
-      <c r="C220" s="4" t="s">
         <v>422</v>
+      </c>
+      <c r="C220" s="3" t="s">
+        <v>337</v>
       </c>
     </row>
     <row r="221" spans="1:3">
       <c r="A221">
-        <v>413010</v>
+        <v>412090</v>
       </c>
       <c r="B221" t="s">
         <v>423</v>
       </c>
       <c r="C221" s="4" t="s">
-        <v>363</v>
+        <v>424</v>
       </c>
     </row>
     <row r="222" spans="1:3">
       <c r="A222">
-        <v>413020</v>
+        <v>413010</v>
       </c>
       <c r="B222" t="s">
-        <v>424</v>
-      </c>
-      <c r="C222" s="3" t="s">
+        <v>425</v>
+      </c>
+      <c r="C222" s="4" t="s">
         <v>365</v>
       </c>
     </row>
     <row r="223" spans="1:3">
       <c r="A223">
-        <v>413030</v>
+        <v>413020</v>
       </c>
       <c r="B223" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="C223" s="3" t="s">
-        <v>344</v>
+        <v>367</v>
       </c>
     </row>
     <row r="224" spans="1:3">
       <c r="A224">
-        <v>413040</v>
+        <v>413030</v>
       </c>
       <c r="B224" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C224" s="3" t="s">
-        <v>365</v>
+        <v>346</v>
       </c>
     </row>
     <row r="225" spans="1:3">
       <c r="A225">
-        <v>413050</v>
+        <v>413040</v>
       </c>
       <c r="B225" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C225" s="3" t="s">
-        <v>344</v>
+        <v>367</v>
       </c>
     </row>
     <row r="226" spans="1:3">
       <c r="A226">
-        <v>413060</v>
+        <v>413050</v>
       </c>
       <c r="B226" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C226" s="3" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="227" spans="1:3">
       <c r="A227">
-        <v>413070</v>
+        <v>413060</v>
       </c>
       <c r="B227" t="s">
-        <v>429</v>
-      </c>
-      <c r="C227" s="4" t="s">
         <v>430</v>
+      </c>
+      <c r="C227" s="3" t="s">
+        <v>346</v>
       </c>
     </row>
     <row r="228" spans="1:3">
       <c r="A228">
-        <v>413080</v>
+        <v>413070</v>
       </c>
       <c r="B228" t="s">
         <v>431</v>
       </c>
-      <c r="C228" s="3" t="s">
-        <v>379</v>
+      <c r="C228" s="4" t="s">
+        <v>432</v>
       </c>
     </row>
     <row r="229" spans="1:3">
       <c r="A229">
-        <v>413090</v>
+        <v>413080</v>
       </c>
       <c r="B229" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="C229" s="3" t="s">
-        <v>433</v>
+        <v>381</v>
       </c>
     </row>
     <row r="230" spans="1:3">
       <c r="A230">
-        <v>414010</v>
+        <v>413090</v>
       </c>
       <c r="B230" t="s">
         <v>434</v>
@@ -43291,7 +43439,7 @@
     </row>
     <row r="231" spans="1:3">
       <c r="A231">
-        <v>414020</v>
+        <v>414010</v>
       </c>
       <c r="B231" t="s">
         <v>436</v>
@@ -43302,178 +43450,189 @@
     </row>
     <row r="232" spans="1:3">
       <c r="A232">
-        <v>414030</v>
+        <v>414020</v>
       </c>
       <c r="B232" t="s">
         <v>438</v>
       </c>
       <c r="C232" s="3" t="s">
-        <v>356</v>
+        <v>439</v>
       </c>
     </row>
     <row r="233" spans="1:3">
       <c r="A233">
-        <v>414040</v>
+        <v>414030</v>
       </c>
       <c r="B233" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C233" s="3" t="s">
-        <v>384</v>
+        <v>358</v>
       </c>
     </row>
     <row r="234" spans="1:3">
       <c r="A234">
-        <v>414050</v>
+        <v>414040</v>
       </c>
       <c r="B234" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C234" s="3" t="s">
-        <v>441</v>
+        <v>386</v>
       </c>
     </row>
     <row r="235" spans="1:3">
       <c r="A235">
-        <v>414060</v>
+        <v>414050</v>
       </c>
       <c r="B235" t="s">
         <v>442</v>
       </c>
-      <c r="C235" s="4" t="s">
-        <v>381</v>
+      <c r="C235" s="3" t="s">
+        <v>443</v>
       </c>
     </row>
     <row r="236" spans="1:3">
       <c r="A236">
-        <v>414070</v>
+        <v>414060</v>
       </c>
       <c r="B236" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C236" s="4" t="s">
-        <v>444</v>
+        <v>383</v>
       </c>
     </row>
     <row r="237" spans="1:3">
       <c r="A237">
-        <v>414080</v>
+        <v>414070</v>
       </c>
       <c r="B237" t="s">
         <v>445</v>
       </c>
-      <c r="C237" s="3" t="s">
-        <v>384</v>
+      <c r="C237" s="4" t="s">
+        <v>446</v>
       </c>
     </row>
     <row r="238" spans="1:3">
       <c r="A238">
-        <v>414090</v>
+        <v>414080</v>
       </c>
       <c r="B238" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C238" s="3" t="s">
-        <v>344</v>
+        <v>386</v>
       </c>
     </row>
     <row r="239" spans="1:3">
       <c r="A239">
-        <v>415010</v>
+        <v>414090</v>
       </c>
       <c r="B239" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C239" s="3" t="s">
-        <v>448</v>
+        <v>346</v>
       </c>
     </row>
     <row r="240" spans="1:3">
       <c r="A240">
-        <v>415020</v>
+        <v>415010</v>
       </c>
       <c r="B240" t="s">
         <v>449</v>
       </c>
       <c r="C240" s="3" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
     </row>
     <row r="241" spans="1:3">
       <c r="A241">
-        <v>415030</v>
+        <v>415020</v>
       </c>
       <c r="B241" t="s">
+        <v>451</v>
+      </c>
+      <c r="C241" s="3" t="s">
         <v>450</v>
-      </c>
-      <c r="C241" s="4" t="s">
-        <v>381</v>
       </c>
     </row>
     <row r="242" spans="1:3">
       <c r="A242">
-        <v>415040</v>
+        <v>415030</v>
       </c>
       <c r="B242" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C242" s="4" t="s">
-        <v>452</v>
+        <v>383</v>
       </c>
     </row>
     <row r="243" spans="1:3">
       <c r="A243">
-        <v>415050</v>
+        <v>415040</v>
       </c>
       <c r="B243" t="s">
         <v>453</v>
       </c>
-      <c r="C243" s="3" t="s">
-        <v>379</v>
+      <c r="C243" s="4" t="s">
+        <v>454</v>
       </c>
     </row>
     <row r="244" spans="1:3">
       <c r="A244">
-        <v>415060</v>
+        <v>415050</v>
       </c>
       <c r="B244" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="C244" s="3" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
     </row>
     <row r="245" spans="1:3">
       <c r="A245">
-        <v>415070</v>
+        <v>415060</v>
       </c>
       <c r="B245" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C245" s="3" t="s">
-        <v>448</v>
+        <v>381</v>
       </c>
     </row>
     <row r="246" spans="1:3">
       <c r="A246">
-        <v>415080</v>
+        <v>415070</v>
       </c>
       <c r="B246" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C246" s="3" t="s">
-        <v>457</v>
+        <v>450</v>
       </c>
     </row>
     <row r="247" spans="1:3">
       <c r="A247">
-        <v>415090</v>
+        <v>415080</v>
       </c>
       <c r="B247" t="s">
         <v>458</v>
       </c>
       <c r="C247" s="3" t="s">
         <v>459</v>
+      </c>
+    </row>
+    <row r="248" spans="1:3">
+      <c r="A248">
+        <v>415090</v>
+      </c>
+      <c r="B248" t="s">
+        <v>460</v>
+      </c>
+      <c r="C248" s="3" t="s">
+        <v>461</v>
       </c>
     </row>
   </sheetData>
@@ -43485,7 +43644,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AC132"/>
+  <dimension ref="A1:AC133"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13"/>
   <cols>
     <col min="3" max="3" width="1.72727272727273" customWidth="1"/>
@@ -43513,19 +43672,19 @@
         <v>12</v>
       </c>
       <c r="M1" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="P1" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="S1" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="U1" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="W1" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="Y1" t="s">
         <v>25</v>
@@ -43536,61 +43695,61 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="D2">
         <v>0</v>
       </c>
       <c r="E2" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="G2">
         <v>0</v>
       </c>
       <c r="H2" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="J2">
         <v>0</v>
       </c>
       <c r="K2" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="M2">
         <v>0</v>
       </c>
       <c r="N2" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="P2">
         <v>0</v>
       </c>
       <c r="Q2" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="U2">
         <v>0</v>
       </c>
       <c r="V2" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="W2">
         <v>0</v>
       </c>
       <c r="X2" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="Y2">
         <v>0</v>
       </c>
       <c r="Z2" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="AB2">
         <v>301</v>
       </c>
       <c r="AC2" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="3" spans="1:29">
@@ -43598,61 +43757,61 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="D3">
         <v>1</v>
       </c>
       <c r="E3" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="G3">
         <v>1</v>
       </c>
       <c r="H3" t="s">
+        <v>472</v>
+      </c>
+      <c r="J3">
+        <v>1</v>
+      </c>
+      <c r="K3" t="s">
+        <v>473</v>
+      </c>
+      <c r="M3">
+        <v>1</v>
+      </c>
+      <c r="N3" t="s">
         <v>470</v>
-      </c>
-      <c r="J3">
-        <v>1</v>
-      </c>
-      <c r="K3" t="s">
-        <v>471</v>
-      </c>
-      <c r="M3">
-        <v>1</v>
-      </c>
-      <c r="N3" t="s">
-        <v>468</v>
       </c>
       <c r="P3">
         <v>1010</v>
       </c>
       <c r="Q3" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="U3">
         <v>1010</v>
       </c>
       <c r="V3" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="W3">
         <v>1</v>
       </c>
       <c r="X3" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="Y3">
         <v>1</v>
       </c>
       <c r="Z3" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="AB3">
         <v>302</v>
       </c>
       <c r="AC3" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
     </row>
     <row r="4" spans="1:29">
@@ -43660,61 +43819,61 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="D4">
         <v>2</v>
       </c>
       <c r="E4" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="G4">
         <v>2</v>
       </c>
       <c r="H4" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="J4">
         <v>2</v>
       </c>
       <c r="K4" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="M4">
         <v>2</v>
       </c>
       <c r="N4" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="P4">
         <v>1020</v>
       </c>
       <c r="Q4" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="U4">
         <v>1020</v>
       </c>
       <c r="V4" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="W4">
         <v>2</v>
       </c>
       <c r="X4" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="Y4">
         <v>2</v>
       </c>
       <c r="Z4" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="AB4" s="2">
         <v>303</v>
       </c>
       <c r="AC4" s="2" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
     </row>
     <row r="5" spans="1:29">
@@ -43722,61 +43881,61 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="D5">
         <v>3</v>
       </c>
       <c r="E5" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="G5">
         <v>3</v>
       </c>
       <c r="H5" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="J5">
         <v>3</v>
       </c>
       <c r="K5" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="M5">
         <v>3</v>
       </c>
       <c r="N5" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="P5">
         <v>1030</v>
       </c>
       <c r="Q5" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="U5">
         <v>1030</v>
       </c>
       <c r="V5" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="W5">
         <v>3</v>
       </c>
       <c r="X5" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="Y5">
         <v>3</v>
       </c>
       <c r="Z5" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="AB5">
         <v>304</v>
       </c>
       <c r="AC5" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
     </row>
     <row r="6" spans="4:29">
@@ -43784,7 +43943,7 @@
         <v>4</v>
       </c>
       <c r="E6" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="G6">
         <v>4</v>
@@ -43796,43 +43955,43 @@
         <v>4</v>
       </c>
       <c r="K6" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="M6">
         <v>4</v>
       </c>
       <c r="N6" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="P6">
         <v>1040</v>
       </c>
       <c r="Q6" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="U6">
         <v>1040</v>
       </c>
       <c r="V6" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="W6">
         <v>4</v>
       </c>
       <c r="X6" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="Y6">
         <v>4</v>
       </c>
       <c r="Z6" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="AB6">
         <v>305</v>
       </c>
       <c r="AC6" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
     </row>
     <row r="7" spans="4:29">
@@ -43840,55 +43999,55 @@
         <v>5</v>
       </c>
       <c r="E7" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="G7">
         <v>5</v>
       </c>
       <c r="H7" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="J7">
         <v>6</v>
       </c>
       <c r="K7" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="M7">
         <v>5</v>
       </c>
       <c r="N7" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="P7">
         <v>1050</v>
       </c>
       <c r="Q7" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="U7">
         <v>1050</v>
       </c>
       <c r="V7" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="W7">
         <v>5</v>
       </c>
       <c r="X7" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="Y7">
         <v>5</v>
       </c>
       <c r="Z7" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="AB7">
         <v>306</v>
       </c>
       <c r="AC7" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
     </row>
     <row r="8" spans="4:29">
@@ -43896,55 +44055,55 @@
         <v>6</v>
       </c>
       <c r="E8" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="G8">
         <v>6</v>
       </c>
       <c r="H8" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="J8">
         <v>7</v>
       </c>
       <c r="K8" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="M8">
         <v>11</v>
       </c>
       <c r="N8" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="P8">
         <v>1060</v>
       </c>
       <c r="Q8" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="U8">
         <v>1060</v>
       </c>
       <c r="V8" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="W8">
         <v>6</v>
       </c>
       <c r="X8" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="Y8">
         <v>11</v>
       </c>
       <c r="Z8" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="AB8">
         <v>307</v>
       </c>
       <c r="AC8" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
     </row>
     <row r="9" spans="7:29">
@@ -43952,49 +44111,49 @@
         <v>11</v>
       </c>
       <c r="H9" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="J9">
         <v>11</v>
       </c>
       <c r="K9" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="M9">
         <v>12</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="P9">
         <v>1070</v>
       </c>
       <c r="Q9" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="U9">
         <v>1130</v>
       </c>
       <c r="V9" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="W9">
         <v>7</v>
       </c>
       <c r="X9" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="Y9">
         <v>20</v>
       </c>
       <c r="Z9" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="AB9">
         <v>308</v>
       </c>
       <c r="AC9" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
     </row>
     <row r="10" spans="7:29">
@@ -44002,49 +44161,49 @@
         <v>12</v>
       </c>
       <c r="H10" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="J10">
         <v>101</v>
       </c>
       <c r="K10" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="M10">
         <v>13</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="P10">
         <v>1080</v>
       </c>
       <c r="Q10" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="U10">
         <v>1140</v>
       </c>
       <c r="V10" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="W10">
         <v>10</v>
       </c>
       <c r="X10" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="Y10">
         <v>24</v>
       </c>
       <c r="Z10" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="AB10">
         <v>309</v>
       </c>
       <c r="AC10" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
     </row>
     <row r="11" spans="13:29">
@@ -44052,19 +44211,19 @@
         <v>21</v>
       </c>
       <c r="N11" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="P11">
         <v>1090</v>
       </c>
       <c r="Q11" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="U11">
         <v>1150</v>
       </c>
       <c r="V11" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="W11">
         <v>11</v>
@@ -44076,13 +44235,13 @@
         <v>31</v>
       </c>
       <c r="Z11" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="AB11">
         <v>310</v>
       </c>
       <c r="AC11" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
     </row>
     <row r="12" spans="13:29">
@@ -44090,37 +44249,37 @@
         <v>31</v>
       </c>
       <c r="N12" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="P12">
         <v>1100</v>
       </c>
       <c r="Q12" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="U12">
         <v>1160</v>
       </c>
       <c r="V12" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="W12">
         <v>99</v>
       </c>
       <c r="X12" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="Y12">
         <v>32</v>
       </c>
       <c r="Z12" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="AB12">
         <v>311</v>
       </c>
       <c r="AC12" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
     </row>
     <row r="13" spans="13:29">
@@ -44128,34 +44287,34 @@
         <v>32</v>
       </c>
       <c r="N13" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="P13">
         <v>1110</v>
       </c>
       <c r="Q13" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="U13">
         <v>2010</v>
       </c>
       <c r="V13" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="W13" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="Y13">
         <v>33</v>
       </c>
       <c r="Z13" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="AB13">
         <v>401</v>
       </c>
       <c r="AC13" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
     </row>
     <row r="14" spans="16:29">
@@ -44163,25 +44322,25 @@
         <v>2010</v>
       </c>
       <c r="Q14" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="U14">
         <v>3010</v>
       </c>
       <c r="V14" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="Y14">
         <v>41</v>
       </c>
       <c r="Z14" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="AB14">
         <v>402</v>
       </c>
       <c r="AC14" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
     </row>
     <row r="15" spans="16:29">
@@ -44189,25 +44348,25 @@
         <v>2020</v>
       </c>
       <c r="Q15" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="U15">
         <v>3020</v>
       </c>
       <c r="V15" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="Y15">
         <v>51</v>
       </c>
       <c r="Z15" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="AB15">
         <v>403</v>
       </c>
       <c r="AC15" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
     </row>
     <row r="16" spans="16:29">
@@ -44215,25 +44374,25 @@
         <v>2030</v>
       </c>
       <c r="Q16" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="U16">
         <v>3030</v>
       </c>
       <c r="V16" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="Y16">
         <v>52</v>
       </c>
       <c r="Z16" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="AB16">
         <v>404</v>
       </c>
       <c r="AC16" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
     </row>
     <row r="17" spans="16:29">
@@ -44241,19 +44400,19 @@
         <v>2040</v>
       </c>
       <c r="Q17" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="U17">
         <v>3040</v>
       </c>
       <c r="V17" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="AB17">
         <v>501</v>
       </c>
       <c r="AC17" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
     </row>
     <row r="18" spans="16:29">
@@ -44261,19 +44420,19 @@
         <v>2110</v>
       </c>
       <c r="Q18" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="U18">
         <v>3050</v>
       </c>
       <c r="V18" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="AB18">
         <v>502</v>
       </c>
       <c r="AC18" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
     </row>
     <row r="19" spans="16:29">
@@ -44281,19 +44440,19 @@
         <v>2120</v>
       </c>
       <c r="Q19" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="U19">
         <v>3060</v>
       </c>
       <c r="V19" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="AB19">
         <v>503</v>
       </c>
       <c r="AC19" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
     </row>
     <row r="20" spans="16:29">
@@ -44301,19 +44460,19 @@
         <v>2130</v>
       </c>
       <c r="Q20" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="U20">
         <v>4010</v>
       </c>
       <c r="V20" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="AB20">
         <v>504</v>
       </c>
       <c r="AC20" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
     </row>
     <row r="21" spans="16:29">
@@ -44321,19 +44480,19 @@
         <v>3010</v>
       </c>
       <c r="Q21" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="U21">
         <v>4020</v>
       </c>
       <c r="V21" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="AB21">
         <v>505</v>
       </c>
       <c r="AC21" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
     </row>
     <row r="22" spans="16:29">
@@ -44341,19 +44500,19 @@
         <v>3020</v>
       </c>
       <c r="Q22" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="U22">
         <v>5010</v>
       </c>
       <c r="V22" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="AB22">
         <v>506</v>
       </c>
       <c r="AC22" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
     </row>
     <row r="23" spans="16:29">
@@ -44361,19 +44520,19 @@
         <v>3030</v>
       </c>
       <c r="Q23" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="U23">
         <v>5020</v>
       </c>
       <c r="V23" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="AB23">
         <v>507</v>
       </c>
       <c r="AC23" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
     </row>
     <row r="24" spans="16:29">
@@ -44381,19 +44540,19 @@
         <v>3040</v>
       </c>
       <c r="Q24" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="U24">
         <v>5030</v>
       </c>
       <c r="V24" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="AB24">
         <v>508</v>
       </c>
       <c r="AC24" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
     </row>
     <row r="25" spans="16:29">
@@ -44401,19 +44560,19 @@
         <v>3050</v>
       </c>
       <c r="Q25" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="U25">
         <v>5040</v>
       </c>
       <c r="V25" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="AB25">
         <v>509</v>
       </c>
       <c r="AC25" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
     </row>
     <row r="26" spans="16:22">
@@ -44421,13 +44580,13 @@
         <v>3060</v>
       </c>
       <c r="Q26" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="U26">
         <v>5050</v>
       </c>
       <c r="V26" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
     </row>
     <row r="27" spans="16:22">
@@ -44435,13 +44594,13 @@
         <v>3070</v>
       </c>
       <c r="Q27" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="U27">
         <v>5060</v>
       </c>
       <c r="V27" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
     </row>
     <row r="28" spans="16:22">
@@ -44449,13 +44608,13 @@
         <v>4010</v>
       </c>
       <c r="Q28" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="U28">
         <v>5070</v>
       </c>
       <c r="V28" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
     </row>
     <row r="29" spans="16:22">
@@ -44463,13 +44622,13 @@
         <v>4020</v>
       </c>
       <c r="Q29" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="U29">
         <v>5080</v>
       </c>
       <c r="V29" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
     </row>
     <row r="30" spans="16:22">
@@ -44477,13 +44636,13 @@
         <v>4030</v>
       </c>
       <c r="Q30" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="U30">
         <v>5090</v>
       </c>
       <c r="V30" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
     </row>
     <row r="31" spans="16:22">
@@ -44491,13 +44650,13 @@
         <v>4040</v>
       </c>
       <c r="Q31" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="U31">
         <v>5100</v>
       </c>
       <c r="V31" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
     </row>
     <row r="32" spans="16:22">
@@ -44505,13 +44664,13 @@
         <v>5010</v>
       </c>
       <c r="Q32" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="U32">
         <v>5110</v>
       </c>
       <c r="V32" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
     <row r="33" spans="16:22">
@@ -44519,13 +44678,13 @@
         <v>5011</v>
       </c>
       <c r="Q33" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="U33">
         <v>5120</v>
       </c>
       <c r="V33" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
     </row>
     <row r="34" spans="16:22">
@@ -44533,13 +44692,13 @@
         <v>5012</v>
       </c>
       <c r="Q34" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="U34">
         <v>5130</v>
       </c>
       <c r="V34" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
     </row>
     <row r="35" spans="16:22">
@@ -44547,13 +44706,13 @@
         <v>5020</v>
       </c>
       <c r="Q35" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="U35">
         <v>5140</v>
       </c>
       <c r="V35" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
     </row>
     <row r="36" spans="16:22">
@@ -44561,13 +44720,13 @@
         <v>5030</v>
       </c>
       <c r="Q36" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="U36">
         <v>5150</v>
       </c>
       <c r="V36" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
     </row>
     <row r="37" spans="16:22">
@@ -44575,13 +44734,13 @@
         <v>5040</v>
       </c>
       <c r="Q37" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="U37">
         <v>6010</v>
       </c>
       <c r="V37" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
     </row>
     <row r="38" spans="16:22">
@@ -44589,13 +44748,13 @@
         <v>5050</v>
       </c>
       <c r="Q38" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="U38">
         <v>6020</v>
       </c>
       <c r="V38" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
     </row>
     <row r="39" spans="16:22">
@@ -44603,13 +44762,13 @@
         <v>6010</v>
       </c>
       <c r="Q39" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="U39">
         <v>6030</v>
       </c>
       <c r="V39" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
     </row>
     <row r="40" spans="16:22">
@@ -44617,13 +44776,13 @@
         <v>6020</v>
       </c>
       <c r="Q40" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="U40">
         <v>6040</v>
       </c>
       <c r="V40" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
     </row>
     <row r="41" spans="16:22">
@@ -44631,13 +44790,13 @@
         <v>6030</v>
       </c>
       <c r="Q41" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="U41">
         <v>6050</v>
       </c>
       <c r="V41" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
     </row>
     <row r="42" spans="16:22">
@@ -44645,13 +44804,13 @@
         <v>6040</v>
       </c>
       <c r="Q42" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="U42">
         <v>6060</v>
       </c>
       <c r="V42" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
     </row>
     <row r="43" spans="16:22">
@@ -44659,13 +44818,13 @@
         <v>6050</v>
       </c>
       <c r="Q43" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="U43">
         <v>6110</v>
       </c>
       <c r="V43" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
     </row>
     <row r="44" spans="16:22">
@@ -44673,13 +44832,13 @@
         <v>6060</v>
       </c>
       <c r="Q44" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="U44">
         <v>6120</v>
       </c>
       <c r="V44" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
     </row>
     <row r="45" spans="16:22">
@@ -44687,13 +44846,13 @@
         <v>6070</v>
       </c>
       <c r="Q45" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="U45">
         <v>6130</v>
       </c>
       <c r="V45" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
     </row>
     <row r="46" spans="16:22">
@@ -44701,13 +44860,13 @@
         <v>6080</v>
       </c>
       <c r="Q46" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="U46">
         <v>6140</v>
       </c>
       <c r="V46" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
     </row>
     <row r="47" spans="16:22">
@@ -44715,13 +44874,13 @@
         <v>6100</v>
       </c>
       <c r="Q47" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="U47">
         <v>6150</v>
       </c>
       <c r="V47" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
     </row>
     <row r="48" spans="16:22">
@@ -44729,13 +44888,13 @@
         <v>6210</v>
       </c>
       <c r="Q48" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="U48">
         <v>6210</v>
       </c>
       <c r="V48" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
     </row>
     <row r="49" spans="16:22">
@@ -44743,13 +44902,13 @@
         <v>6310</v>
       </c>
       <c r="Q49" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="U49">
         <v>6220</v>
       </c>
       <c r="V49" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
     </row>
     <row r="50" spans="16:22">
@@ -44757,13 +44916,13 @@
         <v>7010</v>
       </c>
       <c r="Q50" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="U50">
         <v>6230</v>
       </c>
       <c r="V50" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
     </row>
     <row r="51" spans="16:22">
@@ -44771,13 +44930,13 @@
         <v>7020</v>
       </c>
       <c r="Q51" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="U51">
         <v>6240</v>
       </c>
       <c r="V51" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
     </row>
     <row r="52" spans="16:22">
@@ -44785,13 +44944,13 @@
         <v>7030</v>
       </c>
       <c r="Q52" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="U52">
         <v>6250</v>
       </c>
       <c r="V52" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
     </row>
     <row r="53" spans="16:22">
@@ -44799,13 +44958,13 @@
         <v>8010</v>
       </c>
       <c r="Q53" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="U53">
         <v>6310</v>
       </c>
       <c r="V53" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
     </row>
     <row r="54" spans="16:22">
@@ -44813,13 +44972,13 @@
         <v>8020</v>
       </c>
       <c r="Q54" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="U54">
         <v>6320</v>
       </c>
       <c r="V54" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
     </row>
     <row r="55" spans="16:22">
@@ -44827,13 +44986,13 @@
         <v>9010</v>
       </c>
       <c r="Q55" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="U55">
         <v>6330</v>
       </c>
       <c r="V55" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
     </row>
     <row r="56" spans="16:22">
@@ -44841,13 +45000,13 @@
         <v>10010</v>
       </c>
       <c r="Q56" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="U56">
         <v>6340</v>
       </c>
       <c r="V56" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
     </row>
     <row r="57" spans="16:22">
@@ -44855,13 +45014,13 @@
         <v>10020</v>
       </c>
       <c r="Q57" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="U57">
         <v>6350</v>
       </c>
       <c r="V57" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
     </row>
     <row r="58" spans="16:22">
@@ -44869,13 +45028,13 @@
         <v>11010</v>
       </c>
       <c r="Q58" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="U58">
         <v>7010</v>
       </c>
       <c r="V58" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
     </row>
     <row r="59" spans="16:22">
@@ -44883,13 +45042,13 @@
         <v>12010</v>
       </c>
       <c r="Q59" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="U59">
         <v>7020</v>
       </c>
       <c r="V59" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
     </row>
     <row r="60" spans="16:22">
@@ -44897,13 +45056,13 @@
         <v>13010</v>
       </c>
       <c r="Q60" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="U60">
         <v>7030</v>
       </c>
       <c r="V60" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
     </row>
     <row r="61" spans="21:22">
@@ -44911,7 +45070,7 @@
         <v>7040</v>
       </c>
       <c r="V61" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
     </row>
     <row r="62" spans="21:22">
@@ -44919,7 +45078,7 @@
         <v>7050</v>
       </c>
       <c r="V62" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
     </row>
     <row r="63" spans="21:22">
@@ -44927,7 +45086,7 @@
         <v>7060</v>
       </c>
       <c r="V63" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
     </row>
     <row r="64" spans="21:22">
@@ -44935,7 +45094,7 @@
         <v>7070</v>
       </c>
       <c r="V64" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
     </row>
     <row r="65" spans="21:22">
@@ -44943,7 +45102,7 @@
         <v>8010</v>
       </c>
       <c r="V65" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
     </row>
     <row r="66" spans="21:22">
@@ -44951,7 +45110,7 @@
         <v>8020</v>
       </c>
       <c r="V66" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
     </row>
     <row r="67" spans="21:22">
@@ -44959,7 +45118,7 @@
         <v>8030</v>
       </c>
       <c r="V67" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
     </row>
     <row r="68" spans="21:22">
@@ -44967,7 +45126,7 @@
         <v>8040</v>
       </c>
       <c r="V68" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
     </row>
     <row r="69" spans="21:22">
@@ -44975,7 +45134,7 @@
         <v>8050</v>
       </c>
       <c r="V69" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
     </row>
     <row r="70" spans="21:22">
@@ -44983,7 +45142,7 @@
         <v>8060</v>
       </c>
       <c r="V70" t="s">
-        <v>668</v>
+        <v>670</v>
       </c>
     </row>
     <row r="71" spans="21:22">
@@ -44991,7 +45150,7 @@
         <v>9010</v>
       </c>
       <c r="V71" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
     </row>
     <row r="72" spans="21:22">
@@ -44999,7 +45158,7 @@
         <v>9020</v>
       </c>
       <c r="V72" t="s">
-        <v>670</v>
+        <v>672</v>
       </c>
     </row>
     <row r="73" spans="21:22">
@@ -45007,7 +45166,7 @@
         <v>9030</v>
       </c>
       <c r="V73" t="s">
-        <v>671</v>
+        <v>673</v>
       </c>
     </row>
     <row r="74" spans="21:22">
@@ -45015,7 +45174,7 @@
         <v>9031</v>
       </c>
       <c r="V74" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
     </row>
     <row r="75" spans="21:22">
@@ -45023,7 +45182,7 @@
         <v>9040</v>
       </c>
       <c r="V75" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
     </row>
     <row r="76" spans="21:22">
@@ -45031,7 +45190,7 @@
         <v>9110</v>
       </c>
       <c r="V76" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
     </row>
     <row r="77" spans="21:22">
@@ -45039,7 +45198,7 @@
         <v>9120</v>
       </c>
       <c r="V77" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
     </row>
     <row r="78" spans="21:22">
@@ -45047,7 +45206,7 @@
         <v>10010</v>
       </c>
       <c r="V78" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
     </row>
     <row r="79" spans="21:22">
@@ -45055,7 +45214,7 @@
         <v>10020</v>
       </c>
       <c r="V79" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
     </row>
     <row r="80" spans="21:22">
@@ -45063,7 +45222,7 @@
         <v>10110</v>
       </c>
       <c r="V80" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
     </row>
     <row r="81" spans="21:22">
@@ -45071,7 +45230,7 @@
         <v>11010</v>
       </c>
       <c r="V81" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
     </row>
     <row r="82" spans="21:22">
@@ -45079,7 +45238,7 @@
         <v>11020</v>
       </c>
       <c r="V82" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
     </row>
     <row r="83" spans="21:22">
@@ -45087,7 +45246,7 @@
         <v>12030</v>
       </c>
       <c r="V83" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
     </row>
     <row r="84" spans="21:22">
@@ -45095,7 +45254,7 @@
         <v>12040</v>
       </c>
       <c r="V84" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
     </row>
     <row r="85" spans="21:22">
@@ -45103,7 +45262,7 @@
         <v>12041</v>
       </c>
       <c r="V85" t="s">
-        <v>683</v>
+        <v>685</v>
       </c>
     </row>
     <row r="86" spans="21:22">
@@ -45111,7 +45270,7 @@
         <v>12042</v>
       </c>
       <c r="V86" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
     </row>
     <row r="87" spans="21:22">
@@ -45119,7 +45278,7 @@
         <v>12043</v>
       </c>
       <c r="V87" t="s">
-        <v>685</v>
+        <v>687</v>
       </c>
     </row>
     <row r="88" spans="21:22">
@@ -45127,7 +45286,7 @@
         <v>12050</v>
       </c>
       <c r="V88" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
     </row>
     <row r="89" spans="21:22">
@@ -45135,7 +45294,7 @@
         <v>12060</v>
       </c>
       <c r="V89" t="s">
-        <v>687</v>
+        <v>689</v>
       </c>
     </row>
     <row r="90" spans="21:22">
@@ -45143,7 +45302,7 @@
         <v>12063</v>
       </c>
       <c r="V90" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
     </row>
     <row r="91" spans="21:22">
@@ -45151,7 +45310,7 @@
         <v>12064</v>
       </c>
       <c r="V91" t="s">
-        <v>689</v>
+        <v>691</v>
       </c>
     </row>
     <row r="92" spans="21:22">
@@ -45159,7 +45318,7 @@
         <v>12066</v>
       </c>
       <c r="V92" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
     </row>
     <row r="93" spans="21:22">
@@ -45167,7 +45326,7 @@
         <v>12070</v>
       </c>
       <c r="V93" t="s">
-        <v>691</v>
+        <v>693</v>
       </c>
     </row>
     <row r="94" spans="21:22">
@@ -45175,7 +45334,7 @@
         <v>12071</v>
       </c>
       <c r="V94" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
     </row>
     <row r="95" spans="21:22">
@@ -45183,7 +45342,7 @@
         <v>12082</v>
       </c>
       <c r="V95" t="s">
-        <v>693</v>
+        <v>695</v>
       </c>
     </row>
     <row r="96" spans="21:22">
@@ -45191,7 +45350,7 @@
         <v>12092</v>
       </c>
       <c r="V96" t="s">
-        <v>694</v>
+        <v>696</v>
       </c>
     </row>
     <row r="97" spans="21:22">
@@ -45199,7 +45358,7 @@
         <v>13010</v>
       </c>
       <c r="V97" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
     </row>
     <row r="98" spans="21:22">
@@ -45207,7 +45366,7 @@
         <v>13020</v>
       </c>
       <c r="V98" t="s">
-        <v>696</v>
+        <v>698</v>
       </c>
     </row>
     <row r="99" spans="21:22">
@@ -45215,7 +45374,7 @@
         <v>14010</v>
       </c>
       <c r="V99" t="s">
-        <v>697</v>
+        <v>699</v>
       </c>
     </row>
     <row r="100" spans="21:22">
@@ -45223,7 +45382,7 @@
         <v>14110</v>
       </c>
       <c r="V100" t="s">
-        <v>698</v>
+        <v>700</v>
       </c>
     </row>
     <row r="101" spans="21:22">
@@ -45231,7 +45390,7 @@
         <v>14210</v>
       </c>
       <c r="V101" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
     </row>
     <row r="102" spans="21:22">
@@ -45239,7 +45398,7 @@
         <v>14310</v>
       </c>
       <c r="V102" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
     </row>
     <row r="103" spans="21:22">
@@ -45247,7 +45406,7 @@
         <v>14410</v>
       </c>
       <c r="V103" t="s">
-        <v>701</v>
+        <v>703</v>
       </c>
     </row>
     <row r="104" spans="21:22">
@@ -45255,7 +45414,7 @@
         <v>15010</v>
       </c>
       <c r="V104" t="s">
-        <v>702</v>
+        <v>704</v>
       </c>
     </row>
     <row r="105" spans="21:22">
@@ -45263,7 +45422,7 @@
         <v>15011</v>
       </c>
       <c r="V105" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
     </row>
     <row r="106" spans="21:22">
@@ -45271,7 +45430,7 @@
         <v>15022</v>
       </c>
       <c r="V106" t="s">
-        <v>704</v>
+        <v>706</v>
       </c>
     </row>
     <row r="107" spans="21:22">
@@ -45279,7 +45438,7 @@
         <v>16010</v>
       </c>
       <c r="V107" t="s">
-        <v>705</v>
+        <v>707</v>
       </c>
     </row>
     <row r="108" spans="21:22">
@@ -45287,7 +45446,7 @@
         <v>17010</v>
       </c>
       <c r="V108" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
     </row>
     <row r="109" spans="21:22">
@@ -45295,7 +45454,7 @@
         <v>17020</v>
       </c>
       <c r="V109" t="s">
-        <v>707</v>
+        <v>709</v>
       </c>
     </row>
     <row r="110" spans="21:22">
@@ -45303,7 +45462,7 @@
         <v>17030</v>
       </c>
       <c r="V110" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
     </row>
     <row r="111" spans="21:22">
@@ -45311,7 +45470,7 @@
         <v>17040</v>
       </c>
       <c r="V111" t="s">
-        <v>709</v>
+        <v>711</v>
       </c>
     </row>
     <row r="112" spans="21:22">
@@ -45319,7 +45478,7 @@
         <v>17050</v>
       </c>
       <c r="V112" t="s">
-        <v>710</v>
+        <v>712</v>
       </c>
     </row>
     <row r="113" spans="21:22">
@@ -45327,7 +45486,7 @@
         <v>17060</v>
       </c>
       <c r="V113" t="s">
-        <v>711</v>
+        <v>713</v>
       </c>
     </row>
     <row r="114" spans="21:22">
@@ -45335,7 +45494,7 @@
         <v>18010</v>
       </c>
       <c r="V114" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
     </row>
     <row r="115" spans="21:22">
@@ -45343,7 +45502,7 @@
         <v>18020</v>
       </c>
       <c r="V115" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
     </row>
     <row r="116" spans="21:22">
@@ -45351,7 +45510,7 @@
         <v>19010</v>
       </c>
       <c r="V116" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
     </row>
     <row r="117" spans="21:22">
@@ -45359,7 +45518,7 @@
         <v>19020</v>
       </c>
       <c r="V117" t="s">
-        <v>715</v>
+        <v>717</v>
       </c>
     </row>
     <row r="118" spans="21:22">
@@ -45367,7 +45526,7 @@
         <v>19030</v>
       </c>
       <c r="V118" t="s">
-        <v>716</v>
+        <v>718</v>
       </c>
     </row>
     <row r="119" spans="21:22">
@@ -45375,7 +45534,7 @@
         <v>20030</v>
       </c>
       <c r="V119" t="s">
-        <v>717</v>
+        <v>719</v>
       </c>
     </row>
     <row r="120" spans="21:22">
@@ -45383,7 +45542,7 @@
         <v>20040</v>
       </c>
       <c r="V120" t="s">
-        <v>718</v>
+        <v>720</v>
       </c>
     </row>
     <row r="121" spans="21:22">
@@ -45391,7 +45550,7 @@
         <v>20050</v>
       </c>
       <c r="V121" t="s">
-        <v>719</v>
+        <v>721</v>
       </c>
     </row>
     <row r="122" spans="21:22">
@@ -45399,7 +45558,7 @@
         <v>20070</v>
       </c>
       <c r="V122" t="s">
-        <v>720</v>
+        <v>722</v>
       </c>
     </row>
     <row r="123" spans="21:22">
@@ -45407,7 +45566,7 @@
         <v>20071</v>
       </c>
       <c r="V123" t="s">
-        <v>721</v>
+        <v>723</v>
       </c>
     </row>
     <row r="124" spans="21:22">
@@ -45415,7 +45574,7 @@
         <v>20110</v>
       </c>
       <c r="V124" t="s">
-        <v>722</v>
+        <v>724</v>
       </c>
     </row>
     <row r="125" spans="21:22">
@@ -45423,7 +45582,7 @@
         <v>20120</v>
       </c>
       <c r="V125" t="s">
-        <v>723</v>
+        <v>725</v>
       </c>
     </row>
     <row r="126" spans="21:22">
@@ -45431,7 +45590,7 @@
         <v>20130</v>
       </c>
       <c r="V126" t="s">
-        <v>724</v>
+        <v>726</v>
       </c>
     </row>
     <row r="127" spans="21:22">
@@ -45439,7 +45598,7 @@
         <v>20140</v>
       </c>
       <c r="V127" t="s">
-        <v>725</v>
+        <v>727</v>
       </c>
     </row>
     <row r="128" spans="21:22">
@@ -45447,7 +45606,7 @@
         <v>20150</v>
       </c>
       <c r="V128" t="s">
-        <v>726</v>
+        <v>728</v>
       </c>
     </row>
     <row r="129" spans="21:22">
@@ -45455,7 +45614,7 @@
         <v>20160</v>
       </c>
       <c r="V129" t="s">
-        <v>727</v>
+        <v>729</v>
       </c>
     </row>
     <row r="130" spans="21:22">
@@ -45463,7 +45622,7 @@
         <v>23010</v>
       </c>
       <c r="V130" t="s">
-        <v>728</v>
+        <v>730</v>
       </c>
     </row>
     <row r="131" spans="21:22">
@@ -45471,7 +45630,7 @@
         <v>30010</v>
       </c>
       <c r="V131" t="s">
-        <v>729</v>
+        <v>731</v>
       </c>
     </row>
     <row r="132" spans="21:22">
@@ -45479,7 +45638,15 @@
         <v>30020</v>
       </c>
       <c r="V132" t="s">
-        <v>730</v>
+        <v>732</v>
+      </c>
+    </row>
+    <row r="133" spans="21:22">
+      <c r="U133">
+        <v>40010</v>
+      </c>
+      <c r="V133" t="s">
+        <v>733</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Data/Skills.xlsx
+++ b/Assets/Data/Skills.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="7820" activeTab="1"/>
+    <workbookView windowWidth="19200" windowHeight="7820" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="Skills" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="852" uniqueCount="742">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="853" uniqueCount="743">
   <si>
     <t>Id</t>
   </si>
@@ -1229,7 +1229,8 @@
     <t>錬金術師の遺稿</t>
   </si>
   <si>
-    <t>魔法の配列変換が可能になる</t>
+    <t>(条件)バトル開始時
+前衛の中で1番CTが長い魔法のCT-1</t>
   </si>
   <si>
     <t>ヒールユニット</t>
@@ -2040,189 +2041,189 @@
     <t>人数が少ない列の敵</t>
   </si>
   <si>
+    <t>1番Ctの高い魔法のCt回復</t>
+  </si>
+  <si>
+    <t>〇人以上いる列の味方</t>
+  </si>
+  <si>
     <t>行動後Ap設定</t>
   </si>
   <si>
-    <t>〇人以上いる列の味方</t>
+    <t>〇人以上いる列の敵</t>
   </si>
   <si>
     <t>行動後ApがParam1割</t>
   </si>
   <si>
-    <t>〇人以上いる列の敵</t>
+    <t>〇番目の味方</t>
   </si>
   <si>
     <t>ActionResult扱いでAP指定</t>
   </si>
   <si>
-    <t>〇番目の味方</t>
+    <t>〇番目の敵</t>
   </si>
   <si>
     <t>Ap回復</t>
   </si>
   <si>
-    <t>〇番目の敵</t>
+    <t>後衛がいる</t>
   </si>
   <si>
     <t>再行動する</t>
   </si>
   <si>
-    <t>後衛がいる</t>
+    <t>StateId状態になっている</t>
   </si>
   <si>
     <t>先制攻撃</t>
   </si>
   <si>
-    <t>StateId状態になっている</t>
+    <t>StateId状態になっていない</t>
   </si>
   <si>
     <t>APダメージ</t>
   </si>
   <si>
-    <t>StateId状態になっていない</t>
+    <t>StateId状態になっている味方</t>
   </si>
   <si>
     <t>指定のFeatureのParam1を増やす</t>
   </si>
   <si>
-    <t>StateId状態になっている味方</t>
+    <t>StateId状態になっている敵</t>
   </si>
   <si>
     <t>指定のFeatureのParam2を増やす</t>
   </si>
   <si>
-    <t>StateId状態になっている敵</t>
+    <t>StateId状態になっていない味方</t>
   </si>
   <si>
     <t>指定のFeatureのParam3を増やす</t>
   </si>
   <si>
-    <t>StateId状態になっていない味方</t>
+    <t>StateId状態になっていない敵</t>
   </si>
   <si>
     <t>指定のFeatureのParam1をParam3xステージ勝利数増やす</t>
   </si>
   <si>
-    <t>StateId状態になっていない敵</t>
+    <t>AbnormalのStateにかかっている</t>
   </si>
   <si>
     <t>指定のFeatureのParam2をParam3xステージ勝利数増やす</t>
   </si>
   <si>
-    <t>AbnormalのStateにかかっている</t>
+    <t>AbnormalのStateにかかっている味方</t>
   </si>
   <si>
     <t>指定のFeatureのParam3をParam3xステージ勝利数増やす</t>
   </si>
   <si>
-    <t>AbnormalのStateにかかっている味方</t>
+    <t>AbnormalのStateにかかっている敵</t>
   </si>
   <si>
     <t>指定のFeatuerの成功率を増やす</t>
   </si>
   <si>
-    <t>AbnormalのStateにかかっている敵</t>
+    <t>AbnormalのStateにかかっていない味方</t>
   </si>
   <si>
     <t>指定魔法のCTリセット値を変更する</t>
   </si>
   <si>
-    <t>AbnormalのStateにかかっていない味方</t>
+    <t>AbnormalのStateにかかっていない敵</t>
   </si>
   <si>
     <t>指定魔法の攻撃回数を増やす(強化限定)</t>
   </si>
   <si>
-    <t>AbnormalのStateにかかっていない敵</t>
+    <t>BuffのStateにかかっている</t>
   </si>
   <si>
     <t>指定魔法の対象を変更（強化限定）</t>
   </si>
   <si>
-    <t>BuffのStateにかかっている</t>
+    <t>BuffのStateにかかっている味方</t>
   </si>
   <si>
     <t>指定魔法に行動後スキルを追加する</t>
   </si>
   <si>
-    <t>BuffのStateにかかっている味方</t>
+    <t>BuffのStateにかかっている敵</t>
   </si>
   <si>
     <t>行動後スキル</t>
   </si>
   <si>
-    <t>BuffのStateにかかっている敵</t>
+    <t>BuffのStateにかかっていない味方</t>
   </si>
   <si>
     <t>行動後条件付きスキル</t>
   </si>
   <si>
-    <t>BuffのStateにかかっていない味方</t>
+    <t>BuffのStateにかかっていない敵</t>
   </si>
   <si>
     <t>スキルを習得する</t>
   </si>
   <si>
-    <t>BuffのStateにかかっていない敵</t>
+    <t>DeBuffのStateにかかっている</t>
   </si>
   <si>
     <t>回復特性</t>
   </si>
   <si>
-    <t>DeBuffのStateにかかっている</t>
+    <t>DeBuffのStateにかかっている味方</t>
   </si>
   <si>
     <t>アンデッド特攻</t>
   </si>
   <si>
-    <t>DeBuffのStateにかかっている味方</t>
+    <t>DeBuffのStateにかかっている敵</t>
   </si>
   <si>
     <t>隊列を入れ替え</t>
   </si>
   <si>
-    <t>DeBuffのStateにかかっている敵</t>
+    <t>DeBuffのStateにかかっていない味方</t>
   </si>
   <si>
     <t>行動後にAp+</t>
   </si>
   <si>
-    <t>DeBuffのStateにかかっていない味方</t>
+    <t>DeBuffのStateにかかっていない敵</t>
   </si>
   <si>
     <t>行動後に交代</t>
   </si>
   <si>
-    <t>DeBuffのStateにかかっていない敵</t>
+    <t>神化発動前</t>
   </si>
   <si>
     <t>命中判定しない</t>
   </si>
   <si>
-    <t>神化発動前</t>
+    <t>神化発動後</t>
   </si>
   <si>
     <t>最後に受けたAbnormalを相手に移す</t>
   </si>
   <si>
-    <t>神化発動後</t>
+    <t>神化発動前の味方</t>
   </si>
   <si>
     <t>対象のバフを奪い取る</t>
   </si>
   <si>
-    <t>神化発動前の味方</t>
+    <t>神化発動後の味方</t>
   </si>
   <si>
     <t>アイテム入手</t>
   </si>
   <si>
-    <t>神化発動後の味方</t>
-  </si>
-  <si>
-    <t>配列変換が可能</t>
-  </si>
-  <si>
     <t>神化発動前の敵</t>
   </si>
   <si>
@@ -2428,6 +2429,9 @@
   </si>
   <si>
     <t>攻撃を回避した時</t>
+  </si>
+  <si>
+    <t>対象の中で1番CTの長い魔法を持っている(ScopeTrigger用)</t>
   </si>
   <si>
     <t>終焉まで〇ターン</t>
@@ -2447,9 +2451,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
@@ -2469,7 +2473,37 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -2483,70 +2517,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -2574,6 +2546,37 @@
     </font>
     <font>
       <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -2591,9 +2594,9 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -2605,8 +2608,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -2633,31 +2637,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2669,7 +2655,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2681,13 +2685,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2705,7 +2715,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2717,31 +2763,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2753,37 +2775,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2795,25 +2805,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2842,30 +2846,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FFB2B2B2"/>
       </left>
@@ -2890,6 +2870,21 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top/>
@@ -2901,11 +2896,9 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -2924,6 +2917,17 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -2932,16 +2936,16 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -2950,127 +2954,127 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="14" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -19773,11 +19777,11 @@
         <v>味方</v>
       </c>
       <c r="S168">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T168" t="str">
         <f>INDEX(Define!N:N,MATCH(S168,Define!M:M))</f>
-        <v>全体</v>
+        <v>単体</v>
       </c>
       <c r="U168">
         <v>2</v>
@@ -33529,11 +33533,11 @@
         <v>錬金術師の遺稿</v>
       </c>
       <c r="C235">
-        <v>40020</v>
+        <v>4041</v>
       </c>
       <c r="D235" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C235,Define!P:P))</f>
-        <v>配列変換が可能</v>
+        <v>1番Ctの高い魔法のCt回復</v>
       </c>
       <c r="E235">
         <v>1</v>
@@ -35965,7 +35969,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H122"/>
+  <dimension ref="A1:H123"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="7"/>
   <cols>
     <col min="2" max="2" width="19.7272727272727" customWidth="1"/>
@@ -39360,18 +39364,18 @@
     </row>
     <row r="122" spans="1:8">
       <c r="A122">
-        <v>310130</v>
+        <v>310030</v>
       </c>
       <c r="B122" t="str">
         <f>INDEX(TextData!B:B,MATCH(A122,TextData!A:A))</f>
-        <v>ヒールユニット</v>
+        <v>錬金術師の遺稿</v>
       </c>
       <c r="C122">
-        <v>40010</v>
+        <v>0</v>
       </c>
       <c r="D122" t="str">
         <f>INDEX(Define!V:V,MATCH(C122,Define!U:U))</f>
-        <v>ダンジョンで移動する</v>
+        <v>なし</v>
       </c>
       <c r="E122">
         <v>4</v>
@@ -39383,6 +39387,34 @@
         <v>0</v>
       </c>
       <c r="H122">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123" spans="1:8">
+      <c r="A123">
+        <v>310130</v>
+      </c>
+      <c r="B123" t="str">
+        <f>INDEX(TextData!B:B,MATCH(A123,TextData!A:A))</f>
+        <v>ヒールユニット</v>
+      </c>
+      <c r="C123">
+        <v>40010</v>
+      </c>
+      <c r="D123" t="str">
+        <f>INDEX(Define!V:V,MATCH(C123,Define!U:U))</f>
+        <v>ダンジョンで移動する</v>
+      </c>
+      <c r="E123">
+        <v>4</v>
+      </c>
+      <c r="F123">
+        <v>0</v>
+      </c>
+      <c r="G123">
+        <v>0</v>
+      </c>
+      <c r="H123">
         <v>0</v>
       </c>
     </row>
@@ -39395,7 +39427,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="7"/>
   <cols>
     <col min="2" max="2" width="18.5454545454545" customWidth="1"/>
@@ -39789,6 +39821,34 @@
         <v>1</v>
       </c>
       <c r="H14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
+      <c r="A15">
+        <v>310030</v>
+      </c>
+      <c r="B15" t="str">
+        <f>INDEX(TextData!B:B,MATCH(A15,TextData!A:A))</f>
+        <v>錬金術師の遺稿</v>
+      </c>
+      <c r="C15">
+        <v>24010</v>
+      </c>
+      <c r="D15" t="str">
+        <f>INDEX(Define!V:V,MATCH(C15,Define!U:U))</f>
+        <v>対象の中で1番CTの長い魔法を持っている(ScopeTrigger用)</v>
+      </c>
+      <c r="E15">
+        <v>2</v>
+      </c>
+      <c r="F15">
+        <v>0</v>
+      </c>
+      <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="H15">
         <v>0</v>
       </c>
     </row>
@@ -41629,7 +41689,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="165" customFormat="1" spans="1:3">
+    <row r="165" customFormat="1" ht="26" spans="1:3">
       <c r="A165">
         <v>310030</v>
       </c>
@@ -42595,7 +42655,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AC134"/>
+  <dimension ref="A1:AC135"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13"/>
   <cols>
     <col min="3" max="3" width="1.72727272727273" customWidth="1"/>
@@ -43612,7 +43672,7 @@
     </row>
     <row r="32" spans="16:22">
       <c r="P32">
-        <v>5010</v>
+        <v>4041</v>
       </c>
       <c r="Q32" t="s">
         <v>608</v>
@@ -43626,7 +43686,7 @@
     </row>
     <row r="33" spans="16:22">
       <c r="P33">
-        <v>5011</v>
+        <v>5010</v>
       </c>
       <c r="Q33" t="s">
         <v>610</v>
@@ -43640,7 +43700,7 @@
     </row>
     <row r="34" spans="16:22">
       <c r="P34">
-        <v>5012</v>
+        <v>5011</v>
       </c>
       <c r="Q34" t="s">
         <v>612</v>
@@ -43654,7 +43714,7 @@
     </row>
     <row r="35" spans="16:22">
       <c r="P35">
-        <v>5020</v>
+        <v>5012</v>
       </c>
       <c r="Q35" t="s">
         <v>614</v>
@@ -43668,7 +43728,7 @@
     </row>
     <row r="36" spans="16:22">
       <c r="P36">
-        <v>5030</v>
+        <v>5020</v>
       </c>
       <c r="Q36" t="s">
         <v>616</v>
@@ -43682,7 +43742,7 @@
     </row>
     <row r="37" spans="16:22">
       <c r="P37">
-        <v>5040</v>
+        <v>5030</v>
       </c>
       <c r="Q37" t="s">
         <v>618</v>
@@ -43696,7 +43756,7 @@
     </row>
     <row r="38" spans="16:22">
       <c r="P38">
-        <v>5050</v>
+        <v>5040</v>
       </c>
       <c r="Q38" t="s">
         <v>620</v>
@@ -43710,7 +43770,7 @@
     </row>
     <row r="39" spans="16:22">
       <c r="P39">
-        <v>6010</v>
+        <v>5050</v>
       </c>
       <c r="Q39" t="s">
         <v>622</v>
@@ -43724,7 +43784,7 @@
     </row>
     <row r="40" spans="16:22">
       <c r="P40">
-        <v>6020</v>
+        <v>6010</v>
       </c>
       <c r="Q40" t="s">
         <v>624</v>
@@ -43738,7 +43798,7 @@
     </row>
     <row r="41" spans="16:22">
       <c r="P41">
-        <v>6030</v>
+        <v>6020</v>
       </c>
       <c r="Q41" t="s">
         <v>626</v>
@@ -43752,7 +43812,7 @@
     </row>
     <row r="42" spans="16:22">
       <c r="P42">
-        <v>6040</v>
+        <v>6030</v>
       </c>
       <c r="Q42" t="s">
         <v>628</v>
@@ -43766,7 +43826,7 @@
     </row>
     <row r="43" spans="16:22">
       <c r="P43">
-        <v>6050</v>
+        <v>6040</v>
       </c>
       <c r="Q43" t="s">
         <v>630</v>
@@ -43780,7 +43840,7 @@
     </row>
     <row r="44" spans="16:22">
       <c r="P44">
-        <v>6060</v>
+        <v>6050</v>
       </c>
       <c r="Q44" t="s">
         <v>632</v>
@@ -43794,7 +43854,7 @@
     </row>
     <row r="45" spans="16:22">
       <c r="P45">
-        <v>6070</v>
+        <v>6060</v>
       </c>
       <c r="Q45" t="s">
         <v>634</v>
@@ -43808,7 +43868,7 @@
     </row>
     <row r="46" spans="16:22">
       <c r="P46">
-        <v>6080</v>
+        <v>6070</v>
       </c>
       <c r="Q46" t="s">
         <v>636</v>
@@ -43822,7 +43882,7 @@
     </row>
     <row r="47" spans="16:22">
       <c r="P47">
-        <v>6100</v>
+        <v>6080</v>
       </c>
       <c r="Q47" t="s">
         <v>638</v>
@@ -43836,7 +43896,7 @@
     </row>
     <row r="48" spans="16:22">
       <c r="P48">
-        <v>6210</v>
+        <v>6100</v>
       </c>
       <c r="Q48" t="s">
         <v>640</v>
@@ -43850,7 +43910,7 @@
     </row>
     <row r="49" spans="16:22">
       <c r="P49">
-        <v>6310</v>
+        <v>6210</v>
       </c>
       <c r="Q49" t="s">
         <v>642</v>
@@ -43864,7 +43924,7 @@
     </row>
     <row r="50" spans="16:22">
       <c r="P50">
-        <v>7010</v>
+        <v>6310</v>
       </c>
       <c r="Q50" t="s">
         <v>644</v>
@@ -43878,7 +43938,7 @@
     </row>
     <row r="51" spans="16:22">
       <c r="P51">
-        <v>7020</v>
+        <v>7010</v>
       </c>
       <c r="Q51" t="s">
         <v>646</v>
@@ -43892,7 +43952,7 @@
     </row>
     <row r="52" spans="16:22">
       <c r="P52">
-        <v>7030</v>
+        <v>7020</v>
       </c>
       <c r="Q52" t="s">
         <v>648</v>
@@ -43906,7 +43966,7 @@
     </row>
     <row r="53" spans="16:22">
       <c r="P53">
-        <v>8010</v>
+        <v>7030</v>
       </c>
       <c r="Q53" t="s">
         <v>650</v>
@@ -43920,7 +43980,7 @@
     </row>
     <row r="54" spans="16:22">
       <c r="P54">
-        <v>8020</v>
+        <v>8010</v>
       </c>
       <c r="Q54" t="s">
         <v>652</v>
@@ -43934,7 +43994,7 @@
     </row>
     <row r="55" spans="16:22">
       <c r="P55">
-        <v>9010</v>
+        <v>8020</v>
       </c>
       <c r="Q55" t="s">
         <v>654</v>
@@ -43948,7 +44008,7 @@
     </row>
     <row r="56" spans="16:22">
       <c r="P56">
-        <v>10010</v>
+        <v>9010</v>
       </c>
       <c r="Q56" t="s">
         <v>656</v>
@@ -43962,7 +44022,7 @@
     </row>
     <row r="57" spans="16:22">
       <c r="P57">
-        <v>10020</v>
+        <v>10010</v>
       </c>
       <c r="Q57" t="s">
         <v>658</v>
@@ -43976,7 +44036,7 @@
     </row>
     <row r="58" spans="16:22">
       <c r="P58">
-        <v>11010</v>
+        <v>10020</v>
       </c>
       <c r="Q58" t="s">
         <v>660</v>
@@ -43990,7 +44050,7 @@
     </row>
     <row r="59" spans="16:22">
       <c r="P59">
-        <v>12010</v>
+        <v>11010</v>
       </c>
       <c r="Q59" t="s">
         <v>662</v>
@@ -44004,7 +44064,7 @@
     </row>
     <row r="60" spans="16:22">
       <c r="P60">
-        <v>13010</v>
+        <v>12010</v>
       </c>
       <c r="Q60" t="s">
         <v>664</v>
@@ -44018,7 +44078,7 @@
     </row>
     <row r="61" spans="16:22">
       <c r="P61">
-        <v>40010</v>
+        <v>13010</v>
       </c>
       <c r="Q61" t="s">
         <v>666</v>
@@ -44032,7 +44092,7 @@
     </row>
     <row r="62" spans="16:22">
       <c r="P62">
-        <v>40020</v>
+        <v>40010</v>
       </c>
       <c r="Q62" t="s">
         <v>668</v>
@@ -44590,7 +44650,7 @@
     </row>
     <row r="131" spans="21:22">
       <c r="U131">
-        <v>30010</v>
+        <v>24010</v>
       </c>
       <c r="V131" t="s">
         <v>738</v>
@@ -44598,7 +44658,7 @@
     </row>
     <row r="132" spans="21:22">
       <c r="U132">
-        <v>30020</v>
+        <v>30010</v>
       </c>
       <c r="V132" t="s">
         <v>739</v>
@@ -44606,7 +44666,7 @@
     </row>
     <row r="133" spans="21:22">
       <c r="U133">
-        <v>40010</v>
+        <v>30020</v>
       </c>
       <c r="V133" t="s">
         <v>740</v>
@@ -44614,10 +44674,18 @@
     </row>
     <row r="134" spans="21:22">
       <c r="U134">
-        <v>40020</v>
+        <v>40010</v>
       </c>
       <c r="V134" t="s">
         <v>741</v>
+      </c>
+    </row>
+    <row r="135" spans="21:22">
+      <c r="U135">
+        <v>40020</v>
+      </c>
+      <c r="V135" t="s">
+        <v>742</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Data/Skills.xlsx
+++ b/Assets/Data/Skills.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8270" activeTab="2"/>
+    <workbookView windowWidth="19200" windowHeight="7820"/>
   </bookViews>
   <sheets>
     <sheet name="Skills" sheetId="1" r:id="rId1"/>
@@ -2632,8 +2632,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
@@ -2660,60 +2660,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -2727,34 +2674,18 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -2774,6 +2705,44 @@
     </font>
     <font>
       <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -2782,15 +2751,46 @@
     </font>
     <font>
       <b/>
-      <sz val="18"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -2817,7 +2817,151 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2829,37 +2973,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2871,133 +2991,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3012,6 +3012,21 @@
     </border>
     <border>
       <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
       <right style="thin">
@@ -3022,56 +3037,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -3094,7 +3059,27 @@
       <left/>
       <right/>
       <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
         <color theme="4"/>
       </bottom>
       <diagonal/>
@@ -3108,6 +3093,21 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -3116,7 +3116,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -3125,7 +3125,7 @@
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -3134,127 +3134,127 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="18" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -8149,7 +8149,7 @@
         <v>0</v>
       </c>
       <c r="L24">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M24">
         <v>2</v>
@@ -12323,7 +12323,7 @@
         <v>3</v>
       </c>
       <c r="L75">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="M75">
         <v>2</v>
@@ -14782,11 +14782,11 @@
         <v>0</v>
       </c>
       <c r="M105">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="N105" t="str">
         <f>INDEX(Define!E:E,MATCH(M105,Define!D:D))</f>
-        <v>なし</v>
+        <v>無</v>
       </c>
       <c r="O105">
         <v>1</v>
@@ -14860,11 +14860,11 @@
         <v>330</v>
       </c>
       <c r="M106">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="N106" t="str">
         <f>INDEX(Define!E:E,MATCH(M106,Define!D:D))</f>
-        <v>なし</v>
+        <v>無</v>
       </c>
       <c r="O106">
         <v>7</v>
@@ -14938,11 +14938,11 @@
         <v>330</v>
       </c>
       <c r="M107">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="N107" t="str">
         <f>INDEX(Define!E:E,MATCH(M107,Define!D:D))</f>
-        <v>なし</v>
+        <v>無</v>
       </c>
       <c r="O107">
         <v>7</v>
@@ -15016,11 +15016,11 @@
         <v>330</v>
       </c>
       <c r="M108">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="N108" t="str">
         <f>INDEX(Define!E:E,MATCH(M108,Define!D:D))</f>
-        <v>なし</v>
+        <v>無</v>
       </c>
       <c r="O108">
         <v>7</v>
@@ -20323,7 +20323,7 @@
         <v>0</v>
       </c>
       <c r="L173">
-        <v>220</v>
+        <v>0</v>
       </c>
       <c r="M173">
         <v>4</v>

--- a/Assets/Data/Skills.xlsx
+++ b/Assets/Data/Skills.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="7820"/>
+    <workbookView windowWidth="19200" windowHeight="7820" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Skills" sheetId="1" r:id="rId1"/>
@@ -2632,9 +2632,9 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -2653,14 +2653,37 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -2674,10 +2697,11 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -2705,10 +2729,10 @@
     </font>
     <font>
       <b/>
-      <sz val="18"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -2723,6 +2747,14 @@
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -2742,6 +2774,13 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="13"/>
       <color theme="3"/>
@@ -2750,47 +2789,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -2817,7 +2817,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2829,19 +2841,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2865,7 +2889,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2877,7 +2913,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2889,7 +2937,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2901,7 +2949,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2919,85 +2997,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3011,17 +3011,13 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
+      <left/>
+      <right/>
       <top style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color theme="4"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -3041,6 +3037,21 @@
       <diagonal/>
     </border>
     <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -3052,6 +3063,21 @@
       </top>
       <bottom style="thin">
         <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -3076,35 +3102,9 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
       <top/>
       <bottom style="medium">
         <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -3116,145 +3116,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="18" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -31068,7 +31068,7 @@
         <v>999</v>
       </c>
       <c r="G81">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="H81">
         <v>100</v>
@@ -31100,7 +31100,7 @@
         <v>999</v>
       </c>
       <c r="G82">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="H82">
         <v>100</v>

--- a/Assets/Data/Skills.xlsx
+++ b/Assets/Data/Skills.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="914" uniqueCount="798">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="915" uniqueCount="799">
   <si>
     <t>Id</t>
   </si>
@@ -1248,11 +1248,10 @@
 ランダムに属性の精霊石を1つ入手</t>
   </si>
   <si>
-    <t>錬金術師の遺稿</t>
-  </si>
-  <si>
-    <t>(条件)バトル開始時
-前衛の中で1番CTが長い魔法のCT-1</t>
+    <t>商売の才覚 書</t>
+  </si>
+  <si>
+    <t>取引コマンドのコストを20%下げる</t>
   </si>
   <si>
     <t>レイヴンバナー</t>
@@ -2414,6 +2413,9 @@
   </si>
   <si>
     <t>味方の数が〇以下</t>
+  </si>
+  <si>
+    <t>取引レートダウン</t>
   </si>
   <si>
     <t>敵の数が〇以上</t>
@@ -2632,9 +2634,9 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -2653,6 +2655,21 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
@@ -2660,7 +2677,37 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -2675,7 +2722,61 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -2691,108 +2792,9 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -2817,7 +2819,151 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2829,97 +2975,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2931,37 +2987,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2973,31 +2999,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3008,17 +3010,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -3033,36 +3024,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -3084,9 +3045,35 @@
     <border>
       <left/>
       <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top/>
       <bottom style="double">
         <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -3096,6 +3083,21 @@
       <top/>
       <bottom style="medium">
         <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -3116,133 +3118,103 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="20" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="18" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="18" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="13" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -3251,10 +3223,40 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -20141,7 +20143,7 @@
       </c>
       <c r="C171" t="str">
         <f>INDEX(TextData!B:B,MATCH(B171,TextData!A:A))</f>
-        <v>錬金術師の遺稿</v>
+        <v>商売の才覚 書</v>
       </c>
       <c r="D171">
         <v>6</v>
@@ -35748,17 +35750,17 @@
       </c>
       <c r="B238" t="str">
         <f>INDEX(TextData!B:B,MATCH(A238,TextData!A:A))</f>
-        <v>錬金術師の遺稿</v>
+        <v>商売の才覚 書</v>
       </c>
       <c r="C238">
-        <v>4041</v>
+        <v>40070</v>
       </c>
       <c r="D238" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C238,Define!P:P))</f>
-        <v>1番Ctの高い魔法のCt回復</v>
+        <v>取引レートダウン</v>
       </c>
       <c r="E238">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="F238">
         <v>0</v>
@@ -42278,7 +42280,7 @@
       </c>
       <c r="B124" t="str">
         <f>INDEX(TextData!B:B,MATCH(A124,TextData!A:A))</f>
-        <v>錬金術師の遺稿</v>
+        <v>商売の才覚 書</v>
       </c>
       <c r="C124">
         <v>0</v>
@@ -43328,7 +43330,7 @@
       </c>
       <c r="B15" t="str">
         <f>INDEX(TextData!B:B,MATCH(A15,TextData!A:A))</f>
-        <v>錬金術師の遺稿</v>
+        <v>商売の才覚 書</v>
       </c>
       <c r="C15">
         <v>24010</v>
@@ -45304,7 +45306,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="168" customFormat="1" ht="26" spans="1:3">
+    <row r="168" customFormat="1" spans="1:3">
       <c r="A168">
         <v>310030</v>
       </c>
@@ -48057,12 +48059,18 @@
         <v>727</v>
       </c>
     </row>
-    <row r="69" spans="21:22">
+    <row r="69" spans="16:22">
+      <c r="P69">
+        <v>40070</v>
+      </c>
+      <c r="Q69" t="s">
+        <v>728</v>
+      </c>
       <c r="U69">
         <v>8050</v>
       </c>
       <c r="V69" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
     </row>
     <row r="70" spans="21:22">
@@ -48070,7 +48078,7 @@
         <v>8060</v>
       </c>
       <c r="V70" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
     </row>
     <row r="71" spans="21:22">
@@ -48078,7 +48086,7 @@
         <v>9010</v>
       </c>
       <c r="V71" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
     </row>
     <row r="72" spans="21:22">
@@ -48086,7 +48094,7 @@
         <v>9020</v>
       </c>
       <c r="V72" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
     </row>
     <row r="73" spans="21:22">
@@ -48094,7 +48102,7 @@
         <v>9030</v>
       </c>
       <c r="V73" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
     </row>
     <row r="74" spans="21:22">
@@ -48102,7 +48110,7 @@
         <v>9031</v>
       </c>
       <c r="V74" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
     </row>
     <row r="75" spans="21:22">
@@ -48110,7 +48118,7 @@
         <v>9040</v>
       </c>
       <c r="V75" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
     </row>
     <row r="76" spans="21:22">
@@ -48118,7 +48126,7 @@
         <v>9110</v>
       </c>
       <c r="V76" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
     </row>
     <row r="77" spans="21:22">
@@ -48126,7 +48134,7 @@
         <v>9120</v>
       </c>
       <c r="V77" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
     </row>
     <row r="78" spans="21:22">
@@ -48134,7 +48142,7 @@
         <v>10010</v>
       </c>
       <c r="V78" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
     </row>
     <row r="79" spans="21:22">
@@ -48142,7 +48150,7 @@
         <v>10020</v>
       </c>
       <c r="V79" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
     </row>
     <row r="80" spans="21:22">
@@ -48150,7 +48158,7 @@
         <v>10110</v>
       </c>
       <c r="V80" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
     </row>
     <row r="81" spans="21:22">
@@ -48158,7 +48166,7 @@
         <v>11010</v>
       </c>
       <c r="V81" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
     </row>
     <row r="82" spans="21:22">
@@ -48166,7 +48174,7 @@
         <v>11020</v>
       </c>
       <c r="V82" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
     </row>
     <row r="83" spans="21:22">
@@ -48174,7 +48182,7 @@
         <v>12030</v>
       </c>
       <c r="V83" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
     </row>
     <row r="84" spans="21:22">
@@ -48182,7 +48190,7 @@
         <v>12040</v>
       </c>
       <c r="V84" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
     </row>
     <row r="85" spans="21:22">
@@ -48190,7 +48198,7 @@
         <v>12041</v>
       </c>
       <c r="V85" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
     </row>
     <row r="86" spans="21:22">
@@ -48198,7 +48206,7 @@
         <v>12042</v>
       </c>
       <c r="V86" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
     </row>
     <row r="87" spans="21:22">
@@ -48206,7 +48214,7 @@
         <v>12043</v>
       </c>
       <c r="V87" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
     </row>
     <row r="88" spans="21:22">
@@ -48214,7 +48222,7 @@
         <v>12050</v>
       </c>
       <c r="V88" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
     </row>
     <row r="89" spans="21:22">
@@ -48222,7 +48230,7 @@
         <v>12060</v>
       </c>
       <c r="V89" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
     </row>
     <row r="90" spans="21:22">
@@ -48230,7 +48238,7 @@
         <v>12063</v>
       </c>
       <c r="V90" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
     </row>
     <row r="91" spans="21:22">
@@ -48238,7 +48246,7 @@
         <v>12064</v>
       </c>
       <c r="V91" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
     </row>
     <row r="92" spans="21:22">
@@ -48246,7 +48254,7 @@
         <v>12066</v>
       </c>
       <c r="V92" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
     </row>
     <row r="93" spans="21:22">
@@ -48254,7 +48262,7 @@
         <v>12070</v>
       </c>
       <c r="V93" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
     </row>
     <row r="94" spans="21:22">
@@ -48262,7 +48270,7 @@
         <v>12071</v>
       </c>
       <c r="V94" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
     </row>
     <row r="95" spans="21:22">
@@ -48270,7 +48278,7 @@
         <v>12082</v>
       </c>
       <c r="V95" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
     </row>
     <row r="96" spans="21:22">
@@ -48278,7 +48286,7 @@
         <v>12092</v>
       </c>
       <c r="V96" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
     </row>
     <row r="97" spans="21:22">
@@ -48286,7 +48294,7 @@
         <v>13010</v>
       </c>
       <c r="V97" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
     </row>
     <row r="98" spans="21:22">
@@ -48294,7 +48302,7 @@
         <v>13020</v>
       </c>
       <c r="V98" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
     </row>
     <row r="99" spans="21:22">
@@ -48302,7 +48310,7 @@
         <v>14010</v>
       </c>
       <c r="V99" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
     </row>
     <row r="100" spans="21:22">
@@ -48310,7 +48318,7 @@
         <v>14110</v>
       </c>
       <c r="V100" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
     </row>
     <row r="101" spans="21:22">
@@ -48318,7 +48326,7 @@
         <v>14210</v>
       </c>
       <c r="V101" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
     </row>
     <row r="102" spans="21:22">
@@ -48326,7 +48334,7 @@
         <v>14310</v>
       </c>
       <c r="V102" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
     </row>
     <row r="103" spans="21:22">
@@ -48334,7 +48342,7 @@
         <v>14410</v>
       </c>
       <c r="V103" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
     </row>
     <row r="104" spans="21:22">
@@ -48342,7 +48350,7 @@
         <v>14420</v>
       </c>
       <c r="V104" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
     </row>
     <row r="105" spans="21:22">
@@ -48350,7 +48358,7 @@
         <v>14520</v>
       </c>
       <c r="V105" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
     </row>
     <row r="106" spans="21:22">
@@ -48358,7 +48366,7 @@
         <v>15010</v>
       </c>
       <c r="V106" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
     </row>
     <row r="107" spans="21:22">
@@ -48366,7 +48374,7 @@
         <v>15011</v>
       </c>
       <c r="V107" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
     </row>
     <row r="108" spans="21:22">
@@ -48374,7 +48382,7 @@
         <v>15022</v>
       </c>
       <c r="V108" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
     </row>
     <row r="109" spans="21:22">
@@ -48382,7 +48390,7 @@
         <v>16010</v>
       </c>
       <c r="V109" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
     </row>
     <row r="110" spans="21:22">
@@ -48390,7 +48398,7 @@
         <v>17010</v>
       </c>
       <c r="V110" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
     </row>
     <row r="111" spans="21:22">
@@ -48398,7 +48406,7 @@
         <v>17020</v>
       </c>
       <c r="V111" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
     </row>
     <row r="112" spans="21:22">
@@ -48406,7 +48414,7 @@
         <v>17030</v>
       </c>
       <c r="V112" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
     </row>
     <row r="113" spans="21:22">
@@ -48414,7 +48422,7 @@
         <v>17040</v>
       </c>
       <c r="V113" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
     </row>
     <row r="114" spans="21:22">
@@ -48422,7 +48430,7 @@
         <v>17050</v>
       </c>
       <c r="V114" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
     </row>
     <row r="115" spans="21:22">
@@ -48430,7 +48438,7 @@
         <v>17060</v>
       </c>
       <c r="V115" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
     </row>
     <row r="116" spans="21:22">
@@ -48438,7 +48446,7 @@
         <v>18010</v>
       </c>
       <c r="V116" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
     </row>
     <row r="117" spans="21:22">
@@ -48446,7 +48454,7 @@
         <v>18020</v>
       </c>
       <c r="V117" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
     </row>
     <row r="118" spans="21:22">
@@ -48454,7 +48462,7 @@
         <v>19010</v>
       </c>
       <c r="V118" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
     </row>
     <row r="119" spans="21:22">
@@ -48462,7 +48470,7 @@
         <v>19020</v>
       </c>
       <c r="V119" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
     </row>
     <row r="120" spans="21:22">
@@ -48470,7 +48478,7 @@
         <v>19030</v>
       </c>
       <c r="V120" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
     </row>
     <row r="121" spans="21:22">
@@ -48478,7 +48486,7 @@
         <v>20030</v>
       </c>
       <c r="V121" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
     </row>
     <row r="122" spans="21:22">
@@ -48486,7 +48494,7 @@
         <v>20040</v>
       </c>
       <c r="V122" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
     </row>
     <row r="123" spans="21:22">
@@ -48494,7 +48502,7 @@
         <v>20050</v>
       </c>
       <c r="V123" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
     </row>
     <row r="124" spans="21:22">
@@ -48502,7 +48510,7 @@
         <v>20070</v>
       </c>
       <c r="V124" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
     </row>
     <row r="125" spans="21:22">
@@ -48510,7 +48518,7 @@
         <v>20071</v>
       </c>
       <c r="V125" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
     </row>
     <row r="126" spans="21:22">
@@ -48518,7 +48526,7 @@
         <v>20110</v>
       </c>
       <c r="V126" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
     </row>
     <row r="127" spans="21:22">
@@ -48526,7 +48534,7 @@
         <v>20120</v>
       </c>
       <c r="V127" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
     </row>
     <row r="128" spans="21:22">
@@ -48534,7 +48542,7 @@
         <v>20130</v>
       </c>
       <c r="V128" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
     </row>
     <row r="129" spans="21:22">
@@ -48542,7 +48550,7 @@
         <v>20140</v>
       </c>
       <c r="V129" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
     </row>
     <row r="130" spans="21:22">
@@ -48550,7 +48558,7 @@
         <v>20150</v>
       </c>
       <c r="V130" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
     </row>
     <row r="131" spans="21:22">
@@ -48558,7 +48566,7 @@
         <v>20160</v>
       </c>
       <c r="V131" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
     </row>
     <row r="132" spans="21:22">
@@ -48566,7 +48574,7 @@
         <v>23010</v>
       </c>
       <c r="V132" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
     </row>
     <row r="133" spans="21:22">
@@ -48574,7 +48582,7 @@
         <v>24010</v>
       </c>
       <c r="V133" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
     </row>
     <row r="134" spans="21:22">
@@ -48582,7 +48590,7 @@
         <v>30010</v>
       </c>
       <c r="V134" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
     </row>
     <row r="135" spans="21:22">
@@ -48590,7 +48598,7 @@
         <v>30020</v>
       </c>
       <c r="V135" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
     </row>
     <row r="136" spans="21:22">
@@ -48598,7 +48606,7 @@
         <v>40010</v>
       </c>
       <c r="V136" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
     </row>
     <row r="137" spans="21:22">
@@ -48606,7 +48614,7 @@
         <v>40020</v>
       </c>
       <c r="V137" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
     </row>
     <row r="138" spans="21:22">
@@ -48614,7 +48622,7 @@
         <v>40030</v>
       </c>
       <c r="V138" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Data/Skills.xlsx
+++ b/Assets/Data/Skills.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8270" activeTab="1"/>
+    <workbookView windowWidth="19200" windowHeight="7820" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Skills" sheetId="1" r:id="rId1"/>
@@ -2644,8 +2644,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
@@ -2661,6 +2661,51 @@
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -2680,52 +2725,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -2754,14 +2754,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
@@ -2770,17 +2762,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -2795,16 +2778,33 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -2829,7 +2829,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2841,25 +2877,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2871,13 +2895,67 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2889,19 +2967,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2913,103 +2991,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3020,24 +3020,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -3066,6 +3048,39 @@
     </border>
     <border>
       <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
       <right style="thin">
@@ -3080,17 +3095,13 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
+      <left/>
+      <right/>
       <top style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color theme="4"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -3109,17 +3120,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -3128,16 +3128,16 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -3146,127 +3146,127 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="20" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -28848,7 +28848,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I350"/>
+  <dimension ref="A1:I351"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13"/>
   <cols>
     <col min="2" max="2" width="20" customWidth="1"/>
@@ -30940,18 +30940,18 @@
     </row>
     <row r="72" spans="1:8">
       <c r="A72">
-        <v>6020</v>
+        <v>6010</v>
       </c>
       <c r="B72" t="str">
         <f>INDEX(TextData!B:B,MATCH(A72,TextData!A:A))</f>
-        <v>交代</v>
+        <v>何もしない</v>
       </c>
       <c r="C72">
-        <v>10020</v>
+        <v>0</v>
       </c>
       <c r="D72" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C72,Define!P:P))</f>
-        <v>行動後に交代</v>
+        <v>ない</v>
       </c>
       <c r="E72">
         <v>0</v>
@@ -30966,45 +30966,41 @@
         <v>100</v>
       </c>
     </row>
-    <row r="73" spans="1:9">
+    <row r="73" spans="1:8">
       <c r="A73">
-        <v>10010</v>
+        <v>6020</v>
       </c>
       <c r="B73" t="str">
         <f>INDEX(TextData!B:B,MATCH(A73,TextData!A:A))</f>
-        <v>アンデッド</v>
+        <v>交代</v>
       </c>
       <c r="C73">
-        <v>3010</v>
+        <v>10020</v>
       </c>
       <c r="D73" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C73,Define!P:P))</f>
-        <v>ステート付与</v>
+        <v>行動後に交代</v>
       </c>
       <c r="E73">
-        <v>2270</v>
+        <v>0</v>
       </c>
       <c r="F73">
         <v>0</v>
       </c>
       <c r="G73">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H73">
         <v>100</v>
       </c>
-      <c r="I73" t="str">
-        <f>INDEX([4]TextData!B:B,MATCH(E73,[4]TextData!A:A))</f>
-        <v>アンデッド</v>
-      </c>
     </row>
     <row r="74" spans="1:9">
       <c r="A74">
-        <v>10020</v>
+        <v>10010</v>
       </c>
       <c r="B74" t="str">
         <f>INDEX(TextData!B:B,MATCH(A74,TextData!A:A))</f>
-        <v>エアリアル</v>
+        <v>アンデッド</v>
       </c>
       <c r="C74">
         <v>3010</v>
@@ -31014,29 +31010,29 @@
         <v>ステート付与</v>
       </c>
       <c r="E74">
-        <v>2190</v>
+        <v>2270</v>
       </c>
       <c r="F74">
-        <v>999</v>
+        <v>0</v>
       </c>
       <c r="G74">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H74">
         <v>100</v>
       </c>
       <c r="I74" t="str">
         <f>INDEX([4]TextData!B:B,MATCH(E74,[4]TextData!A:A))</f>
-        <v>対象範囲延長</v>
+        <v>アンデッド</v>
       </c>
     </row>
     <row r="75" spans="1:9">
       <c r="A75">
-        <v>10030</v>
+        <v>10020</v>
       </c>
       <c r="B75" t="str">
         <f>INDEX(TextData!B:B,MATCH(A75,TextData!A:A))</f>
-        <v>悪魔</v>
+        <v>エアリアル</v>
       </c>
       <c r="C75">
         <v>3010</v>
@@ -31046,29 +31042,29 @@
         <v>ステート付与</v>
       </c>
       <c r="E75">
-        <v>1030</v>
+        <v>2190</v>
       </c>
       <c r="F75">
         <v>999</v>
       </c>
       <c r="G75">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H75">
         <v>100</v>
       </c>
       <c r="I75" t="str">
         <f>INDEX([4]TextData!B:B,MATCH(E75,[4]TextData!A:A))</f>
-        <v>最大Mpアップ</v>
+        <v>対象範囲延長</v>
       </c>
     </row>
     <row r="76" spans="1:9">
       <c r="A76">
-        <v>10040</v>
+        <v>10030</v>
       </c>
       <c r="B76" t="str">
         <f>INDEX(TextData!B:B,MATCH(A76,TextData!A:A))</f>
-        <v>クリーチャー</v>
+        <v>悪魔</v>
       </c>
       <c r="C76">
         <v>3010</v>
@@ -31078,29 +31074,29 @@
         <v>ステート付与</v>
       </c>
       <c r="E76">
-        <v>1020</v>
+        <v>1030</v>
       </c>
       <c r="F76">
         <v>999</v>
       </c>
       <c r="G76">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="H76">
         <v>100</v>
       </c>
       <c r="I76" t="str">
         <f>INDEX([4]TextData!B:B,MATCH(E76,[4]TextData!A:A))</f>
-        <v>最大Hpアップ</v>
+        <v>最大Mpアップ</v>
       </c>
     </row>
     <row r="77" spans="1:9">
       <c r="A77">
-        <v>10050</v>
+        <v>10040</v>
       </c>
       <c r="B77" t="str">
         <f>INDEX(TextData!B:B,MATCH(A77,TextData!A:A))</f>
-        <v>野生の記憶</v>
+        <v>クリーチャー</v>
       </c>
       <c r="C77">
         <v>3010</v>
@@ -31110,29 +31106,29 @@
         <v>ステート付与</v>
       </c>
       <c r="E77">
-        <v>1040</v>
+        <v>1020</v>
       </c>
       <c r="F77">
         <v>999</v>
       </c>
       <c r="G77">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="H77">
         <v>100</v>
       </c>
       <c r="I77" t="str">
         <f>INDEX([4]TextData!B:B,MATCH(E77,[4]TextData!A:A))</f>
-        <v>攻撃アップ</v>
+        <v>最大Hpアップ</v>
       </c>
     </row>
     <row r="78" spans="1:9">
       <c r="A78">
-        <v>10060</v>
+        <v>10050</v>
       </c>
       <c r="B78" t="str">
         <f>INDEX(TextData!B:B,MATCH(A78,TextData!A:A))</f>
-        <v>変異生物</v>
+        <v>野生の記憶</v>
       </c>
       <c r="C78">
         <v>3010</v>
@@ -31142,29 +31138,29 @@
         <v>ステート付与</v>
       </c>
       <c r="E78">
-        <v>1050</v>
+        <v>1040</v>
       </c>
       <c r="F78">
         <v>999</v>
       </c>
       <c r="G78">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H78">
         <v>100</v>
       </c>
       <c r="I78" t="str">
         <f>INDEX([4]TextData!B:B,MATCH(E78,[4]TextData!A:A))</f>
-        <v>防御アップ</v>
+        <v>攻撃アップ</v>
       </c>
     </row>
     <row r="79" spans="1:9">
       <c r="A79">
-        <v>11010</v>
+        <v>10060</v>
       </c>
       <c r="B79" t="str">
         <f>INDEX(TextData!B:B,MATCH(A79,TextData!A:A))</f>
-        <v>ウルフソウル</v>
+        <v>変異生物</v>
       </c>
       <c r="C79">
         <v>3010</v>
@@ -31174,29 +31170,29 @@
         <v>ステート付与</v>
       </c>
       <c r="E79">
-        <v>1040</v>
+        <v>1050</v>
       </c>
       <c r="F79">
         <v>999</v>
       </c>
       <c r="G79">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H79">
         <v>100</v>
       </c>
       <c r="I79" t="str">
         <f>INDEX([4]TextData!B:B,MATCH(E79,[4]TextData!A:A))</f>
-        <v>攻撃アップ</v>
+        <v>防御アップ</v>
       </c>
     </row>
     <row r="80" spans="1:9">
       <c r="A80">
-        <v>11020</v>
+        <v>11010</v>
       </c>
       <c r="B80" t="str">
         <f>INDEX(TextData!B:B,MATCH(A80,TextData!A:A))</f>
-        <v>プリディカメント</v>
+        <v>ウルフソウル</v>
       </c>
       <c r="C80">
         <v>3010</v>
@@ -31212,7 +31208,7 @@
         <v>999</v>
       </c>
       <c r="G80">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H80">
         <v>100</v>
@@ -31224,11 +31220,11 @@
     </row>
     <row r="81" spans="1:9">
       <c r="A81">
-        <v>11030</v>
+        <v>11020</v>
       </c>
       <c r="B81" t="str">
         <f>INDEX(TextData!B:B,MATCH(A81,TextData!A:A))</f>
-        <v>アサルトシフト</v>
+        <v>プリディカメント</v>
       </c>
       <c r="C81">
         <v>3010</v>
@@ -31270,7 +31266,7 @@
         <v>ステート付与</v>
       </c>
       <c r="E82">
-        <v>1051</v>
+        <v>1040</v>
       </c>
       <c r="F82">
         <v>999</v>
@@ -31283,44 +31279,48 @@
       </c>
       <c r="I82" t="str">
         <f>INDEX([4]TextData!B:B,MATCH(E82,[4]TextData!A:A))</f>
-        <v>防御ダウン</v>
-      </c>
-    </row>
-    <row r="83" spans="1:8">
+        <v>攻撃アップ</v>
+      </c>
+    </row>
+    <row r="83" spans="1:9">
       <c r="A83">
-        <v>11040</v>
+        <v>11030</v>
       </c>
       <c r="B83" t="str">
         <f>INDEX(TextData!B:B,MATCH(A83,TextData!A:A))</f>
-        <v>アクティブギフト</v>
+        <v>アサルトシフト</v>
       </c>
       <c r="C83">
-        <v>4020</v>
+        <v>3010</v>
       </c>
       <c r="D83" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C83,Define!P:P))</f>
-        <v>Ct回復</v>
+        <v>ステート付与</v>
       </c>
       <c r="E83">
-        <v>1</v>
+        <v>1051</v>
       </c>
       <c r="F83">
-        <v>0</v>
+        <v>999</v>
       </c>
       <c r="G83">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H83">
         <v>100</v>
       </c>
+      <c r="I83" t="str">
+        <f>INDEX([4]TextData!B:B,MATCH(E83,[4]TextData!A:A))</f>
+        <v>防御ダウン</v>
+      </c>
     </row>
     <row r="84" spans="1:8">
       <c r="A84">
-        <v>11050</v>
+        <v>11040</v>
       </c>
       <c r="B84" t="str">
         <f>INDEX(TextData!B:B,MATCH(A84,TextData!A:A))</f>
-        <v>イグナイテッド</v>
+        <v>アクティブギフト</v>
       </c>
       <c r="C84">
         <v>4020</v>
@@ -31330,10 +31330,10 @@
         <v>Ct回復</v>
       </c>
       <c r="E84">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F84">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G84">
         <v>0</v>
@@ -31344,11 +31344,11 @@
     </row>
     <row r="85" spans="1:8">
       <c r="A85">
-        <v>11060</v>
+        <v>11050</v>
       </c>
       <c r="B85" t="str">
         <f>INDEX(TextData!B:B,MATCH(A85,TextData!A:A))</f>
-        <v>ライジングファイア</v>
+        <v>イグナイテッド</v>
       </c>
       <c r="C85">
         <v>4020</v>
@@ -31358,10 +31358,10 @@
         <v>Ct回復</v>
       </c>
       <c r="E85">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F85">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G85">
         <v>0</v>
@@ -31370,45 +31370,41 @@
         <v>100</v>
       </c>
     </row>
-    <row r="86" spans="1:9">
+    <row r="86" spans="1:8">
       <c r="A86">
-        <v>11070</v>
+        <v>11060</v>
       </c>
       <c r="B86" t="str">
         <f>INDEX(TextData!B:B,MATCH(A86,TextData!A:A))</f>
-        <v>ルージュバック</v>
+        <v>ライジングファイア</v>
       </c>
       <c r="C86">
-        <v>3010</v>
+        <v>4020</v>
       </c>
       <c r="D86" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C86,Define!P:P))</f>
-        <v>ステート付与</v>
+        <v>Ct回復</v>
       </c>
       <c r="E86">
-        <v>1044</v>
+        <v>1</v>
       </c>
       <c r="F86">
-        <v>999</v>
+        <v>0</v>
       </c>
       <c r="G86">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H86">
         <v>100</v>
       </c>
-      <c r="I86" t="str">
-        <f>INDEX([4]TextData!B:B,MATCH(E86,[4]TextData!A:A))</f>
-        <v>攻撃アップ</v>
-      </c>
     </row>
     <row r="87" spans="1:9">
       <c r="A87">
-        <v>11080</v>
+        <v>11070</v>
       </c>
       <c r="B87" t="str">
         <f>INDEX(TextData!B:B,MATCH(A87,TextData!A:A))</f>
-        <v>パワーエール</v>
+        <v>ルージュバック</v>
       </c>
       <c r="C87">
         <v>3010</v>
@@ -31418,13 +31414,13 @@
         <v>ステート付与</v>
       </c>
       <c r="E87">
-        <v>1040</v>
+        <v>1044</v>
       </c>
       <c r="F87">
-        <v>1</v>
+        <v>999</v>
       </c>
       <c r="G87">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H87">
         <v>100</v>
@@ -31436,11 +31432,11 @@
     </row>
     <row r="88" spans="1:9">
       <c r="A88">
-        <v>11090</v>
+        <v>11080</v>
       </c>
       <c r="B88" t="str">
         <f>INDEX(TextData!B:B,MATCH(A88,TextData!A:A))</f>
-        <v>スレイプニル</v>
+        <v>パワーエール</v>
       </c>
       <c r="C88">
         <v>3010</v>
@@ -31450,29 +31446,29 @@
         <v>ステート付与</v>
       </c>
       <c r="E88">
-        <v>2330</v>
+        <v>1040</v>
       </c>
       <c r="F88">
         <v>1</v>
       </c>
       <c r="G88">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="H88">
         <v>100</v>
       </c>
       <c r="I88" t="str">
         <f>INDEX([4]TextData!B:B,MATCH(E88,[4]TextData!A:A))</f>
-        <v>貫通</v>
+        <v>攻撃アップ</v>
       </c>
     </row>
     <row r="89" spans="1:9">
       <c r="A89">
-        <v>12010</v>
+        <v>11090</v>
       </c>
       <c r="B89" t="str">
         <f>INDEX(TextData!B:B,MATCH(A89,TextData!A:A))</f>
-        <v>コンセントレイト</v>
+        <v>スレイプニル</v>
       </c>
       <c r="C89">
         <v>3010</v>
@@ -31482,20 +31478,20 @@
         <v>ステート付与</v>
       </c>
       <c r="E89">
-        <v>1080</v>
+        <v>2330</v>
       </c>
       <c r="F89">
-        <v>999</v>
+        <v>1</v>
       </c>
       <c r="G89">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="H89">
         <v>100</v>
       </c>
       <c r="I89" t="str">
         <f>INDEX([4]TextData!B:B,MATCH(E89,[4]TextData!A:A))</f>
-        <v>命中アップ</v>
+        <v>貫通</v>
       </c>
     </row>
     <row r="90" spans="1:9">
@@ -31514,7 +31510,7 @@
         <v>ステート付与</v>
       </c>
       <c r="E90">
-        <v>1090</v>
+        <v>1080</v>
       </c>
       <c r="F90">
         <v>999</v>
@@ -31527,16 +31523,16 @@
       </c>
       <c r="I90" t="str">
         <f>INDEX([4]TextData!B:B,MATCH(E90,[4]TextData!A:A))</f>
-        <v>回避アップ</v>
+        <v>命中アップ</v>
       </c>
     </row>
     <row r="91" spans="1:9">
       <c r="A91">
-        <v>12020</v>
+        <v>12010</v>
       </c>
       <c r="B91" t="str">
         <f>INDEX(TextData!B:B,MATCH(A91,TextData!A:A))</f>
-        <v>ヘブンリーラック</v>
+        <v>コンセントレイト</v>
       </c>
       <c r="C91">
         <v>3010</v>
@@ -31552,7 +31548,7 @@
         <v>999</v>
       </c>
       <c r="G91">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="H91">
         <v>100</v>
@@ -31564,11 +31560,11 @@
     </row>
     <row r="92" spans="1:9">
       <c r="A92">
-        <v>12030</v>
+        <v>12020</v>
       </c>
       <c r="B92" t="str">
         <f>INDEX(TextData!B:B,MATCH(A92,TextData!A:A))</f>
-        <v>スウィフトカレント</v>
+        <v>ヘブンリーラック</v>
       </c>
       <c r="C92">
         <v>3010</v>
@@ -31578,29 +31574,29 @@
         <v>ステート付与</v>
       </c>
       <c r="E92">
-        <v>1060</v>
+        <v>1090</v>
       </c>
       <c r="F92">
         <v>999</v>
       </c>
       <c r="G92">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H92">
         <v>100</v>
       </c>
       <c r="I92" t="str">
         <f>INDEX([4]TextData!B:B,MATCH(E92,[4]TextData!A:A))</f>
-        <v>速度アップ</v>
+        <v>回避アップ</v>
       </c>
     </row>
     <row r="93" spans="1:9">
       <c r="A93">
-        <v>12040</v>
+        <v>12030</v>
       </c>
       <c r="B93" t="str">
         <f>INDEX(TextData!B:B,MATCH(A93,TextData!A:A))</f>
-        <v>イヴェイドオール</v>
+        <v>スウィフトカレント</v>
       </c>
       <c r="C93">
         <v>3010</v>
@@ -31610,7 +31606,7 @@
         <v>ステート付与</v>
       </c>
       <c r="E93">
-        <v>1092</v>
+        <v>1060</v>
       </c>
       <c r="F93">
         <v>999</v>
@@ -31623,54 +31619,58 @@
       </c>
       <c r="I93" t="str">
         <f>INDEX([4]TextData!B:B,MATCH(E93,[4]TextData!A:A))</f>
-        <v>回避アップ</v>
-      </c>
-    </row>
-    <row r="94" spans="1:8">
+        <v>速度アップ</v>
+      </c>
+    </row>
+    <row r="94" spans="1:9">
       <c r="A94">
-        <v>12050</v>
+        <v>12040</v>
       </c>
       <c r="B94" t="str">
         <f>INDEX(TextData!B:B,MATCH(A94,TextData!A:A))</f>
-        <v>クイックムーブ</v>
+        <v>イヴェイドオール</v>
       </c>
       <c r="C94">
-        <v>5020</v>
+        <v>3010</v>
       </c>
       <c r="D94" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C94,Define!P:P))</f>
-        <v>Ap回復</v>
+        <v>ステート付与</v>
       </c>
       <c r="E94">
-        <v>200</v>
+        <v>1092</v>
       </c>
       <c r="F94">
-        <v>0</v>
+        <v>999</v>
       </c>
       <c r="G94">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H94">
         <v>100</v>
       </c>
+      <c r="I94" t="str">
+        <f>INDEX([4]TextData!B:B,MATCH(E94,[4]TextData!A:A))</f>
+        <v>回避アップ</v>
+      </c>
     </row>
     <row r="95" spans="1:8">
       <c r="A95">
-        <v>12060</v>
+        <v>12050</v>
       </c>
       <c r="B95" t="str">
         <f>INDEX(TextData!B:B,MATCH(A95,TextData!A:A))</f>
-        <v>チェイスマジック</v>
+        <v>クイックムーブ</v>
       </c>
       <c r="C95">
-        <v>1010</v>
+        <v>5020</v>
       </c>
       <c r="D95" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C95,Define!P:P))</f>
-        <v>Hpダメージ</v>
+        <v>Ap回復</v>
       </c>
       <c r="E95">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="F95">
         <v>0</v>
@@ -31682,39 +31682,35 @@
         <v>100</v>
       </c>
     </row>
-    <row r="96" spans="1:9">
+    <row r="96" spans="1:8">
       <c r="A96">
-        <v>12070</v>
+        <v>12060</v>
       </c>
       <c r="B96" t="str">
         <f>INDEX(TextData!B:B,MATCH(A96,TextData!A:A))</f>
-        <v>ソーサリーコネクト</v>
+        <v>チェイスマジック</v>
       </c>
       <c r="C96">
-        <v>3010</v>
+        <v>1010</v>
       </c>
       <c r="D96" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C96,Define!P:P))</f>
-        <v>ステート付与</v>
+        <v>Hpダメージ</v>
       </c>
       <c r="E96">
-        <v>1040</v>
+        <v>100</v>
       </c>
       <c r="F96">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G96">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H96">
         <v>100</v>
       </c>
-      <c r="I96" t="str">
-        <f>INDEX([4]TextData!B:B,MATCH(E96,[4]TextData!A:A))</f>
-        <v>攻撃アップ</v>
-      </c>
-    </row>
-    <row r="97" spans="1:8">
+    </row>
+    <row r="97" spans="1:9">
       <c r="A97">
         <v>12070</v>
       </c>
@@ -31723,102 +31719,106 @@
         <v>ソーサリーコネクト</v>
       </c>
       <c r="C97">
-        <v>7010</v>
+        <v>3010</v>
       </c>
       <c r="D97" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C97,Define!P:P))</f>
-        <v>行動後スキル</v>
+        <v>ステート付与</v>
       </c>
       <c r="E97">
-        <v>12071</v>
+        <v>1040</v>
       </c>
       <c r="F97">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G97">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H97">
         <v>100</v>
       </c>
-    </row>
-    <row r="98" spans="1:9">
+      <c r="I97" t="str">
+        <f>INDEX([4]TextData!B:B,MATCH(E97,[4]TextData!A:A))</f>
+        <v>攻撃アップ</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8">
       <c r="A98">
-        <v>12071</v>
+        <v>12070</v>
       </c>
       <c r="B98" t="str">
         <f>INDEX(TextData!B:B,MATCH(A98,TextData!A:A))</f>
         <v>ソーサリーコネクト</v>
       </c>
       <c r="C98">
-        <v>3010</v>
+        <v>7010</v>
       </c>
       <c r="D98" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C98,Define!P:P))</f>
-        <v>ステート付与</v>
+        <v>行動後スキル</v>
       </c>
       <c r="E98">
-        <v>1041</v>
+        <v>12071</v>
       </c>
       <c r="F98">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G98">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H98">
         <v>100</v>
       </c>
-      <c r="I98" t="str">
-        <f>INDEX([4]TextData!B:B,MATCH(E98,[4]TextData!A:A))</f>
-        <v>攻撃ダウン</v>
-      </c>
-    </row>
-    <row r="99" spans="1:8">
+    </row>
+    <row r="99" spans="1:9">
       <c r="A99">
-        <v>12080</v>
+        <v>12071</v>
       </c>
       <c r="B99" t="str">
         <f>INDEX(TextData!B:B,MATCH(A99,TextData!A:A))</f>
-        <v>ウィンドライズ</v>
+        <v>ソーサリーコネクト</v>
       </c>
       <c r="C99">
-        <v>1010</v>
+        <v>3010</v>
       </c>
       <c r="D99" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C99,Define!P:P))</f>
-        <v>Hpダメージ</v>
+        <v>ステート付与</v>
       </c>
       <c r="E99">
-        <v>150</v>
+        <v>1041</v>
       </c>
       <c r="F99">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G99">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H99">
         <v>100</v>
       </c>
+      <c r="I99" t="str">
+        <f>INDEX([4]TextData!B:B,MATCH(E99,[4]TextData!A:A))</f>
+        <v>攻撃ダウン</v>
+      </c>
     </row>
     <row r="100" spans="1:8">
       <c r="A100">
-        <v>12090</v>
+        <v>12080</v>
       </c>
       <c r="B100" t="str">
         <f>INDEX(TextData!B:B,MATCH(A100,TextData!A:A))</f>
-        <v>アウトオブオーダー</v>
+        <v>ウィンドライズ</v>
       </c>
       <c r="C100">
-        <v>5020</v>
+        <v>1010</v>
       </c>
       <c r="D100" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C100,Define!P:P))</f>
-        <v>Ap回復</v>
+        <v>Hpダメージ</v>
       </c>
       <c r="E100">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="F100">
         <v>0</v>
@@ -31830,45 +31830,41 @@
         <v>100</v>
       </c>
     </row>
-    <row r="101" spans="1:9">
+    <row r="101" spans="1:8">
       <c r="A101">
-        <v>13010</v>
+        <v>12090</v>
       </c>
       <c r="B101" t="str">
         <f>INDEX(TextData!B:B,MATCH(A101,TextData!A:A))</f>
-        <v>アーマーコード</v>
+        <v>アウトオブオーダー</v>
       </c>
       <c r="C101">
-        <v>3010</v>
+        <v>5020</v>
       </c>
       <c r="D101" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C101,Define!P:P))</f>
-        <v>ステート付与</v>
+        <v>Ap回復</v>
       </c>
       <c r="E101">
-        <v>1050</v>
+        <v>200</v>
       </c>
       <c r="F101">
-        <v>999</v>
+        <v>0</v>
       </c>
       <c r="G101">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H101">
         <v>100</v>
       </c>
-      <c r="I101" t="str">
-        <f>INDEX([4]TextData!B:B,MATCH(E101,[4]TextData!A:A))</f>
-        <v>防御アップ</v>
-      </c>
     </row>
     <row r="102" spans="1:9">
       <c r="A102">
-        <v>13020</v>
+        <v>13010</v>
       </c>
       <c r="B102" t="str">
         <f>INDEX(TextData!B:B,MATCH(A102,TextData!A:A))</f>
-        <v>クイックバリア</v>
+        <v>アーマーコード</v>
       </c>
       <c r="C102">
         <v>3010</v>
@@ -31878,89 +31874,89 @@
         <v>ステート付与</v>
       </c>
       <c r="E102">
-        <v>1100</v>
+        <v>1050</v>
       </c>
       <c r="F102">
-        <v>1</v>
+        <v>999</v>
       </c>
       <c r="G102">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="H102">
         <v>100</v>
       </c>
       <c r="I102" t="str">
         <f>INDEX([4]TextData!B:B,MATCH(E102,[4]TextData!A:A))</f>
-        <v>ダメージカット</v>
-      </c>
-    </row>
-    <row r="103" spans="1:8">
+        <v>防御アップ</v>
+      </c>
+    </row>
+    <row r="103" spans="1:9">
       <c r="A103">
-        <v>13030</v>
+        <v>13020</v>
       </c>
       <c r="B103" t="str">
         <f>INDEX(TextData!B:B,MATCH(A103,TextData!A:A))</f>
-        <v>クイックキュア</v>
+        <v>クイックバリア</v>
       </c>
       <c r="C103">
-        <v>3030</v>
+        <v>3010</v>
       </c>
       <c r="D103" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C103,Define!P:P))</f>
-        <v>Abnormalステート解除</v>
+        <v>ステート付与</v>
       </c>
       <c r="E103">
-        <v>0</v>
+        <v>1100</v>
       </c>
       <c r="F103">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G103">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="H103">
         <v>100</v>
       </c>
-    </row>
-    <row r="104" spans="1:9">
+      <c r="I103" t="str">
+        <f>INDEX([4]TextData!B:B,MATCH(E103,[4]TextData!A:A))</f>
+        <v>ダメージカット</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8">
       <c r="A104">
-        <v>13040</v>
+        <v>13030</v>
       </c>
       <c r="B104" t="str">
         <f>INDEX(TextData!B:B,MATCH(A104,TextData!A:A))</f>
-        <v>セルフシールド</v>
+        <v>クイックキュア</v>
       </c>
       <c r="C104">
-        <v>3010</v>
+        <v>3030</v>
       </c>
       <c r="D104" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C104,Define!P:P))</f>
-        <v>ステート付与</v>
+        <v>Abnormalステート解除</v>
       </c>
       <c r="E104">
-        <v>1100</v>
+        <v>0</v>
       </c>
       <c r="F104">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G104">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="H104">
         <v>100</v>
       </c>
-      <c r="I104" t="str">
-        <f>INDEX([4]TextData!B:B,MATCH(E104,[4]TextData!A:A))</f>
-        <v>ダメージカット</v>
-      </c>
     </row>
     <row r="105" spans="1:9">
       <c r="A105">
-        <v>13050</v>
+        <v>13040</v>
       </c>
       <c r="B105" t="str">
         <f>INDEX(TextData!B:B,MATCH(A105,TextData!A:A))</f>
-        <v>パッシブジャミング</v>
+        <v>セルフシールド</v>
       </c>
       <c r="C105">
         <v>3010</v>
@@ -31970,29 +31966,29 @@
         <v>ステート付与</v>
       </c>
       <c r="E105">
-        <v>2090</v>
+        <v>1100</v>
       </c>
       <c r="F105">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G105">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="H105">
         <v>100</v>
       </c>
       <c r="I105" t="str">
         <f>INDEX([4]TextData!B:B,MATCH(E105,[4]TextData!A:A))</f>
-        <v>パッシブ封じ</v>
+        <v>ダメージカット</v>
       </c>
     </row>
     <row r="106" spans="1:9">
       <c r="A106">
-        <v>13060</v>
+        <v>13050</v>
       </c>
       <c r="B106" t="str">
         <f>INDEX(TextData!B:B,MATCH(A106,TextData!A:A))</f>
-        <v>サプライカバー</v>
+        <v>パッシブジャミング</v>
       </c>
       <c r="C106">
         <v>3010</v>
@@ -32002,10 +31998,10 @@
         <v>ステート付与</v>
       </c>
       <c r="E106">
-        <v>2430</v>
+        <v>2090</v>
       </c>
       <c r="F106">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G106">
         <v>0</v>
@@ -32015,29 +32011,29 @@
       </c>
       <c r="I106" t="str">
         <f>INDEX([4]TextData!B:B,MATCH(E106,[4]TextData!A:A))</f>
-        <v>かばう</v>
-      </c>
-    </row>
-    <row r="107" spans="1:8">
+        <v>パッシブ封じ</v>
+      </c>
+    </row>
+    <row r="107" spans="1:9">
       <c r="A107">
-        <v>13070</v>
+        <v>13060</v>
       </c>
       <c r="B107" t="str">
         <f>INDEX(TextData!B:B,MATCH(A107,TextData!A:A))</f>
-        <v>アシッドラッシュ</v>
+        <v>サプライカバー</v>
       </c>
       <c r="C107">
-        <v>5050</v>
+        <v>3010</v>
       </c>
       <c r="D107" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C107,Define!P:P))</f>
-        <v>APダメージ</v>
+        <v>ステート付与</v>
       </c>
       <c r="E107">
-        <v>200</v>
+        <v>2430</v>
       </c>
       <c r="F107">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G107">
         <v>0</v>
@@ -32045,46 +32041,46 @@
       <c r="H107">
         <v>100</v>
       </c>
-    </row>
-    <row r="108" spans="1:9">
+      <c r="I107" t="str">
+        <f>INDEX([4]TextData!B:B,MATCH(E107,[4]TextData!A:A))</f>
+        <v>かばう</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8">
       <c r="A108">
-        <v>13080</v>
+        <v>13070</v>
       </c>
       <c r="B108" t="str">
         <f>INDEX(TextData!B:B,MATCH(A108,TextData!A:A))</f>
-        <v>ライフスティール</v>
+        <v>アシッドラッシュ</v>
       </c>
       <c r="C108">
-        <v>3010</v>
+        <v>5050</v>
       </c>
       <c r="D108" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C108,Define!P:P))</f>
-        <v>ステート付与</v>
+        <v>APダメージ</v>
       </c>
       <c r="E108">
-        <v>2060</v>
+        <v>200</v>
       </c>
       <c r="F108">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G108">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="H108">
         <v>100</v>
       </c>
-      <c r="I108" t="str">
-        <f>INDEX([4]TextData!B:B,MATCH(E108,[4]TextData!A:A))</f>
-        <v>ドレイン</v>
-      </c>
     </row>
     <row r="109" spans="1:9">
       <c r="A109">
-        <v>13090</v>
+        <v>13080</v>
       </c>
       <c r="B109" t="str">
         <f>INDEX(TextData!B:B,MATCH(A109,TextData!A:A))</f>
-        <v>アイスセイバー</v>
+        <v>ライフスティール</v>
       </c>
       <c r="C109">
         <v>3010</v>
@@ -32094,7 +32090,7 @@
         <v>ステート付与</v>
       </c>
       <c r="E109">
-        <v>2140</v>
+        <v>2060</v>
       </c>
       <c r="F109">
         <v>1</v>
@@ -32107,16 +32103,16 @@
       </c>
       <c r="I109" t="str">
         <f>INDEX([4]TextData!B:B,MATCH(E109,[4]TextData!A:A))</f>
-        <v>凍結</v>
+        <v>ドレイン</v>
       </c>
     </row>
     <row r="110" spans="1:9">
       <c r="A110">
-        <v>14010</v>
+        <v>13090</v>
       </c>
       <c r="B110" t="str">
         <f>INDEX(TextData!B:B,MATCH(A110,TextData!A:A))</f>
-        <v>ディバインシールド</v>
+        <v>アイスセイバー</v>
       </c>
       <c r="C110">
         <v>3010</v>
@@ -32126,89 +32122,89 @@
         <v>ステート付与</v>
       </c>
       <c r="E110">
-        <v>2180</v>
+        <v>2140</v>
       </c>
       <c r="F110">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G110">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="H110">
         <v>100</v>
       </c>
       <c r="I110" t="str">
         <f>INDEX([4]TextData!B:B,MATCH(E110,[4]TextData!A:A))</f>
-        <v>状態異常回避</v>
-      </c>
-    </row>
-    <row r="111" spans="1:8">
+        <v>凍結</v>
+      </c>
+    </row>
+    <row r="111" spans="1:9">
       <c r="A111">
-        <v>14020</v>
+        <v>14010</v>
       </c>
       <c r="B111" t="str">
         <f>INDEX(TextData!B:B,MATCH(A111,TextData!A:A))</f>
-        <v>ライフディバイド</v>
+        <v>ディバインシールド</v>
       </c>
       <c r="C111">
-        <v>2040</v>
+        <v>3010</v>
       </c>
       <c r="D111" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C111,Define!P:P))</f>
-        <v>Hpを分け与える</v>
+        <v>ステート付与</v>
       </c>
       <c r="E111">
-        <v>25</v>
+        <v>2180</v>
       </c>
       <c r="F111">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G111">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H111">
         <v>100</v>
       </c>
-    </row>
-    <row r="112" spans="1:9">
+      <c r="I111" t="str">
+        <f>INDEX([4]TextData!B:B,MATCH(E111,[4]TextData!A:A))</f>
+        <v>状態異常回避</v>
+      </c>
+    </row>
+    <row r="112" spans="1:8">
       <c r="A112">
-        <v>14030</v>
+        <v>14020</v>
       </c>
       <c r="B112" t="str">
         <f>INDEX(TextData!B:B,MATCH(A112,TextData!A:A))</f>
-        <v>エイミングスコープ</v>
+        <v>ライフディバイド</v>
       </c>
       <c r="C112">
-        <v>3010</v>
+        <v>2040</v>
       </c>
       <c r="D112" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C112,Define!P:P))</f>
-        <v>ステート付与</v>
+        <v>Hpを分け与える</v>
       </c>
       <c r="E112">
-        <v>1081</v>
+        <v>25</v>
       </c>
       <c r="F112">
-        <v>999</v>
+        <v>0</v>
       </c>
       <c r="G112">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H112">
         <v>100</v>
       </c>
-      <c r="I112" t="str">
-        <f>INDEX([4]TextData!B:B,MATCH(E112,[4]TextData!A:A))</f>
-        <v>命中アップ</v>
-      </c>
     </row>
     <row r="113" spans="1:9">
       <c r="A113">
-        <v>14040</v>
+        <v>14030</v>
       </c>
       <c r="B113" t="str">
         <f>INDEX(TextData!B:B,MATCH(A113,TextData!A:A))</f>
-        <v>リジェネレーション</v>
+        <v>エイミングスコープ</v>
       </c>
       <c r="C113">
         <v>3010</v>
@@ -32218,7 +32214,7 @@
         <v>ステート付与</v>
       </c>
       <c r="E113">
-        <v>2040</v>
+        <v>1081</v>
       </c>
       <c r="F113">
         <v>999</v>
@@ -32231,16 +32227,16 @@
       </c>
       <c r="I113" t="str">
         <f>INDEX([4]TextData!B:B,MATCH(E113,[4]TextData!A:A))</f>
-        <v>リジェネ</v>
+        <v>命中アップ</v>
       </c>
     </row>
     <row r="114" spans="1:9">
       <c r="A114">
-        <v>14050</v>
+        <v>14040</v>
       </c>
       <c r="B114" t="str">
         <f>INDEX(TextData!B:B,MATCH(A114,TextData!A:A))</f>
-        <v>ホープフルアイリス</v>
+        <v>リジェネレーション</v>
       </c>
       <c r="C114">
         <v>3010</v>
@@ -32250,70 +32246,74 @@
         <v>ステート付与</v>
       </c>
       <c r="E114">
-        <v>1020</v>
+        <v>2040</v>
       </c>
       <c r="F114">
         <v>999</v>
       </c>
       <c r="G114">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="H114">
         <v>100</v>
       </c>
       <c r="I114" t="str">
         <f>INDEX([4]TextData!B:B,MATCH(E114,[4]TextData!A:A))</f>
-        <v>最大Hpアップ</v>
-      </c>
-    </row>
-    <row r="115" spans="1:8">
+        <v>リジェネ</v>
+      </c>
+    </row>
+    <row r="115" spans="1:9">
       <c r="A115">
-        <v>14060</v>
+        <v>14050</v>
       </c>
       <c r="B115" t="str">
         <f>INDEX(TextData!B:B,MATCH(A115,TextData!A:A))</f>
-        <v>パッシブサプライ</v>
+        <v>ホープフルアイリス</v>
       </c>
       <c r="C115">
-        <v>4020</v>
+        <v>3010</v>
       </c>
       <c r="D115" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C115,Define!P:P))</f>
-        <v>Ct回復</v>
+        <v>ステート付与</v>
       </c>
       <c r="E115">
-        <v>1</v>
+        <v>1020</v>
       </c>
       <c r="F115">
-        <v>0</v>
+        <v>999</v>
       </c>
       <c r="G115">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H115">
         <v>100</v>
       </c>
-    </row>
-    <row r="116" spans="1:9">
+      <c r="I115" t="str">
+        <f>INDEX([4]TextData!B:B,MATCH(E115,[4]TextData!A:A))</f>
+        <v>最大Hpアップ</v>
+      </c>
+    </row>
+    <row r="116" spans="1:8">
       <c r="A116">
-        <v>14070</v>
+        <v>14060</v>
       </c>
       <c r="B116" t="str">
         <f>INDEX(TextData!B:B,MATCH(A116,TextData!A:A))</f>
-        <v>ホーミングクルセイド</v>
+        <v>パッシブサプライ</v>
       </c>
       <c r="C116">
-        <v>3010</v>
+        <v>4020</v>
       </c>
       <c r="D116" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C116,Define!P:P))</f>
-        <v>ステート付与</v>
+        <v>Ct回復</v>
       </c>
       <c r="E116">
-        <v>2240</v>
+        <v>1</v>
       </c>
       <c r="F116">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G116">
         <v>0</v>
@@ -32321,31 +32321,27 @@
       <c r="H116">
         <v>100</v>
       </c>
-      <c r="I116" t="str">
-        <f>INDEX([4]TextData!B:B,MATCH(E116,[4]TextData!A:A))</f>
-        <v>必中</v>
-      </c>
-    </row>
-    <row r="117" spans="1:8">
+    </row>
+    <row r="117" spans="1:9">
       <c r="A117">
-        <v>14080</v>
+        <v>14070</v>
       </c>
       <c r="B117" t="str">
         <f>INDEX(TextData!B:B,MATCH(A117,TextData!A:A))</f>
-        <v>クイックヒール</v>
+        <v>ホーミングクルセイド</v>
       </c>
       <c r="C117">
-        <v>2010</v>
+        <v>3010</v>
       </c>
       <c r="D117" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C117,Define!P:P))</f>
-        <v>Hp回復</v>
+        <v>ステート付与</v>
       </c>
       <c r="E117">
-        <v>10</v>
+        <v>2240</v>
       </c>
       <c r="F117">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G117">
         <v>0</v>
@@ -32353,46 +32349,46 @@
       <c r="H117">
         <v>100</v>
       </c>
-    </row>
-    <row r="118" spans="1:9">
+      <c r="I117" t="str">
+        <f>INDEX([4]TextData!B:B,MATCH(E117,[4]TextData!A:A))</f>
+        <v>必中</v>
+      </c>
+    </row>
+    <row r="118" spans="1:8">
       <c r="A118">
-        <v>14090</v>
+        <v>14080</v>
       </c>
       <c r="B118" t="str">
         <f>INDEX(TextData!B:B,MATCH(A118,TextData!A:A))</f>
-        <v>リレイズ</v>
+        <v>クイックヒール</v>
       </c>
       <c r="C118">
-        <v>3010</v>
+        <v>2010</v>
       </c>
       <c r="D118" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C118,Define!P:P))</f>
-        <v>ステート付与</v>
+        <v>Hp回復</v>
       </c>
       <c r="E118">
-        <v>2450</v>
+        <v>10</v>
       </c>
       <c r="F118">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G118">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H118">
         <v>100</v>
       </c>
-      <c r="I118" t="str">
-        <f>INDEX([4]TextData!B:B,MATCH(E118,[4]TextData!A:A))</f>
-        <v>不死</v>
-      </c>
     </row>
     <row r="119" spans="1:9">
       <c r="A119">
-        <v>15010</v>
+        <v>14090</v>
       </c>
       <c r="B119" t="str">
         <f>INDEX(TextData!B:B,MATCH(A119,TextData!A:A))</f>
-        <v>イーグルアイ</v>
+        <v>リレイズ</v>
       </c>
       <c r="C119">
         <v>3010</v>
@@ -32402,29 +32398,29 @@
         <v>ステート付与</v>
       </c>
       <c r="E119">
-        <v>1070</v>
+        <v>2450</v>
       </c>
       <c r="F119">
-        <v>999</v>
+        <v>1</v>
       </c>
       <c r="G119">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="H119">
         <v>100</v>
       </c>
       <c r="I119" t="str">
         <f>INDEX([4]TextData!B:B,MATCH(E119,[4]TextData!A:A))</f>
-        <v>会心率アップ</v>
+        <v>不死</v>
       </c>
     </row>
     <row r="120" spans="1:9">
       <c r="A120">
-        <v>15020</v>
+        <v>15010</v>
       </c>
       <c r="B120" t="str">
         <f>INDEX(TextData!B:B,MATCH(A120,TextData!A:A))</f>
-        <v>ネヴァーエンド</v>
+        <v>イーグルアイ</v>
       </c>
       <c r="C120">
         <v>3010</v>
@@ -32440,7 +32436,7 @@
         <v>999</v>
       </c>
       <c r="G120">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="H120">
         <v>100</v>
@@ -32450,73 +32446,73 @@
         <v>会心率アップ</v>
       </c>
     </row>
-    <row r="121" spans="1:8">
+    <row r="121" spans="1:9">
       <c r="A121">
-        <v>15030</v>
+        <v>15020</v>
       </c>
       <c r="B121" t="str">
         <f>INDEX(TextData!B:B,MATCH(A121,TextData!A:A))</f>
-        <v>グレイブアクト</v>
+        <v>ネヴァーエンド</v>
       </c>
       <c r="C121">
-        <v>4020</v>
+        <v>3010</v>
       </c>
       <c r="D121" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C121,Define!P:P))</f>
-        <v>Ct回復</v>
+        <v>ステート付与</v>
       </c>
       <c r="E121">
-        <v>2</v>
+        <v>1070</v>
       </c>
       <c r="F121">
-        <v>0</v>
+        <v>999</v>
       </c>
       <c r="G121">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="H121">
         <v>100</v>
       </c>
-    </row>
-    <row r="122" spans="1:9">
+      <c r="I121" t="str">
+        <f>INDEX([4]TextData!B:B,MATCH(E121,[4]TextData!A:A))</f>
+        <v>会心率アップ</v>
+      </c>
+    </row>
+    <row r="122" spans="1:8">
       <c r="A122">
-        <v>15040</v>
+        <v>15030</v>
       </c>
       <c r="B122" t="str">
         <f>INDEX(TextData!B:B,MATCH(A122,TextData!A:A))</f>
-        <v>スカルグラッジ</v>
+        <v>グレイブアクト</v>
       </c>
       <c r="C122">
-        <v>3010</v>
+        <v>4020</v>
       </c>
       <c r="D122" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C122,Define!P:P))</f>
-        <v>ステート付与</v>
+        <v>Ct回復</v>
       </c>
       <c r="E122">
-        <v>2220</v>
+        <v>2</v>
       </c>
       <c r="F122">
-        <v>999</v>
+        <v>0</v>
       </c>
       <c r="G122">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H122">
         <v>100</v>
       </c>
-      <c r="I122" t="str">
-        <f>INDEX([4]TextData!B:B,MATCH(E122,[4]TextData!A:A))</f>
-        <v>即死付与</v>
-      </c>
     </row>
     <row r="123" spans="1:9">
       <c r="A123">
-        <v>15050</v>
+        <v>15040</v>
       </c>
       <c r="B123" t="str">
         <f>INDEX(TextData!B:B,MATCH(A123,TextData!A:A))</f>
-        <v>ネガティブドレイン</v>
+        <v>スカルグラッジ</v>
       </c>
       <c r="C123">
         <v>3010</v>
@@ -32526,29 +32522,29 @@
         <v>ステート付与</v>
       </c>
       <c r="E123">
-        <v>2060</v>
+        <v>2220</v>
       </c>
       <c r="F123">
-        <v>0</v>
+        <v>999</v>
       </c>
       <c r="G123">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="H123">
         <v>100</v>
       </c>
       <c r="I123" t="str">
         <f>INDEX([4]TextData!B:B,MATCH(E123,[4]TextData!A:A))</f>
-        <v>ドレイン</v>
+        <v>即死付与</v>
       </c>
     </row>
     <row r="124" spans="1:9">
       <c r="A124">
-        <v>15060</v>
+        <v>15050</v>
       </c>
       <c r="B124" t="str">
         <f>INDEX(TextData!B:B,MATCH(A124,TextData!A:A))</f>
-        <v>アンデッドペイン</v>
+        <v>ネガティブドレイン</v>
       </c>
       <c r="C124">
         <v>3010</v>
@@ -32558,29 +32554,29 @@
         <v>ステート付与</v>
       </c>
       <c r="E124">
-        <v>2270</v>
+        <v>2060</v>
       </c>
       <c r="F124">
         <v>0</v>
       </c>
       <c r="G124">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="H124">
         <v>100</v>
       </c>
       <c r="I124" t="str">
         <f>INDEX([4]TextData!B:B,MATCH(E124,[4]TextData!A:A))</f>
-        <v>アンデッド</v>
+        <v>ドレイン</v>
       </c>
     </row>
     <row r="125" spans="1:9">
       <c r="A125">
-        <v>15070</v>
+        <v>15060</v>
       </c>
       <c r="B125" t="str">
         <f>INDEX(TextData!B:B,MATCH(A125,TextData!A:A))</f>
-        <v>ジャックポッド</v>
+        <v>アンデッドペイン</v>
       </c>
       <c r="C125">
         <v>3010</v>
@@ -32590,20 +32586,20 @@
         <v>ステート付与</v>
       </c>
       <c r="E125">
-        <v>1070</v>
+        <v>2270</v>
       </c>
       <c r="F125">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G125">
-        <v>50</v>
+        <v>7</v>
       </c>
       <c r="H125">
         <v>100</v>
       </c>
       <c r="I125" t="str">
         <f>INDEX([4]TextData!B:B,MATCH(E125,[4]TextData!A:A))</f>
-        <v>会心率アップ</v>
+        <v>アンデッド</v>
       </c>
     </row>
     <row r="126" spans="1:9">
@@ -32622,7 +32618,7 @@
         <v>ステート付与</v>
       </c>
       <c r="E126">
-        <v>1082</v>
+        <v>1070</v>
       </c>
       <c r="F126">
         <v>1</v>
@@ -32635,145 +32631,149 @@
       </c>
       <c r="I126" t="str">
         <f>INDEX([4]TextData!B:B,MATCH(E126,[4]TextData!A:A))</f>
-        <v>命中ダウン</v>
-      </c>
-    </row>
-    <row r="127" spans="1:8">
+        <v>会心率アップ</v>
+      </c>
+    </row>
+    <row r="127" spans="1:9">
       <c r="A127">
-        <v>15080</v>
+        <v>15070</v>
       </c>
       <c r="B127" t="str">
         <f>INDEX(TextData!B:B,MATCH(A127,TextData!A:A))</f>
-        <v>ヒールハント</v>
+        <v>ジャックポッド</v>
       </c>
       <c r="C127">
-        <v>1100</v>
+        <v>3010</v>
       </c>
       <c r="D127" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C127,Define!P:P))</f>
-        <v>Hp貫通ダメージ</v>
+        <v>ステート付与</v>
       </c>
       <c r="E127">
-        <v>100</v>
+        <v>1082</v>
       </c>
       <c r="F127">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G127">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="H127">
         <v>100</v>
       </c>
-    </row>
-    <row r="128" spans="1:9">
+      <c r="I127" t="str">
+        <f>INDEX([4]TextData!B:B,MATCH(E127,[4]TextData!A:A))</f>
+        <v>命中ダウン</v>
+      </c>
+    </row>
+    <row r="128" spans="1:8">
       <c r="A128">
-        <v>15090</v>
+        <v>15080</v>
       </c>
       <c r="B128" t="str">
         <f>INDEX(TextData!B:B,MATCH(A128,TextData!A:A))</f>
-        <v>クイックカース</v>
+        <v>ヒールハント</v>
       </c>
       <c r="C128">
-        <v>3010</v>
+        <v>1100</v>
       </c>
       <c r="D128" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C128,Define!P:P))</f>
-        <v>ステート付与</v>
+        <v>Hp貫通ダメージ</v>
       </c>
       <c r="E128">
-        <v>1043</v>
+        <v>100</v>
       </c>
       <c r="F128">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G128">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H128">
         <v>100</v>
       </c>
-      <c r="I128" t="str">
-        <f>INDEX([4]TextData!B:B,MATCH(E128,[4]TextData!A:A))</f>
-        <v>攻撃%ダウン</v>
-      </c>
-    </row>
-    <row r="129" spans="1:8">
+    </row>
+    <row r="129" spans="1:9">
       <c r="A129">
-        <v>30010</v>
+        <v>15090</v>
       </c>
       <c r="B129" t="str">
         <f>INDEX(TextData!B:B,MATCH(A129,TextData!A:A))</f>
-        <v>ラーニングピアス</v>
+        <v>クイックカース</v>
       </c>
       <c r="C129">
-        <v>40020</v>
+        <v>3010</v>
       </c>
       <c r="D129" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C129,Define!P:P))</f>
-        <v>獲得Eｘｐ％アップ</v>
+        <v>ステート付与</v>
       </c>
       <c r="E129">
-        <v>0</v>
+        <v>1043</v>
       </c>
       <c r="F129">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="G129">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H129">
         <v>100</v>
       </c>
+      <c r="I129" t="str">
+        <f>INDEX([4]TextData!B:B,MATCH(E129,[4]TextData!A:A))</f>
+        <v>攻撃%ダウン</v>
+      </c>
     </row>
     <row r="130" spans="1:8">
       <c r="A130">
-        <v>30020</v>
+        <v>30010</v>
       </c>
       <c r="B130" t="str">
         <f>INDEX(TextData!B:B,MATCH(A130,TextData!A:A))</f>
-        <v>スティールヒール</v>
+        <v>ラーニングピアス</v>
       </c>
       <c r="C130">
-        <v>2011</v>
+        <v>40020</v>
       </c>
       <c r="D130" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C130,Define!P:P))</f>
-        <v>攻撃対象の最大Hpに比例して回復</v>
+        <v>獲得Eｘｐ％アップ</v>
       </c>
       <c r="E130">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F130">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G130">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H130">
         <v>100</v>
       </c>
     </row>
-    <row r="131" spans="1:9">
+    <row r="131" spans="1:8">
       <c r="A131">
-        <v>30030</v>
+        <v>30020</v>
       </c>
       <c r="B131" t="str">
         <f>INDEX(TextData!B:B,MATCH(A131,TextData!A:A))</f>
-        <v>ガッツ</v>
+        <v>スティールヒール</v>
       </c>
       <c r="C131">
-        <v>3010</v>
+        <v>2011</v>
       </c>
       <c r="D131" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C131,Define!P:P))</f>
-        <v>ステート付与</v>
+        <v>攻撃対象の最大Hpに比例して回復</v>
       </c>
       <c r="E131">
-        <v>2450</v>
+        <v>5</v>
       </c>
       <c r="F131">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G131">
         <v>1</v>
@@ -32781,18 +32781,14 @@
       <c r="H131">
         <v>100</v>
       </c>
-      <c r="I131" t="str">
-        <f>INDEX([4]TextData!B:B,MATCH(E131,[4]TextData!A:A))</f>
-        <v>不死</v>
-      </c>
     </row>
     <row r="132" spans="1:9">
       <c r="A132">
-        <v>100110</v>
+        <v>30030</v>
       </c>
       <c r="B132" t="str">
         <f>INDEX(TextData!B:B,MATCH(A132,TextData!A:A))</f>
-        <v>ソーイングアームド</v>
+        <v>ガッツ</v>
       </c>
       <c r="C132">
         <v>3010</v>
@@ -32802,23 +32798,23 @@
         <v>ステート付与</v>
       </c>
       <c r="E132">
-        <v>2330</v>
+        <v>2450</v>
       </c>
       <c r="F132">
-        <v>999</v>
+        <v>1</v>
       </c>
       <c r="G132">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="H132">
         <v>100</v>
       </c>
       <c r="I132" t="str">
         <f>INDEX([4]TextData!B:B,MATCH(E132,[4]TextData!A:A))</f>
-        <v>貫通</v>
-      </c>
-    </row>
-    <row r="133" spans="1:8">
+        <v>不死</v>
+      </c>
+    </row>
+    <row r="133" spans="1:9">
       <c r="A133">
         <v>100110</v>
       </c>
@@ -32827,42 +32823,46 @@
         <v>ソーイングアームド</v>
       </c>
       <c r="C133">
-        <v>7010</v>
+        <v>3010</v>
       </c>
       <c r="D133" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C133,Define!P:P))</f>
-        <v>行動後スキル</v>
+        <v>ステート付与</v>
       </c>
       <c r="E133">
-        <v>11</v>
+        <v>2330</v>
       </c>
       <c r="F133">
-        <v>0</v>
+        <v>999</v>
       </c>
       <c r="G133">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="H133">
         <v>100</v>
       </c>
+      <c r="I133" t="str">
+        <f>INDEX([4]TextData!B:B,MATCH(E133,[4]TextData!A:A))</f>
+        <v>貫通</v>
+      </c>
     </row>
     <row r="134" spans="1:8">
       <c r="A134">
-        <v>100120</v>
+        <v>100110</v>
       </c>
       <c r="B134" t="str">
         <f>INDEX(TextData!B:B,MATCH(A134,TextData!A:A))</f>
-        <v>エターナルロンド</v>
+        <v>ソーイングアームド</v>
       </c>
       <c r="C134">
-        <v>1010</v>
+        <v>7010</v>
       </c>
       <c r="D134" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C134,Define!P:P))</f>
-        <v>Hpダメージ</v>
+        <v>行動後スキル</v>
       </c>
       <c r="E134">
-        <v>400</v>
+        <v>11</v>
       </c>
       <c r="F134">
         <v>0</v>
@@ -32883,14 +32883,14 @@
         <v>エターナルロンド</v>
       </c>
       <c r="C135">
-        <v>7010</v>
+        <v>1010</v>
       </c>
       <c r="D135" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C135,Define!P:P))</f>
-        <v>行動後スキル</v>
+        <v>Hpダメージ</v>
       </c>
       <c r="E135">
-        <v>21</v>
+        <v>400</v>
       </c>
       <c r="F135">
         <v>0</v>
@@ -32902,39 +32902,35 @@
         <v>100</v>
       </c>
     </row>
-    <row r="136" spans="1:9">
+    <row r="136" spans="1:8">
       <c r="A136">
-        <v>100210</v>
+        <v>100120</v>
       </c>
       <c r="B136" t="str">
         <f>INDEX(TextData!B:B,MATCH(A136,TextData!A:A))</f>
-        <v>アブソリュートパリィ</v>
+        <v>エターナルロンド</v>
       </c>
       <c r="C136">
-        <v>3010</v>
+        <v>7010</v>
       </c>
       <c r="D136" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C136,Define!P:P))</f>
-        <v>ステート付与</v>
+        <v>行動後スキル</v>
       </c>
       <c r="E136">
-        <v>1090</v>
+        <v>21</v>
       </c>
       <c r="F136">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G136">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H136">
         <v>100</v>
       </c>
-      <c r="I136" t="str">
-        <f>INDEX([4]TextData!B:B,MATCH(E136,[4]TextData!A:A))</f>
-        <v>回避アップ</v>
-      </c>
-    </row>
-    <row r="137" spans="1:8">
+    </row>
+    <row r="137" spans="1:9">
       <c r="A137">
         <v>100210</v>
       </c>
@@ -32943,42 +32939,46 @@
         <v>アブソリュートパリィ</v>
       </c>
       <c r="C137">
-        <v>7010</v>
+        <v>3010</v>
       </c>
       <c r="D137" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C137,Define!P:P))</f>
-        <v>行動後スキル</v>
+        <v>ステート付与</v>
       </c>
       <c r="E137">
-        <v>11</v>
+        <v>1090</v>
       </c>
       <c r="F137">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G137">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H137">
         <v>100</v>
       </c>
+      <c r="I137" t="str">
+        <f>INDEX([4]TextData!B:B,MATCH(E137,[4]TextData!A:A))</f>
+        <v>回避アップ</v>
+      </c>
     </row>
     <row r="138" spans="1:8">
       <c r="A138">
-        <v>100220</v>
+        <v>100210</v>
       </c>
       <c r="B138" t="str">
         <f>INDEX(TextData!B:B,MATCH(A138,TextData!A:A))</f>
-        <v>レヴェリー</v>
+        <v>アブソリュートパリィ</v>
       </c>
       <c r="C138">
-        <v>1010</v>
+        <v>7010</v>
       </c>
       <c r="D138" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C138,Define!P:P))</f>
-        <v>Hpダメージ</v>
+        <v>行動後スキル</v>
       </c>
       <c r="E138">
-        <v>50</v>
+        <v>11</v>
       </c>
       <c r="F138">
         <v>0</v>
@@ -32999,14 +32999,14 @@
         <v>レヴェリー</v>
       </c>
       <c r="C139">
-        <v>7010</v>
+        <v>1010</v>
       </c>
       <c r="D139" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C139,Define!P:P))</f>
-        <v>行動後スキル</v>
+        <v>Hpダメージ</v>
       </c>
       <c r="E139">
-        <v>21</v>
+        <v>50</v>
       </c>
       <c r="F139">
         <v>0</v>
@@ -33018,26 +33018,26 @@
         <v>100</v>
       </c>
     </row>
-    <row r="140" spans="1:9">
+    <row r="140" spans="1:8">
       <c r="A140">
-        <v>100310</v>
+        <v>100220</v>
       </c>
       <c r="B140" t="str">
         <f>INDEX(TextData!B:B,MATCH(A140,TextData!A:A))</f>
-        <v>セイクリッドバリア</v>
+        <v>レヴェリー</v>
       </c>
       <c r="C140">
-        <v>3010</v>
+        <v>7010</v>
       </c>
       <c r="D140" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C140,Define!P:P))</f>
-        <v>ステート付与</v>
+        <v>行動後スキル</v>
       </c>
       <c r="E140">
-        <v>2050</v>
+        <v>21</v>
       </c>
       <c r="F140">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G140">
         <v>0</v>
@@ -33045,12 +33045,8 @@
       <c r="H140">
         <v>100</v>
       </c>
-      <c r="I140" t="str">
-        <f>INDEX([4]TextData!B:B,MATCH(E140,[4]TextData!A:A))</f>
-        <v>攻撃無効</v>
-      </c>
-    </row>
-    <row r="141" spans="1:8">
+    </row>
+    <row r="141" spans="1:9">
       <c r="A141">
         <v>100310</v>
       </c>
@@ -33059,17 +33055,17 @@
         <v>セイクリッドバリア</v>
       </c>
       <c r="C141">
-        <v>7010</v>
+        <v>3010</v>
       </c>
       <c r="D141" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C141,Define!P:P))</f>
-        <v>行動後スキル</v>
+        <v>ステート付与</v>
       </c>
       <c r="E141">
-        <v>11</v>
+        <v>2050</v>
       </c>
       <c r="F141">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G141">
         <v>0</v>
@@ -33077,24 +33073,28 @@
       <c r="H141">
         <v>100</v>
       </c>
+      <c r="I141" t="str">
+        <f>INDEX([4]TextData!B:B,MATCH(E141,[4]TextData!A:A))</f>
+        <v>攻撃無効</v>
+      </c>
     </row>
     <row r="142" spans="1:8">
       <c r="A142">
-        <v>100320</v>
+        <v>100310</v>
       </c>
       <c r="B142" t="str">
         <f>INDEX(TextData!B:B,MATCH(A142,TextData!A:A))</f>
-        <v>リベンジニードル</v>
+        <v>セイクリッドバリア</v>
       </c>
       <c r="C142">
-        <v>1090</v>
+        <v>7010</v>
       </c>
       <c r="D142" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C142,Define!P:P))</f>
-        <v>受けたダメージ総計ダメージ</v>
+        <v>行動後スキル</v>
       </c>
       <c r="E142">
-        <v>100</v>
+        <v>11</v>
       </c>
       <c r="F142">
         <v>0</v>
@@ -33115,14 +33115,14 @@
         <v>リベンジニードル</v>
       </c>
       <c r="C143">
-        <v>7010</v>
+        <v>1090</v>
       </c>
       <c r="D143" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C143,Define!P:P))</f>
-        <v>行動後スキル</v>
+        <v>受けたダメージ総計ダメージ</v>
       </c>
       <c r="E143">
-        <v>21</v>
+        <v>100</v>
       </c>
       <c r="F143">
         <v>0</v>
@@ -33134,23 +33134,23 @@
         <v>100</v>
       </c>
     </row>
-    <row r="144" spans="1:9">
+    <row r="144" spans="1:8">
       <c r="A144">
-        <v>100410</v>
+        <v>100320</v>
       </c>
       <c r="B144" t="str">
         <f>INDEX(TextData!B:B,MATCH(A144,TextData!A:A))</f>
-        <v>アバンデンス</v>
+        <v>リベンジニードル</v>
       </c>
       <c r="C144">
-        <v>3020</v>
+        <v>7010</v>
       </c>
       <c r="D144" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C144,Define!P:P))</f>
-        <v>ステート解除</v>
+        <v>行動後スキル</v>
       </c>
       <c r="E144">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="F144">
         <v>0</v>
@@ -33161,12 +33161,8 @@
       <c r="H144">
         <v>100</v>
       </c>
-      <c r="I144" t="str">
-        <f>INDEX([4]TextData!B:B,MATCH(E144,[4]TextData!A:A))</f>
-        <v>戦闘不能</v>
-      </c>
-    </row>
-    <row r="145" spans="1:8">
+    </row>
+    <row r="145" spans="1:9">
       <c r="A145">
         <v>100410</v>
       </c>
@@ -33175,14 +33171,14 @@
         <v>アバンデンス</v>
       </c>
       <c r="C145">
-        <v>2010</v>
+        <v>3020</v>
       </c>
       <c r="D145" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C145,Define!P:P))</f>
-        <v>Hp回復</v>
+        <v>ステート解除</v>
       </c>
       <c r="E145">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="F145">
         <v>0</v>
@@ -33192,6 +33188,10 @@
       </c>
       <c r="H145">
         <v>100</v>
+      </c>
+      <c r="I145" t="str">
+        <f>INDEX([4]TextData!B:B,MATCH(E145,[4]TextData!A:A))</f>
+        <v>戦闘不能</v>
       </c>
     </row>
     <row r="146" spans="1:8">
@@ -33203,14 +33203,14 @@
         <v>アバンデンス</v>
       </c>
       <c r="C146">
-        <v>7010</v>
+        <v>2010</v>
       </c>
       <c r="D146" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C146,Define!P:P))</f>
-        <v>行動後スキル</v>
+        <v>Hp回復</v>
       </c>
       <c r="E146">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="F146">
         <v>0</v>
@@ -33222,39 +33222,35 @@
         <v>100</v>
       </c>
     </row>
-    <row r="147" spans="1:9">
+    <row r="147" spans="1:8">
       <c r="A147">
-        <v>100420</v>
+        <v>100410</v>
       </c>
       <c r="B147" t="str">
         <f>INDEX(TextData!B:B,MATCH(A147,TextData!A:A))</f>
-        <v>ハーヴェスト</v>
+        <v>アバンデンス</v>
       </c>
       <c r="C147">
-        <v>3010</v>
+        <v>7010</v>
       </c>
       <c r="D147" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C147,Define!P:P))</f>
-        <v>ステート付与</v>
+        <v>行動後スキル</v>
       </c>
       <c r="E147">
-        <v>2040</v>
+        <v>11</v>
       </c>
       <c r="F147">
-        <v>999</v>
+        <v>0</v>
       </c>
       <c r="G147">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H147">
         <v>100</v>
       </c>
-      <c r="I147" t="str">
-        <f>INDEX([4]TextData!B:B,MATCH(E147,[4]TextData!A:A))</f>
-        <v>リジェネ</v>
-      </c>
-    </row>
-    <row r="148" spans="1:8">
+    </row>
+    <row r="148" spans="1:9">
       <c r="A148">
         <v>100420</v>
       </c>
@@ -33263,58 +33259,58 @@
         <v>ハーヴェスト</v>
       </c>
       <c r="C148">
-        <v>7010</v>
+        <v>3010</v>
       </c>
       <c r="D148" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C148,Define!P:P))</f>
-        <v>行動後スキル</v>
+        <v>ステート付与</v>
       </c>
       <c r="E148">
-        <v>21</v>
+        <v>2040</v>
       </c>
       <c r="F148">
-        <v>0</v>
+        <v>999</v>
       </c>
       <c r="G148">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H148">
         <v>100</v>
       </c>
-    </row>
-    <row r="149" spans="1:9">
+      <c r="I148" t="str">
+        <f>INDEX([4]TextData!B:B,MATCH(E148,[4]TextData!A:A))</f>
+        <v>リジェネ</v>
+      </c>
+    </row>
+    <row r="149" spans="1:8">
       <c r="A149">
-        <v>100510</v>
+        <v>100420</v>
       </c>
       <c r="B149" t="str">
         <f>INDEX(TextData!B:B,MATCH(A149,TextData!A:A))</f>
-        <v>カースドブレイク</v>
+        <v>ハーヴェスト</v>
       </c>
       <c r="C149">
-        <v>3010</v>
+        <v>7010</v>
       </c>
       <c r="D149" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C149,Define!P:P))</f>
-        <v>ステート付与</v>
+        <v>行動後スキル</v>
       </c>
       <c r="E149">
-        <v>2470</v>
+        <v>21</v>
       </c>
       <c r="F149">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G149">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H149">
         <v>100</v>
       </c>
-      <c r="I149" t="str">
-        <f>INDEX([4]TextData!B:B,MATCH(E149,[4]TextData!A:A))</f>
-        <v>呪詛</v>
-      </c>
-    </row>
-    <row r="150" spans="1:8">
+    </row>
+    <row r="150" spans="1:9">
       <c r="A150">
         <v>100510</v>
       </c>
@@ -33323,58 +33319,58 @@
         <v>カースドブレイク</v>
       </c>
       <c r="C150">
-        <v>7010</v>
+        <v>3010</v>
       </c>
       <c r="D150" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C150,Define!P:P))</f>
-        <v>行動後スキル</v>
+        <v>ステート付与</v>
       </c>
       <c r="E150">
-        <v>11</v>
+        <v>2470</v>
       </c>
       <c r="F150">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G150">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H150">
         <v>100</v>
       </c>
-    </row>
-    <row r="151" spans="1:9">
+      <c r="I150" t="str">
+        <f>INDEX([4]TextData!B:B,MATCH(E150,[4]TextData!A:A))</f>
+        <v>呪詛</v>
+      </c>
+    </row>
+    <row r="151" spans="1:8">
       <c r="A151">
-        <v>100520</v>
+        <v>100510</v>
       </c>
       <c r="B151" t="str">
         <f>INDEX(TextData!B:B,MATCH(A151,TextData!A:A))</f>
-        <v>ムーンライトレイ</v>
+        <v>カースドブレイク</v>
       </c>
       <c r="C151">
-        <v>3010</v>
+        <v>7010</v>
       </c>
       <c r="D151" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C151,Define!P:P))</f>
-        <v>ステート付与</v>
+        <v>行動後スキル</v>
       </c>
       <c r="E151">
-        <v>2010</v>
+        <v>11</v>
       </c>
       <c r="F151">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G151">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="H151">
         <v>100</v>
       </c>
-      <c r="I151" t="str">
-        <f>INDEX([4]TextData!B:B,MATCH(E151,[4]TextData!A:A))</f>
-        <v>毒</v>
-      </c>
-    </row>
-    <row r="152" spans="1:8">
+    </row>
+    <row r="152" spans="1:9">
       <c r="A152">
         <v>100520</v>
       </c>
@@ -33383,42 +33379,46 @@
         <v>ムーンライトレイ</v>
       </c>
       <c r="C152">
-        <v>7010</v>
+        <v>3010</v>
       </c>
       <c r="D152" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C152,Define!P:P))</f>
-        <v>行動後スキル</v>
+        <v>ステート付与</v>
       </c>
       <c r="E152">
-        <v>21</v>
+        <v>2010</v>
       </c>
       <c r="F152">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G152">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="H152">
         <v>100</v>
       </c>
+      <c r="I152" t="str">
+        <f>INDEX([4]TextData!B:B,MATCH(E152,[4]TextData!A:A))</f>
+        <v>毒</v>
+      </c>
     </row>
     <row r="153" spans="1:8">
       <c r="A153">
-        <v>100610</v>
+        <v>100520</v>
       </c>
       <c r="B153" t="str">
         <f>INDEX(TextData!B:B,MATCH(A153,TextData!A:A))</f>
-        <v>サンフレイム</v>
+        <v>ムーンライトレイ</v>
       </c>
       <c r="C153">
-        <v>4020</v>
+        <v>7010</v>
       </c>
       <c r="D153" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C153,Define!P:P))</f>
-        <v>Ct回復</v>
+        <v>行動後スキル</v>
       </c>
       <c r="E153">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="F153">
         <v>0</v>
@@ -33439,14 +33439,14 @@
         <v>サンフレイム</v>
       </c>
       <c r="C154">
-        <v>7010</v>
+        <v>4020</v>
       </c>
       <c r="D154" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C154,Define!P:P))</f>
-        <v>行動後スキル</v>
+        <v>Ct回復</v>
       </c>
       <c r="E154">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="F154">
         <v>0</v>
@@ -33460,21 +33460,21 @@
     </row>
     <row r="155" spans="1:8">
       <c r="A155">
-        <v>100620</v>
+        <v>100610</v>
       </c>
       <c r="B155" t="str">
         <f>INDEX(TextData!B:B,MATCH(A155,TextData!A:A))</f>
-        <v>フレイムタン</v>
+        <v>サンフレイム</v>
       </c>
       <c r="C155">
-        <v>1010</v>
+        <v>7010</v>
       </c>
       <c r="D155" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C155,Define!P:P))</f>
-        <v>Hpダメージ</v>
+        <v>行動後スキル</v>
       </c>
       <c r="E155">
-        <v>200</v>
+        <v>11</v>
       </c>
       <c r="F155">
         <v>0</v>
@@ -33495,14 +33495,14 @@
         <v>フレイムタン</v>
       </c>
       <c r="C156">
-        <v>4010</v>
+        <v>1010</v>
       </c>
       <c r="D156" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C156,Define!P:P))</f>
-        <v>Ctダメージ</v>
+        <v>Hpダメージ</v>
       </c>
       <c r="E156">
-        <v>2</v>
+        <v>200</v>
       </c>
       <c r="F156">
         <v>0</v>
@@ -33523,14 +33523,14 @@
         <v>フレイムタン</v>
       </c>
       <c r="C157">
-        <v>7010</v>
+        <v>4010</v>
       </c>
       <c r="D157" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C157,Define!P:P))</f>
-        <v>行動後スキル</v>
+        <v>Ctダメージ</v>
       </c>
       <c r="E157">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="F157">
         <v>0</v>
@@ -33542,26 +33542,26 @@
         <v>100</v>
       </c>
     </row>
-    <row r="158" spans="1:9">
+    <row r="158" spans="1:8">
       <c r="A158">
-        <v>100710</v>
+        <v>100620</v>
       </c>
       <c r="B158" t="str">
         <f>INDEX(TextData!B:B,MATCH(A158,TextData!A:A))</f>
-        <v>ライズザフラッグ</v>
+        <v>フレイムタン</v>
       </c>
       <c r="C158">
-        <v>3010</v>
+        <v>7010</v>
       </c>
       <c r="D158" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C158,Define!P:P))</f>
-        <v>ステート付与</v>
+        <v>行動後スキル</v>
       </c>
       <c r="E158">
-        <v>2420</v>
+        <v>21</v>
       </c>
       <c r="F158">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G158">
         <v>0</v>
@@ -33569,12 +33569,8 @@
       <c r="H158">
         <v>100</v>
       </c>
-      <c r="I158" t="str">
-        <f>INDEX([4]TextData!B:B,MATCH(E158,[4]TextData!A:A))</f>
-        <v>フォロー</v>
-      </c>
-    </row>
-    <row r="159" spans="1:8">
+    </row>
+    <row r="159" spans="1:9">
       <c r="A159">
         <v>100710</v>
       </c>
@@ -33583,17 +33579,17 @@
         <v>ライズザフラッグ</v>
       </c>
       <c r="C159">
-        <v>7010</v>
+        <v>3010</v>
       </c>
       <c r="D159" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C159,Define!P:P))</f>
-        <v>行動後スキル</v>
+        <v>ステート付与</v>
       </c>
       <c r="E159">
-        <v>11</v>
+        <v>2420</v>
       </c>
       <c r="F159">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G159">
         <v>0</v>
@@ -33601,37 +33597,37 @@
       <c r="H159">
         <v>100</v>
       </c>
-    </row>
-    <row r="160" spans="1:9">
+      <c r="I159" t="str">
+        <f>INDEX([4]TextData!B:B,MATCH(E159,[4]TextData!A:A))</f>
+        <v>フォロー</v>
+      </c>
+    </row>
+    <row r="160" spans="1:8">
       <c r="A160">
-        <v>100720</v>
+        <v>100710</v>
       </c>
       <c r="B160" t="str">
         <f>INDEX(TextData!B:B,MATCH(A160,TextData!A:A))</f>
-        <v>オーバーリミット</v>
+        <v>ライズザフラッグ</v>
       </c>
       <c r="C160">
-        <v>3010</v>
+        <v>7010</v>
       </c>
       <c r="D160" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C160,Define!P:P))</f>
-        <v>ステート付与</v>
+        <v>行動後スキル</v>
       </c>
       <c r="E160">
-        <v>1040</v>
+        <v>11</v>
       </c>
       <c r="F160">
-        <v>999</v>
+        <v>0</v>
       </c>
       <c r="G160">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H160">
         <v>100</v>
-      </c>
-      <c r="I160" t="str">
-        <f>INDEX([4]TextData!B:B,MATCH(E160,[4]TextData!A:A))</f>
-        <v>攻撃アップ</v>
       </c>
     </row>
     <row r="161" spans="1:9">
@@ -33650,7 +33646,7 @@
         <v>ステート付与</v>
       </c>
       <c r="E161">
-        <v>1050</v>
+        <v>1040</v>
       </c>
       <c r="F161">
         <v>999</v>
@@ -33663,10 +33659,10 @@
       </c>
       <c r="I161" t="str">
         <f>INDEX([4]TextData!B:B,MATCH(E161,[4]TextData!A:A))</f>
-        <v>防御アップ</v>
-      </c>
-    </row>
-    <row r="162" spans="1:8">
+        <v>攻撃アップ</v>
+      </c>
+    </row>
+    <row r="162" spans="1:9">
       <c r="A162">
         <v>100720</v>
       </c>
@@ -33675,55 +33671,55 @@
         <v>オーバーリミット</v>
       </c>
       <c r="C162">
-        <v>7010</v>
+        <v>3010</v>
       </c>
       <c r="D162" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C162,Define!P:P))</f>
-        <v>行動後スキル</v>
+        <v>ステート付与</v>
       </c>
       <c r="E162">
-        <v>21</v>
+        <v>1050</v>
       </c>
       <c r="F162">
-        <v>0</v>
+        <v>999</v>
       </c>
       <c r="G162">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H162">
         <v>100</v>
       </c>
-    </row>
-    <row r="163" spans="1:9">
+      <c r="I162" t="str">
+        <f>INDEX([4]TextData!B:B,MATCH(E162,[4]TextData!A:A))</f>
+        <v>防御アップ</v>
+      </c>
+    </row>
+    <row r="163" spans="1:8">
       <c r="A163">
-        <v>100810</v>
+        <v>100720</v>
       </c>
       <c r="B163" t="str">
         <f>INDEX(TextData!B:B,MATCH(A163,TextData!A:A))</f>
-        <v>テンパランス</v>
+        <v>オーバーリミット</v>
       </c>
       <c r="C163">
-        <v>3010</v>
+        <v>7010</v>
       </c>
       <c r="D163" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C163,Define!P:P))</f>
-        <v>ステート付与</v>
+        <v>行動後スキル</v>
       </c>
       <c r="E163">
-        <v>1040</v>
+        <v>21</v>
       </c>
       <c r="F163">
-        <v>999</v>
+        <v>0</v>
       </c>
       <c r="G163">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H163">
         <v>100</v>
-      </c>
-      <c r="I163" t="str">
-        <f>INDEX([4]TextData!B:B,MATCH(E163,[4]TextData!A:A))</f>
-        <v>攻撃アップ</v>
       </c>
     </row>
     <row r="164" spans="1:9">
@@ -33742,7 +33738,7 @@
         <v>ステート付与</v>
       </c>
       <c r="E164">
-        <v>1050</v>
+        <v>1040</v>
       </c>
       <c r="F164">
         <v>999</v>
@@ -33755,10 +33751,10 @@
       </c>
       <c r="I164" t="str">
         <f>INDEX([4]TextData!B:B,MATCH(E164,[4]TextData!A:A))</f>
-        <v>防御アップ</v>
-      </c>
-    </row>
-    <row r="165" spans="1:8">
+        <v>攻撃アップ</v>
+      </c>
+    </row>
+    <row r="165" spans="1:9">
       <c r="A165">
         <v>100810</v>
       </c>
@@ -33767,42 +33763,46 @@
         <v>テンパランス</v>
       </c>
       <c r="C165">
-        <v>7010</v>
+        <v>3010</v>
       </c>
       <c r="D165" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C165,Define!P:P))</f>
-        <v>行動後スキル</v>
+        <v>ステート付与</v>
       </c>
       <c r="E165">
-        <v>11</v>
+        <v>1050</v>
       </c>
       <c r="F165">
-        <v>0</v>
+        <v>999</v>
       </c>
       <c r="G165">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H165">
         <v>100</v>
       </c>
+      <c r="I165" t="str">
+        <f>INDEX([4]TextData!B:B,MATCH(E165,[4]TextData!A:A))</f>
+        <v>防御アップ</v>
+      </c>
     </row>
     <row r="166" spans="1:8">
       <c r="A166">
-        <v>100820</v>
+        <v>100810</v>
       </c>
       <c r="B166" t="str">
         <f>INDEX(TextData!B:B,MATCH(A166,TextData!A:A))</f>
-        <v>シエルクルセイダー</v>
+        <v>テンパランス</v>
       </c>
       <c r="C166">
-        <v>1010</v>
+        <v>7010</v>
       </c>
       <c r="D166" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C166,Define!P:P))</f>
-        <v>Hpダメージ</v>
+        <v>行動後スキル</v>
       </c>
       <c r="E166">
-        <v>300</v>
+        <v>11</v>
       </c>
       <c r="F166">
         <v>0</v>
@@ -33823,14 +33823,14 @@
         <v>シエルクルセイダー</v>
       </c>
       <c r="C167">
-        <v>7010</v>
+        <v>1010</v>
       </c>
       <c r="D167" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C167,Define!P:P))</f>
-        <v>行動後スキル</v>
+        <v>Hpダメージ</v>
       </c>
       <c r="E167">
-        <v>21</v>
+        <v>300</v>
       </c>
       <c r="F167">
         <v>0</v>
@@ -33844,21 +33844,21 @@
     </row>
     <row r="168" spans="1:8">
       <c r="A168">
-        <v>100910</v>
+        <v>100820</v>
       </c>
       <c r="B168" t="str">
         <f>INDEX(TextData!B:B,MATCH(A168,TextData!A:A))</f>
-        <v>バーニングカウンター</v>
+        <v>シエルクルセイダー</v>
       </c>
       <c r="C168">
-        <v>1010</v>
+        <v>7010</v>
       </c>
       <c r="D168" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C168,Define!P:P))</f>
-        <v>Hpダメージ</v>
+        <v>行動後スキル</v>
       </c>
       <c r="E168">
-        <v>350</v>
+        <v>21</v>
       </c>
       <c r="F168">
         <v>0</v>
@@ -33879,14 +33879,14 @@
         <v>バーニングカウンター</v>
       </c>
       <c r="C169">
-        <v>7010</v>
+        <v>1010</v>
       </c>
       <c r="D169" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C169,Define!P:P))</f>
-        <v>行動後スキル</v>
+        <v>Hpダメージ</v>
       </c>
       <c r="E169">
-        <v>100911</v>
+        <v>350</v>
       </c>
       <c r="F169">
         <v>0</v>
@@ -33900,7 +33900,7 @@
     </row>
     <row r="170" spans="1:8">
       <c r="A170">
-        <v>100911</v>
+        <v>100910</v>
       </c>
       <c r="B170" t="str">
         <f>INDEX(TextData!B:B,MATCH(A170,TextData!A:A))</f>
@@ -33914,7 +33914,7 @@
         <v>行動後スキル</v>
       </c>
       <c r="E170">
-        <v>11</v>
+        <v>100911</v>
       </c>
       <c r="F170">
         <v>0</v>
@@ -33928,21 +33928,21 @@
     </row>
     <row r="171" spans="1:8">
       <c r="A171">
-        <v>100920</v>
+        <v>100911</v>
       </c>
       <c r="B171" t="str">
         <f>INDEX(TextData!B:B,MATCH(A171,TextData!A:A))</f>
-        <v>プロミネンス</v>
+        <v>バーニングカウンター</v>
       </c>
       <c r="C171">
-        <v>1010</v>
+        <v>7010</v>
       </c>
       <c r="D171" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C171,Define!P:P))</f>
-        <v>Hpダメージ</v>
+        <v>行動後スキル</v>
       </c>
       <c r="E171">
-        <v>400</v>
+        <v>11</v>
       </c>
       <c r="F171">
         <v>0</v>
@@ -33963,14 +33963,14 @@
         <v>プロミネンス</v>
       </c>
       <c r="C172">
-        <v>7010</v>
+        <v>1010</v>
       </c>
       <c r="D172" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C172,Define!P:P))</f>
-        <v>行動後スキル</v>
+        <v>Hpダメージ</v>
       </c>
       <c r="E172">
-        <v>100921</v>
+        <v>400</v>
       </c>
       <c r="F172">
         <v>0</v>
@@ -33982,39 +33982,35 @@
         <v>100</v>
       </c>
     </row>
-    <row r="173" spans="1:9">
+    <row r="173" spans="1:8">
       <c r="A173">
-        <v>100921</v>
+        <v>100920</v>
       </c>
       <c r="B173" t="str">
         <f>INDEX(TextData!B:B,MATCH(A173,TextData!A:A))</f>
         <v>プロミネンス</v>
       </c>
       <c r="C173">
-        <v>3010</v>
+        <v>7010</v>
       </c>
       <c r="D173" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C173,Define!P:P))</f>
-        <v>ステート付与</v>
+        <v>行動後スキル</v>
       </c>
       <c r="E173">
-        <v>1070</v>
+        <v>100921</v>
       </c>
       <c r="F173">
-        <v>999</v>
+        <v>0</v>
       </c>
       <c r="G173">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="H173">
         <v>100</v>
       </c>
-      <c r="I173" t="str">
-        <f>INDEX([4]TextData!B:B,MATCH(E173,[4]TextData!A:A))</f>
-        <v>会心率アップ</v>
-      </c>
-    </row>
-    <row r="174" spans="1:8">
+    </row>
+    <row r="174" spans="1:9">
       <c r="A174">
         <v>100921</v>
       </c>
@@ -34023,42 +34019,46 @@
         <v>プロミネンス</v>
       </c>
       <c r="C174">
-        <v>7010</v>
+        <v>3010</v>
       </c>
       <c r="D174" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C174,Define!P:P))</f>
-        <v>行動後スキル</v>
+        <v>ステート付与</v>
       </c>
       <c r="E174">
-        <v>21</v>
+        <v>1070</v>
       </c>
       <c r="F174">
-        <v>0</v>
+        <v>999</v>
       </c>
       <c r="G174">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="H174">
         <v>100</v>
       </c>
+      <c r="I174" t="str">
+        <f>INDEX([4]TextData!B:B,MATCH(E174,[4]TextData!A:A))</f>
+        <v>会心率アップ</v>
+      </c>
     </row>
     <row r="175" spans="1:8">
       <c r="A175">
-        <v>101010</v>
+        <v>100921</v>
       </c>
       <c r="B175" t="str">
         <f>INDEX(TextData!B:B,MATCH(A175,TextData!A:A))</f>
-        <v>エウロス</v>
+        <v>プロミネンス</v>
       </c>
       <c r="C175">
-        <v>12010</v>
+        <v>7010</v>
       </c>
       <c r="D175" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C175,Define!P:P))</f>
-        <v>最後に受けたAbnormalを相手に移す</v>
+        <v>行動後スキル</v>
       </c>
       <c r="E175">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="F175">
         <v>0</v>
@@ -34079,11 +34079,11 @@
         <v>エウロス</v>
       </c>
       <c r="C176">
-        <v>13010</v>
+        <v>12010</v>
       </c>
       <c r="D176" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C176,Define!P:P))</f>
-        <v>対象のバフを奪い取る</v>
+        <v>最後に受けたAbnormalを相手に移す</v>
       </c>
       <c r="E176">
         <v>0</v>
@@ -34107,14 +34107,14 @@
         <v>エウロス</v>
       </c>
       <c r="C177">
-        <v>7010</v>
+        <v>13010</v>
       </c>
       <c r="D177" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C177,Define!P:P))</f>
-        <v>行動後スキル</v>
+        <v>対象のバフを奪い取る</v>
       </c>
       <c r="E177">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="F177">
         <v>0</v>
@@ -34128,21 +34128,21 @@
     </row>
     <row r="178" spans="1:8">
       <c r="A178">
-        <v>101020</v>
+        <v>101010</v>
       </c>
       <c r="B178" t="str">
         <f>INDEX(TextData!B:B,MATCH(A178,TextData!A:A))</f>
-        <v>ボレアス</v>
+        <v>エウロス</v>
       </c>
       <c r="C178">
-        <v>1010</v>
+        <v>7010</v>
       </c>
       <c r="D178" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C178,Define!P:P))</f>
-        <v>Hpダメージ</v>
+        <v>行動後スキル</v>
       </c>
       <c r="E178">
-        <v>300</v>
+        <v>11</v>
       </c>
       <c r="F178">
         <v>0</v>
@@ -34163,14 +34163,14 @@
         <v>ボレアス</v>
       </c>
       <c r="C179">
-        <v>7010</v>
+        <v>1010</v>
       </c>
       <c r="D179" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C179,Define!P:P))</f>
-        <v>行動後スキル</v>
+        <v>Hpダメージ</v>
       </c>
       <c r="E179">
-        <v>21</v>
+        <v>300</v>
       </c>
       <c r="F179">
         <v>0</v>
@@ -34182,39 +34182,35 @@
         <v>100</v>
       </c>
     </row>
-    <row r="180" spans="1:9">
+    <row r="180" spans="1:8">
       <c r="A180">
-        <v>101110</v>
+        <v>101020</v>
       </c>
       <c r="B180" t="str">
         <f>INDEX(TextData!B:B,MATCH(A180,TextData!A:A))</f>
-        <v>アバランシュ</v>
+        <v>ボレアス</v>
       </c>
       <c r="C180">
-        <v>3070</v>
+        <v>7010</v>
       </c>
       <c r="D180" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C180,Define!P:P))</f>
-        <v>ステートの効果を変更</v>
+        <v>行動後スキル</v>
       </c>
       <c r="E180">
-        <v>2140</v>
+        <v>21</v>
       </c>
       <c r="F180">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G180">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H180">
         <v>100</v>
       </c>
-      <c r="I180" t="str">
-        <f>INDEX([4]TextData!B:B,MATCH(E180,[4]TextData!A:A))</f>
-        <v>凍結</v>
-      </c>
-    </row>
-    <row r="181" spans="1:8">
+    </row>
+    <row r="181" spans="1:9">
       <c r="A181">
         <v>101110</v>
       </c>
@@ -34223,48 +34219,52 @@
         <v>アバランシュ</v>
       </c>
       <c r="C181">
-        <v>7010</v>
+        <v>3070</v>
       </c>
       <c r="D181" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C181,Define!P:P))</f>
-        <v>行動後スキル</v>
+        <v>ステートの効果を変更</v>
       </c>
       <c r="E181">
-        <v>11</v>
+        <v>2140</v>
       </c>
       <c r="F181">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G181">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H181">
         <v>100</v>
       </c>
+      <c r="I181" t="str">
+        <f>INDEX([4]TextData!B:B,MATCH(E181,[4]TextData!A:A))</f>
+        <v>凍結</v>
+      </c>
     </row>
     <row r="182" spans="1:8">
       <c r="A182">
-        <v>101120</v>
+        <v>101110</v>
       </c>
       <c r="B182" t="str">
         <f>INDEX(TextData!B:B,MATCH(A182,TextData!A:A))</f>
-        <v>ブリザードコフィン</v>
+        <v>アバランシュ</v>
       </c>
       <c r="C182">
-        <v>1040</v>
+        <v>7010</v>
       </c>
       <c r="D182" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C182,Define!P:P))</f>
-        <v>特定ステートダメージ</v>
+        <v>行動後スキル</v>
       </c>
       <c r="E182">
-        <v>400</v>
+        <v>11</v>
       </c>
       <c r="F182">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="G182">
-        <v>2140</v>
+        <v>0</v>
       </c>
       <c r="H182">
         <v>100</v>
@@ -34279,58 +34279,54 @@
         <v>ブリザードコフィン</v>
       </c>
       <c r="C183">
-        <v>7010</v>
+        <v>1040</v>
       </c>
       <c r="D183" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C183,Define!P:P))</f>
-        <v>行動後スキル</v>
+        <v>特定ステートダメージ</v>
       </c>
       <c r="E183">
-        <v>21</v>
+        <v>400</v>
       </c>
       <c r="F183">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="G183">
-        <v>0</v>
+        <v>2140</v>
       </c>
       <c r="H183">
         <v>100</v>
       </c>
     </row>
-    <row r="184" ht="11" customHeight="1" spans="1:9">
+    <row r="184" spans="1:8">
       <c r="A184">
-        <v>200110</v>
+        <v>101120</v>
       </c>
       <c r="B184" t="str">
         <f>INDEX(TextData!B:B,MATCH(A184,TextData!A:A))</f>
-        <v>スリータイムス</v>
+        <v>ブリザードコフィン</v>
       </c>
       <c r="C184">
-        <v>3010</v>
+        <v>7010</v>
       </c>
       <c r="D184" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C184,Define!P:P))</f>
-        <v>ステート付与</v>
+        <v>行動後スキル</v>
       </c>
       <c r="E184">
-        <v>1040</v>
+        <v>21</v>
       </c>
       <c r="F184">
-        <v>999</v>
+        <v>0</v>
       </c>
       <c r="G184">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H184">
         <v>100</v>
       </c>
-      <c r="I184" t="str">
-        <f>INDEX([4]TextData!B:B,MATCH(E184,[4]TextData!A:A))</f>
-        <v>攻撃アップ</v>
-      </c>
-    </row>
-    <row r="185" spans="1:8">
+    </row>
+    <row r="185" ht="11" customHeight="1" spans="1:9">
       <c r="A185">
         <v>200110</v>
       </c>
@@ -34339,42 +34335,46 @@
         <v>スリータイムス</v>
       </c>
       <c r="C185">
-        <v>7010</v>
+        <v>3010</v>
       </c>
       <c r="D185" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C185,Define!P:P))</f>
-        <v>行動後スキル</v>
+        <v>ステート付与</v>
       </c>
       <c r="E185">
-        <v>11</v>
+        <v>1040</v>
       </c>
       <c r="F185">
-        <v>0</v>
+        <v>999</v>
       </c>
       <c r="G185">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H185">
         <v>100</v>
       </c>
+      <c r="I185" t="str">
+        <f>INDEX([4]TextData!B:B,MATCH(E185,[4]TextData!A:A))</f>
+        <v>攻撃アップ</v>
+      </c>
     </row>
     <row r="186" spans="1:8">
       <c r="A186">
-        <v>200120</v>
+        <v>200110</v>
       </c>
       <c r="B186" t="str">
         <f>INDEX(TextData!B:B,MATCH(A186,TextData!A:A))</f>
-        <v>アングリークライ</v>
+        <v>スリータイムス</v>
       </c>
       <c r="C186">
-        <v>1010</v>
+        <v>7010</v>
       </c>
       <c r="D186" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C186,Define!P:P))</f>
-        <v>Hpダメージ</v>
+        <v>行動後スキル</v>
       </c>
       <c r="E186">
-        <v>250</v>
+        <v>11</v>
       </c>
       <c r="F186">
         <v>0</v>
@@ -34395,14 +34395,14 @@
         <v>アングリークライ</v>
       </c>
       <c r="C187">
-        <v>7010</v>
+        <v>1010</v>
       </c>
       <c r="D187" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C187,Define!P:P))</f>
-        <v>行動後スキル</v>
+        <v>Hpダメージ</v>
       </c>
       <c r="E187">
-        <v>21</v>
+        <v>250</v>
       </c>
       <c r="F187">
         <v>0</v>
@@ -34414,39 +34414,35 @@
         <v>100</v>
       </c>
     </row>
-    <row r="188" ht="11" customHeight="1" spans="1:9">
+    <row r="188" spans="1:8">
       <c r="A188">
-        <v>200210</v>
+        <v>200120</v>
       </c>
       <c r="B188" t="str">
         <f>INDEX(TextData!B:B,MATCH(A188,TextData!A:A))</f>
-        <v>マイトレインフォース</v>
+        <v>アングリークライ</v>
       </c>
       <c r="C188">
-        <v>3010</v>
+        <v>7010</v>
       </c>
       <c r="D188" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C188,Define!P:P))</f>
-        <v>ステート付与</v>
+        <v>行動後スキル</v>
       </c>
       <c r="E188">
-        <v>1040</v>
+        <v>21</v>
       </c>
       <c r="F188">
-        <v>999</v>
+        <v>0</v>
       </c>
       <c r="G188">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="H188">
         <v>100</v>
       </c>
-      <c r="I188" t="str">
-        <f>INDEX([4]TextData!B:B,MATCH(E188,[4]TextData!A:A))</f>
-        <v>攻撃アップ</v>
-      </c>
-    </row>
-    <row r="189" spans="1:8">
+    </row>
+    <row r="189" ht="11" customHeight="1" spans="1:9">
       <c r="A189">
         <v>200210</v>
       </c>
@@ -34455,42 +34451,46 @@
         <v>マイトレインフォース</v>
       </c>
       <c r="C189">
-        <v>7010</v>
+        <v>3010</v>
       </c>
       <c r="D189" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C189,Define!P:P))</f>
-        <v>行動後スキル</v>
+        <v>ステート付与</v>
       </c>
       <c r="E189">
-        <v>11</v>
+        <v>1040</v>
       </c>
       <c r="F189">
-        <v>0</v>
+        <v>999</v>
       </c>
       <c r="G189">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H189">
         <v>100</v>
       </c>
+      <c r="I189" t="str">
+        <f>INDEX([4]TextData!B:B,MATCH(E189,[4]TextData!A:A))</f>
+        <v>攻撃アップ</v>
+      </c>
     </row>
     <row r="190" spans="1:8">
       <c r="A190">
-        <v>200220</v>
+        <v>200210</v>
       </c>
       <c r="B190" t="str">
         <f>INDEX(TextData!B:B,MATCH(A190,TextData!A:A))</f>
-        <v>カタストロフィ</v>
+        <v>マイトレインフォース</v>
       </c>
       <c r="C190">
-        <v>1010</v>
+        <v>7010</v>
       </c>
       <c r="D190" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C190,Define!P:P))</f>
-        <v>Hpダメージ</v>
+        <v>行動後スキル</v>
       </c>
       <c r="E190">
-        <v>500</v>
+        <v>11</v>
       </c>
       <c r="F190">
         <v>0</v>
@@ -34511,14 +34511,14 @@
         <v>カタストロフィ</v>
       </c>
       <c r="C191">
-        <v>7010</v>
+        <v>1010</v>
       </c>
       <c r="D191" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C191,Define!P:P))</f>
-        <v>行動後スキル</v>
+        <v>Hpダメージ</v>
       </c>
       <c r="E191">
-        <v>21</v>
+        <v>500</v>
       </c>
       <c r="F191">
         <v>0</v>
@@ -34530,45 +34530,41 @@
         <v>100</v>
       </c>
     </row>
-    <row r="192" spans="1:9">
+    <row r="192" spans="1:8">
       <c r="A192">
-        <v>200230</v>
+        <v>200220</v>
       </c>
       <c r="B192" t="str">
         <f>INDEX(TextData!B:B,MATCH(A192,TextData!A:A))</f>
-        <v>悪魔(ベリト)</v>
+        <v>カタストロフィ</v>
       </c>
       <c r="C192">
-        <v>3010</v>
+        <v>7010</v>
       </c>
       <c r="D192" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C192,Define!P:P))</f>
-        <v>ステート付与</v>
+        <v>行動後スキル</v>
       </c>
       <c r="E192">
-        <v>1040</v>
+        <v>21</v>
       </c>
       <c r="F192">
-        <v>999</v>
+        <v>0</v>
       </c>
       <c r="G192">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="H192">
         <v>100</v>
       </c>
-      <c r="I192" t="str">
-        <f>INDEX([4]TextData!B:B,MATCH(E192,[4]TextData!A:A))</f>
-        <v>攻撃アップ</v>
-      </c>
     </row>
     <row r="193" spans="1:9">
       <c r="A193">
-        <v>200310</v>
+        <v>200230</v>
       </c>
       <c r="B193" t="str">
         <f>INDEX(TextData!B:B,MATCH(A193,TextData!A:A))</f>
-        <v>プルガシオン</v>
+        <v>悪魔(ベリト)</v>
       </c>
       <c r="C193">
         <v>3010</v>
@@ -34578,23 +34574,23 @@
         <v>ステート付与</v>
       </c>
       <c r="E193">
-        <v>2040</v>
+        <v>1040</v>
       </c>
       <c r="F193">
-        <v>3</v>
+        <v>999</v>
       </c>
       <c r="G193">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="H193">
         <v>100</v>
       </c>
       <c r="I193" t="str">
         <f>INDEX([4]TextData!B:B,MATCH(E193,[4]TextData!A:A))</f>
-        <v>リジェネ</v>
-      </c>
-    </row>
-    <row r="194" spans="1:8">
+        <v>攻撃アップ</v>
+      </c>
+    </row>
+    <row r="194" spans="1:9">
       <c r="A194">
         <v>200310</v>
       </c>
@@ -34603,58 +34599,58 @@
         <v>プルガシオン</v>
       </c>
       <c r="C194">
-        <v>7010</v>
+        <v>3010</v>
       </c>
       <c r="D194" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C194,Define!P:P))</f>
-        <v>行動後スキル</v>
+        <v>ステート付与</v>
       </c>
       <c r="E194">
-        <v>11</v>
+        <v>2040</v>
       </c>
       <c r="F194">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G194">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="H194">
         <v>100</v>
       </c>
-    </row>
-    <row r="195" spans="1:9">
+      <c r="I194" t="str">
+        <f>INDEX([4]TextData!B:B,MATCH(E194,[4]TextData!A:A))</f>
+        <v>リジェネ</v>
+      </c>
+    </row>
+    <row r="195" spans="1:8">
       <c r="A195">
-        <v>200320</v>
+        <v>200310</v>
       </c>
       <c r="B195" t="str">
         <f>INDEX(TextData!B:B,MATCH(A195,TextData!A:A))</f>
-        <v>プリエステス</v>
+        <v>プルガシオン</v>
       </c>
       <c r="C195">
-        <v>3010</v>
+        <v>7010</v>
       </c>
       <c r="D195" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C195,Define!P:P))</f>
-        <v>ステート付与</v>
+        <v>行動後スキル</v>
       </c>
       <c r="E195">
-        <v>2030</v>
+        <v>11</v>
       </c>
       <c r="F195">
-        <v>999</v>
+        <v>0</v>
       </c>
       <c r="G195">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="H195">
         <v>100</v>
       </c>
-      <c r="I195" t="str">
-        <f>INDEX([4]TextData!B:B,MATCH(E195,[4]TextData!A:A))</f>
-        <v>カウンタ</v>
-      </c>
-    </row>
-    <row r="196" spans="1:8">
+    </row>
+    <row r="196" spans="1:9">
       <c r="A196">
         <v>200320</v>
       </c>
@@ -34663,55 +34659,55 @@
         <v>プリエステス</v>
       </c>
       <c r="C196">
-        <v>7010</v>
+        <v>3010</v>
       </c>
       <c r="D196" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C196,Define!P:P))</f>
-        <v>行動後スキル</v>
+        <v>ステート付与</v>
       </c>
       <c r="E196">
-        <v>21</v>
+        <v>2030</v>
       </c>
       <c r="F196">
-        <v>0</v>
+        <v>999</v>
       </c>
       <c r="G196">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="H196">
         <v>100</v>
       </c>
-    </row>
-    <row r="197" spans="1:9">
+      <c r="I196" t="str">
+        <f>INDEX([4]TextData!B:B,MATCH(E196,[4]TextData!A:A))</f>
+        <v>カウンタ</v>
+      </c>
+    </row>
+    <row r="197" spans="1:8">
       <c r="A197">
-        <v>200330</v>
+        <v>200320</v>
       </c>
       <c r="B197" t="str">
         <f>INDEX(TextData!B:B,MATCH(A197,TextData!A:A))</f>
-        <v>悪魔(パイモン)</v>
+        <v>プリエステス</v>
       </c>
       <c r="C197">
-        <v>3010</v>
+        <v>7010</v>
       </c>
       <c r="D197" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C197,Define!P:P))</f>
-        <v>ステート付与</v>
+        <v>行動後スキル</v>
       </c>
       <c r="E197">
-        <v>2340</v>
+        <v>21</v>
       </c>
       <c r="F197">
-        <v>999</v>
+        <v>0</v>
       </c>
       <c r="G197">
         <v>0</v>
       </c>
       <c r="H197">
         <v>100</v>
-      </c>
-      <c r="I197" t="str">
-        <f>INDEX([4]TextData!B:B,MATCH(E197,[4]TextData!A:A))</f>
-        <v>対象列化</v>
       </c>
     </row>
     <row r="198" spans="1:9">
@@ -34730,7 +34726,7 @@
         <v>ステート付与</v>
       </c>
       <c r="E198">
-        <v>2190</v>
+        <v>2340</v>
       </c>
       <c r="F198">
         <v>999</v>
@@ -34743,35 +34739,39 @@
       </c>
       <c r="I198" t="str">
         <f>INDEX([4]TextData!B:B,MATCH(E198,[4]TextData!A:A))</f>
-        <v>対象範囲延長</v>
-      </c>
-    </row>
-    <row r="199" spans="1:8">
+        <v>対象列化</v>
+      </c>
+    </row>
+    <row r="199" spans="1:9">
       <c r="A199">
-        <v>200410</v>
+        <v>200330</v>
       </c>
       <c r="B199" t="str">
         <f>INDEX(TextData!B:B,MATCH(A199,TextData!A:A))</f>
-        <v>コウソクテンショウ</v>
+        <v>悪魔(パイモン)</v>
       </c>
       <c r="C199">
-        <v>1010</v>
+        <v>3010</v>
       </c>
       <c r="D199" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C199,Define!P:P))</f>
-        <v>Hpダメージ</v>
+        <v>ステート付与</v>
       </c>
       <c r="E199">
-        <v>300</v>
+        <v>2190</v>
       </c>
       <c r="F199">
-        <v>0</v>
+        <v>999</v>
       </c>
       <c r="G199">
         <v>0</v>
       </c>
       <c r="H199">
         <v>100</v>
+      </c>
+      <c r="I199" t="str">
+        <f>INDEX([4]TextData!B:B,MATCH(E199,[4]TextData!A:A))</f>
+        <v>対象範囲延長</v>
       </c>
     </row>
     <row r="200" spans="1:8">
@@ -34783,14 +34783,14 @@
         <v>コウソクテンショウ</v>
       </c>
       <c r="C200">
-        <v>7010</v>
+        <v>1010</v>
       </c>
       <c r="D200" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C200,Define!P:P))</f>
-        <v>行動後スキル</v>
+        <v>Hpダメージ</v>
       </c>
       <c r="E200">
-        <v>200411</v>
+        <v>300</v>
       </c>
       <c r="F200">
         <v>0</v>
@@ -34802,39 +34802,35 @@
         <v>100</v>
       </c>
     </row>
-    <row r="201" spans="1:9">
+    <row r="201" spans="1:8">
       <c r="A201">
-        <v>200411</v>
+        <v>200410</v>
       </c>
       <c r="B201" t="str">
         <f>INDEX(TextData!B:B,MATCH(A201,TextData!A:A))</f>
         <v>コウソクテンショウ</v>
       </c>
       <c r="C201">
-        <v>3010</v>
+        <v>7010</v>
       </c>
       <c r="D201" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C201,Define!P:P))</f>
-        <v>ステート付与</v>
+        <v>行動後スキル</v>
       </c>
       <c r="E201">
-        <v>2060</v>
+        <v>200411</v>
       </c>
       <c r="F201">
-        <v>999</v>
+        <v>0</v>
       </c>
       <c r="G201">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="H201">
         <v>100</v>
       </c>
-      <c r="I201" t="str">
-        <f>INDEX([4]TextData!B:B,MATCH(E201,[4]TextData!A:A))</f>
-        <v>ドレイン</v>
-      </c>
-    </row>
-    <row r="202" spans="1:8">
+    </row>
+    <row r="202" spans="1:9">
       <c r="A202">
         <v>200411</v>
       </c>
@@ -34843,42 +34839,46 @@
         <v>コウソクテンショウ</v>
       </c>
       <c r="C202">
-        <v>7010</v>
+        <v>3010</v>
       </c>
       <c r="D202" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C202,Define!P:P))</f>
-        <v>行動後スキル</v>
+        <v>ステート付与</v>
       </c>
       <c r="E202">
-        <v>11</v>
+        <v>2060</v>
       </c>
       <c r="F202">
-        <v>0</v>
+        <v>999</v>
       </c>
       <c r="G202">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="H202">
         <v>100</v>
       </c>
+      <c r="I202" t="str">
+        <f>INDEX([4]TextData!B:B,MATCH(E202,[4]TextData!A:A))</f>
+        <v>ドレイン</v>
+      </c>
     </row>
     <row r="203" spans="1:8">
       <c r="A203">
-        <v>200420</v>
+        <v>200411</v>
       </c>
       <c r="B203" t="str">
         <f>INDEX(TextData!B:B,MATCH(A203,TextData!A:A))</f>
-        <v>アンチバフ</v>
+        <v>コウソクテンショウ</v>
       </c>
       <c r="C203">
-        <v>3050</v>
+        <v>7010</v>
       </c>
       <c r="D203" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C203,Define!P:P))</f>
-        <v>バフステート解除</v>
+        <v>行動後スキル</v>
       </c>
       <c r="E203">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F203">
         <v>0</v>
@@ -34899,14 +34899,14 @@
         <v>アンチバフ</v>
       </c>
       <c r="C204">
-        <v>7010</v>
+        <v>3050</v>
       </c>
       <c r="D204" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C204,Define!P:P))</f>
-        <v>行動後スキル</v>
+        <v>バフステート解除</v>
       </c>
       <c r="E204">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="F204">
         <v>0</v>
@@ -34920,65 +34920,61 @@
     </row>
     <row r="205" spans="1:8">
       <c r="A205">
-        <v>200430</v>
+        <v>200420</v>
       </c>
       <c r="B205" t="str">
         <f>INDEX(TextData!B:B,MATCH(A205,TextData!A:A))</f>
-        <v>悪魔(アンドラス)</v>
+        <v>アンチバフ</v>
       </c>
       <c r="C205">
-        <v>6100</v>
+        <v>7010</v>
       </c>
       <c r="D205" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C205,Define!P:P))</f>
-        <v>指定魔法の攻撃回数を増やす(強化限定)</v>
+        <v>行動後スキル</v>
       </c>
       <c r="E205">
-        <v>2010</v>
+        <v>21</v>
       </c>
       <c r="F205">
         <v>0</v>
       </c>
       <c r="G205">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H205">
         <v>100</v>
       </c>
     </row>
-    <row r="206" spans="1:9">
+    <row r="206" spans="1:8">
       <c r="A206">
-        <v>200510</v>
+        <v>200430</v>
       </c>
       <c r="B206" t="str">
         <f>INDEX(TextData!B:B,MATCH(A206,TextData!A:A))</f>
-        <v>カウントダウン</v>
+        <v>悪魔(アンドラス)</v>
       </c>
       <c r="C206">
-        <v>3010</v>
+        <v>6100</v>
       </c>
       <c r="D206" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C206,Define!P:P))</f>
-        <v>ステート付与</v>
+        <v>指定魔法の攻撃回数を増やす(強化限定)</v>
       </c>
       <c r="E206">
-        <v>2050</v>
+        <v>2010</v>
       </c>
       <c r="F206">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G206">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H206">
         <v>100</v>
       </c>
-      <c r="I206" t="str">
-        <f>INDEX([4]TextData!B:B,MATCH(E206,[4]TextData!A:A))</f>
-        <v>攻撃無効</v>
-      </c>
-    </row>
-    <row r="207" spans="1:8">
+    </row>
+    <row r="207" spans="1:9">
       <c r="A207">
         <v>200510</v>
       </c>
@@ -34987,17 +34983,17 @@
         <v>カウントダウン</v>
       </c>
       <c r="C207">
-        <v>7010</v>
+        <v>3010</v>
       </c>
       <c r="D207" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C207,Define!P:P))</f>
-        <v>行動後スキル</v>
+        <v>ステート付与</v>
       </c>
       <c r="E207">
-        <v>11</v>
+        <v>2050</v>
       </c>
       <c r="F207">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G207">
         <v>0</v>
@@ -35005,24 +35001,28 @@
       <c r="H207">
         <v>100</v>
       </c>
-    </row>
-    <row r="208" spans="1:9">
+      <c r="I207" t="str">
+        <f>INDEX([4]TextData!B:B,MATCH(E207,[4]TextData!A:A))</f>
+        <v>攻撃無効</v>
+      </c>
+    </row>
+    <row r="208" spans="1:8">
       <c r="A208">
-        <v>200520</v>
+        <v>200510</v>
       </c>
       <c r="B208" t="str">
         <f>INDEX(TextData!B:B,MATCH(A208,TextData!A:A))</f>
-        <v>グラウンドゼロ</v>
+        <v>カウントダウン</v>
       </c>
       <c r="C208">
-        <v>3010</v>
+        <v>7010</v>
       </c>
       <c r="D208" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C208,Define!P:P))</f>
-        <v>ステート付与</v>
+        <v>行動後スキル</v>
       </c>
       <c r="E208">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="F208">
         <v>0</v>
@@ -35033,12 +35033,8 @@
       <c r="H208">
         <v>100</v>
       </c>
-      <c r="I208" t="str">
-        <f>INDEX([4]TextData!B:B,MATCH(E208,[4]TextData!A:A))</f>
-        <v>戦闘不能</v>
-      </c>
-    </row>
-    <row r="209" spans="1:8">
+    </row>
+    <row r="209" spans="1:9">
       <c r="A209">
         <v>200520</v>
       </c>
@@ -35047,14 +35043,14 @@
         <v>グラウンドゼロ</v>
       </c>
       <c r="C209">
-        <v>11010</v>
+        <v>3010</v>
       </c>
       <c r="D209" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C209,Define!P:P))</f>
-        <v>命中判定しない</v>
+        <v>ステート付与</v>
       </c>
       <c r="E209">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F209">
         <v>0</v>
@@ -35064,6 +35060,10 @@
       </c>
       <c r="H209">
         <v>100</v>
+      </c>
+      <c r="I209" t="str">
+        <f>INDEX([4]TextData!B:B,MATCH(E209,[4]TextData!A:A))</f>
+        <v>戦闘不能</v>
       </c>
     </row>
     <row r="210" spans="1:8">
@@ -35075,14 +35075,14 @@
         <v>グラウンドゼロ</v>
       </c>
       <c r="C210">
-        <v>7010</v>
+        <v>11010</v>
       </c>
       <c r="D210" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C210,Define!P:P))</f>
-        <v>行動後スキル</v>
+        <v>命中判定しない</v>
       </c>
       <c r="E210">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="F210">
         <v>0</v>
@@ -35094,45 +35094,41 @@
         <v>100</v>
       </c>
     </row>
-    <row r="211" spans="1:9">
+    <row r="211" spans="1:8">
       <c r="A211">
-        <v>200530</v>
+        <v>200520</v>
       </c>
       <c r="B211" t="str">
         <f>INDEX(TextData!B:B,MATCH(A211,TextData!A:A))</f>
-        <v>悪魔(ビフロンス)</v>
+        <v>グラウンドゼロ</v>
       </c>
       <c r="C211">
-        <v>3010</v>
+        <v>7010</v>
       </c>
       <c r="D211" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C211,Define!P:P))</f>
-        <v>ステート付与</v>
+        <v>行動後スキル</v>
       </c>
       <c r="E211">
-        <v>2410</v>
+        <v>21</v>
       </c>
       <c r="F211">
-        <v>999</v>
+        <v>0</v>
       </c>
       <c r="G211">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="H211">
         <v>100</v>
       </c>
-      <c r="I211" t="str">
-        <f>INDEX([4]TextData!B:B,MATCH(E211,[4]TextData!A:A))</f>
-        <v>シールド</v>
-      </c>
     </row>
     <row r="212" spans="1:9">
       <c r="A212">
-        <v>201010</v>
+        <v>200530</v>
       </c>
       <c r="B212" t="str">
         <f>INDEX(TextData!B:B,MATCH(A212,TextData!A:A))</f>
-        <v>カオスペイン</v>
+        <v>悪魔(ビフロンス)</v>
       </c>
       <c r="C212">
         <v>3010</v>
@@ -35142,10 +35138,10 @@
         <v>ステート付与</v>
       </c>
       <c r="E212">
-        <v>2010</v>
+        <v>2410</v>
       </c>
       <c r="F212">
-        <v>2</v>
+        <v>999</v>
       </c>
       <c r="G212">
         <v>25</v>
@@ -35155,10 +35151,10 @@
       </c>
       <c r="I212" t="str">
         <f>INDEX([4]TextData!B:B,MATCH(E212,[4]TextData!A:A))</f>
-        <v>毒</v>
-      </c>
-    </row>
-    <row r="213" spans="1:8">
+        <v>シールド</v>
+      </c>
+    </row>
+    <row r="213" spans="1:9">
       <c r="A213">
         <v>201010</v>
       </c>
@@ -35167,42 +35163,46 @@
         <v>カオスペイン</v>
       </c>
       <c r="C213">
-        <v>7010</v>
+        <v>3010</v>
       </c>
       <c r="D213" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C213,Define!P:P))</f>
-        <v>行動後スキル</v>
+        <v>ステート付与</v>
       </c>
       <c r="E213">
-        <v>11</v>
+        <v>2010</v>
       </c>
       <c r="F213">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G213">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="H213">
         <v>100</v>
       </c>
+      <c r="I213" t="str">
+        <f>INDEX([4]TextData!B:B,MATCH(E213,[4]TextData!A:A))</f>
+        <v>毒</v>
+      </c>
     </row>
     <row r="214" spans="1:8">
       <c r="A214">
-        <v>201020</v>
+        <v>201010</v>
       </c>
       <c r="B214" t="str">
         <f>INDEX(TextData!B:B,MATCH(A214,TextData!A:A))</f>
-        <v>フォールンワン</v>
+        <v>カオスペイン</v>
       </c>
       <c r="C214">
-        <v>2030</v>
+        <v>7010</v>
       </c>
       <c r="D214" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C214,Define!P:P))</f>
-        <v>対象のHpを1にする</v>
+        <v>行動後スキル</v>
       </c>
       <c r="E214">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F214">
         <v>0</v>
@@ -35223,11 +35223,11 @@
         <v>フォールンワン</v>
       </c>
       <c r="C215">
-        <v>11010</v>
+        <v>2030</v>
       </c>
       <c r="D215" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C215,Define!P:P))</f>
-        <v>命中判定しない</v>
+        <v>対象のHpを1にする</v>
       </c>
       <c r="E215">
         <v>0</v>
@@ -35251,14 +35251,14 @@
         <v>フォールンワン</v>
       </c>
       <c r="C216">
-        <v>7010</v>
+        <v>11010</v>
       </c>
       <c r="D216" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C216,Define!P:P))</f>
-        <v>行動後スキル</v>
+        <v>命中判定しない</v>
       </c>
       <c r="E216">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="F216">
         <v>0</v>
@@ -35270,26 +35270,26 @@
         <v>100</v>
       </c>
     </row>
-    <row r="217" spans="1:9">
+    <row r="217" spans="1:8">
       <c r="A217">
-        <v>201030</v>
+        <v>201020</v>
       </c>
       <c r="B217" t="str">
         <f>INDEX(TextData!B:B,MATCH(A217,TextData!A:A))</f>
-        <v>アンリマユ</v>
+        <v>フォールンワン</v>
       </c>
       <c r="C217">
-        <v>3010</v>
+        <v>7010</v>
       </c>
       <c r="D217" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C217,Define!P:P))</f>
-        <v>ステート付与</v>
+        <v>行動後スキル</v>
       </c>
       <c r="E217">
-        <v>2050</v>
+        <v>21</v>
       </c>
       <c r="F217">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G217">
         <v>0</v>
@@ -35297,18 +35297,14 @@
       <c r="H217">
         <v>100</v>
       </c>
-      <c r="I217" t="str">
-        <f>INDEX([4]TextData!B:B,MATCH(E217,[4]TextData!A:A))</f>
-        <v>攻撃無効</v>
-      </c>
     </row>
     <row r="218" spans="1:9">
       <c r="A218">
-        <v>300010</v>
+        <v>201030</v>
       </c>
       <c r="B218" t="str">
         <f>INDEX(TextData!B:B,MATCH(A218,TextData!A:A))</f>
-        <v>ライフブースト</v>
+        <v>アンリマユ</v>
       </c>
       <c r="C218">
         <v>3010</v>
@@ -35318,89 +35314,89 @@
         <v>ステート付与</v>
       </c>
       <c r="E218">
-        <v>1020</v>
+        <v>2050</v>
       </c>
       <c r="F218">
-        <v>999</v>
+        <v>2</v>
       </c>
       <c r="G218">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H218">
         <v>100</v>
       </c>
       <c r="I218" t="str">
         <f>INDEX([4]TextData!B:B,MATCH(E218,[4]TextData!A:A))</f>
-        <v>最大Hpアップ</v>
-      </c>
-    </row>
-    <row r="219" spans="1:8">
+        <v>攻撃無効</v>
+      </c>
+    </row>
+    <row r="219" spans="1:9">
       <c r="A219">
-        <v>300020</v>
+        <v>300010</v>
       </c>
       <c r="B219" t="str">
         <f>INDEX(TextData!B:B,MATCH(A219,TextData!A:A))</f>
-        <v>スピリットチャージ</v>
+        <v>ライフブースト</v>
       </c>
       <c r="C219">
-        <v>4040</v>
+        <v>3010</v>
       </c>
       <c r="D219" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C219,Define!P:P))</f>
-        <v>指定魔法のCｔ回復</v>
+        <v>ステート付与</v>
       </c>
       <c r="E219">
-        <v>1</v>
+        <v>1020</v>
       </c>
       <c r="F219">
-        <v>0</v>
+        <v>999</v>
       </c>
       <c r="G219">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H219">
         <v>100</v>
       </c>
-    </row>
-    <row r="220" spans="1:9">
+      <c r="I219" t="str">
+        <f>INDEX([4]TextData!B:B,MATCH(E219,[4]TextData!A:A))</f>
+        <v>最大Hpアップ</v>
+      </c>
+    </row>
+    <row r="220" spans="1:8">
       <c r="A220">
-        <v>300030</v>
+        <v>300020</v>
       </c>
       <c r="B220" t="str">
         <f>INDEX(TextData!B:B,MATCH(A220,TextData!A:A))</f>
-        <v>フォースライズ</v>
+        <v>スピリットチャージ</v>
       </c>
       <c r="C220">
-        <v>3010</v>
+        <v>4040</v>
       </c>
       <c r="D220" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C220,Define!P:P))</f>
-        <v>ステート付与</v>
+        <v>指定魔法のCｔ回復</v>
       </c>
       <c r="E220">
-        <v>1040</v>
+        <v>1</v>
       </c>
       <c r="F220">
-        <v>999</v>
+        <v>0</v>
       </c>
       <c r="G220">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H220">
         <v>100</v>
       </c>
-      <c r="I220" t="str">
-        <f>INDEX([4]TextData!B:B,MATCH(E220,[4]TextData!A:A))</f>
-        <v>攻撃アップ</v>
-      </c>
     </row>
     <row r="221" spans="1:9">
       <c r="A221">
-        <v>300040</v>
+        <v>300030</v>
       </c>
       <c r="B221" t="str">
         <f>INDEX(TextData!B:B,MATCH(A221,TextData!A:A))</f>
-        <v>ディフェンスオーラ</v>
+        <v>フォースライズ</v>
       </c>
       <c r="C221">
         <v>3010</v>
@@ -35410,7 +35406,7 @@
         <v>ステート付与</v>
       </c>
       <c r="E221">
-        <v>1050</v>
+        <v>1040</v>
       </c>
       <c r="F221">
         <v>999</v>
@@ -35423,16 +35419,16 @@
       </c>
       <c r="I221" t="str">
         <f>INDEX([4]TextData!B:B,MATCH(E221,[4]TextData!A:A))</f>
-        <v>防御アップ</v>
+        <v>攻撃アップ</v>
       </c>
     </row>
     <row r="222" spans="1:9">
       <c r="A222">
-        <v>300050</v>
+        <v>300040</v>
       </c>
       <c r="B222" t="str">
         <f>INDEX(TextData!B:B,MATCH(A222,TextData!A:A))</f>
-        <v>ラピッドムーブ</v>
+        <v>ディフェンスオーラ</v>
       </c>
       <c r="C222">
         <v>3010</v>
@@ -35442,29 +35438,29 @@
         <v>ステート付与</v>
       </c>
       <c r="E222">
-        <v>1060</v>
+        <v>1050</v>
       </c>
       <c r="F222">
         <v>999</v>
       </c>
       <c r="G222">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H222">
         <v>100</v>
       </c>
       <c r="I222" t="str">
         <f>INDEX([4]TextData!B:B,MATCH(E222,[4]TextData!A:A))</f>
-        <v>速度アップ</v>
+        <v>防御アップ</v>
       </c>
     </row>
     <row r="223" spans="1:9">
       <c r="A223">
-        <v>300130</v>
+        <v>300050</v>
       </c>
       <c r="B223" t="str">
         <f>INDEX(TextData!B:B,MATCH(A223,TextData!A:A))</f>
-        <v>アタックブレイク</v>
+        <v>ラピッドムーブ</v>
       </c>
       <c r="C223">
         <v>3010</v>
@@ -35474,29 +35470,29 @@
         <v>ステート付与</v>
       </c>
       <c r="E223">
-        <v>1041</v>
+        <v>1060</v>
       </c>
       <c r="F223">
         <v>999</v>
       </c>
       <c r="G223">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H223">
         <v>100</v>
       </c>
       <c r="I223" t="str">
         <f>INDEX([4]TextData!B:B,MATCH(E223,[4]TextData!A:A))</f>
-        <v>攻撃ダウン</v>
+        <v>速度アップ</v>
       </c>
     </row>
     <row r="224" spans="1:9">
       <c r="A224">
-        <v>300140</v>
+        <v>300130</v>
       </c>
       <c r="B224" t="str">
         <f>INDEX(TextData!B:B,MATCH(A224,TextData!A:A))</f>
-        <v>シールドバニッシュ</v>
+        <v>アタックブレイク</v>
       </c>
       <c r="C224">
         <v>3010</v>
@@ -35506,7 +35502,7 @@
         <v>ステート付与</v>
       </c>
       <c r="E224">
-        <v>1051</v>
+        <v>1041</v>
       </c>
       <c r="F224">
         <v>999</v>
@@ -35519,76 +35515,76 @@
       </c>
       <c r="I224" t="str">
         <f>INDEX([4]TextData!B:B,MATCH(E224,[4]TextData!A:A))</f>
-        <v>防御ダウン</v>
-      </c>
-    </row>
-    <row r="225" spans="1:8">
+        <v>攻撃ダウン</v>
+      </c>
+    </row>
+    <row r="225" spans="1:9">
       <c r="A225">
-        <v>300210</v>
+        <v>300140</v>
       </c>
       <c r="B225" t="str">
         <f>INDEX(TextData!B:B,MATCH(A225,TextData!A:A))</f>
-        <v>エーテルリチャージ</v>
+        <v>シールドバニッシュ</v>
       </c>
       <c r="C225">
-        <v>4020</v>
+        <v>3010</v>
       </c>
       <c r="D225" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C225,Define!P:P))</f>
-        <v>Ct回復</v>
+        <v>ステート付与</v>
       </c>
       <c r="E225">
-        <v>1</v>
+        <v>1051</v>
       </c>
       <c r="F225">
-        <v>0</v>
+        <v>999</v>
       </c>
       <c r="G225">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H225">
         <v>100</v>
       </c>
-    </row>
-    <row r="226" spans="1:9">
+      <c r="I225" t="str">
+        <f>INDEX([4]TextData!B:B,MATCH(E225,[4]TextData!A:A))</f>
+        <v>防御ダウン</v>
+      </c>
+    </row>
+    <row r="226" spans="1:8">
       <c r="A226">
-        <v>300220</v>
+        <v>300210</v>
       </c>
       <c r="B226" t="str">
         <f>INDEX(TextData!B:B,MATCH(A226,TextData!A:A))</f>
-        <v>リカバリーエンハンス</v>
+        <v>エーテルリチャージ</v>
       </c>
       <c r="C226">
-        <v>3010</v>
+        <v>4020</v>
       </c>
       <c r="D226" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C226,Define!P:P))</f>
-        <v>ステート付与</v>
+        <v>Ct回復</v>
       </c>
       <c r="E226">
-        <v>2460</v>
+        <v>1</v>
       </c>
       <c r="F226">
-        <v>999</v>
+        <v>0</v>
       </c>
       <c r="G226">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H226">
         <v>100</v>
       </c>
-      <c r="I226" t="str">
-        <f>INDEX([4]TextData!B:B,MATCH(E226,[4]TextData!A:A))</f>
-        <v>Hp回復効果アップ</v>
-      </c>
     </row>
     <row r="227" spans="1:9">
       <c r="A227">
-        <v>300230</v>
+        <v>300220</v>
       </c>
       <c r="B227" t="str">
         <f>INDEX(TextData!B:B,MATCH(A227,TextData!A:A))</f>
-        <v>ヴェンジェンス</v>
+        <v>リカバリーエンハンス</v>
       </c>
       <c r="C227">
         <v>3010</v>
@@ -35598,89 +35594,89 @@
         <v>ステート付与</v>
       </c>
       <c r="E227">
-        <v>2030</v>
+        <v>2460</v>
       </c>
       <c r="F227">
         <v>999</v>
       </c>
       <c r="G227">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="H227">
         <v>100</v>
       </c>
       <c r="I227" t="str">
         <f>INDEX([4]TextData!B:B,MATCH(E227,[4]TextData!A:A))</f>
-        <v>カウンタ</v>
-      </c>
-    </row>
-    <row r="228" spans="1:8">
+        <v>Hp回復効果アップ</v>
+      </c>
+    </row>
+    <row r="228" spans="1:9">
       <c r="A228">
-        <v>301010</v>
+        <v>300230</v>
       </c>
       <c r="B228" t="str">
         <f>INDEX(TextData!B:B,MATCH(A228,TextData!A:A))</f>
-        <v>ディケイドリセット</v>
+        <v>ヴェンジェンス</v>
       </c>
       <c r="C228">
-        <v>5012</v>
+        <v>3010</v>
       </c>
       <c r="D228" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C228,Define!P:P))</f>
-        <v>ActionResult扱いでAP指定</v>
+        <v>ステート付与</v>
       </c>
       <c r="E228">
-        <v>0</v>
+        <v>2030</v>
       </c>
       <c r="F228">
-        <v>0</v>
+        <v>999</v>
       </c>
       <c r="G228">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="H228">
         <v>100</v>
       </c>
-    </row>
-    <row r="229" spans="1:9">
+      <c r="I228" t="str">
+        <f>INDEX([4]TextData!B:B,MATCH(E228,[4]TextData!A:A))</f>
+        <v>カウンタ</v>
+      </c>
+    </row>
+    <row r="229" spans="1:8">
       <c r="A229">
-        <v>301020</v>
+        <v>301010</v>
       </c>
       <c r="B229" t="str">
         <f>INDEX(TextData!B:B,MATCH(A229,TextData!A:A))</f>
-        <v>ウォーリアーブラッド</v>
+        <v>ディケイドリセット</v>
       </c>
       <c r="C229">
-        <v>3010</v>
+        <v>5012</v>
       </c>
       <c r="D229" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C229,Define!P:P))</f>
-        <v>ステート付与</v>
+        <v>ActionResult扱いでAP指定</v>
       </c>
       <c r="E229">
-        <v>1040</v>
+        <v>0</v>
       </c>
       <c r="F229">
-        <v>999</v>
+        <v>0</v>
       </c>
       <c r="G229">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H229">
         <v>100</v>
       </c>
-      <c r="I229" t="str">
-        <f>INDEX([4]TextData!B:B,MATCH(E229,[4]TextData!A:A))</f>
-        <v>攻撃アップ</v>
-      </c>
     </row>
     <row r="230" spans="1:9">
       <c r="A230">
-        <v>301030</v>
+        <v>301020</v>
       </c>
       <c r="B230" t="str">
         <f>INDEX(TextData!B:B,MATCH(A230,TextData!A:A))</f>
-        <v>トライアングルガード</v>
+        <v>ウォーリアーブラッド</v>
       </c>
       <c r="C230">
         <v>3010</v>
@@ -35690,29 +35686,29 @@
         <v>ステート付与</v>
       </c>
       <c r="E230">
-        <v>1100</v>
+        <v>1040</v>
       </c>
       <c r="F230">
-        <v>1</v>
+        <v>999</v>
       </c>
       <c r="G230">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="H230">
         <v>100</v>
       </c>
       <c r="I230" t="str">
         <f>INDEX([4]TextData!B:B,MATCH(E230,[4]TextData!A:A))</f>
-        <v>ダメージカット</v>
+        <v>攻撃アップ</v>
       </c>
     </row>
     <row r="231" spans="1:9">
       <c r="A231">
-        <v>301040</v>
+        <v>301030</v>
       </c>
       <c r="B231" t="str">
         <f>INDEX(TextData!B:B,MATCH(A231,TextData!A:A))</f>
-        <v>セーフティバリア</v>
+        <v>トライアングルガード</v>
       </c>
       <c r="C231">
         <v>3010</v>
@@ -35722,29 +35718,29 @@
         <v>ステート付与</v>
       </c>
       <c r="E231">
-        <v>2050</v>
+        <v>1100</v>
       </c>
       <c r="F231">
         <v>1</v>
       </c>
       <c r="G231">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="H231">
         <v>100</v>
       </c>
       <c r="I231" t="str">
         <f>INDEX([4]TextData!B:B,MATCH(E231,[4]TextData!A:A))</f>
-        <v>攻撃無効</v>
+        <v>ダメージカット</v>
       </c>
     </row>
     <row r="232" spans="1:9">
       <c r="A232">
-        <v>301050</v>
+        <v>301040</v>
       </c>
       <c r="B232" t="str">
         <f>INDEX(TextData!B:B,MATCH(A232,TextData!A:A))</f>
-        <v>ヒロインズハイ</v>
+        <v>セーフティバリア</v>
       </c>
       <c r="C232">
         <v>3010</v>
@@ -35754,55 +35750,55 @@
         <v>ステート付与</v>
       </c>
       <c r="E232">
-        <v>1020</v>
+        <v>2050</v>
       </c>
       <c r="F232">
-        <v>999</v>
+        <v>1</v>
       </c>
       <c r="G232">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="H232">
         <v>100</v>
       </c>
       <c r="I232" t="str">
         <f>INDEX([4]TextData!B:B,MATCH(E232,[4]TextData!A:A))</f>
-        <v>最大Hpアップ</v>
+        <v>攻撃無効</v>
       </c>
     </row>
     <row r="233" spans="1:9">
       <c r="A233">
-        <v>301060</v>
+        <v>301050</v>
       </c>
       <c r="B233" t="str">
         <f>INDEX(TextData!B:B,MATCH(A233,TextData!A:A))</f>
-        <v>セカンドステージ</v>
+        <v>ヒロインズハイ</v>
       </c>
       <c r="C233">
-        <v>3020</v>
+        <v>3010</v>
       </c>
       <c r="D233" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C233,Define!P:P))</f>
-        <v>ステート解除</v>
+        <v>ステート付与</v>
       </c>
       <c r="E233">
-        <v>1</v>
+        <v>1020</v>
       </c>
       <c r="F233">
-        <v>0</v>
+        <v>999</v>
       </c>
       <c r="G233">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="H233">
         <v>100</v>
       </c>
       <c r="I233" t="str">
         <f>INDEX([4]TextData!B:B,MATCH(E233,[4]TextData!A:A))</f>
-        <v>戦闘不能</v>
-      </c>
-    </row>
-    <row r="234" spans="1:8">
+        <v>最大Hpアップ</v>
+      </c>
+    </row>
+    <row r="234" spans="1:9">
       <c r="A234">
         <v>301060</v>
       </c>
@@ -35811,14 +35807,14 @@
         <v>セカンドステージ</v>
       </c>
       <c r="C234">
-        <v>2030</v>
+        <v>3020</v>
       </c>
       <c r="D234" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C234,Define!P:P))</f>
-        <v>対象のHpを1にする</v>
+        <v>ステート解除</v>
       </c>
       <c r="E234">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F234">
         <v>0</v>
@@ -35828,6 +35824,10 @@
       </c>
       <c r="H234">
         <v>100</v>
+      </c>
+      <c r="I234" t="str">
+        <f>INDEX([4]TextData!B:B,MATCH(E234,[4]TextData!A:A))</f>
+        <v>戦闘不能</v>
       </c>
     </row>
     <row r="235" spans="1:8">
@@ -35839,14 +35839,14 @@
         <v>セカンドステージ</v>
       </c>
       <c r="C235">
-        <v>2010</v>
+        <v>2030</v>
       </c>
       <c r="D235" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C235,Define!P:P))</f>
-        <v>Hp回復</v>
+        <v>対象のHpを1にする</v>
       </c>
       <c r="E235">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F235">
         <v>0</v>
@@ -35858,143 +35858,143 @@
         <v>100</v>
       </c>
     </row>
-    <row r="236" spans="1:9">
+    <row r="236" spans="1:8">
       <c r="A236">
-        <v>301070</v>
+        <v>301060</v>
       </c>
       <c r="B236" t="str">
         <f>INDEX(TextData!B:B,MATCH(A236,TextData!A:A))</f>
-        <v>ハイヒットポイント</v>
+        <v>セカンドステージ</v>
       </c>
       <c r="C236">
-        <v>3010</v>
+        <v>2010</v>
       </c>
       <c r="D236" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C236,Define!P:P))</f>
-        <v>ステート付与</v>
+        <v>Hp回復</v>
       </c>
       <c r="E236">
-        <v>1020</v>
+        <v>20</v>
       </c>
       <c r="F236">
-        <v>999</v>
+        <v>0</v>
       </c>
       <c r="G236">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H236">
         <v>100</v>
       </c>
-      <c r="I236" t="str">
-        <f>INDEX([4]TextData!B:B,MATCH(E236,[4]TextData!A:A))</f>
-        <v>最大Hpアップ</v>
-      </c>
-    </row>
-    <row r="237" spans="1:8">
+    </row>
+    <row r="237" spans="1:9">
       <c r="A237">
-        <v>301080</v>
+        <v>301070</v>
       </c>
       <c r="B237" t="str">
         <f>INDEX(TextData!B:B,MATCH(A237,TextData!A:A))</f>
-        <v>セプタブラスト</v>
+        <v>ハイヒットポイント</v>
       </c>
       <c r="C237">
-        <v>1030</v>
+        <v>3010</v>
       </c>
       <c r="D237" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C237,Define!P:P))</f>
-        <v>Hp固定ダメージ</v>
+        <v>ステート付与</v>
       </c>
       <c r="E237">
-        <v>50</v>
+        <v>1020</v>
       </c>
       <c r="F237">
-        <v>0</v>
+        <v>999</v>
       </c>
       <c r="G237">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H237">
         <v>100</v>
       </c>
-    </row>
-    <row r="238" spans="1:9">
+      <c r="I237" t="str">
+        <f>INDEX([4]TextData!B:B,MATCH(E237,[4]TextData!A:A))</f>
+        <v>最大Hpアップ</v>
+      </c>
+    </row>
+    <row r="238" spans="1:8">
       <c r="A238">
-        <v>301090</v>
+        <v>301080</v>
       </c>
       <c r="B238" t="str">
         <f>INDEX(TextData!B:B,MATCH(A238,TextData!A:A))</f>
-        <v>イニシャルブロッカー</v>
+        <v>セプタブラスト</v>
       </c>
       <c r="C238">
-        <v>3010</v>
+        <v>1030</v>
       </c>
       <c r="D238" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C238,Define!P:P))</f>
-        <v>ステート付与</v>
+        <v>Hp固定ダメージ</v>
       </c>
       <c r="E238">
-        <v>2410</v>
+        <v>50</v>
       </c>
       <c r="F238">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G238">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="H238">
         <v>100</v>
       </c>
-      <c r="I238" t="str">
-        <f>INDEX([4]TextData!B:B,MATCH(E238,[4]TextData!A:A))</f>
-        <v>シールド</v>
-      </c>
-    </row>
-    <row r="239" spans="1:8">
+    </row>
+    <row r="239" spans="1:9">
       <c r="A239">
-        <v>301100</v>
+        <v>301090</v>
       </c>
       <c r="B239" t="str">
         <f>INDEX(TextData!B:B,MATCH(A239,TextData!A:A))</f>
-        <v>ファーストテイク</v>
+        <v>イニシャルブロッカー</v>
       </c>
       <c r="C239">
-        <v>5020</v>
+        <v>3010</v>
       </c>
       <c r="D239" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C239,Define!P:P))</f>
-        <v>Ap回復</v>
+        <v>ステート付与</v>
       </c>
       <c r="E239">
-        <v>200</v>
+        <v>2410</v>
       </c>
       <c r="F239">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G239">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="H239">
         <v>100</v>
       </c>
+      <c r="I239" t="str">
+        <f>INDEX([4]TextData!B:B,MATCH(E239,[4]TextData!A:A))</f>
+        <v>シールド</v>
+      </c>
     </row>
     <row r="240" spans="1:8">
       <c r="A240">
-        <v>310010</v>
+        <v>301100</v>
       </c>
       <c r="B240" t="str">
         <f>INDEX(TextData!B:B,MATCH(A240,TextData!A:A))</f>
-        <v>妖精の祈り</v>
+        <v>ファーストテイク</v>
       </c>
       <c r="C240">
-        <v>2010</v>
+        <v>5020</v>
       </c>
       <c r="D240" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C240,Define!P:P))</f>
-        <v>Hp回復</v>
+        <v>Ap回復</v>
       </c>
       <c r="E240">
-        <v>3</v>
+        <v>200</v>
       </c>
       <c r="F240">
         <v>0</v>
@@ -36008,24 +36008,24 @@
     </row>
     <row r="241" spans="1:8">
       <c r="A241">
-        <v>310020</v>
+        <v>310010</v>
       </c>
       <c r="B241" t="str">
         <f>INDEX(TextData!B:B,MATCH(A241,TextData!A:A))</f>
-        <v>月のかけら</v>
+        <v>妖精の祈り</v>
       </c>
       <c r="C241">
-        <v>40010</v>
+        <v>2010</v>
       </c>
       <c r="D241" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C241,Define!P:P))</f>
-        <v>アイテム入手</v>
+        <v>Hp回復</v>
       </c>
       <c r="E241">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="F241">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="G241">
         <v>0</v>
@@ -36036,24 +36036,24 @@
     </row>
     <row r="242" spans="1:8">
       <c r="A242">
-        <v>310030</v>
+        <v>310020</v>
       </c>
       <c r="B242" t="str">
         <f>INDEX(TextData!B:B,MATCH(A242,TextData!A:A))</f>
-        <v>商売の才覚書</v>
+        <v>月のかけら</v>
       </c>
       <c r="C242">
-        <v>40070</v>
+        <v>40010</v>
       </c>
       <c r="D242" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C242,Define!P:P))</f>
-        <v>取引レートダウン</v>
+        <v>アイテム入手</v>
       </c>
       <c r="E242">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F242">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G242">
         <v>0</v>
@@ -36064,84 +36064,80 @@
     </row>
     <row r="243" spans="1:8">
       <c r="A243">
-        <v>310040</v>
+        <v>310030</v>
       </c>
       <c r="B243" t="str">
         <f>INDEX(TextData!B:B,MATCH(A243,TextData!A:A))</f>
-        <v>レイヴンバナー</v>
+        <v>商売の才覚書</v>
       </c>
       <c r="C243">
-        <v>6310</v>
+        <v>40070</v>
       </c>
       <c r="D243" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C243,Define!P:P))</f>
-        <v>指定魔法に行動後スキルを追加する</v>
+        <v>取引レートダウン</v>
       </c>
       <c r="E243">
-        <v>20010</v>
+        <v>20</v>
       </c>
       <c r="F243">
         <v>0</v>
       </c>
       <c r="G243">
-        <v>310041</v>
+        <v>0</v>
       </c>
       <c r="H243">
         <v>100</v>
       </c>
     </row>
-    <row r="244" spans="1:9">
+    <row r="244" spans="1:8">
       <c r="A244">
-        <v>310041</v>
+        <v>310040</v>
       </c>
       <c r="B244" t="str">
         <f>INDEX(TextData!B:B,MATCH(A244,TextData!A:A))</f>
         <v>レイヴンバナー</v>
       </c>
       <c r="C244">
-        <v>3010</v>
+        <v>6310</v>
       </c>
       <c r="D244" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C244,Define!P:P))</f>
-        <v>ステート付与</v>
+        <v>指定魔法に行動後スキルを追加する</v>
       </c>
       <c r="E244">
-        <v>100</v>
+        <v>20010</v>
       </c>
       <c r="F244">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G244">
-        <v>0</v>
+        <v>310041</v>
       </c>
       <c r="H244">
         <v>100</v>
       </c>
-      <c r="I244" t="str">
-        <f>INDEX([4]TextData!B:B,MATCH(E244,[4]TextData!A:A))</f>
-        <v>待機</v>
-      </c>
-    </row>
-    <row r="245" spans="1:8">
+    </row>
+    <row r="245" spans="1:9">
       <c r="A245">
-        <v>310050</v>
+        <v>310041</v>
       </c>
       <c r="B245" t="str">
         <f>INDEX(TextData!B:B,MATCH(A245,TextData!A:A))</f>
-        <v>先陣の心得</v>
+        <v>レイヴンバナー</v>
       </c>
       <c r="C245">
-        <v>5020</v>
+        <v>3010</v>
       </c>
       <c r="D245" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C245,Define!P:P))</f>
-        <v>Ap回復</v>
+        <v>ステート付与</v>
       </c>
       <c r="E245">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="F245">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G245">
         <v>0</v>
@@ -36149,24 +36145,28 @@
       <c r="H245">
         <v>100</v>
       </c>
+      <c r="I245" t="str">
+        <f>INDEX([4]TextData!B:B,MATCH(E245,[4]TextData!A:A))</f>
+        <v>待機</v>
+      </c>
     </row>
     <row r="246" spans="1:8">
       <c r="A246">
-        <v>310130</v>
+        <v>310050</v>
       </c>
       <c r="B246" t="str">
         <f>INDEX(TextData!B:B,MATCH(A246,TextData!A:A))</f>
-        <v>ヒールユニット</v>
+        <v>先陣の心得</v>
       </c>
       <c r="C246">
-        <v>2010</v>
+        <v>5020</v>
       </c>
       <c r="D246" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C246,Define!P:P))</f>
-        <v>Hp回復</v>
+        <v>Ap回復</v>
       </c>
       <c r="E246">
-        <v>1</v>
+        <v>1000</v>
       </c>
       <c r="F246">
         <v>0</v>
@@ -36180,21 +36180,21 @@
     </row>
     <row r="247" spans="1:8">
       <c r="A247">
-        <v>320010</v>
+        <v>310130</v>
       </c>
       <c r="B247" t="str">
         <f>INDEX(TextData!B:B,MATCH(A247,TextData!A:A))</f>
-        <v>訓練所Lv1</v>
+        <v>ヒールユニット</v>
       </c>
       <c r="C247">
-        <v>40030</v>
+        <v>2010</v>
       </c>
       <c r="D247" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C247,Define!P:P))</f>
-        <v>Eｘｐ入手</v>
+        <v>Hp回復</v>
       </c>
       <c r="E247">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="F247">
         <v>0</v>
@@ -36208,11 +36208,11 @@
     </row>
     <row r="248" spans="1:8">
       <c r="A248">
-        <v>320011</v>
+        <v>320010</v>
       </c>
       <c r="B248" t="str">
         <f>INDEX(TextData!B:B,MATCH(A248,TextData!A:A))</f>
-        <v>訓練所Lv2</v>
+        <v>訓練所Lv1</v>
       </c>
       <c r="C248">
         <v>40030</v>
@@ -36222,7 +36222,7 @@
         <v>Eｘｐ入手</v>
       </c>
       <c r="E248">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="F248">
         <v>0</v>
@@ -36236,11 +36236,11 @@
     </row>
     <row r="249" spans="1:8">
       <c r="A249">
-        <v>320012</v>
+        <v>320011</v>
       </c>
       <c r="B249" t="str">
         <f>INDEX(TextData!B:B,MATCH(A249,TextData!A:A))</f>
-        <v>訓練所Lv3</v>
+        <v>訓練所Lv2</v>
       </c>
       <c r="C249">
         <v>40030</v>
@@ -36250,7 +36250,7 @@
         <v>Eｘｐ入手</v>
       </c>
       <c r="E249">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="F249">
         <v>0</v>
@@ -36264,21 +36264,21 @@
     </row>
     <row r="250" spans="1:8">
       <c r="A250">
-        <v>320020</v>
+        <v>320012</v>
       </c>
       <c r="B250" t="str">
         <f>INDEX(TextData!B:B,MATCH(A250,TextData!A:A))</f>
-        <v>研究施設Lv1</v>
+        <v>訓練所Lv3</v>
       </c>
       <c r="C250">
-        <v>40040</v>
+        <v>40030</v>
       </c>
       <c r="D250" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C250,Define!P:P))</f>
-        <v>Nu入手</v>
+        <v>Eｘｐ入手</v>
       </c>
       <c r="E250">
-        <v>2</v>
+        <v>75</v>
       </c>
       <c r="F250">
         <v>0</v>
@@ -36292,11 +36292,11 @@
     </row>
     <row r="251" spans="1:8">
       <c r="A251">
-        <v>320021</v>
+        <v>320020</v>
       </c>
       <c r="B251" t="str">
         <f>INDEX(TextData!B:B,MATCH(A251,TextData!A:A))</f>
-        <v>研究施設Lv2</v>
+        <v>研究施設Lv1</v>
       </c>
       <c r="C251">
         <v>40040</v>
@@ -36306,7 +36306,7 @@
         <v>Nu入手</v>
       </c>
       <c r="E251">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F251">
         <v>0</v>
@@ -36320,11 +36320,11 @@
     </row>
     <row r="252" spans="1:8">
       <c r="A252">
-        <v>320022</v>
+        <v>320021</v>
       </c>
       <c r="B252" t="str">
         <f>INDEX(TextData!B:B,MATCH(A252,TextData!A:A))</f>
-        <v>研究施設Lv3</v>
+        <v>研究施設Lv2</v>
       </c>
       <c r="C252">
         <v>40040</v>
@@ -36334,7 +36334,7 @@
         <v>Nu入手</v>
       </c>
       <c r="E252">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F252">
         <v>0</v>
@@ -36348,24 +36348,24 @@
     </row>
     <row r="253" spans="1:8">
       <c r="A253">
-        <v>320030</v>
+        <v>320022</v>
       </c>
       <c r="B253" t="str">
         <f>INDEX(TextData!B:B,MATCH(A253,TextData!A:A))</f>
-        <v>資料館Lv1</v>
+        <v>研究施設Lv3</v>
       </c>
       <c r="C253">
-        <v>40020</v>
+        <v>40040</v>
       </c>
       <c r="D253" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C253,Define!P:P))</f>
-        <v>獲得Eｘｐ％アップ</v>
+        <v>Nu入手</v>
       </c>
       <c r="E253">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F253">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G253">
         <v>0</v>
@@ -36376,11 +36376,11 @@
     </row>
     <row r="254" spans="1:8">
       <c r="A254">
-        <v>320031</v>
+        <v>320030</v>
       </c>
       <c r="B254" t="str">
         <f>INDEX(TextData!B:B,MATCH(A254,TextData!A:A))</f>
-        <v>資料館Lv2</v>
+        <v>資料館Lv1</v>
       </c>
       <c r="C254">
         <v>40020</v>
@@ -36404,11 +36404,11 @@
     </row>
     <row r="255" spans="1:8">
       <c r="A255">
-        <v>320032</v>
+        <v>320031</v>
       </c>
       <c r="B255" t="str">
         <f>INDEX(TextData!B:B,MATCH(A255,TextData!A:A))</f>
-        <v>資料館Lv3</v>
+        <v>資料館Lv2</v>
       </c>
       <c r="C255">
         <v>40020</v>
@@ -36432,24 +36432,24 @@
     </row>
     <row r="256" spans="1:8">
       <c r="A256">
-        <v>320040</v>
+        <v>320032</v>
       </c>
       <c r="B256" t="str">
         <f>INDEX(TextData!B:B,MATCH(A256,TextData!A:A))</f>
-        <v>潜伏技術Lv1</v>
+        <v>資料館Lv3</v>
       </c>
       <c r="C256">
-        <v>40060</v>
+        <v>40020</v>
       </c>
       <c r="D256" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C256,Define!P:P))</f>
-        <v>ステージ探索猶予アップ</v>
+        <v>獲得Eｘｐ％アップ</v>
       </c>
       <c r="E256">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F256">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="G256">
         <v>0</v>
@@ -36460,24 +36460,24 @@
     </row>
     <row r="257" spans="1:8">
       <c r="A257">
-        <v>321010</v>
+        <v>320040</v>
       </c>
       <c r="B257" t="str">
         <f>INDEX(TextData!B:B,MATCH(A257,TextData!A:A))</f>
-        <v>炎の祭壇</v>
+        <v>潜伏技術Lv1</v>
       </c>
       <c r="C257">
-        <v>40050</v>
+        <v>40060</v>
       </c>
       <c r="D257" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C257,Define!P:P))</f>
-        <v>属性適正アップ</v>
+        <v>ステージ探索猶予アップ</v>
       </c>
       <c r="E257">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F257">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G257">
         <v>0</v>
@@ -36488,11 +36488,11 @@
     </row>
     <row r="258" spans="1:8">
       <c r="A258">
-        <v>321020</v>
+        <v>321010</v>
       </c>
       <c r="B258" t="str">
         <f>INDEX(TextData!B:B,MATCH(A258,TextData!A:A))</f>
-        <v>稲妻の祭壇</v>
+        <v>炎の祭壇</v>
       </c>
       <c r="C258">
         <v>40050</v>
@@ -36502,7 +36502,7 @@
         <v>属性適正アップ</v>
       </c>
       <c r="E258">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F258">
         <v>1</v>
@@ -36516,11 +36516,11 @@
     </row>
     <row r="259" spans="1:8">
       <c r="A259">
-        <v>321030</v>
+        <v>321020</v>
       </c>
       <c r="B259" t="str">
         <f>INDEX(TextData!B:B,MATCH(A259,TextData!A:A))</f>
-        <v>蒼の祭壇</v>
+        <v>稲妻の祭壇</v>
       </c>
       <c r="C259">
         <v>40050</v>
@@ -36530,7 +36530,7 @@
         <v>属性適正アップ</v>
       </c>
       <c r="E259">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F259">
         <v>1</v>
@@ -36544,11 +36544,11 @@
     </row>
     <row r="260" spans="1:8">
       <c r="A260">
-        <v>321040</v>
+        <v>321030</v>
       </c>
       <c r="B260" t="str">
         <f>INDEX(TextData!B:B,MATCH(A260,TextData!A:A))</f>
-        <v>光の祭壇</v>
+        <v>蒼の祭壇</v>
       </c>
       <c r="C260">
         <v>40050</v>
@@ -36558,7 +36558,7 @@
         <v>属性適正アップ</v>
       </c>
       <c r="E260">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F260">
         <v>1</v>
@@ -36572,11 +36572,11 @@
     </row>
     <row r="261" spans="1:8">
       <c r="A261">
-        <v>321050</v>
+        <v>321040</v>
       </c>
       <c r="B261" t="str">
         <f>INDEX(TextData!B:B,MATCH(A261,TextData!A:A))</f>
-        <v>月の祭壇</v>
+        <v>光の祭壇</v>
       </c>
       <c r="C261">
         <v>40050</v>
@@ -36586,7 +36586,7 @@
         <v>属性適正アップ</v>
       </c>
       <c r="E261">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F261">
         <v>1</v>
@@ -36598,45 +36598,41 @@
         <v>100</v>
       </c>
     </row>
-    <row r="262" spans="1:9">
+    <row r="262" spans="1:8">
       <c r="A262">
-        <v>322010</v>
+        <v>321050</v>
       </c>
       <c r="B262" t="str">
         <f>INDEX(TextData!B:B,MATCH(A262,TextData!A:A))</f>
-        <v>食糧庫Lv1</v>
+        <v>月の祭壇</v>
       </c>
       <c r="C262">
-        <v>3010</v>
+        <v>40050</v>
       </c>
       <c r="D262" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C262,Define!P:P))</f>
-        <v>ステート付与</v>
+        <v>属性適正アップ</v>
       </c>
       <c r="E262">
-        <v>1020</v>
+        <v>5</v>
       </c>
       <c r="F262">
-        <v>999</v>
+        <v>1</v>
       </c>
       <c r="G262">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H262">
         <v>100</v>
       </c>
-      <c r="I262" t="str">
-        <f>INDEX([4]TextData!B:B,MATCH(E262,[4]TextData!A:A))</f>
-        <v>最大Hpアップ</v>
-      </c>
     </row>
     <row r="263" spans="1:9">
       <c r="A263">
-        <v>322020</v>
+        <v>322010</v>
       </c>
       <c r="B263" t="str">
         <f>INDEX(TextData!B:B,MATCH(A263,TextData!A:A))</f>
-        <v>攻撃技術Lv1</v>
+        <v>食糧庫Lv1</v>
       </c>
       <c r="C263">
         <v>3010</v>
@@ -36646,29 +36642,29 @@
         <v>ステート付与</v>
       </c>
       <c r="E263">
-        <v>1040</v>
+        <v>1020</v>
       </c>
       <c r="F263">
         <v>999</v>
       </c>
       <c r="G263">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H263">
         <v>100</v>
       </c>
       <c r="I263" t="str">
         <f>INDEX([4]TextData!B:B,MATCH(E263,[4]TextData!A:A))</f>
-        <v>攻撃アップ</v>
+        <v>最大Hpアップ</v>
       </c>
     </row>
     <row r="264" spans="1:9">
       <c r="A264">
-        <v>322030</v>
+        <v>322020</v>
       </c>
       <c r="B264" t="str">
         <f>INDEX(TextData!B:B,MATCH(A264,TextData!A:A))</f>
-        <v>防御技術Lv1</v>
+        <v>攻撃技術Lv1</v>
       </c>
       <c r="C264">
         <v>3010</v>
@@ -36678,7 +36674,7 @@
         <v>ステート付与</v>
       </c>
       <c r="E264">
-        <v>1050</v>
+        <v>1040</v>
       </c>
       <c r="F264">
         <v>999</v>
@@ -36691,16 +36687,16 @@
       </c>
       <c r="I264" t="str">
         <f>INDEX([4]TextData!B:B,MATCH(E264,[4]TextData!A:A))</f>
-        <v>防御アップ</v>
+        <v>攻撃アップ</v>
       </c>
     </row>
     <row r="265" spans="1:9">
       <c r="A265">
-        <v>322040</v>
+        <v>322030</v>
       </c>
       <c r="B265" t="str">
         <f>INDEX(TextData!B:B,MATCH(A265,TextData!A:A))</f>
-        <v>詠唱技術Lv1</v>
+        <v>防御技術Lv1</v>
       </c>
       <c r="C265">
         <v>3010</v>
@@ -36710,7 +36706,7 @@
         <v>ステート付与</v>
       </c>
       <c r="E265">
-        <v>1060</v>
+        <v>1050</v>
       </c>
       <c r="F265">
         <v>999</v>
@@ -36723,44 +36719,48 @@
       </c>
       <c r="I265" t="str">
         <f>INDEX([4]TextData!B:B,MATCH(E265,[4]TextData!A:A))</f>
-        <v>速度アップ</v>
-      </c>
-    </row>
-    <row r="266" spans="1:8">
+        <v>防御アップ</v>
+      </c>
+    </row>
+    <row r="266" spans="1:9">
       <c r="A266">
-        <v>401020</v>
+        <v>322040</v>
       </c>
       <c r="B266" t="str">
         <f>INDEX(TextData!B:B,MATCH(A266,TextData!A:A))</f>
-        <v>バーンストーム+</v>
+        <v>詠唱技術Lv1</v>
       </c>
       <c r="C266">
-        <v>6010</v>
+        <v>3010</v>
       </c>
       <c r="D266" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C266,Define!P:P))</f>
-        <v>指定のFeatureのParam1を増やす</v>
+        <v>ステート付与</v>
       </c>
       <c r="E266">
-        <v>1020</v>
+        <v>1060</v>
       </c>
       <c r="F266">
-        <v>0</v>
+        <v>999</v>
       </c>
       <c r="G266">
-        <v>250</v>
+        <v>2</v>
       </c>
       <c r="H266">
         <v>100</v>
       </c>
+      <c r="I266" t="str">
+        <f>INDEX([4]TextData!B:B,MATCH(E266,[4]TextData!A:A))</f>
+        <v>速度アップ</v>
+      </c>
     </row>
     <row r="267" spans="1:8">
       <c r="A267">
-        <v>401030</v>
+        <v>401020</v>
       </c>
       <c r="B267" t="str">
         <f>INDEX(TextData!B:B,MATCH(A267,TextData!A:A))</f>
-        <v>ヒートスタンプ+</v>
+        <v>バーンストーム+</v>
       </c>
       <c r="C267">
         <v>6010</v>
@@ -36770,13 +36770,13 @@
         <v>指定のFeatureのParam1を増やす</v>
       </c>
       <c r="E267">
-        <v>1030</v>
+        <v>1020</v>
       </c>
       <c r="F267">
         <v>0</v>
       </c>
       <c r="G267">
-        <v>2</v>
+        <v>250</v>
       </c>
       <c r="H267">
         <v>100</v>
@@ -36784,11 +36784,11 @@
     </row>
     <row r="268" spans="1:8">
       <c r="A268">
-        <v>401040</v>
+        <v>401030</v>
       </c>
       <c r="B268" t="str">
         <f>INDEX(TextData!B:B,MATCH(A268,TextData!A:A))</f>
-        <v>ソードアダプト+</v>
+        <v>ヒートスタンプ+</v>
       </c>
       <c r="C268">
         <v>6010</v>
@@ -36798,13 +36798,13 @@
         <v>指定のFeatureのParam1を増やす</v>
       </c>
       <c r="E268">
-        <v>1040</v>
+        <v>1030</v>
       </c>
       <c r="F268">
         <v>0</v>
       </c>
       <c r="G268">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="H268">
         <v>100</v>
@@ -36812,11 +36812,11 @@
     </row>
     <row r="269" spans="1:8">
       <c r="A269">
-        <v>401050</v>
+        <v>401040</v>
       </c>
       <c r="B269" t="str">
         <f>INDEX(TextData!B:B,MATCH(A269,TextData!A:A))</f>
-        <v>フレイムレイン+</v>
+        <v>ソードアダプト+</v>
       </c>
       <c r="C269">
         <v>6010</v>
@@ -36826,13 +36826,13 @@
         <v>指定のFeatureのParam1を増やす</v>
       </c>
       <c r="E269">
-        <v>1050</v>
+        <v>1040</v>
       </c>
       <c r="F269">
         <v>0</v>
       </c>
       <c r="G269">
-        <v>60</v>
+        <v>15</v>
       </c>
       <c r="H269">
         <v>100</v>
@@ -36840,11 +36840,11 @@
     </row>
     <row r="270" spans="1:8">
       <c r="A270">
-        <v>401060</v>
+        <v>401050</v>
       </c>
       <c r="B270" t="str">
         <f>INDEX(TextData!B:B,MATCH(A270,TextData!A:A))</f>
-        <v>イクスティンクション+</v>
+        <v>フレイムレイン+</v>
       </c>
       <c r="C270">
         <v>6010</v>
@@ -36854,13 +36854,13 @@
         <v>指定のFeatureのParam1を増やす</v>
       </c>
       <c r="E270">
-        <v>1060</v>
+        <v>1050</v>
       </c>
       <c r="F270">
         <v>0</v>
       </c>
       <c r="G270">
-        <v>400</v>
+        <v>60</v>
       </c>
       <c r="H270">
         <v>100</v>
@@ -36868,27 +36868,27 @@
     </row>
     <row r="271" spans="1:8">
       <c r="A271">
-        <v>401070</v>
+        <v>401060</v>
       </c>
       <c r="B271" t="str">
         <f>INDEX(TextData!B:B,MATCH(A271,TextData!A:A))</f>
-        <v>バーニングソウル+</v>
+        <v>イクスティンクション+</v>
       </c>
       <c r="C271">
-        <v>6080</v>
+        <v>6010</v>
       </c>
       <c r="D271" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C271,Define!P:P))</f>
-        <v>指定魔法のCTリセット値を変更する</v>
+        <v>指定のFeatureのParam1を増やす</v>
       </c>
       <c r="E271">
-        <v>1070</v>
+        <v>1060</v>
       </c>
       <c r="F271">
         <v>0</v>
       </c>
       <c r="G271">
-        <v>2</v>
+        <v>400</v>
       </c>
       <c r="H271">
         <v>100</v>
@@ -36896,27 +36896,27 @@
     </row>
     <row r="272" spans="1:8">
       <c r="A272">
-        <v>401080</v>
+        <v>401070</v>
       </c>
       <c r="B272" t="str">
         <f>INDEX(TextData!B:B,MATCH(A272,TextData!A:A))</f>
-        <v>レイジングバウンサー+</v>
+        <v>バーニングソウル+</v>
       </c>
       <c r="C272">
-        <v>6030</v>
+        <v>6080</v>
       </c>
       <c r="D272" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C272,Define!P:P))</f>
-        <v>指定のFeatureのParam3を増やす</v>
+        <v>指定魔法のCTリセット値を変更する</v>
       </c>
       <c r="E272">
-        <v>1080</v>
+        <v>1070</v>
       </c>
       <c r="F272">
         <v>0</v>
       </c>
       <c r="G272">
-        <v>45</v>
+        <v>2</v>
       </c>
       <c r="H272">
         <v>100</v>
@@ -36924,27 +36924,27 @@
     </row>
     <row r="273" spans="1:8">
       <c r="A273">
-        <v>402010</v>
+        <v>401080</v>
       </c>
       <c r="B273" t="str">
         <f>INDEX(TextData!B:B,MATCH(A273,TextData!A:A))</f>
-        <v>ディスチャージ+</v>
+        <v>レイジングバウンサー+</v>
       </c>
       <c r="C273">
-        <v>6010</v>
+        <v>6030</v>
       </c>
       <c r="D273" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C273,Define!P:P))</f>
-        <v>指定のFeatureのParam1を増やす</v>
+        <v>指定のFeatureのParam3を増やす</v>
       </c>
       <c r="E273">
-        <v>2010</v>
+        <v>1080</v>
       </c>
       <c r="F273">
         <v>0</v>
       </c>
       <c r="G273">
-        <v>250</v>
+        <v>45</v>
       </c>
       <c r="H273">
         <v>100</v>
@@ -36952,27 +36952,27 @@
     </row>
     <row r="274" spans="1:8">
       <c r="A274">
-        <v>402020</v>
+        <v>402010</v>
       </c>
       <c r="B274" t="str">
         <f>INDEX(TextData!B:B,MATCH(A274,TextData!A:A))</f>
-        <v>イベイドコード+</v>
+        <v>ディスチャージ+</v>
       </c>
       <c r="C274">
-        <v>6030</v>
+        <v>6010</v>
       </c>
       <c r="D274" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C274,Define!P:P))</f>
-        <v>指定のFeatureのParam3を増やす</v>
+        <v>指定のFeatureのParam1を増やす</v>
       </c>
       <c r="E274">
-        <v>2020</v>
+        <v>2010</v>
       </c>
       <c r="F274">
         <v>0</v>
       </c>
       <c r="G274">
-        <v>25</v>
+        <v>250</v>
       </c>
       <c r="H274">
         <v>100</v>
@@ -36980,27 +36980,27 @@
     </row>
     <row r="275" spans="1:8">
       <c r="A275">
-        <v>402030</v>
+        <v>402020</v>
       </c>
       <c r="B275" t="str">
         <f>INDEX(TextData!B:B,MATCH(A275,TextData!A:A))</f>
-        <v>ショックインパルス+</v>
+        <v>イベイドコード+</v>
       </c>
       <c r="C275">
-        <v>6080</v>
+        <v>6030</v>
       </c>
       <c r="D275" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C275,Define!P:P))</f>
-        <v>指定魔法のCTリセット値を変更する</v>
+        <v>指定のFeatureのParam3を増やす</v>
       </c>
       <c r="E275">
-        <v>2030</v>
+        <v>2020</v>
       </c>
       <c r="F275">
         <v>0</v>
       </c>
       <c r="G275">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="H275">
         <v>100</v>
@@ -37008,27 +37008,27 @@
     </row>
     <row r="276" spans="1:8">
       <c r="A276">
-        <v>402040</v>
+        <v>402030</v>
       </c>
       <c r="B276" t="str">
         <f>INDEX(TextData!B:B,MATCH(A276,TextData!A:A))</f>
-        <v>トラストチェイン+</v>
+        <v>ショックインパルス+</v>
       </c>
       <c r="C276">
-        <v>6010</v>
+        <v>6080</v>
       </c>
       <c r="D276" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C276,Define!P:P))</f>
-        <v>指定のFeatureのParam1を増やす</v>
+        <v>指定魔法のCTリセット値を変更する</v>
       </c>
       <c r="E276">
-        <v>2040</v>
+        <v>2030</v>
       </c>
       <c r="F276">
         <v>0</v>
       </c>
       <c r="G276">
-        <v>400</v>
+        <v>2</v>
       </c>
       <c r="H276">
         <v>100</v>
@@ -37036,27 +37036,27 @@
     </row>
     <row r="277" spans="1:8">
       <c r="A277">
-        <v>402050</v>
+        <v>402040</v>
       </c>
       <c r="B277" t="str">
         <f>INDEX(TextData!B:B,MATCH(A277,TextData!A:A))</f>
-        <v>スペルバニシング+</v>
+        <v>トラストチェイン+</v>
       </c>
       <c r="C277">
-        <v>6080</v>
+        <v>6010</v>
       </c>
       <c r="D277" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C277,Define!P:P))</f>
-        <v>指定魔法のCTリセット値を変更する</v>
+        <v>指定のFeatureのParam1を増やす</v>
       </c>
       <c r="E277">
-        <v>2050</v>
+        <v>2040</v>
       </c>
       <c r="F277">
         <v>0</v>
       </c>
       <c r="G277">
-        <v>1</v>
+        <v>400</v>
       </c>
       <c r="H277">
         <v>100</v>
@@ -37064,27 +37064,27 @@
     </row>
     <row r="278" spans="1:8">
       <c r="A278">
-        <v>402060</v>
+        <v>402050</v>
       </c>
       <c r="B278" t="str">
         <f>INDEX(TextData!B:B,MATCH(A278,TextData!A:A))</f>
-        <v>アーテニーストライク+</v>
+        <v>スペルバニシング+</v>
       </c>
       <c r="C278">
-        <v>6010</v>
+        <v>6080</v>
       </c>
       <c r="D278" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C278,Define!P:P))</f>
-        <v>指定のFeatureのParam1を増やす</v>
+        <v>指定魔法のCTリセット値を変更する</v>
       </c>
       <c r="E278">
-        <v>2060</v>
+        <v>2050</v>
       </c>
       <c r="F278">
         <v>0</v>
       </c>
       <c r="G278">
-        <v>250</v>
+        <v>1</v>
       </c>
       <c r="H278">
         <v>100</v>
@@ -37092,27 +37092,27 @@
     </row>
     <row r="279" spans="1:8">
       <c r="A279">
-        <v>402070</v>
+        <v>402060</v>
       </c>
       <c r="B279" t="str">
         <f>INDEX(TextData!B:B,MATCH(A279,TextData!A:A))</f>
-        <v>コンセントレイト+</v>
+        <v>アーテニーストライク+</v>
       </c>
       <c r="C279">
-        <v>6030</v>
+        <v>6010</v>
       </c>
       <c r="D279" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C279,Define!P:P))</f>
-        <v>指定のFeatureのParam3を増やす</v>
+        <v>指定のFeatureのParam1を増やす</v>
       </c>
       <c r="E279">
-        <v>2070</v>
+        <v>2060</v>
       </c>
       <c r="F279">
         <v>0</v>
       </c>
       <c r="G279">
-        <v>40</v>
+        <v>250</v>
       </c>
       <c r="H279">
         <v>100</v>
@@ -37120,27 +37120,27 @@
     </row>
     <row r="280" spans="1:8">
       <c r="A280">
-        <v>402080</v>
+        <v>402070</v>
       </c>
       <c r="B280" t="str">
         <f>INDEX(TextData!B:B,MATCH(A280,TextData!A:A))</f>
-        <v>ディレイマジック+</v>
+        <v>コンセントレイト+</v>
       </c>
       <c r="C280">
-        <v>6010</v>
+        <v>6030</v>
       </c>
       <c r="D280" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C280,Define!P:P))</f>
-        <v>指定のFeatureのParam1を増やす</v>
+        <v>指定のFeatureのParam3を増やす</v>
       </c>
       <c r="E280">
-        <v>2080</v>
+        <v>2070</v>
       </c>
       <c r="F280">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G280">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="H280">
         <v>100</v>
@@ -37148,11 +37148,11 @@
     </row>
     <row r="281" spans="1:8">
       <c r="A281">
-        <v>403010</v>
+        <v>402080</v>
       </c>
       <c r="B281" t="str">
         <f>INDEX(TextData!B:B,MATCH(A281,TextData!A:A))</f>
-        <v>アイスブレイド+</v>
+        <v>ディレイマジック+</v>
       </c>
       <c r="C281">
         <v>6010</v>
@@ -37162,13 +37162,13 @@
         <v>指定のFeatureのParam1を増やす</v>
       </c>
       <c r="E281">
-        <v>3010</v>
+        <v>2080</v>
       </c>
       <c r="F281">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G281">
-        <v>250</v>
+        <v>2</v>
       </c>
       <c r="H281">
         <v>100</v>
@@ -37176,27 +37176,27 @@
     </row>
     <row r="282" spans="1:8">
       <c r="A282">
-        <v>403020</v>
+        <v>403010</v>
       </c>
       <c r="B282" t="str">
         <f>INDEX(TextData!B:B,MATCH(A282,TextData!A:A))</f>
-        <v>カウンターオーラ+</v>
+        <v>アイスブレイド+</v>
       </c>
       <c r="C282">
-        <v>6030</v>
+        <v>6010</v>
       </c>
       <c r="D282" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C282,Define!P:P))</f>
-        <v>指定のFeatureのParam3を増やす</v>
+        <v>指定のFeatureのParam1を増やす</v>
       </c>
       <c r="E282">
-        <v>3020</v>
+        <v>3010</v>
       </c>
       <c r="F282">
         <v>0</v>
       </c>
       <c r="G282">
-        <v>40</v>
+        <v>250</v>
       </c>
       <c r="H282">
         <v>100</v>
@@ -37204,11 +37204,11 @@
     </row>
     <row r="283" spans="1:8">
       <c r="A283">
-        <v>403030</v>
+        <v>403020</v>
       </c>
       <c r="B283" t="str">
         <f>INDEX(TextData!B:B,MATCH(A283,TextData!A:A))</f>
-        <v>ラインプロテクト+</v>
+        <v>カウンターオーラ+</v>
       </c>
       <c r="C283">
         <v>6030</v>
@@ -37218,13 +37218,13 @@
         <v>指定のFeatureのParam3を増やす</v>
       </c>
       <c r="E283">
-        <v>3030</v>
+        <v>3020</v>
       </c>
       <c r="F283">
         <v>0</v>
       </c>
       <c r="G283">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="H283">
         <v>100</v>
@@ -37232,11 +37232,11 @@
     </row>
     <row r="284" spans="1:8">
       <c r="A284">
-        <v>403040</v>
+        <v>403030</v>
       </c>
       <c r="B284" t="str">
         <f>INDEX(TextData!B:B,MATCH(A284,TextData!A:A))</f>
-        <v>エスコートソール+</v>
+        <v>ラインプロテクト+</v>
       </c>
       <c r="C284">
         <v>6030</v>
@@ -37246,13 +37246,13 @@
         <v>指定のFeatureのParam3を増やす</v>
       </c>
       <c r="E284">
-        <v>3040</v>
+        <v>3030</v>
       </c>
       <c r="F284">
         <v>0</v>
       </c>
       <c r="G284">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="H284">
         <v>100</v>
@@ -37260,11 +37260,11 @@
     </row>
     <row r="285" spans="1:8">
       <c r="A285">
-        <v>403050</v>
+        <v>403040</v>
       </c>
       <c r="B285" t="str">
         <f>INDEX(TextData!B:B,MATCH(A285,TextData!A:A))</f>
-        <v>ディープフリーズ+</v>
+        <v>エスコートソール+</v>
       </c>
       <c r="C285">
         <v>6030</v>
@@ -37274,7 +37274,7 @@
         <v>指定のFeatureのParam3を増やす</v>
       </c>
       <c r="E285">
-        <v>3050</v>
+        <v>3040</v>
       </c>
       <c r="F285">
         <v>0</v>
@@ -37288,11 +37288,11 @@
     </row>
     <row r="286" spans="1:8">
       <c r="A286">
-        <v>403060</v>
+        <v>403050</v>
       </c>
       <c r="B286" t="str">
         <f>INDEX(TextData!B:B,MATCH(A286,TextData!A:A))</f>
-        <v>バブルブロウ+</v>
+        <v>ディープフリーズ+</v>
       </c>
       <c r="C286">
         <v>6030</v>
@@ -37302,13 +37302,13 @@
         <v>指定のFeatureのParam3を増やす</v>
       </c>
       <c r="E286">
-        <v>3060</v>
+        <v>3050</v>
       </c>
       <c r="F286">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G286">
-        <v>12</v>
+        <v>40</v>
       </c>
       <c r="H286">
         <v>100</v>
@@ -37316,27 +37316,27 @@
     </row>
     <row r="287" spans="1:8">
       <c r="A287">
-        <v>403070</v>
+        <v>403060</v>
       </c>
       <c r="B287" t="str">
         <f>INDEX(TextData!B:B,MATCH(A287,TextData!A:A))</f>
-        <v>アクアミラージュ+</v>
+        <v>バブルブロウ+</v>
       </c>
       <c r="C287">
-        <v>6020</v>
+        <v>6030</v>
       </c>
       <c r="D287" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C287,Define!P:P))</f>
-        <v>指定のFeatureのParam2を増やす</v>
+        <v>指定のFeatureのParam3を増やす</v>
       </c>
       <c r="E287">
-        <v>3070</v>
+        <v>3060</v>
       </c>
       <c r="F287">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G287">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="H287">
         <v>100</v>
@@ -37344,27 +37344,27 @@
     </row>
     <row r="288" spans="1:8">
       <c r="A288">
-        <v>403080</v>
+        <v>403070</v>
       </c>
       <c r="B288" t="str">
         <f>INDEX(TextData!B:B,MATCH(A288,TextData!A:A))</f>
-        <v>フロストシールド+</v>
+        <v>アクアミラージュ+</v>
       </c>
       <c r="C288">
-        <v>6030</v>
+        <v>6020</v>
       </c>
       <c r="D288" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C288,Define!P:P))</f>
-        <v>指定のFeatureのParam3を増やす</v>
+        <v>指定のFeatureのParam2を増やす</v>
       </c>
       <c r="E288">
-        <v>3080</v>
+        <v>3070</v>
       </c>
       <c r="F288">
         <v>0</v>
       </c>
       <c r="G288">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="H288">
         <v>100</v>
@@ -37372,27 +37372,27 @@
     </row>
     <row r="289" spans="1:8">
       <c r="A289">
-        <v>404010</v>
+        <v>403080</v>
       </c>
       <c r="B289" t="str">
         <f>INDEX(TextData!B:B,MATCH(A289,TextData!A:A))</f>
-        <v>セイントレーザー+</v>
+        <v>フロストシールド+</v>
       </c>
       <c r="C289">
-        <v>6010</v>
+        <v>6030</v>
       </c>
       <c r="D289" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C289,Define!P:P))</f>
-        <v>指定のFeatureのParam1を増やす</v>
+        <v>指定のFeatureのParam3を増やす</v>
       </c>
       <c r="E289">
-        <v>4010</v>
+        <v>3080</v>
       </c>
       <c r="F289">
         <v>0</v>
       </c>
       <c r="G289">
-        <v>250</v>
+        <v>30</v>
       </c>
       <c r="H289">
         <v>100</v>
@@ -37400,11 +37400,11 @@
     </row>
     <row r="290" spans="1:8">
       <c r="A290">
-        <v>404020</v>
+        <v>404010</v>
       </c>
       <c r="B290" t="str">
         <f>INDEX(TextData!B:B,MATCH(A290,TextData!A:A))</f>
-        <v>ペネトレイト+</v>
+        <v>セイントレーザー+</v>
       </c>
       <c r="C290">
         <v>6010</v>
@@ -37414,7 +37414,7 @@
         <v>指定のFeatureのParam1を増やす</v>
       </c>
       <c r="E290">
-        <v>4020</v>
+        <v>4010</v>
       </c>
       <c r="F290">
         <v>0</v>
@@ -37428,27 +37428,27 @@
     </row>
     <row r="291" spans="1:8">
       <c r="A291">
-        <v>404030</v>
+        <v>404020</v>
       </c>
       <c r="B291" t="str">
         <f>INDEX(TextData!B:B,MATCH(A291,TextData!A:A))</f>
-        <v>ヒーリング+</v>
+        <v>ペネトレイト+</v>
       </c>
       <c r="C291">
-        <v>6210</v>
+        <v>6010</v>
       </c>
       <c r="D291" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C291,Define!P:P))</f>
-        <v>指定魔法の対象を変更（強化限定）</v>
+        <v>指定のFeatureのParam1を増やす</v>
       </c>
       <c r="E291">
-        <v>4030</v>
+        <v>4020</v>
       </c>
       <c r="F291">
         <v>0</v>
       </c>
       <c r="G291">
-        <v>31</v>
+        <v>250</v>
       </c>
       <c r="H291">
         <v>100</v>
@@ -37456,27 +37456,27 @@
     </row>
     <row r="292" spans="1:8">
       <c r="A292">
-        <v>404040</v>
+        <v>404030</v>
       </c>
       <c r="B292" t="str">
         <f>INDEX(TextData!B:B,MATCH(A292,TextData!A:A))</f>
-        <v>リザイアフォトン+</v>
+        <v>ヒーリング+</v>
       </c>
       <c r="C292">
-        <v>6030</v>
+        <v>6210</v>
       </c>
       <c r="D292" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C292,Define!P:P))</f>
-        <v>指定のFeatureのParam3を増やす</v>
+        <v>指定魔法の対象を変更（強化限定）</v>
       </c>
       <c r="E292">
-        <v>4040</v>
+        <v>4030</v>
       </c>
       <c r="F292">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G292">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H292">
         <v>100</v>
@@ -37484,27 +37484,27 @@
     </row>
     <row r="293" spans="1:8">
       <c r="A293">
-        <v>404050</v>
+        <v>404040</v>
       </c>
       <c r="B293" t="str">
         <f>INDEX(TextData!B:B,MATCH(A293,TextData!A:A))</f>
-        <v>べネディクション+</v>
+        <v>リザイアフォトン+</v>
       </c>
       <c r="C293">
-        <v>6080</v>
+        <v>6030</v>
       </c>
       <c r="D293" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C293,Define!P:P))</f>
-        <v>指定魔法のCTリセット値を変更する</v>
+        <v>指定のFeatureのParam3を増やす</v>
       </c>
       <c r="E293">
-        <v>4050</v>
+        <v>4040</v>
       </c>
       <c r="F293">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G293">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="H293">
         <v>100</v>
@@ -37512,11 +37512,11 @@
     </row>
     <row r="294" spans="1:8">
       <c r="A294">
-        <v>404060</v>
+        <v>404050</v>
       </c>
       <c r="B294" t="str">
         <f>INDEX(TextData!B:B,MATCH(A294,TextData!A:A))</f>
-        <v>ホーリーグレイス+</v>
+        <v>べネディクション+</v>
       </c>
       <c r="C294">
         <v>6080</v>
@@ -37526,13 +37526,13 @@
         <v>指定魔法のCTリセット値を変更する</v>
       </c>
       <c r="E294">
-        <v>4060</v>
+        <v>4050</v>
       </c>
       <c r="F294">
         <v>0</v>
       </c>
       <c r="G294">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H294">
         <v>100</v>
@@ -37540,27 +37540,27 @@
     </row>
     <row r="295" spans="1:8">
       <c r="A295">
-        <v>404070</v>
+        <v>404060</v>
       </c>
       <c r="B295" t="str">
         <f>INDEX(TextData!B:B,MATCH(A295,TextData!A:A))</f>
-        <v>キュアエール+</v>
+        <v>ホーリーグレイス+</v>
       </c>
       <c r="C295">
-        <v>6030</v>
+        <v>6080</v>
       </c>
       <c r="D295" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C295,Define!P:P))</f>
-        <v>指定のFeatureのParam3を増やす</v>
+        <v>指定魔法のCTリセット値を変更する</v>
       </c>
       <c r="E295">
-        <v>4070</v>
+        <v>4060</v>
       </c>
       <c r="F295">
         <v>0</v>
       </c>
       <c r="G295">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="H295">
         <v>100</v>
@@ -37568,27 +37568,27 @@
     </row>
     <row r="296" spans="1:8">
       <c r="A296">
-        <v>404080</v>
+        <v>404070</v>
       </c>
       <c r="B296" t="str">
         <f>INDEX(TextData!B:B,MATCH(A296,TextData!A:A))</f>
-        <v>ラインバリア+</v>
+        <v>キュアエール+</v>
       </c>
       <c r="C296">
-        <v>6080</v>
+        <v>6030</v>
       </c>
       <c r="D296" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C296,Define!P:P))</f>
-        <v>指定魔法のCTリセット値を変更する</v>
+        <v>指定のFeatureのParam3を増やす</v>
       </c>
       <c r="E296">
-        <v>4080</v>
+        <v>4070</v>
       </c>
       <c r="F296">
         <v>0</v>
       </c>
       <c r="G296">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="H296">
         <v>100</v>
@@ -37596,27 +37596,27 @@
     </row>
     <row r="297" spans="1:8">
       <c r="A297">
-        <v>405010</v>
+        <v>404080</v>
       </c>
       <c r="B297" t="str">
         <f>INDEX(TextData!B:B,MATCH(A297,TextData!A:A))</f>
-        <v>ダークプリズン+</v>
+        <v>ラインバリア+</v>
       </c>
       <c r="C297">
-        <v>6010</v>
+        <v>6080</v>
       </c>
       <c r="D297" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C297,Define!P:P))</f>
-        <v>指定のFeatureのParam1を増やす</v>
+        <v>指定魔法のCTリセット値を変更する</v>
       </c>
       <c r="E297">
-        <v>5010</v>
+        <v>4080</v>
       </c>
       <c r="F297">
         <v>0</v>
       </c>
       <c r="G297">
-        <v>250</v>
+        <v>3</v>
       </c>
       <c r="H297">
         <v>100</v>
@@ -37624,11 +37624,11 @@
     </row>
     <row r="298" spans="1:8">
       <c r="A298">
-        <v>405020</v>
+        <v>405010</v>
       </c>
       <c r="B298" t="str">
         <f>INDEX(TextData!B:B,MATCH(A298,TextData!A:A))</f>
-        <v>ユーサネイジア+</v>
+        <v>ダークプリズン+</v>
       </c>
       <c r="C298">
         <v>6010</v>
@@ -37638,13 +37638,13 @@
         <v>指定のFeatureのParam1を増やす</v>
       </c>
       <c r="E298">
-        <v>5020</v>
+        <v>5010</v>
       </c>
       <c r="F298">
         <v>0</v>
       </c>
       <c r="G298">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="H298">
         <v>100</v>
@@ -37652,27 +37652,27 @@
     </row>
     <row r="299" spans="1:8">
       <c r="A299">
-        <v>405030</v>
+        <v>405020</v>
       </c>
       <c r="B299" t="str">
         <f>INDEX(TextData!B:B,MATCH(A299,TextData!A:A))</f>
-        <v>ドレインヒール+</v>
+        <v>ユーサネイジア+</v>
       </c>
       <c r="C299">
-        <v>6030</v>
+        <v>6010</v>
       </c>
       <c r="D299" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C299,Define!P:P))</f>
-        <v>指定のFeatureのParam3を増やす</v>
+        <v>指定のFeatureのParam1を増やす</v>
       </c>
       <c r="E299">
-        <v>5030</v>
+        <v>5020</v>
       </c>
       <c r="F299">
         <v>0</v>
       </c>
       <c r="G299">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="H299">
         <v>100</v>
@@ -37680,27 +37680,27 @@
     </row>
     <row r="300" spans="1:8">
       <c r="A300">
-        <v>405040</v>
+        <v>405030</v>
       </c>
       <c r="B300" t="str">
         <f>INDEX(TextData!B:B,MATCH(A300,TextData!A:A))</f>
-        <v>アビサルデスペア+</v>
+        <v>ドレインヒール+</v>
       </c>
       <c r="C300">
-        <v>6020</v>
+        <v>6030</v>
       </c>
       <c r="D300" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C300,Define!P:P))</f>
-        <v>指定のFeatureのParam2を増やす</v>
+        <v>指定のFeatureのParam3を増やす</v>
       </c>
       <c r="E300">
-        <v>5040</v>
+        <v>5030</v>
       </c>
       <c r="F300">
         <v>0</v>
       </c>
       <c r="G300">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="H300">
         <v>100</v>
@@ -37708,27 +37708,27 @@
     </row>
     <row r="301" spans="1:8">
       <c r="A301">
-        <v>405050</v>
+        <v>405040</v>
       </c>
       <c r="B301" t="str">
         <f>INDEX(TextData!B:B,MATCH(A301,TextData!A:A))</f>
-        <v>ディプラヴィティ+</v>
+        <v>アビサルデスペア+</v>
       </c>
       <c r="C301">
-        <v>6030</v>
+        <v>6020</v>
       </c>
       <c r="D301" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C301,Define!P:P))</f>
-        <v>指定のFeatureのParam3を増やす</v>
+        <v>指定のFeatureのParam2を増やす</v>
       </c>
       <c r="E301">
-        <v>5050</v>
+        <v>5040</v>
       </c>
       <c r="F301">
         <v>0</v>
       </c>
       <c r="G301">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H301">
         <v>100</v>
@@ -37736,11 +37736,11 @@
     </row>
     <row r="302" spans="1:8">
       <c r="A302">
-        <v>405060</v>
+        <v>405050</v>
       </c>
       <c r="B302" t="str">
         <f>INDEX(TextData!B:B,MATCH(A302,TextData!A:A))</f>
-        <v>ダークネス+</v>
+        <v>ディプラヴィティ+</v>
       </c>
       <c r="C302">
         <v>6030</v>
@@ -37750,13 +37750,13 @@
         <v>指定のFeatureのParam3を増やす</v>
       </c>
       <c r="E302">
-        <v>5060</v>
+        <v>5050</v>
       </c>
       <c r="F302">
         <v>0</v>
       </c>
       <c r="G302">
-        <v>50</v>
+        <v>3</v>
       </c>
       <c r="H302">
         <v>100</v>
@@ -37764,11 +37764,11 @@
     </row>
     <row r="303" spans="1:8">
       <c r="A303">
-        <v>405070</v>
+        <v>405060</v>
       </c>
       <c r="B303" t="str">
         <f>INDEX(TextData!B:B,MATCH(A303,TextData!A:A))</f>
-        <v>シェイディークラウド+</v>
+        <v>ダークネス+</v>
       </c>
       <c r="C303">
         <v>6030</v>
@@ -37778,13 +37778,13 @@
         <v>指定のFeatureのParam3を増やす</v>
       </c>
       <c r="E303">
-        <v>5070</v>
+        <v>5060</v>
       </c>
       <c r="F303">
         <v>0</v>
       </c>
       <c r="G303">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="H303">
         <v>100</v>
@@ -37792,11 +37792,11 @@
     </row>
     <row r="304" spans="1:8">
       <c r="A304">
-        <v>405080</v>
+        <v>405070</v>
       </c>
       <c r="B304" t="str">
         <f>INDEX(TextData!B:B,MATCH(A304,TextData!A:A))</f>
-        <v>ポイズンブロウ+</v>
+        <v>シェイディークラウド+</v>
       </c>
       <c r="C304">
         <v>6030</v>
@@ -37806,13 +37806,13 @@
         <v>指定のFeatureのParam3を増やす</v>
       </c>
       <c r="E304">
-        <v>5080</v>
+        <v>5070</v>
       </c>
       <c r="F304">
         <v>0</v>
       </c>
       <c r="G304">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H304">
         <v>100</v>
@@ -37820,11 +37820,11 @@
     </row>
     <row r="305" spans="1:8">
       <c r="A305">
-        <v>411010</v>
+        <v>405080</v>
       </c>
       <c r="B305" t="str">
         <f>INDEX(TextData!B:B,MATCH(A305,TextData!A:A))</f>
-        <v>ウルフソウル+</v>
+        <v>ポイズンブロウ+</v>
       </c>
       <c r="C305">
         <v>6030</v>
@@ -37834,13 +37834,13 @@
         <v>指定のFeatureのParam3を増やす</v>
       </c>
       <c r="E305">
-        <v>11010</v>
+        <v>5080</v>
       </c>
       <c r="F305">
         <v>0</v>
       </c>
       <c r="G305">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="H305">
         <v>100</v>
@@ -37848,11 +37848,11 @@
     </row>
     <row r="306" spans="1:8">
       <c r="A306">
-        <v>411020</v>
+        <v>411010</v>
       </c>
       <c r="B306" t="str">
         <f>INDEX(TextData!B:B,MATCH(A306,TextData!A:A))</f>
-        <v>プリディカメント+</v>
+        <v>ウルフソウル+</v>
       </c>
       <c r="C306">
         <v>6030</v>
@@ -37862,13 +37862,13 @@
         <v>指定のFeatureのParam3を増やす</v>
       </c>
       <c r="E306">
-        <v>11020</v>
+        <v>11010</v>
       </c>
       <c r="F306">
         <v>0</v>
       </c>
       <c r="G306">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="H306">
         <v>100</v>
@@ -37876,11 +37876,11 @@
     </row>
     <row r="307" spans="1:8">
       <c r="A307">
-        <v>411030</v>
+        <v>411020</v>
       </c>
       <c r="B307" t="str">
         <f>INDEX(TextData!B:B,MATCH(A307,TextData!A:A))</f>
-        <v>アサルトシフト+</v>
+        <v>プリディカメント+</v>
       </c>
       <c r="C307">
         <v>6030</v>
@@ -37890,13 +37890,13 @@
         <v>指定のFeatureのParam3を増やす</v>
       </c>
       <c r="E307">
-        <v>11030</v>
+        <v>11020</v>
       </c>
       <c r="F307">
         <v>0</v>
       </c>
       <c r="G307">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="H307">
         <v>100</v>
@@ -37921,7 +37921,7 @@
         <v>11030</v>
       </c>
       <c r="F308">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G308">
         <v>8</v>
@@ -37932,27 +37932,27 @@
     </row>
     <row r="309" spans="1:8">
       <c r="A309">
-        <v>411040</v>
+        <v>411030</v>
       </c>
       <c r="B309" t="str">
         <f>INDEX(TextData!B:B,MATCH(A309,TextData!A:A))</f>
-        <v>アクティブギフト+</v>
+        <v>アサルトシフト+</v>
       </c>
       <c r="C309">
-        <v>6080</v>
+        <v>6030</v>
       </c>
       <c r="D309" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C309,Define!P:P))</f>
-        <v>指定魔法のCTリセット値を変更する</v>
+        <v>指定のFeatureのParam3を増やす</v>
       </c>
       <c r="E309">
-        <v>11040</v>
+        <v>11030</v>
       </c>
       <c r="F309">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G309">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="H309">
         <v>100</v>
@@ -37960,27 +37960,27 @@
     </row>
     <row r="310" spans="1:8">
       <c r="A310">
-        <v>411050</v>
+        <v>411040</v>
       </c>
       <c r="B310" t="str">
         <f>INDEX(TextData!B:B,MATCH(A310,TextData!A:A))</f>
-        <v>イグナイテッド+</v>
+        <v>アクティブギフト+</v>
       </c>
       <c r="C310">
-        <v>6010</v>
+        <v>6080</v>
       </c>
       <c r="D310" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C310,Define!P:P))</f>
-        <v>指定のFeatureのParam1を増やす</v>
+        <v>指定魔法のCTリセット値を変更する</v>
       </c>
       <c r="E310">
-        <v>11050</v>
+        <v>11040</v>
       </c>
       <c r="F310">
         <v>0</v>
       </c>
       <c r="G310">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H310">
         <v>100</v>
@@ -37988,11 +37988,11 @@
     </row>
     <row r="311" spans="1:8">
       <c r="A311">
-        <v>411060</v>
+        <v>411050</v>
       </c>
       <c r="B311" t="str">
         <f>INDEX(TextData!B:B,MATCH(A311,TextData!A:A))</f>
-        <v>ライジングファイア+</v>
+        <v>イグナイテッド+</v>
       </c>
       <c r="C311">
         <v>6010</v>
@@ -38002,13 +38002,13 @@
         <v>指定のFeatureのParam1を増やす</v>
       </c>
       <c r="E311">
-        <v>11060</v>
+        <v>11050</v>
       </c>
       <c r="F311">
         <v>0</v>
       </c>
       <c r="G311">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H311">
         <v>100</v>
@@ -38016,27 +38016,27 @@
     </row>
     <row r="312" spans="1:8">
       <c r="A312">
-        <v>411070</v>
+        <v>411060</v>
       </c>
       <c r="B312" t="str">
         <f>INDEX(TextData!B:B,MATCH(A312,TextData!A:A))</f>
-        <v>ルージュバック+</v>
+        <v>ライジングファイア+</v>
       </c>
       <c r="C312">
-        <v>6030</v>
+        <v>6010</v>
       </c>
       <c r="D312" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C312,Define!P:P))</f>
-        <v>指定のFeatureのParam3を増やす</v>
+        <v>指定のFeatureのParam1を増やす</v>
       </c>
       <c r="E312">
-        <v>11070</v>
+        <v>11060</v>
       </c>
       <c r="F312">
         <v>0</v>
       </c>
       <c r="G312">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H312">
         <v>100</v>
@@ -38044,11 +38044,11 @@
     </row>
     <row r="313" spans="1:8">
       <c r="A313">
-        <v>411080</v>
+        <v>411070</v>
       </c>
       <c r="B313" t="str">
         <f>INDEX(TextData!B:B,MATCH(A313,TextData!A:A))</f>
-        <v>パワーエール+</v>
+        <v>ルージュバック+</v>
       </c>
       <c r="C313">
         <v>6030</v>
@@ -38058,13 +38058,13 @@
         <v>指定のFeatureのParam3を増やす</v>
       </c>
       <c r="E313">
-        <v>11080</v>
+        <v>11070</v>
       </c>
       <c r="F313">
         <v>0</v>
       </c>
       <c r="G313">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H313">
         <v>100</v>
@@ -38072,11 +38072,11 @@
     </row>
     <row r="314" spans="1:8">
       <c r="A314">
-        <v>411090</v>
+        <v>411080</v>
       </c>
       <c r="B314" t="str">
         <f>INDEX(TextData!B:B,MATCH(A314,TextData!A:A))</f>
-        <v>スレイプニル+</v>
+        <v>パワーエール+</v>
       </c>
       <c r="C314">
         <v>6030</v>
@@ -38086,13 +38086,13 @@
         <v>指定のFeatureのParam3を増やす</v>
       </c>
       <c r="E314">
-        <v>11090</v>
+        <v>11080</v>
       </c>
       <c r="F314">
         <v>0</v>
       </c>
       <c r="G314">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="H314">
         <v>100</v>
@@ -38100,27 +38100,27 @@
     </row>
     <row r="315" spans="1:8">
       <c r="A315">
-        <v>412010</v>
+        <v>411090</v>
       </c>
       <c r="B315" t="str">
         <f>INDEX(TextData!B:B,MATCH(A315,TextData!A:A))</f>
-        <v>エクステンション+</v>
+        <v>スレイプニル+</v>
       </c>
       <c r="C315">
-        <v>6210</v>
+        <v>6030</v>
       </c>
       <c r="D315" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C315,Define!P:P))</f>
-        <v>指定魔法の対象を変更（強化限定）</v>
+        <v>指定のFeatureのParam3を増やす</v>
       </c>
       <c r="E315">
-        <v>12010</v>
+        <v>11090</v>
       </c>
       <c r="F315">
         <v>0</v>
       </c>
       <c r="G315">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="H315">
         <v>100</v>
@@ -38128,27 +38128,27 @@
     </row>
     <row r="316" spans="1:8">
       <c r="A316">
-        <v>412020</v>
+        <v>412010</v>
       </c>
       <c r="B316" t="str">
         <f>INDEX(TextData!B:B,MATCH(A316,TextData!A:A))</f>
-        <v>ヘブンリーラック+</v>
+        <v>エクステンション+</v>
       </c>
       <c r="C316">
-        <v>6030</v>
+        <v>6210</v>
       </c>
       <c r="D316" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C316,Define!P:P))</f>
-        <v>指定のFeatureのParam3を増やす</v>
+        <v>指定魔法の対象を変更（強化限定）</v>
       </c>
       <c r="E316">
-        <v>12020</v>
+        <v>12010</v>
       </c>
       <c r="F316">
         <v>0</v>
       </c>
       <c r="G316">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="H316">
         <v>100</v>
@@ -38156,11 +38156,11 @@
     </row>
     <row r="317" spans="1:8">
       <c r="A317">
-        <v>412030</v>
+        <v>412020</v>
       </c>
       <c r="B317" t="str">
         <f>INDEX(TextData!B:B,MATCH(A317,TextData!A:A))</f>
-        <v>スウィフトカレント+</v>
+        <v>ヘブンリーラック+</v>
       </c>
       <c r="C317">
         <v>6030</v>
@@ -38170,13 +38170,13 @@
         <v>指定のFeatureのParam3を増やす</v>
       </c>
       <c r="E317">
-        <v>12030</v>
+        <v>12020</v>
       </c>
       <c r="F317">
         <v>0</v>
       </c>
       <c r="G317">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="H317">
         <v>100</v>
@@ -38184,11 +38184,11 @@
     </row>
     <row r="318" spans="1:8">
       <c r="A318">
-        <v>412040</v>
+        <v>412030</v>
       </c>
       <c r="B318" t="str">
         <f>INDEX(TextData!B:B,MATCH(A318,TextData!A:A))</f>
-        <v>イヴェイドオール+</v>
+        <v>スウィフトカレント+</v>
       </c>
       <c r="C318">
         <v>6030</v>
@@ -38198,7 +38198,7 @@
         <v>指定のFeatureのParam3を増やす</v>
       </c>
       <c r="E318">
-        <v>12040</v>
+        <v>12030</v>
       </c>
       <c r="F318">
         <v>0</v>
@@ -38212,27 +38212,27 @@
     </row>
     <row r="319" spans="1:8">
       <c r="A319">
-        <v>412050</v>
+        <v>412040</v>
       </c>
       <c r="B319" t="str">
         <f>INDEX(TextData!B:B,MATCH(A319,TextData!A:A))</f>
-        <v>クイックムーブ+</v>
+        <v>イヴェイドオール+</v>
       </c>
       <c r="C319">
-        <v>6010</v>
+        <v>6030</v>
       </c>
       <c r="D319" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C319,Define!P:P))</f>
-        <v>指定のFeatureのParam1を増やす</v>
+        <v>指定のFeatureのParam3を増やす</v>
       </c>
       <c r="E319">
-        <v>12050</v>
+        <v>12040</v>
       </c>
       <c r="F319">
         <v>0</v>
       </c>
       <c r="G319">
-        <v>400</v>
+        <v>10</v>
       </c>
       <c r="H319">
         <v>100</v>
@@ -38240,11 +38240,11 @@
     </row>
     <row r="320" spans="1:8">
       <c r="A320">
-        <v>412060</v>
+        <v>412050</v>
       </c>
       <c r="B320" t="str">
         <f>INDEX(TextData!B:B,MATCH(A320,TextData!A:A))</f>
-        <v>チェイスマジック+</v>
+        <v>クイックムーブ+</v>
       </c>
       <c r="C320">
         <v>6010</v>
@@ -38254,13 +38254,13 @@
         <v>指定のFeatureのParam1を増やす</v>
       </c>
       <c r="E320">
-        <v>12060</v>
+        <v>12050</v>
       </c>
       <c r="F320">
         <v>0</v>
       </c>
       <c r="G320">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="H320">
         <v>100</v>
@@ -38268,27 +38268,27 @@
     </row>
     <row r="321" spans="1:8">
       <c r="A321">
-        <v>412070</v>
+        <v>412060</v>
       </c>
       <c r="B321" t="str">
         <f>INDEX(TextData!B:B,MATCH(A321,TextData!A:A))</f>
-        <v>ソーサリーコネクト+</v>
+        <v>チェイスマジック+</v>
       </c>
       <c r="C321">
-        <v>6030</v>
+        <v>6010</v>
       </c>
       <c r="D321" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C321,Define!P:P))</f>
-        <v>指定のFeatureのParam3を増やす</v>
+        <v>指定のFeatureのParam1を増やす</v>
       </c>
       <c r="E321">
-        <v>12070</v>
+        <v>12060</v>
       </c>
       <c r="F321">
         <v>0</v>
       </c>
       <c r="G321">
-        <v>16</v>
+        <v>300</v>
       </c>
       <c r="H321">
         <v>100</v>
@@ -38296,27 +38296,27 @@
     </row>
     <row r="322" spans="1:8">
       <c r="A322">
-        <v>412080</v>
+        <v>412070</v>
       </c>
       <c r="B322" t="str">
         <f>INDEX(TextData!B:B,MATCH(A322,TextData!A:A))</f>
-        <v>ウィンドライズ+</v>
+        <v>ソーサリーコネクト+</v>
       </c>
       <c r="C322">
-        <v>6010</v>
+        <v>6030</v>
       </c>
       <c r="D322" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C322,Define!P:P))</f>
-        <v>指定のFeatureのParam1を増やす</v>
+        <v>指定のFeatureのParam3を増やす</v>
       </c>
       <c r="E322">
-        <v>12080</v>
+        <v>12070</v>
       </c>
       <c r="F322">
         <v>0</v>
       </c>
       <c r="G322">
-        <v>300</v>
+        <v>16</v>
       </c>
       <c r="H322">
         <v>100</v>
@@ -38324,11 +38324,11 @@
     </row>
     <row r="323" spans="1:8">
       <c r="A323">
-        <v>412090</v>
+        <v>412080</v>
       </c>
       <c r="B323" t="str">
         <f>INDEX(TextData!B:B,MATCH(A323,TextData!A:A))</f>
-        <v>アウトオブオーダー+</v>
+        <v>ウィンドライズ+</v>
       </c>
       <c r="C323">
         <v>6010</v>
@@ -38338,13 +38338,13 @@
         <v>指定のFeatureのParam1を増やす</v>
       </c>
       <c r="E323">
-        <v>12090</v>
+        <v>12080</v>
       </c>
       <c r="F323">
         <v>0</v>
       </c>
       <c r="G323">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="H323">
         <v>100</v>
@@ -38352,27 +38352,27 @@
     </row>
     <row r="324" spans="1:8">
       <c r="A324">
-        <v>413010</v>
+        <v>412090</v>
       </c>
       <c r="B324" t="str">
         <f>INDEX(TextData!B:B,MATCH(A324,TextData!A:A))</f>
-        <v>アーマーコード+</v>
+        <v>アウトオブオーダー+</v>
       </c>
       <c r="C324">
-        <v>6030</v>
+        <v>6010</v>
       </c>
       <c r="D324" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C324,Define!P:P))</f>
-        <v>指定のFeatureのParam3を増やす</v>
+        <v>指定のFeatureのParam1を増やす</v>
       </c>
       <c r="E324">
-        <v>13010</v>
+        <v>12090</v>
       </c>
       <c r="F324">
         <v>0</v>
       </c>
       <c r="G324">
-        <v>8</v>
+        <v>400</v>
       </c>
       <c r="H324">
         <v>100</v>
@@ -38380,11 +38380,11 @@
     </row>
     <row r="325" spans="1:8">
       <c r="A325">
-        <v>413020</v>
+        <v>413010</v>
       </c>
       <c r="B325" t="str">
         <f>INDEX(TextData!B:B,MATCH(A325,TextData!A:A))</f>
-        <v>クイックバリア+</v>
+        <v>アーマーコード+</v>
       </c>
       <c r="C325">
         <v>6030</v>
@@ -38394,13 +38394,13 @@
         <v>指定のFeatureのParam3を増やす</v>
       </c>
       <c r="E325">
-        <v>13020</v>
+        <v>13010</v>
       </c>
       <c r="F325">
         <v>0</v>
       </c>
       <c r="G325">
-        <v>50</v>
+        <v>8</v>
       </c>
       <c r="H325">
         <v>100</v>
@@ -38408,27 +38408,27 @@
     </row>
     <row r="326" spans="1:8">
       <c r="A326">
-        <v>413030</v>
+        <v>413020</v>
       </c>
       <c r="B326" t="str">
         <f>INDEX(TextData!B:B,MATCH(A326,TextData!A:A))</f>
-        <v>クイックキュア+</v>
+        <v>クイックバリア+</v>
       </c>
       <c r="C326">
-        <v>6080</v>
+        <v>6030</v>
       </c>
       <c r="D326" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C326,Define!P:P))</f>
-        <v>指定魔法のCTリセット値を変更する</v>
+        <v>指定のFeatureのParam3を増やす</v>
       </c>
       <c r="E326">
-        <v>14090</v>
+        <v>13020</v>
       </c>
       <c r="F326">
         <v>0</v>
       </c>
       <c r="G326">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="H326">
         <v>100</v>
@@ -38436,27 +38436,27 @@
     </row>
     <row r="327" spans="1:8">
       <c r="A327">
-        <v>413040</v>
+        <v>413030</v>
       </c>
       <c r="B327" t="str">
         <f>INDEX(TextData!B:B,MATCH(A327,TextData!A:A))</f>
-        <v>セルフシールド+</v>
+        <v>クイックキュア+</v>
       </c>
       <c r="C327">
-        <v>6030</v>
+        <v>6080</v>
       </c>
       <c r="D327" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C327,Define!P:P))</f>
-        <v>指定のFeatureのParam3を増やす</v>
+        <v>指定魔法のCTリセット値を変更する</v>
       </c>
       <c r="E327">
-        <v>13040</v>
+        <v>14090</v>
       </c>
       <c r="F327">
         <v>0</v>
       </c>
       <c r="G327">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="H327">
         <v>100</v>
@@ -38464,27 +38464,27 @@
     </row>
     <row r="328" spans="1:8">
       <c r="A328">
-        <v>413050</v>
+        <v>413040</v>
       </c>
       <c r="B328" t="str">
         <f>INDEX(TextData!B:B,MATCH(A328,TextData!A:A))</f>
-        <v>パッシブジャミング+</v>
+        <v>セルフシールド+</v>
       </c>
       <c r="C328">
-        <v>6080</v>
+        <v>6030</v>
       </c>
       <c r="D328" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C328,Define!P:P))</f>
-        <v>指定魔法のCTリセット値を変更する</v>
+        <v>指定のFeatureのParam3を増やす</v>
       </c>
       <c r="E328">
-        <v>14090</v>
+        <v>13040</v>
       </c>
       <c r="F328">
         <v>0</v>
       </c>
       <c r="G328">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="H328">
         <v>100</v>
@@ -38492,11 +38492,11 @@
     </row>
     <row r="329" spans="1:8">
       <c r="A329">
-        <v>413060</v>
+        <v>413050</v>
       </c>
       <c r="B329" t="str">
         <f>INDEX(TextData!B:B,MATCH(A329,TextData!A:A))</f>
-        <v>サプライカバー+</v>
+        <v>パッシブジャミング+</v>
       </c>
       <c r="C329">
         <v>6080</v>
@@ -38520,27 +38520,27 @@
     </row>
     <row r="330" spans="1:8">
       <c r="A330">
-        <v>413070</v>
+        <v>413060</v>
       </c>
       <c r="B330" t="str">
         <f>INDEX(TextData!B:B,MATCH(A330,TextData!A:A))</f>
-        <v>アシッドラッシュ+</v>
+        <v>サプライカバー+</v>
       </c>
       <c r="C330">
-        <v>6010</v>
+        <v>6080</v>
       </c>
       <c r="D330" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C330,Define!P:P))</f>
-        <v>指定のFeatureのParam1を増やす</v>
+        <v>指定魔法のCTリセット値を変更する</v>
       </c>
       <c r="E330">
-        <v>13070</v>
+        <v>14090</v>
       </c>
       <c r="F330">
         <v>0</v>
       </c>
       <c r="G330">
-        <v>400</v>
+        <v>1</v>
       </c>
       <c r="H330">
         <v>100</v>
@@ -38548,27 +38548,27 @@
     </row>
     <row r="331" spans="1:8">
       <c r="A331">
-        <v>413080</v>
+        <v>413070</v>
       </c>
       <c r="B331" t="str">
         <f>INDEX(TextData!B:B,MATCH(A331,TextData!A:A))</f>
-        <v>ライフスティール+</v>
+        <v>アシッドラッシュ+</v>
       </c>
       <c r="C331">
-        <v>6030</v>
+        <v>6010</v>
       </c>
       <c r="D331" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C331,Define!P:P))</f>
-        <v>指定のFeatureのParam3を増やす</v>
+        <v>指定のFeatureのParam1を増やす</v>
       </c>
       <c r="E331">
-        <v>13080</v>
+        <v>13070</v>
       </c>
       <c r="F331">
         <v>0</v>
       </c>
       <c r="G331">
-        <v>50</v>
+        <v>400</v>
       </c>
       <c r="H331">
         <v>100</v>
@@ -38576,11 +38576,11 @@
     </row>
     <row r="332" spans="1:8">
       <c r="A332">
-        <v>413090</v>
+        <v>413080</v>
       </c>
       <c r="B332" t="str">
         <f>INDEX(TextData!B:B,MATCH(A332,TextData!A:A))</f>
-        <v>アイスセイバー+</v>
+        <v>ライフスティール+</v>
       </c>
       <c r="C332">
         <v>6030</v>
@@ -38590,7 +38590,7 @@
         <v>指定のFeatureのParam3を増やす</v>
       </c>
       <c r="E332">
-        <v>13090</v>
+        <v>13080</v>
       </c>
       <c r="F332">
         <v>0</v>
@@ -38604,27 +38604,27 @@
     </row>
     <row r="333" spans="1:8">
       <c r="A333">
-        <v>414010</v>
+        <v>413090</v>
       </c>
       <c r="B333" t="str">
         <f>INDEX(TextData!B:B,MATCH(A333,TextData!A:A))</f>
-        <v>ディバインシールド+</v>
+        <v>アイスセイバー+</v>
       </c>
       <c r="C333">
-        <v>6020</v>
+        <v>6030</v>
       </c>
       <c r="D333" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C333,Define!P:P))</f>
-        <v>指定のFeatureのParam2を増やす</v>
+        <v>指定のFeatureのParam3を増やす</v>
       </c>
       <c r="E333">
-        <v>14010</v>
+        <v>13090</v>
       </c>
       <c r="F333">
         <v>0</v>
       </c>
       <c r="G333">
-        <v>2</v>
+        <v>50</v>
       </c>
       <c r="H333">
         <v>100</v>
@@ -38632,27 +38632,27 @@
     </row>
     <row r="334" spans="1:8">
       <c r="A334">
-        <v>414020</v>
+        <v>414010</v>
       </c>
       <c r="B334" t="str">
         <f>INDEX(TextData!B:B,MATCH(A334,TextData!A:A))</f>
-        <v>ライフディバイド+</v>
+        <v>ディバインシールド+</v>
       </c>
       <c r="C334">
-        <v>6010</v>
+        <v>6020</v>
       </c>
       <c r="D334" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C334,Define!P:P))</f>
-        <v>指定のFeatureのParam1を増やす</v>
+        <v>指定のFeatureのParam2を増やす</v>
       </c>
       <c r="E334">
-        <v>14020</v>
+        <v>14010</v>
       </c>
       <c r="F334">
         <v>0</v>
       </c>
       <c r="G334">
-        <v>50</v>
+        <v>2</v>
       </c>
       <c r="H334">
         <v>100</v>
@@ -38660,27 +38660,27 @@
     </row>
     <row r="335" spans="1:8">
       <c r="A335">
-        <v>414030</v>
+        <v>414020</v>
       </c>
       <c r="B335" t="str">
         <f>INDEX(TextData!B:B,MATCH(A335,TextData!A:A))</f>
-        <v>エイミングスコープ+</v>
+        <v>ライフディバイド+</v>
       </c>
       <c r="C335">
-        <v>6030</v>
+        <v>6010</v>
       </c>
       <c r="D335" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C335,Define!P:P))</f>
-        <v>指定のFeatureのParam3を増やす</v>
+        <v>指定のFeatureのParam1を増やす</v>
       </c>
       <c r="E335">
-        <v>14030</v>
+        <v>14020</v>
       </c>
       <c r="F335">
         <v>0</v>
       </c>
       <c r="G335">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="H335">
         <v>100</v>
@@ -38688,11 +38688,11 @@
     </row>
     <row r="336" spans="1:8">
       <c r="A336">
-        <v>414040</v>
+        <v>414030</v>
       </c>
       <c r="B336" t="str">
         <f>INDEX(TextData!B:B,MATCH(A336,TextData!A:A))</f>
-        <v>リジェネレーション+</v>
+        <v>エイミングスコープ+</v>
       </c>
       <c r="C336">
         <v>6030</v>
@@ -38702,7 +38702,7 @@
         <v>指定のFeatureのParam3を増やす</v>
       </c>
       <c r="E336">
-        <v>14040</v>
+        <v>14030</v>
       </c>
       <c r="F336">
         <v>0</v>
@@ -38716,11 +38716,11 @@
     </row>
     <row r="337" spans="1:8">
       <c r="A337">
-        <v>414050</v>
+        <v>414040</v>
       </c>
       <c r="B337" t="str">
         <f>INDEX(TextData!B:B,MATCH(A337,TextData!A:A))</f>
-        <v>ホープフルアイリス+</v>
+        <v>リジェネレーション+</v>
       </c>
       <c r="C337">
         <v>6030</v>
@@ -38730,13 +38730,13 @@
         <v>指定のFeatureのParam3を増やす</v>
       </c>
       <c r="E337">
-        <v>14050</v>
+        <v>14040</v>
       </c>
       <c r="F337">
         <v>0</v>
       </c>
       <c r="G337">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="H337">
         <v>100</v>
@@ -38744,27 +38744,27 @@
     </row>
     <row r="338" spans="1:8">
       <c r="A338">
-        <v>414060</v>
+        <v>414050</v>
       </c>
       <c r="B338" t="str">
         <f>INDEX(TextData!B:B,MATCH(A338,TextData!A:A))</f>
-        <v>パッシブサプライ+</v>
+        <v>ホープフルアイリス+</v>
       </c>
       <c r="C338">
-        <v>6010</v>
+        <v>6030</v>
       </c>
       <c r="D338" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C338,Define!P:P))</f>
-        <v>指定のFeatureのParam1を増やす</v>
+        <v>指定のFeatureのParam3を増やす</v>
       </c>
       <c r="E338">
-        <v>14060</v>
+        <v>14050</v>
       </c>
       <c r="F338">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G338">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="H338">
         <v>100</v>
@@ -38772,27 +38772,27 @@
     </row>
     <row r="339" spans="1:8">
       <c r="A339">
-        <v>414070</v>
+        <v>414060</v>
       </c>
       <c r="B339" t="str">
         <f>INDEX(TextData!B:B,MATCH(A339,TextData!A:A))</f>
-        <v>ホーミングクルセイド+</v>
+        <v>パッシブサプライ+</v>
       </c>
       <c r="C339">
-        <v>6020</v>
+        <v>6010</v>
       </c>
       <c r="D339" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C339,Define!P:P))</f>
-        <v>指定のFeatureのParam2を増やす</v>
+        <v>指定のFeatureのParam1を増やす</v>
       </c>
       <c r="E339">
-        <v>14070</v>
+        <v>14060</v>
       </c>
       <c r="F339">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G339">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H339">
         <v>100</v>
@@ -38800,27 +38800,27 @@
     </row>
     <row r="340" spans="1:8">
       <c r="A340">
-        <v>414080</v>
+        <v>414070</v>
       </c>
       <c r="B340" t="str">
         <f>INDEX(TextData!B:B,MATCH(A340,TextData!A:A))</f>
-        <v>クイックヒール+</v>
+        <v>ホーミングクルセイド+</v>
       </c>
       <c r="C340">
-        <v>6010</v>
+        <v>6020</v>
       </c>
       <c r="D340" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C340,Define!P:P))</f>
-        <v>指定のFeatureのParam1を増やす</v>
+        <v>指定のFeatureのParam2を増やす</v>
       </c>
       <c r="E340">
-        <v>14080</v>
+        <v>14070</v>
       </c>
       <c r="F340">
         <v>0</v>
       </c>
       <c r="G340">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="H340">
         <v>100</v>
@@ -38828,27 +38828,27 @@
     </row>
     <row r="341" spans="1:8">
       <c r="A341">
-        <v>414090</v>
+        <v>414080</v>
       </c>
       <c r="B341" t="str">
         <f>INDEX(TextData!B:B,MATCH(A341,TextData!A:A))</f>
-        <v>リレイズ+</v>
+        <v>クイックヒール+</v>
       </c>
       <c r="C341">
-        <v>6080</v>
+        <v>6010</v>
       </c>
       <c r="D341" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C341,Define!P:P))</f>
-        <v>指定魔法のCTリセット値を変更する</v>
+        <v>指定のFeatureのParam1を増やす</v>
       </c>
       <c r="E341">
-        <v>14090</v>
+        <v>14080</v>
       </c>
       <c r="F341">
         <v>0</v>
       </c>
       <c r="G341">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="H341">
         <v>100</v>
@@ -38856,27 +38856,27 @@
     </row>
     <row r="342" spans="1:8">
       <c r="A342">
-        <v>415010</v>
+        <v>414090</v>
       </c>
       <c r="B342" t="str">
         <f>INDEX(TextData!B:B,MATCH(A342,TextData!A:A))</f>
-        <v>イーグルアイ+</v>
+        <v>リレイズ+</v>
       </c>
       <c r="C342">
-        <v>6030</v>
+        <v>6080</v>
       </c>
       <c r="D342" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C342,Define!P:P))</f>
-        <v>指定のFeatureのParam3を増やす</v>
+        <v>指定魔法のCTリセット値を変更する</v>
       </c>
       <c r="E342">
-        <v>15010</v>
+        <v>14090</v>
       </c>
       <c r="F342">
         <v>0</v>
       </c>
       <c r="G342">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="H342">
         <v>100</v>
@@ -38884,11 +38884,11 @@
     </row>
     <row r="343" spans="1:8">
       <c r="A343">
-        <v>415020</v>
+        <v>415010</v>
       </c>
       <c r="B343" t="str">
         <f>INDEX(TextData!B:B,MATCH(A343,TextData!A:A))</f>
-        <v>ネヴァーエンド+</v>
+        <v>イーグルアイ+</v>
       </c>
       <c r="C343">
         <v>6030</v>
@@ -38898,13 +38898,13 @@
         <v>指定のFeatureのParam3を増やす</v>
       </c>
       <c r="E343">
-        <v>15020</v>
+        <v>15010</v>
       </c>
       <c r="F343">
         <v>0</v>
       </c>
       <c r="G343">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="H343">
         <v>100</v>
@@ -38912,27 +38912,27 @@
     </row>
     <row r="344" spans="1:8">
       <c r="A344">
-        <v>415030</v>
+        <v>415020</v>
       </c>
       <c r="B344" t="str">
         <f>INDEX(TextData!B:B,MATCH(A344,TextData!A:A))</f>
-        <v>グレイブアクト+</v>
+        <v>ネヴァーエンド+</v>
       </c>
       <c r="C344">
-        <v>6010</v>
+        <v>6030</v>
       </c>
       <c r="D344" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C344,Define!P:P))</f>
-        <v>指定のFeatureのParam1を増やす</v>
+        <v>指定のFeatureのParam3を増やす</v>
       </c>
       <c r="E344">
-        <v>15030</v>
+        <v>15020</v>
       </c>
       <c r="F344">
         <v>0</v>
       </c>
       <c r="G344">
-        <v>2</v>
+        <v>50</v>
       </c>
       <c r="H344">
         <v>100</v>
@@ -38940,27 +38940,27 @@
     </row>
     <row r="345" spans="1:8">
       <c r="A345">
-        <v>415040</v>
+        <v>415030</v>
       </c>
       <c r="B345" t="str">
         <f>INDEX(TextData!B:B,MATCH(A345,TextData!A:A))</f>
-        <v>スカルグラッジ+</v>
+        <v>グレイブアクト+</v>
       </c>
       <c r="C345">
-        <v>6030</v>
+        <v>6010</v>
       </c>
       <c r="D345" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C345,Define!P:P))</f>
-        <v>指定のFeatureのParam3を増やす</v>
+        <v>指定のFeatureのParam1を増やす</v>
       </c>
       <c r="E345">
-        <v>15040</v>
+        <v>15030</v>
       </c>
       <c r="F345">
         <v>0</v>
       </c>
       <c r="G345">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="H345">
         <v>100</v>
@@ -38968,11 +38968,11 @@
     </row>
     <row r="346" spans="1:8">
       <c r="A346">
-        <v>415050</v>
+        <v>415040</v>
       </c>
       <c r="B346" t="str">
         <f>INDEX(TextData!B:B,MATCH(A346,TextData!A:A))</f>
-        <v>ネガティブドレイン+</v>
+        <v>スカルグラッジ+</v>
       </c>
       <c r="C346">
         <v>6030</v>
@@ -38982,13 +38982,13 @@
         <v>指定のFeatureのParam3を増やす</v>
       </c>
       <c r="E346">
-        <v>15050</v>
+        <v>15040</v>
       </c>
       <c r="F346">
         <v>0</v>
       </c>
       <c r="G346">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="H346">
         <v>100</v>
@@ -38996,11 +38996,11 @@
     </row>
     <row r="347" spans="1:8">
       <c r="A347">
-        <v>415060</v>
+        <v>415050</v>
       </c>
       <c r="B347" t="str">
         <f>INDEX(TextData!B:B,MATCH(A347,TextData!A:A))</f>
-        <v>アンデッドペイン+</v>
+        <v>ネガティブドレイン+</v>
       </c>
       <c r="C347">
         <v>6030</v>
@@ -39010,13 +39010,13 @@
         <v>指定のFeatureのParam3を増やす</v>
       </c>
       <c r="E347">
-        <v>15060</v>
+        <v>15050</v>
       </c>
       <c r="F347">
         <v>0</v>
       </c>
       <c r="G347">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="H347">
         <v>100</v>
@@ -39024,11 +39024,11 @@
     </row>
     <row r="348" spans="1:8">
       <c r="A348">
-        <v>415070</v>
+        <v>415060</v>
       </c>
       <c r="B348" t="str">
         <f>INDEX(TextData!B:B,MATCH(A348,TextData!A:A))</f>
-        <v>ジャックポッド+</v>
+        <v>アンデッドペイン+</v>
       </c>
       <c r="C348">
         <v>6030</v>
@@ -39038,13 +39038,13 @@
         <v>指定のFeatureのParam3を増やす</v>
       </c>
       <c r="E348">
-        <v>15070</v>
+        <v>15060</v>
       </c>
       <c r="F348">
         <v>0</v>
       </c>
       <c r="G348">
-        <v>75</v>
+        <v>15</v>
       </c>
       <c r="H348">
         <v>100</v>
@@ -39052,11 +39052,11 @@
     </row>
     <row r="349" spans="1:8">
       <c r="A349">
-        <v>415080</v>
+        <v>415070</v>
       </c>
       <c r="B349" t="str">
         <f>INDEX(TextData!B:B,MATCH(A349,TextData!A:A))</f>
-        <v>ヒールハント+</v>
+        <v>ジャックポッド+</v>
       </c>
       <c r="C349">
         <v>6030</v>
@@ -39066,13 +39066,13 @@
         <v>指定のFeatureのParam3を増やす</v>
       </c>
       <c r="E349">
-        <v>15080</v>
+        <v>15070</v>
       </c>
       <c r="F349">
         <v>0</v>
       </c>
       <c r="G349">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="H349">
         <v>100</v>
@@ -39080,11 +39080,11 @@
     </row>
     <row r="350" spans="1:8">
       <c r="A350">
-        <v>415090</v>
+        <v>415080</v>
       </c>
       <c r="B350" t="str">
         <f>INDEX(TextData!B:B,MATCH(A350,TextData!A:A))</f>
-        <v>クイックカース+</v>
+        <v>ヒールハント+</v>
       </c>
       <c r="C350">
         <v>6030</v>
@@ -39094,15 +39094,43 @@
         <v>指定のFeatureのParam3を増やす</v>
       </c>
       <c r="E350">
+        <v>15080</v>
+      </c>
+      <c r="F350">
+        <v>0</v>
+      </c>
+      <c r="G350">
+        <v>50</v>
+      </c>
+      <c r="H350">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="351" spans="1:8">
+      <c r="A351">
+        <v>415090</v>
+      </c>
+      <c r="B351" t="str">
+        <f>INDEX(TextData!B:B,MATCH(A351,TextData!A:A))</f>
+        <v>クイックカース+</v>
+      </c>
+      <c r="C351">
+        <v>6030</v>
+      </c>
+      <c r="D351" t="str">
+        <f>INDEX(Define!Q:Q,MATCH(C351,Define!P:P))</f>
+        <v>指定のFeatureのParam3を増やす</v>
+      </c>
+      <c r="E351">
         <v>15090</v>
       </c>
-      <c r="F350">
-        <v>0</v>
-      </c>
-      <c r="G350">
+      <c r="F351">
+        <v>0</v>
+      </c>
+      <c r="G351">
         <v>35</v>
       </c>
-      <c r="H350">
+      <c r="H351">
         <v>100</v>
       </c>
     </row>

--- a/Assets/Data/Skills.xlsx
+++ b/Assets/Data/Skills.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="7820" activeTab="1"/>
+    <workbookView windowWidth="19200" windowHeight="7820"/>
   </bookViews>
   <sheets>
     <sheet name="Skills" sheetId="1" r:id="rId1"/>
@@ -2643,10 +2643,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -2664,9 +2664,90 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -2681,66 +2762,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -2762,39 +2784,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -2805,6 +2797,14 @@
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -2829,7 +2829,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2841,7 +2889,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2859,7 +2919,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2871,7 +2985,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2883,133 +3009,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3020,6 +3020,26 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -3038,15 +3058,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FFB2B2B2"/>
       </left>
@@ -3058,15 +3069,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -3097,11 +3099,9 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -3128,145 +3128,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="18" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="18" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -14869,7 +14869,7 @@
         <v>0</v>
       </c>
       <c r="L106">
-        <v>330</v>
+        <v>320</v>
       </c>
       <c r="M106">
         <v>6</v>
@@ -14947,7 +14947,7 @@
         <v>0</v>
       </c>
       <c r="L107">
-        <v>330</v>
+        <v>320</v>
       </c>
       <c r="M107">
         <v>6</v>

--- a/Assets/Data/Skills.xlsx
+++ b/Assets/Data/Skills.xlsx
@@ -2643,10 +2643,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -2665,14 +2665,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -2680,7 +2680,29 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -2695,14 +2717,23 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -2717,37 +2748,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -2760,7 +2761,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -2769,7 +2769,7 @@
     </font>
     <font>
       <b/>
-      <sz val="15"/>
+      <sz val="18"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -2785,10 +2785,10 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <sz val="15"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -2802,7 +2802,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -2829,25 +2829,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2865,13 +2895,67 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2883,7 +2967,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2895,73 +2991,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2973,43 +3003,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3020,26 +3020,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -3054,6 +3034,36 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -3076,23 +3086,17 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -3106,17 +3110,13 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
       </top>
       <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -3128,145 +3128,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="22" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="17" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="18" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="18" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -13562,7 +13562,7 @@
         <v>0</v>
       </c>
       <c r="K90">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L90">
         <v>10</v>
@@ -13890,7 +13890,7 @@
         <v>0</v>
       </c>
       <c r="K94">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L94">
         <v>20</v>

--- a/Assets/Data/Skills.xlsx
+++ b/Assets/Data/Skills.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="7820"/>
+    <workbookView windowWidth="19200" windowHeight="7820" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="Skills" sheetId="1" r:id="rId1"/>
@@ -1264,7 +1264,7 @@
     <t>取引コマンドのコストを20%下げる</t>
   </si>
   <si>
-    <t>レイヴンバナー</t>
+    <t>ワタリガラスの旗</t>
   </si>
   <si>
     <t>(条件)バトル中
@@ -2643,9 +2643,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
@@ -2664,6 +2664,52 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -2678,9 +2724,24 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -2695,37 +2756,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -2739,28 +2770,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -2769,7 +2778,7 @@
     </font>
     <font>
       <b/>
-      <sz val="18"/>
+      <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -2785,24 +2794,15 @@
     </font>
     <font>
       <b/>
-      <sz val="15"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -2829,67 +2829,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2907,7 +2865,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2919,13 +2907,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2937,13 +2931,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2955,43 +2985,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3009,7 +3009,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3039,36 +3039,6 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
         <color rgb="FFB2B2B2"/>
       </left>
       <right style="thin">
@@ -3085,9 +3055,11 @@
     <border>
       <left/>
       <right/>
-      <top/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
       <bottom style="double">
-        <color rgb="FFFF8001"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -3110,13 +3082,41 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
       </top>
       <bottom style="double">
-        <color theme="4"/>
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -3128,16 +3128,16 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="14" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -3146,127 +3146,127 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="22" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="17" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -20395,7 +20395,7 @@
       </c>
       <c r="C174" t="str">
         <f>INDEX(TextData!B:B,MATCH(B174,TextData!A:A))</f>
-        <v>レイヴンバナー</v>
+        <v>ワタリガラスの旗</v>
       </c>
       <c r="D174">
         <v>6</v>
@@ -20473,7 +20473,7 @@
       </c>
       <c r="C175" t="str">
         <f>INDEX(TextData!B:B,MATCH(B175,TextData!A:A))</f>
-        <v>レイヴンバナー</v>
+        <v>ワタリガラスの旗</v>
       </c>
       <c r="D175">
         <v>6</v>
@@ -36096,7 +36096,7 @@
       </c>
       <c r="B244" t="str">
         <f>INDEX(TextData!B:B,MATCH(A244,TextData!A:A))</f>
-        <v>レイヴンバナー</v>
+        <v>ワタリガラスの旗</v>
       </c>
       <c r="C244">
         <v>6310</v>
@@ -36124,7 +36124,7 @@
       </c>
       <c r="B245" t="str">
         <f>INDEX(TextData!B:B,MATCH(A245,TextData!A:A))</f>
-        <v>レイヴンバナー</v>
+        <v>ワタリガラスの旗</v>
       </c>
       <c r="C245">
         <v>3010</v>
@@ -42682,7 +42682,7 @@
       </c>
       <c r="B127" t="str">
         <f>INDEX(TextData!B:B,MATCH(A127,TextData!A:A))</f>
-        <v>レイヴンバナー</v>
+        <v>ワタリガラスの旗</v>
       </c>
       <c r="C127">
         <v>0</v>

--- a/Assets/Data/Skills.xlsx
+++ b/Assets/Data/Skills.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="7820" activeTab="4"/>
+    <workbookView windowWidth="19200" windowHeight="7820" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Skills" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="919" uniqueCount="802">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="920" uniqueCount="803">
   <si>
     <t>Id</t>
   </si>
@@ -312,7 +312,7 @@
     <t>ヒーリング</t>
   </si>
   <si>
-    <t>(制限)バトル中5回まで
+    <t>(制限)バトル中3回まで
 敵味方一人のHpを/f[f,0,1]回復
 アンデッドには2倍のダメージ</t>
   </si>
@@ -2465,6 +2465,9 @@
   </si>
   <si>
     <t>バトル中使用回数が〇以下</t>
+  </si>
+  <si>
+    <t>Period中使用回数が〇以下</t>
   </si>
   <si>
     <t>ターン中使用回数が〇回に満たない</t>
@@ -2643,8 +2646,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
@@ -2664,30 +2667,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -2696,24 +2675,10 @@
     </font>
     <font>
       <b/>
-      <sz val="15"/>
+      <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -2725,7 +2690,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -2733,30 +2705,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -2771,14 +2720,51 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="13"/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -2794,6 +2780,22 @@
     </font>
     <font>
       <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -2801,10 +2803,11 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -2829,7 +2832,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2841,49 +2850,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2901,19 +2904,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2925,7 +2928,73 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2937,79 +3006,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3023,17 +3026,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -3055,29 +3052,24 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
+      <top/>
       <bottom style="double">
-        <color theme="4"/>
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -3099,9 +3091,11 @@
     <border>
       <left/>
       <right/>
-      <top/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
       <bottom style="double">
-        <color rgb="FFFF8001"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -3120,6 +3114,15 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -3128,7 +3131,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -3137,7 +3140,7 @@
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -3146,127 +3149,127 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -32742,10 +32745,10 @@
         <v>獲得Eｘｐ％アップ</v>
       </c>
       <c r="E130">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F130">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="G130">
         <v>0</v>
@@ -39251,7 +39254,7 @@
         <v>0</v>
       </c>
       <c r="F4">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -46910,7 +46913,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AC138"/>
+  <dimension ref="A1:AC139"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13"/>
   <cols>
     <col min="3" max="3" width="1.72727272727273" customWidth="1"/>
@@ -48567,7 +48570,7 @@
     </row>
     <row r="82" spans="21:22">
       <c r="U82">
-        <v>11020</v>
+        <v>11011</v>
       </c>
       <c r="V82" t="s">
         <v>745</v>
@@ -48575,7 +48578,7 @@
     </row>
     <row r="83" spans="21:22">
       <c r="U83">
-        <v>12030</v>
+        <v>11020</v>
       </c>
       <c r="V83" t="s">
         <v>746</v>
@@ -48583,7 +48586,7 @@
     </row>
     <row r="84" spans="21:22">
       <c r="U84">
-        <v>12040</v>
+        <v>12030</v>
       </c>
       <c r="V84" t="s">
         <v>747</v>
@@ -48591,7 +48594,7 @@
     </row>
     <row r="85" spans="21:22">
       <c r="U85">
-        <v>12041</v>
+        <v>12040</v>
       </c>
       <c r="V85" t="s">
         <v>748</v>
@@ -48599,7 +48602,7 @@
     </row>
     <row r="86" spans="21:22">
       <c r="U86">
-        <v>12042</v>
+        <v>12041</v>
       </c>
       <c r="V86" t="s">
         <v>749</v>
@@ -48607,7 +48610,7 @@
     </row>
     <row r="87" spans="21:22">
       <c r="U87">
-        <v>12043</v>
+        <v>12042</v>
       </c>
       <c r="V87" t="s">
         <v>750</v>
@@ -48615,7 +48618,7 @@
     </row>
     <row r="88" spans="21:22">
       <c r="U88">
-        <v>12050</v>
+        <v>12043</v>
       </c>
       <c r="V88" t="s">
         <v>751</v>
@@ -48623,7 +48626,7 @@
     </row>
     <row r="89" spans="21:22">
       <c r="U89">
-        <v>12060</v>
+        <v>12050</v>
       </c>
       <c r="V89" t="s">
         <v>752</v>
@@ -48631,7 +48634,7 @@
     </row>
     <row r="90" spans="21:22">
       <c r="U90">
-        <v>12063</v>
+        <v>12060</v>
       </c>
       <c r="V90" t="s">
         <v>753</v>
@@ -48639,7 +48642,7 @@
     </row>
     <row r="91" spans="21:22">
       <c r="U91">
-        <v>12064</v>
+        <v>12063</v>
       </c>
       <c r="V91" t="s">
         <v>754</v>
@@ -48647,7 +48650,7 @@
     </row>
     <row r="92" spans="21:22">
       <c r="U92">
-        <v>12066</v>
+        <v>12064</v>
       </c>
       <c r="V92" t="s">
         <v>755</v>
@@ -48655,7 +48658,7 @@
     </row>
     <row r="93" spans="21:22">
       <c r="U93">
-        <v>12070</v>
+        <v>12066</v>
       </c>
       <c r="V93" t="s">
         <v>756</v>
@@ -48663,7 +48666,7 @@
     </row>
     <row r="94" spans="21:22">
       <c r="U94">
-        <v>12071</v>
+        <v>12070</v>
       </c>
       <c r="V94" t="s">
         <v>757</v>
@@ -48671,7 +48674,7 @@
     </row>
     <row r="95" spans="21:22">
       <c r="U95">
-        <v>12082</v>
+        <v>12071</v>
       </c>
       <c r="V95" t="s">
         <v>758</v>
@@ -48679,7 +48682,7 @@
     </row>
     <row r="96" spans="21:22">
       <c r="U96">
-        <v>12092</v>
+        <v>12082</v>
       </c>
       <c r="V96" t="s">
         <v>759</v>
@@ -48687,7 +48690,7 @@
     </row>
     <row r="97" spans="21:22">
       <c r="U97">
-        <v>13010</v>
+        <v>12092</v>
       </c>
       <c r="V97" t="s">
         <v>760</v>
@@ -48695,7 +48698,7 @@
     </row>
     <row r="98" spans="21:22">
       <c r="U98">
-        <v>13020</v>
+        <v>13010</v>
       </c>
       <c r="V98" t="s">
         <v>761</v>
@@ -48703,7 +48706,7 @@
     </row>
     <row r="99" spans="21:22">
       <c r="U99">
-        <v>14010</v>
+        <v>13020</v>
       </c>
       <c r="V99" t="s">
         <v>762</v>
@@ -48711,7 +48714,7 @@
     </row>
     <row r="100" spans="21:22">
       <c r="U100">
-        <v>14110</v>
+        <v>14010</v>
       </c>
       <c r="V100" t="s">
         <v>763</v>
@@ -48719,7 +48722,7 @@
     </row>
     <row r="101" spans="21:22">
       <c r="U101">
-        <v>14210</v>
+        <v>14110</v>
       </c>
       <c r="V101" t="s">
         <v>764</v>
@@ -48727,7 +48730,7 @@
     </row>
     <row r="102" spans="21:22">
       <c r="U102">
-        <v>14310</v>
+        <v>14210</v>
       </c>
       <c r="V102" t="s">
         <v>765</v>
@@ -48735,7 +48738,7 @@
     </row>
     <row r="103" spans="21:22">
       <c r="U103">
-        <v>14410</v>
+        <v>14310</v>
       </c>
       <c r="V103" t="s">
         <v>766</v>
@@ -48743,7 +48746,7 @@
     </row>
     <row r="104" spans="21:22">
       <c r="U104">
-        <v>14420</v>
+        <v>14410</v>
       </c>
       <c r="V104" t="s">
         <v>767</v>
@@ -48751,7 +48754,7 @@
     </row>
     <row r="105" spans="21:22">
       <c r="U105">
-        <v>14520</v>
+        <v>14420</v>
       </c>
       <c r="V105" t="s">
         <v>768</v>
@@ -48759,7 +48762,7 @@
     </row>
     <row r="106" spans="21:22">
       <c r="U106">
-        <v>15010</v>
+        <v>14520</v>
       </c>
       <c r="V106" t="s">
         <v>769</v>
@@ -48767,7 +48770,7 @@
     </row>
     <row r="107" spans="21:22">
       <c r="U107">
-        <v>15011</v>
+        <v>15010</v>
       </c>
       <c r="V107" t="s">
         <v>770</v>
@@ -48775,7 +48778,7 @@
     </row>
     <row r="108" spans="21:22">
       <c r="U108">
-        <v>15022</v>
+        <v>15011</v>
       </c>
       <c r="V108" t="s">
         <v>771</v>
@@ -48783,7 +48786,7 @@
     </row>
     <row r="109" spans="21:22">
       <c r="U109">
-        <v>16010</v>
+        <v>15022</v>
       </c>
       <c r="V109" t="s">
         <v>772</v>
@@ -48791,7 +48794,7 @@
     </row>
     <row r="110" spans="21:22">
       <c r="U110">
-        <v>17010</v>
+        <v>16010</v>
       </c>
       <c r="V110" t="s">
         <v>773</v>
@@ -48799,7 +48802,7 @@
     </row>
     <row r="111" spans="21:22">
       <c r="U111">
-        <v>17020</v>
+        <v>17010</v>
       </c>
       <c r="V111" t="s">
         <v>774</v>
@@ -48807,7 +48810,7 @@
     </row>
     <row r="112" spans="21:22">
       <c r="U112">
-        <v>17030</v>
+        <v>17020</v>
       </c>
       <c r="V112" t="s">
         <v>775</v>
@@ -48815,7 +48818,7 @@
     </row>
     <row r="113" spans="21:22">
       <c r="U113">
-        <v>17040</v>
+        <v>17030</v>
       </c>
       <c r="V113" t="s">
         <v>776</v>
@@ -48823,7 +48826,7 @@
     </row>
     <row r="114" spans="21:22">
       <c r="U114">
-        <v>17050</v>
+        <v>17040</v>
       </c>
       <c r="V114" t="s">
         <v>777</v>
@@ -48831,7 +48834,7 @@
     </row>
     <row r="115" spans="21:22">
       <c r="U115">
-        <v>17060</v>
+        <v>17050</v>
       </c>
       <c r="V115" t="s">
         <v>778</v>
@@ -48839,7 +48842,7 @@
     </row>
     <row r="116" spans="21:22">
       <c r="U116">
-        <v>18010</v>
+        <v>17060</v>
       </c>
       <c r="V116" t="s">
         <v>779</v>
@@ -48847,7 +48850,7 @@
     </row>
     <row r="117" spans="21:22">
       <c r="U117">
-        <v>18020</v>
+        <v>18010</v>
       </c>
       <c r="V117" t="s">
         <v>780</v>
@@ -48855,7 +48858,7 @@
     </row>
     <row r="118" spans="21:22">
       <c r="U118">
-        <v>19010</v>
+        <v>18020</v>
       </c>
       <c r="V118" t="s">
         <v>781</v>
@@ -48863,7 +48866,7 @@
     </row>
     <row r="119" spans="21:22">
       <c r="U119">
-        <v>19020</v>
+        <v>19010</v>
       </c>
       <c r="V119" t="s">
         <v>782</v>
@@ -48871,7 +48874,7 @@
     </row>
     <row r="120" spans="21:22">
       <c r="U120">
-        <v>19030</v>
+        <v>19020</v>
       </c>
       <c r="V120" t="s">
         <v>783</v>
@@ -48879,7 +48882,7 @@
     </row>
     <row r="121" spans="21:22">
       <c r="U121">
-        <v>20030</v>
+        <v>19030</v>
       </c>
       <c r="V121" t="s">
         <v>784</v>
@@ -48887,7 +48890,7 @@
     </row>
     <row r="122" spans="21:22">
       <c r="U122">
-        <v>20040</v>
+        <v>20030</v>
       </c>
       <c r="V122" t="s">
         <v>785</v>
@@ -48895,7 +48898,7 @@
     </row>
     <row r="123" spans="21:22">
       <c r="U123">
-        <v>20050</v>
+        <v>20040</v>
       </c>
       <c r="V123" t="s">
         <v>786</v>
@@ -48903,7 +48906,7 @@
     </row>
     <row r="124" spans="21:22">
       <c r="U124">
-        <v>20070</v>
+        <v>20050</v>
       </c>
       <c r="V124" t="s">
         <v>787</v>
@@ -48911,7 +48914,7 @@
     </row>
     <row r="125" spans="21:22">
       <c r="U125">
-        <v>20071</v>
+        <v>20070</v>
       </c>
       <c r="V125" t="s">
         <v>788</v>
@@ -48919,7 +48922,7 @@
     </row>
     <row r="126" spans="21:22">
       <c r="U126">
-        <v>20110</v>
+        <v>20071</v>
       </c>
       <c r="V126" t="s">
         <v>789</v>
@@ -48927,7 +48930,7 @@
     </row>
     <row r="127" spans="21:22">
       <c r="U127">
-        <v>20120</v>
+        <v>20110</v>
       </c>
       <c r="V127" t="s">
         <v>790</v>
@@ -48935,7 +48938,7 @@
     </row>
     <row r="128" spans="21:22">
       <c r="U128">
-        <v>20130</v>
+        <v>20120</v>
       </c>
       <c r="V128" t="s">
         <v>791</v>
@@ -48943,7 +48946,7 @@
     </row>
     <row r="129" spans="21:22">
       <c r="U129">
-        <v>20140</v>
+        <v>20130</v>
       </c>
       <c r="V129" t="s">
         <v>792</v>
@@ -48951,7 +48954,7 @@
     </row>
     <row r="130" spans="21:22">
       <c r="U130">
-        <v>20150</v>
+        <v>20140</v>
       </c>
       <c r="V130" t="s">
         <v>793</v>
@@ -48959,7 +48962,7 @@
     </row>
     <row r="131" spans="21:22">
       <c r="U131">
-        <v>20160</v>
+        <v>20150</v>
       </c>
       <c r="V131" t="s">
         <v>794</v>
@@ -48967,7 +48970,7 @@
     </row>
     <row r="132" spans="21:22">
       <c r="U132">
-        <v>23010</v>
+        <v>20160</v>
       </c>
       <c r="V132" t="s">
         <v>795</v>
@@ -48975,7 +48978,7 @@
     </row>
     <row r="133" spans="21:22">
       <c r="U133">
-        <v>24010</v>
+        <v>23010</v>
       </c>
       <c r="V133" t="s">
         <v>796</v>
@@ -48983,7 +48986,7 @@
     </row>
     <row r="134" spans="21:22">
       <c r="U134">
-        <v>30010</v>
+        <v>24010</v>
       </c>
       <c r="V134" t="s">
         <v>797</v>
@@ -48991,7 +48994,7 @@
     </row>
     <row r="135" spans="21:22">
       <c r="U135">
-        <v>30020</v>
+        <v>30010</v>
       </c>
       <c r="V135" t="s">
         <v>798</v>
@@ -48999,7 +49002,7 @@
     </row>
     <row r="136" spans="21:22">
       <c r="U136">
-        <v>40010</v>
+        <v>30020</v>
       </c>
       <c r="V136" t="s">
         <v>799</v>
@@ -49007,7 +49010,7 @@
     </row>
     <row r="137" spans="21:22">
       <c r="U137">
-        <v>40020</v>
+        <v>40010</v>
       </c>
       <c r="V137" t="s">
         <v>800</v>
@@ -49015,10 +49018,18 @@
     </row>
     <row r="138" spans="21:22">
       <c r="U138">
-        <v>40030</v>
+        <v>40020</v>
       </c>
       <c r="V138" t="s">
         <v>801</v>
+      </c>
+    </row>
+    <row r="139" spans="21:22">
+      <c r="U139">
+        <v>40030</v>
+      </c>
+      <c r="V139" t="s">
+        <v>802</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Data/Skills.xlsx
+++ b/Assets/Data/Skills.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="7820" activeTab="1"/>
+    <workbookView windowWidth="19200" windowHeight="7820" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="Skills" sheetId="1" r:id="rId1"/>
@@ -312,7 +312,7 @@
     <t>ヒーリング</t>
   </si>
   <si>
-    <t>(制限)バトル中3回まで
+    <t>(制限)バトル中1回まで
 敵味方一人のHpを/f[f,0,1]回復
 アンデッドには2倍のダメージ</t>
   </si>
@@ -2646,10 +2646,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -2664,6 +2664,50 @@
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -2682,30 +2726,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -2720,37 +2743,22 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -2765,22 +2773,30 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="18"/>
+      <sz val="11"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -2792,22 +2808,6 @@
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -2832,7 +2832,175 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2844,175 +3012,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3023,6 +3023,36 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -3060,21 +3090,6 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
       <right style="thin">
@@ -3091,35 +3106,20 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -3131,145 +3131,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="21" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -39254,7 +39254,7 @@
         <v>0</v>
       </c>
       <c r="F4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G4">
         <v>0</v>

--- a/Assets/Data/Skills.xlsx
+++ b/Assets/Data/Skills.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="7820" activeTab="4"/>
+    <workbookView windowWidth="19200" windowHeight="7820"/>
   </bookViews>
   <sheets>
     <sheet name="Skills" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="928" uniqueCount="808">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="931" uniqueCount="811">
   <si>
     <t>Id</t>
   </si>
@@ -2049,7 +2049,7 @@
     <t>その他</t>
   </si>
   <si>
-    <t>相手の行動前</t>
+    <t>相手の行動前・対象決定前</t>
   </si>
   <si>
     <t>命令不可</t>
@@ -2091,30 +2091,33 @@
     <t>自身のMpが〇以上</t>
   </si>
   <si>
+    <t>相手の行動前・対象決定後</t>
+  </si>
+  <si>
+    <t>魔法入手</t>
+  </si>
+  <si>
+    <t>自身のHpを1にする</t>
+  </si>
+  <si>
+    <t>Mp〇未満の味方</t>
+  </si>
+  <si>
     <t>ターン開始前</t>
   </si>
   <si>
-    <t>魔法入手</t>
-  </si>
-  <si>
-    <t>自身のHpを1にする</t>
-  </si>
-  <si>
-    <t>Mp〇未満の味方</t>
+    <t>最大HpとMpアップ</t>
+  </si>
+  <si>
+    <t>対象のHpを1にする</t>
+  </si>
+  <si>
+    <t>Mp〇以上の味方</t>
   </si>
   <si>
     <t>ターン開始後</t>
   </si>
   <si>
-    <t>最大HpとMpアップ</t>
-  </si>
-  <si>
-    <t>対象のHpを1にする</t>
-  </si>
-  <si>
-    <t>Mp〇以上の味方</t>
-  </si>
-  <si>
     <t>ターン数アップ</t>
   </si>
   <si>
@@ -2488,6 +2491,12 @@
   </si>
   <si>
     <t>ターン中使用回数が〇回に満たない</t>
+  </si>
+  <si>
+    <t>かばうが成立する</t>
+  </si>
+  <si>
+    <t>かばう成立後かばった対象</t>
   </si>
   <si>
     <t>行動Magicの消費Mpが〇</t>
@@ -2663,9 +2672,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
@@ -2699,37 +2708,15 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -2743,32 +2730,15 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -2789,9 +2759,33 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -2802,13 +2796,6 @@
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -2823,6 +2810,28 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -2849,7 +2858,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2861,13 +2876,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2879,13 +2900,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2897,19 +2918,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2927,13 +2942,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2945,19 +2984,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2975,7 +3008,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2987,49 +3038,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3058,15 +3067,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FFB2B2B2"/>
       </left>
@@ -3078,17 +3078,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -3121,6 +3110,15 @@
       <right/>
       <top/>
       <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
         <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
@@ -3140,6 +3138,17 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -3148,145 +3157,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="22" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="22" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="24" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="10" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -13336,7 +13345,7 @@
         <v>0</v>
       </c>
       <c r="K87">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L87">
         <v>20</v>
@@ -13356,18 +13365,18 @@
         <v>パッシブ</v>
       </c>
       <c r="Q87">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R87" t="str">
         <f>INDEX(Define!K:K,MATCH(Q87,Define!J:J))</f>
-        <v>自身</v>
+        <v>味方</v>
       </c>
       <c r="S87">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="T87" t="str">
         <f>INDEX(Define!N:N,MATCH(S87,Define!M:M))</f>
-        <v>自身</v>
+        <v>単体・自身を除く</v>
       </c>
       <c r="U87">
         <v>1</v>
@@ -13418,7 +13427,7 @@
         <v>0</v>
       </c>
       <c r="K88">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L88">
         <v>0</v>
@@ -39749,7 +39758,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H152"/>
+  <dimension ref="A1:H153"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="7"/>
   <cols>
     <col min="2" max="2" width="19.7272727272727" customWidth="1"/>
@@ -40827,11 +40836,11 @@
         <v>ルミナスカバー</v>
       </c>
       <c r="C39">
-        <v>12060</v>
+        <v>12010</v>
       </c>
       <c r="D39" t="str">
         <f>INDEX(Define!V:V,MATCH(C39,Define!U:U))</f>
-        <v>味方が攻撃を受ける。Param2で対象指定</v>
+        <v>かばうが成立する</v>
       </c>
       <c r="E39">
         <v>41</v>
@@ -40848,21 +40857,21 @@
     </row>
     <row r="40" spans="1:8">
       <c r="A40">
-        <v>14010</v>
+        <v>13101</v>
       </c>
       <c r="B40" t="str">
         <f>INDEX(TextData!B:B,MATCH(A40,TextData!A:A))</f>
-        <v>ディバインシールド</v>
+        <v>ルミナスカバー</v>
       </c>
       <c r="C40">
-        <v>0</v>
+        <v>12011</v>
       </c>
       <c r="D40" t="str">
         <f>INDEX(Define!V:V,MATCH(C40,Define!U:U))</f>
-        <v>なし</v>
+        <v>かばう成立後かばった対象</v>
       </c>
       <c r="E40">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F40">
         <v>0</v>
@@ -40876,30 +40885,30 @@
     </row>
     <row r="41" spans="1:8">
       <c r="A41">
-        <v>14020</v>
+        <v>14010</v>
       </c>
       <c r="B41" t="str">
         <f>INDEX(TextData!B:B,MATCH(A41,TextData!A:A))</f>
-        <v>ライフディバイド</v>
+        <v>ディバインシールド</v>
       </c>
       <c r="C41">
-        <v>12040</v>
+        <v>0</v>
       </c>
       <c r="D41" t="str">
         <f>INDEX(Define!V:V,MATCH(C41,Define!U:U))</f>
-        <v>攻撃を受けた対象のHpがParam1%以下 Param2==1で生存判定しない</v>
+        <v>なし</v>
       </c>
       <c r="E41">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F41">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G41">
         <v>0</v>
       </c>
       <c r="H41">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:8">
@@ -40911,17 +40920,17 @@
         <v>ライフディバイド</v>
       </c>
       <c r="C42">
-        <v>1020</v>
+        <v>12040</v>
       </c>
       <c r="D42" t="str">
         <f>INDEX(Define!V:V,MATCH(C42,Define!U:U))</f>
-        <v>自身のHpが〇%以上</v>
+        <v>攻撃を受けた対象のHpがParam1%以下 Param2==1で生存判定しない</v>
       </c>
       <c r="E42">
         <v>11</v>
       </c>
       <c r="F42">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="G42">
         <v>0</v>
@@ -40939,42 +40948,42 @@
         <v>ライフディバイド</v>
       </c>
       <c r="C43">
-        <v>9120</v>
+        <v>1020</v>
       </c>
       <c r="D43" t="str">
         <f>INDEX(Define!V:V,MATCH(C43,Define!U:U))</f>
-        <v>自身を対象にしない</v>
+        <v>自身のHpが〇%以上</v>
       </c>
       <c r="E43">
         <v>11</v>
       </c>
       <c r="F43">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="G43">
         <v>0</v>
       </c>
       <c r="H43">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44" spans="1:8">
       <c r="A44">
-        <v>14030</v>
+        <v>14020</v>
       </c>
       <c r="B44" t="str">
         <f>INDEX(TextData!B:B,MATCH(A44,TextData!A:A))</f>
-        <v>エイミングスコープ</v>
+        <v>ライフディバイド</v>
       </c>
       <c r="C44">
-        <v>0</v>
+        <v>9120</v>
       </c>
       <c r="D44" t="str">
         <f>INDEX(Define!V:V,MATCH(C44,Define!U:U))</f>
-        <v>なし</v>
+        <v>自身を対象にしない</v>
       </c>
       <c r="E44">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F44">
         <v>0</v>
@@ -40988,11 +40997,11 @@
     </row>
     <row r="45" spans="1:8">
       <c r="A45">
-        <v>14040</v>
+        <v>14030</v>
       </c>
       <c r="B45" t="str">
         <f>INDEX(TextData!B:B,MATCH(A45,TextData!A:A))</f>
-        <v>リジェネレーション</v>
+        <v>エイミングスコープ</v>
       </c>
       <c r="C45">
         <v>0</v>
@@ -41016,11 +41025,11 @@
     </row>
     <row r="46" spans="1:8">
       <c r="A46">
-        <v>14050</v>
+        <v>14040</v>
       </c>
       <c r="B46" t="str">
         <f>INDEX(TextData!B:B,MATCH(A46,TextData!A:A))</f>
-        <v>ホープフルアイリス</v>
+        <v>リジェネレーション</v>
       </c>
       <c r="C46">
         <v>0</v>
@@ -41044,21 +41053,21 @@
     </row>
     <row r="47" spans="1:8">
       <c r="A47">
-        <v>14060</v>
+        <v>14050</v>
       </c>
       <c r="B47" t="str">
         <f>INDEX(TextData!B:B,MATCH(A47,TextData!A:A))</f>
-        <v>パッシブサプライ</v>
+        <v>ホープフルアイリス</v>
       </c>
       <c r="C47">
-        <v>12066</v>
+        <v>0</v>
       </c>
       <c r="D47" t="str">
         <f>INDEX(Define!V:V,MATCH(C47,Define!U:U))</f>
-        <v>自身がパッシブを受ける</v>
+        <v>なし</v>
       </c>
       <c r="E47">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F47">
         <v>0</v>
@@ -41067,7 +41076,7 @@
         <v>0</v>
       </c>
       <c r="H47">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48" spans="1:8">
@@ -41079,45 +41088,45 @@
         <v>パッシブサプライ</v>
       </c>
       <c r="C48">
-        <v>11020</v>
+        <v>12066</v>
       </c>
       <c r="D48" t="str">
         <f>INDEX(Define!V:V,MATCH(C48,Define!U:U))</f>
-        <v>ターン中使用回数が〇回に満たない</v>
+        <v>自身がパッシブを受ける</v>
       </c>
       <c r="E48">
         <v>2</v>
       </c>
       <c r="F48">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G48">
         <v>0</v>
       </c>
       <c r="H48">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49" spans="1:8">
       <c r="A49">
-        <v>14070</v>
+        <v>14060</v>
       </c>
       <c r="B49" t="str">
         <f>INDEX(TextData!B:B,MATCH(A49,TextData!A:A))</f>
-        <v>ホーミングクルセイド</v>
+        <v>パッシブサプライ</v>
       </c>
       <c r="C49">
-        <v>0</v>
+        <v>11020</v>
       </c>
       <c r="D49" t="str">
         <f>INDEX(Define!V:V,MATCH(C49,Define!U:U))</f>
-        <v>なし</v>
+        <v>ターン中使用回数が〇回に満たない</v>
       </c>
       <c r="E49">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F49">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G49">
         <v>0</v>
@@ -41128,30 +41137,30 @@
     </row>
     <row r="50" spans="1:8">
       <c r="A50">
-        <v>14080</v>
+        <v>14070</v>
       </c>
       <c r="B50" t="str">
         <f>INDEX(TextData!B:B,MATCH(A50,TextData!A:A))</f>
-        <v>クイックヒール</v>
+        <v>ホーミングクルセイド</v>
       </c>
       <c r="C50">
-        <v>12040</v>
+        <v>0</v>
       </c>
       <c r="D50" t="str">
         <f>INDEX(Define!V:V,MATCH(C50,Define!U:U))</f>
-        <v>攻撃を受けた対象のHpがParam1%以下 Param2==1で生存判定しない</v>
+        <v>なし</v>
       </c>
       <c r="E50">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F50">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G50">
         <v>0</v>
       </c>
       <c r="H50">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51" spans="1:8">
@@ -41163,42 +41172,42 @@
         <v>クイックヒール</v>
       </c>
       <c r="C51">
-        <v>18010</v>
+        <v>12040</v>
       </c>
       <c r="D51" t="str">
         <f>INDEX(Define!V:V,MATCH(C51,Define!U:U))</f>
-        <v>自分の味方である</v>
+        <v>攻撃を受けた対象のHpがParam1%以下 Param2==1で生存判定しない</v>
       </c>
       <c r="E51">
         <v>11</v>
       </c>
       <c r="F51">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G51">
         <v>0</v>
       </c>
       <c r="H51">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="52" spans="1:8">
       <c r="A52">
-        <v>14090</v>
+        <v>14080</v>
       </c>
       <c r="B52" t="str">
         <f>INDEX(TextData!B:B,MATCH(A52,TextData!A:A))</f>
-        <v>リレイズ</v>
+        <v>クイックヒール</v>
       </c>
       <c r="C52">
-        <v>20050</v>
+        <v>18010</v>
       </c>
       <c r="D52" t="str">
         <f>INDEX(Define!V:V,MATCH(C52,Define!U:U))</f>
-        <v>自身が戦闘不能になる</v>
+        <v>自分の味方である</v>
       </c>
       <c r="E52">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="F52">
         <v>0</v>
@@ -41212,21 +41221,21 @@
     </row>
     <row r="53" spans="1:8">
       <c r="A53">
-        <v>15010</v>
+        <v>14090</v>
       </c>
       <c r="B53" t="str">
         <f>INDEX(TextData!B:B,MATCH(A53,TextData!A:A))</f>
-        <v>イーグルアイ</v>
+        <v>リレイズ</v>
       </c>
       <c r="C53">
-        <v>0</v>
+        <v>20050</v>
       </c>
       <c r="D53" t="str">
         <f>INDEX(Define!V:V,MATCH(C53,Define!U:U))</f>
-        <v>なし</v>
+        <v>自身が戦闘不能になる</v>
       </c>
       <c r="E53">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F53">
         <v>0</v>
@@ -41240,24 +41249,24 @@
     </row>
     <row r="54" spans="1:8">
       <c r="A54">
-        <v>15020</v>
+        <v>15010</v>
       </c>
       <c r="B54" t="str">
         <f>INDEX(TextData!B:B,MATCH(A54,TextData!A:A))</f>
-        <v>ネヴァーエンド</v>
+        <v>イーグルアイ</v>
       </c>
       <c r="C54">
-        <v>1010</v>
+        <v>0</v>
       </c>
       <c r="D54" t="str">
         <f>INDEX(Define!V:V,MATCH(C54,Define!U:U))</f>
-        <v>自身のHpが〇%以下</v>
+        <v>なし</v>
       </c>
       <c r="E54">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F54">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="G54">
         <v>0</v>
@@ -41268,24 +41277,24 @@
     </row>
     <row r="55" spans="1:8">
       <c r="A55">
-        <v>15030</v>
+        <v>15020</v>
       </c>
       <c r="B55" t="str">
         <f>INDEX(TextData!B:B,MATCH(A55,TextData!A:A))</f>
-        <v>グレイブアクト</v>
+        <v>ネヴァーエンド</v>
       </c>
       <c r="C55">
-        <v>12041</v>
+        <v>1010</v>
       </c>
       <c r="D55" t="str">
         <f>INDEX(Define!V:V,MATCH(C55,Define!U:U))</f>
-        <v>攻撃を受けた対象が戦闘不能になった</v>
+        <v>自身のHpが〇%以下</v>
       </c>
       <c r="E55">
         <v>2</v>
       </c>
       <c r="F55">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="G55">
         <v>0</v>
@@ -41296,24 +41305,24 @@
     </row>
     <row r="56" spans="1:8">
       <c r="A56">
-        <v>15040</v>
+        <v>15030</v>
       </c>
       <c r="B56" t="str">
         <f>INDEX(TextData!B:B,MATCH(A56,TextData!A:A))</f>
-        <v>スカルグラッジ</v>
+        <v>グレイブアクト</v>
       </c>
       <c r="C56">
-        <v>1020</v>
+        <v>12041</v>
       </c>
       <c r="D56" t="str">
         <f>INDEX(Define!V:V,MATCH(C56,Define!U:U))</f>
-        <v>自身のHpが〇%以上</v>
+        <v>攻撃を受けた対象が戦闘不能になった</v>
       </c>
       <c r="E56">
         <v>2</v>
       </c>
       <c r="F56">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G56">
         <v>0</v>
@@ -41324,24 +41333,24 @@
     </row>
     <row r="57" spans="1:8">
       <c r="A57">
-        <v>15050</v>
+        <v>15040</v>
       </c>
       <c r="B57" t="str">
         <f>INDEX(TextData!B:B,MATCH(A57,TextData!A:A))</f>
-        <v>ネガティブドレイン</v>
+        <v>スカルグラッジ</v>
       </c>
       <c r="C57">
-        <v>1010</v>
+        <v>1020</v>
       </c>
       <c r="D57" t="str">
         <f>INDEX(Define!V:V,MATCH(C57,Define!U:U))</f>
-        <v>自身のHpが〇%以下</v>
+        <v>自身のHpが〇%以上</v>
       </c>
       <c r="E57">
         <v>2</v>
       </c>
       <c r="F57">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="G57">
         <v>0</v>
@@ -41352,24 +41361,24 @@
     </row>
     <row r="58" spans="1:8">
       <c r="A58">
-        <v>15060</v>
+        <v>15050</v>
       </c>
       <c r="B58" t="str">
         <f>INDEX(TextData!B:B,MATCH(A58,TextData!A:A))</f>
-        <v>アンデッドペイン</v>
+        <v>ネガティブドレイン</v>
       </c>
       <c r="C58">
-        <v>0</v>
+        <v>1010</v>
       </c>
       <c r="D58" t="str">
         <f>INDEX(Define!V:V,MATCH(C58,Define!U:U))</f>
-        <v>なし</v>
+        <v>自身のHpが〇%以下</v>
       </c>
       <c r="E58">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F58">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="G58">
         <v>0</v>
@@ -41380,21 +41389,21 @@
     </row>
     <row r="59" spans="1:8">
       <c r="A59">
-        <v>15070</v>
+        <v>15060</v>
       </c>
       <c r="B59" t="str">
         <f>INDEX(TextData!B:B,MATCH(A59,TextData!A:A))</f>
-        <v>ジャックポッド</v>
+        <v>アンデッドペイン</v>
       </c>
       <c r="C59">
-        <v>15011</v>
+        <v>0</v>
       </c>
       <c r="D59" t="str">
         <f>INDEX(Define!V:V,MATCH(C59,Define!U:U))</f>
-        <v>味方が攻撃タイプの行動をしようとしている</v>
+        <v>なし</v>
       </c>
       <c r="E59">
-        <v>33</v>
+        <v>4</v>
       </c>
       <c r="F59">
         <v>0</v>
@@ -41408,21 +41417,21 @@
     </row>
     <row r="60" spans="1:8">
       <c r="A60">
-        <v>15080</v>
+        <v>15070</v>
       </c>
       <c r="B60" t="str">
         <f>INDEX(TextData!B:B,MATCH(A60,TextData!A:A))</f>
-        <v>ヒールハント</v>
+        <v>ジャックポッド</v>
       </c>
       <c r="C60">
-        <v>12082</v>
+        <v>15011</v>
       </c>
       <c r="D60" t="str">
         <f>INDEX(Define!V:V,MATCH(C60,Define!U:U))</f>
-        <v>相手が回復をする</v>
+        <v>味方が攻撃タイプの行動をしようとしている</v>
       </c>
       <c r="E60">
-        <v>2</v>
+        <v>33</v>
       </c>
       <c r="F60">
         <v>0</v>
@@ -41436,21 +41445,21 @@
     </row>
     <row r="61" spans="1:8">
       <c r="A61">
-        <v>15090</v>
+        <v>15080</v>
       </c>
       <c r="B61" t="str">
         <f>INDEX(TextData!B:B,MATCH(A61,TextData!A:A))</f>
-        <v>クイックカース</v>
+        <v>ヒールハント</v>
       </c>
       <c r="C61">
-        <v>12060</v>
+        <v>12082</v>
       </c>
       <c r="D61" t="str">
         <f>INDEX(Define!V:V,MATCH(C61,Define!U:U))</f>
-        <v>味方が攻撃を受ける。Param2で対象指定</v>
+        <v>相手が回復をする</v>
       </c>
       <c r="E61">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F61">
         <v>0</v>
@@ -41464,21 +41473,21 @@
     </row>
     <row r="62" spans="1:8">
       <c r="A62">
-        <v>30020</v>
+        <v>15090</v>
       </c>
       <c r="B62" t="str">
         <f>INDEX(TextData!B:B,MATCH(A62,TextData!A:A))</f>
-        <v>スティールヒール</v>
+        <v>クイックカース</v>
       </c>
       <c r="C62">
-        <v>20140</v>
+        <v>12060</v>
       </c>
       <c r="D62" t="str">
         <f>INDEX(Define!V:V,MATCH(C62,Define!U:U))</f>
-        <v>自身の攻撃で敵を倒す</v>
+        <v>味方が攻撃を受ける。Param2で対象指定</v>
       </c>
       <c r="E62">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="F62">
         <v>0</v>
@@ -41492,21 +41501,21 @@
     </row>
     <row r="63" spans="1:8">
       <c r="A63">
-        <v>100110</v>
+        <v>30020</v>
       </c>
       <c r="B63" t="str">
         <f>INDEX(TextData!B:B,MATCH(A63,TextData!A:A))</f>
-        <v>ソーイングアームド</v>
+        <v>スティールヒール</v>
       </c>
       <c r="C63">
-        <v>7010</v>
+        <v>20140</v>
       </c>
       <c r="D63" t="str">
         <f>INDEX(Define!V:V,MATCH(C63,Define!U:U))</f>
-        <v>神化発動前</v>
+        <v>自身の攻撃で敵を倒す</v>
       </c>
       <c r="E63">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="F63">
         <v>0</v>
@@ -41515,7 +41524,7 @@
         <v>0</v>
       </c>
       <c r="H63">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64" spans="1:8">
@@ -41527,51 +41536,51 @@
         <v>ソーイングアームド</v>
       </c>
       <c r="C64">
-        <v>17010</v>
+        <v>7010</v>
       </c>
       <c r="D64" t="str">
         <f>INDEX(Define!V:V,MATCH(C64,Define!U:U))</f>
-        <v>魔法を〇回使用する</v>
+        <v>神化発動前</v>
       </c>
       <c r="E64">
         <v>2</v>
       </c>
       <c r="F64">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G64">
-        <v>1060</v>
+        <v>0</v>
       </c>
       <c r="H64">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="65" spans="1:8">
       <c r="A65">
-        <v>100210</v>
+        <v>100110</v>
       </c>
       <c r="B65" t="str">
         <f>INDEX(TextData!B:B,MATCH(A65,TextData!A:A))</f>
-        <v>アブソリュートパリィ</v>
+        <v>ソーイングアームド</v>
       </c>
       <c r="C65">
-        <v>7010</v>
+        <v>17010</v>
       </c>
       <c r="D65" t="str">
         <f>INDEX(Define!V:V,MATCH(C65,Define!U:U))</f>
-        <v>神化発動前</v>
+        <v>魔法を〇回使用する</v>
       </c>
       <c r="E65">
         <v>2</v>
       </c>
       <c r="F65">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G65">
-        <v>0</v>
+        <v>1060</v>
       </c>
       <c r="H65">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66" spans="1:8">
@@ -41583,51 +41592,51 @@
         <v>アブソリュートパリィ</v>
       </c>
       <c r="C66">
-        <v>17040</v>
+        <v>7010</v>
       </c>
       <c r="D66" t="str">
         <f>INDEX(Define!V:V,MATCH(C66,Define!U:U))</f>
-        <v>回避を〇回行う</v>
+        <v>神化発動前</v>
       </c>
       <c r="E66">
         <v>2</v>
       </c>
       <c r="F66">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G66">
         <v>0</v>
       </c>
       <c r="H66">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="67" spans="1:8">
       <c r="A67">
-        <v>100310</v>
+        <v>100210</v>
       </c>
       <c r="B67" t="str">
         <f>INDEX(TextData!B:B,MATCH(A67,TextData!A:A))</f>
-        <v>セイクリッドバリア</v>
+        <v>アブソリュートパリィ</v>
       </c>
       <c r="C67">
-        <v>7010</v>
+        <v>17040</v>
       </c>
       <c r="D67" t="str">
         <f>INDEX(Define!V:V,MATCH(C67,Define!U:U))</f>
-        <v>神化発動前</v>
+        <v>回避を〇回行う</v>
       </c>
       <c r="E67">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="F67">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G67">
         <v>0</v>
       </c>
       <c r="H67">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68" spans="1:8">
@@ -41639,51 +41648,51 @@
         <v>セイクリッドバリア</v>
       </c>
       <c r="C68">
-        <v>17020</v>
+        <v>7010</v>
       </c>
       <c r="D68" t="str">
         <f>INDEX(Define!V:V,MATCH(C68,Define!U:U))</f>
-        <v>攻撃を〇回受ける</v>
+        <v>神化発動前</v>
       </c>
       <c r="E68">
         <v>11</v>
       </c>
       <c r="F68">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G68">
         <v>0</v>
       </c>
       <c r="H68">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="69" spans="1:8">
       <c r="A69">
-        <v>100410</v>
+        <v>100310</v>
       </c>
       <c r="B69" t="str">
         <f>INDEX(TextData!B:B,MATCH(A69,TextData!A:A))</f>
-        <v>アバンデンス</v>
+        <v>セイクリッドバリア</v>
       </c>
       <c r="C69">
-        <v>7010</v>
+        <v>17020</v>
       </c>
       <c r="D69" t="str">
         <f>INDEX(Define!V:V,MATCH(C69,Define!U:U))</f>
-        <v>神化発動前</v>
+        <v>攻撃を〇回受ける</v>
       </c>
       <c r="E69">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="F69">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G69">
         <v>0</v>
       </c>
       <c r="H69">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70" spans="1:8">
@@ -41695,11 +41704,11 @@
         <v>アバンデンス</v>
       </c>
       <c r="C70">
-        <v>20040</v>
+        <v>7010</v>
       </c>
       <c r="D70" t="str">
         <f>INDEX(Define!V:V,MATCH(C70,Define!U:U))</f>
-        <v>自分以外が戦闘不能</v>
+        <v>神化発動前</v>
       </c>
       <c r="E70">
         <v>2</v>
@@ -41711,26 +41720,26 @@
         <v>0</v>
       </c>
       <c r="H70">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="71" spans="1:8">
       <c r="A71">
-        <v>100510</v>
+        <v>100410</v>
       </c>
       <c r="B71" t="str">
         <f>INDEX(TextData!B:B,MATCH(A71,TextData!A:A))</f>
-        <v>カースドブレイク</v>
+        <v>アバンデンス</v>
       </c>
       <c r="C71">
-        <v>7010</v>
+        <v>20040</v>
       </c>
       <c r="D71" t="str">
         <f>INDEX(Define!V:V,MATCH(C71,Define!U:U))</f>
-        <v>神化発動前</v>
+        <v>自分以外が戦闘不能</v>
       </c>
       <c r="E71">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F71">
         <v>0</v>
@@ -41739,7 +41748,7 @@
         <v>0</v>
       </c>
       <c r="H71">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72" spans="1:8">
@@ -41751,11 +41760,11 @@
         <v>カースドブレイク</v>
       </c>
       <c r="C72">
-        <v>20160</v>
+        <v>7010</v>
       </c>
       <c r="D72" t="str">
         <f>INDEX(Define!V:V,MATCH(C72,Define!U:U))</f>
-        <v>自身が戦闘不能になる攻撃を受ける</v>
+        <v>神化発動前</v>
       </c>
       <c r="E72">
         <v>3</v>
@@ -41767,26 +41776,26 @@
         <v>0</v>
       </c>
       <c r="H72">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="73" spans="1:8">
       <c r="A73">
-        <v>100610</v>
+        <v>100510</v>
       </c>
       <c r="B73" t="str">
         <f>INDEX(TextData!B:B,MATCH(A73,TextData!A:A))</f>
-        <v>サンフレイム</v>
+        <v>カースドブレイク</v>
       </c>
       <c r="C73">
-        <v>7010</v>
+        <v>20160</v>
       </c>
       <c r="D73" t="str">
         <f>INDEX(Define!V:V,MATCH(C73,Define!U:U))</f>
-        <v>神化発動前</v>
+        <v>自身が戦闘不能になる攻撃を受ける</v>
       </c>
       <c r="E73">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F73">
         <v>0</v>
@@ -41795,7 +41804,7 @@
         <v>0</v>
       </c>
       <c r="H73">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74" spans="1:8">
@@ -41807,11 +41816,11 @@
         <v>サンフレイム</v>
       </c>
       <c r="C74">
-        <v>7070</v>
+        <v>7010</v>
       </c>
       <c r="D74" t="str">
         <f>INDEX(Define!V:V,MATCH(C74,Define!U:U))</f>
-        <v>神化魔法使用回数の総計</v>
+        <v>神化発動前</v>
       </c>
       <c r="E74">
         <v>2</v>
@@ -41820,26 +41829,26 @@
         <v>0</v>
       </c>
       <c r="G74">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H74">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="75" spans="1:8">
       <c r="A75">
-        <v>100710</v>
+        <v>100610</v>
       </c>
       <c r="B75" t="str">
         <f>INDEX(TextData!B:B,MATCH(A75,TextData!A:A))</f>
-        <v>ライズザフラッグ</v>
+        <v>サンフレイム</v>
       </c>
       <c r="C75">
-        <v>7010</v>
+        <v>7070</v>
       </c>
       <c r="D75" t="str">
         <f>INDEX(Define!V:V,MATCH(C75,Define!U:U))</f>
-        <v>神化発動前</v>
+        <v>神化魔法使用回数の総計</v>
       </c>
       <c r="E75">
         <v>2</v>
@@ -41848,13 +41857,13 @@
         <v>0</v>
       </c>
       <c r="G75">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H75">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="76" ht="12" customHeight="1" spans="1:8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8">
       <c r="A76">
         <v>100710</v>
       </c>
@@ -41863,11 +41872,11 @@
         <v>ライズザフラッグ</v>
       </c>
       <c r="C76">
-        <v>20140</v>
+        <v>7010</v>
       </c>
       <c r="D76" t="str">
         <f>INDEX(Define!V:V,MATCH(C76,Define!U:U))</f>
-        <v>自身の攻撃で敵を倒す</v>
+        <v>神化発動前</v>
       </c>
       <c r="E76">
         <v>2</v>
@@ -41879,23 +41888,23 @@
         <v>0</v>
       </c>
       <c r="H76">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="77" spans="1:8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77" ht="12" customHeight="1" spans="1:8">
       <c r="A77">
-        <v>100810</v>
+        <v>100710</v>
       </c>
       <c r="B77" t="str">
         <f>INDEX(TextData!B:B,MATCH(A77,TextData!A:A))</f>
-        <v>テンパランス</v>
+        <v>ライズザフラッグ</v>
       </c>
       <c r="C77">
-        <v>7010</v>
+        <v>20140</v>
       </c>
       <c r="D77" t="str">
         <f>INDEX(Define!V:V,MATCH(C77,Define!U:U))</f>
-        <v>神化発動前</v>
+        <v>自身の攻撃で敵を倒す</v>
       </c>
       <c r="E77">
         <v>2</v>
@@ -41907,10 +41916,10 @@
         <v>0</v>
       </c>
       <c r="H77">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="78" ht="12" customHeight="1" spans="1:8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8">
       <c r="A78">
         <v>100810</v>
       </c>
@@ -41919,54 +41928,54 @@
         <v>テンパランス</v>
       </c>
       <c r="C78">
-        <v>9020</v>
+        <v>7010</v>
       </c>
       <c r="D78" t="str">
         <f>INDEX(Define!V:V,MATCH(C78,Define!U:U))</f>
-        <v>ターン数が〇</v>
+        <v>神化発動前</v>
       </c>
       <c r="E78">
         <v>2</v>
       </c>
       <c r="F78">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G78">
         <v>0</v>
       </c>
       <c r="H78">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="79" spans="1:8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79" ht="12" customHeight="1" spans="1:8">
       <c r="A79">
-        <v>100910</v>
+        <v>100810</v>
       </c>
       <c r="B79" t="str">
         <f>INDEX(TextData!B:B,MATCH(A79,TextData!A:A))</f>
-        <v>バーニングカウンター</v>
+        <v>テンパランス</v>
       </c>
       <c r="C79">
-        <v>7010</v>
+        <v>9020</v>
       </c>
       <c r="D79" t="str">
         <f>INDEX(Define!V:V,MATCH(C79,Define!U:U))</f>
-        <v>神化発動前</v>
+        <v>ターン数が〇</v>
       </c>
       <c r="E79">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="F79">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G79">
         <v>0</v>
       </c>
       <c r="H79">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="80" ht="12" customHeight="1" spans="1:8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8">
       <c r="A80">
         <v>100910</v>
       </c>
@@ -41975,11 +41984,11 @@
         <v>バーニングカウンター</v>
       </c>
       <c r="C80">
-        <v>12041</v>
+        <v>7010</v>
       </c>
       <c r="D80" t="str">
         <f>INDEX(Define!V:V,MATCH(C80,Define!U:U))</f>
-        <v>攻撃を受けた対象が戦闘不能になった</v>
+        <v>神化発動前</v>
       </c>
       <c r="E80">
         <v>11</v>
@@ -41991,26 +42000,26 @@
         <v>0</v>
       </c>
       <c r="H80">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="81" spans="1:8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81" ht="12" customHeight="1" spans="1:8">
       <c r="A81">
-        <v>101010</v>
+        <v>100910</v>
       </c>
       <c r="B81" t="str">
         <f>INDEX(TextData!B:B,MATCH(A81,TextData!A:A))</f>
-        <v>エウロス</v>
+        <v>バーニングカウンター</v>
       </c>
       <c r="C81">
-        <v>7010</v>
+        <v>12041</v>
       </c>
       <c r="D81" t="str">
         <f>INDEX(Define!V:V,MATCH(C81,Define!U:U))</f>
-        <v>神化発動前</v>
+        <v>攻撃を受けた対象が戦闘不能になった</v>
       </c>
       <c r="E81">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="F81">
         <v>0</v>
@@ -42019,10 +42028,10 @@
         <v>0</v>
       </c>
       <c r="H81">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="82" ht="12" customHeight="1" spans="1:8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8">
       <c r="A82">
         <v>101010</v>
       </c>
@@ -42031,11 +42040,11 @@
         <v>エウロス</v>
       </c>
       <c r="C82">
-        <v>12063</v>
+        <v>7010</v>
       </c>
       <c r="D82" t="str">
         <f>INDEX(Define!V:V,MATCH(C82,Define!U:U))</f>
-        <v>自身が状態異常を受ける</v>
+        <v>神化発動前</v>
       </c>
       <c r="E82">
         <v>2</v>
@@ -42047,23 +42056,23 @@
         <v>0</v>
       </c>
       <c r="H82">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="83" spans="1:8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83" ht="12" customHeight="1" spans="1:8">
       <c r="A83">
-        <v>101110</v>
+        <v>101010</v>
       </c>
       <c r="B83" t="str">
         <f>INDEX(TextData!B:B,MATCH(A83,TextData!A:A))</f>
-        <v>アバランシュ</v>
+        <v>エウロス</v>
       </c>
       <c r="C83">
-        <v>7010</v>
+        <v>12063</v>
       </c>
       <c r="D83" t="str">
         <f>INDEX(Define!V:V,MATCH(C83,Define!U:U))</f>
-        <v>神化発動前</v>
+        <v>自身が状態異常を受ける</v>
       </c>
       <c r="E83">
         <v>2</v>
@@ -42075,10 +42084,10 @@
         <v>0</v>
       </c>
       <c r="H83">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="84" ht="12" customHeight="1" spans="1:8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8">
       <c r="A84">
         <v>101110</v>
       </c>
@@ -42087,11 +42096,11 @@
         <v>アバランシュ</v>
       </c>
       <c r="C84">
-        <v>20071</v>
+        <v>7010</v>
       </c>
       <c r="D84" t="str">
         <f>INDEX(Define!V:V,MATCH(C84,Define!U:U))</f>
-        <v>敵全員が凍結状態</v>
+        <v>神化発動前</v>
       </c>
       <c r="E84">
         <v>2</v>
@@ -42103,23 +42112,23 @@
         <v>0</v>
       </c>
       <c r="H84">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="85" spans="1:8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85" ht="12" customHeight="1" spans="1:8">
       <c r="A85">
-        <v>200110</v>
+        <v>101110</v>
       </c>
       <c r="B85" t="str">
         <f>INDEX(TextData!B:B,MATCH(A85,TextData!A:A))</f>
-        <v>スリータイムス</v>
+        <v>アバランシュ</v>
       </c>
       <c r="C85">
-        <v>7010</v>
+        <v>20071</v>
       </c>
       <c r="D85" t="str">
         <f>INDEX(Define!V:V,MATCH(C85,Define!U:U))</f>
-        <v>神化発動前</v>
+        <v>敵全員が凍結状態</v>
       </c>
       <c r="E85">
         <v>2</v>
@@ -42131,7 +42140,7 @@
         <v>0</v>
       </c>
       <c r="H85">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86" spans="1:8">
@@ -42143,51 +42152,51 @@
         <v>スリータイムス</v>
       </c>
       <c r="C86">
-        <v>17010</v>
+        <v>7010</v>
       </c>
       <c r="D86" t="str">
         <f>INDEX(Define!V:V,MATCH(C86,Define!U:U))</f>
-        <v>魔法を〇回使用する</v>
+        <v>神化発動前</v>
       </c>
       <c r="E86">
         <v>2</v>
       </c>
       <c r="F86">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G86">
-        <v>1010</v>
+        <v>0</v>
       </c>
       <c r="H86">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="87" spans="1:8">
       <c r="A87">
-        <v>200210</v>
+        <v>200110</v>
       </c>
       <c r="B87" t="str">
         <f>INDEX(TextData!B:B,MATCH(A87,TextData!A:A))</f>
-        <v>マイトレインフォース</v>
+        <v>スリータイムス</v>
       </c>
       <c r="C87">
-        <v>7010</v>
+        <v>17010</v>
       </c>
       <c r="D87" t="str">
         <f>INDEX(Define!V:V,MATCH(C87,Define!U:U))</f>
-        <v>神化発動前</v>
+        <v>魔法を〇回使用する</v>
       </c>
       <c r="E87">
         <v>2</v>
       </c>
       <c r="F87">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G87">
-        <v>0</v>
+        <v>1010</v>
       </c>
       <c r="H87">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88" spans="1:8">
@@ -42199,45 +42208,45 @@
         <v>マイトレインフォース</v>
       </c>
       <c r="C88">
-        <v>20040</v>
+        <v>7010</v>
       </c>
       <c r="D88" t="str">
         <f>INDEX(Define!V:V,MATCH(C88,Define!U:U))</f>
-        <v>自分以外が戦闘不能</v>
+        <v>神化発動前</v>
       </c>
       <c r="E88">
         <v>2</v>
       </c>
       <c r="F88">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G88">
         <v>0</v>
       </c>
       <c r="H88">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="89" spans="1:8">
       <c r="A89">
-        <v>200230</v>
+        <v>200210</v>
       </c>
       <c r="B89" t="str">
         <f>INDEX(TextData!B:B,MATCH(A89,TextData!A:A))</f>
-        <v>悪魔(ベリト)</v>
+        <v>マイトレインフォース</v>
       </c>
       <c r="C89">
-        <v>1010</v>
+        <v>20040</v>
       </c>
       <c r="D89" t="str">
         <f>INDEX(Define!V:V,MATCH(C89,Define!U:U))</f>
-        <v>自身のHpが〇%以下</v>
+        <v>自分以外が戦闘不能</v>
       </c>
       <c r="E89">
         <v>2</v>
       </c>
       <c r="F89">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="G89">
         <v>0</v>
@@ -42248,30 +42257,30 @@
     </row>
     <row r="90" spans="1:8">
       <c r="A90">
-        <v>200310</v>
+        <v>200230</v>
       </c>
       <c r="B90" t="str">
         <f>INDEX(TextData!B:B,MATCH(A90,TextData!A:A))</f>
-        <v>プルガシオン</v>
+        <v>悪魔(ベリト)</v>
       </c>
       <c r="C90">
-        <v>7010</v>
+        <v>1010</v>
       </c>
       <c r="D90" t="str">
         <f>INDEX(Define!V:V,MATCH(C90,Define!U:U))</f>
-        <v>神化発動前</v>
+        <v>自身のHpが〇%以下</v>
       </c>
       <c r="E90">
         <v>2</v>
       </c>
       <c r="F90">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="G90">
         <v>0</v>
       </c>
       <c r="H90">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91" spans="1:8">
@@ -42283,45 +42292,45 @@
         <v>プルガシオン</v>
       </c>
       <c r="C91">
-        <v>1010</v>
+        <v>7010</v>
       </c>
       <c r="D91" t="str">
         <f>INDEX(Define!V:V,MATCH(C91,Define!U:U))</f>
-        <v>自身のHpが〇%以下</v>
+        <v>神化発動前</v>
       </c>
       <c r="E91">
         <v>2</v>
       </c>
       <c r="F91">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G91">
         <v>0</v>
       </c>
       <c r="H91">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="92" spans="1:8">
       <c r="A92">
-        <v>200330</v>
+        <v>200310</v>
       </c>
       <c r="B92" t="str">
         <f>INDEX(TextData!B:B,MATCH(A92,TextData!A:A))</f>
-        <v>悪魔(パイモン)</v>
+        <v>プルガシオン</v>
       </c>
       <c r="C92">
-        <v>0</v>
+        <v>1010</v>
       </c>
       <c r="D92" t="str">
         <f>INDEX(Define!V:V,MATCH(C92,Define!U:U))</f>
-        <v>なし</v>
+        <v>自身のHpが〇%以下</v>
       </c>
       <c r="E92">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F92">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="G92">
         <v>0</v>
@@ -42332,21 +42341,21 @@
     </row>
     <row r="93" spans="1:8">
       <c r="A93">
-        <v>200410</v>
+        <v>200330</v>
       </c>
       <c r="B93" t="str">
         <f>INDEX(TextData!B:B,MATCH(A93,TextData!A:A))</f>
-        <v>コウソクテンショウ</v>
+        <v>悪魔(パイモン)</v>
       </c>
       <c r="C93">
-        <v>7010</v>
+        <v>0</v>
       </c>
       <c r="D93" t="str">
         <f>INDEX(Define!V:V,MATCH(C93,Define!U:U))</f>
-        <v>神化発動前</v>
+        <v>なし</v>
       </c>
       <c r="E93">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F93">
         <v>0</v>
@@ -42355,7 +42364,7 @@
         <v>0</v>
       </c>
       <c r="H93">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94" spans="1:8">
@@ -42367,45 +42376,45 @@
         <v>コウソクテンショウ</v>
       </c>
       <c r="C94">
-        <v>1010</v>
+        <v>7010</v>
       </c>
       <c r="D94" t="str">
         <f>INDEX(Define!V:V,MATCH(C94,Define!U:U))</f>
-        <v>自身のHpが〇%以下</v>
+        <v>神化発動前</v>
       </c>
       <c r="E94">
         <v>2</v>
       </c>
       <c r="F94">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="G94">
         <v>0</v>
       </c>
       <c r="H94">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="95" spans="1:8">
       <c r="A95">
-        <v>200430</v>
+        <v>200410</v>
       </c>
       <c r="B95" t="str">
         <f>INDEX(TextData!B:B,MATCH(A95,TextData!A:A))</f>
-        <v>悪魔(アンドラス)</v>
+        <v>コウソクテンショウ</v>
       </c>
       <c r="C95">
-        <v>0</v>
+        <v>1010</v>
       </c>
       <c r="D95" t="str">
         <f>INDEX(Define!V:V,MATCH(C95,Define!U:U))</f>
-        <v>なし</v>
+        <v>自身のHpが〇%以下</v>
       </c>
       <c r="E95">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F95">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="G95">
         <v>0</v>
@@ -42416,21 +42425,21 @@
     </row>
     <row r="96" spans="1:8">
       <c r="A96">
-        <v>200510</v>
+        <v>200430</v>
       </c>
       <c r="B96" t="str">
         <f>INDEX(TextData!B:B,MATCH(A96,TextData!A:A))</f>
-        <v>カウントダウン</v>
+        <v>悪魔(アンドラス)</v>
       </c>
       <c r="C96">
-        <v>7010</v>
+        <v>0</v>
       </c>
       <c r="D96" t="str">
         <f>INDEX(Define!V:V,MATCH(C96,Define!U:U))</f>
-        <v>神化発動前</v>
+        <v>なし</v>
       </c>
       <c r="E96">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F96">
         <v>0</v>
@@ -42439,7 +42448,7 @@
         <v>0</v>
       </c>
       <c r="H96">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="97" spans="1:8">
@@ -42451,11 +42460,11 @@
         <v>カウントダウン</v>
       </c>
       <c r="C97">
-        <v>9040</v>
+        <v>7010</v>
       </c>
       <c r="D97" t="str">
         <f>INDEX(Define!V:V,MATCH(C97,Define!U:U))</f>
-        <v>全体の行動数がparam1 x 行動数 + param2</v>
+        <v>神化発動前</v>
       </c>
       <c r="E97">
         <v>2</v>
@@ -42464,35 +42473,35 @@
         <v>0</v>
       </c>
       <c r="G97">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H97">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="98" spans="1:8">
       <c r="A98">
-        <v>200530</v>
+        <v>200510</v>
       </c>
       <c r="B98" t="str">
         <f>INDEX(TextData!B:B,MATCH(A98,TextData!A:A))</f>
-        <v>悪魔(ビフロンス)</v>
+        <v>カウントダウン</v>
       </c>
       <c r="C98">
-        <v>1010</v>
+        <v>9040</v>
       </c>
       <c r="D98" t="str">
         <f>INDEX(Define!V:V,MATCH(C98,Define!U:U))</f>
-        <v>自身のHpが〇%以下</v>
+        <v>全体の行動数がparam1 x 行動数 + param2</v>
       </c>
       <c r="E98">
         <v>2</v>
       </c>
       <c r="F98">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G98">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H98">
         <v>0</v>
@@ -42500,30 +42509,30 @@
     </row>
     <row r="99" spans="1:8">
       <c r="A99">
-        <v>201010</v>
+        <v>200530</v>
       </c>
       <c r="B99" t="str">
         <f>INDEX(TextData!B:B,MATCH(A99,TextData!A:A))</f>
-        <v>カオスペイン</v>
+        <v>悪魔(ビフロンス)</v>
       </c>
       <c r="C99">
-        <v>7010</v>
+        <v>1010</v>
       </c>
       <c r="D99" t="str">
         <f>INDEX(Define!V:V,MATCH(C99,Define!U:U))</f>
-        <v>神化発動前</v>
+        <v>自身のHpが〇%以下</v>
       </c>
       <c r="E99">
         <v>2</v>
       </c>
       <c r="F99">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="G99">
         <v>0</v>
       </c>
       <c r="H99">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="100" spans="1:8">
@@ -42535,45 +42544,45 @@
         <v>カオスペイン</v>
       </c>
       <c r="C100">
-        <v>1010</v>
+        <v>7010</v>
       </c>
       <c r="D100" t="str">
         <f>INDEX(Define!V:V,MATCH(C100,Define!U:U))</f>
-        <v>自身のHpが〇%以下</v>
+        <v>神化発動前</v>
       </c>
       <c r="E100">
         <v>2</v>
       </c>
       <c r="F100">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="G100">
         <v>0</v>
       </c>
       <c r="H100">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="101" spans="1:8">
       <c r="A101">
-        <v>201030</v>
+        <v>201010</v>
       </c>
       <c r="B101" t="str">
         <f>INDEX(TextData!B:B,MATCH(A101,TextData!A:A))</f>
-        <v>アンリマユ</v>
+        <v>カオスペイン</v>
       </c>
       <c r="C101">
-        <v>0</v>
+        <v>1010</v>
       </c>
       <c r="D101" t="str">
         <f>INDEX(Define!V:V,MATCH(C101,Define!U:U))</f>
-        <v>なし</v>
+        <v>自身のHpが〇%以下</v>
       </c>
       <c r="E101">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F101">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="G101">
         <v>0</v>
@@ -42584,11 +42593,11 @@
     </row>
     <row r="102" spans="1:8">
       <c r="A102">
-        <v>300010</v>
+        <v>201030</v>
       </c>
       <c r="B102" t="str">
         <f>INDEX(TextData!B:B,MATCH(A102,TextData!A:A))</f>
-        <v>ライフブースト</v>
+        <v>アンリマユ</v>
       </c>
       <c r="C102">
         <v>0</v>
@@ -42612,11 +42621,11 @@
     </row>
     <row r="103" spans="1:8">
       <c r="A103">
-        <v>300020</v>
+        <v>300010</v>
       </c>
       <c r="B103" t="str">
         <f>INDEX(TextData!B:B,MATCH(A103,TextData!A:A))</f>
-        <v>スピリットチャージ</v>
+        <v>ライフブースト</v>
       </c>
       <c r="C103">
         <v>0</v>
@@ -42640,11 +42649,11 @@
     </row>
     <row r="104" spans="1:8">
       <c r="A104">
-        <v>300030</v>
+        <v>300020</v>
       </c>
       <c r="B104" t="str">
         <f>INDEX(TextData!B:B,MATCH(A104,TextData!A:A))</f>
-        <v>フォースライズ</v>
+        <v>スピリットチャージ</v>
       </c>
       <c r="C104">
         <v>0</v>
@@ -42668,11 +42677,11 @@
     </row>
     <row r="105" spans="1:8">
       <c r="A105">
-        <v>300040</v>
+        <v>300030</v>
       </c>
       <c r="B105" t="str">
         <f>INDEX(TextData!B:B,MATCH(A105,TextData!A:A))</f>
-        <v>ディフェンスオーラ</v>
+        <v>フォースライズ</v>
       </c>
       <c r="C105">
         <v>0</v>
@@ -42696,11 +42705,11 @@
     </row>
     <row r="106" spans="1:8">
       <c r="A106">
-        <v>300050</v>
+        <v>300040</v>
       </c>
       <c r="B106" t="str">
         <f>INDEX(TextData!B:B,MATCH(A106,TextData!A:A))</f>
-        <v>ラピッドムーブ</v>
+        <v>ディフェンスオーラ</v>
       </c>
       <c r="C106">
         <v>0</v>
@@ -42724,11 +42733,11 @@
     </row>
     <row r="107" spans="1:8">
       <c r="A107">
-        <v>300130</v>
+        <v>300050</v>
       </c>
       <c r="B107" t="str">
         <f>INDEX(TextData!B:B,MATCH(A107,TextData!A:A))</f>
-        <v>アタックブレイク</v>
+        <v>ラピッドムーブ</v>
       </c>
       <c r="C107">
         <v>0</v>
@@ -42752,11 +42761,11 @@
     </row>
     <row r="108" spans="1:8">
       <c r="A108">
-        <v>300140</v>
+        <v>300130</v>
       </c>
       <c r="B108" t="str">
         <f>INDEX(TextData!B:B,MATCH(A108,TextData!A:A))</f>
-        <v>シールドバニッシュ</v>
+        <v>アタックブレイク</v>
       </c>
       <c r="C108">
         <v>0</v>
@@ -42780,11 +42789,11 @@
     </row>
     <row r="109" spans="1:8">
       <c r="A109">
-        <v>300210</v>
+        <v>300140</v>
       </c>
       <c r="B109" t="str">
         <f>INDEX(TextData!B:B,MATCH(A109,TextData!A:A))</f>
-        <v>エーテルリチャージ</v>
+        <v>シールドバニッシュ</v>
       </c>
       <c r="C109">
         <v>0</v>
@@ -42794,7 +42803,7 @@
         <v>なし</v>
       </c>
       <c r="E109">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F109">
         <v>0</v>
@@ -42808,11 +42817,11 @@
     </row>
     <row r="110" spans="1:8">
       <c r="A110">
-        <v>300220</v>
+        <v>300210</v>
       </c>
       <c r="B110" t="str">
         <f>INDEX(TextData!B:B,MATCH(A110,TextData!A:A))</f>
-        <v>リカバリーエンハンス</v>
+        <v>エーテルリチャージ</v>
       </c>
       <c r="C110">
         <v>0</v>
@@ -42822,7 +42831,7 @@
         <v>なし</v>
       </c>
       <c r="E110">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F110">
         <v>0</v>
@@ -42836,11 +42845,11 @@
     </row>
     <row r="111" spans="1:8">
       <c r="A111">
-        <v>300230</v>
+        <v>300220</v>
       </c>
       <c r="B111" t="str">
         <f>INDEX(TextData!B:B,MATCH(A111,TextData!A:A))</f>
-        <v>ヴェンジェンス</v>
+        <v>リカバリーエンハンス</v>
       </c>
       <c r="C111">
         <v>0</v>
@@ -42864,11 +42873,11 @@
     </row>
     <row r="112" spans="1:8">
       <c r="A112">
-        <v>301010</v>
+        <v>300230</v>
       </c>
       <c r="B112" t="str">
         <f>INDEX(TextData!B:B,MATCH(A112,TextData!A:A))</f>
-        <v>ディケイドリセット</v>
+        <v>ヴェンジェンス</v>
       </c>
       <c r="C112">
         <v>0</v>
@@ -42878,7 +42887,7 @@
         <v>なし</v>
       </c>
       <c r="E112">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F112">
         <v>0</v>
@@ -42892,11 +42901,11 @@
     </row>
     <row r="113" spans="1:8">
       <c r="A113">
-        <v>301020</v>
+        <v>301010</v>
       </c>
       <c r="B113" t="str">
         <f>INDEX(TextData!B:B,MATCH(A113,TextData!A:A))</f>
-        <v>ウォーリアーブラッド</v>
+        <v>ディケイドリセット</v>
       </c>
       <c r="C113">
         <v>0</v>
@@ -42920,11 +42929,11 @@
     </row>
     <row r="114" spans="1:8">
       <c r="A114">
-        <v>301030</v>
+        <v>301020</v>
       </c>
       <c r="B114" t="str">
         <f>INDEX(TextData!B:B,MATCH(A114,TextData!A:A))</f>
-        <v>トライアングルガード</v>
+        <v>ウォーリアーブラッド</v>
       </c>
       <c r="C114">
         <v>0</v>
@@ -42948,11 +42957,11 @@
     </row>
     <row r="115" spans="1:8">
       <c r="A115">
-        <v>301040</v>
+        <v>301030</v>
       </c>
       <c r="B115" t="str">
         <f>INDEX(TextData!B:B,MATCH(A115,TextData!A:A))</f>
-        <v>セーフティバリア</v>
+        <v>トライアングルガード</v>
       </c>
       <c r="C115">
         <v>0</v>
@@ -42983,17 +42992,17 @@
         <v>セーフティバリア</v>
       </c>
       <c r="C116">
-        <v>11010</v>
+        <v>0</v>
       </c>
       <c r="D116" t="str">
         <f>INDEX(Define!V:V,MATCH(C116,Define!U:U))</f>
-        <v>バトル中使用回数が〇以下</v>
+        <v>なし</v>
       </c>
       <c r="E116">
         <v>2</v>
       </c>
       <c r="F116">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G116">
         <v>0</v>
@@ -43004,24 +43013,24 @@
     </row>
     <row r="117" spans="1:8">
       <c r="A117">
-        <v>301050</v>
+        <v>301040</v>
       </c>
       <c r="B117" t="str">
         <f>INDEX(TextData!B:B,MATCH(A117,TextData!A:A))</f>
-        <v>ヒロインズハイ</v>
+        <v>セーフティバリア</v>
       </c>
       <c r="C117">
-        <v>13020</v>
+        <v>11010</v>
       </c>
       <c r="D117" t="str">
         <f>INDEX(Define!V:V,MATCH(C117,Define!U:U))</f>
-        <v>〇のKindを持っている敵</v>
+        <v>バトル中使用回数が〇以下</v>
       </c>
       <c r="E117">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F117">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="G117">
         <v>0</v>
@@ -43032,30 +43041,30 @@
     </row>
     <row r="118" spans="1:8">
       <c r="A118">
-        <v>301060</v>
+        <v>301050</v>
       </c>
       <c r="B118" t="str">
         <f>INDEX(TextData!B:B,MATCH(A118,TextData!A:A))</f>
-        <v>セカンドステージ</v>
+        <v>ヒロインズハイ</v>
       </c>
       <c r="C118">
-        <v>0</v>
+        <v>13020</v>
       </c>
       <c r="D118" t="str">
         <f>INDEX(Define!V:V,MATCH(C118,Define!U:U))</f>
-        <v>なし</v>
+        <v>〇のKindを持っている敵</v>
       </c>
       <c r="E118">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F118">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G118">
         <v>0</v>
       </c>
       <c r="H118">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="119" spans="1:8">
@@ -43067,45 +43076,45 @@
         <v>セカンドステージ</v>
       </c>
       <c r="C119">
-        <v>11010</v>
+        <v>0</v>
       </c>
       <c r="D119" t="str">
         <f>INDEX(Define!V:V,MATCH(C119,Define!U:U))</f>
-        <v>バトル中使用回数が〇以下</v>
+        <v>なし</v>
       </c>
       <c r="E119">
         <v>11</v>
       </c>
       <c r="F119">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G119">
         <v>0</v>
       </c>
       <c r="H119">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="120" spans="1:8">
       <c r="A120">
-        <v>301070</v>
+        <v>301060</v>
       </c>
       <c r="B120" t="str">
         <f>INDEX(TextData!B:B,MATCH(A120,TextData!A:A))</f>
-        <v>ハイヒットポイント</v>
+        <v>セカンドステージ</v>
       </c>
       <c r="C120">
-        <v>0</v>
+        <v>11010</v>
       </c>
       <c r="D120" t="str">
         <f>INDEX(Define!V:V,MATCH(C120,Define!U:U))</f>
-        <v>なし</v>
+        <v>バトル中使用回数が〇以下</v>
       </c>
       <c r="E120">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F120">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G120">
         <v>0</v>
@@ -43116,21 +43125,21 @@
     </row>
     <row r="121" spans="1:8">
       <c r="A121">
-        <v>301080</v>
+        <v>301070</v>
       </c>
       <c r="B121" t="str">
         <f>INDEX(TextData!B:B,MATCH(A121,TextData!A:A))</f>
-        <v>セプタブラスト</v>
+        <v>ハイヒットポイント</v>
       </c>
       <c r="C121">
-        <v>12070</v>
+        <v>0</v>
       </c>
       <c r="D121" t="str">
         <f>INDEX(Define!V:V,MATCH(C121,Define!U:U))</f>
-        <v>味方が行動をする</v>
+        <v>なし</v>
       </c>
       <c r="E121">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F121">
         <v>0</v>
@@ -43139,7 +43148,7 @@
         <v>0</v>
       </c>
       <c r="H121">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="122" spans="1:8">
@@ -43151,11 +43160,11 @@
         <v>セプタブラスト</v>
       </c>
       <c r="C122">
-        <v>9031</v>
+        <v>12070</v>
       </c>
       <c r="D122" t="str">
         <f>INDEX(Define!V:V,MATCH(C122,Define!U:U))</f>
-        <v>行動者のターン数がparam1 x ターン数 + param2</v>
+        <v>味方が行動をする</v>
       </c>
       <c r="E122">
         <v>2</v>
@@ -43164,35 +43173,35 @@
         <v>0</v>
       </c>
       <c r="G122">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H122">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="123" spans="1:8">
       <c r="A123">
-        <v>301090</v>
+        <v>301080</v>
       </c>
       <c r="B123" t="str">
         <f>INDEX(TextData!B:B,MATCH(A123,TextData!A:A))</f>
-        <v>イニシャルブロッカー</v>
+        <v>セプタブラスト</v>
       </c>
       <c r="C123">
-        <v>0</v>
+        <v>9031</v>
       </c>
       <c r="D123" t="str">
         <f>INDEX(Define!V:V,MATCH(C123,Define!U:U))</f>
-        <v>なし</v>
+        <v>行動者のターン数がparam1 x ターン数 + param2</v>
       </c>
       <c r="E123">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F123">
         <v>0</v>
       </c>
       <c r="G123">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H123">
         <v>0</v>
@@ -43200,11 +43209,11 @@
     </row>
     <row r="124" spans="1:8">
       <c r="A124">
-        <v>301100</v>
+        <v>301090</v>
       </c>
       <c r="B124" t="str">
         <f>INDEX(TextData!B:B,MATCH(A124,TextData!A:A))</f>
-        <v>ファーストテイク</v>
+        <v>イニシャルブロッカー</v>
       </c>
       <c r="C124">
         <v>0</v>
@@ -43228,11 +43237,11 @@
     </row>
     <row r="125" spans="1:8">
       <c r="A125">
-        <v>310010</v>
+        <v>301100</v>
       </c>
       <c r="B125" t="str">
         <f>INDEX(TextData!B:B,MATCH(A125,TextData!A:A))</f>
-        <v>妖精の祈り</v>
+        <v>ファーストテイク</v>
       </c>
       <c r="C125">
         <v>0</v>
@@ -43256,18 +43265,18 @@
     </row>
     <row r="126" spans="1:8">
       <c r="A126">
-        <v>310020</v>
+        <v>310010</v>
       </c>
       <c r="B126" t="str">
         <f>INDEX(TextData!B:B,MATCH(A126,TextData!A:A))</f>
-        <v>月のかけら</v>
+        <v>妖精の祈り</v>
       </c>
       <c r="C126">
-        <v>40020</v>
+        <v>0</v>
       </c>
       <c r="D126" t="str">
         <f>INDEX(Define!V:V,MATCH(C126,Define!U:U))</f>
-        <v>ピリオド経過</v>
+        <v>なし</v>
       </c>
       <c r="E126">
         <v>4</v>
@@ -43284,18 +43293,18 @@
     </row>
     <row r="127" spans="1:8">
       <c r="A127">
-        <v>310030</v>
+        <v>310020</v>
       </c>
       <c r="B127" t="str">
         <f>INDEX(TextData!B:B,MATCH(A127,TextData!A:A))</f>
-        <v>商売の才覚書</v>
+        <v>月のかけら</v>
       </c>
       <c r="C127">
-        <v>0</v>
+        <v>40020</v>
       </c>
       <c r="D127" t="str">
         <f>INDEX(Define!V:V,MATCH(C127,Define!U:U))</f>
-        <v>なし</v>
+        <v>ピリオド経過</v>
       </c>
       <c r="E127">
         <v>4</v>
@@ -43312,11 +43321,11 @@
     </row>
     <row r="128" spans="1:8">
       <c r="A128">
-        <v>310040</v>
+        <v>310030</v>
       </c>
       <c r="B128" t="str">
         <f>INDEX(TextData!B:B,MATCH(A128,TextData!A:A))</f>
-        <v>ワタリガラスの旗</v>
+        <v>商売の才覚書</v>
       </c>
       <c r="C128">
         <v>0</v>
@@ -43340,11 +43349,11 @@
     </row>
     <row r="129" spans="1:8">
       <c r="A129">
-        <v>310050</v>
+        <v>310040</v>
       </c>
       <c r="B129" t="str">
         <f>INDEX(TextData!B:B,MATCH(A129,TextData!A:A))</f>
-        <v>先陣の心得</v>
+        <v>ワタリガラスの旗</v>
       </c>
       <c r="C129">
         <v>0</v>
@@ -43368,11 +43377,11 @@
     </row>
     <row r="130" spans="1:8">
       <c r="A130">
-        <v>310060</v>
+        <v>310050</v>
       </c>
       <c r="B130" t="str">
         <f>INDEX(TextData!B:B,MATCH(A130,TextData!A:A))</f>
-        <v>ヒスイの勾玉</v>
+        <v>先陣の心得</v>
       </c>
       <c r="C130">
         <v>0</v>
@@ -43396,11 +43405,11 @@
     </row>
     <row r="131" spans="1:8">
       <c r="A131">
-        <v>310070</v>
+        <v>310060</v>
       </c>
       <c r="B131" t="str">
         <f>INDEX(TextData!B:B,MATCH(A131,TextData!A:A))</f>
-        <v>英傑の盾</v>
+        <v>ヒスイの勾玉</v>
       </c>
       <c r="C131">
         <v>0</v>
@@ -43424,11 +43433,11 @@
     </row>
     <row r="132" spans="1:8">
       <c r="A132">
-        <v>310080</v>
+        <v>310070</v>
       </c>
       <c r="B132" t="str">
         <f>INDEX(TextData!B:B,MATCH(A132,TextData!A:A))</f>
-        <v>鷹の目</v>
+        <v>英傑の盾</v>
       </c>
       <c r="C132">
         <v>0</v>
@@ -43452,27 +43461,27 @@
     </row>
     <row r="133" spans="1:8">
       <c r="A133">
-        <v>310130</v>
+        <v>310080</v>
       </c>
       <c r="B133" t="str">
         <f>INDEX(TextData!B:B,MATCH(A133,TextData!A:A))</f>
-        <v>ヒールユニット</v>
+        <v>鷹の目</v>
       </c>
       <c r="C133">
-        <v>40010</v>
+        <v>0</v>
       </c>
       <c r="D133" t="str">
         <f>INDEX(Define!V:V,MATCH(C133,Define!U:U))</f>
-        <v>ダンジョンで移動する param2%turncount == param1</v>
+        <v>なし</v>
       </c>
       <c r="E133">
         <v>4</v>
       </c>
       <c r="F133">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G133">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H133">
         <v>0</v>
@@ -43480,27 +43489,27 @@
     </row>
     <row r="134" spans="1:8">
       <c r="A134">
-        <v>320010</v>
+        <v>310130</v>
       </c>
       <c r="B134" t="str">
         <f>INDEX(TextData!B:B,MATCH(A134,TextData!A:A))</f>
-        <v>訓練所Lv1</v>
+        <v>ヒールユニット</v>
       </c>
       <c r="C134">
-        <v>40020</v>
+        <v>40010</v>
       </c>
       <c r="D134" t="str">
         <f>INDEX(Define!V:V,MATCH(C134,Define!U:U))</f>
-        <v>ピリオド経過</v>
+        <v>ダンジョンで移動する param2%turncount == param1</v>
       </c>
       <c r="E134">
         <v>4</v>
       </c>
       <c r="F134">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G134">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H134">
         <v>0</v>
@@ -43508,11 +43517,11 @@
     </row>
     <row r="135" spans="1:8">
       <c r="A135">
-        <v>320011</v>
+        <v>320010</v>
       </c>
       <c r="B135" t="str">
         <f>INDEX(TextData!B:B,MATCH(A135,TextData!A:A))</f>
-        <v>訓練所Lv2</v>
+        <v>訓練所Lv1</v>
       </c>
       <c r="C135">
         <v>40020</v>
@@ -43536,11 +43545,11 @@
     </row>
     <row r="136" spans="1:8">
       <c r="A136">
-        <v>320012</v>
+        <v>320011</v>
       </c>
       <c r="B136" t="str">
         <f>INDEX(TextData!B:B,MATCH(A136,TextData!A:A))</f>
-        <v>訓練所Lv3</v>
+        <v>訓練所Lv2</v>
       </c>
       <c r="C136">
         <v>40020</v>
@@ -43564,11 +43573,11 @@
     </row>
     <row r="137" spans="1:8">
       <c r="A137">
-        <v>320020</v>
+        <v>320012</v>
       </c>
       <c r="B137" t="str">
         <f>INDEX(TextData!B:B,MATCH(A137,TextData!A:A))</f>
-        <v>研究施設Lv1</v>
+        <v>訓練所Lv3</v>
       </c>
       <c r="C137">
         <v>40020</v>
@@ -43592,11 +43601,11 @@
     </row>
     <row r="138" spans="1:8">
       <c r="A138">
-        <v>320021</v>
+        <v>320020</v>
       </c>
       <c r="B138" t="str">
         <f>INDEX(TextData!B:B,MATCH(A138,TextData!A:A))</f>
-        <v>研究施設Lv2</v>
+        <v>研究施設Lv1</v>
       </c>
       <c r="C138">
         <v>40020</v>
@@ -43620,11 +43629,11 @@
     </row>
     <row r="139" spans="1:8">
       <c r="A139">
-        <v>320022</v>
+        <v>320021</v>
       </c>
       <c r="B139" t="str">
         <f>INDEX(TextData!B:B,MATCH(A139,TextData!A:A))</f>
-        <v>研究施設Lv3</v>
+        <v>研究施設Lv2</v>
       </c>
       <c r="C139">
         <v>40020</v>
@@ -43648,24 +43657,24 @@
     </row>
     <row r="140" spans="1:8">
       <c r="A140">
-        <v>320030</v>
+        <v>320022</v>
       </c>
       <c r="B140" t="str">
         <f>INDEX(TextData!B:B,MATCH(A140,TextData!A:A))</f>
-        <v>資料館Lv1</v>
+        <v>研究施設Lv3</v>
       </c>
       <c r="C140">
-        <v>14420</v>
+        <v>40020</v>
       </c>
       <c r="D140" t="str">
         <f>INDEX(Define!V:V,MATCH(C140,Define!U:U))</f>
-        <v>Lvが〇以下</v>
+        <v>ピリオド経過</v>
       </c>
       <c r="E140">
         <v>4</v>
       </c>
       <c r="F140">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G140">
         <v>0</v>
@@ -43676,11 +43685,11 @@
     </row>
     <row r="141" spans="1:8">
       <c r="A141">
-        <v>320031</v>
+        <v>320030</v>
       </c>
       <c r="B141" t="str">
         <f>INDEX(TextData!B:B,MATCH(A141,TextData!A:A))</f>
-        <v>資料館Lv2</v>
+        <v>資料館Lv1</v>
       </c>
       <c r="C141">
         <v>14420</v>
@@ -43693,7 +43702,7 @@
         <v>4</v>
       </c>
       <c r="F141">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G141">
         <v>0</v>
@@ -43704,11 +43713,11 @@
     </row>
     <row r="142" spans="1:8">
       <c r="A142">
-        <v>320032</v>
+        <v>320031</v>
       </c>
       <c r="B142" t="str">
         <f>INDEX(TextData!B:B,MATCH(A142,TextData!A:A))</f>
-        <v>資料館Lv3</v>
+        <v>資料館Lv2</v>
       </c>
       <c r="C142">
         <v>14420</v>
@@ -43721,7 +43730,7 @@
         <v>4</v>
       </c>
       <c r="F142">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="G142">
         <v>0</v>
@@ -43732,24 +43741,24 @@
     </row>
     <row r="143" spans="1:8">
       <c r="A143">
-        <v>320040</v>
+        <v>320032</v>
       </c>
       <c r="B143" t="str">
         <f>INDEX(TextData!B:B,MATCH(A143,TextData!A:A))</f>
-        <v>潜伏技術Lv1</v>
+        <v>資料館Lv3</v>
       </c>
       <c r="C143">
-        <v>40030</v>
+        <v>14420</v>
       </c>
       <c r="D143" t="str">
         <f>INDEX(Define!V:V,MATCH(C143,Define!U:U))</f>
-        <v>ダンジョン開始時</v>
+        <v>Lvが〇以下</v>
       </c>
       <c r="E143">
         <v>4</v>
       </c>
       <c r="F143">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G143">
         <v>0</v>
@@ -43760,18 +43769,18 @@
     </row>
     <row r="144" spans="1:8">
       <c r="A144">
-        <v>321010</v>
+        <v>320040</v>
       </c>
       <c r="B144" t="str">
         <f>INDEX(TextData!B:B,MATCH(A144,TextData!A:A))</f>
-        <v>炎の祭壇</v>
+        <v>潜伏技術Lv1</v>
       </c>
       <c r="C144">
-        <v>0</v>
+        <v>40030</v>
       </c>
       <c r="D144" t="str">
         <f>INDEX(Define!V:V,MATCH(C144,Define!U:U))</f>
-        <v>なし</v>
+        <v>ダンジョン開始時</v>
       </c>
       <c r="E144">
         <v>4</v>
@@ -43788,11 +43797,11 @@
     </row>
     <row r="145" spans="1:8">
       <c r="A145">
-        <v>321020</v>
+        <v>321010</v>
       </c>
       <c r="B145" t="str">
         <f>INDEX(TextData!B:B,MATCH(A145,TextData!A:A))</f>
-        <v>稲妻の祭壇</v>
+        <v>炎の祭壇</v>
       </c>
       <c r="C145">
         <v>0</v>
@@ -43816,11 +43825,11 @@
     </row>
     <row r="146" spans="1:8">
       <c r="A146">
-        <v>321030</v>
+        <v>321020</v>
       </c>
       <c r="B146" t="str">
         <f>INDEX(TextData!B:B,MATCH(A146,TextData!A:A))</f>
-        <v>蒼の祭壇</v>
+        <v>稲妻の祭壇</v>
       </c>
       <c r="C146">
         <v>0</v>
@@ -43844,11 +43853,11 @@
     </row>
     <row r="147" spans="1:8">
       <c r="A147">
-        <v>321040</v>
+        <v>321030</v>
       </c>
       <c r="B147" t="str">
         <f>INDEX(TextData!B:B,MATCH(A147,TextData!A:A))</f>
-        <v>光の祭壇</v>
+        <v>蒼の祭壇</v>
       </c>
       <c r="C147">
         <v>0</v>
@@ -43872,11 +43881,11 @@
     </row>
     <row r="148" spans="1:8">
       <c r="A148">
-        <v>321050</v>
+        <v>321040</v>
       </c>
       <c r="B148" t="str">
         <f>INDEX(TextData!B:B,MATCH(A148,TextData!A:A))</f>
-        <v>月の祭壇</v>
+        <v>光の祭壇</v>
       </c>
       <c r="C148">
         <v>0</v>
@@ -43900,11 +43909,11 @@
     </row>
     <row r="149" spans="1:8">
       <c r="A149">
-        <v>322010</v>
+        <v>321050</v>
       </c>
       <c r="B149" t="str">
         <f>INDEX(TextData!B:B,MATCH(A149,TextData!A:A))</f>
-        <v>食糧庫Lv1</v>
+        <v>月の祭壇</v>
       </c>
       <c r="C149">
         <v>0</v>
@@ -43928,11 +43937,11 @@
     </row>
     <row r="150" spans="1:8">
       <c r="A150">
-        <v>322020</v>
+        <v>322010</v>
       </c>
       <c r="B150" t="str">
         <f>INDEX(TextData!B:B,MATCH(A150,TextData!A:A))</f>
-        <v>攻撃技術Lv1</v>
+        <v>食糧庫Lv1</v>
       </c>
       <c r="C150">
         <v>0</v>
@@ -43956,11 +43965,11 @@
     </row>
     <row r="151" spans="1:8">
       <c r="A151">
-        <v>322030</v>
+        <v>322020</v>
       </c>
       <c r="B151" t="str">
         <f>INDEX(TextData!B:B,MATCH(A151,TextData!A:A))</f>
-        <v>防御技術Lv1</v>
+        <v>攻撃技術Lv1</v>
       </c>
       <c r="C151">
         <v>0</v>
@@ -43984,11 +43993,11 @@
     </row>
     <row r="152" spans="1:8">
       <c r="A152">
-        <v>322040</v>
+        <v>322030</v>
       </c>
       <c r="B152" t="str">
         <f>INDEX(TextData!B:B,MATCH(A152,TextData!A:A))</f>
-        <v>詠唱技術Lv1</v>
+        <v>防御技術Lv1</v>
       </c>
       <c r="C152">
         <v>0</v>
@@ -44007,6 +44016,34 @@
         <v>0</v>
       </c>
       <c r="H152">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="153" spans="1:8">
+      <c r="A153">
+        <v>322040</v>
+      </c>
+      <c r="B153" t="str">
+        <f>INDEX(TextData!B:B,MATCH(A153,TextData!A:A))</f>
+        <v>詠唱技術Lv1</v>
+      </c>
+      <c r="C153">
+        <v>0</v>
+      </c>
+      <c r="D153" t="str">
+        <f>INDEX(Define!V:V,MATCH(C153,Define!U:U))</f>
+        <v>なし</v>
+      </c>
+      <c r="E153">
+        <v>4</v>
+      </c>
+      <c r="F153">
+        <v>0</v>
+      </c>
+      <c r="G153">
+        <v>0</v>
+      </c>
+      <c r="H153">
         <v>0</v>
       </c>
     </row>
@@ -47672,7 +47709,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AC139"/>
+  <dimension ref="A1:AC141"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13"/>
   <cols>
     <col min="3" max="3" width="1.72727272727273" customWidth="1"/>
@@ -48397,7 +48434,7 @@
         <v>618</v>
       </c>
       <c r="Y15">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="Z15" t="s">
         <v>619</v>
@@ -48423,7 +48460,7 @@
         <v>622</v>
       </c>
       <c r="Y16">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="Z16" t="s">
         <v>623</v>
@@ -48448,11 +48485,17 @@
       <c r="V17" t="s">
         <v>626</v>
       </c>
+      <c r="Y17">
+        <v>52</v>
+      </c>
+      <c r="Z17" t="s">
+        <v>627</v>
+      </c>
       <c r="AB17">
         <v>501</v>
       </c>
       <c r="AC17" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
     </row>
     <row r="18" spans="16:29">
@@ -48460,19 +48503,19 @@
         <v>2040</v>
       </c>
       <c r="Q18" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="U18">
         <v>3050</v>
       </c>
       <c r="V18" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="AB18">
         <v>502</v>
       </c>
       <c r="AC18" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
     </row>
     <row r="19" spans="16:29">
@@ -48480,19 +48523,19 @@
         <v>2110</v>
       </c>
       <c r="Q19" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="U19">
         <v>3060</v>
       </c>
       <c r="V19" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="AB19">
         <v>503</v>
       </c>
       <c r="AC19" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
     </row>
     <row r="20" spans="16:29">
@@ -48500,19 +48543,19 @@
         <v>2120</v>
       </c>
       <c r="Q20" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="U20">
         <v>4010</v>
       </c>
       <c r="V20" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="AB20">
         <v>504</v>
       </c>
       <c r="AC20" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
     </row>
     <row r="21" spans="16:29">
@@ -48520,19 +48563,19 @@
         <v>2130</v>
       </c>
       <c r="Q21" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="U21">
         <v>4020</v>
       </c>
       <c r="V21" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="AB21">
         <v>505</v>
       </c>
       <c r="AC21" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
     </row>
     <row r="22" spans="16:29">
@@ -48540,19 +48583,19 @@
         <v>3010</v>
       </c>
       <c r="Q22" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="U22">
         <v>5010</v>
       </c>
       <c r="V22" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="AB22">
         <v>506</v>
       </c>
       <c r="AC22" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
     </row>
     <row r="23" spans="16:29">
@@ -48560,19 +48603,19 @@
         <v>3020</v>
       </c>
       <c r="Q23" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="U23">
         <v>5020</v>
       </c>
       <c r="V23" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="AB23">
         <v>507</v>
       </c>
       <c r="AC23" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
     </row>
     <row r="24" spans="16:29">
@@ -48580,13 +48623,13 @@
         <v>3030</v>
       </c>
       <c r="Q24" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="U24">
         <v>5030</v>
       </c>
       <c r="V24" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="AB24">
         <v>508</v>
@@ -48600,13 +48643,13 @@
         <v>3040</v>
       </c>
       <c r="Q25" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="U25">
         <v>5040</v>
       </c>
       <c r="V25" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="AB25">
         <v>509</v>
@@ -48620,13 +48663,13 @@
         <v>3050</v>
       </c>
       <c r="Q26" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="U26">
         <v>5050</v>
       </c>
       <c r="V26" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
     </row>
     <row r="27" spans="16:22">
@@ -48634,13 +48677,13 @@
         <v>3060</v>
       </c>
       <c r="Q27" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="U27">
         <v>5060</v>
       </c>
       <c r="V27" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
     </row>
     <row r="28" spans="16:22">
@@ -48648,13 +48691,13 @@
         <v>3070</v>
       </c>
       <c r="Q28" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="U28">
         <v>5070</v>
       </c>
       <c r="V28" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
     </row>
     <row r="29" spans="16:22">
@@ -48662,13 +48705,13 @@
         <v>4010</v>
       </c>
       <c r="Q29" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="U29">
         <v>5080</v>
       </c>
       <c r="V29" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="30" spans="16:22">
@@ -48676,13 +48719,13 @@
         <v>4020</v>
       </c>
       <c r="Q30" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="U30">
         <v>5090</v>
       </c>
       <c r="V30" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
     </row>
     <row r="31" spans="16:22">
@@ -48690,13 +48733,13 @@
         <v>4030</v>
       </c>
       <c r="Q31" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="U31">
         <v>5100</v>
       </c>
       <c r="V31" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
     </row>
     <row r="32" spans="16:22">
@@ -48704,13 +48747,13 @@
         <v>4040</v>
       </c>
       <c r="Q32" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="U32">
         <v>5110</v>
       </c>
       <c r="V32" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
     </row>
     <row r="33" spans="16:22">
@@ -48718,13 +48761,13 @@
         <v>4041</v>
       </c>
       <c r="Q33" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="U33">
         <v>5120</v>
       </c>
       <c r="V33" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
     </row>
     <row r="34" spans="16:22">
@@ -48732,13 +48775,13 @@
         <v>5010</v>
       </c>
       <c r="Q34" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="U34">
         <v>5130</v>
       </c>
       <c r="V34" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
     </row>
     <row r="35" spans="16:22">
@@ -48746,13 +48789,13 @@
         <v>5011</v>
       </c>
       <c r="Q35" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="U35">
         <v>5140</v>
       </c>
       <c r="V35" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
     </row>
     <row r="36" spans="16:22">
@@ -48760,13 +48803,13 @@
         <v>5012</v>
       </c>
       <c r="Q36" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="U36">
         <v>5150</v>
       </c>
       <c r="V36" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
     </row>
     <row r="37" spans="16:22">
@@ -48774,13 +48817,13 @@
         <v>5020</v>
       </c>
       <c r="Q37" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="U37">
         <v>6010</v>
       </c>
       <c r="V37" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
     </row>
     <row r="38" spans="16:22">
@@ -48788,13 +48831,13 @@
         <v>5030</v>
       </c>
       <c r="Q38" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="U38">
         <v>6020</v>
       </c>
       <c r="V38" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
     </row>
     <row r="39" spans="16:22">
@@ -48802,13 +48845,13 @@
         <v>5040</v>
       </c>
       <c r="Q39" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="U39">
         <v>6030</v>
       </c>
       <c r="V39" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
     </row>
     <row r="40" spans="16:22">
@@ -48816,13 +48859,13 @@
         <v>5050</v>
       </c>
       <c r="Q40" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="U40">
         <v>6040</v>
       </c>
       <c r="V40" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
     </row>
     <row r="41" spans="16:22">
@@ -48830,13 +48873,13 @@
         <v>6010</v>
       </c>
       <c r="Q41" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="U41">
         <v>6050</v>
       </c>
       <c r="V41" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
     </row>
     <row r="42" spans="16:22">
@@ -48844,13 +48887,13 @@
         <v>6020</v>
       </c>
       <c r="Q42" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="U42">
         <v>6060</v>
       </c>
       <c r="V42" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
     </row>
     <row r="43" spans="16:22">
@@ -48858,13 +48901,13 @@
         <v>6030</v>
       </c>
       <c r="Q43" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="U43">
         <v>6110</v>
       </c>
       <c r="V43" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
     </row>
     <row r="44" spans="16:22">
@@ -48872,13 +48915,13 @@
         <v>6040</v>
       </c>
       <c r="Q44" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="U44">
         <v>6120</v>
       </c>
       <c r="V44" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
     </row>
     <row r="45" spans="16:22">
@@ -48886,13 +48929,13 @@
         <v>6050</v>
       </c>
       <c r="Q45" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="U45">
         <v>6130</v>
       </c>
       <c r="V45" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
     </row>
     <row r="46" spans="16:22">
@@ -48900,13 +48943,13 @@
         <v>6060</v>
       </c>
       <c r="Q46" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="U46">
         <v>6140</v>
       </c>
       <c r="V46" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
     </row>
     <row r="47" spans="16:22">
@@ -48914,13 +48957,13 @@
         <v>6070</v>
       </c>
       <c r="Q47" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="U47">
         <v>6150</v>
       </c>
       <c r="V47" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
     </row>
     <row r="48" spans="16:22">
@@ -48928,13 +48971,13 @@
         <v>6080</v>
       </c>
       <c r="Q48" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="U48">
         <v>6210</v>
       </c>
       <c r="V48" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
     </row>
     <row r="49" spans="16:22">
@@ -48942,13 +48985,13 @@
         <v>6100</v>
       </c>
       <c r="Q49" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="U49">
         <v>6220</v>
       </c>
       <c r="V49" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
     </row>
     <row r="50" spans="16:22">
@@ -48956,13 +48999,13 @@
         <v>6210</v>
       </c>
       <c r="Q50" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="U50">
         <v>6230</v>
       </c>
       <c r="V50" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
     </row>
     <row r="51" spans="16:22">
@@ -48970,13 +49013,13 @@
         <v>6310</v>
       </c>
       <c r="Q51" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="U51">
         <v>6240</v>
       </c>
       <c r="V51" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
     </row>
     <row r="52" spans="16:22">
@@ -48984,13 +49027,13 @@
         <v>7010</v>
       </c>
       <c r="Q52" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="U52">
         <v>6250</v>
       </c>
       <c r="V52" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
     </row>
     <row r="53" spans="16:22">
@@ -48998,13 +49041,13 @@
         <v>7020</v>
       </c>
       <c r="Q53" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="U53">
         <v>6310</v>
       </c>
       <c r="V53" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
     </row>
     <row r="54" spans="16:22">
@@ -49012,13 +49055,13 @@
         <v>7030</v>
       </c>
       <c r="Q54" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="U54">
         <v>6320</v>
       </c>
       <c r="V54" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
     </row>
     <row r="55" spans="16:22">
@@ -49026,13 +49069,13 @@
         <v>8010</v>
       </c>
       <c r="Q55" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="U55">
         <v>6330</v>
       </c>
       <c r="V55" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
     </row>
     <row r="56" spans="16:22">
@@ -49040,13 +49083,13 @@
         <v>8020</v>
       </c>
       <c r="Q56" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="U56">
         <v>6340</v>
       </c>
       <c r="V56" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
     </row>
     <row r="57" spans="16:22">
@@ -49054,13 +49097,13 @@
         <v>9010</v>
       </c>
       <c r="Q57" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="U57">
         <v>6350</v>
       </c>
       <c r="V57" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
     </row>
     <row r="58" spans="16:22">
@@ -49068,13 +49111,13 @@
         <v>10010</v>
       </c>
       <c r="Q58" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="U58">
         <v>7010</v>
       </c>
       <c r="V58" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
     </row>
     <row r="59" spans="16:22">
@@ -49082,13 +49125,13 @@
         <v>10020</v>
       </c>
       <c r="Q59" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="U59">
         <v>7020</v>
       </c>
       <c r="V59" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
     </row>
     <row r="60" spans="16:22">
@@ -49096,13 +49139,13 @@
         <v>11010</v>
       </c>
       <c r="Q60" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="U60">
         <v>7030</v>
       </c>
       <c r="V60" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
     </row>
     <row r="61" spans="16:22">
@@ -49110,13 +49153,13 @@
         <v>12010</v>
       </c>
       <c r="Q61" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="U61">
         <v>7040</v>
       </c>
       <c r="V61" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
     </row>
     <row r="62" spans="16:22">
@@ -49124,13 +49167,13 @@
         <v>13010</v>
       </c>
       <c r="Q62" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="U62">
         <v>7050</v>
       </c>
       <c r="V62" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
     </row>
     <row r="63" spans="16:22">
@@ -49138,13 +49181,13 @@
         <v>40010</v>
       </c>
       <c r="Q63" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="U63">
         <v>7060</v>
       </c>
       <c r="V63" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
     </row>
     <row r="64" spans="16:22">
@@ -49152,13 +49195,13 @@
         <v>40020</v>
       </c>
       <c r="Q64" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="U64">
         <v>7070</v>
       </c>
       <c r="V64" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
     </row>
     <row r="65" spans="16:22">
@@ -49166,13 +49209,13 @@
         <v>40030</v>
       </c>
       <c r="Q65" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="U65">
         <v>8010</v>
       </c>
       <c r="V65" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
     </row>
     <row r="66" spans="16:22">
@@ -49180,13 +49223,13 @@
         <v>40040</v>
       </c>
       <c r="Q66" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="U66">
         <v>8020</v>
       </c>
       <c r="V66" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
     </row>
     <row r="67" spans="16:22">
@@ -49194,13 +49237,13 @@
         <v>40050</v>
       </c>
       <c r="Q67" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="U67">
         <v>8030</v>
       </c>
       <c r="V67" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
     </row>
     <row r="68" spans="16:22">
@@ -49208,13 +49251,13 @@
         <v>40060</v>
       </c>
       <c r="Q68" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="U68">
         <v>8040</v>
       </c>
       <c r="V68" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
     </row>
     <row r="69" spans="16:22">
@@ -49222,13 +49265,13 @@
         <v>40070</v>
       </c>
       <c r="Q69" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="U69">
         <v>8050</v>
       </c>
       <c r="V69" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
     </row>
     <row r="70" spans="21:22">
@@ -49236,7 +49279,7 @@
         <v>8060</v>
       </c>
       <c r="V70" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
     </row>
     <row r="71" spans="21:22">
@@ -49244,7 +49287,7 @@
         <v>9010</v>
       </c>
       <c r="V71" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
     </row>
     <row r="72" spans="21:22">
@@ -49252,7 +49295,7 @@
         <v>9020</v>
       </c>
       <c r="V72" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
     </row>
     <row r="73" spans="21:22">
@@ -49260,7 +49303,7 @@
         <v>9030</v>
       </c>
       <c r="V73" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
     </row>
     <row r="74" spans="21:22">
@@ -49268,7 +49311,7 @@
         <v>9031</v>
       </c>
       <c r="V74" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
     </row>
     <row r="75" spans="21:22">
@@ -49276,7 +49319,7 @@
         <v>9040</v>
       </c>
       <c r="V75" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
     </row>
     <row r="76" spans="21:22">
@@ -49284,7 +49327,7 @@
         <v>9110</v>
       </c>
       <c r="V76" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
     </row>
     <row r="77" spans="21:22">
@@ -49292,7 +49335,7 @@
         <v>9120</v>
       </c>
       <c r="V77" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
     </row>
     <row r="78" spans="21:22">
@@ -49300,7 +49343,7 @@
         <v>10010</v>
       </c>
       <c r="V78" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
     </row>
     <row r="79" spans="21:22">
@@ -49308,7 +49351,7 @@
         <v>10020</v>
       </c>
       <c r="V79" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
     </row>
     <row r="80" spans="21:22">
@@ -49316,7 +49359,7 @@
         <v>10110</v>
       </c>
       <c r="V80" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
     </row>
     <row r="81" spans="21:22">
@@ -49324,7 +49367,7 @@
         <v>11010</v>
       </c>
       <c r="V81" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
     </row>
     <row r="82" spans="21:22">
@@ -49332,7 +49375,7 @@
         <v>11011</v>
       </c>
       <c r="V82" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
     </row>
     <row r="83" spans="21:22">
@@ -49340,455 +49383,471 @@
         <v>11020</v>
       </c>
       <c r="V83" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
     </row>
     <row r="84" spans="21:22">
       <c r="U84">
-        <v>12030</v>
+        <v>12010</v>
       </c>
       <c r="V84" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
     </row>
     <row r="85" spans="21:22">
       <c r="U85">
-        <v>12040</v>
+        <v>12011</v>
       </c>
       <c r="V85" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
     </row>
     <row r="86" spans="21:22">
       <c r="U86">
-        <v>12041</v>
+        <v>12030</v>
       </c>
       <c r="V86" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
     </row>
     <row r="87" spans="21:22">
       <c r="U87">
-        <v>12042</v>
+        <v>12040</v>
       </c>
       <c r="V87" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
     </row>
     <row r="88" spans="21:22">
       <c r="U88">
-        <v>12043</v>
+        <v>12041</v>
       </c>
       <c r="V88" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
     </row>
     <row r="89" spans="21:22">
       <c r="U89">
-        <v>12050</v>
+        <v>12042</v>
       </c>
       <c r="V89" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
     </row>
     <row r="90" spans="21:22">
       <c r="U90">
-        <v>12060</v>
+        <v>12043</v>
       </c>
       <c r="V90" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
     </row>
     <row r="91" spans="21:22">
       <c r="U91">
-        <v>12063</v>
+        <v>12050</v>
       </c>
       <c r="V91" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
     </row>
     <row r="92" spans="21:22">
       <c r="U92">
-        <v>12064</v>
+        <v>12060</v>
       </c>
       <c r="V92" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
     </row>
     <row r="93" spans="21:22">
       <c r="U93">
-        <v>12066</v>
+        <v>12063</v>
       </c>
       <c r="V93" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
     </row>
     <row r="94" spans="21:22">
       <c r="U94">
-        <v>12070</v>
+        <v>12064</v>
       </c>
       <c r="V94" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
     </row>
     <row r="95" spans="21:22">
       <c r="U95">
-        <v>12071</v>
+        <v>12066</v>
       </c>
       <c r="V95" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
     </row>
     <row r="96" spans="21:22">
       <c r="U96">
-        <v>12082</v>
+        <v>12070</v>
       </c>
       <c r="V96" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
     </row>
     <row r="97" spans="21:22">
       <c r="U97">
-        <v>12092</v>
+        <v>12071</v>
       </c>
       <c r="V97" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
     </row>
     <row r="98" spans="21:22">
       <c r="U98">
-        <v>13010</v>
+        <v>12082</v>
       </c>
       <c r="V98" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
     </row>
     <row r="99" spans="21:22">
       <c r="U99">
-        <v>13020</v>
+        <v>12092</v>
       </c>
       <c r="V99" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
     </row>
     <row r="100" spans="21:22">
       <c r="U100">
-        <v>14010</v>
+        <v>13010</v>
       </c>
       <c r="V100" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
     </row>
     <row r="101" spans="21:22">
       <c r="U101">
-        <v>14110</v>
+        <v>13020</v>
       </c>
       <c r="V101" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
     </row>
     <row r="102" spans="21:22">
       <c r="U102">
-        <v>14210</v>
+        <v>14010</v>
       </c>
       <c r="V102" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
     </row>
     <row r="103" spans="21:22">
       <c r="U103">
-        <v>14310</v>
+        <v>14110</v>
       </c>
       <c r="V103" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
     </row>
     <row r="104" spans="21:22">
       <c r="U104">
-        <v>14410</v>
+        <v>14210</v>
       </c>
       <c r="V104" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
     </row>
     <row r="105" spans="21:22">
       <c r="U105">
-        <v>14420</v>
+        <v>14310</v>
       </c>
       <c r="V105" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
     </row>
     <row r="106" spans="21:22">
       <c r="U106">
-        <v>14520</v>
+        <v>14410</v>
       </c>
       <c r="V106" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
     </row>
     <row r="107" spans="21:22">
       <c r="U107">
-        <v>15010</v>
+        <v>14420</v>
       </c>
       <c r="V107" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
     </row>
     <row r="108" spans="21:22">
       <c r="U108">
-        <v>15011</v>
+        <v>14520</v>
       </c>
       <c r="V108" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
     </row>
     <row r="109" spans="21:22">
       <c r="U109">
-        <v>15022</v>
+        <v>15010</v>
       </c>
       <c r="V109" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
     </row>
     <row r="110" spans="21:22">
       <c r="U110">
-        <v>16010</v>
+        <v>15011</v>
       </c>
       <c r="V110" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
     </row>
     <row r="111" spans="21:22">
       <c r="U111">
-        <v>17010</v>
+        <v>15022</v>
       </c>
       <c r="V111" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
     </row>
     <row r="112" spans="21:22">
       <c r="U112">
-        <v>17020</v>
+        <v>16010</v>
       </c>
       <c r="V112" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
     </row>
     <row r="113" spans="21:22">
       <c r="U113">
-        <v>17030</v>
+        <v>17010</v>
       </c>
       <c r="V113" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
     </row>
     <row r="114" spans="21:22">
       <c r="U114">
-        <v>17040</v>
+        <v>17020</v>
       </c>
       <c r="V114" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
     </row>
     <row r="115" spans="21:22">
       <c r="U115">
-        <v>17050</v>
+        <v>17030</v>
       </c>
       <c r="V115" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
     </row>
     <row r="116" spans="21:22">
       <c r="U116">
-        <v>17060</v>
+        <v>17040</v>
       </c>
       <c r="V116" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
     </row>
     <row r="117" spans="21:22">
       <c r="U117">
-        <v>18010</v>
+        <v>17050</v>
       </c>
       <c r="V117" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
     </row>
     <row r="118" spans="21:22">
       <c r="U118">
-        <v>18020</v>
+        <v>17060</v>
       </c>
       <c r="V118" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
     </row>
     <row r="119" spans="21:22">
       <c r="U119">
-        <v>19010</v>
+        <v>18010</v>
       </c>
       <c r="V119" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
     </row>
     <row r="120" spans="21:22">
       <c r="U120">
-        <v>19020</v>
+        <v>18020</v>
       </c>
       <c r="V120" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
     </row>
     <row r="121" spans="21:22">
       <c r="U121">
-        <v>19030</v>
+        <v>19010</v>
       </c>
       <c r="V121" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
     </row>
     <row r="122" spans="21:22">
       <c r="U122">
-        <v>20030</v>
+        <v>19020</v>
       </c>
       <c r="V122" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
     </row>
     <row r="123" spans="21:22">
       <c r="U123">
-        <v>20040</v>
+        <v>19030</v>
       </c>
       <c r="V123" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
     </row>
     <row r="124" spans="21:22">
       <c r="U124">
-        <v>20050</v>
+        <v>20030</v>
       </c>
       <c r="V124" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
     </row>
     <row r="125" spans="21:22">
       <c r="U125">
-        <v>20070</v>
+        <v>20040</v>
       </c>
       <c r="V125" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
     </row>
     <row r="126" spans="21:22">
       <c r="U126">
-        <v>20071</v>
+        <v>20050</v>
       </c>
       <c r="V126" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
     </row>
     <row r="127" spans="21:22">
       <c r="U127">
-        <v>20110</v>
+        <v>20070</v>
       </c>
       <c r="V127" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
     </row>
     <row r="128" spans="21:22">
       <c r="U128">
-        <v>20120</v>
+        <v>20071</v>
       </c>
       <c r="V128" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
     </row>
     <row r="129" spans="21:22">
       <c r="U129">
-        <v>20130</v>
+        <v>20110</v>
       </c>
       <c r="V129" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
     </row>
     <row r="130" spans="21:22">
       <c r="U130">
-        <v>20140</v>
+        <v>20120</v>
       </c>
       <c r="V130" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
     </row>
     <row r="131" spans="21:22">
       <c r="U131">
-        <v>20150</v>
+        <v>20130</v>
       </c>
       <c r="V131" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
     </row>
     <row r="132" spans="21:22">
       <c r="U132">
-        <v>20160</v>
+        <v>20140</v>
       </c>
       <c r="V132" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
     </row>
     <row r="133" spans="21:22">
       <c r="U133">
-        <v>23010</v>
+        <v>20150</v>
       </c>
       <c r="V133" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
     </row>
     <row r="134" spans="21:22">
       <c r="U134">
-        <v>24010</v>
+        <v>20160</v>
       </c>
       <c r="V134" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
     </row>
     <row r="135" spans="21:22">
       <c r="U135">
-        <v>30010</v>
+        <v>23010</v>
       </c>
       <c r="V135" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
     </row>
     <row r="136" spans="21:22">
       <c r="U136">
-        <v>30020</v>
+        <v>24010</v>
       </c>
       <c r="V136" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="137" spans="21:22">
       <c r="U137">
-        <v>40010</v>
+        <v>30010</v>
       </c>
       <c r="V137" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
     </row>
     <row r="138" spans="21:22">
       <c r="U138">
-        <v>40020</v>
+        <v>30020</v>
       </c>
       <c r="V138" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
     </row>
     <row r="139" spans="21:22">
       <c r="U139">
+        <v>40010</v>
+      </c>
+      <c r="V139" t="s">
+        <v>808</v>
+      </c>
+    </row>
+    <row r="140" spans="21:22">
+      <c r="U140">
+        <v>40020</v>
+      </c>
+      <c r="V140" t="s">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="141" spans="21:22">
+      <c r="U141">
         <v>40030</v>
       </c>
-      <c r="V139" t="s">
-        <v>807</v>
+      <c r="V141" t="s">
+        <v>810</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Data/Skills.xlsx
+++ b/Assets/Data/Skills.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="7820"/>
+    <workbookView windowWidth="19200" windowHeight="7820" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Skills" sheetId="1" r:id="rId1"/>
@@ -2673,8 +2673,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
@@ -2693,8 +2693,32 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -2707,24 +2731,30 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -2748,6 +2778,22 @@
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -2776,38 +2822,6 @@
     </font>
     <font>
       <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -2818,20 +2832,6 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -2858,13 +2858,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2876,37 +2876,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2918,7 +2888,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2936,7 +2918,103 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2948,49 +3026,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3002,43 +3038,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3049,6 +3049,15 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -3091,6 +3100,15 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -3102,24 +3120,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -3157,7 +3157,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -3166,7 +3166,7 @@
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -3175,127 +3175,127 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="22" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="22" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="24" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -36678,14 +36678,14 @@
         <v>先陣の心得</v>
       </c>
       <c r="C249">
-        <v>5020</v>
+        <v>5040</v>
       </c>
       <c r="D249" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C249,Define!P:P))</f>
-        <v>Ap回復</v>
+        <v>先制攻撃</v>
       </c>
       <c r="E249">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="F249">
         <v>0</v>

--- a/Assets/Data/Skills.xlsx
+++ b/Assets/Data/Skills.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="7820" activeTab="1"/>
+    <workbookView windowWidth="19200" windowHeight="7820"/>
   </bookViews>
   <sheets>
     <sheet name="Skills" sheetId="1" r:id="rId1"/>
@@ -2673,9 +2673,9 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -2693,17 +2693,15 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -2717,6 +2715,14 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -2725,7 +2731,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -2740,82 +2746,15 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -2831,7 +2770,68 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -2858,6 +2858,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -2870,13 +2882,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2888,19 +2918,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2912,25 +2942,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2942,13 +2960,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2966,13 +2984,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2984,7 +2996,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2996,49 +3032,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3049,15 +3049,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -3072,6 +3063,47 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -3094,8 +3126,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -3109,43 +3141,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
+      <top/>
       <bottom style="double">
-        <color theme="4"/>
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -3157,145 +3157,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="18" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -4727,6 +4727,382 @@
           </cell>
           <cell r="B167" t="str">
             <v>NA_Effekseer/NA_smoke_004</v>
+          </cell>
+        </row>
+        <row r="168">
+          <cell r="A168">
+            <v>3001</v>
+          </cell>
+          <cell r="B168" t="str">
+            <v>Genfulew_Effect/B&amp;S_MinMax_HpUp</v>
+          </cell>
+        </row>
+        <row r="169">
+          <cell r="A169">
+            <v>3002</v>
+          </cell>
+          <cell r="B169" t="str">
+            <v>Genfulew_Effect/B&amp;S_MinMax_HpDown</v>
+          </cell>
+        </row>
+        <row r="170">
+          <cell r="A170">
+            <v>3003</v>
+          </cell>
+          <cell r="B170" t="str">
+            <v>Genfulew_Effect/B&amp;S_MinMax_MpUp</v>
+          </cell>
+        </row>
+        <row r="171">
+          <cell r="A171">
+            <v>3004</v>
+          </cell>
+          <cell r="B171" t="str">
+            <v>Genfulew_Effect/B&amp;S_MinMax_MpDown</v>
+          </cell>
+        </row>
+        <row r="172">
+          <cell r="A172">
+            <v>3005</v>
+          </cell>
+          <cell r="B172" t="str">
+            <v>Genfulew_Effect/B&amp;S_MinMax_AttackUp</v>
+          </cell>
+        </row>
+        <row r="173">
+          <cell r="A173">
+            <v>3006</v>
+          </cell>
+          <cell r="B173" t="str">
+            <v>Genfulew_Effect/B&amp;S_MinMax_AttackDown</v>
+          </cell>
+        </row>
+        <row r="174">
+          <cell r="A174">
+            <v>3007</v>
+          </cell>
+          <cell r="B174" t="str">
+            <v>Genfulew_Effect/B&amp;S_MinMax_DefenseUp</v>
+          </cell>
+        </row>
+        <row r="175">
+          <cell r="A175">
+            <v>3008</v>
+          </cell>
+          <cell r="B175" t="str">
+            <v>Genfulew_Effect/B&amp;S_MinMax_DefenseDown</v>
+          </cell>
+        </row>
+        <row r="176">
+          <cell r="A176">
+            <v>3009</v>
+          </cell>
+          <cell r="B176" t="str">
+            <v>Genfulew_Effect/B&amp;S_MinMax_MagicAttackUp</v>
+          </cell>
+        </row>
+        <row r="177">
+          <cell r="A177">
+            <v>3010</v>
+          </cell>
+          <cell r="B177" t="str">
+            <v>Genfulew_Effect/B&amp;S_MinMax_MagicAttackDown</v>
+          </cell>
+        </row>
+        <row r="178">
+          <cell r="A178">
+            <v>3011</v>
+          </cell>
+          <cell r="B178" t="str">
+            <v>Genfulew_Effect/B&amp;S_MinMax_MagicDefenseUp</v>
+          </cell>
+        </row>
+        <row r="179">
+          <cell r="A179">
+            <v>3012</v>
+          </cell>
+          <cell r="B179" t="str">
+            <v>Genfulew_Effect/B&amp;S_MinMax_MagicDefenseDown</v>
+          </cell>
+        </row>
+        <row r="180">
+          <cell r="A180">
+            <v>3013</v>
+          </cell>
+          <cell r="B180" t="str">
+            <v>Genfulew_Effect/B&amp;S_MinMax_AgilityUp</v>
+          </cell>
+        </row>
+        <row r="181">
+          <cell r="A181">
+            <v>3014</v>
+          </cell>
+          <cell r="B181" t="str">
+            <v>Genfulew_Effect/B&amp;S_MinMax_AgilityDown</v>
+          </cell>
+        </row>
+        <row r="182">
+          <cell r="A182">
+            <v>3015</v>
+          </cell>
+          <cell r="B182" t="str">
+            <v>Genfulew_Effect/B&amp;S_MinMax_LuckUp</v>
+          </cell>
+        </row>
+        <row r="183">
+          <cell r="A183">
+            <v>3016</v>
+          </cell>
+          <cell r="B183" t="str">
+            <v>Genfulew_Effect/B&amp;S_MinMax_LuckDown</v>
+          </cell>
+        </row>
+        <row r="184">
+          <cell r="A184">
+            <v>3017</v>
+          </cell>
+          <cell r="B184" t="str">
+            <v>Genfulew_Effect/B&amp;S_MinMax_AllUp</v>
+          </cell>
+        </row>
+        <row r="185">
+          <cell r="A185">
+            <v>3018</v>
+          </cell>
+          <cell r="B185" t="str">
+            <v>Genfulew_Effect/B&amp;S_MinMax_AllDown</v>
+          </cell>
+        </row>
+        <row r="186">
+          <cell r="A186">
+            <v>3019</v>
+          </cell>
+          <cell r="B186" t="str">
+            <v>Genfulew_Effect/B&amp;S_MinMax_Resurrection1</v>
+          </cell>
+        </row>
+        <row r="187">
+          <cell r="A187">
+            <v>3020</v>
+          </cell>
+          <cell r="B187" t="str">
+            <v>Genfulew_Effect/B&amp;S_MinMax_Resurrection2</v>
+          </cell>
+        </row>
+        <row r="188">
+          <cell r="A188">
+            <v>3021</v>
+          </cell>
+          <cell r="B188" t="str">
+            <v>Genfulew_Effect/B&amp;S_MinMax_Resurrection3</v>
+          </cell>
+        </row>
+        <row r="189">
+          <cell r="A189">
+            <v>3022</v>
+          </cell>
+          <cell r="B189" t="str">
+            <v>Genfulew_Effect/B&amp;S_MinMax_Resurrection4</v>
+          </cell>
+        </row>
+        <row r="190">
+          <cell r="A190">
+            <v>3023</v>
+          </cell>
+          <cell r="B190" t="str">
+            <v>Genfulew_Effect/B&amp;S_MinMax_Cure</v>
+          </cell>
+        </row>
+        <row r="191">
+          <cell r="A191">
+            <v>3024</v>
+          </cell>
+          <cell r="B191" t="str">
+            <v>Genfulew_Effect/B&amp;S_MinMax_HpAbsorp</v>
+          </cell>
+        </row>
+        <row r="192">
+          <cell r="A192">
+            <v>3025</v>
+          </cell>
+          <cell r="B192" t="str">
+            <v>Genfulew_Effect/B&amp;S_MinMax_MpAbsorp</v>
+          </cell>
+        </row>
+        <row r="193">
+          <cell r="A193">
+            <v>3026</v>
+          </cell>
+          <cell r="B193" t="str">
+            <v>Genfulew_Effect/B&amp;S_MinMax_MpDamage</v>
+          </cell>
+        </row>
+        <row r="194">
+          <cell r="A194">
+            <v>3027</v>
+          </cell>
+          <cell r="B194" t="str">
+            <v>Genfulew_Effect/B&amp;S_MinMax_Regeneration1</v>
+          </cell>
+        </row>
+        <row r="195">
+          <cell r="A195">
+            <v>3028</v>
+          </cell>
+          <cell r="B195" t="str">
+            <v>Genfulew_Effect/B&amp;S_MinMax_Regeneration2</v>
+          </cell>
+        </row>
+        <row r="196">
+          <cell r="A196">
+            <v>3029</v>
+          </cell>
+          <cell r="B196" t="str">
+            <v>Genfulew_Effect/B&amp;S_MinMax_Regeneration3</v>
+          </cell>
+        </row>
+        <row r="197">
+          <cell r="A197">
+            <v>3030</v>
+          </cell>
+          <cell r="B197" t="str">
+            <v>Genfulew_Effect/B&amp;S_MinMax_Poison</v>
+          </cell>
+        </row>
+        <row r="198">
+          <cell r="A198">
+            <v>3031</v>
+          </cell>
+          <cell r="B198" t="str">
+            <v>Genfulew_Effect/B&amp;S_MinMax_Blind</v>
+          </cell>
+        </row>
+        <row r="199">
+          <cell r="A199">
+            <v>3032</v>
+          </cell>
+          <cell r="B199" t="str">
+            <v>Genfulew_Effect/B&amp;S_MinMax_Silent</v>
+          </cell>
+        </row>
+        <row r="200">
+          <cell r="A200">
+            <v>3033</v>
+          </cell>
+          <cell r="B200" t="str">
+            <v>Genfulew_Effect/B&amp;S_MinMax_Rage</v>
+          </cell>
+        </row>
+        <row r="201">
+          <cell r="A201">
+            <v>3034</v>
+          </cell>
+          <cell r="B201" t="str">
+            <v>Genfulew_Effect/B&amp;S_MinMax_Confusion</v>
+          </cell>
+        </row>
+        <row r="202">
+          <cell r="A202">
+            <v>3035</v>
+          </cell>
+          <cell r="B202" t="str">
+            <v>Genfulew_Effect/B&amp;S_MinMax_Charm</v>
+          </cell>
+        </row>
+        <row r="203">
+          <cell r="A203">
+            <v>3036</v>
+          </cell>
+          <cell r="B203" t="str">
+            <v>Genfulew_Effect/B&amp;S_MinMax_Sleep</v>
+          </cell>
+        </row>
+        <row r="204">
+          <cell r="A204">
+            <v>3037</v>
+          </cell>
+          <cell r="B204" t="str">
+            <v>Genfulew_Effect/B&amp;S_MinMax_Paralyze</v>
+          </cell>
+        </row>
+        <row r="205">
+          <cell r="A205">
+            <v>3038</v>
+          </cell>
+          <cell r="B205" t="str">
+            <v>Genfulew_Effect/B&amp;S_MinMax_Stun</v>
+          </cell>
+        </row>
+        <row r="206">
+          <cell r="A206">
+            <v>3039</v>
+          </cell>
+          <cell r="B206" t="str">
+            <v>Genfulew_Effect/B&amp;S_MinMax_Petrifaction</v>
+          </cell>
+        </row>
+        <row r="207">
+          <cell r="A207">
+            <v>3040</v>
+          </cell>
+          <cell r="B207" t="str">
+            <v>Genfulew_Effect/B&amp;S_MinMax_Death</v>
+          </cell>
+        </row>
+        <row r="208">
+          <cell r="A208">
+            <v>3041</v>
+          </cell>
+          <cell r="B208" t="str">
+            <v>Genfulew_Effect/B&amp;S_MinMax_Burn</v>
+          </cell>
+        </row>
+        <row r="209">
+          <cell r="A209">
+            <v>3042</v>
+          </cell>
+          <cell r="B209" t="str">
+            <v>Genfulew_Effect/B&amp;S_MinMax_Freeze</v>
+          </cell>
+        </row>
+        <row r="210">
+          <cell r="A210">
+            <v>3043</v>
+          </cell>
+          <cell r="B210" t="str">
+            <v>Genfulew_Effect/B&amp;S_MinMax_Reflect</v>
+          </cell>
+        </row>
+        <row r="211">
+          <cell r="A211">
+            <v>3044</v>
+          </cell>
+          <cell r="B211" t="str">
+            <v>Genfulew_Effect/B&amp;S_MinMax_Transparent</v>
+          </cell>
+        </row>
+        <row r="212">
+          <cell r="A212">
+            <v>3045</v>
+          </cell>
+          <cell r="B212" t="str">
+            <v>Genfulew_Effect/B&amp;S_MinMax_Float</v>
+          </cell>
+        </row>
+        <row r="213">
+          <cell r="A213">
+            <v>3046</v>
+          </cell>
+          <cell r="B213" t="str">
+            <v>Genfulew_Effect/B&amp;S_MinMax_Zombie</v>
+          </cell>
+        </row>
+        <row r="214">
+          <cell r="A214">
+            <v>3047</v>
+          </cell>
+          <cell r="B214" t="str">
+            <v>Genfulew_Effect/B&amp;S_MinMax_Dispel</v>
           </cell>
         </row>
       </sheetData>
@@ -6284,7 +6660,8 @@
   <cols>
     <col min="1" max="2" width="7.63636363636364" customWidth="1"/>
     <col min="3" max="3" width="19.7272727272727" customWidth="1"/>
-    <col min="6" max="7" width="15.0909090909091" customWidth="1"/>
+    <col min="6" max="6" width="15.0909090909091" customWidth="1"/>
+    <col min="7" max="7" width="25.8181818181818" customWidth="1"/>
     <col min="8" max="8" width="14.4545454545455" customWidth="1"/>
     <col min="9" max="10" width="5.54545454545455" customWidth="1"/>
     <col min="11" max="12" width="6.63636363636364" customWidth="1"/>
@@ -11032,11 +11409,11 @@
         <v>自己強化</v>
       </c>
       <c r="F59">
-        <v>51</v>
+        <v>3005</v>
       </c>
       <c r="G59" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F59,[1]Animations!A:A))</f>
-        <v>NA_Effekseer/NA_aura_001</v>
+        <v>Genfulew_Effect/B&amp;S_MinMax_AttackUp</v>
       </c>
       <c r="H59">
         <v>1</v>
@@ -11114,11 +11491,11 @@
         <v>自己強化</v>
       </c>
       <c r="F60">
-        <v>51</v>
+        <v>3005</v>
       </c>
       <c r="G60" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F60,[1]Animations!A:A))</f>
-        <v>NA_Effekseer/NA_aura_001</v>
+        <v>Genfulew_Effect/B&amp;S_MinMax_AttackUp</v>
       </c>
       <c r="H60">
         <v>1</v>
@@ -11196,11 +11573,11 @@
         <v>自己強化</v>
       </c>
       <c r="F61">
-        <v>51</v>
+        <v>3005</v>
       </c>
       <c r="G61" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F61,[1]Animations!A:A))</f>
-        <v>NA_Effekseer/NA_aura_001</v>
+        <v>Genfulew_Effect/B&amp;S_MinMax_AttackUp</v>
       </c>
       <c r="H61">
         <v>1</v>
@@ -11524,11 +11901,11 @@
         <v>自己強化</v>
       </c>
       <c r="F65">
-        <v>51</v>
+        <v>3005</v>
       </c>
       <c r="G65" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F65,[1]Animations!A:A))</f>
-        <v>NA_Effekseer/NA_aura_001</v>
+        <v>Genfulew_Effect/B&amp;S_MinMax_AttackUp</v>
       </c>
       <c r="H65">
         <v>1</v>
@@ -11606,11 +11983,11 @@
         <v>自己強化</v>
       </c>
       <c r="F66">
-        <v>51</v>
+        <v>3005</v>
       </c>
       <c r="G66" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F66,[1]Animations!A:A))</f>
-        <v>NA_Effekseer/NA_aura_001</v>
+        <v>Genfulew_Effect/B&amp;S_MinMax_AttackUp</v>
       </c>
       <c r="H66">
         <v>1</v>
@@ -11688,11 +12065,11 @@
         <v>自己強化</v>
       </c>
       <c r="F67">
-        <v>51</v>
+        <v>3005</v>
       </c>
       <c r="G67" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F67,[1]Animations!A:A))</f>
-        <v>NA_Effekseer/NA_aura_001</v>
+        <v>Genfulew_Effect/B&amp;S_MinMax_AttackUp</v>
       </c>
       <c r="H67">
         <v>1</v>

--- a/Assets/Data/Skills.xlsx
+++ b/Assets/Data/Skills.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="7820"/>
+    <workbookView windowWidth="19200" windowHeight="8270"/>
   </bookViews>
   <sheets>
     <sheet name="Skills" sheetId="1" r:id="rId1"/>
@@ -2673,8 +2673,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
@@ -2694,6 +2694,13 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
@@ -2707,17 +2714,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -2725,13 +2723,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -2745,16 +2736,16 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -2769,6 +2760,22 @@
     </font>
     <font>
       <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -2776,10 +2783,11 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -2791,8 +2799,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -2807,31 +2816,22 @@
     </font>
     <font>
       <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -2858,7 +2858,127 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2870,139 +2990,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3020,25 +3032,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3049,6 +3049,15 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -3067,13 +3076,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
       <top style="thin">
-        <color theme="4"/>
+        <color rgb="FFB2B2B2"/>
       </top>
-      <bottom style="double">
-        <color theme="4"/>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -3108,21 +3121,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
@@ -3143,9 +3141,11 @@
     <border>
       <left/>
       <right/>
-      <top/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
       <bottom style="double">
-        <color rgb="FFFF8001"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -3157,7 +3157,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -3166,7 +3166,7 @@
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -3175,127 +3175,127 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="21" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="21" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="16" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="19" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="18" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>

--- a/Assets/Data/Skills.xlsx
+++ b/Assets/Data/Skills.xlsx
@@ -2674,8 +2674,8 @@
   <numFmts count="4">
     <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -2694,7 +2694,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -2702,20 +2702,6 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -2736,9 +2722,40 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -2753,7 +2770,14 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -2767,9 +2791,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -2792,22 +2815,6 @@
     </font>
     <font>
       <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -2825,13 +2832,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -2858,13 +2858,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2876,49 +2906,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2936,7 +2924,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2948,7 +2942,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2960,7 +2984,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2978,31 +3002,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3020,13 +3020,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3038,7 +3038,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3049,15 +3049,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -3072,6 +3063,15 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -3106,6 +3106,15 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -3117,15 +3126,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -3157,145 +3157,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="18" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="18" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="14" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="21" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="21" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="16" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -4331,777 +4331,785 @@
         </row>
         <row r="118">
           <cell r="A118">
-            <v>2101</v>
+            <v>1501</v>
           </cell>
           <cell r="B118" t="str">
-            <v>tktk01/Fire2</v>
+            <v>BallsOfLight</v>
           </cell>
         </row>
         <row r="119">
           <cell r="A119">
-            <v>2102</v>
+            <v>2101</v>
           </cell>
           <cell r="B119" t="str">
-            <v>NA_Effekseer/NA_Fire_001</v>
+            <v>tktk01/Fire2</v>
           </cell>
         </row>
         <row r="120">
           <cell r="A120">
-            <v>2103</v>
+            <v>2102</v>
           </cell>
           <cell r="B120" t="str">
-            <v>NA_Effekseer/NA_sword_001</v>
+            <v>NA_Effekseer/NA_Fire_001</v>
           </cell>
         </row>
         <row r="121">
           <cell r="A121">
-            <v>2104</v>
+            <v>2103</v>
           </cell>
           <cell r="B121" t="str">
-            <v>NA_Effekseer/NA_magic_006_c1</v>
+            <v>NA_Effekseer/NA_sword_001</v>
           </cell>
         </row>
         <row r="122">
           <cell r="A122">
-            <v>2105</v>
+            <v>2104</v>
           </cell>
           <cell r="B122" t="str">
-            <v>NA_Effekseer/NA_magic_004_c1</v>
+            <v>NA_Effekseer/NA_magic_006_c1</v>
           </cell>
         </row>
         <row r="123">
           <cell r="A123">
-            <v>2106</v>
+            <v>2105</v>
           </cell>
           <cell r="B123" t="str">
-            <v>NA_Effekseer_Vol_2/NA_v2_2.5d_element reservoir_fire</v>
+            <v>NA_Effekseer/NA_magic_004_c1</v>
           </cell>
         </row>
         <row r="124">
           <cell r="A124">
-            <v>2201</v>
+            <v>2106</v>
           </cell>
           <cell r="B124" t="str">
-            <v>NA_Effekseer/NA_shooting_002</v>
+            <v>NA_Effekseer_Vol_2/NA_v2_2.5d_element reservoir_fire</v>
           </cell>
         </row>
         <row r="125">
           <cell r="A125">
-            <v>2202</v>
+            <v>2201</v>
           </cell>
           <cell r="B125" t="str">
-            <v>NA_Effekseer/NA_net_001</v>
+            <v>NA_Effekseer/NA_shooting_002</v>
           </cell>
         </row>
         <row r="126">
           <cell r="A126">
-            <v>2203</v>
+            <v>2202</v>
           </cell>
           <cell r="B126" t="str">
-            <v>NA_Effekseer/NA_status_005</v>
+            <v>NA_Effekseer/NA_net_001</v>
           </cell>
         </row>
         <row r="127">
           <cell r="A127">
-            <v>2204</v>
+            <v>2203</v>
           </cell>
           <cell r="B127" t="str">
-            <v>NA_Effekseer/NA_magic_003</v>
+            <v>NA_Effekseer/NA_status_005</v>
           </cell>
         </row>
         <row r="128">
           <cell r="A128">
-            <v>2205</v>
+            <v>2204</v>
           </cell>
           <cell r="B128" t="str">
-            <v>NA_Effekseer/NA_exchange_001</v>
+            <v>NA_Effekseer/NA_magic_003</v>
           </cell>
         </row>
         <row r="129">
           <cell r="A129">
-            <v>2206</v>
+            <v>2205</v>
           </cell>
           <cell r="B129" t="str">
-            <v>tktk01/Blow10</v>
+            <v>NA_Effekseer/NA_exchange_001</v>
           </cell>
         </row>
         <row r="130">
           <cell r="A130">
-            <v>2207</v>
+            <v>2206</v>
           </cell>
           <cell r="B130" t="str">
-            <v>NA_Effekseer/NA_net_002</v>
+            <v>tktk01/Blow10</v>
           </cell>
         </row>
         <row r="131">
           <cell r="A131">
-            <v>2208</v>
+            <v>2207</v>
           </cell>
           <cell r="B131" t="str">
-            <v>EffekseerVol_3/NA_v3_3d_element shot_electric</v>
+            <v>NA_Effekseer/NA_net_002</v>
           </cell>
         </row>
         <row r="132">
           <cell r="A132">
-            <v>2209</v>
+            <v>2208</v>
           </cell>
           <cell r="B132" t="str">
-            <v>NA_Effekseer/NA_aura_003</v>
+            <v>EffekseerVol_3/NA_v3_3d_element shot_electric</v>
           </cell>
         </row>
         <row r="133">
           <cell r="A133">
-            <v>2210</v>
+            <v>2209</v>
           </cell>
           <cell r="B133" t="str">
-            <v>NA_Effekseer/NA_magic_006_c5</v>
+            <v>NA_Effekseer/NA_aura_003</v>
           </cell>
         </row>
         <row r="134">
           <cell r="A134">
-            <v>2211</v>
+            <v>2210</v>
           </cell>
           <cell r="B134" t="str">
-            <v>NA_Effekseer_Vol_2/NA_v2_2.5d_jump move_normal</v>
+            <v>NA_Effekseer/NA_magic_006_c5</v>
           </cell>
         </row>
         <row r="135">
           <cell r="A135">
-            <v>2301</v>
+            <v>2211</v>
           </cell>
           <cell r="B135" t="str">
-            <v>NA_Effekseer/NA_slash_003_c3</v>
+            <v>NA_Effekseer_Vol_2/NA_v2_2.5d_jump move_normal</v>
           </cell>
         </row>
         <row r="136">
           <cell r="A136">
-            <v>2302</v>
+            <v>2301</v>
           </cell>
           <cell r="B136" t="str">
-            <v>tktk02/Light1</v>
+            <v>NA_Effekseer/NA_slash_003_c3</v>
           </cell>
         </row>
         <row r="137">
           <cell r="A137">
-            <v>2303</v>
+            <v>2302</v>
           </cell>
           <cell r="B137" t="str">
-            <v>tktk02/Gun2</v>
+            <v>tktk02/Light1</v>
           </cell>
         </row>
         <row r="138">
           <cell r="A138">
-            <v>2304</v>
+            <v>2303</v>
           </cell>
           <cell r="B138" t="str">
-            <v>NA_Effekseer/NA_wave_001</v>
+            <v>tktk02/Gun2</v>
           </cell>
         </row>
         <row r="139">
           <cell r="A139">
-            <v>2305</v>
+            <v>2304</v>
           </cell>
           <cell r="B139" t="str">
-            <v>NA_Effekseer/NA_magic_006</v>
+            <v>NA_Effekseer/NA_wave_001</v>
           </cell>
         </row>
         <row r="140">
           <cell r="A140">
-            <v>2306</v>
+            <v>2305</v>
           </cell>
           <cell r="B140" t="str">
-            <v>NA_Effekseer/NA_barrier_001</v>
+            <v>NA_Effekseer/NA_magic_006</v>
           </cell>
         </row>
         <row r="141">
           <cell r="A141">
-            <v>2307</v>
+            <v>2306</v>
           </cell>
           <cell r="B141" t="str">
-            <v>NA_Effekseer/NA_magic_008_c3</v>
+            <v>NA_Effekseer/NA_barrier_001</v>
           </cell>
         </row>
         <row r="142">
           <cell r="A142">
-            <v>2308</v>
+            <v>2307</v>
           </cell>
           <cell r="B142" t="str">
-            <v>EffekseerVol_3/NA_v3_3d_fairy light_1</v>
+            <v>NA_Effekseer/NA_magic_008_c3</v>
           </cell>
         </row>
         <row r="143">
           <cell r="A143">
-            <v>2309</v>
+            <v>2308</v>
           </cell>
           <cell r="B143" t="str">
-            <v>EffekseerVol_3/NA_v3_2.5d_fog_2</v>
+            <v>EffekseerVol_3/NA_v3_3d_fairy light_1</v>
           </cell>
         </row>
         <row r="144">
           <cell r="A144">
-            <v>2310</v>
+            <v>2309</v>
           </cell>
           <cell r="B144" t="str">
-            <v>NA_Effekseer/NA_magic_006_c2</v>
+            <v>EffekseerVol_3/NA_v3_2.5d_fog_2</v>
           </cell>
         </row>
         <row r="145">
           <cell r="A145">
-            <v>2311</v>
+            <v>2310</v>
           </cell>
           <cell r="B145" t="str">
-            <v>EffekseerVol_3/NA_v3_3d_residue_water</v>
+            <v>NA_Effekseer/NA_magic_006_c2</v>
           </cell>
         </row>
         <row r="146">
           <cell r="A146">
-            <v>2401</v>
+            <v>2311</v>
           </cell>
           <cell r="B146" t="str">
-            <v>NA_Effekseer/NA_magic_007</v>
+            <v>EffekseerVol_3/NA_v3_3d_residue_water</v>
           </cell>
         </row>
         <row r="147">
           <cell r="A147">
-            <v>2402</v>
+            <v>2401</v>
           </cell>
           <cell r="B147" t="str">
-            <v>tktk01/Sword7</v>
+            <v>NA_Effekseer/NA_magic_007</v>
           </cell>
         </row>
         <row r="148">
           <cell r="A148">
-            <v>2403</v>
+            <v>2402</v>
           </cell>
           <cell r="B148" t="str">
-            <v>NA_Effekseer/NA_healing_001</v>
+            <v>tktk01/Sword7</v>
           </cell>
         </row>
         <row r="149">
           <cell r="A149">
-            <v>2404</v>
+            <v>2403</v>
           </cell>
           <cell r="B149" t="str">
-            <v>tktk01/Light2</v>
+            <v>NA_Effekseer/NA_healing_001</v>
           </cell>
         </row>
         <row r="150">
           <cell r="A150">
-            <v>2405</v>
+            <v>2404</v>
           </cell>
           <cell r="B150" t="str">
-            <v>tktk02/Light3</v>
+            <v>tktk01/Light2</v>
           </cell>
         </row>
         <row r="151">
           <cell r="A151">
-            <v>2406</v>
+            <v>2405</v>
           </cell>
           <cell r="B151" t="str">
-            <v>tktk01/Cure2</v>
+            <v>tktk02/Light3</v>
           </cell>
         </row>
         <row r="152">
           <cell r="A152">
-            <v>2407</v>
+            <v>2406</v>
           </cell>
           <cell r="B152" t="str">
-            <v>NA_Effekseer/NA_aura_005</v>
+            <v>tktk01/Cure2</v>
           </cell>
         </row>
         <row r="153">
           <cell r="A153">
-            <v>2408</v>
+            <v>2407</v>
           </cell>
           <cell r="B153" t="str">
-            <v>EffekseerVol_3/NA_v3_2.5d_crash_1</v>
+            <v>NA_Effekseer/NA_aura_005</v>
           </cell>
         </row>
         <row r="154">
           <cell r="A154">
-            <v>2409</v>
+            <v>2408</v>
           </cell>
           <cell r="B154" t="str">
-            <v>EffekseerVol_3/NA_v3_2.5d_shining_5</v>
+            <v>EffekseerVol_3/NA_v3_2.5d_crash_1</v>
           </cell>
         </row>
         <row r="155">
           <cell r="A155">
-            <v>2410</v>
+            <v>2409</v>
           </cell>
           <cell r="B155" t="str">
-            <v>tktk01/Cure1</v>
+            <v>EffekseerVol_3/NA_v3_2.5d_shining_5</v>
           </cell>
         </row>
         <row r="156">
           <cell r="A156">
-            <v>2411</v>
+            <v>2410</v>
           </cell>
           <cell r="B156" t="str">
-            <v>NA_Effekseer/NA_magic_006_c7</v>
+            <v>tktk01/Cure1</v>
           </cell>
         </row>
         <row r="157">
           <cell r="A157">
-            <v>2501</v>
+            <v>2411</v>
           </cell>
           <cell r="B157" t="str">
-            <v>tktk02/Dark1</v>
+            <v>NA_Effekseer/NA_magic_006_c7</v>
           </cell>
         </row>
         <row r="158">
           <cell r="A158">
-            <v>2502</v>
+            <v>2501</v>
           </cell>
           <cell r="B158" t="str">
-            <v>NA_Effekseer/NA_wave_003</v>
+            <v>tktk02/Dark1</v>
           </cell>
         </row>
         <row r="159">
           <cell r="A159">
-            <v>2503</v>
+            <v>2502</v>
           </cell>
           <cell r="B159" t="str">
-            <v>tktk01/Dark3</v>
+            <v>NA_Effekseer/NA_wave_003</v>
           </cell>
         </row>
         <row r="160">
           <cell r="A160">
-            <v>2504</v>
+            <v>2503</v>
           </cell>
           <cell r="B160" t="str">
-            <v>NA_Effekseer/NA_magic_002</v>
+            <v>tktk01/Dark3</v>
           </cell>
         </row>
         <row r="161">
           <cell r="A161">
-            <v>2505</v>
+            <v>2504</v>
           </cell>
           <cell r="B161" t="str">
-            <v>NA_Effekseer/NA_curse_001</v>
+            <v>NA_Effekseer/NA_magic_002</v>
           </cell>
         </row>
         <row r="162">
           <cell r="A162">
-            <v>2506</v>
+            <v>2505</v>
           </cell>
           <cell r="B162" t="str">
-            <v>NA_Effekseer/NA_smoke_003_c7</v>
+            <v>NA_Effekseer/NA_curse_001</v>
           </cell>
         </row>
         <row r="163">
           <cell r="A163">
-            <v>2507</v>
+            <v>2506</v>
           </cell>
           <cell r="B163" t="str">
-            <v>NA_Effekseer/NA_magic_009</v>
+            <v>NA_Effekseer/NA_smoke_003_c7</v>
           </cell>
         </row>
         <row r="164">
           <cell r="A164">
-            <v>2508</v>
+            <v>2507</v>
           </cell>
           <cell r="B164" t="str">
-            <v>MakerEffect/Death</v>
+            <v>NA_Effekseer/NA_magic_009</v>
           </cell>
         </row>
         <row r="165">
           <cell r="A165">
-            <v>2509</v>
+            <v>2508</v>
           </cell>
           <cell r="B165" t="str">
-            <v>MakerEffect/Darkness1</v>
+            <v>MakerEffect/Death</v>
           </cell>
         </row>
         <row r="166">
           <cell r="A166">
-            <v>2510</v>
+            <v>2509</v>
           </cell>
           <cell r="B166" t="str">
-            <v>NA_Effekseer/NA_magic_006_c8</v>
+            <v>MakerEffect/Darkness1</v>
           </cell>
         </row>
         <row r="167">
           <cell r="A167">
-            <v>2511</v>
+            <v>2510</v>
           </cell>
           <cell r="B167" t="str">
-            <v>NA_Effekseer/NA_smoke_004</v>
+            <v>NA_Effekseer/NA_magic_006_c8</v>
           </cell>
         </row>
         <row r="168">
           <cell r="A168">
-            <v>3001</v>
+            <v>2511</v>
           </cell>
           <cell r="B168" t="str">
-            <v>Genfulew_Effect/B&amp;S_MinMax_HpUp</v>
+            <v>NA_Effekseer/NA_smoke_004</v>
           </cell>
         </row>
         <row r="169">
           <cell r="A169">
-            <v>3002</v>
+            <v>3001</v>
           </cell>
           <cell r="B169" t="str">
-            <v>Genfulew_Effect/B&amp;S_MinMax_HpDown</v>
+            <v>Genfulew_Effect/B&amp;S_MinMax_HpUp</v>
           </cell>
         </row>
         <row r="170">
           <cell r="A170">
-            <v>3003</v>
+            <v>3002</v>
           </cell>
           <cell r="B170" t="str">
-            <v>Genfulew_Effect/B&amp;S_MinMax_MpUp</v>
+            <v>Genfulew_Effect/B&amp;S_MinMax_HpDown</v>
           </cell>
         </row>
         <row r="171">
           <cell r="A171">
-            <v>3004</v>
+            <v>3003</v>
           </cell>
           <cell r="B171" t="str">
-            <v>Genfulew_Effect/B&amp;S_MinMax_MpDown</v>
+            <v>Genfulew_Effect/B&amp;S_MinMax_MpUp</v>
           </cell>
         </row>
         <row r="172">
           <cell r="A172">
-            <v>3005</v>
+            <v>3004</v>
           </cell>
           <cell r="B172" t="str">
-            <v>Genfulew_Effect/B&amp;S_MinMax_AttackUp</v>
+            <v>Genfulew_Effect/B&amp;S_MinMax_MpDown</v>
           </cell>
         </row>
         <row r="173">
           <cell r="A173">
-            <v>3006</v>
+            <v>3005</v>
           </cell>
           <cell r="B173" t="str">
-            <v>Genfulew_Effect/B&amp;S_MinMax_AttackDown</v>
+            <v>Genfulew_Effect/B&amp;S_MinMax_AttackUp</v>
           </cell>
         </row>
         <row r="174">
           <cell r="A174">
-            <v>3007</v>
+            <v>3006</v>
           </cell>
           <cell r="B174" t="str">
-            <v>Genfulew_Effect/B&amp;S_MinMax_DefenseUp</v>
+            <v>Genfulew_Effect/B&amp;S_MinMax_AttackDown</v>
           </cell>
         </row>
         <row r="175">
           <cell r="A175">
-            <v>3008</v>
+            <v>3007</v>
           </cell>
           <cell r="B175" t="str">
-            <v>Genfulew_Effect/B&amp;S_MinMax_DefenseDown</v>
+            <v>Genfulew_Effect/B&amp;S_MinMax_DefenseUp</v>
           </cell>
         </row>
         <row r="176">
           <cell r="A176">
-            <v>3009</v>
+            <v>3008</v>
           </cell>
           <cell r="B176" t="str">
-            <v>Genfulew_Effect/B&amp;S_MinMax_MagicAttackUp</v>
+            <v>Genfulew_Effect/B&amp;S_MinMax_DefenseDown</v>
           </cell>
         </row>
         <row r="177">
           <cell r="A177">
-            <v>3010</v>
+            <v>3009</v>
           </cell>
           <cell r="B177" t="str">
-            <v>Genfulew_Effect/B&amp;S_MinMax_MagicAttackDown</v>
+            <v>Genfulew_Effect/B&amp;S_MinMax_MagicAttackUp</v>
           </cell>
         </row>
         <row r="178">
           <cell r="A178">
-            <v>3011</v>
+            <v>3010</v>
           </cell>
           <cell r="B178" t="str">
-            <v>Genfulew_Effect/B&amp;S_MinMax_MagicDefenseUp</v>
+            <v>Genfulew_Effect/B&amp;S_MinMax_MagicAttackDown</v>
           </cell>
         </row>
         <row r="179">
           <cell r="A179">
-            <v>3012</v>
+            <v>3011</v>
           </cell>
           <cell r="B179" t="str">
-            <v>Genfulew_Effect/B&amp;S_MinMax_MagicDefenseDown</v>
+            <v>Genfulew_Effect/B&amp;S_MinMax_MagicDefenseUp</v>
           </cell>
         </row>
         <row r="180">
           <cell r="A180">
-            <v>3013</v>
+            <v>3012</v>
           </cell>
           <cell r="B180" t="str">
-            <v>Genfulew_Effect/B&amp;S_MinMax_AgilityUp</v>
+            <v>Genfulew_Effect/B&amp;S_MinMax_MagicDefenseDown</v>
           </cell>
         </row>
         <row r="181">
           <cell r="A181">
-            <v>3014</v>
+            <v>3013</v>
           </cell>
           <cell r="B181" t="str">
-            <v>Genfulew_Effect/B&amp;S_MinMax_AgilityDown</v>
+            <v>Genfulew_Effect/B&amp;S_MinMax_AgilityUp</v>
           </cell>
         </row>
         <row r="182">
           <cell r="A182">
-            <v>3015</v>
+            <v>3014</v>
           </cell>
           <cell r="B182" t="str">
-            <v>Genfulew_Effect/B&amp;S_MinMax_LuckUp</v>
+            <v>Genfulew_Effect/B&amp;S_MinMax_AgilityDown</v>
           </cell>
         </row>
         <row r="183">
           <cell r="A183">
-            <v>3016</v>
+            <v>3015</v>
           </cell>
           <cell r="B183" t="str">
-            <v>Genfulew_Effect/B&amp;S_MinMax_LuckDown</v>
+            <v>Genfulew_Effect/B&amp;S_MinMax_LuckUp</v>
           </cell>
         </row>
         <row r="184">
           <cell r="A184">
-            <v>3017</v>
+            <v>3016</v>
           </cell>
           <cell r="B184" t="str">
-            <v>Genfulew_Effect/B&amp;S_MinMax_AllUp</v>
+            <v>Genfulew_Effect/B&amp;S_MinMax_LuckDown</v>
           </cell>
         </row>
         <row r="185">
           <cell r="A185">
-            <v>3018</v>
+            <v>3017</v>
           </cell>
           <cell r="B185" t="str">
-            <v>Genfulew_Effect/B&amp;S_MinMax_AllDown</v>
+            <v>Genfulew_Effect/B&amp;S_MinMax_AllUp</v>
           </cell>
         </row>
         <row r="186">
           <cell r="A186">
-            <v>3019</v>
+            <v>3018</v>
           </cell>
           <cell r="B186" t="str">
-            <v>Genfulew_Effect/B&amp;S_MinMax_Resurrection1</v>
+            <v>Genfulew_Effect/B&amp;S_MinMax_AllDown</v>
           </cell>
         </row>
         <row r="187">
           <cell r="A187">
-            <v>3020</v>
+            <v>3019</v>
           </cell>
           <cell r="B187" t="str">
-            <v>Genfulew_Effect/B&amp;S_MinMax_Resurrection2</v>
+            <v>Genfulew_Effect/B&amp;S_MinMax_Resurrection1</v>
           </cell>
         </row>
         <row r="188">
           <cell r="A188">
-            <v>3021</v>
+            <v>3020</v>
           </cell>
           <cell r="B188" t="str">
-            <v>Genfulew_Effect/B&amp;S_MinMax_Resurrection3</v>
+            <v>Genfulew_Effect/B&amp;S_MinMax_Resurrection2</v>
           </cell>
         </row>
         <row r="189">
           <cell r="A189">
-            <v>3022</v>
+            <v>3021</v>
           </cell>
           <cell r="B189" t="str">
-            <v>Genfulew_Effect/B&amp;S_MinMax_Resurrection4</v>
+            <v>Genfulew_Effect/B&amp;S_MinMax_Resurrection3</v>
           </cell>
         </row>
         <row r="190">
           <cell r="A190">
-            <v>3023</v>
+            <v>3022</v>
           </cell>
           <cell r="B190" t="str">
-            <v>Genfulew_Effect/B&amp;S_MinMax_Cure</v>
+            <v>Genfulew_Effect/B&amp;S_MinMax_Resurrection4</v>
           </cell>
         </row>
         <row r="191">
           <cell r="A191">
-            <v>3024</v>
+            <v>3023</v>
           </cell>
           <cell r="B191" t="str">
-            <v>Genfulew_Effect/B&amp;S_MinMax_HpAbsorp</v>
+            <v>Genfulew_Effect/B&amp;S_MinMax_Cure</v>
           </cell>
         </row>
         <row r="192">
           <cell r="A192">
-            <v>3025</v>
+            <v>3024</v>
           </cell>
           <cell r="B192" t="str">
-            <v>Genfulew_Effect/B&amp;S_MinMax_MpAbsorp</v>
+            <v>Genfulew_Effect/B&amp;S_MinMax_HpAbsorp</v>
           </cell>
         </row>
         <row r="193">
           <cell r="A193">
-            <v>3026</v>
+            <v>3025</v>
           </cell>
           <cell r="B193" t="str">
-            <v>Genfulew_Effect/B&amp;S_MinMax_MpDamage</v>
+            <v>Genfulew_Effect/B&amp;S_MinMax_MpAbsorp</v>
           </cell>
         </row>
         <row r="194">
           <cell r="A194">
-            <v>3027</v>
+            <v>3026</v>
           </cell>
           <cell r="B194" t="str">
-            <v>Genfulew_Effect/B&amp;S_MinMax_Regeneration1</v>
+            <v>Genfulew_Effect/B&amp;S_MinMax_MpDamage</v>
           </cell>
         </row>
         <row r="195">
           <cell r="A195">
-            <v>3028</v>
+            <v>3027</v>
           </cell>
           <cell r="B195" t="str">
-            <v>Genfulew_Effect/B&amp;S_MinMax_Regeneration2</v>
+            <v>Genfulew_Effect/B&amp;S_MinMax_Regeneration1</v>
           </cell>
         </row>
         <row r="196">
           <cell r="A196">
-            <v>3029</v>
+            <v>3028</v>
           </cell>
           <cell r="B196" t="str">
-            <v>Genfulew_Effect/B&amp;S_MinMax_Regeneration3</v>
+            <v>Genfulew_Effect/B&amp;S_MinMax_Regeneration2</v>
           </cell>
         </row>
         <row r="197">
           <cell r="A197">
-            <v>3030</v>
+            <v>3029</v>
           </cell>
           <cell r="B197" t="str">
-            <v>Genfulew_Effect/B&amp;S_MinMax_Poison</v>
+            <v>Genfulew_Effect/B&amp;S_MinMax_Regeneration3</v>
           </cell>
         </row>
         <row r="198">
           <cell r="A198">
-            <v>3031</v>
+            <v>3030</v>
           </cell>
           <cell r="B198" t="str">
-            <v>Genfulew_Effect/B&amp;S_MinMax_Blind</v>
+            <v>Genfulew_Effect/B&amp;S_MinMax_Poison</v>
           </cell>
         </row>
         <row r="199">
           <cell r="A199">
-            <v>3032</v>
+            <v>3031</v>
           </cell>
           <cell r="B199" t="str">
-            <v>Genfulew_Effect/B&amp;S_MinMax_Silent</v>
+            <v>Genfulew_Effect/B&amp;S_MinMax_Blind</v>
           </cell>
         </row>
         <row r="200">
           <cell r="A200">
-            <v>3033</v>
+            <v>3032</v>
           </cell>
           <cell r="B200" t="str">
-            <v>Genfulew_Effect/B&amp;S_MinMax_Rage</v>
+            <v>Genfulew_Effect/B&amp;S_MinMax_Silent</v>
           </cell>
         </row>
         <row r="201">
           <cell r="A201">
-            <v>3034</v>
+            <v>3033</v>
           </cell>
           <cell r="B201" t="str">
-            <v>Genfulew_Effect/B&amp;S_MinMax_Confusion</v>
+            <v>Genfulew_Effect/B&amp;S_MinMax_Rage</v>
           </cell>
         </row>
         <row r="202">
           <cell r="A202">
-            <v>3035</v>
+            <v>3034</v>
           </cell>
           <cell r="B202" t="str">
-            <v>Genfulew_Effect/B&amp;S_MinMax_Charm</v>
+            <v>Genfulew_Effect/B&amp;S_MinMax_Confusion</v>
           </cell>
         </row>
         <row r="203">
           <cell r="A203">
-            <v>3036</v>
+            <v>3035</v>
           </cell>
           <cell r="B203" t="str">
-            <v>Genfulew_Effect/B&amp;S_MinMax_Sleep</v>
+            <v>Genfulew_Effect/B&amp;S_MinMax_Charm</v>
           </cell>
         </row>
         <row r="204">
           <cell r="A204">
-            <v>3037</v>
+            <v>3036</v>
           </cell>
           <cell r="B204" t="str">
-            <v>Genfulew_Effect/B&amp;S_MinMax_Paralyze</v>
+            <v>Genfulew_Effect/B&amp;S_MinMax_Sleep</v>
           </cell>
         </row>
         <row r="205">
           <cell r="A205">
-            <v>3038</v>
+            <v>3037</v>
           </cell>
           <cell r="B205" t="str">
-            <v>Genfulew_Effect/B&amp;S_MinMax_Stun</v>
+            <v>Genfulew_Effect/B&amp;S_MinMax_Paralyze</v>
           </cell>
         </row>
         <row r="206">
           <cell r="A206">
-            <v>3039</v>
+            <v>3038</v>
           </cell>
           <cell r="B206" t="str">
-            <v>Genfulew_Effect/B&amp;S_MinMax_Petrifaction</v>
+            <v>Genfulew_Effect/B&amp;S_MinMax_Stun</v>
           </cell>
         </row>
         <row r="207">
           <cell r="A207">
-            <v>3040</v>
+            <v>3039</v>
           </cell>
           <cell r="B207" t="str">
-            <v>Genfulew_Effect/B&amp;S_MinMax_Death</v>
+            <v>Genfulew_Effect/B&amp;S_MinMax_Petrifaction</v>
           </cell>
         </row>
         <row r="208">
           <cell r="A208">
-            <v>3041</v>
+            <v>3040</v>
           </cell>
           <cell r="B208" t="str">
-            <v>Genfulew_Effect/B&amp;S_MinMax_Burn</v>
+            <v>Genfulew_Effect/B&amp;S_MinMax_Death</v>
           </cell>
         </row>
         <row r="209">
           <cell r="A209">
-            <v>3042</v>
+            <v>3041</v>
           </cell>
           <cell r="B209" t="str">
-            <v>Genfulew_Effect/B&amp;S_MinMax_Freeze</v>
+            <v>Genfulew_Effect/B&amp;S_MinMax_Burn</v>
           </cell>
         </row>
         <row r="210">
           <cell r="A210">
-            <v>3043</v>
+            <v>3042</v>
           </cell>
           <cell r="B210" t="str">
-            <v>Genfulew_Effect/B&amp;S_MinMax_Reflect</v>
+            <v>Genfulew_Effect/B&amp;S_MinMax_Freeze</v>
           </cell>
         </row>
         <row r="211">
           <cell r="A211">
-            <v>3044</v>
+            <v>3043</v>
           </cell>
           <cell r="B211" t="str">
-            <v>Genfulew_Effect/B&amp;S_MinMax_Transparent</v>
+            <v>Genfulew_Effect/B&amp;S_MinMax_Reflect</v>
           </cell>
         </row>
         <row r="212">
           <cell r="A212">
-            <v>3045</v>
+            <v>3044</v>
           </cell>
           <cell r="B212" t="str">
-            <v>Genfulew_Effect/B&amp;S_MinMax_Float</v>
+            <v>Genfulew_Effect/B&amp;S_MinMax_Transparent</v>
           </cell>
         </row>
         <row r="213">
           <cell r="A213">
-            <v>3046</v>
+            <v>3045</v>
           </cell>
           <cell r="B213" t="str">
-            <v>Genfulew_Effect/B&amp;S_MinMax_Zombie</v>
+            <v>Genfulew_Effect/B&amp;S_MinMax_Float</v>
           </cell>
         </row>
         <row r="214">
           <cell r="A214">
+            <v>3046</v>
+          </cell>
+          <cell r="B214" t="str">
+            <v>Genfulew_Effect/B&amp;S_MinMax_Zombie</v>
+          </cell>
+        </row>
+        <row r="215">
+          <cell r="A215">
             <v>3047</v>
           </cell>
-          <cell r="B214" t="str">
+          <cell r="B215" t="str">
             <v>Genfulew_Effect/B&amp;S_MinMax_Dispel</v>
           </cell>
         </row>
@@ -6661,7 +6669,7 @@
     <col min="1" max="2" width="7.63636363636364" customWidth="1"/>
     <col min="3" max="3" width="19.7272727272727" customWidth="1"/>
     <col min="6" max="6" width="15.0909090909091" customWidth="1"/>
-    <col min="7" max="7" width="25.8181818181818" customWidth="1"/>
+    <col min="7" max="7" width="37.6363636363636" customWidth="1"/>
     <col min="8" max="8" width="14.4545454545455" customWidth="1"/>
     <col min="9" max="10" width="5.54545454545455" customWidth="1"/>
     <col min="11" max="12" width="6.63636363636364" customWidth="1"/>
@@ -7645,11 +7653,11 @@
         <v>精神</v>
       </c>
       <c r="F13">
-        <v>51</v>
+        <v>3005</v>
       </c>
       <c r="G13" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F13,[1]Animations!A:A))</f>
-        <v>NA_Effekseer/NA_aura_001</v>
+        <v>Genfulew_Effect/B&amp;S_MinMax_AttackUp</v>
       </c>
       <c r="H13">
         <v>1</v>
@@ -7727,11 +7735,11 @@
         <v>元素</v>
       </c>
       <c r="F14">
-        <v>101</v>
+        <v>2104</v>
       </c>
       <c r="G14" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F14,[1]Animations!A:A))</f>
-        <v>FireOne1</v>
+        <v>NA_Effekseer/NA_magic_006_c1</v>
       </c>
       <c r="H14">
         <v>1</v>
@@ -7809,11 +7817,11 @@
         <v>元素</v>
       </c>
       <c r="F15">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G15" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F15,[1]Animations!A:A))</f>
-        <v>FireOne1</v>
+        <v>FireOne2</v>
       </c>
       <c r="H15">
         <v>1</v>
@@ -7973,11 +7981,11 @@
         <v>元素</v>
       </c>
       <c r="F17">
-        <v>51</v>
+        <v>3005</v>
       </c>
       <c r="G17" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F17,[1]Animations!A:A))</f>
-        <v>NA_Effekseer/NA_aura_001</v>
+        <v>Genfulew_Effect/B&amp;S_MinMax_AttackUp</v>
       </c>
       <c r="H17">
         <v>1</v>
@@ -8137,11 +8145,11 @@
         <v>精神</v>
       </c>
       <c r="F19">
-        <v>51</v>
+        <v>2203</v>
       </c>
       <c r="G19" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F19,[1]Animations!A:A))</f>
-        <v>NA_Effekseer/NA_aura_001</v>
+        <v>NA_Effekseer/NA_status_005</v>
       </c>
       <c r="H19">
         <v>1</v>
@@ -8219,11 +8227,11 @@
         <v>理術</v>
       </c>
       <c r="F20">
-        <v>201</v>
+        <v>2204</v>
       </c>
       <c r="G20" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F20,[1]Animations!A:A))</f>
-        <v>ThunderOne1</v>
+        <v>NA_Effekseer/NA_magic_003</v>
       </c>
       <c r="H20">
         <v>1</v>
@@ -8301,11 +8309,11 @@
         <v>元素</v>
       </c>
       <c r="F21">
-        <v>51</v>
+        <v>2205</v>
       </c>
       <c r="G21" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F21,[1]Animations!A:A))</f>
-        <v>NA_Effekseer/NA_aura_001</v>
+        <v>NA_Effekseer/NA_exchange_001</v>
       </c>
       <c r="H21">
         <v>1</v>
@@ -8547,11 +8555,11 @@
         <v>元素</v>
       </c>
       <c r="F24">
-        <v>51</v>
+        <v>1109</v>
       </c>
       <c r="G24" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F24,[1]Animations!A:A))</f>
-        <v>NA_Effekseer/NA_aura_001</v>
+        <v>Flash</v>
       </c>
       <c r="H24">
         <v>1</v>
@@ -8875,11 +8883,11 @@
         <v>光</v>
       </c>
       <c r="F28">
-        <v>301</v>
+        <v>2302</v>
       </c>
       <c r="G28" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F28,[1]Animations!A:A))</f>
-        <v>IceOne1</v>
+        <v>tktk02/Light1</v>
       </c>
       <c r="H28">
         <v>1</v>
@@ -8957,11 +8965,11 @@
         <v>精神</v>
       </c>
       <c r="F29">
-        <v>51</v>
+        <v>3007</v>
       </c>
       <c r="G29" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F29,[1]Animations!A:A))</f>
-        <v>NA_Effekseer/NA_aura_001</v>
+        <v>Genfulew_Effect/B&amp;S_MinMax_DefenseUp</v>
       </c>
       <c r="H29">
         <v>1</v>
@@ -9039,11 +9047,11 @@
         <v>理術</v>
       </c>
       <c r="F30">
-        <v>61</v>
+        <v>2304</v>
       </c>
       <c r="G30" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F30,[1]Animations!A:A))</f>
-        <v>NA_Effekseer/NA_aura_002</v>
+        <v>NA_Effekseer/NA_wave_001</v>
       </c>
       <c r="H30">
         <v>1</v>
@@ -9121,11 +9129,11 @@
         <v>理術</v>
       </c>
       <c r="F31">
-        <v>301</v>
+        <v>2305</v>
       </c>
       <c r="G31" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F31,[1]Animations!A:A))</f>
-        <v>IceOne1</v>
+        <v>NA_Effekseer/NA_magic_006</v>
       </c>
       <c r="H31">
         <v>1</v>
@@ -9203,11 +9211,11 @@
         <v>理術</v>
       </c>
       <c r="F32">
-        <v>301</v>
+        <v>2310</v>
       </c>
       <c r="G32" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F32,[1]Animations!A:A))</f>
-        <v>IceOne1</v>
+        <v>NA_Effekseer/NA_magic_006_c2</v>
       </c>
       <c r="H32">
         <v>1</v>
@@ -9285,11 +9293,11 @@
         <v>精神</v>
       </c>
       <c r="F33">
-        <v>51</v>
+        <v>1104</v>
       </c>
       <c r="G33" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F33,[1]Animations!A:A))</f>
-        <v>NA_Effekseer/NA_aura_001</v>
+        <v>Fog</v>
       </c>
       <c r="H33">
         <v>1</v>
@@ -9367,11 +9375,11 @@
         <v>精神</v>
       </c>
       <c r="F34">
-        <v>51</v>
+        <v>3007</v>
       </c>
       <c r="G34" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F34,[1]Animations!A:A))</f>
-        <v>NA_Effekseer/NA_aura_001</v>
+        <v>Genfulew_Effect/B&amp;S_MinMax_DefenseUp</v>
       </c>
       <c r="H34">
         <v>1</v>
@@ -9449,11 +9457,11 @@
         <v>元素</v>
       </c>
       <c r="F35">
-        <v>401</v>
+        <v>2401</v>
       </c>
       <c r="G35" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F35,[1]Animations!A:A))</f>
-        <v>LightOne1</v>
+        <v>NA_Effekseer/NA_magic_007</v>
       </c>
       <c r="H35">
         <v>1</v>
@@ -9531,11 +9539,11 @@
         <v>元素</v>
       </c>
       <c r="F36">
-        <v>401</v>
+        <v>2402</v>
       </c>
       <c r="G36" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F36,[1]Animations!A:A))</f>
-        <v>LightOne1</v>
+        <v>tktk01/Sword7</v>
       </c>
       <c r="H36">
         <v>1</v>
@@ -9613,11 +9621,11 @@
         <v>光</v>
       </c>
       <c r="F37">
-        <v>21</v>
+        <v>2403</v>
       </c>
       <c r="G37" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F37,[1]Animations!A:A))</f>
-        <v>tktk01/Magic2</v>
+        <v>NA_Effekseer/NA_healing_001</v>
       </c>
       <c r="H37">
         <v>1</v>
@@ -9777,11 +9785,11 @@
         <v>光</v>
       </c>
       <c r="F39">
-        <v>21</v>
+        <v>2410</v>
       </c>
       <c r="G39" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F39,[1]Animations!A:A))</f>
-        <v>tktk01/Magic2</v>
+        <v>tktk01/Cure1</v>
       </c>
       <c r="H39">
         <v>1</v>
@@ -9859,11 +9867,11 @@
         <v>光</v>
       </c>
       <c r="F40">
-        <v>21</v>
+        <v>2410</v>
       </c>
       <c r="G40" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F40,[1]Animations!A:A))</f>
-        <v>tktk01/Magic2</v>
+        <v>tktk01/Cure1</v>
       </c>
       <c r="H40">
         <v>1</v>
@@ -9941,11 +9949,11 @@
         <v>光</v>
       </c>
       <c r="F41">
-        <v>21</v>
+        <v>3023</v>
       </c>
       <c r="G41" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F41,[1]Animations!A:A))</f>
-        <v>tktk01/Magic2</v>
+        <v>Genfulew_Effect/B&amp;S_MinMax_Cure</v>
       </c>
       <c r="H41">
         <v>1</v>
@@ -10023,11 +10031,11 @@
         <v>光</v>
       </c>
       <c r="F42">
-        <v>51</v>
+        <v>3007</v>
       </c>
       <c r="G42" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F42,[1]Animations!A:A))</f>
-        <v>NA_Effekseer/NA_aura_001</v>
+        <v>Genfulew_Effect/B&amp;S_MinMax_DefenseUp</v>
       </c>
       <c r="H42">
         <v>1</v>
@@ -10105,11 +10113,11 @@
         <v>超次元</v>
       </c>
       <c r="F43">
-        <v>501</v>
+        <v>2501</v>
       </c>
       <c r="G43" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F43,[1]Animations!A:A))</f>
-        <v>DarknessOne1</v>
+        <v>tktk02/Dark1</v>
       </c>
       <c r="H43">
         <v>1</v>
@@ -10187,11 +10195,11 @@
         <v>超次元</v>
       </c>
       <c r="F44">
-        <v>501</v>
+        <v>2502</v>
       </c>
       <c r="G44" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F44,[1]Animations!A:A))</f>
-        <v>DarknessOne1</v>
+        <v>NA_Effekseer/NA_wave_003</v>
       </c>
       <c r="H44">
         <v>1</v>
@@ -10269,11 +10277,11 @@
         <v>超次元</v>
       </c>
       <c r="F45">
-        <v>501</v>
+        <v>2503</v>
       </c>
       <c r="G45" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F45,[1]Animations!A:A))</f>
-        <v>DarknessOne1</v>
+        <v>tktk01/Dark3</v>
       </c>
       <c r="H45">
         <v>1</v>
@@ -10433,11 +10441,11 @@
         <v>理術</v>
       </c>
       <c r="F47">
-        <v>501</v>
+        <v>2505</v>
       </c>
       <c r="G47" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F47,[1]Animations!A:A))</f>
-        <v>DarknessOne1</v>
+        <v>NA_Effekseer/NA_curse_001</v>
       </c>
       <c r="H47">
         <v>1</v>
@@ -10515,11 +10523,11 @@
         <v>理術</v>
       </c>
       <c r="F48">
-        <v>61</v>
+        <v>2510</v>
       </c>
       <c r="G48" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F48,[1]Animations!A:A))</f>
-        <v>NA_Effekseer/NA_aura_002</v>
+        <v>NA_Effekseer/NA_magic_006_c8</v>
       </c>
       <c r="H48">
         <v>1</v>
@@ -10597,11 +10605,11 @@
         <v>超次元</v>
       </c>
       <c r="F49">
-        <v>61</v>
+        <v>2511</v>
       </c>
       <c r="G49" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F49,[1]Animations!A:A))</f>
-        <v>NA_Effekseer/NA_aura_002</v>
+        <v>NA_Effekseer/NA_smoke_004</v>
       </c>
       <c r="H49">
         <v>1</v>
@@ -10679,11 +10687,11 @@
         <v>超次元</v>
       </c>
       <c r="F50">
-        <v>501</v>
+        <v>3030</v>
       </c>
       <c r="G50" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F50,[1]Animations!A:A))</f>
-        <v>DarknessOne1</v>
+        <v>Genfulew_Effect/B&amp;S_MinMax_Poison</v>
       </c>
       <c r="H50">
         <v>1</v>
@@ -11655,11 +11663,11 @@
         <v>自己強化</v>
       </c>
       <c r="F62">
-        <v>51</v>
+        <v>1109</v>
       </c>
       <c r="G62" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F62,[1]Animations!A:A))</f>
-        <v>NA_Effekseer/NA_aura_001</v>
+        <v>Flash</v>
       </c>
       <c r="H62">
         <v>1</v>
@@ -11737,11 +11745,11 @@
         <v>自己強化</v>
       </c>
       <c r="F63">
-        <v>51</v>
+        <v>1109</v>
       </c>
       <c r="G63" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F63,[1]Animations!A:A))</f>
-        <v>NA_Effekseer/NA_aura_001</v>
+        <v>Flash</v>
       </c>
       <c r="H63">
         <v>1</v>
@@ -11819,11 +11827,11 @@
         <v>自己強化</v>
       </c>
       <c r="F64">
-        <v>51</v>
+        <v>1109</v>
       </c>
       <c r="G64" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F64,[1]Animations!A:A))</f>
-        <v>NA_Effekseer/NA_aura_001</v>
+        <v>Flash</v>
       </c>
       <c r="H64">
         <v>1</v>
@@ -12147,11 +12155,11 @@
         <v>自己強化</v>
       </c>
       <c r="F68">
-        <v>51</v>
+        <v>1501</v>
       </c>
       <c r="G68" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F68,[1]Animations!A:A))</f>
-        <v>NA_Effekseer/NA_aura_001</v>
+        <v>BallsOfLight</v>
       </c>
       <c r="H68">
         <v>1</v>
@@ -12229,11 +12237,11 @@
         <v>自己強化</v>
       </c>
       <c r="F69">
-        <v>51</v>
+        <v>1501</v>
       </c>
       <c r="G69" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F69,[1]Animations!A:A))</f>
-        <v>NA_Effekseer/NA_aura_001</v>
+        <v>BallsOfLight</v>
       </c>
       <c r="H69">
         <v>1</v>
@@ -12311,11 +12319,11 @@
         <v>自己強化</v>
       </c>
       <c r="F70">
-        <v>51</v>
+        <v>1501</v>
       </c>
       <c r="G70" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F70,[1]Animations!A:A))</f>
-        <v>NA_Effekseer/NA_aura_001</v>
+        <v>BallsOfLight</v>
       </c>
       <c r="H70">
         <v>1</v>
@@ -12393,11 +12401,11 @@
         <v>自己強化</v>
       </c>
       <c r="F71">
-        <v>51</v>
+        <v>1501</v>
       </c>
       <c r="G71" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F71,[1]Animations!A:A))</f>
-        <v>NA_Effekseer/NA_aura_001</v>
+        <v>BallsOfLight</v>
       </c>
       <c r="H71">
         <v>1</v>
@@ -12475,11 +12483,11 @@
         <v>自己強化</v>
       </c>
       <c r="F72">
-        <v>51</v>
+        <v>1501</v>
       </c>
       <c r="G72" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F72,[1]Animations!A:A))</f>
-        <v>NA_Effekseer/NA_aura_001</v>
+        <v>BallsOfLight</v>
       </c>
       <c r="H72">
         <v>1</v>
@@ -12557,11 +12565,11 @@
         <v>自己強化</v>
       </c>
       <c r="F73">
-        <v>201</v>
+        <v>1109</v>
       </c>
       <c r="G73" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F73,[1]Animations!A:A))</f>
-        <v>ThunderOne1</v>
+        <v>Flash</v>
       </c>
       <c r="H73">
         <v>1</v>
@@ -12639,11 +12647,11 @@
         <v>自己強化</v>
       </c>
       <c r="F74">
-        <v>51</v>
+        <v>3005</v>
       </c>
       <c r="G74" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F74,[1]Animations!A:A))</f>
-        <v>NA_Effekseer/NA_aura_001</v>
+        <v>Genfulew_Effect/B&amp;S_MinMax_AttackUp</v>
       </c>
       <c r="H74">
         <v>1</v>
@@ -12721,11 +12729,11 @@
         <v>自己強化</v>
       </c>
       <c r="F75">
-        <v>61</v>
+        <v>3006</v>
       </c>
       <c r="G75" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F75,[1]Animations!A:A))</f>
-        <v>NA_Effekseer/NA_aura_002</v>
+        <v>Genfulew_Effect/B&amp;S_MinMax_AttackDown</v>
       </c>
       <c r="H75">
         <v>1</v>
@@ -12803,11 +12811,11 @@
         <v>自己強化</v>
       </c>
       <c r="F76">
-        <v>201</v>
+        <v>1501</v>
       </c>
       <c r="G76" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F76,[1]Animations!A:A))</f>
-        <v>ThunderOne1</v>
+        <v>BallsOfLight</v>
       </c>
       <c r="H76">
         <v>1</v>
@@ -12885,11 +12893,11 @@
         <v>自己強化</v>
       </c>
       <c r="F77">
-        <v>51</v>
+        <v>1501</v>
       </c>
       <c r="G77" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F77,[1]Animations!A:A))</f>
-        <v>NA_Effekseer/NA_aura_001</v>
+        <v>BallsOfLight</v>
       </c>
       <c r="H77">
         <v>1</v>
@@ -12967,11 +12975,11 @@
         <v>自己強化</v>
       </c>
       <c r="F78">
-        <v>51</v>
+        <v>3007</v>
       </c>
       <c r="G78" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F78,[1]Animations!A:A))</f>
-        <v>NA_Effekseer/NA_aura_001</v>
+        <v>Genfulew_Effect/B&amp;S_MinMax_DefenseUp</v>
       </c>
       <c r="H78">
         <v>1</v>
@@ -13049,11 +13057,11 @@
         <v>自己強化</v>
       </c>
       <c r="F79">
-        <v>21</v>
+        <v>803</v>
       </c>
       <c r="G79" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F79,[1]Animations!A:A))</f>
-        <v>tktk01/Magic2</v>
+        <v>Powerup3</v>
       </c>
       <c r="H79">
         <v>1</v>
@@ -13131,11 +13139,11 @@
         <v>自己強化</v>
       </c>
       <c r="F80">
-        <v>51</v>
+        <v>3023</v>
       </c>
       <c r="G80" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F80,[1]Animations!A:A))</f>
-        <v>NA_Effekseer/NA_aura_001</v>
+        <v>Genfulew_Effect/B&amp;S_MinMax_Cure</v>
       </c>
       <c r="H80">
         <v>1</v>
@@ -13213,11 +13221,11 @@
         <v>自己強化</v>
       </c>
       <c r="F81">
-        <v>51</v>
+        <v>3007</v>
       </c>
       <c r="G81" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F81,[1]Animations!A:A))</f>
-        <v>NA_Effekseer/NA_aura_001</v>
+        <v>Genfulew_Effect/B&amp;S_MinMax_DefenseUp</v>
       </c>
       <c r="H81">
         <v>1</v>
@@ -13295,11 +13303,11 @@
         <v>自己強化</v>
       </c>
       <c r="F82">
-        <v>51</v>
+        <v>1109</v>
       </c>
       <c r="G82" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F82,[1]Animations!A:A))</f>
-        <v>NA_Effekseer/NA_aura_001</v>
+        <v>Flash</v>
       </c>
       <c r="H82">
         <v>1</v>
@@ -13377,11 +13385,11 @@
         <v>自己強化</v>
       </c>
       <c r="F83">
-        <v>51</v>
+        <v>1109</v>
       </c>
       <c r="G83" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F83,[1]Animations!A:A))</f>
-        <v>NA_Effekseer/NA_aura_001</v>
+        <v>Flash</v>
       </c>
       <c r="H83">
         <v>1</v>
@@ -13459,11 +13467,11 @@
         <v>自己強化</v>
       </c>
       <c r="F84">
-        <v>51</v>
+        <v>1024</v>
       </c>
       <c r="G84" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F84,[1]Animations!A:A))</f>
-        <v>NA_Effekseer/NA_aura_001</v>
+        <v>PierceIce</v>
       </c>
       <c r="H84">
         <v>1</v>
@@ -13541,11 +13549,11 @@
         <v>自己強化</v>
       </c>
       <c r="F85">
-        <v>51</v>
+        <v>3024</v>
       </c>
       <c r="G85" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F85,[1]Animations!A:A))</f>
-        <v>NA_Effekseer/NA_aura_001</v>
+        <v>Genfulew_Effect/B&amp;S_MinMax_HpAbsorp</v>
       </c>
       <c r="H85">
         <v>1</v>
@@ -13623,11 +13631,11 @@
         <v>自己強化</v>
       </c>
       <c r="F86">
-        <v>51</v>
+        <v>1024</v>
       </c>
       <c r="G86" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F86,[1]Animations!A:A))</f>
-        <v>NA_Effekseer/NA_aura_001</v>
+        <v>PierceIce</v>
       </c>
       <c r="H86">
         <v>1</v>
@@ -13705,11 +13713,11 @@
         <v>自己強化</v>
       </c>
       <c r="F87">
-        <v>51</v>
+        <v>1109</v>
       </c>
       <c r="G87" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F87,[1]Animations!A:A))</f>
-        <v>NA_Effekseer/NA_aura_001</v>
+        <v>Flash</v>
       </c>
       <c r="H87">
         <v>1</v>
@@ -13787,11 +13795,11 @@
         <v>自己強化</v>
       </c>
       <c r="F88">
-        <v>51</v>
+        <v>803</v>
       </c>
       <c r="G88" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F88,[1]Animations!A:A))</f>
-        <v>NA_Effekseer/NA_aura_001</v>
+        <v>Powerup3</v>
       </c>
       <c r="H88">
         <v>1</v>
@@ -13869,11 +13877,11 @@
         <v>自己強化</v>
       </c>
       <c r="F89">
-        <v>51</v>
+        <v>1109</v>
       </c>
       <c r="G89" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F89,[1]Animations!A:A))</f>
-        <v>NA_Effekseer/NA_aura_001</v>
+        <v>Flash</v>
       </c>
       <c r="H89">
         <v>1</v>
@@ -13951,11 +13959,11 @@
         <v>自己強化</v>
       </c>
       <c r="F90">
-        <v>21</v>
+        <v>3023</v>
       </c>
       <c r="G90" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F90,[1]Animations!A:A))</f>
-        <v>tktk01/Magic2</v>
+        <v>Genfulew_Effect/B&amp;S_MinMax_Cure</v>
       </c>
       <c r="H90">
         <v>1</v>
@@ -14033,11 +14041,11 @@
         <v>自己強化</v>
       </c>
       <c r="F91">
-        <v>51</v>
+        <v>1109</v>
       </c>
       <c r="G91" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F91,[1]Animations!A:A))</f>
-        <v>NA_Effekseer/NA_aura_001</v>
+        <v>Flash</v>
       </c>
       <c r="H91">
         <v>1</v>
@@ -14115,11 +14123,11 @@
         <v>自己強化</v>
       </c>
       <c r="F92">
-        <v>21</v>
+        <v>3023</v>
       </c>
       <c r="G92" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F92,[1]Animations!A:A))</f>
-        <v>tktk01/Magic2</v>
+        <v>Genfulew_Effect/B&amp;S_MinMax_Cure</v>
       </c>
       <c r="H92">
         <v>1</v>
@@ -14197,11 +14205,11 @@
         <v>自己強化</v>
       </c>
       <c r="F93">
-        <v>51</v>
+        <v>1109</v>
       </c>
       <c r="G93" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F93,[1]Animations!A:A))</f>
-        <v>NA_Effekseer/NA_aura_001</v>
+        <v>Flash</v>
       </c>
       <c r="H93">
         <v>1</v>
@@ -14279,11 +14287,11 @@
         <v>自己強化</v>
       </c>
       <c r="F94">
-        <v>51</v>
+        <v>1109</v>
       </c>
       <c r="G94" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F94,[1]Animations!A:A))</f>
-        <v>NA_Effekseer/NA_aura_001</v>
+        <v>Flash</v>
       </c>
       <c r="H94">
         <v>1</v>
@@ -14361,11 +14369,11 @@
         <v>自己強化</v>
       </c>
       <c r="F95">
-        <v>51</v>
+        <v>1109</v>
       </c>
       <c r="G95" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F95,[1]Animations!A:A))</f>
-        <v>NA_Effekseer/NA_aura_001</v>
+        <v>Flash</v>
       </c>
       <c r="H95">
         <v>1</v>
@@ -14443,11 +14451,11 @@
         <v>自己強化</v>
       </c>
       <c r="F96">
-        <v>21</v>
+        <v>3023</v>
       </c>
       <c r="G96" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F96,[1]Animations!A:A))</f>
-        <v>tktk01/Magic2</v>
+        <v>Genfulew_Effect/B&amp;S_MinMax_Cure</v>
       </c>
       <c r="H96">
         <v>1</v>
@@ -14525,11 +14533,11 @@
         <v>自己強化</v>
       </c>
       <c r="F97">
-        <v>21</v>
+        <v>3027</v>
       </c>
       <c r="G97" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F97,[1]Animations!A:A))</f>
-        <v>tktk01/Magic2</v>
+        <v>Genfulew_Effect/B&amp;S_MinMax_Regeneration1</v>
       </c>
       <c r="H97">
         <v>1</v>
@@ -14607,11 +14615,11 @@
         <v>自己強化</v>
       </c>
       <c r="F98">
-        <v>51</v>
+        <v>3009</v>
       </c>
       <c r="G98" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F98,[1]Animations!A:A))</f>
-        <v>NA_Effekseer/NA_aura_001</v>
+        <v>Genfulew_Effect/B&amp;S_MinMax_MagicAttackUp</v>
       </c>
       <c r="H98">
         <v>1</v>
@@ -14689,11 +14697,11 @@
         <v>自己強化</v>
       </c>
       <c r="F99">
-        <v>51</v>
+        <v>3047</v>
       </c>
       <c r="G99" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F99,[1]Animations!A:A))</f>
-        <v>NA_Effekseer/NA_aura_001</v>
+        <v>Genfulew_Effect/B&amp;S_MinMax_Dispel</v>
       </c>
       <c r="H99">
         <v>1</v>
@@ -14771,11 +14779,11 @@
         <v>自己強化</v>
       </c>
       <c r="F100">
-        <v>51</v>
+        <v>3047</v>
       </c>
       <c r="G100" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F100,[1]Animations!A:A))</f>
-        <v>NA_Effekseer/NA_aura_001</v>
+        <v>Genfulew_Effect/B&amp;S_MinMax_Dispel</v>
       </c>
       <c r="H100">
         <v>1</v>
@@ -14853,11 +14861,11 @@
         <v>自己強化</v>
       </c>
       <c r="F101">
-        <v>51</v>
+        <v>3047</v>
       </c>
       <c r="G101" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F101,[1]Animations!A:A))</f>
-        <v>NA_Effekseer/NA_aura_001</v>
+        <v>Genfulew_Effect/B&amp;S_MinMax_Dispel</v>
       </c>
       <c r="H101">
         <v>1</v>
@@ -14935,11 +14943,11 @@
         <v>自己強化</v>
       </c>
       <c r="F102">
-        <v>51</v>
+        <v>3047</v>
       </c>
       <c r="G102" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F102,[1]Animations!A:A))</f>
-        <v>NA_Effekseer/NA_aura_001</v>
+        <v>Genfulew_Effect/B&amp;S_MinMax_Dispel</v>
       </c>
       <c r="H102">
         <v>1</v>
@@ -15017,11 +15025,11 @@
         <v>自己強化</v>
       </c>
       <c r="F103">
-        <v>51</v>
+        <v>3047</v>
       </c>
       <c r="G103" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F103,[1]Animations!A:A))</f>
-        <v>NA_Effekseer/NA_aura_001</v>
+        <v>Genfulew_Effect/B&amp;S_MinMax_Dispel</v>
       </c>
       <c r="H103">
         <v>1</v>
@@ -15099,11 +15107,11 @@
         <v>自己強化</v>
       </c>
       <c r="F104">
-        <v>51</v>
+        <v>3047</v>
       </c>
       <c r="G104" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F104,[1]Animations!A:A))</f>
-        <v>NA_Effekseer/NA_aura_001</v>
+        <v>Genfulew_Effect/B&amp;S_MinMax_Dispel</v>
       </c>
       <c r="H104">
         <v>1</v>
@@ -15181,11 +15189,11 @@
         <v>自己強化</v>
       </c>
       <c r="F105">
-        <v>51</v>
+        <v>3047</v>
       </c>
       <c r="G105" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F105,[1]Animations!A:A))</f>
-        <v>NA_Effekseer/NA_aura_001</v>
+        <v>Genfulew_Effect/B&amp;S_MinMax_Dispel</v>
       </c>
       <c r="H105">
         <v>1</v>
@@ -15263,11 +15271,11 @@
         <v>自己強化</v>
       </c>
       <c r="F106">
-        <v>61</v>
+        <v>3047</v>
       </c>
       <c r="G106" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F106,[1]Animations!A:A))</f>
-        <v>NA_Effekseer/NA_aura_002</v>
+        <v>Genfulew_Effect/B&amp;S_MinMax_Dispel</v>
       </c>
       <c r="H106">
         <v>1</v>

--- a/Assets/Data/Skills.xlsx
+++ b/Assets/Data/Skills.xlsx
@@ -2672,9 +2672,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
@@ -2693,8 +2693,54 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -2708,22 +2754,21 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="13"/>
+      <sz val="11"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -2738,24 +2783,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -2768,39 +2798,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -2816,9 +2815,9 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -2830,8 +2829,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -2858,13 +2858,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2876,31 +2900,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2912,13 +2912,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2936,13 +2942,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2954,55 +2978,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3014,31 +3026,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3077,30 +3077,15 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF3F3F3F"/>
       </left>
       <right style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF3F3F3F"/>
       </right>
       <top style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF3F3F3F"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
         <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
@@ -3116,16 +3101,16 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FFB2B2B2"/>
       </left>
       <right style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FFB2B2B2"/>
       </right>
       <top style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FFB2B2B2"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -3149,6 +3134,21 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -3157,145 +3157,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="18" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="18" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="14" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>

--- a/Assets/Data/Skills.xlsx
+++ b/Assets/Data/Skills.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8270"/>
+    <workbookView windowWidth="19200" windowHeight="7820"/>
   </bookViews>
   <sheets>
     <sheet name="Skills" sheetId="1" r:id="rId1"/>
@@ -2672,10 +2672,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -2693,16 +2693,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -2716,16 +2708,38 @@
     </font>
     <font>
       <b/>
-      <sz val="13"/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -2746,6 +2760,15 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -2754,38 +2777,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -2798,15 +2790,24 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="15"/>
+      <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -2823,15 +2824,14 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -2858,7 +2858,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2870,7 +2870,79 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2882,19 +2954,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2906,73 +3014,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2984,55 +3032,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3076,16 +3076,16 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
+      <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
-      <right style="thin">
+      <right style="double">
         <color rgb="FF3F3F3F"/>
       </right>
-      <top style="thin">
+      <top style="double">
         <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="thin">
+      <bottom style="double">
         <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
@@ -3117,15 +3117,6 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
       <top style="thin">
         <color theme="4"/>
       </top>
@@ -3135,17 +3126,26 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
+      <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
-      <right style="double">
+      <right style="thin">
         <color rgb="FF3F3F3F"/>
       </right>
-      <top style="double">
+      <top style="thin">
         <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="double">
+      <bottom style="thin">
         <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -3157,145 +3157,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="22" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="22" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -6670,9 +6670,10 @@
     <col min="3" max="3" width="19.7272727272727" customWidth="1"/>
     <col min="6" max="6" width="15.0909090909091" customWidth="1"/>
     <col min="7" max="7" width="37.6363636363636" customWidth="1"/>
-    <col min="8" max="8" width="14.4545454545455" customWidth="1"/>
+    <col min="8" max="8" width="6.36363636363636" customWidth="1"/>
     <col min="9" max="10" width="5.54545454545455" customWidth="1"/>
-    <col min="11" max="12" width="6.63636363636364" customWidth="1"/>
+    <col min="11" max="11" width="6.63636363636364" customWidth="1"/>
+    <col min="12" max="12" width="5.63636363636364" customWidth="1"/>
     <col min="13" max="13" width="5.36363636363636" style="6" customWidth="1"/>
     <col min="14" max="14" width="4.90909090909091" style="6" customWidth="1"/>
     <col min="15" max="15" width="4.45454545454545" customWidth="1"/>
@@ -7837,7 +7838,7 @@
         <v>3</v>
       </c>
       <c r="L15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M15">
         <v>1</v>
@@ -8001,7 +8002,7 @@
         <v>2</v>
       </c>
       <c r="L17">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M17">
         <v>1</v>
@@ -8903,7 +8904,7 @@
         <v>2</v>
       </c>
       <c r="L28">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M28">
         <v>3</v>
@@ -9395,7 +9396,7 @@
         <v>5</v>
       </c>
       <c r="L34">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M34">
         <v>3</v>
@@ -9641,7 +9642,7 @@
         <v>3</v>
       </c>
       <c r="L37">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M37">
         <v>4</v>
@@ -9887,7 +9888,7 @@
         <v>7</v>
       </c>
       <c r="L40">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M40">
         <v>4</v>
@@ -10215,7 +10216,7 @@
         <v>5</v>
       </c>
       <c r="L44">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M44">
         <v>5</v>
@@ -10625,7 +10626,7 @@
         <v>2</v>
       </c>
       <c r="L49">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M49">
         <v>5</v>
@@ -11683,7 +11684,7 @@
         <v>4</v>
       </c>
       <c r="L62">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="M62">
         <v>1</v>
@@ -11765,7 +11766,7 @@
         <v>0</v>
       </c>
       <c r="L63">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="M63">
         <v>1</v>
@@ -11847,7 +11848,7 @@
         <v>0</v>
       </c>
       <c r="L64">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="M64">
         <v>1</v>
@@ -12093,7 +12094,7 @@
         <v>3</v>
       </c>
       <c r="L67">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="M67">
         <v>1</v>
@@ -12421,7 +12422,7 @@
         <v>0</v>
       </c>
       <c r="L71">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="M71">
         <v>2</v>
@@ -12585,7 +12586,7 @@
         <v>3</v>
       </c>
       <c r="L73">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="M73">
         <v>2</v>
@@ -12831,7 +12832,7 @@
         <v>0</v>
       </c>
       <c r="L76">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="M76">
         <v>2</v>
@@ -12975,11 +12976,11 @@
         <v>自己強化</v>
       </c>
       <c r="F78">
-        <v>3007</v>
+        <v>803</v>
       </c>
       <c r="G78" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F78,[1]Animations!A:A))</f>
-        <v>Genfulew_Effect/B&amp;S_MinMax_DefenseUp</v>
+        <v>Powerup3</v>
       </c>
       <c r="H78">
         <v>1</v>
@@ -13159,7 +13160,7 @@
         <v>2</v>
       </c>
       <c r="L80">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="M80">
         <v>3</v>
@@ -13221,11 +13222,11 @@
         <v>自己強化</v>
       </c>
       <c r="F81">
-        <v>3007</v>
+        <v>803</v>
       </c>
       <c r="G81" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F81,[1]Animations!A:A))</f>
-        <v>Genfulew_Effect/B&amp;S_MinMax_DefenseUp</v>
+        <v>Powerup3</v>
       </c>
       <c r="H81">
         <v>1</v>
@@ -13323,7 +13324,7 @@
         <v>5</v>
       </c>
       <c r="L82">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="M82">
         <v>3</v>
@@ -13405,7 +13406,7 @@
         <v>2</v>
       </c>
       <c r="L83">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="M83">
         <v>3</v>
@@ -13733,7 +13734,7 @@
         <v>3</v>
       </c>
       <c r="L87">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="M87">
         <v>3</v>
@@ -13979,7 +13980,7 @@
         <v>3</v>
       </c>
       <c r="L90">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="M90">
         <v>4</v>
@@ -14143,7 +14144,7 @@
         <v>3</v>
       </c>
       <c r="L92">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="M92">
         <v>4</v>
@@ -14553,7 +14554,7 @@
         <v>5</v>
       </c>
       <c r="L97">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="M97">
         <v>4</v>
@@ -14799,7 +14800,7 @@
         <v>0</v>
       </c>
       <c r="L100">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="M100">
         <v>5</v>
@@ -14881,7 +14882,7 @@
         <v>0</v>
       </c>
       <c r="L101">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="M101">
         <v>5</v>
@@ -15045,7 +15046,7 @@
         <v>0</v>
       </c>
       <c r="L103">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="M103">
         <v>5</v>
@@ -15127,7 +15128,7 @@
         <v>3</v>
       </c>
       <c r="L104">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="M104">
         <v>5</v>

--- a/Assets/Data/Skills.xlsx
+++ b/Assets/Data/Skills.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8270" activeTab="2"/>
+    <workbookView windowWidth="19200" windowHeight="7820" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Skills" sheetId="1" r:id="rId1"/>
@@ -2790,8 +2790,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
@@ -2817,47 +2817,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -2872,9 +2833,41 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -2892,24 +2885,23 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -2924,6 +2916,22 @@
     </font>
     <font>
       <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -2934,14 +2942,6 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -2975,7 +2975,85 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2987,7 +3065,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2999,19 +3089,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3023,97 +3125,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3125,13 +3137,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3143,19 +3155,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3186,8 +3186,10 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
         <color theme="4"/>
       </bottom>
       <diagonal/>
@@ -3236,6 +3238,15 @@
       <right/>
       <top/>
       <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
         <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
@@ -3255,17 +3266,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -3274,7 +3274,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -3292,127 +3292,127 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="18" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="18" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>

--- a/Assets/Data/Skills.xlsx
+++ b/Assets/Data/Skills.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="7820" activeTab="1"/>
+    <workbookView windowWidth="19200" windowHeight="7820" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="Skills" sheetId="1" r:id="rId1"/>
@@ -639,7 +639,7 @@
   <si>
     <t>(条件)バトル開始時
 \sの初動が少し早くなる
-自身のATKを/f[f,0,2]ターン/f[f,0,3]ダウン</t>
+自身のATKを/f[f,1,2]ターン/f[f,1,3]ダウン</t>
   </si>
   <si>
     <t>アクトスタンス+</t>
@@ -647,7 +647,7 @@
   <si>
     <t>(条件)バトル開始時
 \sの初動が早くなる
-自身のATKを/f[f,0,2]ターン/f[f,0,3]ダウン</t>
+自身のATKを/f[f,1,2]ターン/f[f,1,3]ダウン</t>
   </si>
   <si>
     <t>アーマーコード</t>
@@ -2810,9 +2810,45 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -2834,8 +2870,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -2843,9 +2880,17 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -2858,74 +2903,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -2941,9 +2926,24 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -2975,7 +2975,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2987,13 +3035,73 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3005,25 +3113,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3035,127 +3155,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3172,8 +3172,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -3184,6 +3184,15 @@
         <color theme="4"/>
       </top>
       <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
         <color theme="4"/>
       </bottom>
       <diagonal/>
@@ -3219,11 +3228,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
       <bottom style="double">
-        <color rgb="FFFF8001"/>
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -3239,21 +3254,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -3274,7 +3274,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="17" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -3283,7 +3283,7 @@
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -3292,127 +3292,127 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="13" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="13" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="18" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="23" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>

--- a/Assets/Data/Skills.xlsx
+++ b/Assets/Data/Skills.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="7820" activeTab="4"/>
+    <workbookView windowWidth="19200" windowHeight="7820" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Skills" sheetId="1" r:id="rId1"/>
@@ -2789,9 +2789,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="21">
@@ -2811,16 +2811,76 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -2833,14 +2893,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -2848,7 +2901,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -2863,16 +2916,8 @@
     </font>
     <font>
       <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -2887,36 +2932,6 @@
     </font>
     <font>
       <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -2926,22 +2941,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -2975,7 +2975,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2987,13 +3017,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3005,13 +3029,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3029,19 +3059,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3053,7 +3071,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3065,55 +3101,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3131,7 +3131,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3143,19 +3143,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3166,50 +3166,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -3224,21 +3180,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -3262,7 +3203,66 @@
       <right/>
       <top/>
       <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
         <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -3274,145 +3274,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="17" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="19" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="13" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="20" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="13" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="20" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="18" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -38008,11 +38008,11 @@
     </row>
     <row r="103" spans="1:9">
       <c r="A103">
-        <v>12041</v>
+        <v>12040</v>
       </c>
       <c r="B103" t="str">
         <f>INDEX(TextData!B:B,MATCH(A103,TextData!A:A))</f>
-        <v>イヴェイドオール+</v>
+        <v>イヴェイドオール</v>
       </c>
       <c r="C103">
         <v>3010</v>
@@ -38040,11 +38040,11 @@
     </row>
     <row r="104" spans="1:9">
       <c r="A104">
-        <v>12040</v>
+        <v>12041</v>
       </c>
       <c r="B104" t="str">
         <f>INDEX(TextData!B:B,MATCH(A104,TextData!A:A))</f>
-        <v>イヴェイドオール</v>
+        <v>イヴェイドオール+</v>
       </c>
       <c r="C104">
         <v>3010</v>

--- a/Assets/Data/Skills.xlsx
+++ b/Assets/Data/Skills.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8270"/>
+    <workbookView windowWidth="19200" windowHeight="7820"/>
   </bookViews>
   <sheets>
     <sheet name="Skills" sheetId="1" r:id="rId1"/>
@@ -2921,10 +2921,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -2942,16 +2942,30 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -2965,14 +2979,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -2983,22 +2990,6 @@
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -3019,7 +3010,23 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -3027,30 +3034,23 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <sz val="15"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -3071,16 +3071,16 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -3107,6 +3107,36 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -3119,7 +3149,103 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3131,7 +3257,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3143,151 +3287,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3298,24 +3298,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -3364,6 +3346,44 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -3378,26 +3398,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -3406,16 +3406,16 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -3424,127 +3424,127 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="21" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="21" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="12" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="15" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>

--- a/Assets/Data/Skills.xlsx
+++ b/Assets/Data/Skills.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="7820"/>
+    <workbookView windowWidth="19200" windowHeight="7820" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Skills" sheetId="1" r:id="rId1"/>
@@ -651,7 +651,7 @@
   <si>
     <t>(条件)自身の攻撃成功時
 火傷状態ではない対象に/f[f,0,2]ターン/f[f,0,3]%ダメージの火傷付与
-会得していたらさらに/f[f,1,3]アップ
+会得していたらさらに/f[f,0,3]%アップ
 /s</t>
   </si>
   <si>
@@ -2508,19 +2508,19 @@
     <t>StateId状態になっている敵</t>
   </si>
   <si>
-    <t>指定のFeatureのParam1を増やす</t>
+    <t>FeatureのParam1を指定値に上書き</t>
   </si>
   <si>
     <t>StateId状態になっていない味方</t>
   </si>
   <si>
-    <t>指定のFeatureのParam2を増やす</t>
+    <t>FeatureのParam2を指定値に上書き</t>
   </si>
   <si>
     <t>StateId状態になっていない敵</t>
   </si>
   <si>
-    <t>指定のFeatureのParam3を増やす</t>
+    <t>FeatureのParam3を指定値に上書き</t>
   </si>
   <si>
     <t>AbnormalのStateにかかっている</t>
@@ -2922,8 +2922,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="21">
@@ -2943,21 +2943,6 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
@@ -2965,92 +2950,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -3065,7 +2965,115 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -3073,14 +3081,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -3107,109 +3107,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3227,7 +3131,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3239,7 +3197,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3251,19 +3239,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3275,19 +3263,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3298,6 +3298,39 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -3317,21 +3350,6 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
       <right style="thin">
@@ -3342,35 +3360,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -3398,6 +3387,17 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -3406,7 +3406,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -3415,7 +3415,7 @@
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -3424,127 +3424,127 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="21" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="17" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="17" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="21" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -34875,7 +34875,7 @@
       </c>
       <c r="D80" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C80,Define!P:P))</f>
-        <v>指定のFeatureのParam3を増やす</v>
+        <v>FeatureのParam3を指定値に上書き</v>
       </c>
       <c r="E80">
         <v>11010</v>
@@ -34884,7 +34884,7 @@
         <v>0</v>
       </c>
       <c r="G80">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H80">
         <v>100</v>
@@ -34937,7 +34937,7 @@
       </c>
       <c r="D82" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C82,Define!P:P))</f>
-        <v>指定のFeatureのParam3を増やす</v>
+        <v>FeatureのParam3を指定値に上書き</v>
       </c>
       <c r="E82">
         <v>11020</v>
@@ -34946,7 +34946,7 @@
         <v>0</v>
       </c>
       <c r="G82">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="H82">
         <v>100</v>
@@ -35030,7 +35030,7 @@
       </c>
       <c r="D85" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C85,Define!P:P))</f>
-        <v>指定のFeatureのParam3を増やす</v>
+        <v>FeatureのParam3を指定値に上書き</v>
       </c>
       <c r="E85">
         <v>11030</v>
@@ -35039,7 +35039,7 @@
         <v>0</v>
       </c>
       <c r="G85">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H85">
         <v>100</v>
@@ -35266,7 +35266,7 @@
       </c>
       <c r="D93" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C93,Define!P:P))</f>
-        <v>指定のFeatureのParam1を増やす</v>
+        <v>FeatureのParam1を指定値に上書き</v>
       </c>
       <c r="E93">
         <v>11000</v>
@@ -35275,7 +35275,7 @@
         <v>0</v>
       </c>
       <c r="G93">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H93">
         <v>100</v>
@@ -35303,7 +35303,7 @@
         <v>2</v>
       </c>
       <c r="G94">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="H94">
         <v>100</v>
@@ -35325,7 +35325,7 @@
       </c>
       <c r="D95" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C95,Define!P:P))</f>
-        <v>指定のFeatureのParam3を増やす</v>
+        <v>FeatureのParam3を指定値に上書き</v>
       </c>
       <c r="E95">
         <v>11110</v>
@@ -35449,7 +35449,7 @@
       </c>
       <c r="D99" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C99,Define!P:P))</f>
-        <v>指定のFeatureのParam3を増やす</v>
+        <v>FeatureのParam3を指定値に上書き</v>
       </c>
       <c r="E99">
         <v>12020</v>
@@ -35458,7 +35458,7 @@
         <v>0</v>
       </c>
       <c r="G99">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="H99">
         <v>100</v>
@@ -35511,7 +35511,7 @@
       </c>
       <c r="D101" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C101,Define!P:P))</f>
-        <v>指定のFeatureのParam3を増やす</v>
+        <v>FeatureのParam3を指定値に上書き</v>
       </c>
       <c r="E101">
         <v>12030</v>
@@ -35520,7 +35520,7 @@
         <v>0</v>
       </c>
       <c r="G101">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H101">
         <v>100</v>
@@ -35573,7 +35573,7 @@
       </c>
       <c r="D103" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C103,Define!P:P))</f>
-        <v>指定のFeatureのParam3を増やす</v>
+        <v>FeatureのParam3を指定値に上書き</v>
       </c>
       <c r="E103">
         <v>12040</v>
@@ -35582,7 +35582,7 @@
         <v>0</v>
       </c>
       <c r="G103">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H103">
         <v>100</v>
@@ -35632,7 +35632,7 @@
       </c>
       <c r="D105" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C105,Define!P:P))</f>
-        <v>指定のFeatureのParam1を増やす</v>
+        <v>FeatureのParam1を指定値に上書き</v>
       </c>
       <c r="E105">
         <v>12050</v>
@@ -35641,7 +35641,7 @@
         <v>0</v>
       </c>
       <c r="G105">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="H105">
         <v>100</v>
@@ -35924,7 +35924,7 @@
       </c>
       <c r="D115" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C115,Define!P:P))</f>
-        <v>指定のFeatureのParam3を増やす</v>
+        <v>FeatureのParam3を指定値に上書き</v>
       </c>
       <c r="E115">
         <v>12110</v>
@@ -35933,7 +35933,7 @@
         <v>0</v>
       </c>
       <c r="G115">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="H115">
         <v>100</v>
@@ -35983,7 +35983,7 @@
       </c>
       <c r="D117" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C117,Define!P:P))</f>
-        <v>指定のFeatureのParam3を増やす</v>
+        <v>FeatureのParam3を指定値に上書き</v>
       </c>
       <c r="E117">
         <v>13010</v>
@@ -35992,7 +35992,7 @@
         <v>0</v>
       </c>
       <c r="G117">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H117">
         <v>100</v>
@@ -36104,7 +36104,7 @@
       </c>
       <c r="D121" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C121,Define!P:P))</f>
-        <v>指定のFeatureのParam3を増やす</v>
+        <v>FeatureのParam3を指定値に上書き</v>
       </c>
       <c r="E121">
         <v>13040</v>
@@ -36113,7 +36113,7 @@
         <v>0</v>
       </c>
       <c r="G121">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="H121">
         <v>100</v>
@@ -36225,7 +36225,7 @@
       </c>
       <c r="D125" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C125,Define!P:P))</f>
-        <v>指定のFeatureのParam1を増やす</v>
+        <v>FeatureのParam1を指定値に上書き</v>
       </c>
       <c r="E125">
         <v>13070</v>
@@ -36234,7 +36234,7 @@
         <v>0</v>
       </c>
       <c r="G125">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="H125">
         <v>100</v>
@@ -36284,7 +36284,7 @@
       </c>
       <c r="D127" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C127,Define!P:P))</f>
-        <v>指定のFeatureのParam3を増やす</v>
+        <v>FeatureのParam3を指定値に上書き</v>
       </c>
       <c r="E127">
         <v>13080</v>
@@ -36293,7 +36293,7 @@
         <v>0</v>
       </c>
       <c r="G127">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="H127">
         <v>100</v>
@@ -36585,7 +36585,7 @@
       </c>
       <c r="D137" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C137,Define!P:P))</f>
-        <v>指定のFeatureのParam2を増やす</v>
+        <v>FeatureのParam2を指定値に上書き</v>
       </c>
       <c r="E137">
         <v>14010</v>
@@ -36594,7 +36594,7 @@
         <v>0</v>
       </c>
       <c r="G137">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H137">
         <v>100</v>
@@ -36675,7 +36675,7 @@
       </c>
       <c r="D140" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C140,Define!P:P))</f>
-        <v>指定のFeatureのParam3を増やす</v>
+        <v>FeatureのParam3を指定値に上書き</v>
       </c>
       <c r="E140">
         <v>14030</v>
@@ -36684,7 +36684,7 @@
         <v>0</v>
       </c>
       <c r="G140">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H140">
         <v>100</v>
@@ -36768,7 +36768,7 @@
       </c>
       <c r="D143" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C143,Define!P:P))</f>
-        <v>指定のFeatureのParam3を増やす</v>
+        <v>FeatureのParam3を指定値に上書き</v>
       </c>
       <c r="E143">
         <v>14050</v>
@@ -36777,7 +36777,7 @@
         <v>0</v>
       </c>
       <c r="G143">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H143">
         <v>100</v>
@@ -36886,7 +36886,7 @@
       </c>
       <c r="D147" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C147,Define!P:P))</f>
-        <v>指定のFeatureのParam1を増やす</v>
+        <v>FeatureのParam1を指定値に上書き</v>
       </c>
       <c r="E147">
         <v>14080</v>
@@ -36895,7 +36895,7 @@
         <v>0</v>
       </c>
       <c r="G147">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H147">
         <v>100</v>
@@ -37060,7 +37060,7 @@
       </c>
       <c r="D153" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C153,Define!P:P))</f>
-        <v>指定のFeatureのParam3を増やす</v>
+        <v>FeatureのParam3を指定値に上書き</v>
       </c>
       <c r="E153">
         <v>15010</v>
@@ -37069,7 +37069,7 @@
         <v>0</v>
       </c>
       <c r="G153">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="H153">
         <v>100</v>
@@ -37122,7 +37122,7 @@
       </c>
       <c r="D155" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C155,Define!P:P))</f>
-        <v>指定のFeatureのParam3を増やす</v>
+        <v>FeatureのParam3を指定値に上書き</v>
       </c>
       <c r="E155">
         <v>15020</v>
@@ -37131,7 +37131,7 @@
         <v>0</v>
       </c>
       <c r="G155">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="H155">
         <v>100</v>
@@ -37243,7 +37243,7 @@
       </c>
       <c r="D159" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C159,Define!P:P))</f>
-        <v>指定のFeatureのParam3を増やす</v>
+        <v>FeatureのParam3を指定値に上書き</v>
       </c>
       <c r="E159">
         <v>15050</v>
@@ -37252,7 +37252,7 @@
         <v>0</v>
       </c>
       <c r="G159">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="H159">
         <v>100</v>
@@ -37488,7 +37488,7 @@
       </c>
       <c r="D167" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C167,Define!P:P))</f>
-        <v>指定のFeatureのParam3を増やす</v>
+        <v>FeatureのParam3を指定値に上書き</v>
       </c>
       <c r="E167">
         <v>15100</v>
@@ -37497,7 +37497,7 @@
         <v>0</v>
       </c>
       <c r="G167">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="H167">
         <v>100</v>
@@ -37519,7 +37519,7 @@
       </c>
       <c r="D168" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C168,Define!P:P))</f>
-        <v>指定のFeatureのParam3を増やす</v>
+        <v>FeatureのParam3を指定値に上書き</v>
       </c>
       <c r="E168">
         <v>15100</v>
@@ -37528,7 +37528,7 @@
         <v>1</v>
       </c>
       <c r="G168">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="H168">
         <v>100</v>
@@ -41822,7 +41822,7 @@
       </c>
       <c r="D316" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C316,Define!P:P))</f>
-        <v>指定のFeatureのParam1を増やす</v>
+        <v>FeatureのParam1を指定値に上書き</v>
       </c>
       <c r="E316">
         <v>1020</v>
@@ -41850,7 +41850,7 @@
       </c>
       <c r="D317" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C317,Define!P:P))</f>
-        <v>指定のFeatureのParam1を増やす</v>
+        <v>FeatureのParam1を指定値に上書き</v>
       </c>
       <c r="E317">
         <v>1030</v>
@@ -41878,7 +41878,7 @@
       </c>
       <c r="D318" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C318,Define!P:P))</f>
-        <v>指定のFeatureのParam1を増やす</v>
+        <v>FeatureのParam1を指定値に上書き</v>
       </c>
       <c r="E318">
         <v>1040</v>
@@ -41906,7 +41906,7 @@
       </c>
       <c r="D319" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C319,Define!P:P))</f>
-        <v>指定のFeatureのParam1を増やす</v>
+        <v>FeatureのParam1を指定値に上書き</v>
       </c>
       <c r="E319">
         <v>1050</v>
@@ -41934,7 +41934,7 @@
       </c>
       <c r="D320" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C320,Define!P:P))</f>
-        <v>指定のFeatureのParam1を増やす</v>
+        <v>FeatureのParam1を指定値に上書き</v>
       </c>
       <c r="E320">
         <v>1060</v>
@@ -41990,7 +41990,7 @@
       </c>
       <c r="D322" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C322,Define!P:P))</f>
-        <v>指定のFeatureのParam3を増やす</v>
+        <v>FeatureのParam3を指定値に上書き</v>
       </c>
       <c r="E322">
         <v>1080</v>
@@ -42018,7 +42018,7 @@
       </c>
       <c r="D323" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C323,Define!P:P))</f>
-        <v>指定のFeatureのParam1を増やす</v>
+        <v>FeatureのParam1を指定値に上書き</v>
       </c>
       <c r="E323">
         <v>2010</v>
@@ -42046,7 +42046,7 @@
       </c>
       <c r="D324" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C324,Define!P:P))</f>
-        <v>指定のFeatureのParam3を増やす</v>
+        <v>FeatureのParam3を指定値に上書き</v>
       </c>
       <c r="E324">
         <v>2020</v>
@@ -42102,7 +42102,7 @@
       </c>
       <c r="D326" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C326,Define!P:P))</f>
-        <v>指定のFeatureのParam1を増やす</v>
+        <v>FeatureのParam1を指定値に上書き</v>
       </c>
       <c r="E326">
         <v>2040</v>
@@ -42158,7 +42158,7 @@
       </c>
       <c r="D328" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C328,Define!P:P))</f>
-        <v>指定のFeatureのParam1を増やす</v>
+        <v>FeatureのParam1を指定値に上書き</v>
       </c>
       <c r="E328">
         <v>2060</v>
@@ -42186,7 +42186,7 @@
       </c>
       <c r="D329" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C329,Define!P:P))</f>
-        <v>指定のFeatureのParam3を増やす</v>
+        <v>FeatureのParam3を指定値に上書き</v>
       </c>
       <c r="E329">
         <v>2070</v>
@@ -42214,7 +42214,7 @@
       </c>
       <c r="D330" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C330,Define!P:P))</f>
-        <v>指定のFeatureのParam1を増やす</v>
+        <v>FeatureのParam1を指定値に上書き</v>
       </c>
       <c r="E330">
         <v>2080</v>
@@ -42242,7 +42242,7 @@
       </c>
       <c r="D331" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C331,Define!P:P))</f>
-        <v>指定のFeatureのParam1を増やす</v>
+        <v>FeatureのParam1を指定値に上書き</v>
       </c>
       <c r="E331">
         <v>3010</v>
@@ -42270,7 +42270,7 @@
       </c>
       <c r="D332" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C332,Define!P:P))</f>
-        <v>指定のFeatureのParam3を増やす</v>
+        <v>FeatureのParam3を指定値に上書き</v>
       </c>
       <c r="E332">
         <v>3020</v>
@@ -42298,7 +42298,7 @@
       </c>
       <c r="D333" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C333,Define!P:P))</f>
-        <v>指定のFeatureのParam3を増やす</v>
+        <v>FeatureのParam3を指定値に上書き</v>
       </c>
       <c r="E333">
         <v>3030</v>
@@ -42326,7 +42326,7 @@
       </c>
       <c r="D334" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C334,Define!P:P))</f>
-        <v>指定のFeatureのParam3を増やす</v>
+        <v>FeatureのParam3を指定値に上書き</v>
       </c>
       <c r="E334">
         <v>3040</v>
@@ -42354,7 +42354,7 @@
       </c>
       <c r="D335" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C335,Define!P:P))</f>
-        <v>指定のFeatureのParam3を増やす</v>
+        <v>FeatureのParam3を指定値に上書き</v>
       </c>
       <c r="E335">
         <v>3050</v>
@@ -42382,7 +42382,7 @@
       </c>
       <c r="D336" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C336,Define!P:P))</f>
-        <v>指定のFeatureのParam3を増やす</v>
+        <v>FeatureのParam3を指定値に上書き</v>
       </c>
       <c r="E336">
         <v>3060</v>
@@ -42410,7 +42410,7 @@
       </c>
       <c r="D337" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C337,Define!P:P))</f>
-        <v>指定のFeatureのParam2を増やす</v>
+        <v>FeatureのParam2を指定値に上書き</v>
       </c>
       <c r="E337">
         <v>3070</v>
@@ -42438,7 +42438,7 @@
       </c>
       <c r="D338" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C338,Define!P:P))</f>
-        <v>指定のFeatureのParam3を増やす</v>
+        <v>FeatureのParam3を指定値に上書き</v>
       </c>
       <c r="E338">
         <v>3080</v>
@@ -42466,7 +42466,7 @@
       </c>
       <c r="D339" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C339,Define!P:P))</f>
-        <v>指定のFeatureのParam1を増やす</v>
+        <v>FeatureのParam1を指定値に上書き</v>
       </c>
       <c r="E339">
         <v>4010</v>
@@ -42494,7 +42494,7 @@
       </c>
       <c r="D340" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C340,Define!P:P))</f>
-        <v>指定のFeatureのParam1を増やす</v>
+        <v>FeatureのParam1を指定値に上書き</v>
       </c>
       <c r="E340">
         <v>4020</v>
@@ -42550,7 +42550,7 @@
       </c>
       <c r="D342" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C342,Define!P:P))</f>
-        <v>指定のFeatureのParam3を増やす</v>
+        <v>FeatureのParam3を指定値に上書き</v>
       </c>
       <c r="E342">
         <v>4040</v>
@@ -42634,7 +42634,7 @@
       </c>
       <c r="D345" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C345,Define!P:P))</f>
-        <v>指定のFeatureのParam3を増やす</v>
+        <v>FeatureのParam3を指定値に上書き</v>
       </c>
       <c r="E345">
         <v>4070</v>
@@ -42690,7 +42690,7 @@
       </c>
       <c r="D347" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C347,Define!P:P))</f>
-        <v>指定のFeatureのParam1を増やす</v>
+        <v>FeatureのParam1を指定値に上書き</v>
       </c>
       <c r="E347">
         <v>5010</v>
@@ -42718,7 +42718,7 @@
       </c>
       <c r="D348" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C348,Define!P:P))</f>
-        <v>指定のFeatureのParam1を増やす</v>
+        <v>FeatureのParam1を指定値に上書き</v>
       </c>
       <c r="E348">
         <v>5020</v>
@@ -42746,7 +42746,7 @@
       </c>
       <c r="D349" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C349,Define!P:P))</f>
-        <v>指定のFeatureのParam3を増やす</v>
+        <v>FeatureのParam3を指定値に上書き</v>
       </c>
       <c r="E349">
         <v>5030</v>
@@ -42774,7 +42774,7 @@
       </c>
       <c r="D350" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C350,Define!P:P))</f>
-        <v>指定のFeatureのParam2を増やす</v>
+        <v>FeatureのParam2を指定値に上書き</v>
       </c>
       <c r="E350">
         <v>5040</v>
@@ -42802,7 +42802,7 @@
       </c>
       <c r="D351" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C351,Define!P:P))</f>
-        <v>指定のFeatureのParam3を増やす</v>
+        <v>FeatureのParam3を指定値に上書き</v>
       </c>
       <c r="E351">
         <v>5050</v>
@@ -42830,7 +42830,7 @@
       </c>
       <c r="D352" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C352,Define!P:P))</f>
-        <v>指定のFeatureのParam3を増やす</v>
+        <v>FeatureのParam3を指定値に上書き</v>
       </c>
       <c r="E352">
         <v>5060</v>
@@ -42858,7 +42858,7 @@
       </c>
       <c r="D353" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C353,Define!P:P))</f>
-        <v>指定のFeatureのParam3を増やす</v>
+        <v>FeatureのParam3を指定値に上書き</v>
       </c>
       <c r="E353">
         <v>5070</v>
@@ -42886,7 +42886,7 @@
       </c>
       <c r="D354" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C354,Define!P:P))</f>
-        <v>指定のFeatureのParam3を増やす</v>
+        <v>FeatureのParam3を指定値に上書き</v>
       </c>
       <c r="E354">
         <v>5080</v>
@@ -42914,7 +42914,7 @@
       </c>
       <c r="D355" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C355,Define!P:P))</f>
-        <v>指定のFeatureのParam3を増やす</v>
+        <v>FeatureのParam3を指定値に上書き</v>
       </c>
       <c r="E355">
         <v>11010</v>
@@ -42942,7 +42942,7 @@
       </c>
       <c r="D356" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C356,Define!P:P))</f>
-        <v>指定のFeatureのParam3を増やす</v>
+        <v>FeatureのParam3を指定値に上書き</v>
       </c>
       <c r="E356">
         <v>11020</v>
@@ -42970,7 +42970,7 @@
       </c>
       <c r="D357" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C357,Define!P:P))</f>
-        <v>指定のFeatureのParam3を増やす</v>
+        <v>FeatureのParam3を指定値に上書き</v>
       </c>
       <c r="E357">
         <v>11030</v>
@@ -42998,7 +42998,7 @@
       </c>
       <c r="D358" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C358,Define!P:P))</f>
-        <v>指定のFeatureのParam3を増やす</v>
+        <v>FeatureのParam3を指定値に上書き</v>
       </c>
       <c r="E358">
         <v>11030</v>
@@ -43054,7 +43054,7 @@
       </c>
       <c r="D360" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C360,Define!P:P))</f>
-        <v>指定のFeatureのParam1を増やす</v>
+        <v>FeatureのParam1を指定値に上書き</v>
       </c>
       <c r="E360">
         <v>11050</v>
@@ -43082,7 +43082,7 @@
       </c>
       <c r="D361" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C361,Define!P:P))</f>
-        <v>指定のFeatureのParam1を増やす</v>
+        <v>FeatureのParam1を指定値に上書き</v>
       </c>
       <c r="E361">
         <v>11060</v>
@@ -43110,7 +43110,7 @@
       </c>
       <c r="D362" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C362,Define!P:P))</f>
-        <v>指定のFeatureのParam3を増やす</v>
+        <v>FeatureのParam3を指定値に上書き</v>
       </c>
       <c r="E362">
         <v>11070</v>
@@ -43138,7 +43138,7 @@
       </c>
       <c r="D363" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C363,Define!P:P))</f>
-        <v>指定のFeatureのParam3を増やす</v>
+        <v>FeatureのParam3を指定値に上書き</v>
       </c>
       <c r="E363">
         <v>11080</v>
@@ -43166,7 +43166,7 @@
       </c>
       <c r="D364" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C364,Define!P:P))</f>
-        <v>指定のFeatureのParam3を増やす</v>
+        <v>FeatureのParam3を指定値に上書き</v>
       </c>
       <c r="E364">
         <v>11090</v>
@@ -43222,7 +43222,7 @@
       </c>
       <c r="D366" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C366,Define!P:P))</f>
-        <v>指定のFeatureのParam3を増やす</v>
+        <v>FeatureのParam3を指定値に上書き</v>
       </c>
       <c r="E366">
         <v>12020</v>
@@ -43250,7 +43250,7 @@
       </c>
       <c r="D367" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C367,Define!P:P))</f>
-        <v>指定のFeatureのParam3を増やす</v>
+        <v>FeatureのParam3を指定値に上書き</v>
       </c>
       <c r="E367">
         <v>12030</v>
@@ -43278,7 +43278,7 @@
       </c>
       <c r="D368" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C368,Define!P:P))</f>
-        <v>指定のFeatureのParam3を増やす</v>
+        <v>FeatureのParam3を指定値に上書き</v>
       </c>
       <c r="E368">
         <v>12040</v>
@@ -43306,7 +43306,7 @@
       </c>
       <c r="D369" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C369,Define!P:P))</f>
-        <v>指定のFeatureのParam1を増やす</v>
+        <v>FeatureのParam1を指定値に上書き</v>
       </c>
       <c r="E369">
         <v>12050</v>
@@ -43334,7 +43334,7 @@
       </c>
       <c r="D370" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C370,Define!P:P))</f>
-        <v>指定のFeatureのParam1を増やす</v>
+        <v>FeatureのParam1を指定値に上書き</v>
       </c>
       <c r="E370">
         <v>12060</v>
@@ -43362,7 +43362,7 @@
       </c>
       <c r="D371" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C371,Define!P:P))</f>
-        <v>指定のFeatureのParam3を増やす</v>
+        <v>FeatureのParam3を指定値に上書き</v>
       </c>
       <c r="E371">
         <v>12070</v>
@@ -43390,7 +43390,7 @@
       </c>
       <c r="D372" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C372,Define!P:P))</f>
-        <v>指定のFeatureのParam1を増やす</v>
+        <v>FeatureのParam1を指定値に上書き</v>
       </c>
       <c r="E372">
         <v>12080</v>
@@ -43418,7 +43418,7 @@
       </c>
       <c r="D373" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C373,Define!P:P))</f>
-        <v>指定のFeatureのParam1を増やす</v>
+        <v>FeatureのParam1を指定値に上書き</v>
       </c>
       <c r="E373">
         <v>12090</v>
@@ -43446,7 +43446,7 @@
       </c>
       <c r="D374" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C374,Define!P:P))</f>
-        <v>指定のFeatureのParam3を増やす</v>
+        <v>FeatureのParam3を指定値に上書き</v>
       </c>
       <c r="E374">
         <v>13010</v>
@@ -43474,7 +43474,7 @@
       </c>
       <c r="D375" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C375,Define!P:P))</f>
-        <v>指定のFeatureのParam3を増やす</v>
+        <v>FeatureのParam3を指定値に上書き</v>
       </c>
       <c r="E375">
         <v>13020</v>
@@ -43530,7 +43530,7 @@
       </c>
       <c r="D377" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C377,Define!P:P))</f>
-        <v>指定のFeatureのParam3を増やす</v>
+        <v>FeatureのParam3を指定値に上書き</v>
       </c>
       <c r="E377">
         <v>13040</v>
@@ -43614,7 +43614,7 @@
       </c>
       <c r="D380" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C380,Define!P:P))</f>
-        <v>指定のFeatureのParam1を増やす</v>
+        <v>FeatureのParam1を指定値に上書き</v>
       </c>
       <c r="E380">
         <v>13070</v>
@@ -43642,7 +43642,7 @@
       </c>
       <c r="D381" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C381,Define!P:P))</f>
-        <v>指定のFeatureのParam3を増やす</v>
+        <v>FeatureのParam3を指定値に上書き</v>
       </c>
       <c r="E381">
         <v>13080</v>
@@ -43670,7 +43670,7 @@
       </c>
       <c r="D382" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C382,Define!P:P))</f>
-        <v>指定のFeatureのParam3を増やす</v>
+        <v>FeatureのParam3を指定値に上書き</v>
       </c>
       <c r="E382">
         <v>13090</v>
@@ -43698,7 +43698,7 @@
       </c>
       <c r="D383" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C383,Define!P:P))</f>
-        <v>指定のFeatureのParam2を増やす</v>
+        <v>FeatureのParam2を指定値に上書き</v>
       </c>
       <c r="E383">
         <v>14010</v>
@@ -43726,7 +43726,7 @@
       </c>
       <c r="D384" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C384,Define!P:P))</f>
-        <v>指定のFeatureのParam1を増やす</v>
+        <v>FeatureのParam1を指定値に上書き</v>
       </c>
       <c r="E384">
         <v>14020</v>
@@ -43754,7 +43754,7 @@
       </c>
       <c r="D385" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C385,Define!P:P))</f>
-        <v>指定のFeatureのParam3を増やす</v>
+        <v>FeatureのParam3を指定値に上書き</v>
       </c>
       <c r="E385">
         <v>14030</v>
@@ -43782,7 +43782,7 @@
       </c>
       <c r="D386" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C386,Define!P:P))</f>
-        <v>指定のFeatureのParam3を増やす</v>
+        <v>FeatureのParam3を指定値に上書き</v>
       </c>
       <c r="E386">
         <v>14040</v>
@@ -43810,7 +43810,7 @@
       </c>
       <c r="D387" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C387,Define!P:P))</f>
-        <v>指定のFeatureのParam3を増やす</v>
+        <v>FeatureのParam3を指定値に上書き</v>
       </c>
       <c r="E387">
         <v>14050</v>
@@ -43838,7 +43838,7 @@
       </c>
       <c r="D388" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C388,Define!P:P))</f>
-        <v>指定のFeatureのParam1を増やす</v>
+        <v>FeatureのParam1を指定値に上書き</v>
       </c>
       <c r="E388">
         <v>14060</v>
@@ -43866,7 +43866,7 @@
       </c>
       <c r="D389" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C389,Define!P:P))</f>
-        <v>指定のFeatureのParam2を増やす</v>
+        <v>FeatureのParam2を指定値に上書き</v>
       </c>
       <c r="E389">
         <v>14070</v>
@@ -43894,7 +43894,7 @@
       </c>
       <c r="D390" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C390,Define!P:P))</f>
-        <v>指定のFeatureのParam1を増やす</v>
+        <v>FeatureのParam1を指定値に上書き</v>
       </c>
       <c r="E390">
         <v>14080</v>
@@ -43950,7 +43950,7 @@
       </c>
       <c r="D392" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C392,Define!P:P))</f>
-        <v>指定のFeatureのParam3を増やす</v>
+        <v>FeatureのParam3を指定値に上書き</v>
       </c>
       <c r="E392">
         <v>15010</v>
@@ -43978,7 +43978,7 @@
       </c>
       <c r="D393" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C393,Define!P:P))</f>
-        <v>指定のFeatureのParam3を増やす</v>
+        <v>FeatureのParam3を指定値に上書き</v>
       </c>
       <c r="E393">
         <v>15020</v>
@@ -44006,7 +44006,7 @@
       </c>
       <c r="D394" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C394,Define!P:P))</f>
-        <v>指定のFeatureのParam1を増やす</v>
+        <v>FeatureのParam1を指定値に上書き</v>
       </c>
       <c r="E394">
         <v>15030</v>
@@ -44034,7 +44034,7 @@
       </c>
       <c r="D395" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C395,Define!P:P))</f>
-        <v>指定のFeatureのParam3を増やす</v>
+        <v>FeatureのParam3を指定値に上書き</v>
       </c>
       <c r="E395">
         <v>15040</v>
@@ -44062,7 +44062,7 @@
       </c>
       <c r="D396" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C396,Define!P:P))</f>
-        <v>指定のFeatureのParam3を増やす</v>
+        <v>FeatureのParam3を指定値に上書き</v>
       </c>
       <c r="E396">
         <v>15050</v>
@@ -44090,7 +44090,7 @@
       </c>
       <c r="D397" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C397,Define!P:P))</f>
-        <v>指定のFeatureのParam3を増やす</v>
+        <v>FeatureのParam3を指定値に上書き</v>
       </c>
       <c r="E397">
         <v>15060</v>
@@ -44118,7 +44118,7 @@
       </c>
       <c r="D398" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C398,Define!P:P))</f>
-        <v>指定のFeatureのParam3を増やす</v>
+        <v>FeatureのParam3を指定値に上書き</v>
       </c>
       <c r="E398">
         <v>15070</v>
@@ -44146,7 +44146,7 @@
       </c>
       <c r="D399" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C399,Define!P:P))</f>
-        <v>指定のFeatureのParam3を増やす</v>
+        <v>FeatureのParam3を指定値に上書き</v>
       </c>
       <c r="E399">
         <v>15080</v>
@@ -44174,7 +44174,7 @@
       </c>
       <c r="D400" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C400,Define!P:P))</f>
-        <v>指定のFeatureのParam3を増やす</v>
+        <v>FeatureのParam3を指定値に上書き</v>
       </c>
       <c r="E400">
         <v>15090</v>

--- a/Assets/Data/Skills.xlsx
+++ b/Assets/Data/Skills.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1109" uniqueCount="881">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1110" uniqueCount="881">
   <si>
     <t>Id</t>
   </si>
@@ -430,7 +430,7 @@
     <t>ヒーリング</t>
   </si>
   <si>
-    <t>(制限)バトル中1回まで
+    <t>(制限)出撃中5回まで
 敵味方一人のHpを/f[f,0,1]回復
 アンデッドには2倍のダメージ</t>
   </si>
@@ -791,7 +791,7 @@
   <si>
     <t>(条件)自身が行動する前に発動
 ダメージの/f[f,0,3]%分Hp回復
-会得していたらさらに/f[f,1,3]分Hp回復</t>
+会得していたらさらに/f[f,1,3]%分Hp回復</t>
   </si>
   <si>
     <t>アイスセイバー</t>
@@ -815,8 +815,8 @@
   <si>
     <t>(条件)自身の攻撃成功時
 挑発状態ではない対象に挑発付与
-自身のDEFを/f[f,1,2]ターン/f[f,1,3]アップ
-会得していたらさらに/f[f,2,3]アップ
+自身のDEFを1ターン2アップ
+会得していたらさらに2アップ
 /s</t>
   </si>
   <si>
@@ -2921,10 +2921,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -2950,7 +2950,98 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -2965,52 +3056,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -3019,37 +3065,6 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -3066,21 +3081,6 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -3107,7 +3107,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3119,7 +3155,97 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3131,67 +3257,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3209,85 +3287,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3298,6 +3298,45 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -3318,8 +3357,10 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
         <color theme="4"/>
       </bottom>
       <diagonal/>
@@ -3330,36 +3371,6 @@
       <top/>
       <bottom style="double">
         <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -3387,17 +3398,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -3406,145 +3406,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="17" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="17" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="17" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -17506,11 +17506,11 @@
         <v>自己強化</v>
       </c>
       <c r="F110">
-        <v>3347</v>
-      </c>
-      <c r="G110" t="str">
+        <v>0</v>
+      </c>
+      <c r="G110" t="e">
         <f>INDEX([1]Animations!B:B,MATCH(F110,[1]Animations!A:A))</f>
-        <v>Genfulew_Effect/Enemy_CR_Charge2</v>
+        <v>#N/A</v>
       </c>
       <c r="H110">
         <v>1</v>
@@ -36482,32 +36482,35 @@
         <v>100</v>
       </c>
     </row>
-    <row r="134" spans="1:8">
+    <row r="134" spans="1:9">
       <c r="A134">
-        <v>13110</v>
+        <v>13111</v>
       </c>
       <c r="B134" t="str">
         <f>INDEX(TextData!B:B,MATCH(A134,TextData!A:A))</f>
         <v>デコイプラス</v>
       </c>
       <c r="C134">
-        <v>13110</v>
+        <v>3010</v>
       </c>
       <c r="D134" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C134,Define!P:P))</f>
-        <v>対象のバフを奪い取る</v>
+        <v>ステート付与</v>
       </c>
       <c r="E134">
-        <v>6030</v>
+        <v>1050</v>
       </c>
       <c r="F134">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G134">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H134">
         <v>100</v>
+      </c>
+      <c r="I134" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="135" spans="1:9">
@@ -36519,11 +36522,11 @@
         <v>デコイプラス</v>
       </c>
       <c r="C135">
-        <v>3010</v>
+        <v>6030</v>
       </c>
       <c r="D135" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C135,Define!P:P))</f>
-        <v>ステート付与</v>
+        <v>FeatureのParam3を指定値に上書き</v>
       </c>
       <c r="E135">
         <v>1050</v>
@@ -41051,7 +41054,7 @@
         <v>10</v>
       </c>
       <c r="F289">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G289">
         <v>0</v>
@@ -44296,17 +44299,17 @@
         <v>ヒーリング</v>
       </c>
       <c r="C4">
-        <v>11010</v>
+        <v>11011</v>
       </c>
       <c r="D4" t="str">
         <f>INDEX(Define!V:V,MATCH(C4,Define!U:U))</f>
-        <v>バトル中使用回数が〇以下</v>
+        <v>Period中使用回数が〇以下</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G4">
         <v>0</v>

--- a/Assets/Data/Skills.xlsx
+++ b/Assets/Data/Skills.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8270"/>
+    <workbookView windowWidth="19200" windowHeight="7820"/>
   </bookViews>
   <sheets>
     <sheet name="Skills" sheetId="1" r:id="rId1"/>
@@ -2956,10 +2956,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -2977,6 +2977,36 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -2984,8 +3014,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -2999,22 +3030,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
-      <sz val="18"/>
+      <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -3030,7 +3047,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -3044,9 +3061,15 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -3054,6 +3077,13 @@
     <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -3084,38 +3114,8 @@
     </font>
     <font>
       <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -3142,13 +3142,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3166,7 +3172,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3178,7 +3184,121 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3190,109 +3310,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3304,25 +3322,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3333,6 +3333,30 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -3351,17 +3375,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -3401,15 +3419,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -3424,15 +3433,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -3441,145 +3441,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="25" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="20" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="20" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="23" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -13361,7 +13361,6 @@
       <c r="F59">
         <v>0</v>
       </c>
-      <c r="G59"/>
       <c r="H59">
         <v>1</v>
       </c>
@@ -16640,7 +16639,7 @@
         <v>3</v>
       </c>
       <c r="L99">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="M99">
         <v>3</v>

--- a/Assets/Data/Skills.xlsx
+++ b/Assets/Data/Skills.xlsx
@@ -2957,9 +2957,9 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -2978,6 +2978,38 @@
     </font>
     <font>
       <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="18"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -2985,16 +3017,31 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -3014,9 +3061,23 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -3024,7 +3085,7 @@
     <font>
       <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -3038,24 +3099,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <i/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -3069,53 +3115,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -3142,7 +3142,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3154,7 +3160,157 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3166,163 +3322,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3333,30 +3333,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -3395,11 +3371,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
       <bottom style="double">
-        <color rgb="FFFF8001"/>
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -3419,17 +3401,35 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
       </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
       </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
       </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -3441,145 +3441,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="25" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -12822,21 +12822,21 @@
         <v>魔法</v>
       </c>
       <c r="Q52">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R52" t="str">
         <f>INDEX(Define!K:K,MATCH(Q52,Define!J:J))</f>
-        <v>自身</v>
+        <v>味方</v>
       </c>
       <c r="S52">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="T52" t="str">
         <f>INDEX(Define!N:N,MATCH(S52,Define!M:M))</f>
-        <v>自身</v>
+        <v>単体・自身を除く</v>
       </c>
       <c r="U52">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V52">
         <v>1</v>

--- a/Assets/Data/Skills.xlsx
+++ b/Assets/Data/Skills.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="7820"/>
+    <workbookView windowWidth="19200" windowHeight="7960" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Skills" sheetId="1" r:id="rId1"/>
@@ -2956,9 +2956,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
@@ -2977,7 +2977,67 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -2993,6 +3053,14 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
@@ -3001,9 +3069,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <u/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -3018,90 +3086,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -3116,6 +3101,21 @@
     <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -3142,7 +3142,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3154,7 +3184,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3166,37 +3214,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3208,31 +3226,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3250,7 +3244,73 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3262,67 +3322,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3360,6 +3360,21 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top style="thin">
@@ -3386,17 +3401,20 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -3415,24 +3433,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -3441,16 +3441,16 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -3459,127 +3459,127 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>

--- a/Assets/Data/Skills.xlsx
+++ b/Assets/Data/Skills.xlsx
@@ -571,35 +571,35 @@
 DEFが/f[f,0,3]アップ</t>
   </si>
   <si>
-    <t>炎の加護</t>
+    <t>先天属性・炎</t>
   </si>
   <si>
     <t>炎属性適性が高く
 氷属性攻撃に弱くなる</t>
   </si>
   <si>
-    <t>雷の加護</t>
+    <t>先天属性・雷</t>
   </si>
   <si>
     <t>雷属性適性が高く
 炎属性攻撃に弱くなる</t>
   </si>
   <si>
-    <t>氷の加護</t>
+    <t>先天属性・氷</t>
   </si>
   <si>
     <t>氷属性適性が高く
 雷属性攻撃に弱くなる</t>
   </si>
   <si>
-    <t>光の加護</t>
+    <t>先天属性・光</t>
   </si>
   <si>
     <t>光属性適性が高く
 闇属性攻撃に弱くなる</t>
   </si>
   <si>
-    <t>闇の加護</t>
+    <t>先天属性・闇</t>
   </si>
   <si>
     <t>闇属性適性が高く
@@ -2956,10 +2956,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -2977,6 +2977,21 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -2984,32 +2999,24 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -3024,15 +3031,30 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -3046,7 +3068,7 @@
     </font>
     <font>
       <b/>
-      <sz val="15"/>
+      <sz val="11"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -3055,23 +3077,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -3085,6 +3091,22 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -3093,29 +3115,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -3148,7 +3148,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3160,7 +3202,103 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3178,151 +3316,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3333,6 +3333,30 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -3351,15 +3375,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -3370,32 +3385,6 @@
         <color rgb="FF3F3F3F"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
         <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
@@ -3419,17 +3408,28 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
       </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
       </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color theme="4"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -3441,145 +3441,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="13" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="13" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="24" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -13349,7 +13349,7 @@
       </c>
       <c r="C59" t="str">
         <f>INDEX(TextData!B:B,MATCH(B59,TextData!A:A))</f>
-        <v>雷の加護</v>
+        <v>先天属性・雷</v>
       </c>
       <c r="D59">
         <v>6</v>
@@ -13427,7 +13427,7 @@
       </c>
       <c r="C60" t="str">
         <f>INDEX(TextData!B:B,MATCH(B60,TextData!A:A))</f>
-        <v>氷の加護</v>
+        <v>先天属性・氷</v>
       </c>
       <c r="D60">
         <v>6</v>
@@ -13505,7 +13505,7 @@
       </c>
       <c r="C61" t="str">
         <f>INDEX(TextData!B:B,MATCH(B61,TextData!A:A))</f>
-        <v>炎の加護</v>
+        <v>先天属性・炎</v>
       </c>
       <c r="D61">
         <v>6</v>
@@ -13583,7 +13583,7 @@
       </c>
       <c r="C62" t="str">
         <f>INDEX(TextData!B:B,MATCH(B62,TextData!A:A))</f>
-        <v>闇の加護</v>
+        <v>先天属性・闇</v>
       </c>
       <c r="D62">
         <v>6</v>
@@ -13661,7 +13661,7 @@
       </c>
       <c r="C63" t="str">
         <f>INDEX(TextData!B:B,MATCH(B63,TextData!A:A))</f>
-        <v>光の加護</v>
+        <v>先天属性・光</v>
       </c>
       <c r="D63">
         <v>6</v>

--- a/Assets/Data/Skills.xlsx
+++ b/Assets/Data/Skills.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="7960" activeTab="1"/>
+    <workbookView windowWidth="19200" windowHeight="8340" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Skills" sheetId="1" r:id="rId1"/>
@@ -20,13 +20,14 @@
   </externalReferences>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Skills!$F$1:$F$258</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Triggers!$E$1:$E$163</definedName>
   </definedNames>
   <calcPr calcId="144525" concurrentCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1120" uniqueCount="891">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1115" uniqueCount="886">
   <si>
     <t>Id</t>
   </si>
@@ -2102,222 +2103,222 @@
     <t>元素</t>
   </si>
   <si>
+    <t>バトル開始時</t>
+  </si>
+  <si>
+    <t>Numinouse消費率</t>
+  </si>
+  <si>
+    <t>列</t>
+  </si>
+  <si>
+    <t>雷</t>
+  </si>
+  <si>
+    <t>パッシブ</t>
+  </si>
+  <si>
+    <t>味方</t>
+  </si>
+  <si>
+    <t>Hp吸収ダメージ</t>
+  </si>
+  <si>
+    <t>自身のHpが〇%以上</t>
+  </si>
+  <si>
+    <t>光</t>
+  </si>
+  <si>
+    <t>Hpが減る</t>
+  </si>
+  <si>
+    <t>敵Lv</t>
+  </si>
+  <si>
+    <t>全体</t>
+  </si>
+  <si>
+    <t>氷</t>
+  </si>
+  <si>
+    <t>神化</t>
+  </si>
+  <si>
+    <t>全員</t>
+  </si>
+  <si>
+    <t>Hp固定ダメージ</t>
+  </si>
+  <si>
+    <t>Hp%〇以下の味方</t>
+  </si>
+  <si>
+    <t>理術</t>
+  </si>
+  <si>
+    <t>自身の行動前</t>
+  </si>
+  <si>
+    <t>SP加算</t>
+  </si>
+  <si>
+    <t>自身</t>
+  </si>
+  <si>
+    <t>特定ステートダメージ</t>
+  </si>
+  <si>
+    <t>Hp%〇以上の味方</t>
+  </si>
+  <si>
+    <t>精神</t>
+  </si>
+  <si>
+    <t>相手の行動前・対象決定前</t>
+  </si>
+  <si>
+    <t>隷従属度</t>
+  </si>
+  <si>
+    <t>闇</t>
+  </si>
+  <si>
+    <t>レリック</t>
+  </si>
+  <si>
+    <t>反撃</t>
+  </si>
+  <si>
+    <t>最前列のみ</t>
+  </si>
+  <si>
+    <t>効果無視Hpダメージ</t>
+  </si>
+  <si>
+    <t>Hp%〇以下の敵</t>
+  </si>
+  <si>
+    <t>超次元</t>
+  </si>
+  <si>
+    <t>味方の行動前</t>
+  </si>
+  <si>
+    <t>アルカナ変更</t>
+  </si>
+  <si>
+    <t>無</t>
+  </si>
+  <si>
+    <t>強化</t>
+  </si>
+  <si>
+    <t>追撃</t>
+  </si>
+  <si>
+    <t>単体・自身を除く</t>
+  </si>
+  <si>
+    <t>Hp割合固定ダメージ</t>
+  </si>
+  <si>
+    <t>Hp%〇以上の敵</t>
+  </si>
+  <si>
+    <t>自己強化</t>
+  </si>
+  <si>
+    <t>割り込み(直前)</t>
+  </si>
+  <si>
+    <t>ステータスコスト減算</t>
+  </si>
+  <si>
+    <t>装備</t>
+  </si>
+  <si>
+    <t>Triggerの条件を満たす</t>
+  </si>
+  <si>
+    <t>列・自身を除く</t>
+  </si>
+  <si>
+    <t>Hpダメージ割合追加ダメージ</t>
+  </si>
+  <si>
+    <t>最もHpが少ない味方</t>
+  </si>
+  <si>
+    <t>工作</t>
+  </si>
+  <si>
+    <t>かばう専用。割り込みの最優先</t>
+  </si>
+  <si>
+    <t>敵前衛消滅</t>
+  </si>
+  <si>
+    <t>カインド</t>
+  </si>
+  <si>
+    <t>パーティ</t>
+  </si>
+  <si>
+    <t>全体・自身を除く</t>
+  </si>
+  <si>
+    <t>Hp犠牲ダメージ</t>
+  </si>
+  <si>
+    <t>最もHpが多い味方</t>
+  </si>
+  <si>
+    <t>半神</t>
+  </si>
+  <si>
+    <t>相手の行動前・対象決定後</t>
+  </si>
+  <si>
+    <t>撃破SPアップ</t>
+  </si>
+  <si>
+    <t>アルカナ使用</t>
+  </si>
+  <si>
+    <t>ランダム</t>
+  </si>
+  <si>
+    <t>受けたダメージ総計ダメージ</t>
+  </si>
+  <si>
+    <t>最もHpが少ない敵</t>
+  </si>
+  <si>
     <t>使ったとき</t>
   </si>
   <si>
-    <t>Numinouse消費率</t>
-  </si>
-  <si>
-    <t>列</t>
-  </si>
-  <si>
-    <t>雷</t>
-  </si>
-  <si>
-    <t>パッシブ</t>
-  </si>
-  <si>
-    <t>味方</t>
-  </si>
-  <si>
-    <t>Hp吸収ダメージ</t>
-  </si>
-  <si>
-    <t>自身のHpが〇%以上</t>
-  </si>
-  <si>
-    <t>光</t>
+    <t>属性適性増加</t>
+  </si>
+  <si>
+    <t>転生</t>
+  </si>
+  <si>
+    <t>単体と両隣</t>
+  </si>
+  <si>
+    <t>Hp貫通ダメージ</t>
+  </si>
+  <si>
+    <t>最もHpが多い敵</t>
+  </si>
+  <si>
+    <t>その他</t>
   </si>
   <si>
     <t>使った後</t>
   </si>
   <si>
-    <t>敵Lv</t>
-  </si>
-  <si>
-    <t>全体</t>
-  </si>
-  <si>
-    <t>氷</t>
-  </si>
-  <si>
-    <t>神化</t>
-  </si>
-  <si>
-    <t>全員</t>
-  </si>
-  <si>
-    <t>Hp固定ダメージ</t>
-  </si>
-  <si>
-    <t>Hp%〇以下の味方</t>
-  </si>
-  <si>
-    <t>理術</t>
-  </si>
-  <si>
-    <t>割り込み</t>
-  </si>
-  <si>
-    <t>SP加算</t>
-  </si>
-  <si>
-    <t>自身</t>
-  </si>
-  <si>
-    <t>特定ステートダメージ</t>
-  </si>
-  <si>
-    <t>Hp%〇以上の味方</t>
-  </si>
-  <si>
-    <t>精神</t>
-  </si>
-  <si>
-    <t>バトル開始時</t>
-  </si>
-  <si>
-    <t>隷従属度</t>
-  </si>
-  <si>
-    <t>闇</t>
-  </si>
-  <si>
-    <t>レリック</t>
-  </si>
-  <si>
-    <t>反撃</t>
-  </si>
-  <si>
-    <t>最前列のみ</t>
-  </si>
-  <si>
-    <t>効果無視Hpダメージ</t>
-  </si>
-  <si>
-    <t>Hp%〇以下の敵</t>
-  </si>
-  <si>
-    <t>超次元</t>
-  </si>
-  <si>
-    <t>行動開始前</t>
-  </si>
-  <si>
-    <t>アルカナ変更</t>
-  </si>
-  <si>
-    <t>無</t>
-  </si>
-  <si>
-    <t>強化</t>
-  </si>
-  <si>
-    <t>追撃</t>
-  </si>
-  <si>
-    <t>単体・自身を除く</t>
-  </si>
-  <si>
-    <t>Hp割合固定ダメージ</t>
-  </si>
-  <si>
-    <t>Hp%〇以上の敵</t>
-  </si>
-  <si>
-    <t>自己強化</t>
-  </si>
-  <si>
-    <t>Hpが減る</t>
-  </si>
-  <si>
-    <t>ステータスコスト減算</t>
-  </si>
-  <si>
-    <t>装備</t>
-  </si>
-  <si>
-    <t>Triggerの条件を満たす</t>
-  </si>
-  <si>
-    <t>列・自身を除く</t>
-  </si>
-  <si>
-    <t>Hpダメージ割合追加ダメージ</t>
-  </si>
-  <si>
-    <t>最もHpが少ない味方</t>
-  </si>
-  <si>
-    <t>工作</t>
-  </si>
-  <si>
-    <t>バトル開始時と行動開始前</t>
-  </si>
-  <si>
-    <t>敵前衛消滅</t>
-  </si>
-  <si>
-    <t>カインド</t>
-  </si>
-  <si>
-    <t>パーティ</t>
-  </si>
-  <si>
-    <t>全体・自身を除く</t>
-  </si>
-  <si>
-    <t>Hp犠牲ダメージ</t>
-  </si>
-  <si>
-    <t>最もHpが多い味方</t>
-  </si>
-  <si>
-    <t>半神</t>
-  </si>
-  <si>
-    <t>バトル開始時と使った後</t>
-  </si>
-  <si>
-    <t>撃破SPアップ</t>
-  </si>
-  <si>
-    <t>アルカナ使用</t>
-  </si>
-  <si>
-    <t>ランダム</t>
-  </si>
-  <si>
-    <t>受けたダメージ総計ダメージ</t>
-  </si>
-  <si>
-    <t>最もHpが少ない敵</t>
-  </si>
-  <si>
-    <t>自身の行動前</t>
-  </si>
-  <si>
-    <t>属性適性増加</t>
-  </si>
-  <si>
-    <t>転生</t>
-  </si>
-  <si>
-    <t>単体と両隣</t>
-  </si>
-  <si>
-    <t>Hp貫通ダメージ</t>
-  </si>
-  <si>
-    <t>最もHpが多い敵</t>
-  </si>
-  <si>
-    <t>その他</t>
-  </si>
-  <si>
-    <t>相手の行動前・対象決定前</t>
-  </si>
-  <si>
     <t>命令不可</t>
   </si>
   <si>
@@ -2333,9 +2334,6 @@
     <t xml:space="preserve"> </t>
   </si>
   <si>
-    <t>味方の行動前</t>
-  </si>
-  <si>
     <t>コマンドLvアップ</t>
   </si>
   <si>
@@ -2345,9 +2343,6 @@
     <t>自身のMpが〇以下</t>
   </si>
   <si>
-    <t>かばう専用。割り込みの最優先</t>
-  </si>
-  <si>
     <t>ステータスアップ</t>
   </si>
   <si>
@@ -2357,9 +2352,6 @@
     <t>自身のMpが〇以上</t>
   </si>
   <si>
-    <t>相手の行動前・対象決定後</t>
-  </si>
-  <si>
     <t>魔法入手</t>
   </si>
   <si>
@@ -2369,9 +2361,6 @@
     <t>Mp〇未満の味方</t>
   </si>
   <si>
-    <t>ターン開始前</t>
-  </si>
-  <si>
     <t>最大HpとMpアップ</t>
   </si>
   <si>
@@ -2379,9 +2368,6 @@
   </si>
   <si>
     <t>Mp〇以上の味方</t>
-  </si>
-  <si>
-    <t>ターン開始後</t>
   </si>
   <si>
     <t>ターン数アップ</t>
@@ -2956,10 +2942,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -2977,21 +2963,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -3000,68 +2971,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -3077,7 +2987,52 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -3091,9 +3046,31 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -3107,15 +3084,24 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -3142,13 +3128,67 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3160,25 +3200,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3190,103 +3242,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3304,25 +3278,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3333,45 +3319,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -3393,8 +3340,38 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -3404,6 +3381,15 @@
       <top/>
       <bottom style="medium">
         <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -3441,145 +3427,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="14" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="13" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="13" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="24" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="26" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -3617,12 +3603,12 @@
     <cellStyle name="通貨[0]" xfId="4" builtinId="7"/>
     <cellStyle name="40% - アクセント 5" xfId="5" builtinId="47"/>
     <cellStyle name="通貨" xfId="6" builtinId="4"/>
-    <cellStyle name="パーセント" xfId="7" builtinId="5"/>
-    <cellStyle name="ハイパーリンク" xfId="8" builtinId="8"/>
-    <cellStyle name="アクセント 2" xfId="9" builtinId="33"/>
-    <cellStyle name="訪問済ハイパーリンク" xfId="10" builtinId="9"/>
-    <cellStyle name="20% - アクセント 4" xfId="11" builtinId="42"/>
-    <cellStyle name="メモ" xfId="12" builtinId="10"/>
+    <cellStyle name="20% - アクセント 4" xfId="7" builtinId="42"/>
+    <cellStyle name="メモ" xfId="8" builtinId="10"/>
+    <cellStyle name="パーセント" xfId="9" builtinId="5"/>
+    <cellStyle name="ハイパーリンク" xfId="10" builtinId="8"/>
+    <cellStyle name="アクセント 2" xfId="11" builtinId="33"/>
+    <cellStyle name="訪問済ハイパーリンク" xfId="12" builtinId="9"/>
     <cellStyle name="良い" xfId="13" builtinId="26"/>
     <cellStyle name="警告文" xfId="14" builtinId="11"/>
     <cellStyle name="リンクセル" xfId="15" builtinId="24"/>
@@ -44675,7 +44661,7 @@
         <v>自身の攻撃で敵を倒す</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>61</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -44703,7 +44689,7 @@
         <v>StateId状態になっている</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>61</v>
       </c>
       <c r="F3">
         <v>2030</v>
@@ -44759,7 +44745,7 @@
         <v>なし</v>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F5">
         <v>0</v>
@@ -44787,7 +44773,7 @@
         <v>Lvが〇以上</v>
       </c>
       <c r="E6">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F6">
         <v>20</v>
@@ -44815,7 +44801,7 @@
         <v>なし</v>
       </c>
       <c r="E7">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F7">
         <v>0</v>
@@ -44843,7 +44829,7 @@
         <v>Lvが〇以上</v>
       </c>
       <c r="E8">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F8">
         <v>20</v>
@@ -44871,7 +44857,7 @@
         <v>Lvが〇以上</v>
       </c>
       <c r="E9">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F9">
         <v>20</v>
@@ -44899,7 +44885,7 @@
         <v>Lvが〇以上</v>
       </c>
       <c r="E10">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F10">
         <v>20</v>
@@ -44927,7 +44913,7 @@
         <v>なし</v>
       </c>
       <c r="E11">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F11">
         <v>0</v>
@@ -44955,7 +44941,7 @@
         <v>自身のHpが〇%以下</v>
       </c>
       <c r="E12">
-        <v>2</v>
+        <v>61</v>
       </c>
       <c r="F12">
         <v>25</v>
@@ -44983,7 +44969,7 @@
         <v>なし</v>
       </c>
       <c r="E13">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F13">
         <v>0</v>
@@ -45011,7 +44997,7 @@
         <v>味方が攻撃タイプの行動をしようとしている</v>
       </c>
       <c r="E14">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="F14">
         <v>0</v>
@@ -45039,7 +45025,7 @@
         <v>StateId状態になっている</v>
       </c>
       <c r="E15">
-        <v>2</v>
+        <v>61</v>
       </c>
       <c r="F15">
         <v>1010</v>
@@ -45067,7 +45053,7 @@
         <v>バトル中使用回数が〇以下</v>
       </c>
       <c r="E16">
-        <v>2</v>
+        <v>61</v>
       </c>
       <c r="F16">
         <v>1</v>
@@ -45151,7 +45137,7 @@
         <v>味方が攻撃タイプの行動をしようとしている</v>
       </c>
       <c r="E19">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="F19">
         <v>0</v>
@@ -45179,7 +45165,7 @@
         <v>自身が攻撃タイプの行動をしようとしている</v>
       </c>
       <c r="E20">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="F20">
         <v>0</v>
@@ -45207,7 +45193,7 @@
         <v>味方がPassive魔法を成功する</v>
       </c>
       <c r="E21">
-        <v>2</v>
+        <v>61</v>
       </c>
       <c r="F21">
         <v>0</v>
@@ -45235,7 +45221,7 @@
         <v>攻撃成功時相手が火傷ではない</v>
       </c>
       <c r="E22">
-        <v>2</v>
+        <v>61</v>
       </c>
       <c r="F22">
         <v>0</v>
@@ -45263,7 +45249,7 @@
         <v>なし</v>
       </c>
       <c r="E23">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F23">
         <v>0</v>
@@ -45291,7 +45277,7 @@
         <v>なし</v>
       </c>
       <c r="E24">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F24">
         <v>0</v>
@@ -45319,7 +45305,7 @@
         <v>なし</v>
       </c>
       <c r="E25">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F25">
         <v>0</v>
@@ -45347,7 +45333,7 @@
         <v>なし</v>
       </c>
       <c r="E26">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F26">
         <v>0</v>
@@ -45375,7 +45361,7 @@
         <v>なし</v>
       </c>
       <c r="E27">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F27">
         <v>0</v>
@@ -45403,7 +45389,7 @@
         <v>味方が攻撃を成功する</v>
       </c>
       <c r="E28">
-        <v>2</v>
+        <v>61</v>
       </c>
       <c r="F28">
         <v>0</v>
@@ -45431,7 +45417,7 @@
         <v>味方が攻撃タイプの行動をしようとしている</v>
       </c>
       <c r="E29">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="F29">
         <v>0</v>
@@ -45459,7 +45445,7 @@
         <v>攻撃を回避した時</v>
       </c>
       <c r="E30">
-        <v>2</v>
+        <v>61</v>
       </c>
       <c r="F30">
         <v>0</v>
@@ -45487,7 +45473,7 @@
         <v>なし</v>
       </c>
       <c r="E31">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F31">
         <v>0</v>
@@ -45515,7 +45501,7 @@
         <v>味方が攻撃を受ける。Param2で対象指定</v>
       </c>
       <c r="E32">
-        <v>3</v>
+        <v>31</v>
       </c>
       <c r="F32">
         <v>0</v>
@@ -45571,7 +45557,7 @@
         <v>なし</v>
       </c>
       <c r="E34">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F34">
         <v>0</v>
@@ -45599,7 +45585,7 @@
         <v>なし</v>
       </c>
       <c r="E35">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F35">
         <v>0</v>
@@ -45627,7 +45613,7 @@
         <v>味方が攻撃を受ける。Param2で対象指定</v>
       </c>
       <c r="E36">
-        <v>3</v>
+        <v>31</v>
       </c>
       <c r="F36">
         <v>0</v>
@@ -45655,7 +45641,7 @@
         <v>攻撃を受けた対象がAbnorml状態になった</v>
       </c>
       <c r="E37">
-        <v>2</v>
+        <v>61</v>
       </c>
       <c r="F37">
         <v>0</v>
@@ -45683,7 +45669,7 @@
         <v>味方が攻撃を受ける。Param2で対象指定</v>
       </c>
       <c r="E38">
-        <v>3</v>
+        <v>31</v>
       </c>
       <c r="F38">
         <v>0</v>
@@ -45711,7 +45697,7 @@
         <v>相手がバフの行動をしようとしている</v>
       </c>
       <c r="E39">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="F39">
         <v>0</v>
@@ -45767,7 +45753,7 @@
         <v>攻撃成功時〇%で</v>
       </c>
       <c r="E41">
-        <v>1</v>
+        <v>51</v>
       </c>
       <c r="F41">
         <v>33</v>
@@ -45795,7 +45781,7 @@
         <v>自身が攻撃タイプの行動をしようとしている</v>
       </c>
       <c r="E42">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="F42">
         <v>0</v>
@@ -45823,7 +45809,7 @@
         <v>攻撃成功時相手が凍結ではない</v>
       </c>
       <c r="E43">
-        <v>2</v>
+        <v>61</v>
       </c>
       <c r="F43">
         <v>0</v>
@@ -45879,7 +45865,7 @@
         <v>かばう成立後かばった対象</v>
       </c>
       <c r="E45">
-        <v>2</v>
+        <v>61</v>
       </c>
       <c r="F45">
         <v>0</v>
@@ -45907,7 +45893,7 @@
         <v>攻撃成功時相手が挑発ではない</v>
       </c>
       <c r="E46">
-        <v>2</v>
+        <v>61</v>
       </c>
       <c r="F46">
         <v>0</v>
@@ -45935,7 +45921,7 @@
         <v>なし</v>
       </c>
       <c r="E47">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F47">
         <v>0</v>
@@ -46047,7 +46033,7 @@
         <v>なし</v>
       </c>
       <c r="E51">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F51">
         <v>0</v>
@@ -46075,7 +46061,7 @@
         <v>なし</v>
       </c>
       <c r="E52">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F52">
         <v>0</v>
@@ -46103,7 +46089,7 @@
         <v>なし</v>
       </c>
       <c r="E53">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F53">
         <v>0</v>
@@ -46131,7 +46117,7 @@
         <v>自身がパッシブを受ける</v>
       </c>
       <c r="E54">
-        <v>2</v>
+        <v>61</v>
       </c>
       <c r="F54">
         <v>0</v>
@@ -46159,7 +46145,7 @@
         <v>ターン中使用回数が〇回に満たない</v>
       </c>
       <c r="E55">
-        <v>2</v>
+        <v>61</v>
       </c>
       <c r="F55">
         <v>1</v>
@@ -46187,7 +46173,7 @@
         <v>なし</v>
       </c>
       <c r="E56">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F56">
         <v>0</v>
@@ -46271,7 +46257,7 @@
         <v>自身が戦闘不能になる</v>
       </c>
       <c r="E59">
-        <v>3</v>
+        <v>31</v>
       </c>
       <c r="F59">
         <v>0</v>
@@ -46299,7 +46285,7 @@
         <v>なし</v>
       </c>
       <c r="E60">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F60">
         <v>0</v>
@@ -46327,7 +46313,7 @@
         <v>自身がデバフを受ける</v>
       </c>
       <c r="E61">
-        <v>2</v>
+        <v>61</v>
       </c>
       <c r="F61">
         <v>0</v>
@@ -46355,7 +46341,7 @@
         <v>なし</v>
       </c>
       <c r="E62">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F62">
         <v>0</v>
@@ -46383,7 +46369,7 @@
         <v>自身のHpが〇%以下</v>
       </c>
       <c r="E63">
-        <v>2</v>
+        <v>61</v>
       </c>
       <c r="F63">
         <v>25</v>
@@ -46411,7 +46397,7 @@
         <v>攻撃を受けた対象が戦闘不能になった</v>
       </c>
       <c r="E64">
-        <v>2</v>
+        <v>61</v>
       </c>
       <c r="F64">
         <v>0</v>
@@ -46439,7 +46425,7 @@
         <v>自身のHpが〇%以上</v>
       </c>
       <c r="E65">
-        <v>2</v>
+        <v>61</v>
       </c>
       <c r="F65">
         <v>100</v>
@@ -46467,7 +46453,7 @@
         <v>自身のHpが〇%以下</v>
       </c>
       <c r="E66">
-        <v>2</v>
+        <v>61</v>
       </c>
       <c r="F66">
         <v>50</v>
@@ -46495,7 +46481,7 @@
         <v>なし</v>
       </c>
       <c r="E67">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F67">
         <v>0</v>
@@ -46523,7 +46509,7 @@
         <v>味方が攻撃タイプの行動をしようとしている</v>
       </c>
       <c r="E68">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="F68">
         <v>0</v>
@@ -46551,7 +46537,7 @@
         <v>相手が回復をする</v>
       </c>
       <c r="E69">
-        <v>2</v>
+        <v>61</v>
       </c>
       <c r="F69">
         <v>0</v>
@@ -46579,7 +46565,7 @@
         <v>味方が攻撃を受ける。Param2で対象指定</v>
       </c>
       <c r="E70">
-        <v>3</v>
+        <v>31</v>
       </c>
       <c r="F70">
         <v>0</v>
@@ -46635,7 +46621,7 @@
         <v>会心攻撃成功時</v>
       </c>
       <c r="E72">
-        <v>1</v>
+        <v>51</v>
       </c>
       <c r="F72">
         <v>100</v>
@@ -46691,7 +46677,7 @@
         <v>なし</v>
       </c>
       <c r="E74">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F74">
         <v>0</v>
@@ -46719,7 +46705,7 @@
         <v>神化発動前</v>
       </c>
       <c r="E75">
-        <v>2</v>
+        <v>61</v>
       </c>
       <c r="F75">
         <v>0</v>
@@ -46747,7 +46733,7 @@
         <v>魔法を〇回使用する</v>
       </c>
       <c r="E76">
-        <v>2</v>
+        <v>61</v>
       </c>
       <c r="F76">
         <v>3</v>
@@ -46775,7 +46761,7 @@
         <v>神化発動前</v>
       </c>
       <c r="E77">
-        <v>2</v>
+        <v>61</v>
       </c>
       <c r="F77">
         <v>0</v>
@@ -46803,7 +46789,7 @@
         <v>回避を〇回行う</v>
       </c>
       <c r="E78">
-        <v>2</v>
+        <v>61</v>
       </c>
       <c r="F78">
         <v>3</v>
@@ -46887,7 +46873,7 @@
         <v>神化発動前</v>
       </c>
       <c r="E81">
-        <v>2</v>
+        <v>61</v>
       </c>
       <c r="F81">
         <v>0</v>
@@ -46915,7 +46901,7 @@
         <v>自分以外が戦闘不能</v>
       </c>
       <c r="E82">
-        <v>2</v>
+        <v>61</v>
       </c>
       <c r="F82">
         <v>0</v>
@@ -46943,7 +46929,7 @@
         <v>神化発動前</v>
       </c>
       <c r="E83">
-        <v>3</v>
+        <v>31</v>
       </c>
       <c r="F83">
         <v>0</v>
@@ -46971,7 +46957,7 @@
         <v>自身が戦闘不能になる攻撃を受ける</v>
       </c>
       <c r="E84">
-        <v>3</v>
+        <v>31</v>
       </c>
       <c r="F84">
         <v>0</v>
@@ -46999,7 +46985,7 @@
         <v>神化発動前</v>
       </c>
       <c r="E85">
-        <v>2</v>
+        <v>61</v>
       </c>
       <c r="F85">
         <v>0</v>
@@ -47027,7 +47013,7 @@
         <v>神化魔法使用回数の総計</v>
       </c>
       <c r="E86">
-        <v>2</v>
+        <v>61</v>
       </c>
       <c r="F86">
         <v>0</v>
@@ -47055,7 +47041,7 @@
         <v>神化発動前</v>
       </c>
       <c r="E87">
-        <v>2</v>
+        <v>61</v>
       </c>
       <c r="F87">
         <v>0</v>
@@ -47083,7 +47069,7 @@
         <v>自身の攻撃で敵を倒す</v>
       </c>
       <c r="E88">
-        <v>2</v>
+        <v>61</v>
       </c>
       <c r="F88">
         <v>0</v>
@@ -47111,7 +47097,7 @@
         <v>神化発動前</v>
       </c>
       <c r="E89">
-        <v>2</v>
+        <v>61</v>
       </c>
       <c r="F89">
         <v>0</v>
@@ -47139,7 +47125,7 @@
         <v>ターン数が〇</v>
       </c>
       <c r="E90">
-        <v>2</v>
+        <v>61</v>
       </c>
       <c r="F90">
         <v>10</v>
@@ -47223,7 +47209,7 @@
         <v>神化発動前</v>
       </c>
       <c r="E93">
-        <v>2</v>
+        <v>61</v>
       </c>
       <c r="F93">
         <v>0</v>
@@ -47251,7 +47237,7 @@
         <v>自身が状態異常を受ける</v>
       </c>
       <c r="E94">
-        <v>2</v>
+        <v>61</v>
       </c>
       <c r="F94">
         <v>0</v>
@@ -47279,7 +47265,7 @@
         <v>神化発動前</v>
       </c>
       <c r="E95">
-        <v>2</v>
+        <v>61</v>
       </c>
       <c r="F95">
         <v>0</v>
@@ -47307,7 +47293,7 @@
         <v>敵全員が凍結状態</v>
       </c>
       <c r="E96">
-        <v>2</v>
+        <v>61</v>
       </c>
       <c r="F96">
         <v>0</v>
@@ -47335,7 +47321,7 @@
         <v>神化発動前</v>
       </c>
       <c r="E97">
-        <v>2</v>
+        <v>61</v>
       </c>
       <c r="F97">
         <v>0</v>
@@ -47363,7 +47349,7 @@
         <v>魔法を〇回使用する</v>
       </c>
       <c r="E98">
-        <v>2</v>
+        <v>61</v>
       </c>
       <c r="F98">
         <v>3</v>
@@ -47391,7 +47377,7 @@
         <v>神化発動前</v>
       </c>
       <c r="E99">
-        <v>2</v>
+        <v>61</v>
       </c>
       <c r="F99">
         <v>0</v>
@@ -47419,7 +47405,7 @@
         <v>自分以外が戦闘不能</v>
       </c>
       <c r="E100">
-        <v>2</v>
+        <v>61</v>
       </c>
       <c r="F100">
         <v>1</v>
@@ -47447,7 +47433,7 @@
         <v>自身のHpが〇%以下</v>
       </c>
       <c r="E101">
-        <v>2</v>
+        <v>61</v>
       </c>
       <c r="F101">
         <v>25</v>
@@ -47475,7 +47461,7 @@
         <v>神化発動前</v>
       </c>
       <c r="E102">
-        <v>2</v>
+        <v>61</v>
       </c>
       <c r="F102">
         <v>0</v>
@@ -47503,7 +47489,7 @@
         <v>自身のHpが〇%以下</v>
       </c>
       <c r="E103">
-        <v>2</v>
+        <v>61</v>
       </c>
       <c r="F103">
         <v>50</v>
@@ -47531,7 +47517,7 @@
         <v>なし</v>
       </c>
       <c r="E104">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F104">
         <v>0</v>
@@ -47559,7 +47545,7 @@
         <v>神化発動前</v>
       </c>
       <c r="E105">
-        <v>2</v>
+        <v>61</v>
       </c>
       <c r="F105">
         <v>0</v>
@@ -47587,7 +47573,7 @@
         <v>自身のHpが〇%以下</v>
       </c>
       <c r="E106">
-        <v>2</v>
+        <v>61</v>
       </c>
       <c r="F106">
         <v>40</v>
@@ -47615,7 +47601,7 @@
         <v>なし</v>
       </c>
       <c r="E107">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F107">
         <v>0</v>
@@ -47643,7 +47629,7 @@
         <v>神化発動前</v>
       </c>
       <c r="E108">
-        <v>2</v>
+        <v>61</v>
       </c>
       <c r="F108">
         <v>0</v>
@@ -47671,7 +47657,7 @@
         <v>全体の行動数がparam1 x 行動数 + param2</v>
       </c>
       <c r="E109">
-        <v>2</v>
+        <v>61</v>
       </c>
       <c r="F109">
         <v>0</v>
@@ -47699,7 +47685,7 @@
         <v>自身のHpが〇%以下</v>
       </c>
       <c r="E110">
-        <v>2</v>
+        <v>61</v>
       </c>
       <c r="F110">
         <v>50</v>
@@ -47727,7 +47713,7 @@
         <v>神化発動前</v>
       </c>
       <c r="E111">
-        <v>2</v>
+        <v>61</v>
       </c>
       <c r="F111">
         <v>0</v>
@@ -47755,7 +47741,7 @@
         <v>自身のHpが〇%以下</v>
       </c>
       <c r="E112">
-        <v>2</v>
+        <v>61</v>
       </c>
       <c r="F112">
         <v>25</v>
@@ -47783,7 +47769,7 @@
         <v>なし</v>
       </c>
       <c r="E113">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F113">
         <v>0</v>
@@ -47811,7 +47797,7 @@
         <v>なし</v>
       </c>
       <c r="E114">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F114">
         <v>0</v>
@@ -47839,7 +47825,7 @@
         <v>なし</v>
       </c>
       <c r="E115">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F115">
         <v>0</v>
@@ -47867,7 +47853,7 @@
         <v>なし</v>
       </c>
       <c r="E116">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F116">
         <v>0</v>
@@ -47895,7 +47881,7 @@
         <v>なし</v>
       </c>
       <c r="E117">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F117">
         <v>0</v>
@@ -47923,7 +47909,7 @@
         <v>なし</v>
       </c>
       <c r="E118">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F118">
         <v>0</v>
@@ -47951,7 +47937,7 @@
         <v>なし</v>
       </c>
       <c r="E119">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F119">
         <v>0</v>
@@ -47979,7 +47965,7 @@
         <v>なし</v>
       </c>
       <c r="E120">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F120">
         <v>0</v>
@@ -48007,7 +47993,7 @@
         <v>なし</v>
       </c>
       <c r="E121">
-        <v>2</v>
+        <v>61</v>
       </c>
       <c r="F121">
         <v>0</v>
@@ -48035,7 +48021,7 @@
         <v>なし</v>
       </c>
       <c r="E122">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F122">
         <v>0</v>
@@ -48063,7 +48049,7 @@
         <v>なし</v>
       </c>
       <c r="E123">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F123">
         <v>0</v>
@@ -48091,7 +48077,7 @@
         <v>なし</v>
       </c>
       <c r="E124">
-        <v>2</v>
+        <v>61</v>
       </c>
       <c r="F124">
         <v>0</v>
@@ -48119,7 +48105,7 @@
         <v>なし</v>
       </c>
       <c r="E125">
-        <v>2</v>
+        <v>61</v>
       </c>
       <c r="F125">
         <v>0</v>
@@ -48147,7 +48133,7 @@
         <v>なし</v>
       </c>
       <c r="E126">
-        <v>2</v>
+        <v>61</v>
       </c>
       <c r="F126">
         <v>0</v>
@@ -48175,7 +48161,7 @@
         <v>なし</v>
       </c>
       <c r="E127">
-        <v>2</v>
+        <v>61</v>
       </c>
       <c r="F127">
         <v>0</v>
@@ -48203,7 +48189,7 @@
         <v>バトル中使用回数が〇以下</v>
       </c>
       <c r="E128">
-        <v>2</v>
+        <v>61</v>
       </c>
       <c r="F128">
         <v>1</v>
@@ -48231,7 +48217,7 @@
         <v>〇のKindを持っている敵</v>
       </c>
       <c r="E129">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F129">
         <v>12</v>
@@ -48315,7 +48301,7 @@
         <v>なし</v>
       </c>
       <c r="E132">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F132">
         <v>0</v>
@@ -48343,7 +48329,7 @@
         <v>味方が行動をする</v>
       </c>
       <c r="E133">
-        <v>2</v>
+        <v>61</v>
       </c>
       <c r="F133">
         <v>0</v>
@@ -48371,7 +48357,7 @@
         <v>行動者のターン数がparam1 x ターン数 + param2</v>
       </c>
       <c r="E134">
-        <v>2</v>
+        <v>61</v>
       </c>
       <c r="F134">
         <v>0</v>
@@ -48399,7 +48385,7 @@
         <v>なし</v>
       </c>
       <c r="E135">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F135">
         <v>0</v>
@@ -48427,7 +48413,7 @@
         <v>なし</v>
       </c>
       <c r="E136">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F136">
         <v>0</v>
@@ -48455,7 +48441,7 @@
         <v>なし</v>
       </c>
       <c r="E137">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F137">
         <v>0</v>
@@ -48483,7 +48469,7 @@
         <v>ピリオド経過</v>
       </c>
       <c r="E138">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F138">
         <v>0</v>
@@ -48511,7 +48497,7 @@
         <v>なし</v>
       </c>
       <c r="E139">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F139">
         <v>0</v>
@@ -48539,7 +48525,7 @@
         <v>なし</v>
       </c>
       <c r="E140">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F140">
         <v>0</v>
@@ -48567,7 +48553,7 @@
         <v>なし</v>
       </c>
       <c r="E141">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F141">
         <v>0</v>
@@ -48595,7 +48581,7 @@
         <v>なし</v>
       </c>
       <c r="E142">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F142">
         <v>0</v>
@@ -48623,7 +48609,7 @@
         <v>なし</v>
       </c>
       <c r="E143">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F143">
         <v>0</v>
@@ -48651,7 +48637,7 @@
         <v>ダンジョンで移動する param2%turncount == param1</v>
       </c>
       <c r="E144">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F144">
         <v>1</v>
@@ -48679,7 +48665,7 @@
         <v>ピリオド経過</v>
       </c>
       <c r="E145">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F145">
         <v>0</v>
@@ -48707,7 +48693,7 @@
         <v>ピリオド経過</v>
       </c>
       <c r="E146">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F146">
         <v>0</v>
@@ -48735,7 +48721,7 @@
         <v>ピリオド経過</v>
       </c>
       <c r="E147">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F147">
         <v>0</v>
@@ -48763,7 +48749,7 @@
         <v>ピリオド経過</v>
       </c>
       <c r="E148">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F148">
         <v>0</v>
@@ -48791,7 +48777,7 @@
         <v>ピリオド経過</v>
       </c>
       <c r="E149">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F149">
         <v>0</v>
@@ -48819,7 +48805,7 @@
         <v>ピリオド経過</v>
       </c>
       <c r="E150">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F150">
         <v>0</v>
@@ -48847,7 +48833,7 @@
         <v>Lvが〇以下</v>
       </c>
       <c r="E151">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F151">
         <v>10</v>
@@ -48875,7 +48861,7 @@
         <v>Lvが〇以下</v>
       </c>
       <c r="E152">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F152">
         <v>15</v>
@@ -48903,7 +48889,7 @@
         <v>Lvが〇以下</v>
       </c>
       <c r="E153">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F153">
         <v>20</v>
@@ -48931,7 +48917,7 @@
         <v>ダンジョン開始時</v>
       </c>
       <c r="E154">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F154">
         <v>0</v>
@@ -48959,7 +48945,7 @@
         <v>なし</v>
       </c>
       <c r="E155">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F155">
         <v>0</v>
@@ -48987,7 +48973,7 @@
         <v>なし</v>
       </c>
       <c r="E156">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F156">
         <v>0</v>
@@ -49015,7 +49001,7 @@
         <v>なし</v>
       </c>
       <c r="E157">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F157">
         <v>0</v>
@@ -49043,7 +49029,7 @@
         <v>なし</v>
       </c>
       <c r="E158">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F158">
         <v>0</v>
@@ -49071,7 +49057,7 @@
         <v>なし</v>
       </c>
       <c r="E159">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F159">
         <v>0</v>
@@ -49099,7 +49085,7 @@
         <v>なし</v>
       </c>
       <c r="E160">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F160">
         <v>0</v>
@@ -49127,7 +49113,7 @@
         <v>なし</v>
       </c>
       <c r="E161">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F161">
         <v>0</v>
@@ -49155,7 +49141,7 @@
         <v>なし</v>
       </c>
       <c r="E162">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F162">
         <v>0</v>
@@ -49183,7 +49169,7 @@
         <v>なし</v>
       </c>
       <c r="E163">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F163">
         <v>0</v>
@@ -49196,6 +49182,9 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="E1:E163">
+    <extLst/>
+  </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
@@ -53056,6 +53045,7 @@
     <col min="18" max="18" width="2.45454545454545" customWidth="1"/>
     <col min="20" max="20" width="10.3636363636364" customWidth="1"/>
     <col min="22" max="22" width="37.4545454545455" customWidth="1"/>
+    <col min="26" max="26" width="30.0909090909091" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:25">
@@ -53140,7 +53130,7 @@
         <v>599</v>
       </c>
       <c r="Y2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="Z2" t="s">
         <v>599</v>
@@ -53264,7 +53254,7 @@
         <v>616</v>
       </c>
       <c r="Y4">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="Z4" t="s">
         <v>617</v>
@@ -53326,7 +53316,7 @@
         <v>625</v>
       </c>
       <c r="Y5">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="Z5" t="s">
         <v>626</v>
@@ -53382,7 +53372,7 @@
         <v>631</v>
       </c>
       <c r="Y6">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="Z6" t="s">
         <v>632</v>
@@ -53438,7 +53428,7 @@
         <v>640</v>
       </c>
       <c r="Y7">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="Z7" t="s">
         <v>641</v>
@@ -53494,7 +53484,7 @@
         <v>649</v>
       </c>
       <c r="Y8">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="Z8" t="s">
         <v>650</v>
@@ -53544,7 +53534,7 @@
         <v>657</v>
       </c>
       <c r="Y9">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="Z9" t="s">
         <v>658</v>
@@ -53594,7 +53584,7 @@
         <v>665</v>
       </c>
       <c r="Y10">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="Z10" t="s">
         <v>666</v>
@@ -53638,7 +53628,7 @@
         <v>71</v>
       </c>
       <c r="Y11">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="Z11" t="s">
         <v>672</v>
@@ -53682,7 +53672,7 @@
         <v>678</v>
       </c>
       <c r="Y12">
-        <v>32</v>
+        <v>61</v>
       </c>
       <c r="Z12" t="s">
         <v>679</v>
@@ -53716,17 +53706,11 @@
       <c r="W13" t="s">
         <v>684</v>
       </c>
-      <c r="Y13">
-        <v>33</v>
-      </c>
-      <c r="Z13" t="s">
-        <v>685</v>
-      </c>
       <c r="AB13">
         <v>401</v>
       </c>
       <c r="AC13" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
     </row>
     <row r="14" spans="16:29">
@@ -53734,25 +53718,19 @@
         <v>2010</v>
       </c>
       <c r="Q14" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="U14">
         <v>3010</v>
       </c>
       <c r="V14" t="s">
-        <v>688</v>
-      </c>
-      <c r="Y14">
-        <v>41</v>
-      </c>
-      <c r="Z14" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="AB14">
         <v>402</v>
       </c>
       <c r="AC14" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
     </row>
     <row r="15" spans="16:29">
@@ -53760,25 +53738,19 @@
         <v>2011</v>
       </c>
       <c r="Q15" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="U15">
         <v>3020</v>
       </c>
       <c r="V15" t="s">
-        <v>692</v>
-      </c>
-      <c r="Y15">
-        <v>42</v>
-      </c>
-      <c r="Z15" t="s">
-        <v>693</v>
+        <v>690</v>
       </c>
       <c r="AB15">
         <v>403</v>
       </c>
       <c r="AC15" t="s">
-        <v>694</v>
+        <v>691</v>
       </c>
     </row>
     <row r="16" spans="16:29">
@@ -53786,25 +53758,19 @@
         <v>2020</v>
       </c>
       <c r="Q16" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="U16">
         <v>3030</v>
       </c>
       <c r="V16" t="s">
-        <v>696</v>
-      </c>
-      <c r="Y16">
-        <v>51</v>
-      </c>
-      <c r="Z16" t="s">
-        <v>697</v>
+        <v>693</v>
       </c>
       <c r="AB16">
         <v>404</v>
       </c>
       <c r="AC16" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
     </row>
     <row r="17" spans="16:29">
@@ -53812,25 +53778,19 @@
         <v>2030</v>
       </c>
       <c r="Q17" t="s">
-        <v>699</v>
+        <v>695</v>
       </c>
       <c r="U17">
         <v>3040</v>
       </c>
       <c r="V17" t="s">
-        <v>700</v>
-      </c>
-      <c r="Y17">
-        <v>52</v>
-      </c>
-      <c r="Z17" t="s">
-        <v>701</v>
+        <v>696</v>
       </c>
       <c r="AB17">
         <v>501</v>
       </c>
       <c r="AC17" t="s">
-        <v>702</v>
+        <v>697</v>
       </c>
     </row>
     <row r="18" spans="16:29">
@@ -53838,19 +53798,19 @@
         <v>2040</v>
       </c>
       <c r="Q18" t="s">
-        <v>703</v>
+        <v>698</v>
       </c>
       <c r="U18">
         <v>3050</v>
       </c>
       <c r="V18" t="s">
-        <v>704</v>
+        <v>699</v>
       </c>
       <c r="AB18">
         <v>502</v>
       </c>
       <c r="AC18" t="s">
-        <v>705</v>
+        <v>700</v>
       </c>
     </row>
     <row r="19" spans="16:29">
@@ -53858,19 +53818,19 @@
         <v>2110</v>
       </c>
       <c r="Q19" t="s">
-        <v>706</v>
+        <v>701</v>
       </c>
       <c r="U19">
         <v>3060</v>
       </c>
       <c r="V19" t="s">
-        <v>707</v>
+        <v>702</v>
       </c>
       <c r="AB19">
         <v>503</v>
       </c>
       <c r="AC19" t="s">
-        <v>708</v>
+        <v>703</v>
       </c>
     </row>
     <row r="20" spans="16:29">
@@ -53878,19 +53838,19 @@
         <v>2120</v>
       </c>
       <c r="Q20" t="s">
-        <v>709</v>
+        <v>704</v>
       </c>
       <c r="U20">
         <v>4010</v>
       </c>
       <c r="V20" t="s">
-        <v>710</v>
+        <v>705</v>
       </c>
       <c r="AB20">
         <v>504</v>
       </c>
       <c r="AC20" t="s">
-        <v>711</v>
+        <v>706</v>
       </c>
     </row>
     <row r="21" spans="16:29">
@@ -53898,19 +53858,19 @@
         <v>2130</v>
       </c>
       <c r="Q21" t="s">
-        <v>712</v>
+        <v>707</v>
       </c>
       <c r="U21">
         <v>4020</v>
       </c>
       <c r="V21" t="s">
-        <v>713</v>
+        <v>708</v>
       </c>
       <c r="AB21">
         <v>505</v>
       </c>
       <c r="AC21" t="s">
-        <v>714</v>
+        <v>709</v>
       </c>
     </row>
     <row r="22" spans="16:29">
@@ -53918,19 +53878,19 @@
         <v>3010</v>
       </c>
       <c r="Q22" t="s">
-        <v>715</v>
+        <v>710</v>
       </c>
       <c r="U22">
         <v>5010</v>
       </c>
       <c r="V22" t="s">
-        <v>716</v>
+        <v>711</v>
       </c>
       <c r="AB22">
         <v>506</v>
       </c>
       <c r="AC22" t="s">
-        <v>717</v>
+        <v>712</v>
       </c>
     </row>
     <row r="23" spans="16:29">
@@ -53938,19 +53898,19 @@
         <v>3020</v>
       </c>
       <c r="Q23" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="U23">
         <v>5020</v>
       </c>
       <c r="V23" t="s">
-        <v>719</v>
+        <v>714</v>
       </c>
       <c r="AB23">
         <v>507</v>
       </c>
       <c r="AC23" t="s">
-        <v>720</v>
+        <v>715</v>
       </c>
     </row>
     <row r="24" spans="16:29">
@@ -53958,19 +53918,19 @@
         <v>3030</v>
       </c>
       <c r="Q24" t="s">
-        <v>721</v>
+        <v>716</v>
       </c>
       <c r="U24">
         <v>5030</v>
       </c>
       <c r="V24" t="s">
-        <v>722</v>
+        <v>717</v>
       </c>
       <c r="AB24">
         <v>508</v>
       </c>
       <c r="AC24" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
     </row>
     <row r="25" spans="16:29">
@@ -53978,19 +53938,19 @@
         <v>3040</v>
       </c>
       <c r="Q25" t="s">
-        <v>723</v>
+        <v>718</v>
       </c>
       <c r="U25">
         <v>5040</v>
       </c>
       <c r="V25" t="s">
-        <v>724</v>
+        <v>719</v>
       </c>
       <c r="AB25">
         <v>509</v>
       </c>
       <c r="AC25" t="s">
-        <v>694</v>
+        <v>691</v>
       </c>
     </row>
     <row r="26" spans="16:22">
@@ -53998,13 +53958,13 @@
         <v>3050</v>
       </c>
       <c r="Q26" t="s">
-        <v>725</v>
+        <v>720</v>
       </c>
       <c r="U26">
         <v>5050</v>
       </c>
       <c r="V26" t="s">
-        <v>726</v>
+        <v>721</v>
       </c>
     </row>
     <row r="27" spans="16:22">
@@ -54012,13 +53972,13 @@
         <v>3060</v>
       </c>
       <c r="Q27" t="s">
-        <v>727</v>
+        <v>722</v>
       </c>
       <c r="U27">
         <v>5060</v>
       </c>
       <c r="V27" t="s">
-        <v>728</v>
+        <v>723</v>
       </c>
     </row>
     <row r="28" spans="16:22">
@@ -54026,13 +53986,13 @@
         <v>3070</v>
       </c>
       <c r="Q28" t="s">
-        <v>729</v>
+        <v>724</v>
       </c>
       <c r="U28">
         <v>5070</v>
       </c>
       <c r="V28" t="s">
-        <v>730</v>
+        <v>725</v>
       </c>
     </row>
     <row r="29" spans="16:22">
@@ -54040,13 +54000,13 @@
         <v>4010</v>
       </c>
       <c r="Q29" t="s">
-        <v>731</v>
+        <v>726</v>
       </c>
       <c r="U29">
         <v>5080</v>
       </c>
       <c r="V29" t="s">
-        <v>732</v>
+        <v>727</v>
       </c>
     </row>
     <row r="30" spans="16:22">
@@ -54054,13 +54014,13 @@
         <v>4020</v>
       </c>
       <c r="Q30" t="s">
-        <v>733</v>
+        <v>728</v>
       </c>
       <c r="U30">
         <v>5090</v>
       </c>
       <c r="V30" t="s">
-        <v>734</v>
+        <v>729</v>
       </c>
     </row>
     <row r="31" spans="16:22">
@@ -54068,13 +54028,13 @@
         <v>4030</v>
       </c>
       <c r="Q31" t="s">
-        <v>735</v>
+        <v>730</v>
       </c>
       <c r="U31">
         <v>5100</v>
       </c>
       <c r="V31" t="s">
-        <v>736</v>
+        <v>731</v>
       </c>
     </row>
     <row r="32" spans="16:22">
@@ -54082,13 +54042,13 @@
         <v>4040</v>
       </c>
       <c r="Q32" t="s">
-        <v>737</v>
+        <v>732</v>
       </c>
       <c r="U32">
         <v>5110</v>
       </c>
       <c r="V32" t="s">
-        <v>738</v>
+        <v>733</v>
       </c>
     </row>
     <row r="33" spans="16:22">
@@ -54096,13 +54056,13 @@
         <v>4041</v>
       </c>
       <c r="Q33" t="s">
-        <v>739</v>
+        <v>734</v>
       </c>
       <c r="U33">
         <v>5120</v>
       </c>
       <c r="V33" t="s">
-        <v>740</v>
+        <v>735</v>
       </c>
     </row>
     <row r="34" spans="16:22">
@@ -54110,13 +54070,13 @@
         <v>5010</v>
       </c>
       <c r="Q34" t="s">
-        <v>741</v>
+        <v>736</v>
       </c>
       <c r="U34">
         <v>5130</v>
       </c>
       <c r="V34" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
     </row>
     <row r="35" spans="16:22">
@@ -54124,13 +54084,13 @@
         <v>5011</v>
       </c>
       <c r="Q35" t="s">
-        <v>743</v>
+        <v>738</v>
       </c>
       <c r="U35">
         <v>5140</v>
       </c>
       <c r="V35" t="s">
-        <v>744</v>
+        <v>739</v>
       </c>
     </row>
     <row r="36" spans="16:22">
@@ -54138,13 +54098,13 @@
         <v>5012</v>
       </c>
       <c r="Q36" t="s">
-        <v>745</v>
+        <v>740</v>
       </c>
       <c r="U36">
         <v>5150</v>
       </c>
       <c r="V36" t="s">
-        <v>746</v>
+        <v>741</v>
       </c>
     </row>
     <row r="37" spans="16:22">
@@ -54152,13 +54112,13 @@
         <v>5020</v>
       </c>
       <c r="Q37" t="s">
-        <v>747</v>
+        <v>742</v>
       </c>
       <c r="U37">
         <v>6010</v>
       </c>
       <c r="V37" t="s">
-        <v>748</v>
+        <v>743</v>
       </c>
     </row>
     <row r="38" spans="16:22">
@@ -54166,13 +54126,13 @@
         <v>5030</v>
       </c>
       <c r="Q38" t="s">
-        <v>749</v>
+        <v>744</v>
       </c>
       <c r="U38">
         <v>6020</v>
       </c>
       <c r="V38" t="s">
-        <v>750</v>
+        <v>745</v>
       </c>
     </row>
     <row r="39" spans="16:22">
@@ -54180,13 +54140,13 @@
         <v>5040</v>
       </c>
       <c r="Q39" t="s">
-        <v>751</v>
+        <v>746</v>
       </c>
       <c r="U39">
         <v>6030</v>
       </c>
       <c r="V39" t="s">
-        <v>752</v>
+        <v>747</v>
       </c>
     </row>
     <row r="40" spans="16:22">
@@ -54194,13 +54154,13 @@
         <v>5050</v>
       </c>
       <c r="Q40" t="s">
-        <v>753</v>
+        <v>748</v>
       </c>
       <c r="U40">
         <v>6040</v>
       </c>
       <c r="V40" t="s">
-        <v>754</v>
+        <v>749</v>
       </c>
     </row>
     <row r="41" spans="16:22">
@@ -54208,13 +54168,13 @@
         <v>6010</v>
       </c>
       <c r="Q41" t="s">
-        <v>755</v>
+        <v>750</v>
       </c>
       <c r="U41">
         <v>6050</v>
       </c>
       <c r="V41" t="s">
-        <v>756</v>
+        <v>751</v>
       </c>
     </row>
     <row r="42" spans="16:22">
@@ -54222,13 +54182,13 @@
         <v>6020</v>
       </c>
       <c r="Q42" t="s">
-        <v>757</v>
+        <v>752</v>
       </c>
       <c r="U42">
         <v>6060</v>
       </c>
       <c r="V42" t="s">
-        <v>758</v>
+        <v>753</v>
       </c>
     </row>
     <row r="43" spans="16:22">
@@ -54236,13 +54196,13 @@
         <v>6030</v>
       </c>
       <c r="Q43" t="s">
-        <v>759</v>
+        <v>754</v>
       </c>
       <c r="U43">
         <v>6110</v>
       </c>
       <c r="V43" t="s">
-        <v>760</v>
+        <v>755</v>
       </c>
     </row>
     <row r="44" spans="16:22">
@@ -54250,13 +54210,13 @@
         <v>6040</v>
       </c>
       <c r="Q44" t="s">
-        <v>761</v>
+        <v>756</v>
       </c>
       <c r="U44">
         <v>6120</v>
       </c>
       <c r="V44" t="s">
-        <v>762</v>
+        <v>757</v>
       </c>
     </row>
     <row r="45" spans="16:22">
@@ -54264,13 +54224,13 @@
         <v>6050</v>
       </c>
       <c r="Q45" t="s">
-        <v>763</v>
+        <v>758</v>
       </c>
       <c r="U45">
         <v>6130</v>
       </c>
       <c r="V45" t="s">
-        <v>764</v>
+        <v>759</v>
       </c>
     </row>
     <row r="46" spans="16:22">
@@ -54278,13 +54238,13 @@
         <v>6060</v>
       </c>
       <c r="Q46" t="s">
-        <v>765</v>
+        <v>760</v>
       </c>
       <c r="U46">
         <v>6140</v>
       </c>
       <c r="V46" t="s">
-        <v>766</v>
+        <v>761</v>
       </c>
     </row>
     <row r="47" spans="16:22">
@@ -54292,13 +54252,13 @@
         <v>6070</v>
       </c>
       <c r="Q47" t="s">
-        <v>767</v>
+        <v>762</v>
       </c>
       <c r="U47">
         <v>6150</v>
       </c>
       <c r="V47" t="s">
-        <v>768</v>
+        <v>763</v>
       </c>
     </row>
     <row r="48" spans="16:22">
@@ -54306,13 +54266,13 @@
         <v>6080</v>
       </c>
       <c r="Q48" t="s">
-        <v>769</v>
+        <v>764</v>
       </c>
       <c r="U48">
         <v>6210</v>
       </c>
       <c r="V48" t="s">
-        <v>770</v>
+        <v>765</v>
       </c>
     </row>
     <row r="49" spans="16:22">
@@ -54320,13 +54280,13 @@
         <v>6100</v>
       </c>
       <c r="Q49" t="s">
-        <v>771</v>
+        <v>766</v>
       </c>
       <c r="U49">
         <v>6220</v>
       </c>
       <c r="V49" t="s">
-        <v>772</v>
+        <v>767</v>
       </c>
     </row>
     <row r="50" spans="16:22">
@@ -54334,13 +54294,13 @@
         <v>6210</v>
       </c>
       <c r="Q50" t="s">
-        <v>773</v>
+        <v>768</v>
       </c>
       <c r="U50">
         <v>6230</v>
       </c>
       <c r="V50" t="s">
-        <v>774</v>
+        <v>769</v>
       </c>
     </row>
     <row r="51" spans="16:22">
@@ -54348,13 +54308,13 @@
         <v>6310</v>
       </c>
       <c r="Q51" t="s">
-        <v>775</v>
+        <v>770</v>
       </c>
       <c r="U51">
         <v>6240</v>
       </c>
       <c r="V51" t="s">
-        <v>776</v>
+        <v>771</v>
       </c>
     </row>
     <row r="52" spans="16:22">
@@ -54362,13 +54322,13 @@
         <v>7010</v>
       </c>
       <c r="Q52" t="s">
-        <v>777</v>
+        <v>772</v>
       </c>
       <c r="U52">
         <v>6250</v>
       </c>
       <c r="V52" t="s">
-        <v>778</v>
+        <v>773</v>
       </c>
     </row>
     <row r="53" spans="16:22">
@@ -54376,13 +54336,13 @@
         <v>7020</v>
       </c>
       <c r="Q53" t="s">
-        <v>779</v>
+        <v>774</v>
       </c>
       <c r="U53">
         <v>6310</v>
       </c>
       <c r="V53" t="s">
-        <v>780</v>
+        <v>775</v>
       </c>
     </row>
     <row r="54" spans="16:22">
@@ -54390,13 +54350,13 @@
         <v>7030</v>
       </c>
       <c r="Q54" t="s">
-        <v>781</v>
+        <v>776</v>
       </c>
       <c r="U54">
         <v>6320</v>
       </c>
       <c r="V54" t="s">
-        <v>782</v>
+        <v>777</v>
       </c>
     </row>
     <row r="55" spans="16:22">
@@ -54404,13 +54364,13 @@
         <v>8010</v>
       </c>
       <c r="Q55" t="s">
-        <v>783</v>
+        <v>778</v>
       </c>
       <c r="U55">
         <v>6330</v>
       </c>
       <c r="V55" t="s">
-        <v>784</v>
+        <v>779</v>
       </c>
     </row>
     <row r="56" spans="16:22">
@@ -54418,13 +54378,13 @@
         <v>8020</v>
       </c>
       <c r="Q56" t="s">
-        <v>785</v>
+        <v>780</v>
       </c>
       <c r="U56">
         <v>6340</v>
       </c>
       <c r="V56" t="s">
-        <v>786</v>
+        <v>781</v>
       </c>
     </row>
     <row r="57" spans="16:22">
@@ -54432,13 +54392,13 @@
         <v>9010</v>
       </c>
       <c r="Q57" t="s">
-        <v>787</v>
+        <v>782</v>
       </c>
       <c r="U57">
         <v>6350</v>
       </c>
       <c r="V57" t="s">
-        <v>788</v>
+        <v>783</v>
       </c>
     </row>
     <row r="58" spans="16:22">
@@ -54446,13 +54406,13 @@
         <v>10010</v>
       </c>
       <c r="Q58" t="s">
-        <v>789</v>
+        <v>784</v>
       </c>
       <c r="U58">
         <v>7010</v>
       </c>
       <c r="V58" t="s">
-        <v>790</v>
+        <v>785</v>
       </c>
     </row>
     <row r="59" spans="16:22">
@@ -54460,13 +54420,13 @@
         <v>10020</v>
       </c>
       <c r="Q59" t="s">
-        <v>791</v>
+        <v>786</v>
       </c>
       <c r="U59">
         <v>7020</v>
       </c>
       <c r="V59" t="s">
-        <v>792</v>
+        <v>787</v>
       </c>
     </row>
     <row r="60" spans="16:22">
@@ -54474,13 +54434,13 @@
         <v>11010</v>
       </c>
       <c r="Q60" t="s">
-        <v>793</v>
+        <v>788</v>
       </c>
       <c r="U60">
         <v>7030</v>
       </c>
       <c r="V60" t="s">
-        <v>794</v>
+        <v>789</v>
       </c>
     </row>
     <row r="61" spans="16:22">
@@ -54488,13 +54448,13 @@
         <v>12010</v>
       </c>
       <c r="Q61" t="s">
-        <v>795</v>
+        <v>790</v>
       </c>
       <c r="U61">
         <v>7040</v>
       </c>
       <c r="V61" t="s">
-        <v>796</v>
+        <v>791</v>
       </c>
     </row>
     <row r="62" spans="16:22">
@@ -54502,13 +54462,13 @@
         <v>13010</v>
       </c>
       <c r="Q62" t="s">
-        <v>797</v>
+        <v>792</v>
       </c>
       <c r="U62">
         <v>7050</v>
       </c>
       <c r="V62" t="s">
-        <v>798</v>
+        <v>793</v>
       </c>
     </row>
     <row r="63" spans="16:22">
@@ -54516,13 +54476,13 @@
         <v>40010</v>
       </c>
       <c r="Q63" t="s">
-        <v>799</v>
+        <v>794</v>
       </c>
       <c r="U63">
         <v>7060</v>
       </c>
       <c r="V63" t="s">
-        <v>800</v>
+        <v>795</v>
       </c>
     </row>
     <row r="64" spans="16:22">
@@ -54530,13 +54490,13 @@
         <v>40020</v>
       </c>
       <c r="Q64" t="s">
-        <v>801</v>
+        <v>796</v>
       </c>
       <c r="U64">
         <v>7070</v>
       </c>
       <c r="V64" t="s">
-        <v>802</v>
+        <v>797</v>
       </c>
     </row>
     <row r="65" spans="16:22">
@@ -54544,13 +54504,13 @@
         <v>40030</v>
       </c>
       <c r="Q65" t="s">
-        <v>803</v>
+        <v>798</v>
       </c>
       <c r="U65">
         <v>8010</v>
       </c>
       <c r="V65" t="s">
-        <v>804</v>
+        <v>799</v>
       </c>
     </row>
     <row r="66" spans="16:22">
@@ -54558,13 +54518,13 @@
         <v>40040</v>
       </c>
       <c r="Q66" t="s">
-        <v>805</v>
+        <v>800</v>
       </c>
       <c r="U66">
         <v>8020</v>
       </c>
       <c r="V66" t="s">
-        <v>806</v>
+        <v>801</v>
       </c>
     </row>
     <row r="67" spans="16:22">
@@ -54572,13 +54532,13 @@
         <v>40050</v>
       </c>
       <c r="Q67" t="s">
-        <v>807</v>
+        <v>802</v>
       </c>
       <c r="U67">
         <v>8030</v>
       </c>
       <c r="V67" t="s">
-        <v>808</v>
+        <v>803</v>
       </c>
     </row>
     <row r="68" spans="16:22">
@@ -54586,13 +54546,13 @@
         <v>40060</v>
       </c>
       <c r="Q68" t="s">
-        <v>809</v>
+        <v>804</v>
       </c>
       <c r="U68">
         <v>8040</v>
       </c>
       <c r="V68" t="s">
-        <v>810</v>
+        <v>805</v>
       </c>
     </row>
     <row r="69" spans="16:22">
@@ -54600,13 +54560,13 @@
         <v>40070</v>
       </c>
       <c r="Q69" t="s">
-        <v>811</v>
+        <v>806</v>
       </c>
       <c r="U69">
         <v>8050</v>
       </c>
       <c r="V69" t="s">
-        <v>812</v>
+        <v>807</v>
       </c>
     </row>
     <row r="70" spans="16:22">
@@ -54614,13 +54574,13 @@
         <v>40080</v>
       </c>
       <c r="Q70" t="s">
-        <v>813</v>
+        <v>808</v>
       </c>
       <c r="U70">
         <v>8060</v>
       </c>
       <c r="V70" t="s">
-        <v>814</v>
+        <v>809</v>
       </c>
     </row>
     <row r="71" spans="21:22">
@@ -54628,7 +54588,7 @@
         <v>9010</v>
       </c>
       <c r="V71" t="s">
-        <v>815</v>
+        <v>810</v>
       </c>
     </row>
     <row r="72" spans="21:22">
@@ -54636,7 +54596,7 @@
         <v>9020</v>
       </c>
       <c r="V72" t="s">
-        <v>816</v>
+        <v>811</v>
       </c>
     </row>
     <row r="73" spans="21:22">
@@ -54644,7 +54604,7 @@
         <v>9030</v>
       </c>
       <c r="V73" t="s">
-        <v>817</v>
+        <v>812</v>
       </c>
     </row>
     <row r="74" spans="21:22">
@@ -54652,7 +54612,7 @@
         <v>9031</v>
       </c>
       <c r="V74" t="s">
-        <v>818</v>
+        <v>813</v>
       </c>
     </row>
     <row r="75" spans="21:22">
@@ -54660,7 +54620,7 @@
         <v>9040</v>
       </c>
       <c r="V75" t="s">
-        <v>819</v>
+        <v>814</v>
       </c>
     </row>
     <row r="76" spans="21:22">
@@ -54668,7 +54628,7 @@
         <v>9110</v>
       </c>
       <c r="V76" t="s">
-        <v>820</v>
+        <v>815</v>
       </c>
     </row>
     <row r="77" spans="21:22">
@@ -54676,7 +54636,7 @@
         <v>9120</v>
       </c>
       <c r="V77" t="s">
-        <v>821</v>
+        <v>816</v>
       </c>
     </row>
     <row r="78" spans="21:22">
@@ -54684,7 +54644,7 @@
         <v>10010</v>
       </c>
       <c r="V78" t="s">
-        <v>822</v>
+        <v>817</v>
       </c>
     </row>
     <row r="79" spans="21:22">
@@ -54692,7 +54652,7 @@
         <v>10020</v>
       </c>
       <c r="V79" t="s">
-        <v>823</v>
+        <v>818</v>
       </c>
     </row>
     <row r="80" spans="21:22">
@@ -54700,7 +54660,7 @@
         <v>10030</v>
       </c>
       <c r="V80" t="s">
-        <v>824</v>
+        <v>819</v>
       </c>
     </row>
     <row r="81" spans="21:22">
@@ -54708,7 +54668,7 @@
         <v>10110</v>
       </c>
       <c r="V81" t="s">
-        <v>825</v>
+        <v>820</v>
       </c>
     </row>
     <row r="82" spans="21:22">
@@ -54716,7 +54676,7 @@
         <v>10120</v>
       </c>
       <c r="V82" t="s">
-        <v>826</v>
+        <v>821</v>
       </c>
     </row>
     <row r="83" spans="21:22">
@@ -54724,7 +54684,7 @@
         <v>10130</v>
       </c>
       <c r="V83" t="s">
-        <v>827</v>
+        <v>822</v>
       </c>
     </row>
     <row r="84" spans="21:22">
@@ -54732,7 +54692,7 @@
         <v>11010</v>
       </c>
       <c r="V84" t="s">
-        <v>828</v>
+        <v>823</v>
       </c>
     </row>
     <row r="85" spans="21:22">
@@ -54740,7 +54700,7 @@
         <v>11011</v>
       </c>
       <c r="V85" t="s">
-        <v>829</v>
+        <v>824</v>
       </c>
     </row>
     <row r="86" spans="21:22">
@@ -54748,7 +54708,7 @@
         <v>11020</v>
       </c>
       <c r="V86" t="s">
-        <v>830</v>
+        <v>825</v>
       </c>
     </row>
     <row r="87" spans="21:22">
@@ -54756,7 +54716,7 @@
         <v>12010</v>
       </c>
       <c r="V87" t="s">
-        <v>831</v>
+        <v>826</v>
       </c>
     </row>
     <row r="88" spans="21:22">
@@ -54764,7 +54724,7 @@
         <v>12011</v>
       </c>
       <c r="V88" t="s">
-        <v>832</v>
+        <v>827</v>
       </c>
     </row>
     <row r="89" spans="21:22">
@@ -54772,7 +54732,7 @@
         <v>12030</v>
       </c>
       <c r="V89" t="s">
-        <v>833</v>
+        <v>828</v>
       </c>
     </row>
     <row r="90" spans="21:22">
@@ -54780,7 +54740,7 @@
         <v>12040</v>
       </c>
       <c r="V90" t="s">
-        <v>834</v>
+        <v>829</v>
       </c>
     </row>
     <row r="91" spans="21:22">
@@ -54788,7 +54748,7 @@
         <v>12041</v>
       </c>
       <c r="V91" t="s">
-        <v>835</v>
+        <v>830</v>
       </c>
     </row>
     <row r="92" spans="21:22">
@@ -54796,7 +54756,7 @@
         <v>12042</v>
       </c>
       <c r="V92" t="s">
-        <v>836</v>
+        <v>831</v>
       </c>
     </row>
     <row r="93" spans="21:22">
@@ -54804,7 +54764,7 @@
         <v>12043</v>
       </c>
       <c r="V93" t="s">
-        <v>837</v>
+        <v>832</v>
       </c>
     </row>
     <row r="94" spans="21:22">
@@ -54812,7 +54772,7 @@
         <v>12050</v>
       </c>
       <c r="V94" t="s">
-        <v>838</v>
+        <v>833</v>
       </c>
     </row>
     <row r="95" spans="21:22">
@@ -54820,7 +54780,7 @@
         <v>12060</v>
       </c>
       <c r="V95" t="s">
-        <v>839</v>
+        <v>834</v>
       </c>
     </row>
     <row r="96" spans="21:22">
@@ -54828,7 +54788,7 @@
         <v>12063</v>
       </c>
       <c r="V96" t="s">
-        <v>840</v>
+        <v>835</v>
       </c>
     </row>
     <row r="97" spans="21:22">
@@ -54836,7 +54796,7 @@
         <v>12064</v>
       </c>
       <c r="V97" t="s">
-        <v>841</v>
+        <v>836</v>
       </c>
     </row>
     <row r="98" spans="21:22">
@@ -54844,7 +54804,7 @@
         <v>12066</v>
       </c>
       <c r="V98" t="s">
-        <v>842</v>
+        <v>837</v>
       </c>
     </row>
     <row r="99" spans="21:22">
@@ -54852,7 +54812,7 @@
         <v>12067</v>
       </c>
       <c r="V99" t="s">
-        <v>843</v>
+        <v>838</v>
       </c>
     </row>
     <row r="100" spans="21:22">
@@ -54860,7 +54820,7 @@
         <v>12070</v>
       </c>
       <c r="V100" t="s">
-        <v>844</v>
+        <v>839</v>
       </c>
     </row>
     <row r="101" spans="21:22">
@@ -54868,7 +54828,7 @@
         <v>12071</v>
       </c>
       <c r="V101" t="s">
-        <v>845</v>
+        <v>840</v>
       </c>
     </row>
     <row r="102" spans="21:22">
@@ -54876,7 +54836,7 @@
         <v>12072</v>
       </c>
       <c r="V102" t="s">
-        <v>846</v>
+        <v>841</v>
       </c>
     </row>
     <row r="103" spans="21:22">
@@ -54884,7 +54844,7 @@
         <v>12082</v>
       </c>
       <c r="V103" t="s">
-        <v>847</v>
+        <v>842</v>
       </c>
     </row>
     <row r="104" spans="21:22">
@@ -54892,7 +54852,7 @@
         <v>12092</v>
       </c>
       <c r="V104" t="s">
-        <v>848</v>
+        <v>843</v>
       </c>
     </row>
     <row r="105" spans="21:22">
@@ -54900,7 +54860,7 @@
         <v>13010</v>
       </c>
       <c r="V105" t="s">
-        <v>849</v>
+        <v>844</v>
       </c>
     </row>
     <row r="106" spans="21:22">
@@ -54908,7 +54868,7 @@
         <v>13020</v>
       </c>
       <c r="V106" t="s">
-        <v>850</v>
+        <v>845</v>
       </c>
     </row>
     <row r="107" spans="21:22">
@@ -54916,7 +54876,7 @@
         <v>14010</v>
       </c>
       <c r="V107" t="s">
-        <v>851</v>
+        <v>846</v>
       </c>
     </row>
     <row r="108" spans="21:22">
@@ -54924,7 +54884,7 @@
         <v>14110</v>
       </c>
       <c r="V108" t="s">
-        <v>852</v>
+        <v>847</v>
       </c>
     </row>
     <row r="109" spans="21:22">
@@ -54932,7 +54892,7 @@
         <v>14210</v>
       </c>
       <c r="V109" t="s">
-        <v>853</v>
+        <v>848</v>
       </c>
     </row>
     <row r="110" spans="21:22">
@@ -54940,7 +54900,7 @@
         <v>14310</v>
       </c>
       <c r="V110" t="s">
-        <v>854</v>
+        <v>849</v>
       </c>
     </row>
     <row r="111" spans="21:22">
@@ -54948,7 +54908,7 @@
         <v>14410</v>
       </c>
       <c r="V111" t="s">
-        <v>855</v>
+        <v>850</v>
       </c>
     </row>
     <row r="112" spans="21:22">
@@ -54956,7 +54916,7 @@
         <v>14420</v>
       </c>
       <c r="V112" t="s">
-        <v>856</v>
+        <v>851</v>
       </c>
     </row>
     <row r="113" spans="21:22">
@@ -54964,7 +54924,7 @@
         <v>14520</v>
       </c>
       <c r="V113" t="s">
-        <v>857</v>
+        <v>852</v>
       </c>
     </row>
     <row r="114" spans="21:22">
@@ -54972,7 +54932,7 @@
         <v>15010</v>
       </c>
       <c r="V114" t="s">
-        <v>858</v>
+        <v>853</v>
       </c>
     </row>
     <row r="115" spans="21:22">
@@ -54980,7 +54940,7 @@
         <v>15011</v>
       </c>
       <c r="V115" t="s">
-        <v>859</v>
+        <v>854</v>
       </c>
     </row>
     <row r="116" spans="21:22">
@@ -54988,7 +54948,7 @@
         <v>15022</v>
       </c>
       <c r="V116" t="s">
-        <v>860</v>
+        <v>855</v>
       </c>
     </row>
     <row r="117" spans="21:22">
@@ -54996,7 +54956,7 @@
         <v>16010</v>
       </c>
       <c r="V117" t="s">
-        <v>861</v>
+        <v>856</v>
       </c>
     </row>
     <row r="118" spans="21:22">
@@ -55004,7 +54964,7 @@
         <v>17010</v>
       </c>
       <c r="V118" t="s">
-        <v>862</v>
+        <v>857</v>
       </c>
     </row>
     <row r="119" spans="21:22">
@@ -55012,7 +54972,7 @@
         <v>17020</v>
       </c>
       <c r="V119" t="s">
-        <v>863</v>
+        <v>858</v>
       </c>
     </row>
     <row r="120" spans="21:22">
@@ -55020,7 +54980,7 @@
         <v>17030</v>
       </c>
       <c r="V120" t="s">
-        <v>864</v>
+        <v>859</v>
       </c>
     </row>
     <row r="121" spans="21:22">
@@ -55028,7 +54988,7 @@
         <v>17040</v>
       </c>
       <c r="V121" t="s">
-        <v>865</v>
+        <v>860</v>
       </c>
     </row>
     <row r="122" spans="21:22">
@@ -55036,7 +54996,7 @@
         <v>17050</v>
       </c>
       <c r="V122" t="s">
-        <v>866</v>
+        <v>861</v>
       </c>
     </row>
     <row r="123" spans="21:22">
@@ -55044,7 +55004,7 @@
         <v>17060</v>
       </c>
       <c r="V123" t="s">
-        <v>867</v>
+        <v>862</v>
       </c>
     </row>
     <row r="124" spans="21:22">
@@ -55052,7 +55012,7 @@
         <v>18010</v>
       </c>
       <c r="V124" t="s">
-        <v>868</v>
+        <v>863</v>
       </c>
     </row>
     <row r="125" spans="21:22">
@@ -55060,7 +55020,7 @@
         <v>18020</v>
       </c>
       <c r="V125" t="s">
-        <v>869</v>
+        <v>864</v>
       </c>
     </row>
     <row r="126" spans="21:22">
@@ -55068,7 +55028,7 @@
         <v>19010</v>
       </c>
       <c r="V126" t="s">
-        <v>870</v>
+        <v>865</v>
       </c>
     </row>
     <row r="127" spans="21:22">
@@ -55076,7 +55036,7 @@
         <v>19020</v>
       </c>
       <c r="V127" t="s">
-        <v>871</v>
+        <v>866</v>
       </c>
     </row>
     <row r="128" spans="21:22">
@@ -55084,7 +55044,7 @@
         <v>19030</v>
       </c>
       <c r="V128" t="s">
-        <v>872</v>
+        <v>867</v>
       </c>
     </row>
     <row r="129" spans="21:22">
@@ -55092,7 +55052,7 @@
         <v>20030</v>
       </c>
       <c r="V129" t="s">
-        <v>873</v>
+        <v>868</v>
       </c>
     </row>
     <row r="130" spans="21:22">
@@ -55100,7 +55060,7 @@
         <v>20040</v>
       </c>
       <c r="V130" t="s">
-        <v>874</v>
+        <v>869</v>
       </c>
     </row>
     <row r="131" spans="21:22">
@@ -55108,7 +55068,7 @@
         <v>20050</v>
       </c>
       <c r="V131" t="s">
-        <v>875</v>
+        <v>870</v>
       </c>
     </row>
     <row r="132" spans="21:22">
@@ -55116,7 +55076,7 @@
         <v>20070</v>
       </c>
       <c r="V132" t="s">
-        <v>876</v>
+        <v>871</v>
       </c>
     </row>
     <row r="133" spans="21:22">
@@ -55124,7 +55084,7 @@
         <v>20071</v>
       </c>
       <c r="V133" t="s">
-        <v>877</v>
+        <v>872</v>
       </c>
     </row>
     <row r="134" spans="21:22">
@@ -55132,7 +55092,7 @@
         <v>20110</v>
       </c>
       <c r="V134" t="s">
-        <v>878</v>
+        <v>873</v>
       </c>
     </row>
     <row r="135" spans="21:22">
@@ -55140,7 +55100,7 @@
         <v>20120</v>
       </c>
       <c r="V135" t="s">
-        <v>879</v>
+        <v>874</v>
       </c>
     </row>
     <row r="136" spans="21:22">
@@ -55148,7 +55108,7 @@
         <v>20130</v>
       </c>
       <c r="V136" t="s">
-        <v>880</v>
+        <v>875</v>
       </c>
     </row>
     <row r="137" spans="21:22">
@@ -55156,7 +55116,7 @@
         <v>20140</v>
       </c>
       <c r="V137" t="s">
-        <v>881</v>
+        <v>876</v>
       </c>
     </row>
     <row r="138" spans="21:22">
@@ -55164,7 +55124,7 @@
         <v>20150</v>
       </c>
       <c r="V138" t="s">
-        <v>882</v>
+        <v>877</v>
       </c>
     </row>
     <row r="139" spans="21:22">
@@ -55172,7 +55132,7 @@
         <v>20160</v>
       </c>
       <c r="V139" t="s">
-        <v>883</v>
+        <v>878</v>
       </c>
     </row>
     <row r="140" spans="21:22">
@@ -55180,7 +55140,7 @@
         <v>23010</v>
       </c>
       <c r="V140" t="s">
-        <v>884</v>
+        <v>879</v>
       </c>
     </row>
     <row r="141" spans="21:22">
@@ -55188,7 +55148,7 @@
         <v>24010</v>
       </c>
       <c r="V141" t="s">
-        <v>885</v>
+        <v>880</v>
       </c>
     </row>
     <row r="142" spans="21:22">
@@ -55196,7 +55156,7 @@
         <v>30010</v>
       </c>
       <c r="V142" t="s">
-        <v>886</v>
+        <v>881</v>
       </c>
     </row>
     <row r="143" spans="21:22">
@@ -55204,7 +55164,7 @@
         <v>30020</v>
       </c>
       <c r="V143" t="s">
-        <v>887</v>
+        <v>882</v>
       </c>
     </row>
     <row r="144" spans="21:22">
@@ -55212,7 +55172,7 @@
         <v>40010</v>
       </c>
       <c r="V144" t="s">
-        <v>888</v>
+        <v>883</v>
       </c>
     </row>
     <row r="145" spans="21:22">
@@ -55220,7 +55180,7 @@
         <v>40020</v>
       </c>
       <c r="V145" t="s">
-        <v>889</v>
+        <v>884</v>
       </c>
     </row>
     <row r="146" spans="21:22">
@@ -55228,7 +55188,7 @@
         <v>40030</v>
       </c>
       <c r="V146" t="s">
-        <v>890</v>
+        <v>885</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Data/Skills.xlsx
+++ b/Assets/Data/Skills.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8340" activeTab="2"/>
+    <workbookView windowWidth="18650" windowHeight="8390" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="Skills" sheetId="1" r:id="rId1"/>
@@ -2942,10 +2942,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -2979,6 +2979,44 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -2987,7 +3025,46 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -3008,87 +3085,11 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -3099,9 +3100,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -3128,7 +3128,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3140,13 +3140,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3158,31 +3158,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3200,7 +3200,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3212,7 +3218,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3224,19 +3254,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3254,25 +3278,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3284,31 +3308,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3319,6 +3319,41 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -3337,15 +3372,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
@@ -3357,6 +3383,15 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -3384,41 +3419,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -3427,97 +3427,97 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="14" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="14" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="26" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -3526,46 +3526,46 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -3732,7 +3732,7 @@
             <v>101</v>
           </cell>
           <cell r="B9" t="str">
-            <v>FireOne1</v>
+            <v>MakerEffect/FireOne1</v>
           </cell>
         </row>
         <row r="10">
@@ -3740,7 +3740,7 @@
             <v>102</v>
           </cell>
           <cell r="B10" t="str">
-            <v>FireOne2</v>
+            <v>MakerEffect/FireOne2</v>
           </cell>
         </row>
         <row r="11">
@@ -3748,7 +3748,7 @@
             <v>111</v>
           </cell>
           <cell r="B11" t="str">
-            <v>FireAll1</v>
+            <v>MakerEffect/FireAll1</v>
           </cell>
         </row>
         <row r="12">
@@ -3756,7 +3756,7 @@
             <v>112</v>
           </cell>
           <cell r="B12" t="str">
-            <v>FireAll2</v>
+            <v>MakerEffect/FireAll2</v>
           </cell>
         </row>
         <row r="13">
@@ -3764,7 +3764,7 @@
             <v>113</v>
           </cell>
           <cell r="B13" t="str">
-            <v>FireAll3</v>
+            <v>MakerEffect/FireAll3</v>
           </cell>
         </row>
         <row r="14">
@@ -3772,7 +3772,7 @@
             <v>201</v>
           </cell>
           <cell r="B14" t="str">
-            <v>ThunderOne1</v>
+            <v>MakerEffect/ThunderOne1</v>
           </cell>
         </row>
         <row r="15">
@@ -3780,7 +3780,7 @@
             <v>202</v>
           </cell>
           <cell r="B15" t="str">
-            <v>ThunderOne2</v>
+            <v>MakerEffect/ThunderOne2</v>
           </cell>
         </row>
         <row r="16">
@@ -3788,7 +3788,7 @@
             <v>211</v>
           </cell>
           <cell r="B16" t="str">
-            <v>ThunderAll1</v>
+            <v>MakerEffect/ThunderAll1</v>
           </cell>
         </row>
         <row r="17">
@@ -3796,7 +3796,7 @@
             <v>212</v>
           </cell>
           <cell r="B17" t="str">
-            <v>ThunderAll2</v>
+            <v>MakerEffect/ThunderAll2</v>
           </cell>
         </row>
         <row r="18">
@@ -3804,7 +3804,7 @@
             <v>213</v>
           </cell>
           <cell r="B18" t="str">
-            <v>ThunderAll3</v>
+            <v>MakerEffect/ThunderAll3</v>
           </cell>
         </row>
         <row r="19">
@@ -3812,7 +3812,7 @@
             <v>301</v>
           </cell>
           <cell r="B19" t="str">
-            <v>IceOne1</v>
+            <v>MakerEffect/IceOne1</v>
           </cell>
         </row>
         <row r="20">
@@ -3820,7 +3820,7 @@
             <v>302</v>
           </cell>
           <cell r="B20" t="str">
-            <v>IceOne2</v>
+            <v>MakerEffect/IceOne2</v>
           </cell>
         </row>
         <row r="21">
@@ -3828,7 +3828,7 @@
             <v>311</v>
           </cell>
           <cell r="B21" t="str">
-            <v>IceAll1</v>
+            <v>MakerEffect/IceAll1</v>
           </cell>
         </row>
         <row r="22">
@@ -3836,7 +3836,7 @@
             <v>312</v>
           </cell>
           <cell r="B22" t="str">
-            <v>IceAll2</v>
+            <v>MakerEffect/IceAll2</v>
           </cell>
         </row>
         <row r="23">
@@ -3844,7 +3844,7 @@
             <v>313</v>
           </cell>
           <cell r="B23" t="str">
-            <v>IceAll3</v>
+            <v>MakerEffect/IceAll3</v>
           </cell>
         </row>
         <row r="24">
@@ -3852,7 +3852,7 @@
             <v>401</v>
           </cell>
           <cell r="B24" t="str">
-            <v>LightOne1</v>
+            <v>MakerEffect/LightOne1</v>
           </cell>
         </row>
         <row r="25">
@@ -3860,7 +3860,7 @@
             <v>402</v>
           </cell>
           <cell r="B25" t="str">
-            <v>LightOne2</v>
+            <v>MakerEffect/LightOne2</v>
           </cell>
         </row>
         <row r="26">
@@ -3868,7 +3868,7 @@
             <v>411</v>
           </cell>
           <cell r="B26" t="str">
-            <v>LightAll1</v>
+            <v>MakerEffect/LightAll1</v>
           </cell>
         </row>
         <row r="27">
@@ -3876,7 +3876,7 @@
             <v>412</v>
           </cell>
           <cell r="B27" t="str">
-            <v>LightAll2</v>
+            <v>MakerEffect/LightAll2</v>
           </cell>
         </row>
         <row r="28">
@@ -3884,7 +3884,7 @@
             <v>413</v>
           </cell>
           <cell r="B28" t="str">
-            <v>LightAll3</v>
+            <v>MakerEffect/LightAll3</v>
           </cell>
         </row>
         <row r="29">
@@ -3892,7 +3892,7 @@
             <v>501</v>
           </cell>
           <cell r="B29" t="str">
-            <v>DarknessOne1</v>
+            <v>MakerEffect/DarknessOne1</v>
           </cell>
         </row>
         <row r="30">
@@ -3900,7 +3900,7 @@
             <v>502</v>
           </cell>
           <cell r="B30" t="str">
-            <v>DarknessOne2</v>
+            <v>MakerEffect/DarknessOne2</v>
           </cell>
         </row>
         <row r="31">
@@ -3908,7 +3908,7 @@
             <v>511</v>
           </cell>
           <cell r="B31" t="str">
-            <v>DarknessAll1</v>
+            <v>MakerEffect/DarknessAll1</v>
           </cell>
         </row>
         <row r="32">
@@ -3916,7 +3916,7 @@
             <v>512</v>
           </cell>
           <cell r="B32" t="str">
-            <v>DarknessAll2</v>
+            <v>MakerEffect/DarknessAll2</v>
           </cell>
         </row>
         <row r="33">
@@ -3924,7 +3924,7 @@
             <v>513</v>
           </cell>
           <cell r="B33" t="str">
-            <v>DarknessAll3</v>
+            <v>MakerEffect/DarknessAll3</v>
           </cell>
         </row>
         <row r="34">
@@ -3932,7 +3932,7 @@
             <v>601</v>
           </cell>
           <cell r="B34" t="str">
-            <v>NeutralOne1</v>
+            <v>MakerEffect/NeutralOne1</v>
           </cell>
         </row>
         <row r="35">
@@ -3940,7 +3940,7 @@
             <v>602</v>
           </cell>
           <cell r="B35" t="str">
-            <v>NeutralOne2</v>
+            <v>MakerEffect/NeutralOne2</v>
           </cell>
         </row>
         <row r="36">
@@ -3948,7 +3948,7 @@
             <v>611</v>
           </cell>
           <cell r="B36" t="str">
-            <v>NeutralAll1</v>
+            <v>MakerEffect/NeutralAll1</v>
           </cell>
         </row>
         <row r="37">
@@ -3956,7 +3956,7 @@
             <v>612</v>
           </cell>
           <cell r="B37" t="str">
-            <v>NeutralAll2</v>
+            <v>MakerEffect/NeutralAll2</v>
           </cell>
         </row>
         <row r="38">
@@ -3964,7 +3964,7 @@
             <v>613</v>
           </cell>
           <cell r="B38" t="str">
-            <v>NeutralAll3</v>
+            <v>MakerEffect/NeutralAll3</v>
           </cell>
         </row>
         <row r="39">
@@ -3972,7 +3972,7 @@
             <v>701</v>
           </cell>
           <cell r="B39" t="str">
-            <v>HealOne1</v>
+            <v>MakerEffect/HealOne1</v>
           </cell>
         </row>
         <row r="40">
@@ -3980,7 +3980,7 @@
             <v>702</v>
           </cell>
           <cell r="B40" t="str">
-            <v>HealOne2</v>
+            <v>MakerEffect/HealOne2</v>
           </cell>
         </row>
         <row r="41">
@@ -3988,7 +3988,7 @@
             <v>711</v>
           </cell>
           <cell r="B41" t="str">
-            <v>HealAll1</v>
+            <v>MakerEffect/HealAll1</v>
           </cell>
         </row>
         <row r="42">
@@ -3996,7 +3996,7 @@
             <v>712</v>
           </cell>
           <cell r="B42" t="str">
-            <v>HealAll2</v>
+            <v>MakerEffect/HealAll2</v>
           </cell>
         </row>
         <row r="43">
@@ -4004,7 +4004,7 @@
             <v>721</v>
           </cell>
           <cell r="B43" t="str">
-            <v>CureOne1</v>
+            <v>MakerEffect/CureOne1</v>
           </cell>
         </row>
         <row r="44">
@@ -4012,7 +4012,7 @@
             <v>722</v>
           </cell>
           <cell r="B44" t="str">
-            <v>CureOne2</v>
+            <v>MakerEffect/CureOne2</v>
           </cell>
         </row>
         <row r="45">
@@ -4020,7 +4020,7 @@
             <v>731</v>
           </cell>
           <cell r="B45" t="str">
-            <v>CureAll1</v>
+            <v>MakerEffect/CureAll1</v>
           </cell>
         </row>
         <row r="46">
@@ -4028,7 +4028,7 @@
             <v>732</v>
           </cell>
           <cell r="B46" t="str">
-            <v>CureAll2</v>
+            <v>MakerEffect/CureAll2</v>
           </cell>
         </row>
         <row r="47">
@@ -4036,7 +4036,7 @@
             <v>741</v>
           </cell>
           <cell r="B47" t="str">
-            <v>Revive1</v>
+            <v>MakerEffect/Revive1</v>
           </cell>
         </row>
         <row r="48">
@@ -4044,7 +4044,7 @@
             <v>742</v>
           </cell>
           <cell r="B48" t="str">
-            <v>Revive2</v>
+            <v>MakerEffect/Revive2</v>
           </cell>
         </row>
         <row r="49">
@@ -4052,7 +4052,7 @@
             <v>801</v>
           </cell>
           <cell r="B49" t="str">
-            <v>Powerup1</v>
+            <v>MakerEffect/Powerup1</v>
           </cell>
         </row>
         <row r="50">
@@ -4060,7 +4060,7 @@
             <v>802</v>
           </cell>
           <cell r="B50" t="str">
-            <v>Powerup2</v>
+            <v>MakerEffect/Powerup2</v>
           </cell>
         </row>
         <row r="51">
@@ -4068,7 +4068,7 @@
             <v>803</v>
           </cell>
           <cell r="B51" t="str">
-            <v>Powerup3</v>
+            <v>MakerEffect/Powerup3</v>
           </cell>
         </row>
         <row r="52">
@@ -4076,7 +4076,7 @@
             <v>811</v>
           </cell>
           <cell r="B52" t="str">
-            <v>Powerdown1</v>
+            <v>MakerEffect/Powerdown1</v>
           </cell>
         </row>
         <row r="53">
@@ -4084,7 +4084,7 @@
             <v>812</v>
           </cell>
           <cell r="B53" t="str">
-            <v>Powerdown2</v>
+            <v>MakerEffect/Powerdown2</v>
           </cell>
         </row>
         <row r="54">
@@ -4092,7 +4092,7 @@
             <v>813</v>
           </cell>
           <cell r="B54" t="str">
-            <v>Powerdown3</v>
+            <v>MakerEffect/Powerdown3</v>
           </cell>
         </row>
         <row r="55">
@@ -4100,7 +4100,7 @@
             <v>901</v>
           </cell>
           <cell r="B55" t="str">
-            <v>Bind</v>
+            <v>MakerEffect/Bind</v>
           </cell>
         </row>
         <row r="56">
@@ -4108,7 +4108,7 @@
             <v>902</v>
           </cell>
           <cell r="B56" t="str">
-            <v>Absorb</v>
+            <v>MakerEffect/Absorb</v>
           </cell>
         </row>
         <row r="57">
@@ -4116,7 +4116,7 @@
             <v>903</v>
           </cell>
           <cell r="B57" t="str">
-            <v>Poison</v>
+            <v>MakerEffect/Poison</v>
           </cell>
         </row>
         <row r="58">
@@ -4124,7 +4124,7 @@
             <v>904</v>
           </cell>
           <cell r="B58" t="str">
-            <v>Blind</v>
+            <v>MakerEffect/Blind</v>
           </cell>
         </row>
         <row r="59">
@@ -4132,7 +4132,7 @@
             <v>905</v>
           </cell>
           <cell r="B59" t="str">
-            <v>Silence</v>
+            <v>MakerEffect/Silence</v>
           </cell>
         </row>
         <row r="60">
@@ -4140,7 +4140,7 @@
             <v>906</v>
           </cell>
           <cell r="B60" t="str">
-            <v>Sleep</v>
+            <v>MakerEffect/Sleep</v>
           </cell>
         </row>
         <row r="61">
@@ -4148,7 +4148,7 @@
             <v>907</v>
           </cell>
           <cell r="B61" t="str">
-            <v>Confusion</v>
+            <v>MakerEffect/Confusion</v>
           </cell>
         </row>
         <row r="62">
@@ -4156,7 +4156,7 @@
             <v>908</v>
           </cell>
           <cell r="B62" t="str">
-            <v>Paralyze</v>
+            <v>MakerEffect/Paralyze</v>
           </cell>
         </row>
         <row r="63">
@@ -4164,7 +4164,7 @@
             <v>909</v>
           </cell>
           <cell r="B63" t="str">
-            <v>Death</v>
+            <v>MakerEffect/Death</v>
           </cell>
         </row>
         <row r="64">
@@ -4172,7 +4172,7 @@
             <v>1001</v>
           </cell>
           <cell r="B64" t="str">
-            <v>HitPhysical</v>
+            <v>MakerEffect/HitPhysical</v>
           </cell>
         </row>
         <row r="65">
@@ -4180,7 +4180,7 @@
             <v>1002</v>
           </cell>
           <cell r="B65" t="str">
-            <v>HitEffect</v>
+            <v>MakerEffect/HitEffect</v>
           </cell>
         </row>
         <row r="66">
@@ -4188,7 +4188,7 @@
             <v>1003</v>
           </cell>
           <cell r="B66" t="str">
-            <v>HitFire</v>
+            <v>MakerEffect/HitFire</v>
           </cell>
         </row>
         <row r="67">
@@ -4196,7 +4196,7 @@
             <v>1004</v>
           </cell>
           <cell r="B67" t="str">
-            <v>HitIce</v>
+            <v>MakerEffect/HitIce</v>
           </cell>
         </row>
         <row r="68">
@@ -4204,7 +4204,7 @@
             <v>1005</v>
           </cell>
           <cell r="B68" t="str">
-            <v>HitThunder</v>
+            <v>MakerEffect/HitThunder</v>
           </cell>
         </row>
         <row r="69">
@@ -4212,7 +4212,7 @@
             <v>1011</v>
           </cell>
           <cell r="B69" t="str">
-            <v>SlashPhysical</v>
+            <v>MakerEffect/SlashPhysical</v>
           </cell>
         </row>
         <row r="70">
@@ -4220,7 +4220,7 @@
             <v>1012</v>
           </cell>
           <cell r="B70" t="str">
-            <v>SlashEffect</v>
+            <v>MakerEffect/SlashEffect</v>
           </cell>
         </row>
         <row r="71">
@@ -4228,7 +4228,7 @@
             <v>1013</v>
           </cell>
           <cell r="B71" t="str">
-            <v>SlashFire</v>
+            <v>MakerEffect/SlashFire</v>
           </cell>
         </row>
         <row r="72">
@@ -4236,7 +4236,7 @@
             <v>1014</v>
           </cell>
           <cell r="B72" t="str">
-            <v>SlashIce</v>
+            <v>MakerEffect/SlashIce</v>
           </cell>
         </row>
         <row r="73">
@@ -4244,7 +4244,7 @@
             <v>1015</v>
           </cell>
           <cell r="B73" t="str">
-            <v>SlashThunder</v>
+            <v>MakerEffect/SlashThunder</v>
           </cell>
         </row>
         <row r="74">
@@ -4252,7 +4252,7 @@
             <v>1021</v>
           </cell>
           <cell r="B74" t="str">
-            <v>PiercePhysical</v>
+            <v>MakerEffect/PiercePhysical</v>
           </cell>
         </row>
         <row r="75">
@@ -4260,7 +4260,7 @@
             <v>1022</v>
           </cell>
           <cell r="B75" t="str">
-            <v>PierceEffect</v>
+            <v>MakerEffect/PierceEffect</v>
           </cell>
         </row>
         <row r="76">
@@ -4268,7 +4268,7 @@
             <v>1023</v>
           </cell>
           <cell r="B76" t="str">
-            <v>PierceFire</v>
+            <v>MakerEffect/PierceFire</v>
           </cell>
         </row>
         <row r="77">
@@ -4276,7 +4276,7 @@
             <v>1024</v>
           </cell>
           <cell r="B77" t="str">
-            <v>PierceIce</v>
+            <v>MakerEffect/PierceIce</v>
           </cell>
         </row>
         <row r="78">
@@ -4284,7 +4284,7 @@
             <v>1025</v>
           </cell>
           <cell r="B78" t="str">
-            <v>PierceThunder</v>
+            <v>MakerEffect/PierceThunder</v>
           </cell>
         </row>
         <row r="79">
@@ -4292,7 +4292,7 @@
             <v>1031</v>
           </cell>
           <cell r="B79" t="str">
-            <v>ClawPhysical</v>
+            <v>MakerEffect/ClawPhysical</v>
           </cell>
         </row>
         <row r="80">
@@ -4300,7 +4300,7 @@
             <v>1032</v>
           </cell>
           <cell r="B80" t="str">
-            <v>ClawEffect</v>
+            <v>MakerEffect/ClawEffect</v>
           </cell>
         </row>
         <row r="81">
@@ -4308,7 +4308,7 @@
             <v>1033</v>
           </cell>
           <cell r="B81" t="str">
-            <v>ClawFire</v>
+            <v>MakerEffect/ClawFire</v>
           </cell>
         </row>
         <row r="82">
@@ -4316,7 +4316,7 @@
             <v>1034</v>
           </cell>
           <cell r="B82" t="str">
-            <v>ClawIce</v>
+            <v>MakerEffect/ClawIce</v>
           </cell>
         </row>
         <row r="83">
@@ -4324,7 +4324,7 @@
             <v>1035</v>
           </cell>
           <cell r="B83" t="str">
-            <v>ClawThunder</v>
+            <v>MakerEffect/ClawThunder</v>
           </cell>
         </row>
         <row r="84">
@@ -4332,7 +4332,7 @@
             <v>1041</v>
           </cell>
           <cell r="B84" t="str">
-            <v>HitSpecial1</v>
+            <v>MakerEffect/HitSpecial1</v>
           </cell>
         </row>
         <row r="85">
@@ -4340,7 +4340,7 @@
             <v>1042</v>
           </cell>
           <cell r="B85" t="str">
-            <v>HitSpecial2</v>
+            <v>MakerEffect/HitSpecial2</v>
           </cell>
         </row>
         <row r="86">
@@ -4348,7 +4348,7 @@
             <v>1051</v>
           </cell>
           <cell r="B86" t="str">
-            <v>SlashSpecial1</v>
+            <v>MakerEffect/SlashSpecial1</v>
           </cell>
         </row>
         <row r="87">
@@ -4356,7 +4356,7 @@
             <v>1052</v>
           </cell>
           <cell r="B87" t="str">
-            <v>SlashSpecial2</v>
+            <v>MakerEffect/SlashSpecial2</v>
           </cell>
         </row>
         <row r="88">
@@ -4364,7 +4364,7 @@
             <v>1061</v>
           </cell>
           <cell r="B88" t="str">
-            <v>PierceSpecial1</v>
+            <v>MakerEffect/PierceSpecial1</v>
           </cell>
         </row>
         <row r="89">
@@ -4372,7 +4372,7 @@
             <v>1062</v>
           </cell>
           <cell r="B89" t="str">
-            <v>PierceSpecial2</v>
+            <v>MakerEffect/PierceSpecial2</v>
           </cell>
         </row>
         <row r="90">
@@ -4380,7 +4380,7 @@
             <v>1071</v>
           </cell>
           <cell r="B90" t="str">
-            <v>ClawSpecial</v>
+            <v>MakerEffect/ClawSpecial</v>
           </cell>
         </row>
         <row r="91">
@@ -4388,7 +4388,7 @@
             <v>1081</v>
           </cell>
           <cell r="B91" t="str">
-            <v>ArrowSpecial</v>
+            <v>MakerEffect/ArrowSpecial</v>
           </cell>
         </row>
         <row r="92">
@@ -4396,7 +4396,7 @@
             <v>1091</v>
           </cell>
           <cell r="B92" t="str">
-            <v>GeneralSpecial1</v>
+            <v>MakerEffect/GeneralSpecial1</v>
           </cell>
         </row>
         <row r="93">
@@ -4404,7 +4404,7 @@
             <v>1092</v>
           </cell>
           <cell r="B93" t="str">
-            <v>GeneralSpecial2</v>
+            <v>MakerEffect/GeneralSpecial2</v>
           </cell>
         </row>
         <row r="94">
@@ -4412,7 +4412,7 @@
             <v>1101</v>
           </cell>
           <cell r="B94" t="str">
-            <v>Breath</v>
+            <v>MakerEffect/Breath</v>
           </cell>
         </row>
         <row r="95">
@@ -4420,7 +4420,7 @@
             <v>1102</v>
           </cell>
           <cell r="B95" t="str">
-            <v>Pollen</v>
+            <v>MakerEffect/Pollen</v>
           </cell>
         </row>
         <row r="96">
@@ -4428,7 +4428,7 @@
             <v>1103</v>
           </cell>
           <cell r="B96" t="str">
-            <v>SonicWave</v>
+            <v>MakerEffect/SonicWave</v>
           </cell>
         </row>
         <row r="97">
@@ -4436,7 +4436,7 @@
             <v>1104</v>
           </cell>
           <cell r="B97" t="str">
-            <v>Fog</v>
+            <v>MakerEffect/Fog</v>
           </cell>
         </row>
         <row r="98">
@@ -4444,7 +4444,7 @@
             <v>1105</v>
           </cell>
           <cell r="B98" t="str">
-            <v>Song</v>
+            <v>MakerEffect/Song</v>
           </cell>
         </row>
         <row r="99">
@@ -4452,7 +4452,7 @@
             <v>1106</v>
           </cell>
           <cell r="B99" t="str">
-            <v>Shout</v>
+            <v>MakerEffect/Shout</v>
           </cell>
         </row>
         <row r="100">
@@ -4460,7 +4460,7 @@
             <v>1107</v>
           </cell>
           <cell r="B100" t="str">
-            <v>Sweep</v>
+            <v>MakerEffect/Sweep</v>
           </cell>
         </row>
         <row r="101">
@@ -4468,7 +4468,7 @@
             <v>1108</v>
           </cell>
           <cell r="B101" t="str">
-            <v>Bodyslam</v>
+            <v>MakerEffect/Bodyslam</v>
           </cell>
         </row>
         <row r="102">
@@ -4476,7 +4476,7 @@
             <v>1109</v>
           </cell>
           <cell r="B102" t="str">
-            <v>Flash</v>
+            <v>MakerEffect/Flash</v>
           </cell>
         </row>
         <row r="103">
@@ -4484,7 +4484,7 @@
             <v>1201</v>
           </cell>
           <cell r="B103" t="str">
-            <v>WaterOne1</v>
+            <v>MakerEffect/WaterOne1</v>
           </cell>
         </row>
         <row r="104">
@@ -4492,7 +4492,7 @@
             <v>1202</v>
           </cell>
           <cell r="B104" t="str">
-            <v>WaterOne2</v>
+            <v>MakerEffect/WaterOne2</v>
           </cell>
         </row>
         <row r="105">
@@ -4500,7 +4500,7 @@
             <v>1211</v>
           </cell>
           <cell r="B105" t="str">
-            <v>WaterAll1</v>
+            <v>MakerEffect/WaterAll1</v>
           </cell>
         </row>
         <row r="106">
@@ -4508,7 +4508,7 @@
             <v>1212</v>
           </cell>
           <cell r="B106" t="str">
-            <v>WaterAll2</v>
+            <v>MakerEffect/WaterAll2</v>
           </cell>
         </row>
         <row r="107">
@@ -4516,7 +4516,7 @@
             <v>1213</v>
           </cell>
           <cell r="B107" t="str">
-            <v>WaterAll3</v>
+            <v>MakerEffect/WaterAll3</v>
           </cell>
         </row>
         <row r="108">
@@ -4524,7 +4524,7 @@
             <v>1301</v>
           </cell>
           <cell r="B108" t="str">
-            <v>EarthOne1</v>
+            <v>MakerEffect/EarthOne1</v>
           </cell>
         </row>
         <row r="109">
@@ -4532,7 +4532,7 @@
             <v>1302</v>
           </cell>
           <cell r="B109" t="str">
-            <v>EarthOne2</v>
+            <v>MakerEffect/EarthOne2</v>
           </cell>
         </row>
         <row r="110">
@@ -4540,7 +4540,7 @@
             <v>1311</v>
           </cell>
           <cell r="B110" t="str">
-            <v>EarthAll1</v>
+            <v>MakerEffect/EarthAll1</v>
           </cell>
         </row>
         <row r="111">
@@ -4548,7 +4548,7 @@
             <v>1312</v>
           </cell>
           <cell r="B111" t="str">
-            <v>EarthAll2</v>
+            <v>MakerEffect/EarthAll2</v>
           </cell>
         </row>
         <row r="112">
@@ -4556,7 +4556,7 @@
             <v>1313</v>
           </cell>
           <cell r="B112" t="str">
-            <v>EarthAll3</v>
+            <v>MakerEffect/EarthAll3</v>
           </cell>
         </row>
         <row r="113">
@@ -4564,7 +4564,7 @@
             <v>1401</v>
           </cell>
           <cell r="B113" t="str">
-            <v>WindOne1</v>
+            <v>MakerEffect/WindOne1</v>
           </cell>
         </row>
         <row r="114">
@@ -4572,7 +4572,7 @@
             <v>1402</v>
           </cell>
           <cell r="B114" t="str">
-            <v>WindOne2</v>
+            <v>MakerEffect/WindOne2</v>
           </cell>
         </row>
         <row r="115">
@@ -4580,7 +4580,7 @@
             <v>1411</v>
           </cell>
           <cell r="B115" t="str">
-            <v>WindAll1</v>
+            <v>MakerEffect/WindAll1</v>
           </cell>
         </row>
         <row r="116">
@@ -4588,7 +4588,7 @@
             <v>1412</v>
           </cell>
           <cell r="B116" t="str">
-            <v>WindAll2</v>
+            <v>MakerEffect/WindAll2</v>
           </cell>
         </row>
         <row r="117">
@@ -4596,7 +4596,7 @@
             <v>1413</v>
           </cell>
           <cell r="B117" t="str">
-            <v>WindAll3</v>
+            <v>MakerEffect/WindAll3</v>
           </cell>
         </row>
         <row r="118">
@@ -4604,7 +4604,7 @@
             <v>1501</v>
           </cell>
           <cell r="B118" t="str">
-            <v>BallsOfLight</v>
+            <v>MakerEffect/BallsOfLight</v>
           </cell>
         </row>
         <row r="119">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="G11" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F11,[1]Animations!A:A))</f>
-        <v>FireOne1</v>
+        <v>MakerEffect/FireOne1</v>
       </c>
       <c r="H11">
         <v>2</v>
@@ -9749,7 +9749,7 @@
       </c>
       <c r="G15" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F15,[1]Animations!A:A))</f>
-        <v>FireOne2</v>
+        <v>MakerEffect/FireOne2</v>
       </c>
       <c r="H15">
         <v>1</v>
@@ -9831,7 +9831,7 @@
       </c>
       <c r="G16" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F16,[1]Animations!A:A))</f>
-        <v>FireOne1</v>
+        <v>MakerEffect/FireOne1</v>
       </c>
       <c r="H16">
         <v>1</v>
@@ -9995,7 +9995,7 @@
       </c>
       <c r="G18" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F18,[1]Animations!A:A))</f>
-        <v>ThunderOne1</v>
+        <v>MakerEffect/ThunderOne1</v>
       </c>
       <c r="H18">
         <v>1</v>
@@ -10323,7 +10323,7 @@
       </c>
       <c r="G22" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F22,[1]Animations!A:A))</f>
-        <v>ThunderOne1</v>
+        <v>MakerEffect/ThunderOne1</v>
       </c>
       <c r="H22">
         <v>1</v>
@@ -10405,7 +10405,7 @@
       </c>
       <c r="G23" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F23,[1]Animations!A:A))</f>
-        <v>ThunderOne1</v>
+        <v>MakerEffect/ThunderOne1</v>
       </c>
       <c r="H23">
         <v>1</v>
@@ -10487,7 +10487,7 @@
       </c>
       <c r="G24" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F24,[1]Animations!A:A))</f>
-        <v>Flash</v>
+        <v>MakerEffect/Flash</v>
       </c>
       <c r="H24">
         <v>1</v>
@@ -10651,7 +10651,7 @@
       </c>
       <c r="G26" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F26,[1]Animations!A:A))</f>
-        <v>ThunderOne1</v>
+        <v>MakerEffect/ThunderOne1</v>
       </c>
       <c r="H26">
         <v>1</v>
@@ -10733,7 +10733,7 @@
       </c>
       <c r="G27" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F27,[1]Animations!A:A))</f>
-        <v>IceOne1</v>
+        <v>MakerEffect/IceOne1</v>
       </c>
       <c r="H27">
         <v>1</v>
@@ -11225,7 +11225,7 @@
       </c>
       <c r="G33" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F33,[1]Animations!A:A))</f>
-        <v>Fog</v>
+        <v>MakerEffect/Fog</v>
       </c>
       <c r="H33">
         <v>1</v>
@@ -11635,7 +11635,7 @@
       </c>
       <c r="G38" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F38,[1]Animations!A:A))</f>
-        <v>LightOne1</v>
+        <v>MakerEffect/LightOne1</v>
       </c>
       <c r="H38">
         <v>1</v>
@@ -12291,7 +12291,7 @@
       </c>
       <c r="G46" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F46,[1]Animations!A:A))</f>
-        <v>DarknessOne1</v>
+        <v>MakerEffect/DarknessOne1</v>
       </c>
       <c r="H46">
         <v>1</v>
@@ -13985,7 +13985,7 @@
       </c>
       <c r="G67" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F67,[1]Animations!A:A))</f>
-        <v>Flash</v>
+        <v>MakerEffect/Flash</v>
       </c>
       <c r="H67">
         <v>1</v>
@@ -14067,7 +14067,7 @@
       </c>
       <c r="G68" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F68,[1]Animations!A:A))</f>
-        <v>Flash</v>
+        <v>MakerEffect/Flash</v>
       </c>
       <c r="H68">
         <v>1</v>
@@ -14149,7 +14149,7 @@
       </c>
       <c r="G69" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F69,[1]Animations!A:A))</f>
-        <v>Flash</v>
+        <v>MakerEffect/Flash</v>
       </c>
       <c r="H69">
         <v>1</v>
@@ -14477,7 +14477,7 @@
       </c>
       <c r="G73" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F73,[1]Animations!A:A))</f>
-        <v>Flash</v>
+        <v>MakerEffect/Flash</v>
       </c>
       <c r="H73">
         <v>1</v>
@@ -14559,7 +14559,7 @@
       </c>
       <c r="G74" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F74,[1]Animations!A:A))</f>
-        <v>Flash</v>
+        <v>MakerEffect/Flash</v>
       </c>
       <c r="H74">
         <v>1</v>
@@ -14641,7 +14641,7 @@
       </c>
       <c r="G75" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F75,[1]Animations!A:A))</f>
-        <v>BallsOfLight</v>
+        <v>MakerEffect/BallsOfLight</v>
       </c>
       <c r="H75">
         <v>1</v>
@@ -14723,7 +14723,7 @@
       </c>
       <c r="G76" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F76,[1]Animations!A:A))</f>
-        <v>BallsOfLight</v>
+        <v>MakerEffect/BallsOfLight</v>
       </c>
       <c r="H76">
         <v>1</v>
@@ -14805,7 +14805,7 @@
       </c>
       <c r="G77" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F77,[1]Animations!A:A))</f>
-        <v>BallsOfLight</v>
+        <v>MakerEffect/BallsOfLight</v>
       </c>
       <c r="H77">
         <v>1</v>
@@ -14887,7 +14887,7 @@
       </c>
       <c r="G78" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F78,[1]Animations!A:A))</f>
-        <v>BallsOfLight</v>
+        <v>MakerEffect/BallsOfLight</v>
       </c>
       <c r="H78">
         <v>1</v>
@@ -14969,7 +14969,7 @@
       </c>
       <c r="G79" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F79,[1]Animations!A:A))</f>
-        <v>BallsOfLight</v>
+        <v>MakerEffect/BallsOfLight</v>
       </c>
       <c r="H79">
         <v>1</v>
@@ -15051,7 +15051,7 @@
       </c>
       <c r="G80" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F80,[1]Animations!A:A))</f>
-        <v>Flash</v>
+        <v>MakerEffect/Flash</v>
       </c>
       <c r="H80">
         <v>1</v>
@@ -15297,7 +15297,7 @@
       </c>
       <c r="G83" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F83,[1]Animations!A:A))</f>
-        <v>BallsOfLight</v>
+        <v>MakerEffect/BallsOfLight</v>
       </c>
       <c r="H83">
         <v>1</v>
@@ -15379,7 +15379,7 @@
       </c>
       <c r="G84" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F84,[1]Animations!A:A))</f>
-        <v>BallsOfLight</v>
+        <v>MakerEffect/BallsOfLight</v>
       </c>
       <c r="H84">
         <v>1</v>
@@ -15461,7 +15461,7 @@
       </c>
       <c r="G85" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F85,[1]Animations!A:A))</f>
-        <v>Flash</v>
+        <v>MakerEffect/Flash</v>
       </c>
       <c r="H85">
         <v>1</v>
@@ -15543,7 +15543,7 @@
       </c>
       <c r="G86" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F86,[1]Animations!A:A))</f>
-        <v>Flash</v>
+        <v>MakerEffect/Flash</v>
       </c>
       <c r="H86">
         <v>1</v>
@@ -15625,7 +15625,7 @@
       </c>
       <c r="G87" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F87,[1]Animations!A:A))</f>
-        <v>Powerup3</v>
+        <v>MakerEffect/Powerup3</v>
       </c>
       <c r="H87">
         <v>1</v>
@@ -15707,7 +15707,7 @@
       </c>
       <c r="G88" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F88,[1]Animations!A:A))</f>
-        <v>Powerup3</v>
+        <v>MakerEffect/Powerup3</v>
       </c>
       <c r="H88">
         <v>1</v>
@@ -15871,7 +15871,7 @@
       </c>
       <c r="G90" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F90,[1]Animations!A:A))</f>
-        <v>Powerup3</v>
+        <v>MakerEffect/Powerup3</v>
       </c>
       <c r="H90">
         <v>1</v>
@@ -15953,7 +15953,7 @@
       </c>
       <c r="G91" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F91,[1]Animations!A:A))</f>
-        <v>Flash</v>
+        <v>MakerEffect/Flash</v>
       </c>
       <c r="H91">
         <v>1</v>
@@ -16035,7 +16035,7 @@
       </c>
       <c r="G92" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F92,[1]Animations!A:A))</f>
-        <v>Flash</v>
+        <v>MakerEffect/Flash</v>
       </c>
       <c r="H92">
         <v>1</v>
@@ -16117,7 +16117,7 @@
       </c>
       <c r="G93" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F93,[1]Animations!A:A))</f>
-        <v>PierceIce</v>
+        <v>MakerEffect/PierceIce</v>
       </c>
       <c r="H93">
         <v>1</v>
@@ -16281,7 +16281,7 @@
       </c>
       <c r="G95" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F95,[1]Animations!A:A))</f>
-        <v>PierceIce</v>
+        <v>MakerEffect/PierceIce</v>
       </c>
       <c r="H95">
         <v>1</v>
@@ -16363,7 +16363,7 @@
       </c>
       <c r="G96" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F96,[1]Animations!A:A))</f>
-        <v>Flash</v>
+        <v>MakerEffect/Flash</v>
       </c>
       <c r="H96">
         <v>1</v>
@@ -16445,7 +16445,7 @@
       </c>
       <c r="G97" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F97,[1]Animations!A:A))</f>
-        <v>Powerup3</v>
+        <v>MakerEffect/Powerup3</v>
       </c>
       <c r="H97">
         <v>1</v>
@@ -16527,7 +16527,7 @@
       </c>
       <c r="G98" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F98,[1]Animations!A:A))</f>
-        <v>PierceIce</v>
+        <v>MakerEffect/PierceIce</v>
       </c>
       <c r="H98">
         <v>1</v>
@@ -16609,7 +16609,7 @@
       </c>
       <c r="G99" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F99,[1]Animations!A:A))</f>
-        <v>Powerup3</v>
+        <v>MakerEffect/Powerup3</v>
       </c>
       <c r="H99">
         <v>1</v>
@@ -16691,7 +16691,7 @@
       </c>
       <c r="G100" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F100,[1]Animations!A:A))</f>
-        <v>Flash</v>
+        <v>MakerEffect/Flash</v>
       </c>
       <c r="H100">
         <v>1</v>
@@ -16855,7 +16855,7 @@
       </c>
       <c r="G102" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F102,[1]Animations!A:A))</f>
-        <v>Flash</v>
+        <v>MakerEffect/Flash</v>
       </c>
       <c r="H102">
         <v>1</v>
@@ -17019,7 +17019,7 @@
       </c>
       <c r="G104" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F104,[1]Animations!A:A))</f>
-        <v>Flash</v>
+        <v>MakerEffect/Flash</v>
       </c>
       <c r="H104">
         <v>1</v>
@@ -17101,7 +17101,7 @@
       </c>
       <c r="G105" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F105,[1]Animations!A:A))</f>
-        <v>Flash</v>
+        <v>MakerEffect/Flash</v>
       </c>
       <c r="H105">
         <v>1</v>
@@ -17183,7 +17183,7 @@
       </c>
       <c r="G106" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F106,[1]Animations!A:A))</f>
-        <v>Flash</v>
+        <v>MakerEffect/Flash</v>
       </c>
       <c r="H106">
         <v>1</v>
@@ -17757,7 +17757,7 @@
       </c>
       <c r="G113" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F113,[1]Animations!A:A))</f>
-        <v>Flash</v>
+        <v>MakerEffect/Flash</v>
       </c>
       <c r="H113">
         <v>1</v>
@@ -18971,7 +18971,7 @@
       </c>
       <c r="G128" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F128,[1]Animations!A:A))</f>
-        <v>FireOne1</v>
+        <v>MakerEffect/FireOne1</v>
       </c>
       <c r="H128">
         <v>1</v>
@@ -19135,7 +19135,7 @@
       </c>
       <c r="G130" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F130,[1]Animations!A:A))</f>
-        <v>HitEffect</v>
+        <v>MakerEffect/HitEffect</v>
       </c>
       <c r="H130">
         <v>1</v>
@@ -19299,7 +19299,7 @@
       </c>
       <c r="G132" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F132,[1]Animations!A:A))</f>
-        <v>HitFire</v>
+        <v>MakerEffect/HitFire</v>
       </c>
       <c r="H132">
         <v>1</v>
@@ -19381,7 +19381,7 @@
       </c>
       <c r="G133" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F133,[1]Animations!A:A))</f>
-        <v>LightOne1</v>
+        <v>MakerEffect/LightOne1</v>
       </c>
       <c r="H133">
         <v>1</v>
@@ -19463,7 +19463,7 @@
       </c>
       <c r="G134" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F134,[1]Animations!A:A))</f>
-        <v>HitIce</v>
+        <v>MakerEffect/HitIce</v>
       </c>
       <c r="H134">
         <v>1</v>
@@ -19627,7 +19627,7 @@
       </c>
       <c r="G136" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F136,[1]Animations!A:A))</f>
-        <v>HitThunder</v>
+        <v>MakerEffect/HitThunder</v>
       </c>
       <c r="H136">
         <v>1</v>
@@ -19791,7 +19791,7 @@
       </c>
       <c r="G138" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F138,[1]Animations!A:A))</f>
-        <v>HitThunder</v>
+        <v>MakerEffect/HitThunder</v>
       </c>
       <c r="H138">
         <v>1</v>
@@ -19873,7 +19873,7 @@
       </c>
       <c r="G139" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F139,[1]Animations!A:A))</f>
-        <v>ThunderOne1</v>
+        <v>MakerEffect/ThunderOne1</v>
       </c>
       <c r="H139">
         <v>1</v>
@@ -19955,7 +19955,7 @@
       </c>
       <c r="G140" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F140,[1]Animations!A:A))</f>
-        <v>HitThunder</v>
+        <v>MakerEffect/HitThunder</v>
       </c>
       <c r="H140">
         <v>1</v>
@@ -20119,7 +20119,7 @@
       </c>
       <c r="G142" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F142,[1]Animations!A:A))</f>
-        <v>HitThunder</v>
+        <v>MakerEffect/HitThunder</v>
       </c>
       <c r="H142">
         <v>1</v>
@@ -20201,7 +20201,7 @@
       </c>
       <c r="G143" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F143,[1]Animations!A:A))</f>
-        <v>FireOne1</v>
+        <v>MakerEffect/FireOne1</v>
       </c>
       <c r="H143">
         <v>1</v>
@@ -20365,7 +20365,7 @@
       </c>
       <c r="G145" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F145,[1]Animations!A:A))</f>
-        <v>HitThunder</v>
+        <v>MakerEffect/HitThunder</v>
       </c>
       <c r="H145">
         <v>1</v>
@@ -20611,7 +20611,7 @@
       </c>
       <c r="G148" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F148,[1]Animations!A:A))</f>
-        <v>HitThunder</v>
+        <v>MakerEffect/HitThunder</v>
       </c>
       <c r="H148">
         <v>1</v>
@@ -20693,7 +20693,7 @@
       </c>
       <c r="G149" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F149,[1]Animations!A:A))</f>
-        <v>IceOne1</v>
+        <v>MakerEffect/IceOne1</v>
       </c>
       <c r="H149">
         <v>1</v>
@@ -20775,7 +20775,7 @@
       </c>
       <c r="G150" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F150,[1]Animations!A:A))</f>
-        <v>HitThunder</v>
+        <v>MakerEffect/HitThunder</v>
       </c>
       <c r="H150">
         <v>1</v>
@@ -20939,7 +20939,7 @@
       </c>
       <c r="G152" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F152,[1]Animations!A:A))</f>
-        <v>HitFire</v>
+        <v>MakerEffect/HitFire</v>
       </c>
       <c r="H152">
         <v>1</v>
@@ -21103,7 +21103,7 @@
       </c>
       <c r="G154" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F154,[1]Animations!A:A))</f>
-        <v>FireOne1</v>
+        <v>MakerEffect/FireOne1</v>
       </c>
       <c r="H154">
         <v>1</v>
@@ -21267,7 +21267,7 @@
       </c>
       <c r="G156" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F156,[1]Animations!A:A))</f>
-        <v>FireOne1</v>
+        <v>MakerEffect/FireOne1</v>
       </c>
       <c r="H156">
         <v>1</v>
@@ -21677,7 +21677,7 @@
       </c>
       <c r="G161" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F161,[1]Animations!A:A))</f>
-        <v>ThunderOne1</v>
+        <v>MakerEffect/ThunderOne1</v>
       </c>
       <c r="H161">
         <v>1</v>
@@ -22087,7 +22087,7 @@
       </c>
       <c r="G166" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F166,[1]Animations!A:A))</f>
-        <v>IceOne1</v>
+        <v>MakerEffect/IceOne1</v>
       </c>
       <c r="H166">
         <v>1</v>
@@ -22251,7 +22251,7 @@
       </c>
       <c r="G168" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F168,[1]Animations!A:A))</f>
-        <v>DarknessOne1</v>
+        <v>MakerEffect/DarknessOne1</v>
       </c>
       <c r="H168">
         <v>1</v>
@@ -22333,7 +22333,7 @@
       </c>
       <c r="G169" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F169,[1]Animations!A:A))</f>
-        <v>DarknessOne1</v>
+        <v>MakerEffect/DarknessOne1</v>
       </c>
       <c r="H169">
         <v>1</v>
@@ -23891,7 +23891,7 @@
       </c>
       <c r="G188" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F188,[1]Animations!A:A))</f>
-        <v>FireOne1</v>
+        <v>MakerEffect/FireOne1</v>
       </c>
       <c r="H188">
         <v>1</v>
@@ -26321,7 +26321,7 @@
       </c>
       <c r="G219" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F219,[1]Animations!A:A))</f>
-        <v>FireOne1</v>
+        <v>MakerEffect/FireOne1</v>
       </c>
       <c r="H219">
         <v>1</v>
@@ -26403,7 +26403,7 @@
       </c>
       <c r="G220" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F220,[1]Animations!A:A))</f>
-        <v>FireOne1</v>
+        <v>MakerEffect/FireOne1</v>
       </c>
       <c r="H220">
         <v>2</v>
@@ -26649,7 +26649,7 @@
       </c>
       <c r="G223" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F223,[1]Animations!A:A))</f>
-        <v>FireOne1</v>
+        <v>MakerEffect/FireOne1</v>
       </c>
       <c r="H223">
         <v>1</v>
@@ -26731,7 +26731,7 @@
       </c>
       <c r="G224" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F224,[1]Animations!A:A))</f>
-        <v>FireOne1</v>
+        <v>MakerEffect/FireOne1</v>
       </c>
       <c r="H224">
         <v>1</v>
@@ -26813,7 +26813,7 @@
       </c>
       <c r="G225" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F225,[1]Animations!A:A))</f>
-        <v>FireOne1</v>
+        <v>MakerEffect/FireOne1</v>
       </c>
       <c r="H225">
         <v>1</v>
@@ -26977,7 +26977,7 @@
       </c>
       <c r="G227" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F227,[1]Animations!A:A))</f>
-        <v>ThunderOne1</v>
+        <v>MakerEffect/ThunderOne1</v>
       </c>
       <c r="H227">
         <v>1</v>
@@ -27141,7 +27141,7 @@
       </c>
       <c r="G229" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F229,[1]Animations!A:A))</f>
-        <v>ThunderOne1</v>
+        <v>MakerEffect/ThunderOne1</v>
       </c>
       <c r="H229">
         <v>1</v>
@@ -27305,7 +27305,7 @@
       </c>
       <c r="G231" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F231,[1]Animations!A:A))</f>
-        <v>ThunderOne1</v>
+        <v>MakerEffect/ThunderOne1</v>
       </c>
       <c r="H231">
         <v>1</v>
@@ -27387,7 +27387,7 @@
       </c>
       <c r="G232" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F232,[1]Animations!A:A))</f>
-        <v>ThunderOne1</v>
+        <v>MakerEffect/ThunderOne1</v>
       </c>
       <c r="H232">
         <v>1</v>
@@ -27551,7 +27551,7 @@
       </c>
       <c r="G234" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F234,[1]Animations!A:A))</f>
-        <v>ThunderOne1</v>
+        <v>MakerEffect/ThunderOne1</v>
       </c>
       <c r="H234">
         <v>1</v>
@@ -27633,7 +27633,7 @@
       </c>
       <c r="G235" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F235,[1]Animations!A:A))</f>
-        <v>IceOne1</v>
+        <v>MakerEffect/IceOne1</v>
       </c>
       <c r="H235">
         <v>1</v>
@@ -27715,7 +27715,7 @@
       </c>
       <c r="G236" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F236,[1]Animations!A:A))</f>
-        <v>IceOne1</v>
+        <v>MakerEffect/IceOne1</v>
       </c>
       <c r="H236">
         <v>1</v>
@@ -27961,7 +27961,7 @@
       </c>
       <c r="G239" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F239,[1]Animations!A:A))</f>
-        <v>IceOne1</v>
+        <v>MakerEffect/IceOne1</v>
       </c>
       <c r="H239">
         <v>1</v>
@@ -28043,7 +28043,7 @@
       </c>
       <c r="G240" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F240,[1]Animations!A:A))</f>
-        <v>IceOne1</v>
+        <v>MakerEffect/IceOne1</v>
       </c>
       <c r="H240">
         <v>1</v>
@@ -28289,7 +28289,7 @@
       </c>
       <c r="G243" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F243,[1]Animations!A:A))</f>
-        <v>LightOne1</v>
+        <v>MakerEffect/LightOne1</v>
       </c>
       <c r="H243">
         <v>1</v>
@@ -28371,7 +28371,7 @@
       </c>
       <c r="G244" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F244,[1]Animations!A:A))</f>
-        <v>LightOne1</v>
+        <v>MakerEffect/LightOne1</v>
       </c>
       <c r="H244">
         <v>1</v>
@@ -28535,7 +28535,7 @@
       </c>
       <c r="G246" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F246,[1]Animations!A:A))</f>
-        <v>LightOne1</v>
+        <v>MakerEffect/LightOne1</v>
       </c>
       <c r="H246">
         <v>1</v>
@@ -28945,7 +28945,7 @@
       </c>
       <c r="G251" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F251,[1]Animations!A:A))</f>
-        <v>DarknessOne1</v>
+        <v>MakerEffect/DarknessOne1</v>
       </c>
       <c r="H251">
         <v>1</v>
@@ -29027,7 +29027,7 @@
       </c>
       <c r="G252" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F252,[1]Animations!A:A))</f>
-        <v>DarknessOne1</v>
+        <v>MakerEffect/DarknessOne1</v>
       </c>
       <c r="H252">
         <v>3</v>
@@ -29109,7 +29109,7 @@
       </c>
       <c r="G253" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F253,[1]Animations!A:A))</f>
-        <v>DarknessOne1</v>
+        <v>MakerEffect/DarknessOne1</v>
       </c>
       <c r="H253">
         <v>1</v>
@@ -29191,7 +29191,7 @@
       </c>
       <c r="G254" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F254,[1]Animations!A:A))</f>
-        <v>DarknessOne1</v>
+        <v>MakerEffect/DarknessOne1</v>
       </c>
       <c r="H254">
         <v>1</v>
@@ -29273,7 +29273,7 @@
       </c>
       <c r="G255" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F255,[1]Animations!A:A))</f>
-        <v>DarknessOne1</v>
+        <v>MakerEffect/DarknessOne1</v>
       </c>
       <c r="H255">
         <v>1</v>
@@ -29519,7 +29519,7 @@
       </c>
       <c r="G258" t="str">
         <f>INDEX([1]Animations!B:B,MATCH(F258,[1]Animations!A:A))</f>
-        <v>DarknessOne1</v>
+        <v>MakerEffect/DarknessOne1</v>
       </c>
       <c r="H258">
         <v>1</v>

--- a/Assets/Data/Skills.xlsx
+++ b/Assets/Data/Skills.xlsx
@@ -611,7 +611,7 @@
   </si>
   <si>
     <t>\sのATKが/f[f,0,3]アップ
-会得していたらさらに/f[f,1,3]アップ</t>
+(会得時)/f[f,1,3]アップ</t>
   </si>
   <si>
     <t>プリディカメント</t>
@@ -619,7 +619,7 @@
   <si>
     <t>(条件)Hpが25%以下
 \sのATKが/f[f,0,3]アップ
-会得していたらさらに/f[f,1,3]アップ</t>
+(会得時)/f[f,1,3]アップ</t>
   </si>
   <si>
     <t>アサルトシフト</t>
@@ -627,7 +627,7 @@
   <si>
     <t>(条件)バトル開始時
 \sのDEFが/f[f,0,3]ダウンしATKが/f[f,0,3]アップ
-会得していたらさらに/f[f,2,3]アップ</t>
+(会得時)/f[f,2,3]アップ</t>
   </si>
   <si>
     <t>アクティブギフト</t>
@@ -687,7 +687,7 @@
   <si>
     <t>(条件)自身の攻撃成功時
 火傷状態ではない対象に/f[f,0,2]ターン/f[f,0,3]%ダメージの火傷付与
-会得していたらさらに/f[f,0,3]%アップ
+(会得時)/f[f,0,3]%アップ
 /s</t>
   </si>
   <si>
@@ -704,7 +704,7 @@
   </si>
   <si>
     <t>\sのSPDが/f[f,0,3]アップ
-会得していたらさらに/f[f,1,3]アップ</t>
+(会得時)/f[f,1,3]アップ</t>
   </si>
   <si>
     <t>イヴェイドオール</t>
@@ -712,7 +712,7 @@
   <si>
     <t>(条件)バトル開始時
 \sの回避率を/f[f,0,3]%アップ(永続)
-会得していたらさらに/f[f,1,3]アップ
+(会得時)/f[f,1,3]アップ
 最大5回まで重ね掛け可能</t>
   </si>
   <si>
@@ -721,7 +721,7 @@
   <si>
     <t>(条件)バトル開始時
 \sの初動がわずかに早くなる
-会得していたらさらに早くなる</t>
+(会得時)さらに早くなる</t>
   </si>
   <si>
     <t>チェイスマジック</t>
@@ -766,7 +766,7 @@
   <si>
     <t>(条件)バトル開始時
 \sの初動が少し早くなる
-会得していたらさらに早くなる
+(会得時)さらに早くなる
 自身のATKを/f[f,1,2]ターン/f[f,1,3]ダウン</t>
   </si>
   <si>
@@ -774,7 +774,7 @@
   </si>
   <si>
     <t>\sのDEFが/f[f,0,3]アップ
-会得していたらさらに/f[f,1,3]アップ</t>
+(会得時)/f[f,1,3]アップ</t>
   </si>
   <si>
     <t>クイックバリア</t>
@@ -796,7 +796,7 @@
   <si>
     <t>(条件)自身が攻撃を受ける直前
 ダメージを/f[f,0,3]%カット
-会得していたらさらに/f[f,1,3]カット</t>
+(会得時)/f[f,1,3]カット</t>
   </si>
   <si>
     <t>パッシブジャミング</t>
@@ -819,7 +819,7 @@
   <si>
     <t>(条件)攻撃成功時33%の確率で
 行動待機時間を/f[f,0,1]延長
-会得していたらさらに/f[f,1,3]延長</t>
+(会得時)/f[f,1,3]延長</t>
   </si>
   <si>
     <t>ライフスティール</t>
@@ -827,7 +827,7 @@
   <si>
     <t>(条件)自身が行動する前に発動
 ダメージの/f[f,0,3]%分Hp回復
-会得していたらさらに/f[f,1,3]%分Hp回復</t>
+(会得時)/f[f,1,3]%分Hp回復</t>
   </si>
   <si>
     <t>アイスセイバー</t>
@@ -853,7 +853,7 @@
     <t>(条件)自身の攻撃成功時
 挑発状態ではない対象に挑発付与
 自身のDEFを1ターン2アップ
-会得していたらさらに2アップ
+(会得時)2アップ
 /s</t>
   </si>
   <si>
@@ -862,7 +862,7 @@
   <si>
     <t>(制限)バトル中/f[f,0,2]回まで
 状態異常を回避する
-会得していたらさらに/f[f,0,3]回アップ
+(会得時)/f[f,0,3]回アップ
 /s</t>
   </si>
   <si>
@@ -878,7 +878,7 @@
   </si>
   <si>
     <t>\sの命中率が/f[f,0,3]%アップ
-会得していたらさらに/f[f,1,3]アップ
+(会得時)/f[f,1,3]アップ
 最大5回まで重ね掛け可能</t>
   </si>
   <si>
@@ -892,7 +892,7 @@
   </si>
   <si>
     <t>\sの最大Hpが/f[f,0,3]アップ
-会得していたらさらに/f[f,1,3]アップ</t>
+(会得時)/f[f,1,3]アップ</t>
   </si>
   <si>
     <t>パッシブサプライ</t>
@@ -916,7 +916,7 @@
   <si>
     <t>(条件)味方が攻撃を受けた際に発動
 対象のHpを/f[f,0,1]回復
-会得していたらさらに/f[f,1,3]回復</t>
+(会得時)/f[f,1,3]回復</t>
   </si>
   <si>
     <t>リレイズ</t>
@@ -957,7 +957,7 @@
   <si>
     <t>(条件)Hpが25%以下
 \sの会心率が/f[f,0,3]%アップ
-会得していたらさらに/f[f,1,3]%アップ</t>
+(会得時)/f[f,1,3]%アップ</t>
   </si>
   <si>
     <t>グレイブアクト</t>
@@ -980,7 +980,7 @@
   <si>
     <t>(条件)Hpが50%以下
 ダメージの/f[f,0,3]%分Hp回復
-会得していたらさらに/f[f,1,3]分Hp回復</t>
+(会得時)/f[f,1,3]分Hp回復</t>
   </si>
   <si>
     <t>アンデッドペイン</t>
@@ -1019,7 +1019,7 @@
   <si>
     <t>(条件)自身が攻撃を受けた際に発動
 \sのATKとDEFが/f[f,0,2]ターン/f[f,0,3]アップ
-会得していたらさらに/f[f,2,3]アップ</t>
+(会得時)/f[f,2,3]アップ</t>
   </si>
   <si>
     <t>リープリアクト</t>
@@ -1028,7 +1028,7 @@
     <t>(条件)会心攻撃をした後
 再行動できる
 \sの会心率が/f[f,1,2]ターン/f[f,1,3]%ダウン
-会得していたらさらに会心率が5%アップ</t>
+(会得時)会心率が5%アップ</t>
   </si>
   <si>
     <t>ウェイトユニゾン</t>
@@ -2948,8 +2948,8 @@
   <numFmts count="4">
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -2967,6 +2967,66 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -2974,18 +3034,19 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -3006,83 +3067,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -3105,7 +3090,22 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -3132,19 +3132,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3156,91 +3162,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3258,7 +3186,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3270,7 +3198,79 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3282,25 +3282,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3312,7 +3306,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3350,6 +3350,32 @@
       <diagonal/>
     </border>
     <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
@@ -3368,28 +3394,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
       <bottom style="double">
         <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -3409,17 +3415,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -3431,145 +3431,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="18" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>

--- a/Assets/Data/Skills.xlsx
+++ b/Assets/Data/Skills.xlsx
@@ -679,7 +679,8 @@
   </si>
   <si>
     <t>(条件)他の味方がPassive魔法を使用する際に発動
-\sのCT-/f[f,0,1]</t>
+\sのCT-/f[f,0,1]
+(会得時)使用者のレストアのCT-1</t>
   </si>
   <si>
     <t>フレイムセイバー</t>
@@ -2946,10 +2947,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -2967,8 +2968,75 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -2983,7 +3051,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -2991,62 +3059,9 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -3058,23 +3073,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <i/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -3090,15 +3091,15 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -3138,43 +3139,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3192,7 +3175,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3204,13 +3223,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3222,7 +3283,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3234,85 +3313,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3323,15 +3324,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -3346,32 +3338,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -3394,8 +3360,41 @@
       <left/>
       <right/>
       <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="double">
         <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -3417,9 +3416,11 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -3431,145 +3432,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="28" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="18" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="20" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -50727,7 +50728,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="71" customFormat="1" ht="26" spans="1:3">
+    <row r="71" customFormat="1" ht="39" spans="1:3">
       <c r="A71">
         <v>11100</v>
       </c>

--- a/Assets/Data/Skills.xlsx
+++ b/Assets/Data/Skills.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="18650" windowHeight="8390" activeTab="4"/>
+    <workbookView windowWidth="18650" windowHeight="8390" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Skills" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1117" uniqueCount="887">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1118" uniqueCount="887">
   <si>
     <t>Id</t>
   </si>
@@ -1062,7 +1062,7 @@
     <t>ソーイングアームド</t>
   </si>
   <si>
-    <t>(条件)イクスティンクションを3回使用する
+    <t>(条件)敵を撃破する
 \sにDEF/f[f,0,3]%無視の貫通を付与（永続）
 覚醒状態に移行
 /s</t>
@@ -2813,6 +2813,9 @@
     <t>相手が攻撃無効を発揮する</t>
   </si>
   <si>
+    <t>攻撃をした時に相手が戦闘不能になる</t>
+  </si>
+  <si>
     <t>〇のKindを持っている味方</t>
   </si>
   <si>
@@ -2886,9 +2889,6 @@
   </si>
   <si>
     <t>自身が〇状態の時に攻撃を受ける</t>
-  </si>
-  <si>
-    <t>攻撃をした時に相手が戦闘不能になる</t>
   </si>
   <si>
     <t>自分以外が戦闘不能</t>
@@ -2947,10 +2947,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -2965,43 +2965,6 @@
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="128"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -3021,7 +2984,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -3030,6 +2993,28 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -3051,7 +3036,21 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -3066,6 +3065,14 @@
     </font>
     <font>
       <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="18"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -3073,9 +3080,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -3089,24 +3096,17 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <i/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <u/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -3133,7 +3133,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3145,13 +3187,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3163,7 +3199,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3175,7 +3217,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3187,25 +3259,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3223,31 +3295,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3259,61 +3307,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3324,6 +3324,24 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -3338,30 +3356,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -3383,9 +3377,26 @@
     <border>
       <left/>
       <right/>
-      <top/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
       <bottom style="double">
-        <color rgb="FFFF8001"/>
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -3413,17 +3424,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -3432,145 +3432,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="28" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="18" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="18" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="20" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -33148,14 +33148,14 @@
         <v>覚醒解除</v>
       </c>
       <c r="C4">
-        <v>3020</v>
+        <v>0</v>
       </c>
       <c r="D4" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C4,Define!P:P))</f>
-        <v>ステート解除</v>
+        <v>ない</v>
       </c>
       <c r="E4">
-        <v>1010</v>
+        <v>0</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -33166,9 +33166,9 @@
       <c r="H4">
         <v>100</v>
       </c>
-      <c r="I4" t="str">
+      <c r="I4" t="e">
         <f>INDEX([2]TextData!B:B,MATCH(E4,[2]TextData!A:A))</f>
-        <v>覚醒</v>
+        <v>#N/A</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -46928,20 +46928,20 @@
         <v>ソーイングアームド</v>
       </c>
       <c r="C78">
-        <v>17010</v>
+        <v>12110</v>
       </c>
       <c r="D78" t="str">
         <f>INDEX(Define!V:V,MATCH(C78,Define!U:U))</f>
-        <v>魔法を〇回使用する</v>
+        <v>攻撃をした時に相手が戦闘不能になる</v>
       </c>
       <c r="E78">
         <v>61</v>
       </c>
       <c r="F78">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G78">
-        <v>1060</v>
+        <v>0</v>
       </c>
       <c r="H78">
         <v>0</v>
@@ -53263,7 +53263,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AC147"/>
+  <dimension ref="A1:AC148"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13"/>
   <cols>
     <col min="3" max="3" width="1.72727272727273" customWidth="1"/>
@@ -55087,7 +55087,7 @@
     </row>
     <row r="105" spans="21:22">
       <c r="U105">
-        <v>13010</v>
+        <v>12110</v>
       </c>
       <c r="V105" t="s">
         <v>844</v>
@@ -55095,7 +55095,7 @@
     </row>
     <row r="106" spans="21:22">
       <c r="U106">
-        <v>13020</v>
+        <v>13010</v>
       </c>
       <c r="V106" t="s">
         <v>845</v>
@@ -55103,7 +55103,7 @@
     </row>
     <row r="107" spans="21:22">
       <c r="U107">
-        <v>14010</v>
+        <v>13020</v>
       </c>
       <c r="V107" t="s">
         <v>846</v>
@@ -55111,7 +55111,7 @@
     </row>
     <row r="108" spans="21:22">
       <c r="U108">
-        <v>14110</v>
+        <v>14010</v>
       </c>
       <c r="V108" t="s">
         <v>847</v>
@@ -55119,7 +55119,7 @@
     </row>
     <row r="109" spans="21:22">
       <c r="U109">
-        <v>14210</v>
+        <v>14110</v>
       </c>
       <c r="V109" t="s">
         <v>848</v>
@@ -55127,7 +55127,7 @@
     </row>
     <row r="110" spans="21:22">
       <c r="U110">
-        <v>14310</v>
+        <v>14210</v>
       </c>
       <c r="V110" t="s">
         <v>849</v>
@@ -55135,7 +55135,7 @@
     </row>
     <row r="111" spans="21:22">
       <c r="U111">
-        <v>14410</v>
+        <v>14310</v>
       </c>
       <c r="V111" t="s">
         <v>850</v>
@@ -55143,7 +55143,7 @@
     </row>
     <row r="112" spans="21:22">
       <c r="U112">
-        <v>14420</v>
+        <v>14410</v>
       </c>
       <c r="V112" t="s">
         <v>851</v>
@@ -55151,7 +55151,7 @@
     </row>
     <row r="113" spans="21:22">
       <c r="U113">
-        <v>14520</v>
+        <v>14420</v>
       </c>
       <c r="V113" t="s">
         <v>852</v>
@@ -55159,7 +55159,7 @@
     </row>
     <row r="114" spans="21:22">
       <c r="U114">
-        <v>15010</v>
+        <v>14520</v>
       </c>
       <c r="V114" t="s">
         <v>853</v>
@@ -55167,7 +55167,7 @@
     </row>
     <row r="115" spans="21:22">
       <c r="U115">
-        <v>15011</v>
+        <v>15010</v>
       </c>
       <c r="V115" t="s">
         <v>854</v>
@@ -55175,7 +55175,7 @@
     </row>
     <row r="116" spans="21:22">
       <c r="U116">
-        <v>15022</v>
+        <v>15011</v>
       </c>
       <c r="V116" t="s">
         <v>855</v>
@@ -55183,7 +55183,7 @@
     </row>
     <row r="117" spans="21:22">
       <c r="U117">
-        <v>16010</v>
+        <v>15022</v>
       </c>
       <c r="V117" t="s">
         <v>856</v>
@@ -55191,7 +55191,7 @@
     </row>
     <row r="118" spans="21:22">
       <c r="U118">
-        <v>16020</v>
+        <v>16010</v>
       </c>
       <c r="V118" t="s">
         <v>857</v>
@@ -55199,7 +55199,7 @@
     </row>
     <row r="119" spans="21:22">
       <c r="U119">
-        <v>17010</v>
+        <v>16020</v>
       </c>
       <c r="V119" t="s">
         <v>858</v>
@@ -55207,7 +55207,7 @@
     </row>
     <row r="120" spans="21:22">
       <c r="U120">
-        <v>17020</v>
+        <v>17010</v>
       </c>
       <c r="V120" t="s">
         <v>859</v>
@@ -55215,7 +55215,7 @@
     </row>
     <row r="121" spans="21:22">
       <c r="U121">
-        <v>17030</v>
+        <v>17020</v>
       </c>
       <c r="V121" t="s">
         <v>860</v>
@@ -55223,7 +55223,7 @@
     </row>
     <row r="122" spans="21:22">
       <c r="U122">
-        <v>17040</v>
+        <v>17030</v>
       </c>
       <c r="V122" t="s">
         <v>861</v>
@@ -55231,7 +55231,7 @@
     </row>
     <row r="123" spans="21:22">
       <c r="U123">
-        <v>17050</v>
+        <v>17040</v>
       </c>
       <c r="V123" t="s">
         <v>862</v>
@@ -55239,7 +55239,7 @@
     </row>
     <row r="124" spans="21:22">
       <c r="U124">
-        <v>17060</v>
+        <v>17050</v>
       </c>
       <c r="V124" t="s">
         <v>863</v>
@@ -55247,7 +55247,7 @@
     </row>
     <row r="125" spans="21:22">
       <c r="U125">
-        <v>18010</v>
+        <v>17060</v>
       </c>
       <c r="V125" t="s">
         <v>864</v>
@@ -55255,7 +55255,7 @@
     </row>
     <row r="126" spans="21:22">
       <c r="U126">
-        <v>18020</v>
+        <v>18010</v>
       </c>
       <c r="V126" t="s">
         <v>865</v>
@@ -55263,7 +55263,7 @@
     </row>
     <row r="127" spans="21:22">
       <c r="U127">
-        <v>19010</v>
+        <v>18020</v>
       </c>
       <c r="V127" t="s">
         <v>866</v>
@@ -55271,7 +55271,7 @@
     </row>
     <row r="128" spans="21:22">
       <c r="U128">
-        <v>19020</v>
+        <v>19010</v>
       </c>
       <c r="V128" t="s">
         <v>867</v>
@@ -55279,7 +55279,7 @@
     </row>
     <row r="129" spans="21:22">
       <c r="U129">
-        <v>19030</v>
+        <v>19020</v>
       </c>
       <c r="V129" t="s">
         <v>868</v>
@@ -55287,7 +55287,7 @@
     </row>
     <row r="130" spans="21:22">
       <c r="U130">
-        <v>20030</v>
+        <v>19030</v>
       </c>
       <c r="V130" t="s">
         <v>869</v>
@@ -55295,137 +55295,145 @@
     </row>
     <row r="131" spans="21:22">
       <c r="U131">
-        <v>20040</v>
+        <v>20030</v>
       </c>
       <c r="V131" t="s">
-        <v>870</v>
+        <v>844</v>
       </c>
     </row>
     <row r="132" spans="21:22">
       <c r="U132">
-        <v>20050</v>
+        <v>20040</v>
       </c>
       <c r="V132" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
     </row>
     <row r="133" spans="21:22">
       <c r="U133">
-        <v>20070</v>
+        <v>20050</v>
       </c>
       <c r="V133" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
     </row>
     <row r="134" spans="21:22">
       <c r="U134">
-        <v>20071</v>
+        <v>20070</v>
       </c>
       <c r="V134" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
     </row>
     <row r="135" spans="21:22">
       <c r="U135">
-        <v>20110</v>
+        <v>20071</v>
       </c>
       <c r="V135" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
     </row>
     <row r="136" spans="21:22">
       <c r="U136">
-        <v>20120</v>
+        <v>20110</v>
       </c>
       <c r="V136" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
     </row>
     <row r="137" spans="21:22">
       <c r="U137">
-        <v>20130</v>
+        <v>20120</v>
       </c>
       <c r="V137" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
     </row>
     <row r="138" spans="21:22">
       <c r="U138">
-        <v>20140</v>
+        <v>20130</v>
       </c>
       <c r="V138" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
     </row>
     <row r="139" spans="21:22">
       <c r="U139">
-        <v>20150</v>
+        <v>20140</v>
       </c>
       <c r="V139" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
     </row>
     <row r="140" spans="21:22">
       <c r="U140">
-        <v>20160</v>
+        <v>20150</v>
       </c>
       <c r="V140" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
     </row>
     <row r="141" spans="21:22">
       <c r="U141">
-        <v>23010</v>
+        <v>20160</v>
       </c>
       <c r="V141" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
     </row>
     <row r="142" spans="21:22">
       <c r="U142">
-        <v>24010</v>
+        <v>23010</v>
       </c>
       <c r="V142" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
     </row>
     <row r="143" spans="21:22">
       <c r="U143">
-        <v>30010</v>
+        <v>24010</v>
       </c>
       <c r="V143" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
     </row>
     <row r="144" spans="21:22">
       <c r="U144">
-        <v>30020</v>
+        <v>30010</v>
       </c>
       <c r="V144" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
     </row>
     <row r="145" spans="21:22">
       <c r="U145">
-        <v>40010</v>
+        <v>30020</v>
       </c>
       <c r="V145" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="146" spans="21:22">
       <c r="U146">
-        <v>40020</v>
+        <v>40010</v>
       </c>
       <c r="V146" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
     </row>
     <row r="147" spans="21:22">
       <c r="U147">
+        <v>40020</v>
+      </c>
+      <c r="V147" t="s">
+        <v>885</v>
+      </c>
+    </row>
+    <row r="148" spans="21:22">
+      <c r="U148">
         <v>40030</v>
       </c>
-      <c r="V147" t="s">
+      <c r="V148" t="s">
         <v>886</v>
       </c>
     </row>

--- a/Assets/Data/Skills.xlsx
+++ b/Assets/Data/Skills.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="18650" windowHeight="8390" activeTab="1"/>
+    <workbookView windowWidth="18650" windowHeight="8390"/>
   </bookViews>
   <sheets>
     <sheet name="Skills" sheetId="1" r:id="rId1"/>
@@ -2947,10 +2947,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -2969,37 +2969,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -3012,36 +2982,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -3049,8 +2989,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -3072,17 +3013,53 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
-      <sz val="18"/>
+      <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -3096,17 +3073,40 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -3133,103 +3133,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3241,67 +3145,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3317,6 +3161,162 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="9">
     <border>
@@ -3327,20 +3327,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
       <bottom style="double">
-        <color rgb="FFFF8001"/>
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -3360,28 +3357,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -3404,8 +3384,17 @@
       <left/>
       <right/>
       <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -3424,6 +3413,17 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -3432,145 +3432,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="22" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="20" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="20" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="18" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="18" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>

--- a/Assets/Data/Skills.xlsx
+++ b/Assets/Data/Skills.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="18650" windowHeight="8390" activeTab="4"/>
+    <workbookView windowWidth="18650" windowHeight="8390"/>
   </bookViews>
   <sheets>
     <sheet name="Skills" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1150" uniqueCount="901">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1152" uniqueCount="903">
   <si>
     <t>Id</t>
   </si>
@@ -2083,6 +2083,12 @@
   </si>
   <si>
     <t>会心率+5%</t>
+  </si>
+  <si>
+    <t>獲得Exp+30%</t>
+  </si>
+  <si>
+    <t>\sの獲得EXPが/f[f,0,1]%アップ</t>
   </si>
   <si>
     <t>Scope</t>
@@ -2999,24 +3005,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -3030,7 +3020,37 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -3040,6 +3060,53 @@
       <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -3053,51 +3120,13 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -3107,15 +3136,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -3123,21 +3144,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -3164,7 +3170,97 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3176,25 +3272,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3206,85 +3308,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3302,49 +3326,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3355,15 +3361,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -3378,6 +3375,30 @@
       </top>
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -3401,31 +3422,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -3455,6 +3452,15 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -3463,7 +3469,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="16" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="18" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -3472,16 +3478,16 @@
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -3490,118 +3496,118 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="26" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="26" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="23" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -8634,7 +8640,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:X324"/>
+  <dimension ref="A1:X325"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13"/>
   <cols>
     <col min="1" max="2" width="7.63636363636364" customWidth="1"/>
@@ -34606,6 +34612,81 @@
         <v>0</v>
       </c>
     </row>
+    <row r="325" ht="12" customHeight="1" spans="1:24">
+      <c r="A325">
+        <v>506010</v>
+      </c>
+      <c r="B325">
+        <v>506010</v>
+      </c>
+      <c r="C325" t="str">
+        <f>INDEX(TextData!B:B,MATCH(B325,TextData!A:A))</f>
+        <v>獲得Exp+30%</v>
+      </c>
+      <c r="D325">
+        <v>6</v>
+      </c>
+      <c r="E325" t="str">
+        <f>INDEX(Define!X:X,MATCH(D325,Define!W:W))</f>
+        <v>自己強化</v>
+      </c>
+      <c r="H325">
+        <v>1</v>
+      </c>
+      <c r="I325" t="str">
+        <f>INDEX(Define!B:B,MATCH(H325,Define!A:A))</f>
+        <v>単体</v>
+      </c>
+      <c r="J325">
+        <v>0</v>
+      </c>
+      <c r="K325">
+        <v>0</v>
+      </c>
+      <c r="L325">
+        <v>10</v>
+      </c>
+      <c r="M325">
+        <v>6</v>
+      </c>
+      <c r="N325" t="str">
+        <f>INDEX(Define!E:E,MATCH(M325,Define!D:D))</f>
+        <v>無</v>
+      </c>
+      <c r="O325">
+        <v>9</v>
+      </c>
+      <c r="P325" t="str">
+        <f>INDEX(Define!H:H,MATCH(O325,Define!G:G))</f>
+        <v>装備パッシブ</v>
+      </c>
+      <c r="Q325">
+        <v>4</v>
+      </c>
+      <c r="R325" t="str">
+        <f>INDEX(Define!K:K,MATCH(Q325,Define!J:J))</f>
+        <v>自身</v>
+      </c>
+      <c r="S325">
+        <v>4</v>
+      </c>
+      <c r="T325" t="str">
+        <f>INDEX(Define!N:N,MATCH(S325,Define!M:M))</f>
+        <v>自身</v>
+      </c>
+      <c r="U325">
+        <v>1</v>
+      </c>
+      <c r="V325">
+        <v>1</v>
+      </c>
+      <c r="W325">
+        <v>1</v>
+      </c>
+      <c r="X325">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="F1:F264">
     <extLst/>
@@ -34619,7 +34700,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I403"/>
+  <dimension ref="A1:I404"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13"/>
   <cols>
     <col min="2" max="2" width="20" customWidth="1"/>
@@ -46315,6 +46396,34 @@
         <v>5</v>
       </c>
       <c r="H403">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="404" spans="1:8">
+      <c r="A404">
+        <v>506010</v>
+      </c>
+      <c r="B404" t="str">
+        <f>INDEX(TextData!B:B,MATCH(A404,TextData!A:A))</f>
+        <v>獲得Exp+30%</v>
+      </c>
+      <c r="C404">
+        <v>40020</v>
+      </c>
+      <c r="D404" t="str">
+        <f>INDEX(Define!Q:Q,MATCH(C404,Define!P:P))</f>
+        <v>獲得Eｘｐ％アップ</v>
+      </c>
+      <c r="E404">
+        <v>30</v>
+      </c>
+      <c r="F404">
+        <v>0</v>
+      </c>
+      <c r="G404">
+        <v>0</v>
+      </c>
+      <c r="H404">
         <v>100</v>
       </c>
     </row>
@@ -51650,7 +51759,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D319"/>
+  <dimension ref="A1:D320"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="3"/>
   <cols>
     <col min="2" max="2" width="20" customWidth="1"/>
@@ -55181,6 +55290,17 @@
       </c>
       <c r="C319" t="s">
         <v>274</v>
+      </c>
+    </row>
+    <row r="320" spans="1:3">
+      <c r="A320">
+        <v>506010</v>
+      </c>
+      <c r="B320" t="s">
+        <v>605</v>
+      </c>
+      <c r="C320" t="s">
+        <v>606</v>
       </c>
     </row>
   </sheetData>
@@ -55221,19 +55341,19 @@
         <v>12</v>
       </c>
       <c r="M1" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="P1" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="S1" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="U1" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="W1" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="Y1" t="s">
         <v>65</v>
@@ -55244,61 +55364,61 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="D2">
         <v>0</v>
       </c>
       <c r="E2" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="G2">
         <v>0</v>
       </c>
       <c r="H2" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="J2">
         <v>0</v>
       </c>
       <c r="K2" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="M2">
         <v>0</v>
       </c>
       <c r="N2" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="P2">
         <v>0</v>
       </c>
       <c r="Q2" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="U2">
         <v>0</v>
       </c>
       <c r="V2" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="W2">
         <v>0</v>
       </c>
       <c r="X2" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="Y2">
         <v>-1</v>
       </c>
       <c r="Z2" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="AB2">
         <v>301</v>
       </c>
       <c r="AC2" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
     </row>
     <row r="3" spans="1:29">
@@ -55312,19 +55432,19 @@
         <v>1</v>
       </c>
       <c r="E3" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="G3">
         <v>1</v>
       </c>
       <c r="H3" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="J3">
         <v>1</v>
       </c>
       <c r="K3" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="M3">
         <v>1</v>
@@ -55336,31 +55456,31 @@
         <v>1010</v>
       </c>
       <c r="Q3" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="U3">
         <v>1010</v>
       </c>
       <c r="V3" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="W3">
         <v>1</v>
       </c>
       <c r="X3" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="Y3">
         <v>1</v>
       </c>
       <c r="Z3" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="AB3">
         <v>302</v>
       </c>
       <c r="AC3" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
     </row>
     <row r="4" spans="1:29">
@@ -55368,61 +55488,61 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="D4">
         <v>2</v>
       </c>
       <c r="E4" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="G4">
         <v>2</v>
       </c>
       <c r="H4" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="J4">
         <v>2</v>
       </c>
       <c r="K4" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="M4">
         <v>2</v>
       </c>
       <c r="N4" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="P4">
         <v>1020</v>
       </c>
       <c r="Q4" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="U4">
         <v>1020</v>
       </c>
       <c r="V4" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="W4">
         <v>2</v>
       </c>
       <c r="X4" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="Y4">
         <v>11</v>
       </c>
       <c r="Z4" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="AB4" s="2">
         <v>303</v>
       </c>
       <c r="AC4" s="2" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
     </row>
     <row r="5" spans="1:29">
@@ -55430,61 +55550,61 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="D5">
         <v>3</v>
       </c>
       <c r="E5" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="G5">
         <v>3</v>
       </c>
       <c r="H5" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="J5">
         <v>3</v>
       </c>
       <c r="K5" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="M5">
         <v>3</v>
       </c>
       <c r="N5" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="P5">
         <v>1030</v>
       </c>
       <c r="Q5" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="U5">
         <v>1030</v>
       </c>
       <c r="V5" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="W5">
         <v>3</v>
       </c>
       <c r="X5" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="Y5">
         <v>21</v>
       </c>
       <c r="Z5" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="AB5">
         <v>304</v>
       </c>
       <c r="AC5" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
     </row>
     <row r="6" spans="4:29">
@@ -55492,7 +55612,7 @@
         <v>4</v>
       </c>
       <c r="E6" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="G6">
         <v>4</v>
@@ -55504,43 +55624,43 @@
         <v>4</v>
       </c>
       <c r="K6" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="M6">
         <v>4</v>
       </c>
       <c r="N6" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="P6">
         <v>1040</v>
       </c>
       <c r="Q6" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="U6">
         <v>1040</v>
       </c>
       <c r="V6" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="W6">
         <v>4</v>
       </c>
       <c r="X6" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="Y6">
         <v>22</v>
       </c>
       <c r="Z6" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="AB6">
         <v>305</v>
       </c>
       <c r="AC6" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
     </row>
     <row r="7" spans="4:29">
@@ -55548,55 +55668,55 @@
         <v>5</v>
       </c>
       <c r="E7" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="G7">
         <v>5</v>
       </c>
       <c r="H7" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="J7">
         <v>6</v>
       </c>
       <c r="K7" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="M7">
         <v>5</v>
       </c>
       <c r="N7" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="P7">
         <v>1050</v>
       </c>
       <c r="Q7" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="U7">
         <v>1050</v>
       </c>
       <c r="V7" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="W7">
         <v>5</v>
       </c>
       <c r="X7" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="Y7">
         <v>23</v>
       </c>
       <c r="Z7" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="AB7">
         <v>306</v>
       </c>
       <c r="AC7" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="8" spans="4:29">
@@ -55604,55 +55724,55 @@
         <v>6</v>
       </c>
       <c r="E8" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="G8">
         <v>6</v>
       </c>
       <c r="H8" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="J8">
         <v>7</v>
       </c>
       <c r="K8" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="M8">
         <v>11</v>
       </c>
       <c r="N8" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="P8">
         <v>1060</v>
       </c>
       <c r="Q8" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="U8">
         <v>1060</v>
       </c>
       <c r="V8" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="W8">
         <v>6</v>
       </c>
       <c r="X8" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="Y8">
         <v>31</v>
       </c>
       <c r="Z8" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="AB8">
         <v>307</v>
       </c>
       <c r="AC8" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
     </row>
     <row r="9" spans="7:29">
@@ -55660,49 +55780,49 @@
         <v>7</v>
       </c>
       <c r="H9" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="J9">
         <v>11</v>
       </c>
       <c r="K9" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="M9">
         <v>12</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="P9">
         <v>1070</v>
       </c>
       <c r="Q9" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="U9">
         <v>1130</v>
       </c>
       <c r="V9" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="W9">
         <v>7</v>
       </c>
       <c r="X9" t="s">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="Y9">
         <v>41</v>
       </c>
       <c r="Z9" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="AB9">
         <v>308</v>
       </c>
       <c r="AC9" t="s">
-        <v>670</v>
+        <v>672</v>
       </c>
     </row>
     <row r="10" spans="7:29">
@@ -55710,49 +55830,49 @@
         <v>8</v>
       </c>
       <c r="H10" t="s">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="J10">
         <v>101</v>
       </c>
       <c r="K10" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="M10">
         <v>13</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="P10">
         <v>1080</v>
       </c>
       <c r="Q10" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="U10">
         <v>1140</v>
       </c>
       <c r="V10" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="W10">
         <v>10</v>
       </c>
       <c r="X10" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="Y10">
         <v>42</v>
       </c>
       <c r="Z10" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="AB10">
         <v>309</v>
       </c>
       <c r="AC10" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
     </row>
     <row r="11" spans="7:29">
@@ -55760,25 +55880,25 @@
         <v>9</v>
       </c>
       <c r="H11" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="M11">
         <v>21</v>
       </c>
       <c r="N11" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="P11">
         <v>1090</v>
       </c>
       <c r="Q11" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="U11">
         <v>1150</v>
       </c>
       <c r="V11" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="W11">
         <v>11</v>
@@ -55790,13 +55910,13 @@
         <v>51</v>
       </c>
       <c r="Z11" t="s">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="AB11">
         <v>310</v>
       </c>
       <c r="AC11" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
     </row>
     <row r="12" spans="7:29">
@@ -55804,43 +55924,43 @@
         <v>11</v>
       </c>
       <c r="H12" t="s">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="M12">
         <v>31</v>
       </c>
       <c r="N12" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="P12">
         <v>1100</v>
       </c>
       <c r="Q12" t="s">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="U12">
         <v>1160</v>
       </c>
       <c r="V12" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="W12">
         <v>99</v>
       </c>
       <c r="X12" t="s">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="Y12">
         <v>61</v>
       </c>
       <c r="Z12" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="AB12">
         <v>311</v>
       </c>
       <c r="AC12" t="s">
-        <v>691</v>
+        <v>693</v>
       </c>
     </row>
     <row r="13" spans="7:29">
@@ -55848,40 +55968,40 @@
         <v>12</v>
       </c>
       <c r="H13" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="M13">
         <v>32</v>
       </c>
       <c r="N13" t="s">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="P13">
         <v>1110</v>
       </c>
       <c r="Q13" t="s">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="U13">
         <v>2010</v>
       </c>
       <c r="V13" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="W13" t="s">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="Y13">
         <v>101</v>
       </c>
       <c r="Z13" t="s">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="AB13">
         <v>401</v>
       </c>
       <c r="AC13" t="s">
-        <v>698</v>
+        <v>700</v>
       </c>
     </row>
     <row r="14" spans="16:29">
@@ -55889,19 +56009,19 @@
         <v>2010</v>
       </c>
       <c r="Q14" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="U14">
         <v>3010</v>
       </c>
       <c r="V14" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="AB14">
         <v>402</v>
       </c>
       <c r="AC14" t="s">
-        <v>701</v>
+        <v>703</v>
       </c>
     </row>
     <row r="15" spans="16:29">
@@ -55909,19 +56029,19 @@
         <v>2011</v>
       </c>
       <c r="Q15" t="s">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="U15">
         <v>3020</v>
       </c>
       <c r="V15" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="AB15">
         <v>403</v>
       </c>
       <c r="AC15" t="s">
-        <v>704</v>
+        <v>706</v>
       </c>
     </row>
     <row r="16" spans="16:29">
@@ -55929,19 +56049,19 @@
         <v>2020</v>
       </c>
       <c r="Q16" t="s">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="U16">
         <v>3030</v>
       </c>
       <c r="V16" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="AB16">
         <v>404</v>
       </c>
       <c r="AC16" t="s">
-        <v>707</v>
+        <v>709</v>
       </c>
     </row>
     <row r="17" spans="16:29">
@@ -55949,19 +56069,19 @@
         <v>2030</v>
       </c>
       <c r="Q17" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="U17">
         <v>3040</v>
       </c>
       <c r="V17" t="s">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="AB17">
         <v>501</v>
       </c>
       <c r="AC17" t="s">
-        <v>710</v>
+        <v>712</v>
       </c>
     </row>
     <row r="18" spans="16:29">
@@ -55969,19 +56089,19 @@
         <v>2040</v>
       </c>
       <c r="Q18" t="s">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="U18">
         <v>3050</v>
       </c>
       <c r="V18" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="AB18">
         <v>502</v>
       </c>
       <c r="AC18" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
     </row>
     <row r="19" spans="16:29">
@@ -55989,19 +56109,19 @@
         <v>2110</v>
       </c>
       <c r="Q19" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="U19">
         <v>3060</v>
       </c>
       <c r="V19" t="s">
-        <v>715</v>
+        <v>717</v>
       </c>
       <c r="AB19">
         <v>503</v>
       </c>
       <c r="AC19" t="s">
-        <v>716</v>
+        <v>718</v>
       </c>
     </row>
     <row r="20" spans="16:29">
@@ -56009,19 +56129,19 @@
         <v>2120</v>
       </c>
       <c r="Q20" t="s">
-        <v>717</v>
+        <v>719</v>
       </c>
       <c r="U20">
         <v>4010</v>
       </c>
       <c r="V20" t="s">
-        <v>718</v>
+        <v>720</v>
       </c>
       <c r="AB20">
         <v>504</v>
       </c>
       <c r="AC20" t="s">
-        <v>719</v>
+        <v>721</v>
       </c>
     </row>
     <row r="21" spans="16:29">
@@ -56029,19 +56149,19 @@
         <v>2130</v>
       </c>
       <c r="Q21" t="s">
-        <v>720</v>
+        <v>722</v>
       </c>
       <c r="U21">
         <v>4020</v>
       </c>
       <c r="V21" t="s">
-        <v>721</v>
+        <v>723</v>
       </c>
       <c r="AB21">
         <v>505</v>
       </c>
       <c r="AC21" t="s">
-        <v>722</v>
+        <v>724</v>
       </c>
     </row>
     <row r="22" spans="16:29">
@@ -56049,19 +56169,19 @@
         <v>3010</v>
       </c>
       <c r="Q22" t="s">
-        <v>723</v>
+        <v>725</v>
       </c>
       <c r="U22">
         <v>5010</v>
       </c>
       <c r="V22" t="s">
-        <v>724</v>
+        <v>726</v>
       </c>
       <c r="AB22">
         <v>506</v>
       </c>
       <c r="AC22" t="s">
-        <v>725</v>
+        <v>727</v>
       </c>
     </row>
     <row r="23" spans="16:29">
@@ -56069,19 +56189,19 @@
         <v>3020</v>
       </c>
       <c r="Q23" t="s">
-        <v>726</v>
+        <v>728</v>
       </c>
       <c r="U23">
         <v>5020</v>
       </c>
       <c r="V23" t="s">
-        <v>727</v>
+        <v>729</v>
       </c>
       <c r="AB23">
         <v>507</v>
       </c>
       <c r="AC23" t="s">
-        <v>728</v>
+        <v>730</v>
       </c>
     </row>
     <row r="24" spans="16:29">
@@ -56089,19 +56209,19 @@
         <v>3030</v>
       </c>
       <c r="Q24" t="s">
-        <v>729</v>
+        <v>731</v>
       </c>
       <c r="U24">
         <v>5030</v>
       </c>
       <c r="V24" t="s">
-        <v>730</v>
+        <v>732</v>
       </c>
       <c r="AB24">
         <v>508</v>
       </c>
       <c r="AC24" t="s">
-        <v>698</v>
+        <v>700</v>
       </c>
     </row>
     <row r="25" spans="16:29">
@@ -56109,19 +56229,19 @@
         <v>3040</v>
       </c>
       <c r="Q25" t="s">
-        <v>731</v>
+        <v>733</v>
       </c>
       <c r="U25">
         <v>5040</v>
       </c>
       <c r="V25" t="s">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="AB25">
         <v>509</v>
       </c>
       <c r="AC25" t="s">
-        <v>704</v>
+        <v>706</v>
       </c>
     </row>
     <row r="26" spans="16:22">
@@ -56129,13 +56249,13 @@
         <v>3050</v>
       </c>
       <c r="Q26" t="s">
-        <v>733</v>
+        <v>735</v>
       </c>
       <c r="U26">
         <v>5050</v>
       </c>
       <c r="V26" t="s">
-        <v>734</v>
+        <v>736</v>
       </c>
     </row>
     <row r="27" spans="16:22">
@@ -56143,13 +56263,13 @@
         <v>3060</v>
       </c>
       <c r="Q27" t="s">
-        <v>735</v>
+        <v>737</v>
       </c>
       <c r="U27">
         <v>5060</v>
       </c>
       <c r="V27" t="s">
-        <v>736</v>
+        <v>738</v>
       </c>
     </row>
     <row r="28" spans="16:22">
@@ -56157,13 +56277,13 @@
         <v>3070</v>
       </c>
       <c r="Q28" t="s">
-        <v>737</v>
+        <v>739</v>
       </c>
       <c r="U28">
         <v>5070</v>
       </c>
       <c r="V28" t="s">
-        <v>738</v>
+        <v>740</v>
       </c>
     </row>
     <row r="29" spans="16:22">
@@ -56171,13 +56291,13 @@
         <v>4010</v>
       </c>
       <c r="Q29" t="s">
-        <v>739</v>
+        <v>741</v>
       </c>
       <c r="U29">
         <v>5080</v>
       </c>
       <c r="V29" t="s">
-        <v>740</v>
+        <v>742</v>
       </c>
     </row>
     <row r="30" spans="16:22">
@@ -56185,13 +56305,13 @@
         <v>4020</v>
       </c>
       <c r="Q30" t="s">
-        <v>741</v>
+        <v>743</v>
       </c>
       <c r="U30">
         <v>5090</v>
       </c>
       <c r="V30" t="s">
-        <v>742</v>
+        <v>744</v>
       </c>
     </row>
     <row r="31" spans="16:22">
@@ -56199,13 +56319,13 @@
         <v>4030</v>
       </c>
       <c r="Q31" t="s">
-        <v>743</v>
+        <v>745</v>
       </c>
       <c r="U31">
         <v>5100</v>
       </c>
       <c r="V31" t="s">
-        <v>744</v>
+        <v>746</v>
       </c>
     </row>
     <row r="32" spans="16:22">
@@ -56213,13 +56333,13 @@
         <v>4040</v>
       </c>
       <c r="Q32" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
       <c r="U32">
         <v>5110</v>
       </c>
       <c r="V32" t="s">
-        <v>746</v>
+        <v>748</v>
       </c>
     </row>
     <row r="33" spans="16:22">
@@ -56227,13 +56347,13 @@
         <v>4041</v>
       </c>
       <c r="Q33" t="s">
-        <v>747</v>
+        <v>749</v>
       </c>
       <c r="U33">
         <v>5120</v>
       </c>
       <c r="V33" t="s">
-        <v>748</v>
+        <v>750</v>
       </c>
     </row>
     <row r="34" spans="16:22">
@@ -56241,13 +56361,13 @@
         <v>5010</v>
       </c>
       <c r="Q34" t="s">
-        <v>749</v>
+        <v>751</v>
       </c>
       <c r="U34">
         <v>5130</v>
       </c>
       <c r="V34" t="s">
-        <v>750</v>
+        <v>752</v>
       </c>
     </row>
     <row r="35" spans="16:22">
@@ -56255,13 +56375,13 @@
         <v>5011</v>
       </c>
       <c r="Q35" t="s">
-        <v>751</v>
+        <v>753</v>
       </c>
       <c r="U35">
         <v>5140</v>
       </c>
       <c r="V35" t="s">
-        <v>752</v>
+        <v>754</v>
       </c>
     </row>
     <row r="36" spans="16:22">
@@ -56269,13 +56389,13 @@
         <v>5012</v>
       </c>
       <c r="Q36" t="s">
-        <v>753</v>
+        <v>755</v>
       </c>
       <c r="U36">
         <v>5150</v>
       </c>
       <c r="V36" t="s">
-        <v>754</v>
+        <v>756</v>
       </c>
     </row>
     <row r="37" spans="16:22">
@@ -56283,13 +56403,13 @@
         <v>5020</v>
       </c>
       <c r="Q37" t="s">
-        <v>755</v>
+        <v>757</v>
       </c>
       <c r="U37">
         <v>6010</v>
       </c>
       <c r="V37" t="s">
-        <v>756</v>
+        <v>758</v>
       </c>
     </row>
     <row r="38" spans="16:22">
@@ -56297,13 +56417,13 @@
         <v>5030</v>
       </c>
       <c r="Q38" t="s">
-        <v>757</v>
+        <v>759</v>
       </c>
       <c r="U38">
         <v>6020</v>
       </c>
       <c r="V38" t="s">
-        <v>758</v>
+        <v>760</v>
       </c>
     </row>
     <row r="39" spans="16:22">
@@ -56311,13 +56431,13 @@
         <v>5040</v>
       </c>
       <c r="Q39" t="s">
-        <v>759</v>
+        <v>761</v>
       </c>
       <c r="U39">
         <v>6030</v>
       </c>
       <c r="V39" t="s">
-        <v>760</v>
+        <v>762</v>
       </c>
     </row>
     <row r="40" spans="16:22">
@@ -56325,13 +56445,13 @@
         <v>5050</v>
       </c>
       <c r="Q40" t="s">
-        <v>761</v>
+        <v>763</v>
       </c>
       <c r="U40">
         <v>6040</v>
       </c>
       <c r="V40" t="s">
-        <v>762</v>
+        <v>764</v>
       </c>
     </row>
     <row r="41" spans="16:22">
@@ -56339,13 +56459,13 @@
         <v>6010</v>
       </c>
       <c r="Q41" t="s">
-        <v>763</v>
+        <v>765</v>
       </c>
       <c r="U41">
         <v>6050</v>
       </c>
       <c r="V41" t="s">
-        <v>764</v>
+        <v>766</v>
       </c>
     </row>
     <row r="42" spans="16:22">
@@ -56353,13 +56473,13 @@
         <v>6020</v>
       </c>
       <c r="Q42" t="s">
-        <v>765</v>
+        <v>767</v>
       </c>
       <c r="U42">
         <v>6060</v>
       </c>
       <c r="V42" t="s">
-        <v>766</v>
+        <v>768</v>
       </c>
     </row>
     <row r="43" spans="16:22">
@@ -56367,13 +56487,13 @@
         <v>6030</v>
       </c>
       <c r="Q43" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="U43">
         <v>6110</v>
       </c>
       <c r="V43" t="s">
-        <v>768</v>
+        <v>770</v>
       </c>
     </row>
     <row r="44" spans="16:22">
@@ -56381,13 +56501,13 @@
         <v>6040</v>
       </c>
       <c r="Q44" t="s">
-        <v>769</v>
+        <v>771</v>
       </c>
       <c r="U44">
         <v>6120</v>
       </c>
       <c r="V44" t="s">
-        <v>770</v>
+        <v>772</v>
       </c>
     </row>
     <row r="45" spans="16:22">
@@ -56395,13 +56515,13 @@
         <v>6050</v>
       </c>
       <c r="Q45" t="s">
-        <v>771</v>
+        <v>773</v>
       </c>
       <c r="U45">
         <v>6130</v>
       </c>
       <c r="V45" t="s">
-        <v>772</v>
+        <v>774</v>
       </c>
     </row>
     <row r="46" spans="16:22">
@@ -56409,13 +56529,13 @@
         <v>6060</v>
       </c>
       <c r="Q46" t="s">
-        <v>773</v>
+        <v>775</v>
       </c>
       <c r="U46">
         <v>6140</v>
       </c>
       <c r="V46" t="s">
-        <v>774</v>
+        <v>776</v>
       </c>
     </row>
     <row r="47" spans="16:22">
@@ -56423,13 +56543,13 @@
         <v>6070</v>
       </c>
       <c r="Q47" t="s">
-        <v>775</v>
+        <v>777</v>
       </c>
       <c r="U47">
         <v>6150</v>
       </c>
       <c r="V47" t="s">
-        <v>776</v>
+        <v>778</v>
       </c>
     </row>
     <row r="48" spans="16:22">
@@ -56437,13 +56557,13 @@
         <v>6080</v>
       </c>
       <c r="Q48" t="s">
-        <v>777</v>
+        <v>779</v>
       </c>
       <c r="U48">
         <v>6210</v>
       </c>
       <c r="V48" t="s">
-        <v>778</v>
+        <v>780</v>
       </c>
     </row>
     <row r="49" spans="16:22">
@@ -56451,13 +56571,13 @@
         <v>6100</v>
       </c>
       <c r="Q49" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="U49">
         <v>6220</v>
       </c>
       <c r="V49" t="s">
-        <v>780</v>
+        <v>782</v>
       </c>
     </row>
     <row r="50" spans="16:22">
@@ -56465,13 +56585,13 @@
         <v>6210</v>
       </c>
       <c r="Q50" t="s">
-        <v>781</v>
+        <v>783</v>
       </c>
       <c r="U50">
         <v>6230</v>
       </c>
       <c r="V50" t="s">
-        <v>782</v>
+        <v>784</v>
       </c>
     </row>
     <row r="51" spans="16:22">
@@ -56479,13 +56599,13 @@
         <v>6310</v>
       </c>
       <c r="Q51" t="s">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="U51">
         <v>6240</v>
       </c>
       <c r="V51" t="s">
-        <v>784</v>
+        <v>786</v>
       </c>
     </row>
     <row r="52" spans="16:22">
@@ -56493,13 +56613,13 @@
         <v>7010</v>
       </c>
       <c r="Q52" t="s">
-        <v>785</v>
+        <v>787</v>
       </c>
       <c r="U52">
         <v>6250</v>
       </c>
       <c r="V52" t="s">
-        <v>786</v>
+        <v>788</v>
       </c>
     </row>
     <row r="53" spans="16:22">
@@ -56507,13 +56627,13 @@
         <v>7020</v>
       </c>
       <c r="Q53" t="s">
-        <v>787</v>
+        <v>789</v>
       </c>
       <c r="U53">
         <v>6310</v>
       </c>
       <c r="V53" t="s">
-        <v>788</v>
+        <v>790</v>
       </c>
     </row>
     <row r="54" spans="16:22">
@@ -56521,13 +56641,13 @@
         <v>7030</v>
       </c>
       <c r="Q54" t="s">
-        <v>789</v>
+        <v>791</v>
       </c>
       <c r="U54">
         <v>6320</v>
       </c>
       <c r="V54" t="s">
-        <v>790</v>
+        <v>792</v>
       </c>
     </row>
     <row r="55" spans="16:22">
@@ -56535,13 +56655,13 @@
         <v>8010</v>
       </c>
       <c r="Q55" t="s">
-        <v>791</v>
+        <v>793</v>
       </c>
       <c r="U55">
         <v>6330</v>
       </c>
       <c r="V55" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
     </row>
     <row r="56" spans="16:22">
@@ -56549,13 +56669,13 @@
         <v>8020</v>
       </c>
       <c r="Q56" t="s">
-        <v>793</v>
+        <v>795</v>
       </c>
       <c r="U56">
         <v>6340</v>
       </c>
       <c r="V56" t="s">
-        <v>794</v>
+        <v>796</v>
       </c>
     </row>
     <row r="57" spans="16:22">
@@ -56563,13 +56683,13 @@
         <v>9010</v>
       </c>
       <c r="Q57" t="s">
-        <v>795</v>
+        <v>797</v>
       </c>
       <c r="U57">
         <v>6350</v>
       </c>
       <c r="V57" t="s">
-        <v>796</v>
+        <v>798</v>
       </c>
     </row>
     <row r="58" spans="16:22">
@@ -56577,13 +56697,13 @@
         <v>10010</v>
       </c>
       <c r="Q58" t="s">
-        <v>797</v>
+        <v>799</v>
       </c>
       <c r="U58">
         <v>7010</v>
       </c>
       <c r="V58" t="s">
-        <v>798</v>
+        <v>800</v>
       </c>
     </row>
     <row r="59" spans="16:22">
@@ -56591,13 +56711,13 @@
         <v>10020</v>
       </c>
       <c r="Q59" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="U59">
         <v>7020</v>
       </c>
       <c r="V59" t="s">
-        <v>800</v>
+        <v>802</v>
       </c>
     </row>
     <row r="60" spans="16:22">
@@ -56605,13 +56725,13 @@
         <v>11010</v>
       </c>
       <c r="Q60" t="s">
-        <v>801</v>
+        <v>803</v>
       </c>
       <c r="U60">
         <v>7030</v>
       </c>
       <c r="V60" t="s">
-        <v>802</v>
+        <v>804</v>
       </c>
     </row>
     <row r="61" spans="16:22">
@@ -56619,13 +56739,13 @@
         <v>12010</v>
       </c>
       <c r="Q61" t="s">
-        <v>803</v>
+        <v>805</v>
       </c>
       <c r="U61">
         <v>7040</v>
       </c>
       <c r="V61" t="s">
-        <v>804</v>
+        <v>806</v>
       </c>
     </row>
     <row r="62" spans="16:22">
@@ -56633,13 +56753,13 @@
         <v>13010</v>
       </c>
       <c r="Q62" t="s">
-        <v>805</v>
+        <v>807</v>
       </c>
       <c r="U62">
         <v>7050</v>
       </c>
       <c r="V62" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
     </row>
     <row r="63" spans="16:22">
@@ -56647,13 +56767,13 @@
         <v>14010</v>
       </c>
       <c r="Q63" t="s">
-        <v>807</v>
+        <v>809</v>
       </c>
       <c r="U63">
         <v>7060</v>
       </c>
       <c r="V63" t="s">
-        <v>808</v>
+        <v>810</v>
       </c>
     </row>
     <row r="64" spans="16:22">
@@ -56661,13 +56781,13 @@
         <v>40010</v>
       </c>
       <c r="Q64" t="s">
-        <v>809</v>
+        <v>811</v>
       </c>
       <c r="U64">
         <v>7070</v>
       </c>
       <c r="V64" t="s">
-        <v>810</v>
+        <v>812</v>
       </c>
     </row>
     <row r="65" spans="16:22">
@@ -56675,13 +56795,13 @@
         <v>40020</v>
       </c>
       <c r="Q65" t="s">
-        <v>811</v>
+        <v>813</v>
       </c>
       <c r="U65">
         <v>8010</v>
       </c>
       <c r="V65" t="s">
-        <v>812</v>
+        <v>814</v>
       </c>
     </row>
     <row r="66" spans="16:22">
@@ -56689,13 +56809,13 @@
         <v>40030</v>
       </c>
       <c r="Q66" t="s">
-        <v>813</v>
+        <v>815</v>
       </c>
       <c r="U66">
         <v>8020</v>
       </c>
       <c r="V66" t="s">
-        <v>814</v>
+        <v>816</v>
       </c>
     </row>
     <row r="67" spans="16:22">
@@ -56703,13 +56823,13 @@
         <v>40040</v>
       </c>
       <c r="Q67" t="s">
-        <v>815</v>
+        <v>817</v>
       </c>
       <c r="U67">
         <v>8030</v>
       </c>
       <c r="V67" t="s">
-        <v>816</v>
+        <v>818</v>
       </c>
     </row>
     <row r="68" spans="16:22">
@@ -56717,13 +56837,13 @@
         <v>40050</v>
       </c>
       <c r="Q68" t="s">
-        <v>817</v>
+        <v>819</v>
       </c>
       <c r="U68">
         <v>8040</v>
       </c>
       <c r="V68" t="s">
-        <v>818</v>
+        <v>820</v>
       </c>
     </row>
     <row r="69" spans="16:22">
@@ -56731,13 +56851,13 @@
         <v>40060</v>
       </c>
       <c r="Q69" t="s">
-        <v>819</v>
+        <v>821</v>
       </c>
       <c r="U69">
         <v>8050</v>
       </c>
       <c r="V69" t="s">
-        <v>820</v>
+        <v>822</v>
       </c>
     </row>
     <row r="70" spans="16:22">
@@ -56745,13 +56865,13 @@
         <v>40070</v>
       </c>
       <c r="Q70" t="s">
-        <v>821</v>
+        <v>823</v>
       </c>
       <c r="U70">
         <v>8060</v>
       </c>
       <c r="V70" t="s">
-        <v>822</v>
+        <v>824</v>
       </c>
     </row>
     <row r="71" spans="16:22">
@@ -56759,13 +56879,13 @@
         <v>40080</v>
       </c>
       <c r="Q71" t="s">
-        <v>823</v>
+        <v>825</v>
       </c>
       <c r="U71">
         <v>9010</v>
       </c>
       <c r="V71" t="s">
-        <v>824</v>
+        <v>826</v>
       </c>
     </row>
     <row r="72" spans="21:22">
@@ -56773,7 +56893,7 @@
         <v>9020</v>
       </c>
       <c r="V72" t="s">
-        <v>825</v>
+        <v>827</v>
       </c>
     </row>
     <row r="73" spans="21:22">
@@ -56781,7 +56901,7 @@
         <v>9030</v>
       </c>
       <c r="V73" t="s">
-        <v>826</v>
+        <v>828</v>
       </c>
     </row>
     <row r="74" spans="21:22">
@@ -56789,7 +56909,7 @@
         <v>9031</v>
       </c>
       <c r="V74" t="s">
-        <v>827</v>
+        <v>829</v>
       </c>
     </row>
     <row r="75" spans="21:22">
@@ -56797,7 +56917,7 @@
         <v>9040</v>
       </c>
       <c r="V75" t="s">
-        <v>828</v>
+        <v>830</v>
       </c>
     </row>
     <row r="76" spans="21:22">
@@ -56805,7 +56925,7 @@
         <v>9110</v>
       </c>
       <c r="V76" t="s">
-        <v>829</v>
+        <v>831</v>
       </c>
     </row>
     <row r="77" spans="21:22">
@@ -56813,7 +56933,7 @@
         <v>9120</v>
       </c>
       <c r="V77" t="s">
-        <v>830</v>
+        <v>832</v>
       </c>
     </row>
     <row r="78" spans="21:22">
@@ -56821,7 +56941,7 @@
         <v>10010</v>
       </c>
       <c r="V78" t="s">
-        <v>831</v>
+        <v>833</v>
       </c>
     </row>
     <row r="79" spans="21:22">
@@ -56829,7 +56949,7 @@
         <v>10020</v>
       </c>
       <c r="V79" t="s">
-        <v>832</v>
+        <v>834</v>
       </c>
     </row>
     <row r="80" spans="21:22">
@@ -56837,7 +56957,7 @@
         <v>10030</v>
       </c>
       <c r="V80" t="s">
-        <v>833</v>
+        <v>835</v>
       </c>
     </row>
     <row r="81" spans="21:22">
@@ -56845,7 +56965,7 @@
         <v>10110</v>
       </c>
       <c r="V81" t="s">
-        <v>834</v>
+        <v>836</v>
       </c>
     </row>
     <row r="82" spans="21:22">
@@ -56853,7 +56973,7 @@
         <v>10120</v>
       </c>
       <c r="V82" t="s">
-        <v>835</v>
+        <v>837</v>
       </c>
     </row>
     <row r="83" spans="21:22">
@@ -56861,7 +56981,7 @@
         <v>10130</v>
       </c>
       <c r="V83" t="s">
-        <v>836</v>
+        <v>838</v>
       </c>
     </row>
     <row r="84" spans="21:22">
@@ -56869,7 +56989,7 @@
         <v>11010</v>
       </c>
       <c r="V84" t="s">
-        <v>837</v>
+        <v>839</v>
       </c>
     </row>
     <row r="85" spans="21:22">
@@ -56877,7 +56997,7 @@
         <v>11011</v>
       </c>
       <c r="V85" t="s">
-        <v>838</v>
+        <v>840</v>
       </c>
     </row>
     <row r="86" spans="21:22">
@@ -56885,7 +57005,7 @@
         <v>11020</v>
       </c>
       <c r="V86" t="s">
-        <v>839</v>
+        <v>841</v>
       </c>
     </row>
     <row r="87" spans="21:22">
@@ -56893,7 +57013,7 @@
         <v>12010</v>
       </c>
       <c r="V87" t="s">
-        <v>840</v>
+        <v>842</v>
       </c>
     </row>
     <row r="88" spans="21:22">
@@ -56901,7 +57021,7 @@
         <v>12011</v>
       </c>
       <c r="V88" t="s">
-        <v>841</v>
+        <v>843</v>
       </c>
     </row>
     <row r="89" spans="21:22">
@@ -56909,7 +57029,7 @@
         <v>12030</v>
       </c>
       <c r="V89" t="s">
-        <v>842</v>
+        <v>844</v>
       </c>
     </row>
     <row r="90" spans="21:22">
@@ -56917,7 +57037,7 @@
         <v>12040</v>
       </c>
       <c r="V90" t="s">
-        <v>843</v>
+        <v>845</v>
       </c>
     </row>
     <row r="91" spans="21:22">
@@ -56925,7 +57045,7 @@
         <v>12041</v>
       </c>
       <c r="V91" t="s">
-        <v>844</v>
+        <v>846</v>
       </c>
     </row>
     <row r="92" spans="21:22">
@@ -56933,7 +57053,7 @@
         <v>12042</v>
       </c>
       <c r="V92" t="s">
-        <v>845</v>
+        <v>847</v>
       </c>
     </row>
     <row r="93" spans="21:22">
@@ -56941,7 +57061,7 @@
         <v>12043</v>
       </c>
       <c r="V93" t="s">
-        <v>846</v>
+        <v>848</v>
       </c>
     </row>
     <row r="94" spans="21:22">
@@ -56949,7 +57069,7 @@
         <v>12050</v>
       </c>
       <c r="V94" t="s">
-        <v>847</v>
+        <v>849</v>
       </c>
     </row>
     <row r="95" spans="21:22">
@@ -56957,7 +57077,7 @@
         <v>12060</v>
       </c>
       <c r="V95" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
     </row>
     <row r="96" spans="21:22">
@@ -56965,7 +57085,7 @@
         <v>12063</v>
       </c>
       <c r="V96" t="s">
-        <v>849</v>
+        <v>851</v>
       </c>
     </row>
     <row r="97" spans="21:22">
@@ -56973,7 +57093,7 @@
         <v>12064</v>
       </c>
       <c r="V97" t="s">
-        <v>850</v>
+        <v>852</v>
       </c>
     </row>
     <row r="98" spans="21:22">
@@ -56981,7 +57101,7 @@
         <v>12066</v>
       </c>
       <c r="V98" t="s">
-        <v>851</v>
+        <v>853</v>
       </c>
     </row>
     <row r="99" spans="21:22">
@@ -56989,7 +57109,7 @@
         <v>12067</v>
       </c>
       <c r="V99" t="s">
-        <v>852</v>
+        <v>854</v>
       </c>
     </row>
     <row r="100" spans="21:22">
@@ -56997,7 +57117,7 @@
         <v>12070</v>
       </c>
       <c r="V100" t="s">
-        <v>853</v>
+        <v>855</v>
       </c>
     </row>
     <row r="101" spans="21:22">
@@ -57005,7 +57125,7 @@
         <v>12071</v>
       </c>
       <c r="V101" t="s">
-        <v>854</v>
+        <v>856</v>
       </c>
     </row>
     <row r="102" spans="21:22">
@@ -57013,7 +57133,7 @@
         <v>12072</v>
       </c>
       <c r="V102" t="s">
-        <v>855</v>
+        <v>857</v>
       </c>
     </row>
     <row r="103" spans="21:22">
@@ -57021,7 +57141,7 @@
         <v>12082</v>
       </c>
       <c r="V103" t="s">
-        <v>856</v>
+        <v>858</v>
       </c>
     </row>
     <row r="104" spans="21:22">
@@ -57029,7 +57149,7 @@
         <v>12092</v>
       </c>
       <c r="V104" t="s">
-        <v>857</v>
+        <v>859</v>
       </c>
     </row>
     <row r="105" spans="21:22">
@@ -57037,7 +57157,7 @@
         <v>12110</v>
       </c>
       <c r="V105" t="s">
-        <v>858</v>
+        <v>860</v>
       </c>
     </row>
     <row r="106" spans="21:22">
@@ -57045,7 +57165,7 @@
         <v>13010</v>
       </c>
       <c r="V106" t="s">
-        <v>859</v>
+        <v>861</v>
       </c>
     </row>
     <row r="107" spans="21:22">
@@ -57053,7 +57173,7 @@
         <v>13020</v>
       </c>
       <c r="V107" t="s">
-        <v>860</v>
+        <v>862</v>
       </c>
     </row>
     <row r="108" spans="21:22">
@@ -57061,7 +57181,7 @@
         <v>14010</v>
       </c>
       <c r="V108" t="s">
-        <v>861</v>
+        <v>863</v>
       </c>
     </row>
     <row r="109" spans="21:22">
@@ -57069,7 +57189,7 @@
         <v>14110</v>
       </c>
       <c r="V109" t="s">
-        <v>862</v>
+        <v>864</v>
       </c>
     </row>
     <row r="110" spans="21:22">
@@ -57077,7 +57197,7 @@
         <v>14210</v>
       </c>
       <c r="V110" t="s">
-        <v>863</v>
+        <v>865</v>
       </c>
     </row>
     <row r="111" spans="21:22">
@@ -57085,7 +57205,7 @@
         <v>14310</v>
       </c>
       <c r="V111" t="s">
-        <v>864</v>
+        <v>866</v>
       </c>
     </row>
     <row r="112" spans="21:22">
@@ -57093,7 +57213,7 @@
         <v>14410</v>
       </c>
       <c r="V112" t="s">
-        <v>865</v>
+        <v>867</v>
       </c>
     </row>
     <row r="113" spans="21:22">
@@ -57101,7 +57221,7 @@
         <v>14420</v>
       </c>
       <c r="V113" t="s">
-        <v>866</v>
+        <v>868</v>
       </c>
     </row>
     <row r="114" spans="21:22">
@@ -57109,7 +57229,7 @@
         <v>14520</v>
       </c>
       <c r="V114" t="s">
-        <v>867</v>
+        <v>869</v>
       </c>
     </row>
     <row r="115" spans="21:22">
@@ -57117,7 +57237,7 @@
         <v>15010</v>
       </c>
       <c r="V115" t="s">
-        <v>868</v>
+        <v>870</v>
       </c>
     </row>
     <row r="116" spans="21:22">
@@ -57125,7 +57245,7 @@
         <v>15011</v>
       </c>
       <c r="V116" t="s">
-        <v>869</v>
+        <v>871</v>
       </c>
     </row>
     <row r="117" spans="21:22">
@@ -57133,7 +57253,7 @@
         <v>15022</v>
       </c>
       <c r="V117" t="s">
-        <v>870</v>
+        <v>872</v>
       </c>
     </row>
     <row r="118" spans="21:22">
@@ -57141,7 +57261,7 @@
         <v>16010</v>
       </c>
       <c r="V118" t="s">
-        <v>871</v>
+        <v>873</v>
       </c>
     </row>
     <row r="119" spans="21:22">
@@ -57149,7 +57269,7 @@
         <v>16020</v>
       </c>
       <c r="V119" t="s">
-        <v>872</v>
+        <v>874</v>
       </c>
     </row>
     <row r="120" spans="21:22">
@@ -57157,7 +57277,7 @@
         <v>17010</v>
       </c>
       <c r="V120" t="s">
-        <v>873</v>
+        <v>875</v>
       </c>
     </row>
     <row r="121" spans="21:22">
@@ -57165,7 +57285,7 @@
         <v>17020</v>
       </c>
       <c r="V121" t="s">
-        <v>874</v>
+        <v>876</v>
       </c>
     </row>
     <row r="122" spans="21:22">
@@ -57173,7 +57293,7 @@
         <v>17030</v>
       </c>
       <c r="V122" t="s">
-        <v>875</v>
+        <v>877</v>
       </c>
     </row>
     <row r="123" spans="21:22">
@@ -57181,7 +57301,7 @@
         <v>17040</v>
       </c>
       <c r="V123" t="s">
-        <v>876</v>
+        <v>878</v>
       </c>
     </row>
     <row r="124" spans="21:22">
@@ -57189,7 +57309,7 @@
         <v>17050</v>
       </c>
       <c r="V124" t="s">
-        <v>877</v>
+        <v>879</v>
       </c>
     </row>
     <row r="125" spans="21:22">
@@ -57197,7 +57317,7 @@
         <v>17060</v>
       </c>
       <c r="V125" t="s">
-        <v>878</v>
+        <v>880</v>
       </c>
     </row>
     <row r="126" spans="21:22">
@@ -57205,7 +57325,7 @@
         <v>18010</v>
       </c>
       <c r="V126" t="s">
-        <v>879</v>
+        <v>881</v>
       </c>
     </row>
     <row r="127" spans="21:22">
@@ -57213,7 +57333,7 @@
         <v>18020</v>
       </c>
       <c r="V127" t="s">
-        <v>880</v>
+        <v>882</v>
       </c>
     </row>
     <row r="128" spans="21:22">
@@ -57221,7 +57341,7 @@
         <v>19010</v>
       </c>
       <c r="V128" t="s">
-        <v>881</v>
+        <v>883</v>
       </c>
     </row>
     <row r="129" spans="21:22">
@@ -57229,7 +57349,7 @@
         <v>19020</v>
       </c>
       <c r="V129" t="s">
-        <v>882</v>
+        <v>884</v>
       </c>
     </row>
     <row r="130" spans="21:22">
@@ -57237,7 +57357,7 @@
         <v>19030</v>
       </c>
       <c r="V130" t="s">
-        <v>883</v>
+        <v>885</v>
       </c>
     </row>
     <row r="131" spans="21:22">
@@ -57245,7 +57365,7 @@
         <v>20030</v>
       </c>
       <c r="V131" t="s">
-        <v>858</v>
+        <v>860</v>
       </c>
     </row>
     <row r="132" spans="21:22">
@@ -57253,7 +57373,7 @@
         <v>20040</v>
       </c>
       <c r="V132" t="s">
-        <v>884</v>
+        <v>886</v>
       </c>
     </row>
     <row r="133" spans="21:22">
@@ -57261,7 +57381,7 @@
         <v>20050</v>
       </c>
       <c r="V133" t="s">
-        <v>885</v>
+        <v>887</v>
       </c>
     </row>
     <row r="134" spans="21:22">
@@ -57269,7 +57389,7 @@
         <v>20070</v>
       </c>
       <c r="V134" t="s">
-        <v>886</v>
+        <v>888</v>
       </c>
     </row>
     <row r="135" spans="21:22">
@@ -57277,7 +57397,7 @@
         <v>20071</v>
       </c>
       <c r="V135" t="s">
-        <v>887</v>
+        <v>889</v>
       </c>
     </row>
     <row r="136" spans="21:22">
@@ -57285,7 +57405,7 @@
         <v>20110</v>
       </c>
       <c r="V136" t="s">
-        <v>888</v>
+        <v>890</v>
       </c>
     </row>
     <row r="137" spans="21:22">
@@ -57293,7 +57413,7 @@
         <v>20120</v>
       </c>
       <c r="V137" t="s">
-        <v>889</v>
+        <v>891</v>
       </c>
     </row>
     <row r="138" spans="21:22">
@@ -57301,7 +57421,7 @@
         <v>20130</v>
       </c>
       <c r="V138" t="s">
-        <v>890</v>
+        <v>892</v>
       </c>
     </row>
     <row r="139" spans="21:22">
@@ -57309,7 +57429,7 @@
         <v>20140</v>
       </c>
       <c r="V139" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
     </row>
     <row r="140" spans="21:22">
@@ -57317,7 +57437,7 @@
         <v>20150</v>
       </c>
       <c r="V140" t="s">
-        <v>892</v>
+        <v>894</v>
       </c>
     </row>
     <row r="141" spans="21:22">
@@ -57325,7 +57445,7 @@
         <v>20160</v>
       </c>
       <c r="V141" t="s">
-        <v>893</v>
+        <v>895</v>
       </c>
     </row>
     <row r="142" spans="21:22">
@@ -57333,7 +57453,7 @@
         <v>23010</v>
       </c>
       <c r="V142" t="s">
-        <v>894</v>
+        <v>896</v>
       </c>
     </row>
     <row r="143" spans="21:22">
@@ -57341,7 +57461,7 @@
         <v>24010</v>
       </c>
       <c r="V143" t="s">
-        <v>895</v>
+        <v>897</v>
       </c>
     </row>
     <row r="144" spans="21:22">
@@ -57349,7 +57469,7 @@
         <v>30010</v>
       </c>
       <c r="V144" t="s">
-        <v>896</v>
+        <v>898</v>
       </c>
     </row>
     <row r="145" spans="21:22">
@@ -57357,7 +57477,7 @@
         <v>30020</v>
       </c>
       <c r="V145" t="s">
-        <v>897</v>
+        <v>899</v>
       </c>
     </row>
     <row r="146" spans="21:22">
@@ -57365,7 +57485,7 @@
         <v>40010</v>
       </c>
       <c r="V146" t="s">
-        <v>898</v>
+        <v>900</v>
       </c>
     </row>
     <row r="147" spans="21:22">
@@ -57373,7 +57493,7 @@
         <v>40020</v>
       </c>
       <c r="V147" t="s">
-        <v>899</v>
+        <v>901</v>
       </c>
     </row>
     <row r="148" spans="21:22">
@@ -57381,7 +57501,7 @@
         <v>40030</v>
       </c>
       <c r="V148" t="s">
-        <v>900</v>
+        <v>902</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Data/Skills.xlsx
+++ b/Assets/Data/Skills.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="18650" windowHeight="8390"/>
+    <workbookView windowWidth="18650" windowHeight="8390" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="Skills" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1152" uniqueCount="903">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1155" uniqueCount="906">
   <si>
     <t>Id</t>
   </si>
@@ -2091,6 +2091,13 @@
     <t>\sの獲得EXPが/f[f,0,1]%アップ</t>
   </si>
   <si>
+    <t>ATK⇔DEF交換</t>
+  </si>
+  <si>
+    <t>\sのATKとDEF値を交換する
+同系統複数装備不可</t>
+  </si>
+  <si>
     <t>Scope</t>
   </si>
   <si>
@@ -2703,52 +2710,55 @@
     <t>神化発動後の敵</t>
   </si>
   <si>
+    <t>Param1とParam2のステータス値を交換する</t>
+  </si>
+  <si>
+    <t>神化魔法使用回数の総計</t>
+  </si>
+  <si>
     <t>アイテム入手</t>
   </si>
   <si>
-    <t>神化魔法使用回数の総計</t>
+    <t>味方より敵が多い</t>
   </si>
   <si>
     <t>獲得Eｘｐ％アップ</t>
   </si>
   <si>
-    <t>味方より敵が多い</t>
+    <t>味方より敵が少ない</t>
   </si>
   <si>
     <t>Eｘｐ入手</t>
   </si>
   <si>
-    <t>味方より敵が少ない</t>
+    <t>味方の数が〇以上</t>
   </si>
   <si>
     <t>Nu入手</t>
   </si>
   <si>
-    <t>味方の数が〇以上</t>
+    <t>味方の数が〇以下</t>
   </si>
   <si>
     <t>属性適正アップ</t>
   </si>
   <si>
-    <t>味方の数が〇以下</t>
+    <t>敵の数が〇以上</t>
   </si>
   <si>
     <t>ステージ探索猶予アップ</t>
   </si>
   <si>
-    <t>敵の数が〇以上</t>
+    <t>敵の数が〇以下</t>
   </si>
   <si>
     <t>取引レートダウン</t>
   </si>
   <si>
-    <t>敵の数が〇以下</t>
+    <t>ターン数が〇以内</t>
   </si>
   <si>
     <t>ダンジョンから離れる時にPeriodが進まない</t>
-  </si>
-  <si>
-    <t>ターン数が〇以内</t>
   </si>
   <si>
     <t>ターン数が〇</t>
@@ -2984,10 +2994,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -3006,6 +3016,67 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
@@ -3019,6 +3090,30 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -3026,16 +3121,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <u/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -3049,51 +3137,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="18"/>
       <color theme="3"/>
@@ -3102,48 +3145,15 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -3170,7 +3180,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3182,7 +3228,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3194,7 +3276,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3206,37 +3336,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3248,31 +3348,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3284,73 +3360,7 @